--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -1401,7 +1401,7 @@
     <t xml:space="preserve">Georges BERKELEY</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley"    title=" Wikipedia"&gt;Georges BERKELEY&lt;/a&gt; était un philosophe, évêque anglican et scientifique anglo-irlandais, célèbre pour sa philosophie empiriste et idéaliste, souvent résumée par la formule latine &lt;a href="https://www.youtube.com/watch?v=gcyFtJ1ZtrA" style="color:#88A1E9" title=" Berkeley Être c'est être perçu ou percevoir par Coursitout"&gt;"Esse est percipi"&lt;/a&gt; (être, c'est être perçu).&lt;/p&gt; &lt;p&gt;L'Idéalisme  &lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Immatérialisme  par Wikipedia"&gt; immatérialiste&lt;/a&gt; est le cœur de sa philosophie. Il soutenait que la réalité ne consiste qu'en esprits et leurs idées. Pour lui, les objets physiques n'existent pas indépendamment d'être perçus. Quand nous ne percevons pas un objet, il continue d'exister parce que Dieu le perçoit constamment et il croit que toute connaissance provient de l'expérience sensorielle. Cependant, il pousse l'empirisme à sa conclusion logique en niant l'existence d'une "substance matérielle" indépendante des perceptions. Il affirme que toutes les qualités sont des perceptions. Il n'y a pas de matière "derrière" les qualités perçues.&lt;/p&gt; &lt;p&gt;Ses trois oeuvres principales sont "Essai sur une nouvelle théorie de la vision sortie en 1709,  &lt;a href="https://www.youtube.com/watch?v=wBivRdgKgd0"  title=" Berkeley pour les nuls  par Alexis Vildier"&gt;"Traité des principes de la connaissance humaine"&lt;/a&gt; en 1710 et "Trois dialogues entre Hylas et Philonous en 1713. Sa  pensée, bien que souvent considérée comme contre-intuitive, est très cohérente et a marqué l'histoire de la philosophie par son radicalisme et sa remise en question des conceptions traditionnelles de la réalité. &lt;/p&gt; 
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley"    title=" Wikipedia"&gt;Georges BERKELEY&lt;/a&gt; était un philosophe, évêque anglican et scientifique anglo-irlandais, célèbre pour sa philosophie empiriste et idéaliste, souvent résumée par la formule latine &lt;a href="https://www.youtube.com/watch?v=gcyFtJ1ZtrA"  title=" Berkeley Être c'est être perçu ou percevoir par Coursitout"&gt;"Esse est percipi"&lt;/a&gt; (être, c'est être perçu).&lt;/p&gt; &lt;p&gt;L'Idéalisme  &lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Immatérialisme  par Wikipedia"&gt; immatérialiste&lt;/a&gt; est le cœur de sa philosophie. Il soutenait que la réalité ne consiste qu'en esprits et leurs idées. Pour lui, les objets physiques n'existent pas indépendamment d'être perçus. Quand nous ne percevons pas un objet, il continue d'exister parce que Dieu le perçoit constamment et il croit que toute connaissance provient de l'expérience sensorielle. Cependant, il pousse l'empirisme à sa conclusion logique en niant l'existence d'une "substance matérielle" indépendante des perceptions. Il affirme que toutes les qualités sont des perceptions. Il n'y a pas de matière "derrière" les qualités perçues.&lt;/p&gt; &lt;p&gt;Ses trois oeuvres principales sont "Essai sur une nouvelle théorie de la vision sortie en 1709,  &lt;a href="https://www.youtube.com/watch?v=wBivRdgKgd0"  title=" Berkeley pour les nuls  par Alexis Vildier"&gt;"Traité des principes de la connaissance humaine"&lt;/a&gt; en 1710 et "Trois dialogues entre Hylas et Philonous en 1713. Sa  pensée, bien que souvent considérée comme contre-intuitive, est très cohérente et a marqué l'histoire de la philosophie par son radicalisme et sa remise en question des conceptions traditionnelles de la réalité. &lt;/p&gt; 
 </t>
   </si>
   <si>
@@ -1414,7 +1414,7 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/berkeley-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">Immatérialisme</t>
+    <t xml:space="preserve">Immatérialisme ; Phénoménisme</t>
   </si>
   <si>
     <t xml:space="preserve">philosophe et évêque irlandais célèbre pour sa philosophie empiriste et idéaliste.</t>
@@ -4860,7 +4860,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="164.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="n">
         <v>1685</v>
       </c>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -1902,7 +1902,7 @@
     <t xml:space="preserve">https://www.laphilo.fr/pho/kant-mini.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">Criticisme ; Agnosticisme ; Anthropocentrisme</t>
+    <t xml:space="preserve">Criticisme ; Agnosticisme ; Anthropocentrisme ; Constructivisme</t>
   </si>
   <si>
     <t xml:space="preserve">philosophe allemand qui a développé une théorie appelé 'l'éthique Kantienne'.</t>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -4755,12 +4755,12 @@
       </c>
       <c r="D67" s="48" t="inlineStr">
         <is>
-          <t>Immanuel KANT</t>
+          <t>Emmanuel KANT</t>
         </is>
       </c>
       <c r="E67" s="58" t="inlineStr">
         <is>
-          <t>&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant"  title=" Wikipedia"&gt; Immanuel KANT&lt;/a&gt; était un philosophe &lt;a href="https://la-philosophie.com/philosophie-lumieres" style="color:#88A1E9"   title="La philosophie des Lumières par la-philosophie.com"&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant"  title="La philosophie pratique de Kant de l'encyclopédie Wikipédia"&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href="https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos"   title="C'est quoi la raison pure par Kosmos"&gt;"Critique de la raison pure"&lt;/a&gt; , publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href="https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos"  title="La loi morale par Kosmos"&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href="https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'impératif catégorique par le Précepteur"&gt;"Fondement de la métaphysique des moeurs"&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href="https://la-philosophie.com/espace-public-et-democratie"  title="Espace public par la-philosophie.com"&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les "Lumières" comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href="https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume"  title="Faculté de jugement par la-philosophie.com"&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title="Le monde: entre déterminisme et liberté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t>&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant"  title=" Wikipedia"&gt; Emmanuel KANT&lt;/a&gt; était un philosophe &lt;a href="https://la-philosophie.com/philosophie-lumieres" style="color:#88A1E9"   title="La philosophie des Lumières par la-philosophie.com"&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant"  title="La philosophie pratique de Kant de l'encyclopédie Wikipédia"&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href="https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos"   title="C'est quoi la raison pure par Kosmos"&gt;"Critique de la raison pure"&lt;/a&gt; , publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href="https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos"  title="La loi morale par Kosmos"&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href="https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'impératif catégorique par le Précepteur"&gt;"Fondement de la métaphysique des moeurs"&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href="https://la-philosophie.com/espace-public-et-democratie"  title="Espace public par la-philosophie.com"&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les "Lumières" comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href="https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume"  title="Faculté de jugement par la-philosophie.com"&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title="Le monde: entre déterminisme et liberté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F67" s="47" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="E77" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcus_Herz"  title=" Wikipedia"&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Immanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2" title="Kant, Lettre à Marcus Herz du 21 février 1772 par Persée"&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la "révolution copernicienne"), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent "Betrachtungen aus der spekulativen Weltweisheit"  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et "Versuch über den Geschmack" en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcus_Herz"  title=" Wikipedia"&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Emmanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2" title="Kant, Lettre à Marcus Herz du 21 février 1772 par Persée"&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la "révolution copernicienne"), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent "Betrachtungen aus der spekulativen Weltweisheit"  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et "Versuch über den Geschmack" en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F77" s="47" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -819,6 +819,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N3" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="137.25" customHeight="1" s="39">
       <c r="A4" s="47" t="n">
@@ -3055,6 +3060,11 @@
           <t>philosophe néerlandais qui prôna le Déterminisme par sa vision Rationaliste.</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="138" customHeight="1" s="39">
       <c r="A40" s="47" t="n">
@@ -4861,6 +4871,11 @@
           <t>philosophe juif allemand moderne &amp; figure de la Haskala.</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="127.5" customHeight="1" s="39">
       <c r="A69" s="47" t="n">
@@ -5415,6 +5430,11 @@
           <t>philosophe juif allemand, disciple de Kant &amp; figure des Lumières berlinoises.</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="178.5" customHeight="1" s="39">
       <c r="A78" s="47" t="n">
@@ -5532,6 +5552,11 @@
       <c r="M79" s="35" t="inlineStr">
         <is>
           <t>philosophe juif allemand plus connu comme pionnier de l'Haskalah.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -824,6 +824,16 @@
           <t xml:space="preserve">Traditions</t>
         </is>
       </c>
+      <c r="O3" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="P3" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importance</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="137.25" customHeight="1" s="39">
       <c r="A4" s="47" t="n">
@@ -888,6 +898,11 @@
           <t>philosophe italien qui voulut unifier les traditions religieuses et philosophiques.</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="126.75" customHeight="1" s="39">
       <c r="A5" s="47" t="n">
@@ -951,6 +966,11 @@
           <t>philosophe hollandais dit le prince des Humanistes.</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="144" customHeight="1" s="39">
       <c r="A6" s="47" t="n">
@@ -1012,6 +1032,14 @@
           <t>philosophe italien qui influença fortement l'art de gouverner.</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" ht="191.25" customFormat="1" customHeight="1" s="38">
       <c r="A7" s="51" t="n">
@@ -1069,6 +1097,11 @@
           <t>philosophe écossais élève et proche collaborateur de Jean Major.</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="165" customFormat="1" customHeight="1" s="38">
       <c r="A8" s="51" t="n">
@@ -1130,6 +1163,11 @@
           <t>philosophe et homme d'église anglais, principale figure de la renaissance.</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="175.5" customFormat="1" customHeight="1" s="38">
       <c r="A9" s="51" t="n">
@@ -1191,6 +1229,11 @@
           <t>philosophe français, auteur du premier ouvrage scientifique imprimé en français.</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="175.5" customFormat="1" customHeight="1" s="38">
       <c r="A10" s="51" t="n">
@@ -1247,6 +1290,11 @@
           <t>humaniste, théologien et théoricien de la musique allemand, adversaire de Martin Luther.</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="183.75" customFormat="1" customHeight="1" s="38">
       <c r="A11" s="51" t="n">
@@ -1306,6 +1354,11 @@
       <c r="M11" s="45" t="inlineStr">
         <is>
           <t>philosophe espagnol qui fut le premier à défendre les peuples indigènes.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1375,6 +1428,11 @@
           <t>philosophe et prêtre augustin allemand initiateur du protestantisme.</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="154.5" customHeight="1" s="39">
       <c r="A13" s="47" t="n">
@@ -1434,6 +1492,11 @@
       <c r="M13" s="35" t="inlineStr">
         <is>
           <t>philosophe et mathématicien italien d'un esprit à la fois rationaliste et mystique.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1501,6 +1564,11 @@
           <t>pasteur et théologien qui joua un rôle central dans le développement du protestantisme.</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="168" customHeight="1" s="39">
       <c r="A15" s="47" t="n">
@@ -1563,6 +1631,11 @@
           <t>philosophe naturaliste italien qui secoua Aristote pour l'étude de la nature.</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="276" customHeight="1" s="39">
       <c r="A16" s="47" t="n">
@@ -1623,6 +1696,11 @@
           <t xml:space="preserve"> philosophe, logicien français appartenant au contexte intellectuel de l’humanisme et de la Réforme.</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="129.75" customHeight="1" s="39">
       <c r="A17" s="47" t="n">
@@ -1686,6 +1764,11 @@
           <t>philosophe et savant italien principal défenseur du platonisme contre l'aristotélisme.</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="183.75" customHeight="1" s="39">
       <c r="A18" s="47" t="n">
@@ -1746,6 +1829,14 @@
         <is>
           <t>philosophe et écrivain français, l'un des fondateurs du Scepticisme moderne.</t>
         </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" ht="139.5" customHeight="1" s="39">
@@ -1812,6 +1903,11 @@
           <t>philosophe humaniste italien commentateur latin d'Aristote le plus réputé.</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="137.25" customHeight="1" s="39">
       <c r="A20" s="47" t="n">
@@ -1871,6 +1967,11 @@
       <c r="M20" s="35" t="inlineStr">
         <is>
           <t>philosophe et moraliste français sceptique qui défendait la tolérance religieuse.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1941,6 +2042,11 @@
           <t>philosophe et scientifique italien de la renaissance qui croyait en d'autres mondes.</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="178.5" customHeight="1" s="39">
       <c r="A22" s="47" t="n">
@@ -2002,6 +2108,11 @@
           <t>philosophe espagnol pionnier du droit international moderne.</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="157.5" customHeight="1" s="39">
       <c r="A23" s="47" t="n">
@@ -2061,6 +2172,11 @@
       <c r="M23" s="35" t="inlineStr">
         <is>
           <t>philosophe anglais qui fut l'un des premiers adeptes de l'Empirisme.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -2127,6 +2243,11 @@
           <t>philosophe dominicain italien connu pour ses idées utopiques.</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="135" customHeight="1" s="39">
       <c r="A25" s="47" t="n">
@@ -2188,6 +2309,11 @@
           <t>philosophe mystique allemand surnommé le "Philosophus Teutonicus".</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="168" customHeight="1" s="39">
       <c r="A26" s="47" t="n">
@@ -2249,6 +2375,11 @@
       <c r="M26" s="35" t="inlineStr">
         <is>
           <t>humaniste hollandais fondateur du droit international moderne.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -2317,6 +2448,11 @@
           <t>philosophe et libre-penseur italien représentant radical du naturalisme.</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="137.25" customHeight="1" s="39">
       <c r="A28" s="47" t="n">
@@ -2380,6 +2516,14 @@
           <t>philosophe anglais qui a eu une grande influence sur la politique moderne.</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P28">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" ht="157.5" customHeight="1" s="39">
       <c r="A29" s="47" t="n">
@@ -2442,6 +2586,11 @@
           <t>philosophe et encyclopédiste protestant calviniste allemand.</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="102.75" customHeight="1" s="39">
       <c r="A30" s="47" t="n">
@@ -2504,6 +2653,11 @@
           <t>philosophe français connu pour avoir réintroduit la notion d'atome et défendu le vide.</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="132" customHeight="1" s="39">
       <c r="A31" s="47" t="n">
@@ -2566,6 +2720,11 @@
           <t>philosophe, théologien tchèque, considéré comme le père de la pédagogie moderne.</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="223.5" customHeight="1" s="39">
       <c r="A32" s="47" t="n">
@@ -2628,6 +2787,14 @@
           <t>philosophe français qui proposa d'atteindre la vérité par la raison.</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P32">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" ht="220.5" customHeight="1" s="39">
       <c r="A33" s="47" t="n">
@@ -2690,6 +2857,11 @@
           <t>philosophe espagnol connu pour sa réflexion sur la prudence et la lucidité.</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="346.5" customHeight="1" s="39">
       <c r="A34" s="47" t="n">
@@ -2747,6 +2919,11 @@
       <c r="M34" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe, théologien, logicien et mathématicien français, figure du jansénisme.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -2815,6 +2992,14 @@
           <t>philosophe et mathématicien français pris entre pessimisme et scepticisme.</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P35">
+        <v>3</v>
+      </c>
     </row>
     <row r="36" ht="180" customHeight="1" s="39">
       <c r="A36" s="47" t="n">
@@ -2877,6 +3062,11 @@
           <t>philosophe flamand disciple radical de Descartes et pionnier de l'occasionnalisme.</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="199.5" customHeight="1" s="39">
       <c r="A37" s="47" t="n">
@@ -2939,6 +3129,11 @@
           <t>philosophe allemand connu pour ses tentatives de fonder une "pansophie universelle".</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="265.5" customHeight="1" s="39">
       <c r="A38" s="47" t="n">
@@ -2998,6 +3193,11 @@
           <t xml:space="preserve"> philosophe, théologien, logicien et polémiste français, proche de Port-Royal et du mouvement janséniste.</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="168" customHeight="1" s="39">
       <c r="A39" s="47" t="n">
@@ -3064,6 +3264,14 @@
         <is>
           <t xml:space="preserve">juive</t>
         </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P39">
+        <v>3</v>
       </c>
     </row>
     <row r="40" ht="138" customHeight="1" s="39">
@@ -3129,6 +3337,14 @@
           <t>philosophe anglais qui a développé une théorie de la connaissance Empirique.</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P40">
+        <v>3</v>
+      </c>
     </row>
     <row r="41" ht="155.25" customHeight="1" s="39">
       <c r="A41" s="47" t="n">
@@ -3193,6 +3409,11 @@
           <t>philosophe français principal représentant de l'occasionnalisme.</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="155.25" customHeight="1" s="39">
       <c r="A42" s="47" t="n">
@@ -3257,6 +3478,11 @@
           <t>philosophe allemand et l'un des principaux représentants du Rationalisme.</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="131.25" customHeight="1" s="39">
       <c r="A43" s="47" t="n">
@@ -3316,6 +3542,11 @@
       <c r="M43" s="35" t="inlineStr">
         <is>
           <t>philosophe français et l'un des premiers féministes.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3381,6 +3612,11 @@
       <c r="M44" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour sa défense de la tolérance religieuse.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3449,6 +3685,11 @@
           <t>philosophe et prêtre français connu pour son Athéisme radical.</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="147.75" customHeight="1" s="39">
       <c r="A46" s="47" t="n">
@@ -3510,6 +3751,11 @@
           <t>philosophe italien qui élabora une métaphysique et une philosophie de l'histoire.</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="126.75" customHeight="1" s="39">
       <c r="A47" s="47" t="n">
@@ -3571,6 +3817,11 @@
           <t>philosophe hollandais célèbre par son ouvrage satirique "La Fable des Abeilles".</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="147.75" customHeight="1" s="39">
       <c r="A48" s="47" t="n">
@@ -3632,6 +3883,11 @@
           <t>philosophe allemand qui systématisa la philosophie rationnelle en allemand.</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="164.9" customHeight="1" s="39">
       <c r="A49" s="47" t="n">
@@ -3694,6 +3950,14 @@
           <t>philosophe et évêque irlandais célèbre pour sa philosophie empiriste et idéaliste.</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P49">
+        <v>2</v>
+      </c>
     </row>
     <row r="50" ht="150" customHeight="1" s="39">
       <c r="A50" s="47" t="n">
@@ -3755,6 +4019,11 @@
           <t>philosophe suédois qui est passé du rationalisme scientifique au mysticisme chrétien.</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="168" customHeight="1" s="39">
       <c r="A51" s="47" t="n">
@@ -3815,6 +4084,11 @@
       <c r="M51" s="35" t="inlineStr">
         <is>
           <t>philosophe penseur de l'organisation politique et sociale des sociétés modernes.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3882,6 +4156,14 @@
           <t>philosophe et écrivain français Déiste de l'époque des lumières.</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P52">
+        <v>3</v>
+      </c>
     </row>
     <row r="53" ht="147.75" customHeight="1" s="39">
       <c r="A53" s="47" t="n">
@@ -3944,6 +4226,11 @@
           <t>philosophe irlando-écossais  majeur des Lumières écossaises.</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="133.5" customHeight="1" s="39">
       <c r="A54" s="47" t="n">
@@ -4005,6 +4292,11 @@
           <t>philosophe anglais déclencheur d'un réveil de l'Église d'Angleterre, le méthodisme.</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="166.5" customHeight="1" s="39">
       <c r="A55" s="47" t="n">
@@ -4068,6 +4360,11 @@
           <t>philosophe et psychologue anglais précurseur dans l'étude de l'esprit humain.</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="135" customHeight="1" s="39">
       <c r="A56" s="47" t="n">
@@ -4130,6 +4427,11 @@
           <t>philosophe français connu pour son matérialisme radical et son athéisme.</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="120" customHeight="1" s="39">
       <c r="A57" s="47" t="n">
@@ -4192,6 +4494,11 @@
           <t>philosophe des Lumières écossaises, fondateur de l'école du sens commun.</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="115.5" customHeight="1" s="39">
       <c r="A58" s="47" t="n">
@@ -4253,6 +4560,14 @@
         <is>
           <t>philosophe écossais Sceptique et fondateur de l'Empirisme moderne.</t>
         </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P58">
+        <v>3</v>
       </c>
     </row>
     <row r="59" ht="126.75" customHeight="1" s="39">
@@ -4317,6 +4632,14 @@
         <is>
           <t>philosophe et écrivain franco-suisse de l'époque des lumières.</t>
         </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P59">
+        <v>3</v>
       </c>
     </row>
     <row r="60" ht="148.5" customHeight="1" s="39">
@@ -4383,6 +4706,11 @@
           <t>philosophe et écrivain français des lumières qui rejetait les dogmes.</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="166.5" customHeight="1" s="39">
       <c r="A61" s="47" t="n">
@@ -4445,6 +4773,11 @@
           <t>philosophe allemand considéré comme le père de l'esthétique.</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="166.5" customHeight="1" s="39">
       <c r="A62" s="47" t="n">
@@ -4501,6 +4834,11 @@
           <t>philosophe et théologien protestant allemand, représentant des Lumières religieuses.</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="153.75" customHeight="1" s="39">
       <c r="A63" s="47" t="n">
@@ -4563,6 +4901,11 @@
           <t>philosophe français connu pour son matérialisme radical et son utilitarisme.</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="88.5" customHeight="1" s="39">
       <c r="A64" s="47" t="n">
@@ -4625,6 +4968,11 @@
           <t>philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie.</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="126" customHeight="1" s="39">
       <c r="A65" s="47" t="n">
@@ -4686,6 +5034,11 @@
           <t>philosophe écossais Libéraliste qui développa sa théorie de la 'main invisible'.</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="101.25" customHeight="1" s="39">
       <c r="A66" s="47" t="n">
@@ -4748,6 +5101,11 @@
           <t>philosophe matérialiste allemand athée des Lumières.</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="166.5" customHeight="1" s="39">
       <c r="A67" s="47" t="n">
@@ -4809,6 +5167,14 @@
           <t>philosophe allemand qui a développé une théorie appelée « éthique kantienne ».</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P67">
+        <v>3</v>
+      </c>
     </row>
     <row r="68" ht="140.25" customHeight="1" s="39">
       <c r="A68" s="47" t="n">
@@ -4876,6 +5242,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="127.5" customHeight="1" s="39">
       <c r="A69" s="47" t="n">
@@ -4939,6 +5310,11 @@
           <t>philosophe anglo-irlandais considéré comme l'un des fondateurs du conservatisme moderne.</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="143.25" customHeight="1" s="39">
       <c r="A70" s="47" t="n">
@@ -4999,6 +5375,11 @@
           <t>philosophe allemand &amp; figure centrale des Lumières allemandes.</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="131.25" customHeight="1" s="39">
       <c r="A71" s="47" t="n">
@@ -5061,6 +5442,11 @@
           <t>philosophe français connu pour ses écrits provocateurs et controversés.</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="116.25" customHeight="1" s="39">
       <c r="A72" s="47" t="n">
@@ -5123,6 +5509,11 @@
           <t>théologien, poète et philosophe suisse, connu comme pionnier de la physiognomonie.</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="158.25" customHeight="1" s="39">
       <c r="A73" s="47" t="n">
@@ -5185,6 +5576,11 @@
           <t>philosophe français figure du mysticisme chrétien au XVIIIe siècle.</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="187.5" customHeight="1" s="39">
       <c r="A74" s="47" t="n">
@@ -5246,6 +5642,11 @@
           <t>philosophe français figure des Lumières et défenseur du progrès humain indéfini.</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="148.5" customHeight="1" s="39">
       <c r="A75" s="47" t="n">
@@ -5308,6 +5709,11 @@
           <t>philosophe juif allemand critique majeur du rationalisme des Lumières.</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="155.25" customHeight="1" s="39">
       <c r="A76" s="47" t="n">
@@ -5369,6 +5775,11 @@
           <t>philosophe allemand père de la philosophie de la culture et de l’idée moderne de nation.</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="112.5" customHeight="1" s="39">
       <c r="A77" s="47" t="n">
@@ -5435,6 +5846,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="178.5" customHeight="1" s="39">
       <c r="A78" s="47" t="n">
@@ -5496,6 +5912,11 @@
           <t>philosophe et économiste anglais considéré comme fondateur de l'Utilitarisme.</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="141.75" customHeight="1" s="39">
       <c r="A79" s="47" t="n">
@@ -5559,6 +5980,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="157.5" customHeight="1" s="39">
       <c r="A80" s="47" t="n">
@@ -5620,6 +6046,11 @@
           <t>philosophe français figure de la contre-révolution &amp; critique des Lumières.</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="148.5" customHeight="1" s="39">
       <c r="A81" s="47" t="n">
@@ -5682,6 +6113,11 @@
           <t>philosophe et théoricien contre-révolutionnaire français, chef de file du traditionalisme.</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="135" customHeight="1" s="39">
       <c r="A82" s="34" t="n">
@@ -5740,6 +6176,11 @@
           <t>philosophe français fondateur du courant philosophique des Idéologues.</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="104.25" customHeight="1" s="39">
       <c r="A83" s="34" t="n">
@@ -5798,6 +6239,11 @@
           <t>philosophe français connu pour avoir réformé la psychologie rationnelle.</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="109.5" customHeight="1" s="39">
       <c r="A84" s="34" t="n">
@@ -5856,6 +6302,11 @@
           <t>philosophe figure majeure du matérialisme et de l'idéologie de la Révolution française.</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="135.75" customHeight="1" s="39">
       <c r="A85" s="47" t="n">
@@ -5917,6 +6368,11 @@
           <t>philosophe français figure majeure du libéralisme modéré.</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="317.25" customFormat="1" customHeight="1" s="38">
       <c r="A86" s="38" t="n">
@@ -5975,6 +6431,11 @@
           <t>penseur et réformateur social français, fondateur du saint-simonisme.</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="130.5" customHeight="1" s="39">
       <c r="A87" s="47" t="n">
@@ -6034,6 +6495,11 @@
       <c r="M87" s="35" t="inlineStr">
         <is>
           <t>philosophe français fondateur de la philosophie de l'intériorité et du spiritualisme.</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -6501,6 +6501,386 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
+      </c>
+    </row>
+    <row r="88" ht="130.5" customHeight="1" s="39">
+      <c r="A88" s="47">
+        <v>1565</v>
+      </c>
+      <c r="B88" s="47">
+        <v>1645</v>
+      </c>
+      <c r="C88" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1565 - 1645</t>
+        </is>
+      </c>
+      <c r="D88" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marie de GOURNAY</t>
+        </is>
+      </c>
+      <c r="E88" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marie_de_Gournay"  title=" Wikipedia"&gt;Marie de GOURNAY&lt;/a&gt; (1565-1645) est une femme de lettres et philosophe française. Autodidacte, elle apprit seule le latin et découvrit adolescente les &lt;em&gt;Essais&lt;/em&gt; de Montaigne, qui la bouleversèrent. Elle rencontra l'auteur en 1588 et devint sa « fille d'alliance », une amitié intellectuelle profonde.&lt;/p&gt; &lt;p&gt;Après la mort de Montaigne, sa veuve lui confia le manuscrit annoté des &lt;em&gt;Essais&lt;/em&gt;. Marie de Gournay consacra une grande partie de sa vie à en préparer les éditions, dont celle de 1595, qui a fait autorité pendant des siècles. Elle vécut de sa plume, chose très rare pour une femme de son époque, et fréquenta les milieux savants de Paris, où elle fut souvent moquée pour son indépendance.&lt;/p&gt; &lt;p&gt;Marie de Gournay s'intéressa aussi à la langue française, qu'elle défendit contre les réformes de Malherbe qui voulaient l'appauvrir selon elle, et publia un recueil de ses œuvres sous le titre &lt;em&gt;L'Ombre de la demoiselle de Gournay&lt;/em&gt; (1626), puis &lt;em&gt;Les Advis ou les Présens&lt;/em&gt; (1634). Elle y traite de l'éducation des princes, de la poésie, de la calomnie et de la condition des femmes savantes, qu'on ridiculisait pour mieux les écarter.&lt;/p&gt; &lt;p&gt;Elle est surtout connue pour deux textes pionniers : &lt;em&gt;Égalité des hommes et des femmes&lt;/em&gt; (1622) et &lt;em&gt;Grief des dames&lt;/em&gt; (1626). Elle y soutient que la différence entre hommes et femmes ne tient pas à la nature mais à l'éducation, et que « l'animal humain n'est ni homme ni femme » par l'âme. Elle s'appuie sur la Bible, les Pères de l'Église et les philosophes antiques pour montrer que rien ne justifie l'exclusion des femmes du savoir. Elle est considérée comme l'une des premières penseuses de l'égalité des sexes.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J88" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K88" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L88" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Féminisme</t>
+        </is>
+      </c>
+      <c r="M88" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme de lettres française, « fille d'alliance » de Montaigne et pionnière de la défense de l'égalité des sexes.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="130.5" customHeight="1" s="39">
+      <c r="A89" s="47">
+        <v>1618</v>
+      </c>
+      <c r="B89" s="47">
+        <v>1680</v>
+      </c>
+      <c r="C89" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1618 - 1680</t>
+        </is>
+      </c>
+      <c r="D89" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ÉLISABETH de Bohême</t>
+        </is>
+      </c>
+      <c r="E89" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Élisabeth_de_Bohême_(1618-1680)"  title=" Wikipedia"&gt;ÉLISABETH de Bohême&lt;/a&gt; (1618-1680), princesse palatine, était la fille de Frédéric V, l'éphémère « roi d'hiver » de Bohême, chassé de son trône au début de la guerre de Trente Ans. Elle grandit en exil aux Pays-Bas, où elle reçut une éducation très poussée en langues, mathématiques et philosophie.&lt;/p&gt; &lt;p&gt;Elle est célèbre pour sa correspondance avec René Descartes, commencée en 1643. Dès sa première lettre, elle lui pose une question redoutable : si l'âme est une substance pensante, sans étendue, comment peut-elle mettre en mouvement le corps, qui est une chose étendue ? Descartes eut beaucoup de mal à lui répondre, et cette objection reste au cœur de ce que l'on appelle aujourd'hui le problème de l'esprit et du corps.&lt;/p&gt; &lt;p&gt;La correspondance entre Élisabeth et Descartes, qui dura jusqu'à la mort du philosophe en 1650, compte une soixantaine de lettres. On y voit la princesse contester, avec politesse mais fermeté, plusieurs points de la doctrine cartésienne, et proposer ses propres solutions, par exemple sur la manière dont l'âme peut être affectée par la maladie du corps. Descartes lui-même reconnaissait qu'elle était la personne qui comprenait le mieux sa philosophie.&lt;/p&gt; &lt;p&gt;Leurs échanges portèrent aussi sur les passions, la vertu, le bonheur et la politique : c'est pour elle que Descartes écrivit son &lt;em&gt;Traité des passions de l'âme&lt;/em&gt;, et il lui dédia ses &lt;em&gt;Principes de la philosophie&lt;/em&gt;. Élisabeth y défend une morale attentive aux réalités de la vie et du corps. Elle devint ensuite abbesse de l'abbaye protestante de Herford, en Allemagne, où elle accueillit des penseurs persécutés. Elle est aujourd'hui reconnue comme une philosophe à part entière, et non plus seulement comme une correspondante de Descartes.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J89" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allemande</t>
+        </is>
+      </c>
+      <c r="K89" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; ethique</t>
+        </is>
+      </c>
+      <c r="L89" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartésianisme</t>
+        </is>
+      </c>
+      <c r="M89" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">princesse palatine dont la correspondance avec Descartes pose le problème de l'union de l'âme et du corps.</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" ht="130.5" customHeight="1" s="39">
+      <c r="A90" s="47">
+        <v>1623</v>
+      </c>
+      <c r="B90" s="47">
+        <v>1673</v>
+      </c>
+      <c r="C90" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1623 - 1673</t>
+        </is>
+      </c>
+      <c r="D90" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Margaret CAVENDISH</t>
+        </is>
+      </c>
+      <c r="E90" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Margaret_Cavendish"  title=" Wikipedia"&gt;Margaret CAVENDISH&lt;/a&gt; (1623-1673), duchesse de Newcastle, est une philosophe, poétesse et romancière anglaise. Pendant la guerre civile anglaise, elle suivit la reine en exil à Paris, où elle épousa William Cavendish et fréquenta, grâce à lui, des penseurs comme Hobbes, Descartes et Gassendi.&lt;/p&gt; &lt;p&gt;Elle publia sous son propre nom une douzaine d'ouvrages de philosophie naturelle, ce qui était presque impensable pour une femme de son temps. Elle y développe une philosophie matérialiste et vitaliste : la nature entière est faite d'une seule matière, mais cette matière est douée de mouvement, de perception et même de raison. Elle critique à la fois le mécanisme de Descartes et de Hobbes, et la science expérimentale de la Royal Society, qui prétendait connaître la nature grâce aux microscopes.&lt;/p&gt; &lt;p&gt;Cavendish réfléchit aussi à la condition des femmes, qu'elle juge tenues à l'écart du savoir et du pouvoir par la coutume plutôt que par la nature. Dans ses préfaces, elle revendique ouvertement le désir de gloire et de reconnaissance, ce qui choquait ses contemporains. Ses &lt;em&gt;Observations sur la philosophie expérimentale&lt;/em&gt; (1666) contiennent l'une des premières critiques philosophiques de la confiance aveugle dans les instruments scientifiques.&lt;/p&gt; &lt;p&gt;En 1667, elle fut la première femme invitée à assister à une séance de la Royal Society de Londres. Son récit &lt;em&gt;Le Monde glorieux&lt;/em&gt; (&lt;em&gt;The Blazing World&lt;/em&gt;, 1666), où une femme devient impératrice d'un monde imaginaire peuplé de savants animaux, est souvent considéré comme l'un des premiers romans de science-fiction. Surnommée « Mad Madge » par ses contemporains, elle est aujourd'hui redécouverte comme une philosophe originale et audacieuse.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J90" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K90" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L90" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matérialisme</t>
+        </is>
+      </c>
+      <c r="M90" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe anglaise, penseuse matérialiste de la nature et autrice de l'un des premiers romans de science-fiction.</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="130.5" customHeight="1" s="39">
+      <c r="A91" s="47">
+        <v>1631</v>
+      </c>
+      <c r="B91" s="47">
+        <v>1679</v>
+      </c>
+      <c r="C91" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1631 - 1679</t>
+        </is>
+      </c>
+      <c r="D91" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anne CONWAY</t>
+        </is>
+      </c>
+      <c r="E91" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Conway"  title=" Wikipedia"&gt;Anne CONWAY&lt;/a&gt; (1631-1679) est une philosophe anglaise, proche du groupe des platoniciens de Cambridge. Souffrant toute sa vie de violentes migraines, elle reçut une éducation principalement par correspondance, notamment avec le philosophe Henry More, qui devint son ami et son maître.&lt;/p&gt; &lt;p&gt;Son unique ouvrage, les &lt;em&gt;Principes de la plus ancienne et de la plus moderne philosophie&lt;/em&gt;, fut publié après sa mort, en latin en 1690, puis en anglais. Elle y rejette le dualisme de Descartes, qui sépare l'esprit et la matière, et le matérialisme de Hobbes et de Spinoza. Pour elle, tout ce qui existe est à la fois esprit et corps à des degrés divers : la matière n'est qu'un esprit « épaissi », et toutes les créatures, même les pierres, sont vivantes et capables de se perfectionner.&lt;/p&gt; &lt;p&gt;Sa philosophie répond aussi à une question personnelle : comment donner un sens à la douleur ? Pour Anne Conway, la souffrance n'est pas un châtiment arbitraire mais un moyen de purification, qui permet à chaque créature de se rapprocher de Dieu. Aucune créature n'est condamnée pour toujours : toutes sont appelées à progresser vers le bien, ce qui fait de sa pensée l'une des plus optimistes de son temps.&lt;/p&gt; &lt;p&gt;Anne Conway propose une vision d'un monde en constante évolution vers le bien, où la souffrance a un sens puisqu'elle aide les êtres à progresser. Influencée par la kabbale et par les quakers, qu'elle rejoignit à la fin de sa vie, elle eut une influence directe sur Leibniz, qui la cite et lui emprunta sans doute l'idée de « monade ». Longtemps oubliée, elle est aujourd'hui considérée comme l'une des philosophes les plus originales du XVIIe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J91" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K91" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L91" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoplatonisme</t>
+        </is>
+      </c>
+      <c r="M91" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe anglaise, penseuse d'un monde fait d'un seul esprit vivant, qui influença Leibniz.</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="130.5" customHeight="1" s="39">
+      <c r="A92" s="47">
+        <v>1666</v>
+      </c>
+      <c r="B92" s="47">
+        <v>1731</v>
+      </c>
+      <c r="C92" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1666 - 1731</t>
+        </is>
+      </c>
+      <c r="D92" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mary ASTELL</t>
+        </is>
+      </c>
+      <c r="E92" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Astell"  title=" Wikipedia"&gt;Mary ASTELL&lt;/a&gt; (1666-1731) est une philosophe et écrivaine anglaise, souvent présentée comme la première féministe anglaise. Fille d'un marchand de charbon de Newcastle, elle fut instruite par son oncle, puis s'installa seule à Londres, où elle vécut de sa plume grâce au soutien de protectrices aristocratiques.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Une proposition sérieuse aux dames&lt;/em&gt; (1694), elle propose de créer une sorte d'institution où les femmes pourraient se consacrer à l'étude et à la réflexion, loin des futilités auxquelles la société les condamne. Disciple de Descartes et du philosophe Malebranche, elle affirme que les femmes ont la même raison que les hommes et que leur prétendue infériorité vient uniquement de leur manque d'éducation.&lt;/p&gt; &lt;p&gt;Mary Astell fut aussi une polémiste redoutée, qui débattit avec les penseurs les plus en vue de son temps, dont John Locke et le philosophe John Norris, avec qui elle échangea des lettres sur l'amour de Dieu. Elle fonda à Chelsea une école de charité pour les filles pauvres, qu'elle soutint jusqu'à sa mort. Son idée d'une communauté de femmes consacrée à l'étude, jugée trop proche des couvents catholiques, ne vit jamais le jour, mais elle inspira de nombreuses féministes après elle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Réflexions sur le mariage&lt;/em&gt; (1700), elle critique avec ironie la condition des épouses, soumises à un pouvoir absolu de leur mari. Elle retourne contre ses adversaires les idées de John Locke : « si tous les hommes naissent libres, comment se fait-il que toutes les femmes naissent esclaves ? ». Anglicane conservatrice en politique, elle n'en fut pas moins l'une des premières à penser la domination des femmes comme une question philosophique et politique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J92" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K92" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L92" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rationalisme ; Féminisme</t>
+        </is>
+      </c>
+      <c r="M92" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe anglaise, considérée comme l'une des premières féministes, qui défendit l'éducation des femmes.</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="130.5" customHeight="1" s="39">
+      <c r="A93" s="47">
+        <v>1706</v>
+      </c>
+      <c r="B93" s="47">
+        <v>1749</v>
+      </c>
+      <c r="C93" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1706 - 1749</t>
+        </is>
+      </c>
+      <c r="D93" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Émilie du CHÂTELET</t>
+        </is>
+      </c>
+      <c r="E93" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Émilie_du_Châtelet"  title=" Wikipedia"&gt;Émilie du CHÂTELET&lt;/a&gt; (1706-1749) est une mathématicienne, physicienne et philosophe française des Lumières. Issue de l'aristocratie, elle reçut une éducation rare pour une fille, en latin, en mathématiques et en sciences. Compagne de Voltaire pendant quinze ans, elle fit de leur château de Cirey un véritable centre d'étude, où ils travaillaient côte à côte.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Institutions de physique&lt;/em&gt; (1740) tentent de concilier la physique de Newton et la métaphysique de Leibniz, en particulier le principe de raison suffisante. Elle participa à la grande controverse sur la notion de « force vive », en montrant que l'énergie d'un corps en mouvement dépend du carré de sa vitesse, une idée essentielle pour la physique moderne.&lt;/p&gt; &lt;p&gt;Elle entretint une correspondance avec les plus grands savants de son temps, comme les mathématiciens Maupertuis et Clairaut, et fut la première femme dont un mémoire scientifique, sur la nature du feu, fut publié par l'Académie des sciences de Paris en 1738. Elle ne pouvait pourtant pas en être membre, et il lui arriva de se déguiser en homme pour entrer dans les cafés où se retrouvaient les savants.&lt;/p&gt; &lt;p&gt;Son œuvre majeure est la traduction commentée en français des &lt;em&gt;Principes mathématiques de la philosophie naturelle&lt;/em&gt; de Newton, achevée juste avant sa mort en couches, à 42 ans. Elle reste aujourd'hui la seule traduction française complète de ce texte fondateur. Dans son &lt;em&gt;Discours sur le bonheur&lt;/em&gt;, elle fait de l'étude et de la passion du savoir une source de bonheur indépendante des autres, notamment pour les femmes, exclues de tant d'autres chemins de la gloire.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J93" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K93" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L93" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rationalisme</t>
+        </is>
+      </c>
+      <c r="M93" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mathématicienne et philosophe française des Lumières, traductrice de Newton et penseuse du bonheur.</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" ht="130.5" customHeight="1" s="39">
+      <c r="A94" s="47">
+        <v>1748</v>
+      </c>
+      <c r="B94" s="47">
+        <v>1793</v>
+      </c>
+      <c r="C94" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1748 - 1793</t>
+        </is>
+      </c>
+      <c r="D94" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Olympe de GOUGES</t>
+        </is>
+      </c>
+      <c r="E94" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympe_de_Gouges"  title=" Wikipedia"&gt;Olympe de GOUGES&lt;/a&gt; (1748-1793), de son vrai nom Marie Gouze, est une femme de lettres et une femme politique française. Née à Montauban dans un milieu modeste, veuve très jeune, elle s'installa à Paris où elle écrivit des pièces de théâtre, dont une dénonçant l'esclavage des Noirs, qui fit scandale.&lt;/p&gt; &lt;p&gt;Pendant la Révolution française, elle publia de nombreuses brochures sur les questions sociales et politiques : aide aux pauvres, divorce, protection des enfants nés hors mariage. En 1791, elle rédigea la &lt;em&gt;Déclaration des droits de la femme et de la citoyenne&lt;/em&gt;, qui reprend article par article la Déclaration de 1789 pour montrer qu'elle exclut la moitié de l'humanité. Elle y écrit : « La femme a le droit de monter sur l'échafaud ; elle doit avoir également celui de monter à la tribune ».&lt;/p&gt; &lt;p&gt;Olympe de Gouges réclamait aussi l'accès des femmes à toutes les fonctions publiques, le droit de vote, le partage des biens entre époux et le droit de rechercher la paternité. Dans le postambule de sa Déclaration, elle appelle les femmes à se réveiller et à reconnaître leurs droits. Sa pensée associe l'égalité des sexes, l'abolition de l'esclavage et la justice sociale, bien avant que ces combats soient reconnus.&lt;/p&gt; &lt;p&gt;Proche des Girondins, elle critiqua ouvertement Robespierre et la Terreur. Arrêtée pour ses écrits, elle fut condamnée à mort et guillotinée le 3 novembre 1793. Longtemps caricaturée, elle est aujourd'hui considérée comme une pionnière du féminisme et de la défense des droits humains.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J94" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K94" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L94" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Féminisme</t>
+        </is>
+      </c>
+      <c r="M94" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme de lettres et révolutionnaire française, autrice de la Déclaration des droits de la femme et de la citoyenne.</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P94">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D21" s="48" t="inlineStr">
         <is>
-          <t>Giodano BRUNO</t>
+          <t xml:space="preserve">Giordano BRUNO</t>
         </is>
       </c>
       <c r="E21" s="58" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="D53" s="48" t="inlineStr">
         <is>
-          <t>Françis HUTCHESON</t>
+          <t xml:space="preserve">Francis HUTCHESON</t>
         </is>
       </c>
       <c r="E53" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francis_Hutcheson_(philosophe)"   title=" Wikipedia"&gt;Françis HUTCHESON&lt;/a&gt;  était un philosophe irlando-écossais  majeur des Lumières écossaises, surtout connu pour sa théorie du sens moral et pour son influence sur Hume, Smith et Reid. Il a enseigné la philosophie morale à l’université de Glasgow et a contribué aussi à l’esthétique, à la psychologie morale et à la pensée politique. Sa thèse la plus célèbre est que &lt;a href="https://www.persee.fr/doc/dhs_0070-6760_1994_num_26_1_2013_t1_0566_0000_3"   title=" Two Texts on Human Nature par Persée "&gt;l’être humain &lt;/a&gt; possède une faculté morale innée, un « moral sense », qui nous fait approuver spontanément les actions vertueuses et désapprouver les actions vicieuses, sans passer d’abord par un long raisonnement. &lt;/p&gt; &lt;p&gt; Il s’oppose aux théories qui réduisent la morale à l’égoïsme, comme celles de Hobbes ou de Mandeville, et il insiste au contraire sur le rôle de la bienveillance dans l’action morale. Il est aussi souvent vu comme un précurseur de &lt;a href="https://fr.wikipedia.org/wiki/Utilitarisme"   title=" Utilitarisme par Wikipedia "&gt;l’utilitarisme, &lt;/a&gt; parce qu’il relie le bien moral au bien-être général et à l’idée du « plus grand bonheur du plus grand nombre ». &lt;/p&gt; &lt;p&gt; Parmi ses textes les plus connus, on trouve An Inquiry into the Original of Our Ideas of Beauty and Virtue (1725) et An Essay on the Nature and Conduct of the Passions and Affections (1728). Ces ouvrages ont joué un rôle important dans la naissance de la philosophie morale moderne en langue anglaise. &lt;/p&gt; &lt;p&gt; Il  a fortement influencé la philosophie morale écossaise et des penseurs comme Adam Smith et David Hume. On lui doit aussi d’avoir contribué à faire de l’esthétique un domaine philosophique à part entière, en montrant que le beau peut aussi être perçu par une forme de sens intérieur. &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francis_Hutcheson_(philosophe)"   title=" Wikipedia"&gt;Francis HUTCHESON&lt;/a&gt;  était un philosophe irlando-écossais  majeur des Lumières écossaises, surtout connu pour sa théorie du sens moral et pour son influence sur Hume, Smith et Reid. Il a enseigné la philosophie morale à l’université de Glasgow et a contribué aussi à l’esthétique, à la psychologie morale et à la pensée politique. Sa thèse la plus célèbre est que &lt;a href="https://www.persee.fr/doc/dhs_0070-6760_1994_num_26_1_2013_t1_0566_0000_3"   title=" Two Texts on Human Nature par Persée "&gt;l’être humain &lt;/a&gt; possède une faculté morale innée, un « moral sense », qui nous fait approuver spontanément les actions vertueuses et désapprouver les actions vicieuses, sans passer d’abord par un long raisonnement. &lt;/p&gt; &lt;p&gt; Il s’oppose aux théories qui réduisent la morale à l’égoïsme, comme celles de Hobbes ou de Mandeville, et il insiste au contraire sur le rôle de la bienveillance dans l’action morale. Il est aussi souvent vu comme un précurseur de &lt;a href="https://fr.wikipedia.org/wiki/Utilitarisme"   title=" Utilitarisme par Wikipedia "&gt;l’utilitarisme, &lt;/a&gt; parce qu’il relie le bien moral au bien-être général et à l’idée du « plus grand bonheur du plus grand nombre ». &lt;/p&gt; &lt;p&gt; Parmi ses textes les plus connus, on trouve An Inquiry into the Original of Our Ideas of Beauty and Virtue (1725) et An Essay on the Nature and Conduct of the Passions and Affections (1728). Ces ouvrages ont joué un rôle important dans la naissance de la philosophie morale moderne en langue anglaise. &lt;/p&gt; &lt;p&gt; Il  a fortement influencé la philosophie morale écossaise et des penseurs comme Adam Smith et David Hume. On lui doit aussi d’avoir contribué à faire de l’esthétique un domaine philosophique à part entière, en montrant que le beau peut aussi être perçu par une forme de sens intérieur. &lt;/p&gt;
 </t>
         </is>
       </c>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -6880,6 +6880,127 @@
         </is>
       </c>
       <c r="P94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" ht="130.5" customHeight="1" s="39">
+      <c r="A95" s="47">
+        <v>1550</v>
+      </c>
+      <c r="B95" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1623</t>
+        </is>
+      </c>
+      <c r="C95" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1550 – 1623</t>
+        </is>
+      </c>
+      <c r="D95" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francisco SANCHES</t>
+        </is>
+      </c>
+      <c r="E95" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Sanchez" title=" Wikipedia"&gt;Francisco SANCHES&lt;/a&gt; est un médecin et philosophe d’origine portugaise, l’un des grands sceptiques de la Renaissance. Né vers 1550, à Braga ou à Tui, dans une famille de juifs convertis, que la menace de l’Inquisition pousse à quitter la péninsule Ibérique, il grandit à Bordeaux. Il étudie la médecine à Montpellier, séjourne en Italie, puis s’installe à Toulouse, où il exerce la médecine à l’hôpital et enseigne la philosophie et la médecine à l’université jusqu’à sa mort en 1623. Il serait un parent de &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne" title=" Wikipedia"&gt;Montaigne&lt;/a&gt;, par la mère de celui-ci.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Que rien ne se sait&lt;/em&gt; (&lt;em&gt;Quod nihil scitur&lt;/em&gt;), publié à Lyon en 1581, attaque la science des écoles, fondée sur Aristote : ses définitions ne sont que des mots, ses syllogismes ne font que répéter ce qu’on savait déjà, et l’on croit savoir quand on ne fait que nommer. La connaissance parfaite d’une chose supposerait de la connaître dans toutes ses causes et ses relations avec tout le reste, ce qui est impossible à un esprit fini. Il commence chaque argument par une question et termine son livre par un « Quoi ? » ironique.&lt;/p&gt; &lt;p&gt;Mais son &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_%28philosophie%29" title=" Wikipedia"&gt;scepticisme&lt;/a&gt; n’est pas un renoncement. Faute de savoir parfait, il faut s’en remettre à l’observation attentive et à l’expérience, comme le fait le médecin au chevet des malades, et avancer prudemment de jugement en jugement. Il annonce ainsi, avant Bacon et Descartes, l’esprit de la méthode expérimentale. Son œuvre, contemporaine des &lt;em&gt;Essais&lt;/em&gt; de Montaigne, a été redécouverte au XXe siècle comme un moment important du doute moderne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sanches-mini.webp</t>
+        </is>
+      </c>
+      <c r="J95" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portugaise</t>
+        </is>
+      </c>
+      <c r="K95" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie</t>
+        </is>
+      </c>
+      <c r="L95" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scepticisme</t>
+        </is>
+      </c>
+      <c r="M95" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">médecin et philosophe sceptique d’origine portugaise, auteur de Que rien ne se sait.</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" ht="130.5" customHeight="1" s="39">
+      <c r="A96" s="47">
+        <v>1608</v>
+      </c>
+      <c r="B96" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1697</t>
+        </is>
+      </c>
+      <c r="C96" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1608 – 1697</t>
+        </is>
+      </c>
+      <c r="D96" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">António VIEIRA</t>
+        </is>
+      </c>
+      <c r="E96" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ant%C3%B3nio_Vieira" title=" Wikipedia"&gt;António VIEIRA&lt;/a&gt; est un prêtre jésuite portugais, prédicateur, diplomate et écrivain, l’un des plus grands prosateurs de la langue portugaise. Né à Lisbonne, il part enfant pour le Brésil, à Bahia, où il entre chez les jésuites et apprend les langues indiennes. Ses sermons, d’une éloquence baroque éblouissante, le rendent célèbre : il en a laissé plus de deux cents. Conseiller du roi Jean IV après la restauration de l’indépendance portugaise en 1640, il est chargé de missions diplomatiques en France, en Hollande et à Rome.&lt;/p&gt; &lt;p&gt;Il prend la défense des Indiens d’Amazonie, réduits en esclavage par les colons, et se fait de puissants ennemis : son &lt;em&gt;Sermon de saint Antoine aux poissons&lt;/em&gt; (1654), où il prêche aux poissons faute d’être écouté des hommes, est une satire célèbre des colons. Ses adversaires obtiennent son expulsion du Maranhão en 1661. Dans plusieurs sermons, il dénonce aussi la souffrance des esclaves africains, tout en restant prisonnier des idées de son temps. Il plaide enfin pour les « nouveaux chrétiens », juifs convertis persécutés au Portugal, et demande que l’&lt;a href="https://fr.wikipedia.org/wiki/Inquisition_portugaise" title=" Wikipedia"&gt;Inquisition&lt;/a&gt; cesse de les poursuivre et que leurs capitaux servent au royaume.&lt;/p&gt; &lt;p&gt;Ses rêves prophétiques d’un &lt;a href="https://fr.wikipedia.org/wiki/Quint-Empire" title=" Wikipedia"&gt;Cinquième Empire&lt;/a&gt;, un règne universel de paix et de justice dont le Portugal serait l’instrument, lui valent d’être poursuivi par l’Inquisition, qui l’emprisonne de 1665 à 1667. Libéré, il obtient du pape une protection contre elle. Il passe ses dernières années à Bahia, où il meurt en 1697. Le poète Fernando Pessoa l’appelait « l’empereur de la langue portugaise ».&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vieira-mini.webp</t>
+        </is>
+      </c>
+      <c r="J96" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portugaise</t>
+        </is>
+      </c>
+      <c r="K96" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L96" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme</t>
+        </is>
+      </c>
+      <c r="M96" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jésuite portugais, prédicateur baroque, défenseur des Indiens du Brésil et des nouveaux chrétiens.</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P96">
         <v>2</v>
       </c>
     </row>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -3431,12 +3431,12 @@
       </c>
       <c r="D42" s="48" t="inlineStr">
         <is>
-          <t>Gottfried LIEBNIZ</t>
+          <t xml:space="preserve">Gottfried Wilhelm LEIBNIZ</t>
         </is>
       </c>
       <c r="E42" s="49" t="inlineStr">
         <is>
-          <t>&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gottfried_Wilhelm_Leibniz"  title=" Wikipedia"&gt;Gottfried LIEBNIZ&lt;/a&gt; était un philosophe allemand très &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme"  title=""éclectisme par Wikipedia"&gt;éclectique&lt;/a&gt;, de la théologie en passant par les mathématiques, la logique et la philosophie politique ou encore la métaphysique où il est connu pour sa théorie des monades, selon laquelle l'univers est composé d'un nombre infini d'entités individuelles et autonomes appelées monades. Chaque monade est une substance simple, sans parties, qui possède une perception et une appétition, c'est-à-dire une tendance à rechercher le bien et à &lt;a href="https://www.youtube.com/watch?v=ZJKr-vJt3NE&amp;ab_channel=LePr%C3%A9cepteur"  title="Le mal n'existe pas par le Précepteur"&gt; éviter le mal &lt;/a&gt; . Les monades ne peuvent pas interagir directement les unes avec les autres, mais leur perception et leur appétition sont harmonisées par Dieu, qui a créé l'univers de manière à ce qu'il soit le meilleur des mondes possibles. &lt;/p&gt; &lt;p&gt;
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gottfried_Wilhelm_Leibniz"  title=" Wikipedia"&gt;Gottfried Wilhelm LEIBNIZ&lt;/a&gt; était un philosophe allemand très &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme"  title=""éclectisme par Wikipedia"&gt;éclectique&lt;/a&gt;, de la théologie en passant par les mathématiques, la logique et la philosophie politique ou encore la métaphysique où il est connu pour sa théorie des monades, selon laquelle l'univers est composé d'un nombre infini d'entités individuelles et autonomes appelées monades. Chaque monade est une substance simple, sans parties, qui possède une perception et une appétition, c'est-à-dire une tendance à rechercher le bien et à &lt;a href="https://www.youtube.com/watch?v=ZJKr-vJt3NE&amp;ab_channel=LePr%C3%A9cepteur"  title="Le mal n'existe pas par le Précepteur"&gt; éviter le mal &lt;/a&gt; . Les monades ne peuvent pas interagir directement les unes avec les autres, mais leur perception et leur appétition sont harmonisées par Dieu, qui a créé l'univers de manière à ce qu'il soit le meilleur des mondes possibles. &lt;/p&gt; &lt;p&gt;
 La théorie a des implications dans de nombreux domaines, y compris la métaphysique, la théologie, l'épistémologie et l'éthique. Elle implique que la connaissance de chaque monade est limitée à sa propre perspective, ce qui soulève des questions intéressantes sur la nature de la vérité et de la connaissance.&lt;/p&gt; &lt;p&gt; 
 En mathématiques, il est connu pour avoir inventé le calcul infinitésimal, une méthode qui permet de manipuler des quantités infiniment petites. Cette découverte a été réalisée de manière indépendante par Leibniz et Isaac Newton, et les deux hommes ont été impliqués dans une longue querelle pour savoir qui était le véritable inventeur.&lt;/p&gt; &lt;p&gt; 
 En philosophie politique, Leibniz a soutenu que le pouvoir politique devrait être détenu par une élite instruite, qui gouvernerait de manière éclairée et rationnelle. &lt;/p&gt;  &lt;audio controls title="La Monadologie par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/11/s47/RF_F56A3AEF-9E04-487F-89BF-2C4FBCA2B21D_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G42" s="49" t="inlineStr">
         <is>
-          <t>"Liebniz et le sophisme paresseux" par Monsieur Phi</t>
+          <t xml:space="preserve">"Leibniz et le sophisme paresseux" par Monsieur Phi</t>
         </is>
       </c>
       <c r="H42" s="49" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -890,7 +890,7 @@
       </c>
       <c r="L4" s="46" t="inlineStr">
         <is>
-          <t>Humanisme ; Néoplatonisme</t>
+          <t xml:space="preserve">Humanisme ; Néoplatonisme ; Kabbale</t>
         </is>
       </c>
       <c r="M4" s="35" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L68" s="46" t="inlineStr">
         <is>
-          <t>Rationalisme ; Illuminisme</t>
+          <t xml:space="preserve">Rationalisme ; Illuminisme ; Haskala</t>
         </is>
       </c>
       <c r="M68" s="35" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="L77" s="46" t="inlineStr">
         <is>
-          <t>Criticisme</t>
+          <t xml:space="preserve">Criticisme ; Haskala</t>
         </is>
       </c>
       <c r="M77" s="35" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="L79" s="46" t="inlineStr">
         <is>
-          <t>Rationalisme</t>
+          <t xml:space="preserve">Rationalisme ; Haskala</t>
         </is>
       </c>
       <c r="M79" s="35" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -4078,7 +4078,7 @@
       </c>
       <c r="L51" s="46" t="inlineStr">
         <is>
-          <t>Libéralisme</t>
+          <t xml:space="preserve">Libéralisme ; Lumières</t>
         </is>
       </c>
       <c r="M51" s="35" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="L52" s="46" t="inlineStr">
         <is>
-          <t>Déisme ; Libéralisme</t>
+          <t xml:space="preserve">Déisme ; Libéralisme ; Lumières</t>
         </is>
       </c>
       <c r="M52" s="35" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="L58" s="46" t="inlineStr">
         <is>
-          <t>Empirisme ; Scepticisme ; Agnosticisme</t>
+          <t xml:space="preserve">Empirisme ; Scepticisme ; Agnosticisme ; Lumières</t>
         </is>
       </c>
       <c r="M58" s="35" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="L59" s="46" t="inlineStr">
         <is>
-          <t>Contractualisme</t>
+          <t xml:space="preserve">Contractualisme ; Lumières</t>
         </is>
       </c>
       <c r="M59" s="35" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L60" s="46" t="inlineStr">
         <is>
-          <t>Matérialisme</t>
+          <t xml:space="preserve">Matérialisme ; Lumières</t>
         </is>
       </c>
       <c r="M60" s="35" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="L63" s="46" t="inlineStr">
         <is>
-          <t>Matérialisme ; Utilitarisme</t>
+          <t xml:space="preserve">Matérialisme ; Utilitarisme ; Lumières</t>
         </is>
       </c>
       <c r="M63" s="35" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="L65" s="46" t="inlineStr">
         <is>
-          <t>Libéralisme</t>
+          <t xml:space="preserve">Libéralisme ; Lumières</t>
         </is>
       </c>
       <c r="M65" s="35" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="L66" s="46" t="inlineStr">
         <is>
-          <t>Matérialisme ; Athéisme</t>
+          <t xml:space="preserve">Matérialisme ; Athéisme ; Lumières</t>
         </is>
       </c>
       <c r="M66" s="35" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="L67" s="46" t="inlineStr">
         <is>
-          <t>Criticisme ; Agnosticisme ; Anthropocentrisme ; Constructivisme</t>
+          <t xml:space="preserve">Criticisme ; Agnosticisme ; Anthropocentrisme ; Constructivisme ; Lumières</t>
         </is>
       </c>
       <c r="M67" s="35" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L68" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rationalisme ; Illuminisme ; Haskala</t>
+          <t xml:space="preserve">Rationalisme ; Lumières ; Haskala</t>
         </is>
       </c>
       <c r="M68" s="35" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="L70" s="46" t="inlineStr">
         <is>
-          <t>Déisme</t>
+          <t xml:space="preserve">Déisme ; Lumières</t>
         </is>
       </c>
       <c r="M70" s="35" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L74" s="46" t="inlineStr">
         <is>
-          <t>Positivisme</t>
+          <t xml:space="preserve">Positivisme ; Lumières</t>
         </is>
       </c>
       <c r="M74" s="35" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="L93" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rationalisme</t>
+          <t xml:space="preserve">Rationalisme ; Lumières</t>
         </is>
       </c>
       <c r="M93" s="35" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="L94" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Féminisme</t>
+          <t xml:space="preserve">Féminisme ; Lumières</t>
         </is>
       </c>
       <c r="M94" s="35" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G34" s="49" t="inlineStr">
         <is>
-          <t>Antoine Arnauld par Vis Philo</t>
+          <t xml:space="preserve">Antoine Arnauld par VIS PHILO</t>
         </is>
       </c>
       <c r="H34" s="58" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="G39" s="49" t="inlineStr">
         <is>
-          <t>"Le parcourt de Spinoza" par Essence de Livres</t>
+          <t xml:space="preserve">"Le parcourt de Spinoza" par Essence des Livres</t>
         </is>
       </c>
       <c r="H39" s="49" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="G78" s="49" t="inlineStr">
         <is>
-          <t>"L'utilitarisme" par le Précepteur</t>
+          <t xml:space="preserve">"L'utilitarisme" par Le Précepteur</t>
         </is>
       </c>
       <c r="H78" s="49" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="G86" s="45" t="inlineStr">
         <is>
-          <t>saint simon – transformer la société par therence carvalho</t>
+          <t xml:space="preserve">saint simon – transformer la société par Thérence Carvalho</t>
         </is>
       </c>
       <c r="H86" s="45" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="L26" s="46" t="inlineStr">
         <is>
-          <t>Rationalisme</t>
+          <t xml:space="preserve">Rationalisme ; Oecuménisme</t>
         </is>
       </c>
       <c r="M26" s="35" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="L31" s="46" t="inlineStr">
         <is>
-          <t>Humanisme ; Pansophisme</t>
+          <t xml:space="preserve">Humanisme ; Pansophisme ; Oecuménisme</t>
         </is>
       </c>
       <c r="M31" s="35" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="L42" s="46" t="inlineStr">
         <is>
-          <t>Rationalisme ; Fatalisme</t>
+          <t xml:space="preserve">Rationalisme ; Fatalisme ; Oecuménisme</t>
         </is>
       </c>
       <c r="M42" s="35" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="L67" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Criticisme ; Agnosticisme ; Anthropocentrisme ; Constructivisme ; Lumières</t>
+          <t xml:space="preserve">Criticisme ; Agnosticisme ; Anthropocentrisme ; Constructivisme ; Lumières ; Déontologisme</t>
         </is>
       </c>
       <c r="M67" s="35" t="inlineStr">
@@ -7003,6 +7003,118 @@
       <c r="P96">
         <v>2</v>
       </c>
+    </row>
+    <row r="97" ht="130.5" customHeight="1" s="39">
+      <c r="A97" s="47">
+        <v>1530</v>
+      </c>
+      <c r="B97" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1596</t>
+        </is>
+      </c>
+      <c r="C97" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1530 – 1596</t>
+        </is>
+      </c>
+      <c r="D97" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jean BODIN</t>
+        </is>
+      </c>
+      <c r="E97" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Bodin" title=" Wikipedia"&gt;Jean BODIN&lt;/a&gt; est un juriste, philosophe et économiste français de la Renaissance, le grand théoricien de la &lt;a href="https://fr.wikipedia.org/wiki/Souverainet%C3%A9" title=" Wikipedia"&gt;souveraineté&lt;/a&gt;. Né à Angers vers 1530, il est d’abord moine carme, puis étudie et enseigne le droit à Toulouse avant de devenir avocat au Parlement de Paris. Il vit les guerres de Religion qui déchirent la France. Député du tiers état aux états généraux de Blois en 1576, il s’oppose à la reprise de la guerre contre les protestants et à la vente du domaine royal. Il finit procureur du roi à Laon, où il meurt de la peste en 1596.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Six Livres de la République&lt;/em&gt; (1576), il définit l’État par la souveraineté, « puissance absolue et perpétuelle d’une République ». Elle est indivisible, et son premier attribut est de « donner et casser la loi » sans le consentement de personne. Le souverain reste pourtant soumis aux lois de Dieu et de la nature : il doit respecter la propriété de ses sujets et ne peut lever d’impôt sans leur accord. Écrite contre l’anarchie des guerres civiles, cette théorie prépare la monarchie absolue et toute la pensée moderne de l’État, de Hobbes à Rousseau. Bodin y expose aussi une théorie des climats que reprendra Montesquieu.&lt;/p&gt; &lt;p&gt;Il est aussi l’un des premiers économistes. Dans sa &lt;em&gt;Réponse aux paradoxes de M. de Malestroit&lt;/em&gt; (1568), il explique la hausse des prix qui frappe l’Europe par l’afflux de l’or et de l’argent d’Amérique : c’est une première forme de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_quantitative_de_la_monnaie" title=" Wikipedia"&gt;théorie quantitative de la monnaie&lt;/a&gt;. Partisan d’un commerce actif et de la protection des manufactures, il annonce le &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt;. Son &lt;em&gt;Colloque des sept sages&lt;/em&gt; fait dialoguer un catholique, un luthérien, un calviniste, un juif, un musulman, un partisan de la religion naturelle et un sceptique, sans désigner de vainqueur : un plaidoyer pour la tolérance. Mais le même Bodin publie en 1580 une &lt;em&gt;Démonomanie des sorciers&lt;/em&gt; qui encourage leur persécution.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/bodin-mini.webp</t>
+        </is>
+      </c>
+      <c r="J97" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K97" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L97" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Mercantilisme</t>
+        </is>
+      </c>
+      <c r="M97" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juriste et philosophe français, théoricien de la souveraineté et pionnier de la pensée économique.</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P97"/>
+    </row>
+    <row r="98" ht="130.5" customHeight="1" s="39">
+      <c r="A98" s="47">
+        <v>1575</v>
+      </c>
+      <c r="B98" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1621</t>
+        </is>
+      </c>
+      <c r="C98" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1575 – 1621</t>
+        </is>
+      </c>
+      <c r="D98" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antoine de MONTCHRESTIEN</t>
+        </is>
+      </c>
+      <c r="E98" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine_de_Montchrestien" title=" Wikipedia"&gt;Antoine de MONTCHRESTIEN&lt;/a&gt; est un dramaturge et économiste français, l’inventeur de l’expression « &lt;a href="https://fr.wikipedia.org/wiki/%C3%89conomie_politique" title=" Wikipedia"&gt;économie politique&lt;/a&gt; ». Né à Falaise, en Normandie, vers 1575, fils d’un apothicaire, il se fait d’abord connaître comme poète tragique : sa tragédie &lt;em&gt;L’Écossaise&lt;/em&gt;, sur la mort de Marie Stuart, est l’une des premières pièces françaises consacrées à l’histoire récente. Après avoir tué un adversaire en duel, il s’exile en Angleterre et aux Pays-Bas, où il observe l’essor du commerce et des manufactures.&lt;/p&gt; &lt;p&gt;Revenu en France, il fonde une fabrique de couteaux et d’outils, et publie en 1615 son &lt;em&gt;Traité de l’économie politique&lt;/em&gt;, dédié au jeune Louis XIII et à sa mère Marie de Médicis. Le titre est nouveau : l’« économie », qui désignait chez Aristote la gestion de la maison, devient la science de la richesse de tout le royaume. Pour Montchrestien, la vraie richesse n’est pas seulement l’or, mais le travail des hommes et l’abondance des choses nécessaires. Le roi doit développer les manufactures, mettre les oisifs au travail, réserver le marché national aux produits français, protéger la marine et fonder des colonies. Il dénonce les marchands étrangers qui s’enrichissent aux dépens de la France.&lt;/p&gt; &lt;p&gt;Ces idées font de lui l’un des grands auteurs du &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt; français, que la politique de Colbert mettra en œuvre un demi-siècle plus tard. Protestant, Montchrestien prend part au soulèvement huguenot de 1621 ; il est tué dans une embuscade près de Domfront, et son corps est jugé, puis brûlé. Son traité, longtemps oublié, a été redécouvert au XIXe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/montchrestien-mini.webp</t>
+        </is>
+      </c>
+      <c r="J98" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K98" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique</t>
+        </is>
+      </c>
+      <c r="L98" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mercantilisme</t>
+        </is>
+      </c>
+      <c r="M98" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dramaturge et économiste français, inventeur de l’expression « économie politique ».</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P98"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -925,7 +925,7 @@
       </c>
       <c r="E5" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/%C3%89rasme"  title=" Wikipedia"&gt;ÉRASME de Rotterdam&lt;/a&gt; était un philosophe et Humaniste, un mouvement &lt;a href="https://www.youtube.com/watch?v=yIz5ltk3lJA&amp;ab_channel=Rienneveutriendire"  title="Portrait d'un intellectuel par Rien ne veut rien dire"&gt;intellectuel&lt;/a&gt; qui a émergé pendant la Renaissance en Europe et qui a mis l'accent sur l'importance de l'individu, de la raison et de l'éducation. Il croyait que l'éducation était la clé pour améliorer la vie humaine et promouvoir le progrès social. &lt;/p&gt; &lt;p&gt; Il a écrit de nombreux livres, notamment &lt;a href="https://www.youtube.com/watch?v=bwZbMqs9F1w&amp;ab_channel=%C3%89ditionsDianedeSelliers"  title="l'Eloge de la folie illustré par les peintres de la Renaissance du Nord par Diane de Selliers"&gt;"L'Éloge de la Folie"&lt;/a&gt; où il présente la Folie comme une divinité qui, par son pouvoir, rend supportable la vie humaine et les faiblesses de l'humanité. et "Le Manuel du Chrétien", qui ont été largement lus et influents à l'époque. &lt;/p&gt; &lt;p&gt; Érasme a également travaillé à la réforme de l'Église catholique et a critiqué les abus et les excès de l'Église de son époque. Il a plaidé pour un retour aux sources du christianisme, en se basant sur les textes originaux de la Bible, plutôt que sur les traditions et les dogmes de l'Église. Il avait un grand intérêt pour la musique, qu'il considérait comme un moyen important pour les gens de se rapprocher de Dieu et d'atteindre un état de bien-être spirituel.&lt;/p&gt; &lt;p&gt;
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/%C3%89rasme"  title=" Wikipedia"&gt;ÉRASME de Rotterdam&lt;/a&gt; était un philosophe et Humaniste, un mouvement &lt;a href="https://www.youtube.com/watch?v=yIz5ltk3lJA&amp;ab_channel=Rienneveutriendire"  title="Portrait d'un intellectuel par Rien ne veut rien dire"&gt;intellectuel&lt;/a&gt; qui a émergé pendant la Renaissance en Europe et qui a mis l'accent sur l'importance de l'individu, de la raison et de l'éducation. Il croyait que l'éducation était la clé pour améliorer la vie humaine et promouvoir le progrès social. &lt;/p&gt; &lt;p&gt; Il a écrit de nombreux livres, notamment &lt;a href="https://www.youtube.com/watch?v=bwZbMqs9F1w&amp;ab_channel=%C3%89ditionsDianedeSelliers"  title="l'Eloge de la folie illustré par les peintres de la Renaissance du Nord par Diane de Selliers"&gt;"L'Éloge de la Folie"&lt;/a&gt; où il présente la Folie comme une divinité qui, par son pouvoir, rend supportable la vie humaine et les faiblesses de l'humanité, et "Le Manuel du Chrétien", qui ont été largement lus et influents à l'époque. &lt;/p&gt; &lt;p&gt; Érasme a également travaillé à la réforme de l'Église catholique et a critiqué les abus et les excès de l'Église de son époque. Il a plaidé pour un retour aux sources du christianisme, en se basant sur les textes originaux de la Bible, plutôt que sur les traditions et les dogmes de l'Église. Il avait un grand intérêt pour la musique, qu'il considérait comme un moyen important pour les gens de se rapprocher de Dieu et d'atteindre un état de bien-être spirituel.&lt;/p&gt; &lt;p&gt;
 Il a lui-même joué de plusieurs instruments de musique, dont le luth et l'orgue et a également &lt;a href="https://www.youtube.com/watch?v=byUyM3fwf5Y&amp;ab_channel=KARLMORE"   title="Marche guérrière ottomane par Karl More"&gt;écrit sur la musique&lt;/a&gt;  dans plusieurs de ses œuvres, y compris dans "De ratione studii puerilis".   &lt;/p&gt;   &lt;audio controls title="Erasme, l'Européen par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-27.07.2019-ITEMA_22116176-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
@@ -993,7 +993,7 @@
       </c>
       <c r="E6" s="50" t="inlineStr">
         <is>
-          <t>&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Machiavel" title=" Wikipedia"&gt;Nicolas MACHIAVEL&lt;/a&gt; était un philosophe italien connu pour son livre &lt;a href="https://www.youtube.com/watch?v=x4z-TLoOQ5Q&amp;ab_channel=AlainBajom%C3%A9ef"    title="Le Prince par Alain Bajomée"&gt; "Le Prince" &lt;/a&gt;, publié en 1532, qui aborde les thèmes de la politique et de la tactique politique ou &lt;a href="https://www.youtube.com/watch?v=9tt12zMrx3M&amp;ab_channel=LePr%C3%A9cepteur"  title="L'art de gouverner par le Précepteur"&gt; "l'Art de Gouverner" &lt;/a&gt; et où il  plaide en faveur de la raison d'État, une approche selon laquelle les dirigeants doivent faire des choix politiques en fonction des intérêts de l'État, même si cela signifie enfreindre les normes éthiques ou morales.&lt;/p&gt;  &lt;p&gt; Cet ouvrage  est un traité pragmatique sur l'art de gouverner, prônant l'usage de la ruse, de la force et de la virtù (énergie audacieuse) pour maintenir le pouvoir, où la fin justifie les moyens. Il écrit aussi les Discours sur la première décade de Tite-Live (favorisant les républiques), L'Art de la guerre et la comédie &lt;a href="https://www.youtube.com/watch?v=mN425No69K4"  title="La philosophie de Machiavel par Parole de philosophes"&gt; La Mandragore &lt;/a&gt;. Ces textes analysent l'histoire romaine pour en tirer des leçons politiques concrètes.   &lt;p&gt;  Il sépare la politique de la morale et de la religion, la fondant sur l'expérience historique et le réalisme : le dirigeant doit inspirer la crainte plus que l'amour si nécessaire, et s'adapter aux circonstances (fortuna) par la virtù. Pour lui, la politique repose sur le mouvement, le conflit et la rhétorique persuasive, préfigurant une science laïque &lt;a href="https://www.youtube.com/watch?v=QP_o9y1B1nw"  title="Machiavel c’est quoi le pouvoir par Kosmos"&gt; du pouvoir &lt;/a&gt;. Son nom a donné l'adjectif "machiavélique", connotant ruse et cynisme, bien qu'il visait surtout l'unité italienne face aux divisions de l'époque.https://www.youtube.com/watch?v=YoYshBzpaqY   Il soutient également que les dirigeants doivent être prêts à utiliser la force pour maintenir le pouvoir et la stabilité de l'État. Il inspirera tous les grands hommes d'Etat, de Mitterrand à De Gaulle en passant par Churchill et Napoléon. &lt;/p&gt; &lt;p&gt;  En raison de ses idées controversées, il a souvent été considéré comme un théoricien de la tyrannie et de la manipulation politique.&lt;/p&gt; &lt;p&gt;  Malgré les accusations de cruauté et de déshumanisation, ses pensées continuent d'être étudiées et on utilise le terme de 'machiavélique' aujourd'hui dans la langue Française. &lt;/&gt;  &lt;audio controls title="Machiavel, le précurseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21877-15.03.2022-ITEMA_22963725-2022C42575E0002-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Machiavel" title=" Wikipedia"&gt;Nicolas MACHIAVEL&lt;/a&gt; était un philosophe italien connu pour son livre &lt;a href="https://www.youtube.com/watch?v=x4z-TLoOQ5Q&amp;ab_channel=AlainBajom%C3%A9ef"    title="Le Prince par Alain Bajomée"&gt; "Le Prince"&lt;/a&gt;, publié en 1532, qui aborde les thèmes de la politique et de la tactique politique ou &lt;a href="https://www.youtube.com/watch?v=9tt12zMrx3M&amp;ab_channel=LePr%C3%A9cepteur"  title="L'art de gouverner par le Précepteur"&gt; "l'Art de Gouverner" &lt;/a&gt; et où il  plaide en faveur de la raison d'État, une approche selon laquelle les dirigeants doivent faire des choix politiques en fonction des intérêts de l'État, même si cela signifie enfreindre les normes éthiques ou morales.&lt;/p&gt;  &lt;p&gt; Cet ouvrage  est un traité pragmatique sur l'art de gouverner, prônant l'usage de la ruse, de la force et de la virtù (énergie audacieuse) pour maintenir le pouvoir, où la fin justifie les moyens. Il écrit aussi les Discours sur la première décade de Tite-Live (favorisant les républiques), L'Art de la guerre et la comédie &lt;a href="https://www.youtube.com/watch?v=mN425No69K4"  title="La philosophie de Machiavel par Parole de philosophes"&gt; La Mandragore&lt;/a&gt;. Ces textes analysent l'histoire romaine pour en tirer des leçons politiques concrètes.   &lt;p&gt;  Il sépare la politique de la morale et de la religion, la fondant sur l'expérience historique et le réalisme : le dirigeant doit inspirer la crainte plus que l'amour si nécessaire, et s'adapter aux circonstances (fortuna) par la virtù. Pour lui, la politique repose sur le mouvement, le conflit et la rhétorique persuasive, préfigurant une science laïque &lt;a href="https://www.youtube.com/watch?v=QP_o9y1B1nw"  title="Machiavel c’est quoi le pouvoir par Kosmos"&gt; du pouvoir&lt;/a&gt;. Son nom a donné l'adjectif "machiavélique", connotant ruse et cynisme, bien qu'il visait surtout l'unité italienne face aux divisions de l'époque.https://www.youtube.com/watch?v=YoYshBzpaqY   Il soutient également que les dirigeants doivent être prêts à utiliser la force pour maintenir le pouvoir et la stabilité de l'État. Il inspirera tous les grands hommes d'Etat, de Mitterrand à De Gaulle en passant par Churchill et Napoléon. &lt;/p&gt; &lt;p&gt;  En raison de ses idées controversées, il a souvent été considéré comme un théoricien de la tyrannie et de la manipulation politique.&lt;/p&gt; &lt;p&gt;  Malgré les accusations de cruauté et de déshumanisation, ses pensées continuent d'être étudiées et on utilise le terme de 'machiavélique' aujourd'hui dans la langue Française. &lt;/&gt;  &lt;audio controls title="Machiavel, le précurseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21877-15.03.2022-ITEMA_22963725-2022C42575E0002-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F6" s="47" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="E14" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Calvin"   title=" Wikipedia"&gt;Jean CALVIN&lt;/a&gt; était un théologien, pasteur et réformateur français qui a joué un rôle central dans le développement du protestantisme, en particulier de la branche réformée, mouvement de contestation de l'autorité de l'Église catholique romaine et de retour aux sources bibliques. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus importante est  &lt;a href="https://www.youtube.com/watch?v=O1w5GbNMX0Y"  title="L'institution de la religion par Musée protestant "&gt;"L'Institution de la religion chrétienne"&lt;/a&gt; (1536) . Elle expose de manière systématique les principes de la foi réformée. Voici les idées clés de cette œuvre : &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Calvin"   title=" Wikipedia"&gt;Jean CALVIN&lt;/a&gt; était un théologien, pasteur et réformateur français qui a joué un rôle central dans le développement du protestantisme, en particulier de la branche réformée, mouvement de contestation de l'autorité de l'Église catholique romaine et de retour aux sources bibliques. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus importante est  &lt;a href="https://www.youtube.com/watch?v=O1w5GbNMX0Y"  title="L'institution de la religion par Musée protestant "&gt;"L'Institution de la religion chrétienne"&lt;/a&gt; (1536). Elle expose de manière systématique les principes de la foi réformée. Voici les idées clés de cette œuvre : &lt;/p&gt;
 &lt;dd&gt; - La souveraineté de Dieu : Il insiste sur la toute-puissance et la souveraineté absolue de Dieu. Tout ce qui arrive est selon la volonté divine. &lt;/dd&gt;
 &lt;dd&gt; -  La prédestination : Il développe la doctrine de la prédestination, selon laquelle Dieu a choisi de toute éternité ceux qui seront sauvés (les élus) et ceux qui seront damnés (les réprouvés). &lt;/dd&gt;
 &lt;dd&gt; -  L'autorité des Écritures : Pour lui, la Bible est la seule autorité en matière de foi et de pratique religieuse. Il rejette les traditions et les dogmes de l'Église qui ne sont pas explicitement fondés sur les Écritures. &lt;/dd&gt;
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_de_La_Ram%C3%A9e"   title=" Wikipedia"&gt;Pierre de la RAMÉE&lt;/a&gt; , plus connu sous son nom latin de Petrus Ramus ou Ramus, était un philosophe, logicien, rhétoricien et pédagogue français de la Renaissance.  Il appartient au contexte intellectuel de l’humanisme et de la Réforme. Issu d’un milieu modeste, il parvient à étudier à Paris et devient professeur. Sa pensée s’inscrit dans une volonté générale de réformer l’enseignement et de rendre les savoirs plus clairs, plus pratiques et mieux organisés. &lt;/p&gt; &lt;p&gt; Sa philosophie se construit d’abord contre la scolastique et contre l’autorité excessive accordée à Aristote dans les universités. En 1543, ses Aristotelicae Animadversiones critiquent vivement la logique aristotélicienne et provoquent un scandale académique. Il ne rejette cependant pas toute la philosophie d’Aristote : il conteste surtout l’usage mécanique et scolaire de ses textes. Pour lui, on ne doit pas accepter une proposition parce qu’elle vient d’une autorité, mais l’examiner par la raison et par l’expérience du discours. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la dialectique, qu’il identifie largement à la logique. Celle-ci est, selon lui, &lt;a href="https://www.youtube.com/watch?v=06iiHDjuuqU"  title="Petrus ramus par vis philo "&gt;l’« art de bien disserter » &lt;/a&gt; et se divise en deux opérations fondamentales : l’invention et le jugement. L’invention consiste à trouver les idées, les arguments et les preuves nécessaires à l’examen d’une question ; le jugement consiste ensuite à les évaluer et à les ordonner. Il simplifie ainsi la logique traditionnelle afin de la rapprocher de l’activité concrète de penser, d’argumenter et d’enseigner. &lt;/p&gt; &lt;p&gt; Il accorde également une importance décisive à la méthode en cherchant à organiser les connaissances selon une progression rationnelle, allant généralement du général au particulier, par définitions, divisions et exemples. Une méthode correcte doit ne retenir que ce qui est vrai et nécessaire, respecter le domaine propre de chaque discipline et traiter le général comme général et le particulier comme particulier. Cette conception contribue à faire de la méthode un problème central de la philosophie moderne et annonce, sur certains points, les préoccupations de penseurs comme Descartes, même si il ne peut pas être considéré comme un simple précurseur du cartésianisme. &lt;/p&gt; &lt;p&gt; Sa pensée est inséparable d’un projet de réforme de l’éducation. Il veut   &lt;a href="https://www.persee.fr/doc/rhren_0181-6799_2002_num_54_1_2510"  title="pierre de la ramée grammaire par persée "&gt;enseigner la grammaire, &lt;/a&gt;  la rhétorique, les mathématiques et les sciences selon des plans ordonnés, accessibles et utiles. Ses manuels de logique et de dialectique connaissent une large diffusion en Europe, notamment sa Dialectique de 1555, l’un des premiers grands ouvrages de logique publiés dans une langue moderne. Son influence fut importante, mais son système a aussi été critiqué parce qu’il réduisait parfois la richesse de la logique, de la rhétorique et de la philosophie à des schémas méthodiques. Ramus reste ainsi une figure majeure de la Renaissance : moins un philosophe spéculatif qu’un réformateur de la pensée, du langage et de l’enseignement. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_de_La_Ram%C3%A9e"   title=" Wikipedia"&gt;Pierre de la RAMÉE&lt;/a&gt;, plus connu sous son nom latin de Petrus Ramus ou Ramus, était un philosophe, logicien, rhétoricien et pédagogue français de la Renaissance.  Il appartient au contexte intellectuel de l’humanisme et de la Réforme. Issu d’un milieu modeste, il parvient à étudier à Paris et devient professeur. Sa pensée s’inscrit dans une volonté générale de réformer l’enseignement et de rendre les savoirs plus clairs, plus pratiques et mieux organisés. &lt;/p&gt; &lt;p&gt; Sa philosophie se construit d’abord contre la scolastique et contre l’autorité excessive accordée à Aristote dans les universités. En 1543, ses Aristotelicae Animadversiones critiquent vivement la logique aristotélicienne et provoquent un scandale académique. Il ne rejette cependant pas toute la philosophie d’Aristote : il conteste surtout l’usage mécanique et scolaire de ses textes. Pour lui, on ne doit pas accepter une proposition parce qu’elle vient d’une autorité, mais l’examiner par la raison et par l’expérience du discours. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la dialectique, qu’il identifie largement à la logique. Celle-ci est, selon lui, &lt;a href="https://www.youtube.com/watch?v=06iiHDjuuqU"  title="Petrus ramus par vis philo "&gt;l’« art de bien disserter » &lt;/a&gt; et se divise en deux opérations fondamentales : l’invention et le jugement. L’invention consiste à trouver les idées, les arguments et les preuves nécessaires à l’examen d’une question ; le jugement consiste ensuite à les évaluer et à les ordonner. Il simplifie ainsi la logique traditionnelle afin de la rapprocher de l’activité concrète de penser, d’argumenter et d’enseigner. &lt;/p&gt; &lt;p&gt; Il accorde également une importance décisive à la méthode en cherchant à organiser les connaissances selon une progression rationnelle, allant généralement du général au particulier, par définitions, divisions et exemples. Une méthode correcte doit ne retenir que ce qui est vrai et nécessaire, respecter le domaine propre de chaque discipline et traiter le général comme général et le particulier comme particulier. Cette conception contribue à faire de la méthode un problème central de la philosophie moderne et annonce, sur certains points, les préoccupations de penseurs comme Descartes, même si il ne peut pas être considéré comme un simple précurseur du cartésianisme. &lt;/p&gt; &lt;p&gt; Sa pensée est inséparable d’un projet de réforme de l’éducation. Il veut   &lt;a href="https://www.persee.fr/doc/rhren_0181-6799_2002_num_54_1_2510"  title="pierre de la ramée grammaire par persée "&gt;enseigner la grammaire, &lt;/a&gt;  la rhétorique, les mathématiques et les sciences selon des plans ordonnés, accessibles et utiles. Ses manuels de logique et de dialectique connaissent une large diffusion en Europe, notamment sa Dialectique de 1555, l’un des premiers grands ouvrages de logique publiés dans une langue moderne. Son influence fut importante, mais son système a aussi été critiqué parce qu’il réduisait parfois la richesse de la logique, de la rhétorique et de la philosophie à des schémas méthodiques. Ramus reste ainsi une figure majeure de la Renaissance : moins un philosophe spéculatif qu’un réformateur de la pensée, du langage et de l’enseignement. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t>&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne"  title=" Wikipedia"&gt; Michel de MONTAIGNE&lt;/a&gt; était un philosophe, écrivain français qui naquit près de Bordeaux, issu d’une famille de la petite noblesse terrienne. Après des études de droit, il exerce des fonctions de magistrat au Parlement de Bordeaux de 1557 à 1571, puis se retire de la vie publique pour se consacrer à la réflexion et à l’écriture. &lt;/p&gt; &lt;p&gt; Son œuvre majeure est &lt;a href="https://www.youtube.com/watch?v=qKXwK8Sj-24&amp;ab_channel=Kosmos" title="Les Essais par Kosmos"&gt; &lt;en&gt; Les Essais &lt;/em&gt;&lt;/a&gt;, publiés en trois livres entre 1580 et 1588, qu’il réécrit et enrichit tout au long de sa vie. Il livre aussi une traduction de la Théologie naturelle de Raymond Sebond (1569) et un Journal de voyage en Italie publié après sa mort, qui montre son goût pour l’observation concrète du monde. Il part de son expérience personnelle (sa santé, ses habitudes, ses lectures, ses voyages) pour &gt;&lt;a href="https://www.youtube.com/watch?v=dIH-Pg1q1pE"  title=" La Philosophie de Montaigne par Paroles de philosophe"&gt;interroger l’homme &lt;/a&gt;, la connaissance, la mort, l’amitié ou l’éducation, en adoptant un ton très libre et décousu. Il met en doute les certitudes de la science ou de la religion de son époque, prône la curiosité, la tolérance et la connaissance de soi, et ouvre la voie au relativisme et au scepticisme moderne. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs du &lt;a href="https://www.youtube.com/watch?v=IcW1ZnRUoGI"  title="Le scepticisme de Montaigne par Le Prisme Humain"&gt;scepticisme moderne &lt;/a&gt;, une approche philosophique qui remet en question la capacité de la raison humaine à atteindre une vérité absolue. Il est également connu pour sa conception de la philosophie comme une pratique personnelle de l'auto-examen et de la réflexion sur soi. Il croyait que la sagesse ne pouvait pas être trouvée dans les livres ou les enseignements des autres, mais devait être découverte à travers l'expérience de la vie et la contemplation de soi. &lt;/p&gt; &lt;p&gt; Il pronait la tolérance religieuse et la coexistence pacifique des différentes religions. Il était aussi un défenseur de la liberté de pensée et d'expression car les individus devaient être libres de penser et de s'exprimer sans crainte de persécution. &lt;/p&gt; &lt;p&gt; Il est important d'accepter notre nature humaine et ne pas essayer de nous conformer à des normes artificielles ou idéalisées. Il a écrit sur &lt;a href="https://preo.u-bourgogne.fr/shc/index.php?id=78" title="La vanité par Ed LETS"&gt;la vanité &lt;/a&gt; de l'homme et la nécessité de reconnaître nos faiblesses et nos imperfections.  &lt;/p&gt; &lt;audio controls title="La fable de l'identité  par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/03/s11/RF_B993FBEB-CED3-4D8B-A48F-2D502E485A89_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne"  title=" Wikipedia"&gt; Michel de MONTAIGNE&lt;/a&gt; était un philosophe, écrivain français qui naquit près de Bordeaux, issu d’une famille de la petite noblesse terrienne. Après des études de droit, il exerce des fonctions de magistrat au Parlement de Bordeaux de 1557 à 1571, puis se retire de la vie publique pour se consacrer à la réflexion et à l’écriture. &lt;/p&gt; &lt;p&gt; Son œuvre majeure est &lt;a href="https://www.youtube.com/watch?v=qKXwK8Sj-24&amp;ab_channel=Kosmos" title="Les Essais par Kosmos"&gt; &lt;en&gt; Les Essais&lt;/em&gt;&lt;/a&gt;, publiés en trois livres entre 1580 et 1588, qu’il réécrit et enrichit tout au long de sa vie. Il livre aussi une traduction de la Théologie naturelle de Raymond Sebond (1569) et un Journal de voyage en Italie publié après sa mort, qui montre son goût pour l’observation concrète du monde. Il part de son expérience personnelle (sa santé, ses habitudes, ses lectures, ses voyages) pour &gt;&lt;a href="https://www.youtube.com/watch?v=dIH-Pg1q1pE"  title=" La Philosophie de Montaigne par Paroles de philosophe"&gt;interroger l’homme&lt;/a&gt;, la connaissance, la mort, l’amitié ou l’éducation, en adoptant un ton très libre et décousu. Il met en doute les certitudes de la science ou de la religion de son époque, prône la curiosité, la tolérance et la connaissance de soi, et ouvre la voie au relativisme et au scepticisme moderne. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs du &lt;a href="https://www.youtube.com/watch?v=IcW1ZnRUoGI"  title="Le scepticisme de Montaigne par Le Prisme Humain"&gt;scepticisme moderne&lt;/a&gt;, une approche philosophique qui remet en question la capacité de la raison humaine à atteindre une vérité absolue. Il est également connu pour sa conception de la philosophie comme une pratique personnelle de l'auto-examen et de la réflexion sur soi. Il croyait que la sagesse ne pouvait pas être trouvée dans les livres ou les enseignements des autres, mais devait être découverte à travers l'expérience de la vie et la contemplation de soi. &lt;/p&gt; &lt;p&gt; Il pronait la tolérance religieuse et la coexistence pacifique des différentes religions. Il était aussi un défenseur de la liberté de pensée et d'expression car les individus devaient être libres de penser et de s'exprimer sans crainte de persécution. &lt;/p&gt; &lt;p&gt; Il est important d'accepter notre nature humaine et ne pas essayer de nous conformer à des normes artificielles ou idéalisées. Il a écrit sur &lt;a href="https://preo.u-bourgogne.fr/shc/index.php?id=78" title="La vanité par Ed LETS"&gt;la vanité &lt;/a&gt; de l'homme et la nécessité de reconnaître nos faiblesses et nos imperfections.  &lt;/p&gt; &lt;audio controls title="La fable de l'identité  par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/03/s11/RF_B993FBEB-CED3-4D8B-A48F-2D502E485A89_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F18" s="47" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E24" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tommaso_Campanella" title=" Wikipedia"&gt;Tommaso CAMPANELLA&lt;/a&gt; était  un philosophe, théologien et moine dominicain italien, connu pour ses   &lt;a href="https://www.youtube.com/watch?v=wAl4GvGSVJM" style="color:#88A1E9" title="Jean Delumeau : Le mystère Campanella par Canal Academies "&gt;idées utopiques&lt;/a&gt; , sa pensée politique audacieuse et son engagement en faveur d’une réforme sociale et religieuse.  Il sera marqué par la pensée d’Aristote, mais aussi par les idées novatrices de Bernardino Telesio, un philosophe naturaliste qui rejette l’aristotélisme traditionnel. &lt;/p&gt; &lt;p&gt; Il  s’oppose à l’autorité espagnole en Italie et participe à un complot visant à établir une république mais le projet échoue. Il est arrêté, torturé et condamné à mort, il simule la folie pour éviter l’exécution et passera 27 ans en prison, où il écrit son œuvre majeure : &lt;/p&gt; &lt;p&gt; -  &lt;a href="https://www.persee.fr/doc/barb_0001-4133_1992_num_3_1_38762" title="Tommaso Campanella, « La Cité du Soleil » par Persée "&gt;La Cité du Soleil&lt;/a&gt; : Utopie politique et sociale, inspirée de La République de Platon et de L'Utopie de Thomas More. Une société idéale gouvernée par des savants, où la propriété privée est abolie, les biens sont communs, et l’éducation est centralisée. &lt;/p&gt; &lt;p&gt; - Philosophia sensibus demonstrata : Il s’inspire de Telesio pour promouvoir une philosophie basée sur l’observation de la nature, rejetant la scolastique aristotélicienne.&lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tommaso_Campanella" title=" Wikipedia"&gt;Tommaso CAMPANELLA&lt;/a&gt; était  un philosophe, théologien et moine dominicain italien, connu pour ses   &lt;a href="https://www.youtube.com/watch?v=wAl4GvGSVJM" style="color:#88A1E9" title="Jean Delumeau : Le mystère Campanella par Canal Academies "&gt;idées utopiques&lt;/a&gt;, sa pensée politique audacieuse et son engagement en faveur d’une réforme sociale et religieuse.  Il sera marqué par la pensée d’Aristote, mais aussi par les idées novatrices de Bernardino Telesio, un philosophe naturaliste qui rejette l’aristotélisme traditionnel. &lt;/p&gt; &lt;p&gt; Il  s’oppose à l’autorité espagnole en Italie et participe à un complot visant à établir une république mais le projet échoue. Il est arrêté, torturé et condamné à mort, il simule la folie pour éviter l’exécution et passera 27 ans en prison, où il écrit son œuvre majeure : &lt;/p&gt; &lt;p&gt; -  &lt;a href="https://www.persee.fr/doc/barb_0001-4133_1992_num_3_1_38762" title="Tommaso Campanella, « La Cité du Soleil » par Persée "&gt;La Cité du Soleil&lt;/a&gt; : Utopie politique et sociale, inspirée de La République de Platon et de L'Utopie de Thomas More. Une société idéale gouvernée par des savants, où la propriété privée est abolie, les biens sont communs, et l’éducation est centralisée. &lt;/p&gt; &lt;p&gt; - Philosophia sensibus demonstrata : Il s’inspire de Telesio pour promouvoir une philosophie basée sur l’observation de la nature, rejetant la scolastique aristotélicienne.&lt;/p&gt; 
 &lt;p&gt; - Atheismus triumphatus : Critique de l’athéisme, mais aussi des dogmatismes religieux. Il prédit une réforme universelle de l’Église et de la société, influencé par le millénarisme (âge d’or futur). &lt;/p&gt; 
 &lt;p&gt; - Monarchie d'Espagne : Projet politique pour une monarchie universelle sous domination espagnole.  Il rejette la séparation de la morale et de la politique, prônant un État vertueux. &lt;/p&gt; &lt;p&gt; Il  reste une figure complexe, à mi-chemin entre mysticisme et rationalisme, dont les idées résonnent encore dans les débats sur la justice sociale et le rôle de la science. &lt;/p&gt; 
 </t>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E25" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jakob_B%C3%B6hme" title=" Wikipedia"&gt;Jacob BÖEHME&lt;/a&gt; était un philosophe mystique allemand  surnommé le  &lt;a href="https://www.youtube.com/watch?v=MZA137IGPB0&amp;t=761s" style="color:#88A1E9" title=" Jacob Boehme par Carmel de Saint-Elie"&gt; "Philosophus Teutonicus" &lt;/a&gt; et simple cordonnier sans éducation formelle. Pourtant, il a développé une pensée théosophique et philosophique d'une profondeur et d'une complexité   &lt;a href="https://livres-mystiques.com/partieTEXTES/Besson/Articles/boehm.html"  title="  Jacob BOEHME par Livres mystiques"&gt; remarquables&lt;/a&gt;, qu'il disait avoir reçue par des illuminations divines.&lt;/p&gt; &lt;p&gt;  L'une de ses idées les plus connues est celle de  &lt;a href="https://www.youtube.com/watch?v=krUTxK9Adks" title="  L’Ungrund, le sans-fond de Jacob Böhme par BAGLIS TV"&gt;  l'Ungrund &lt;/a&gt;, le "sans-fond"  où Dieu n'est pas un être statique, mais une réalité dynamique, insondable, d'où émergent les oppositions et la création. Cette dialectique entre le "oui" et le "non", la lumière et l'obscurité, le bien et le mal, est centrale à sa pensée. &lt;/p&gt; &lt;p&gt;  Il  s'est penché sur l'épineux problème de l'existence du mal dans un monde créé par un Dieu bon. Contrairement à d'autres théologiens qui le réduisaient à une simple absence du bien, il voyait le mal comme une composante nécessaire du processus divin de manifestation et de la liberté humaine. &lt;/p&gt; &lt;p&gt;  Parmi ses œuvres les plus importantes, on peut citer  &lt;a href="https://www.youtube.com/watch?v=hNRrhozhNSE"  title="  Le royaume Angelique par Dominique Debray"&gt; "L'Aurore naissante" &lt;/a&gt; , "Des trois principes de l'essence divine", "De la signature des choses"  et "De l'élection de la grâce" mais sa pensée non conventionnelle lui a valu d'être en butte aux critiques et aux persécutions de l'orthodoxie luthérienne de son temps, le forçant parfois à cesser d'écrire pendant un certain temps.&lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jakob_B%C3%B6hme" title=" Wikipedia"&gt;Jacob BÖEHME&lt;/a&gt; était un philosophe mystique allemand  surnommé le  &lt;a href="https://www.youtube.com/watch?v=MZA137IGPB0&amp;t=761s" style="color:#88A1E9" title=" Jacob Boehme par Carmel de Saint-Elie"&gt; "Philosophus Teutonicus" &lt;/a&gt; et simple cordonnier sans éducation formelle. Pourtant, il a développé une pensée théosophique et philosophique d'une profondeur et d'une complexité   &lt;a href="https://livres-mystiques.com/partieTEXTES/Besson/Articles/boehm.html"  title="  Jacob BOEHME par Livres mystiques"&gt; remarquables&lt;/a&gt;, qu'il disait avoir reçue par des illuminations divines.&lt;/p&gt; &lt;p&gt;  L'une de ses idées les plus connues est celle de  &lt;a href="https://www.youtube.com/watch?v=krUTxK9Adks" title="  L’Ungrund, le sans-fond de Jacob Böhme par BAGLIS TV"&gt;  l'Ungrund&lt;/a&gt;, le "sans-fond"  où Dieu n'est pas un être statique, mais une réalité dynamique, insondable, d'où émergent les oppositions et la création. Cette dialectique entre le "oui" et le "non", la lumière et l'obscurité, le bien et le mal, est centrale à sa pensée. &lt;/p&gt; &lt;p&gt;  Il  s'est penché sur l'épineux problème de l'existence du mal dans un monde créé par un Dieu bon. Contrairement à d'autres théologiens qui le réduisaient à une simple absence du bien, il voyait le mal comme une composante nécessaire du processus divin de manifestation et de la liberté humaine. &lt;/p&gt; &lt;p&gt;  Parmi ses œuvres les plus importantes, on peut citer  &lt;a href="https://www.youtube.com/watch?v=hNRrhozhNSE"  title="  Le royaume Angelique par Dominique Debray"&gt; "L'Aurore naissante"&lt;/a&gt;, "Des trois principes de l'essence divine", "De la signature des choses"  et "De l'élection de la grâce" mais sa pensée non conventionnelle lui a valu d'être en butte aux critiques et aux persécutions de l'orthodoxie luthérienne de son temps, le forçant parfois à cesser d'écrire pendant un certain temps.&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F25" s="47" t="inlineStr">
@@ -2336,9 +2336,9 @@
       </c>
       <c r="E26" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugo_Grotius" title=" Wikipedia"&gt;Hugo GROTUIS&lt;/a&gt; était une figure majeure de l'histoire intellectuelle Néerlandaise , juridique et politique, il est souvent considéré comme l'un des fondateurs du droit international moderne.  Il a vécu à une époque marquée par des conflits religieux et politiques intenses, notamment la guerre de Quatre-Vingts Ans entre les Pays-Bas et l'Espagne, ainsi que la guerre de Trente Ans en Europe. Ces conflits ont influencé sa pensée, notamment en ce qui concerne la nécessité d'un &lt;a href="https://www.youtube.com/watch?v=BoTTE8ohmJ0" style="color:#88A1E9" title="Le droit des gens et le droit international par Radio J "&gt;système juridique&lt;/a&gt; pour réguler les relations entre États. &lt;/p&gt; &lt;p&gt; Ses contributions majeures en droit international : &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugo_Grotius" title=" Wikipedia"&gt;Hugo GROTUIS&lt;/a&gt; était une figure majeure de l'histoire intellectuelle Néerlandaise, juridique et politique, il est souvent considéré comme l'un des fondateurs du droit international moderne.  Il a vécu à une époque marquée par des conflits religieux et politiques intenses, notamment la guerre de Quatre-Vingts Ans entre les Pays-Bas et l'Espagne, ainsi que la guerre de Trente Ans en Europe. Ces conflits ont influencé sa pensée, notamment en ce qui concerne la nécessité d'un &lt;a href="https://www.youtube.com/watch?v=BoTTE8ohmJ0" style="color:#88A1E9" title="Le droit des gens et le droit international par Radio J "&gt;système juridique&lt;/a&gt; pour réguler les relations entre États. &lt;/p&gt; &lt;p&gt; Ses contributions majeures en droit international : &lt;/p&gt;
 &lt;dd&gt; - &lt;a href="https://www.persee.fr/doc/ridc_0035-3337_1954_num_6_4_9126"  title="H Grotius par Persée "&gt;"De jure belli ac pacis"&lt;/a&gt;  (Du droit de la guerre et de la paix, 1625) : œuvres fondatrices du droit international. Il y développe l'idée que les relations entre États devraient être régies par des principes juridiques plutôt que par la force brute. Il introduit le concept de "droit naturel", qui est universel et immuable, et qui s'applique à tous les êtres humains, indépendamment de leur nationalité ou de leur religion. &lt;/dd&gt;
-&lt;dd&gt; - "Mare Liberum"   (La mer libre, 1609) : les mers doivent être libres d'accès pour tous les États, une idée qui a eu un impact sur le droit maritime international. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  Il a défendu l'idée que la souveraineté de l'État est limitée par le droit naturel et que les gouvernements ont des obligations envers leurs citoyens. ll a plaidé pour la tolérance religieuse et a cherché à réconcilier les différentes confessions chrétiennes. Son ouvrage &lt;a href="https://www.penseesdepascal.fr/General/Grotius.php" title="De veritate religionis christianae par penseesdepascal "&gt;"De veritate religionis Christianae" &lt;/a&gt; (Sur la vérité de la religion chrétienne) est une défense rationnelle du christianisme.&lt;/p&gt; &lt;p&gt; Il est souvent appelé le "père du droit international" et ses idées ont jeté les bases de nombreuses institutions internationales modernes, comme les Nations Unies. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; </t>
+&lt;dd&gt; - "Mare Liberum"   (La mer libre, 1609) : les mers doivent être libres d'accès pour tous les États, une idée qui a eu un impact sur le droit maritime international. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  Il a défendu l'idée que la souveraineté de l'État est limitée par le droit naturel et que les gouvernements ont des obligations envers leurs citoyens. Il a plaidé pour la tolérance religieuse et a cherché à réconcilier les différentes confessions chrétiennes. Son ouvrage &lt;a href="https://www.penseesdepascal.fr/General/Grotius.php" title="De veritate religionis christianae par penseesdepascal "&gt;"De veritate religionis Christianae" &lt;/a&gt; (Sur la vérité de la religion chrétienne) est une défense rationnelle du christianisme.&lt;/p&gt; &lt;p&gt; Il est souvent appelé le "père du droit international" et ses idées ont jeté les bases de nombreuses institutions internationales modernes, comme les Nations Unies. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F26" s="47" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="E29" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Heinrich_Alsted"  title=" Wikipedia"&gt;Johann Heinrich ALSTED&lt;/a&gt; était un théologien, philosophe et encyclopédiste protestant calviniste allemand, connu comme un polyhistor et un pionnier des encyclopédies modernes. Né à Ballersbach près d'Herborn, il enseigna la philosophie et la théologie à l'académie calviniste de Herborn, puis à Weissenburg en Transylvanie. Professeur influent, il fut impliqué dans la Synode de Dort et émigra en Transylvanie pour fuir les troubles religieux. Son élève Johann Amos Comenius diffusa largement ses idées en pédagogie et en réformes universelles. Il mourut en 1638, laissant une œuvre marquée par le ramisme, le lullisme et un chiliasme calviniste , &lt;/p&gt; &lt;p&gt; Il distinguait philosophie (raison, foedus naturae) et théologie (révélation, foedus gratiae), tout en cherchant une synthèse universelle des savoirs. Il intégrait logique ramiste, art de la mémoire lulliste et aristotélisme pour ordonner tout le savoir humain, visant une "réforme générale" hermétique et alchimique. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : - Encyclopaedia septem tomis distincta (1630) : Son chef-d'œuvre, un "système de tous les systèmes" résumant les disciplines (logique, physique, théologie), loué par ses contemporains. - Logicae Systema Harmonicum (1614) : Traité de logique appliquée à l'ensemble des connaissances. - Prodromus (1635) : Défense calviniste de la Trinité contre les anti-trinitariens.  Ses encyclopédies influencèrent la pédagogie européenne et les réformateurs du XVIIe siècle.  &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Heinrich_Alsted"  title=" Wikipedia"&gt;Johann Heinrich ALSTED&lt;/a&gt; était un théologien, philosophe et encyclopédiste protestant calviniste allemand, connu comme un polyhistor et un pionnier des encyclopédies modernes. Né à Ballersbach près d'Herborn, il enseigna la philosophie et la théologie à l'académie calviniste de Herborn, puis à Weissenburg en Transylvanie. Professeur influent, il fut impliqué dans la Synode de Dort et émigra en Transylvanie pour fuir les troubles religieux. Son élève Johann Amos Comenius diffusa largement ses idées en pédagogie et en réformes universelles. Il mourut en 1638, laissant une œuvre marquée par le ramisme, le lullisme et un chiliasme calviniste, &lt;/p&gt; &lt;p&gt; Il distinguait philosophie (raison, foedus naturae) et théologie (révélation, foedus gratiae), tout en cherchant une synthèse universelle des savoirs. Il intégrait logique ramiste, art de la mémoire lulliste et aristotélisme pour ordonner tout le savoir humain, visant une "réforme générale" hermétique et alchimique. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : - Encyclopaedia septem tomis distincta (1630) : Son chef-d'œuvre, un "système de tous les systèmes" résumant les disciplines (logique, physique, théologie), loué par ses contemporains. - Logicae Systema Harmonicum (1614) : Traité de logique appliquée à l'ensemble des connaissances. - Prodromus (1635) : Défense calviniste de la Trinité contre les anti-trinitariens.  Ses encyclopédies influencèrent la pédagogie européenne et les réformateurs du XVIIe siècle.  &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Comenius"  title=" Wikipedia"&gt;COMENIUS&lt;/a&gt;   de son nom tchèque Jan Amos Komenský, était un philosophe, théologien et pédagogue tchèque, considéré comme le père de la pédagogie moderne. Évêque des Frères moraves, il fuit les persécutions religieuses et erra en Europe, promouvant une éducation universelle &lt;a href="https://www.youtube.com/watch?v=oGscXWKpLAA"  title="comment donner accès à tous les savoirs par Benoit Urgelli"&gt;accessible à tous, &lt;/a&gt; y compris aux filles et aux pauvres. &lt;/p&gt; &lt;p&gt; Orphelin jeune, il étudie à l’université de Heidelberg et devient enseignant dans les écoles moraves. Exilé après la bataille de la Montagne Blanche (1620), il enseigne à Lissa, Amsterdam et ailleurs, influencé par Alsted dont il fut l’élève. Il meurt à Naarden aux Pays-Bas, rêvant d’une restauration de son pays. &lt;/p&gt; &lt;p&gt; Il  prône une "pansophie" : une sagesse universelle enseignant tout à tous via la nature, la raison et la révélation divine. Il rejette les châtiments corporels, favorise l’apprentissage naturel, ludique et progressif (du sensoriel à l’abstrait), avec &lt;a href="https://www.youtube.com/watch?v=CMFh0seMZUg"  title="The dramatic story on education par Czech the History"&gt;des écoles pour tous &lt;/a&gt; les âges et sexes. &lt;/p&gt; &lt;p&gt; Ses Oeuvres majeures majeures : - Didactica Magna (1657) : Traité sur l’art  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1969_num_49_1_3943"  title="Jean Amos COMENIUS par Persée"&gt; d’enseigner universellement, &lt;/a&gt; sans violence. - Orbis Sensualium Pictus (1658) : Premier manuel illustré bilingue pour enfants, associant mots et images.https://fr.wikipedia.org/wiki/Comenius - De Rerum Humanarum Emendatione : Consultation catholique pour une réforme mondiale du savoir et de la paix. Ses idées inspirèrent l’éducation européenne et l’UNESCO le nomme "Père de l’éducation". &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Comenius"  title=" Wikipedia"&gt;COMENIUS&lt;/a&gt;   de son nom tchèque Jan Amos Komenský, était un philosophe, théologien et pédagogue tchèque, considéré comme le père de la pédagogie moderne. Évêque des Frères moraves, il fuit les persécutions religieuses et erra en Europe, promouvant une éducation universelle &lt;a href="https://www.youtube.com/watch?v=oGscXWKpLAA"  title="comment donner accès à tous les savoirs par Benoit Urgelli"&gt;accessible à tous, &lt;/a&gt; y compris aux filles et aux pauvres. &lt;/p&gt; &lt;p&gt; Orphelin jeune, il étudie à l’université de Heidelberg et devient enseignant dans les écoles moraves. Exilé après la bataille de la Montagne Blanche (1620), il enseigne à Lissa, Amsterdam et ailleurs, influencé par Alsted dont il fut l’élève. Il meurt à Naarden aux Pays-Bas, rêvant d’une restauration de son pays. &lt;/p&gt; &lt;p&gt; Il  prône une "pansophie" : une sagesse universelle enseignant tout à tous via la nature, la raison et la révélation divine. Il rejette les châtiments corporels, favorise l’apprentissage naturel, ludique et progressif (du sensoriel à l’abstrait), avec &lt;a href="https://www.youtube.com/watch?v=CMFh0seMZUg"  title="The dramatic story on education par Czech the History"&gt;des écoles pour tous &lt;/a&gt; les âges et sexes. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : - Didactica Magna (1657) : Traité sur l’art  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1969_num_49_1_3943"  title="Jean Amos COMENIUS par Persée"&gt; d’enseigner universellement, &lt;/a&gt; sans violence. - Orbis Sensualium Pictus (1658) : Premier manuel illustré bilingue pour enfants, associant mots et images.https://fr.wikipedia.org/wiki/Comenius - De Rerum Humanarum Emendatione : Consultation catholique pour une réforme mondiale du savoir et de la paix. Ses idées inspirèrent l’éducation européenne et l’UNESCO le nomme "Père de l’éducation". &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="E35" s="58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Blaise_Pascal" title="Blaise PASCAL par Wikipédia"&gt; Blaise PASCAL&lt;/a&gt;  était un mathématicien, philosophe et écrivain français. Il a inventé à 19 ans, la première calculatrice mécanique, connue sous le nom de "machine de Pascal". Il fut ensuite célèbre pour son &lt;a href="https://blaisepascal.bibliotheques-clermontmetropole.eu/son-oeuvre/pascal-savant/mathematiques/le-triangle-arithmetique"  title="Le triangle arithmétique par Clermont metropole"&gt; "Triangle de Pascal" &lt;/a&gt;, un arrangement de nombres qui est devenu un élément fondamental de la théorie des probabilités et de l'algèbre combinatoire. Il a aussi étudié la pression atmosphérique et a contribué à la compréhension de la manière dont la pression varie avec l'altitude. L'unité de pression "pascal" (Pa) porte son nom.  &lt;/p&gt; &lt;p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Blaise_Pascal" title="Blaise PASCAL par Wikipédia"&gt; Blaise PASCAL&lt;/a&gt;  était un mathématicien, philosophe et écrivain français. Il a inventé à 19 ans, la première calculatrice mécanique, connue sous le nom de "machine de Pascal". Il fut ensuite célèbre pour son &lt;a href="https://blaisepascal.bibliotheques-clermontmetropole.eu/son-oeuvre/pascal-savant/mathematiques/le-triangle-arithmetique"  title="Le triangle arithmétique par Clermont metropole"&gt; "Triangle de Pascal"&lt;/a&gt;, un arrangement de nombres qui est devenu un élément fondamental de la théorie des probabilités et de l'algèbre combinatoire. Il a aussi étudié la pression atmosphérique et a contribué à la compréhension de la manière dont la pression varie avec l'altitude. L'unité de pression "pascal" (Pa) porte son nom.  &lt;/p&gt; &lt;p&gt;
 Il était un chrétien dévot, et sa philosophie a été profondément influencée par sa foi. Il a écrit &lt;a href="https://www.youtube.com/watch?v=3uIjGv6jfSE&amp;ab_channel=Kosmos"   title="Pensées par Kosmos"&gt; "Pensées"&lt;/a&gt;, ce recueil de pensées, d'aphorismes et de réflexions où  Il a développé l'argument connu sous le nom de &lt;a href="https://www.youtube.com/watch?v=FoWFLpm8eX0&amp;ab_channel=AlainBajom%C3%A9e"  title="Le pari de Pascal par Alain Bajomée"&gt; "pari de Pascal,"&lt;/a&gt; qui suggère que, même en l'absence de preuves rationnelles concluantes de l'existence de Dieu, il est plus raisonnable de &lt;a href="https://www.youtube.com/watch?v=6KLWy3dWFMw&amp;ab_channel=LePr%C3%A9cepteur"   title="le pari par Le Précepteur"&gt;parier sur son existence&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;   Voici quelques-unes des contributions les plus importantes : &lt;p&gt;
 &lt;dd&gt;  &lt;a href="https://www.youtube.com/watch?v=OL4fFfld9Pw&amp;ab_channel=Kosmos"  title="le pouvoir par Kosmos"&gt;- La condition humaine :&lt;/a&gt;  Il l'aborde avec une perspective réaliste et parfois pessimiste. Il explore la vulnérabilité de l'homme, sa nature pécheresse et sa tendance à la vanité. Il souligne également l'incertitude de la vie humaine et la fragilité de l'existence. &lt;/dd&gt;
 &lt;dd&gt;  - Le désespoir et l'angoisse : Il a exploré le sentiment de vide et de malaise que les êtres humains peuvent ressentir lorsqu'ils sont confrontés à l'absurdité de la vie. Il a suggéré que la quête de sens et de bonheur peut être trouvée dans une relation personnelle avec Dieu.  &lt;/dd&gt;
@@ -3220,7 +3220,7 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza"  title=" Wikipedia"&gt; Baruch SPINOZA&lt;/a&gt; était un philosophe hollandais et un penseur influent en opposition à Descartes en son époque. &lt;/p&gt; &lt;p&gt; Sa philosophie &lt;a href="https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur"  title="Le déterminisme par le Précepteur"&gt;Déterministe.&lt;/a&gt; se caractérise par sa vision &lt;a href="https://fr.wikipedia.org/wiki/Monisme"    title="Le monisme est la position philosophique qui affirme l'unité indivisible de l'être"&gt;moniste&lt;/a&gt; de l'univers, selon laquelle tout ce qui existe est une expression de la même substance divine, qu'il appelle &lt;a href="https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur"  title="Dieu égale nature"&gt;Dieu ou Nature&lt;/a&gt; et elle est souvent associée au rationalisme, à l'athéisme et au panthéisme. &lt;/p&gt; &lt;p&gt; Pour lui, la raison est la clé de la liberté et du bonheur. Il affirme que  &lt;a href="https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos"  title="Les passions tristes par Kosmos"&gt;les passions.&lt;/a&gt; peuvent nous éloigner de la vérité et nous rendre esclaves de nos désirs. &lt;/p&gt; &lt;p&gt;Pour être libre, l'homme doit comprendre la nature des choses et apprendre à contrôler ses passions. Cela implique une acceptation de la nécessité et de la causalité, car tout ce qui arrive est le résultat de la nature des choses et que, de ce fait, &lt;a  href="https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur"   title="Le libre arbitre n'est il qu'une illusion? par le Précepteur"&gt;le libre arbitre n'existe pas.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Dans sa célèbre œuvre "L'Éthique", il élabore une théorie éthique basée sur l'idée que la raison est la clé de la liberté et du bonheur avec sa notion de &lt;a href="https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur"   title="Le conatus par le Précepteur"&gt;"Conatus".&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; En politique, il est souvent associé à la défense de la liberté d'expression et de la tolérance religieuse. Il a écrit un ouvrage intitulé  &lt;a href="https://www.youtube.com/watch?v=Zqt0QZVrTkI"   title="Le Traité TP par PrepaUp"&gt;"Le Traité théologico-politique"&lt;/a&gt; dans lequel il soutient que la religion doit être séparée de l'État et que chacun doit être libre de pratiquer sa religion sans être persécuté.&lt;/p&gt;    &lt;audio controls title="Spinoza est il le philosophe du bonheur ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza"  title=" Wikipedia"&gt; Baruch SPINOZA&lt;/a&gt; était un philosophe hollandais et un penseur influent en opposition à Descartes en son époque. &lt;/p&gt; &lt;p&gt; Sa philosophie &lt;a href="https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur"  title="Le déterminisme par le Précepteur"&gt;déterministe&lt;/a&gt; se caractérise par sa vision &lt;a href="https://fr.wikipedia.org/wiki/Monisme"    title="Le monisme est la position philosophique qui affirme l'unité indivisible de l'être"&gt;moniste&lt;/a&gt; de l'univers, selon laquelle tout ce qui existe est une expression de la même substance divine, qu'il appelle &lt;a href="https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur"  title="Dieu égale nature"&gt;Dieu ou Nature&lt;/a&gt; et elle est souvent associée au rationalisme, à l'athéisme et au panthéisme. &lt;/p&gt; &lt;p&gt; Pour lui, la raison est la clé de la liberté et du bonheur. Il affirme que  &lt;a href="https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos"  title="Les passions tristes par Kosmos"&gt;les passions&lt;/a&gt; peuvent nous éloigner de la vérité et nous rendre esclaves de nos désirs. &lt;/p&gt; &lt;p&gt;Pour être libre, l'homme doit comprendre la nature des choses et apprendre à contrôler ses passions. Cela implique une acceptation de la nécessité et de la causalité, car tout ce qui arrive est le résultat de la nature des choses et que, de ce fait, &lt;a  href="https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur"   title="Le libre arbitre n'est il qu'une illusion? par le Précepteur"&gt;le libre arbitre n'existe pas.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Dans sa célèbre œuvre "L'Éthique", il élabore une théorie éthique basée sur l'idée que la raison est la clé de la liberté et du bonheur avec sa notion de &lt;a href="https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur"   title="Le conatus par le Précepteur"&gt;"Conatus".&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; En politique, il est souvent associé à la défense de la liberté d'expression et de la tolérance religieuse. Il a écrit un ouvrage intitulé  &lt;a href="https://www.youtube.com/watch?v=Zqt0QZVrTkI"   title="Le Traité TP par PrepaUp"&gt;"Le Traité théologico-politique"&lt;/a&gt; dans lequel il soutient que la religion doit être séparée de l'État et que chacun doit être libre de pratiquer sa religion sans être persécuté.&lt;/p&gt;    &lt;audio controls title="Spinoza est il le philosophe du bonheur ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
@@ -3295,9 +3295,9 @@
       </c>
       <c r="E40" s="49" t="inlineStr">
         <is>
-          <t>&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/John_Locke"  title=" Wikipedia"&gt;John LOCKE&lt;/a&gt; était un philosophe anglais connu pour ses contributions en philosophie politique, en épistémologie et en théorie de l'éducation. &lt;/p&gt; &lt;p&gt; L'une de ses idées les plus célèbres est celle de la tabula rasa, qui signifie "table rase" en latin. Selon lui, l'esprit humain est vide à la naissance, sans aucune connaissance innée ou idées préconçues. C'est seulement par l'expérience sensorielle et la réflexion que nous acquérons des connaissances et des idées.&lt;/p&gt; &lt;p&gt; 
-Dans son ouvrage majeur,  &lt;a href="https://fr.wikisource.org/wiki/Livre:Locke_-_Essai_sur_l%E2%80%99entendement_humain.djvu"  title="Essai sur l'entendement humain par Wikisource"&gt;"Essai sur l'entendement humain" &lt;/a&gt;, il élabore une théorie de la connaissance empirique, qui affirme que toute notre connaissance provient de l'expérience. Il soutient également que la raison humaine est limitée et que les connaissances les plus élevées ne peuvent être atteintes que par une observation attentive des faits et des phénomènes. &lt;/p&gt; &lt;p&gt; 
-En politique, il est connu pour sa théorie du &lt;a href="https://www.youtube.com/watch?v=lU_sAreHchQ&amp;ab_channel=Lespodcastsphilosophiques"  title="la liberté politique par Les podcasts philo"&gt;"contrat social" &lt;/a&gt;, qui stipule que le gouvernement tire sa légitimité du consentement des gouvernés. Selon lui, les individus ont des droits naturels inaliénables tels que la vie, la liberté et la propriété, que le gouvernement a pour tâche de protéger. &lt;/p&gt; &lt;p&gt; 
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/John_Locke"  title=" Wikipedia"&gt;John LOCKE&lt;/a&gt; était un philosophe anglais connu pour ses contributions en philosophie politique, en épistémologie et en théorie de l'éducation. &lt;/p&gt; &lt;p&gt; L'une de ses idées les plus célèbres est celle de la tabula rasa, qui signifie "table rase" en latin. Selon lui, l'esprit humain est vide à la naissance, sans aucune connaissance innée ou idées préconçues. C'est seulement par l'expérience sensorielle et la réflexion que nous acquérons des connaissances et des idées.&lt;/p&gt; &lt;p&gt; 
+Dans son ouvrage majeur,  &lt;a href="https://fr.wikisource.org/wiki/Livre:Locke_-_Essai_sur_l%E2%80%99entendement_humain.djvu"  title="Essai sur l'entendement humain par Wikisource"&gt;"Essai sur l'entendement humain"&lt;/a&gt;, il élabore une théorie de la connaissance empirique, qui affirme que toute notre connaissance provient de l'expérience. Il soutient également que la raison humaine est limitée et que les connaissances les plus élevées ne peuvent être atteintes que par une observation attentive des faits et des phénomènes. &lt;/p&gt; &lt;p&gt; 
+En politique, il est connu pour sa théorie du &lt;a href="https://www.youtube.com/watch?v=lU_sAreHchQ&amp;ab_channel=Lespodcastsphilosophiques"  title="la liberté politique par Les podcasts philo"&gt;"contrat social"&lt;/a&gt;, qui stipule que le gouvernement tire sa légitimité du consentement des gouvernés. Selon lui, les individus ont des droits naturels inaliénables tels que la vie, la liberté et la propriété, que le gouvernement a pour tâche de protéger. &lt;/p&gt; &lt;p&gt; 
 Il a également plaidé pour la tolérance religieuse et la séparation de l'Église et de l'État et a soutenu que chaque individu devrait être libre de pratiquer sa religion sans crainte de persécution.  &lt;/p&gt;  &lt;audio controls title="L'invention de la conscience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21976-01.02.2021-ITEMA_22560721-2015C12410S0287.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E42" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gottfried_Wilhelm_Leibniz"  title=" Wikipedia"&gt;Gottfried Wilhelm LEIBNIZ&lt;/a&gt; était un philosophe allemand très &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme"  title=""éclectisme par Wikipedia"&gt;éclectique&lt;/a&gt;, de la théologie en passant par les mathématiques, la logique et la philosophie politique ou encore la métaphysique où il est connu pour sa théorie des monades, selon laquelle l'univers est composé d'un nombre infini d'entités individuelles et autonomes appelées monades. Chaque monade est une substance simple, sans parties, qui possède une perception et une appétition, c'est-à-dire une tendance à rechercher le bien et à &lt;a href="https://www.youtube.com/watch?v=ZJKr-vJt3NE&amp;ab_channel=LePr%C3%A9cepteur"  title="Le mal n'existe pas par le Précepteur"&gt; éviter le mal &lt;/a&gt; . Les monades ne peuvent pas interagir directement les unes avec les autres, mais leur perception et leur appétition sont harmonisées par Dieu, qui a créé l'univers de manière à ce qu'il soit le meilleur des mondes possibles. &lt;/p&gt; &lt;p&gt;
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gottfried_Wilhelm_Leibniz"  title=" Wikipedia"&gt;Gottfried Wilhelm LEIBNIZ&lt;/a&gt; était un philosophe allemand très &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme"  title=""éclectisme par Wikipedia"&gt;éclectique&lt;/a&gt;, de la théologie en passant par les mathématiques, la logique et la philosophie politique ou encore la métaphysique où il est connu pour sa théorie des monades, selon laquelle l'univers est composé d'un nombre infini d'entités individuelles et autonomes appelées monades. Chaque monade est une substance simple, sans parties, qui possède une perception et une appétition, c'est-à-dire une tendance à rechercher le bien et à &lt;a href="https://www.youtube.com/watch?v=ZJKr-vJt3NE&amp;ab_channel=LePr%C3%A9cepteur"  title="Le mal n'existe pas par le Précepteur"&gt; éviter le mal&lt;/a&gt;. Les monades ne peuvent pas interagir directement les unes avec les autres, mais leur perception et leur appétition sont harmonisées par Dieu, qui a créé l'univers de manière à ce qu'il soit le meilleur des mondes possibles. &lt;/p&gt; &lt;p&gt;
 La théorie a des implications dans de nombreux domaines, y compris la métaphysique, la théologie, l'épistémologie et l'éthique. Elle implique que la connaissance de chaque monade est limitée à sa propre perspective, ce qui soulève des questions intéressantes sur la nature de la vérité et de la connaissance.&lt;/p&gt; &lt;p&gt; 
 En mathématiques, il est connu pour avoir inventé le calcul infinitésimal, une méthode qui permet de manipuler des quantités infiniment petites. Cette découverte a été réalisée de manière indépendante par Leibniz et Isaac Newton, et les deux hommes ont été impliqués dans une longue querelle pour savoir qui était le véritable inventeur.&lt;/p&gt; &lt;p&gt; 
 En philosophie politique, Leibniz a soutenu que le pouvoir politique devrait être détenu par une élite instruite, qui gouvernerait de manière éclairée et rationnelle. &lt;/p&gt;  &lt;audio controls title="La Monadologie par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/11/s47/RF_F56A3AEF-9E04-487F-89BF-2C4FBCA2B21D_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
@@ -3571,9 +3571,9 @@
       </c>
       <c r="E44" s="49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Bayle"   title=" Wikipedia"&gt;Pierre BAYLE&lt;/a&gt; était un philosophe français connu pour son scepticisme, sa défense de  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1965_num_39_2_2413" title="Pierre Bayle précurseur des théologies modernes de la liberté religieuse  par Persée"&gt;la tolérance religieuse &lt;/a&gt; et son monumental Dictionnaire historique et critique, qui en fait un précurseur majeur des Lumières. Sa pensée mêle critique radicale des dogmes religieux, exigence de rigueur historique et réflexion sur les limites de la raison. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un sceptique : il met en évidence les contradictions de la raison, notamment quand elle prétend démontrer les dogmes religieux (Trinité, providence, miracle, etc.). Il aime exposer des opinions paradoxales, voire scandaleuses, et les renforcer par des arguments rigoureux, sans dire clairement s’il les adopte lui‑même, ce qui déroutait ses contemporains. Concernant le problème du mal, il montre que la raison ne parvient pas à concilier l’existence du mal avec celle d’un Dieu tout‑puissant et parfaitement bon.
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Bayle"   title=" Wikipedia"&gt;Pierre BAYLE&lt;/a&gt; était un philosophe français connu pour son scepticisme, sa défense de  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1965_num_39_2_2413" title="Pierre Bayle précurseur des théologies modernes de la liberté religieuse  par Persée"&gt;la tolérance religieuse &lt;/a&gt; et son monumental Dictionnaire historique et critique, qui en fait un précurseur majeur des Lumières. Sa pensée mêle critique radicale des dogmes religieux, exigence de rigueur historique et réflexion sur les limites de la raison. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un sceptique : il met en évidence les contradictions de la raison, notamment quand elle prétend démontrer les dogmes religieux (Trinité, providence, miracle, etc.). Il aime exposer des opinions paradoxales, voire scandaleuses, et les renforcer par des arguments rigoureux, sans dire clairement s’il les adopte lui‑même, ce qui déroutait ses contemporains. Concernant le problème du mal, il montre que la raison ne parvient pas à concilier l’existence du mal avec celle d’un Dieu tout‑puissant et parfaitement bon.
  &lt;/p&gt; &lt;p&gt; Il défend la tolérance civile : l’État ne doit pas persécuter pour des motifs religieux et doit protéger la liberté de conscience de toutes les confessions, y compris juifs, musulmans et athées. Il soutient qu’une société composée d’athées pourrait être ordonnée et morale, anticipant l’idée moderne d’une morale indépendante de la religion.  &lt;/p&gt; &lt;p&gt; 
-Le &lt;a href="https://fr.wikipedia.org/wiki/Dictionnaire_historique_et_critique" title=" Pierre Bayle : Dictionnaire historique et critique par Wikipedia"&gt;Dictionnaire historique et critique &lt;/a&gt; est un véritable "labyrinthe" de textes et de notes, où la partie la plus subversive se trouve souvent dans les renvois et les commentaires en marge. Il y pratique une critique érudite des sources, confrontant témoignages, chronologies et récits, et affaiblissant ainsi l’autorité de la tradition dogmatique. Les philosophes des Lumières (Voltaire, Diderot, etc.) lisent et l'utilisent , qu’ils voient comme un précurseur par son antifanatisme, son scepticisme et son exigence critique. &lt;/p&gt; &lt;p&gt; Ses autes ouvrages : - "Pensées diverses sur la comète" paru 1682 : partant de la comète de 1680, il y dénonce les superstitions qui associent phénomènes célestes et malheurs terrestres, et y formule le fameux paradoxe de "l’athée vertueux".  - "Ce que c’est que la France toute catholique sous le règne de Louis‑le‑Grand" paru en 1686 : critique ironique de la politique religieuse de Louis XIV et de la persécution des protestants. - Commentaire philosophique sur ces paroles de Jésus‑Christ : “Contrains‑les d’entrer” en 1686 : texte majeur pour la &lt;a href="https://www.youtube.com/watch?v=ew4sBCkUseA" title=" Pierre Bayle : tolérance et liberté religieuse  par Institut Coppet"&gt;théorie moderne de la tolérance &lt;/a&gt; , il argumente contre toute coercition en matière de foi, y compris envers les hérétiques et les athées. &lt;/p&gt; 
+Le &lt;a href="https://fr.wikipedia.org/wiki/Dictionnaire_historique_et_critique" title=" Pierre Bayle : Dictionnaire historique et critique par Wikipedia"&gt;Dictionnaire historique et critique &lt;/a&gt; est un véritable "labyrinthe" de textes et de notes, où la partie la plus subversive se trouve souvent dans les renvois et les commentaires en marge. Il y pratique une critique érudite des sources, confrontant témoignages, chronologies et récits, et affaiblissant ainsi l’autorité de la tradition dogmatique. Les philosophes des Lumières (Voltaire, Diderot, etc.) lisent et l'utilisent, qu’ils voient comme un précurseur par son antifanatisme, son scepticisme et son exigence critique. &lt;/p&gt; &lt;p&gt; Ses autes ouvrages : - "Pensées diverses sur la comète" paru 1682 : partant de la comète de 1680, il y dénonce les superstitions qui associent phénomènes célestes et malheurs terrestres, et y formule le fameux paradoxe de "l’athée vertueux".  - "Ce que c’est que la France toute catholique sous le règne de Louis‑le‑Grand" paru en 1686 : critique ironique de la politique religieuse de Louis XIV et de la persécution des protestants. - Commentaire philosophique sur ces paroles de Jésus‑Christ : “Contrains‑les d’entrer” en 1686 : texte majeur pour la &lt;a href="https://www.youtube.com/watch?v=ew4sBCkUseA" title=" Pierre Bayle : tolérance et liberté religieuse  par Institut Coppet"&gt;théorie moderne de la tolérance&lt;/a&gt;, il argumente contre toute coercition en matière de foi, y compris envers les hérétiques et les athées. &lt;/p&gt; 
 ​
 &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Le scandaleux Pierre Bayle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-04.04.2008-ITEMA_20118105-2008C6409S0095-NET_66658CCB-7933-4384-84A0-F0495954D09D_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="E46" s="49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giambattista_Vico"  title=" Wikipedia"&gt;Giambattista VICO&lt;/a&gt; était un  philosophe, historien et pédagogue italien reconnu comme un pionnier de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_6790" style="color:#88A1E9" title=" La sagesse de l'histoire. Jean-Baptiste Vico et la philosophie pratique  par Persée"&gt; philosophie pratique&lt;/a&gt;, de l’histoire et des sciences humaines avec son ouvrage "La Science nouvelle" (paru en 1725), où il critique le rationalisme cartésien et propose une &lt;a href="https://www.youtube.com/watch?v=-OWc7ej_ixM" style="color:#88A1E9" title="Giambattista Vico: Consciousness and the Cycles of History par Spiritual Quest"&gt;approche alternative&lt;/a&gt; , centrée sur la complexité et l’historicité des sociétés humaines. Il y développe l’idée que la vérité n’est pas simplement découverte mais également construite. Selon lui, alors que Dieu connaît parfaitement la nature en tant que créateur, l’humain ne connaît parfaitement que ce qu’il crée lui-même, comme les mathématiques et les institutions humaines. &lt;/p&gt; &lt;p&gt; Il est aussi considéré comme le précurseur de la  &lt;a href="https://www.youtube.com/watch?v=vEYpuH4KdWM" style="color:#88A1E9" title=" Giambattista Vico, "The New Science" | A Philosophy of the History of Human Ideas and Institutions par Gavin Young Philosophy"&gt;philosophie de l’histoire&lt;/a&gt; et de l'épistémologie constructiviste, car il affirme que la connaissance humaine résulte essentiellement d’un processus collectif de création et d’invention. Sa critique du cartésianisme, son attention à la pluralité des formes de savoir (histoire, philologie, droit, rhétorique) et son intuition de la spécificité des sciences sociales l’inscrivent à contre-courant des philosophies réductionnistes de son époque. &lt;/p&gt; &lt;p&gt; Il élabore une théorie cyclique du développement des sociétés, fondée sur trois âges : l’âge des dieux, l’âge des héros et l’âge des hommes, chacun marquant une transformation des mœurs, du droit et de la politique. Il affirme que chaque peuple passe par ces étapes, de la mythologie religieuse à la raison civique, et que ce mouvement forme la trame de l’histoire humaine.  &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giambattista_Vico"  title=" Wikipedia"&gt;Giambattista VICO&lt;/a&gt; était un  philosophe, historien et pédagogue italien reconnu comme un pionnier de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_6790" style="color:#88A1E9" title=" La sagesse de l'histoire. Jean-Baptiste Vico et la philosophie pratique  par Persée"&gt; philosophie pratique&lt;/a&gt;, de l’histoire et des sciences humaines avec son ouvrage "La Science nouvelle" (paru en 1725), où il critique le rationalisme cartésien et propose une &lt;a href="https://www.youtube.com/watch?v=-OWc7ej_ixM" style="color:#88A1E9" title="Giambattista Vico: Consciousness and the Cycles of History par Spiritual Quest"&gt;approche alternative&lt;/a&gt;, centrée sur la complexité et l’historicité des sociétés humaines. Il y développe l’idée que la vérité n’est pas simplement découverte mais également construite. Selon lui, alors que Dieu connaît parfaitement la nature en tant que créateur, l’humain ne connaît parfaitement que ce qu’il crée lui-même, comme les mathématiques et les institutions humaines. &lt;/p&gt; &lt;p&gt; Il est aussi considéré comme le précurseur de la  &lt;a href="https://www.youtube.com/watch?v=vEYpuH4KdWM" style="color:#88A1E9" title=" Giambattista Vico, "The New Science" | A Philosophy of the History of Human Ideas and Institutions par Gavin Young Philosophy"&gt;philosophie de l’histoire&lt;/a&gt; et de l'épistémologie constructiviste, car il affirme que la connaissance humaine résulte essentiellement d’un processus collectif de création et d’invention. Sa critique du cartésianisme, son attention à la pluralité des formes de savoir (histoire, philologie, droit, rhétorique) et son intuition de la spécificité des sciences sociales l’inscrivent à contre-courant des philosophies réductionnistes de son époque. &lt;/p&gt; &lt;p&gt; Il élabore une théorie cyclique du développement des sociétés, fondée sur trois âges : l’âge des dieux, l’âge des héros et l’âge des hommes, chacun marquant une transformation des mœurs, du droit et de la politique. Il affirme que chaque peuple passe par ces étapes, de la mythologie religieuse à la raison civique, et que ce mouvement forme la trame de l’histoire humaine.  &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F46" s="47" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="E48" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Wolff_(philosophe)"   title=" Wikipedia"&gt;Christian WOLFF&lt;/a&gt;  était un philosophe, mathématicien et juriste allemand majeur de l'Aufklärung, &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1964_num_62_74_7932_t1_0360_0000_2" title="Christian Wolff, Philosophia prima sive Ontologia edidit et curavit Joannes Ecole par Persée"&gt;l'Éclairage allemand &lt;/a&gt; précoce. Disciple de Leibniz, il systématisa la philosophie rationnelle en allemand, influençant Kant et Baumgarten.  étudia la théologie à l'université de Iéna en 1699, puis se tourna vers les mathématiques sous l'influence d'Erhard Weigel. &lt;/p&gt; &lt;p&gt; Il popularisa le rationalisme leibnizien via une œuvre encyclopédique : "Philosophia rationalis sive logica" paru en 1712, "Philosophia prima" en 1729 et "Philosophie pratique" en  1738. Il  &lt;a href="https://www.youtube.com/watch?v=vfmME7Qcgh4"  title="Christian Wolff (philosopher) par WikiReader"&gt;structura la philosophie &lt;/a&gt; en domaines (ontologie, cosmologie, psychologie rationnelle, théologie naturelle) et contribua à l'économie politique, au droit international et à la subsidiarité. &lt;/p&gt; &lt;p&gt; Son "wolffianisme" forma la philosophie allemande du XVIIIe siècle, faisant du langage allemand un outil philosophique majeur et favorisant les Lumières prussiennes. Kant le critiqua pour son dogmatisme excessif, mais reconnut sa rigueur systématique. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Wolff_(philosophe)"   title=" Wikipedia"&gt;Christian WOLFF&lt;/a&gt;  était un philosophe, mathématicien et juriste allemand majeur de l'Aufklärung, &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1964_num_62_74_7932_t1_0360_0000_2" title="Christian Wolff, Philosophia prima sive Ontologia edidit et curavit Joannes Ecole par Persée"&gt;l'Éclairage allemand &lt;/a&gt; précoce. Disciple de Leibniz, il systématisa la philosophie rationnelle en allemand, influençant Kant et Baumgarten. Il étudia la théologie à l'université de Iéna en 1699, puis se tourna vers les mathématiques sous l'influence d'Erhard Weigel. &lt;/p&gt; &lt;p&gt; Il popularisa le rationalisme leibnizien via une œuvre encyclopédique : "Philosophia rationalis sive logica" paru en 1712, "Philosophia prima" en 1729 et "Philosophie pratique" en  1738. Il  &lt;a href="https://www.youtube.com/watch?v=vfmME7Qcgh4"  title="Christian Wolff (philosopher) par WikiReader"&gt;structura la philosophie &lt;/a&gt; en domaines (ontologie, cosmologie, psychologie rationnelle, théologie naturelle) et contribua à l'économie politique, au droit international et à la subsidiarité. &lt;/p&gt; &lt;p&gt; Son "wolffianisme" forma la philosophie allemande du XVIIIe siècle, faisant du langage allemand un outil philosophique majeur et favorisant les Lumières prussiennes. Kant le critiqua pour son dogmatisme excessif, mais reconnut sa rigueur systématique. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F48" s="47" t="inlineStr">
@@ -4114,7 +4114,7 @@
       <c r="E52" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Voltaire"   title=" Wikipedia"&gt; VOLTAIRE&lt;/a&gt;, de son vrai nom François-Marie Arouet, est un philosophe de l'époque des  &lt;a href="https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;t=380s&amp;ab_channel=LePr%C3%A9cepteur"  title=" La philosophie des lumières par le Précepteur "&gt;Lumières&lt;/a&gt; (ou Illuministe) en France. Il était aussi écrivain, poète, dramaturge et philosophe. &lt;/p&gt; &lt;p&gt;
-Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href="https://www.youtube.com/watch?v=XE1Z8jpVJUA" title=" la vie de Voltaire  par Portrait Historiques"&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation . Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;
+Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href="https://www.youtube.com/watch?v=XE1Z8jpVJUA" title=" la vie de Voltaire  par Portrait Historiques"&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation. Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;
 Voltaire, qui était &lt;a href="https://www.youtube.com/watch?v=RO_aeh1cBgA&amp;ab_channel=Kurious"   title=" Regard critique sur le déîsme par Kurious "&gt;déiste&lt;/a&gt; s'est opposé aux abus de l'Église catholique et a plaidé en faveur de la tolérance envers les minorités religieuses. Dans son ouvrage &lt;a href="https://www.youtube.com/watch?v=1RlS8GKL7SU"  title=" Voltaire-Tolérence par Culture Philo "&gt;"Traité sur la tolérance"&lt;/a&gt;, (1763) il a condamné les persécutions religieuses et a défendu le principe selon lequel chaque individu devait être libre de pratiquer sa religion sans être inquiété. &lt;/p&gt; &lt;p&gt;
 Son ouvrage le plus connu est  &lt;a href="https://www.youtube.com/watch?v=kom2zFvrj5I&amp;ab_channel=T%C3%A9l%C3%A9Crayon"  title=" Candide de Voltaire par TéléCrayon "&gt;"Candide"&lt;/a&gt; (1759), un conte philosophique qui critique les idées optimistes de l'époque et souligne les absurdités et les injustices du monde. &lt;/p&gt; &lt;p&gt;
 La contribution de Voltaire à la philosophie se caractérise par son engagement envers la raison, la liberté et la justice. Il a influencé de nombreux penseurs ultérieurs et a contribué à jeter les bases de la pensée libérale et humaniste qui a marqué les siècles suivants. Sa défense de la liberté d'expression reste une valeur fondamentale de nos sociétés démocratiques aujourd'hui. &lt;/p&gt; &lt;audio controls title="Voltaire et les Lumières par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-13.01.2021-ITEMA_22540842-2021C24632S0013.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="E54" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Wesley"  title=" Wikipedia"&gt;John WESLEY&lt;/a&gt; était un philosophe, religieux, théologien et évangélisateur anglais qui fut le déclencheur d'un mouvement de réveil au sein de l'Église d'Angleterre, connu sous le nom &lt;a href="https://www.youtube.com/watch?v=d1F_Ye3mSnE"  title="  John Wesley: les origines du méthodisme | Dans la lignée des héros de la foi par Ainsi parle l'éternel"&gt;de méthodisme&lt;/a&gt; .  Il combine une vaste culture (philosophie, langues, théologie) à une activité de prédication et de réforme. &lt;/p&gt; &lt;p&gt; Il étudie les lettres classiques à Oxford, apprend plusieurs langues et se destine à une vie religieuse dès 1725. Après un séjour d’évangélisation aux États-Unis, il revient marqué par la ferveur des moraves et, lors d’une  &lt;a href="https://www.youtube.com/watch?v=v-B6rEPbNQk"  title=" Qu’est ce qu’une expérience spirituelle par Numérologie &amp; Spiritualité"&gt;expérience spirituelle&lt;/a&gt; en 1738, affirme avoir trouvé l'assurance du salut – événement clé du méthodisme, qui repose sur le réveil personnel et l’expérience directe de la foi. Il se distingue par son opposition à la doctrine de la prédestination et par son attachement à l’arminianisme, qui valorise la responsabilité humaine et la conversion personnelle. Il insiste sur la « sanctification » : vivre selon l’amour du Christ et tendre vers une  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_2008_num_88_3_1347" title="Le Cheminement théologique de John Wesley (1703-1791) avec le catholicisme par Persée"&gt; perfection chrétienne&lt;/a&gt; dans la vie morale et sociale. Il combat aussi le déisme des Lumières, défendant un christianisme de révélation et d’engagement immédiat. &lt;/p&gt; &lt;p&gt; Il est aussi connu pour son engagement contre l’esclavage ; il considère la liberté comme un droit naturel et publie plusieurs écrits abolitionnistes. Il a influencé d’autres figures majeures du mouvement antiesclavagiste et prôné un christianisme impliqué dans la justice sociale. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Wesley"  title=" Wikipedia"&gt;John WESLEY&lt;/a&gt; était un philosophe, religieux, théologien et évangélisateur anglais qui fut le déclencheur d'un mouvement de réveil au sein de l'Église d'Angleterre, connu sous le nom &lt;a href="https://www.youtube.com/watch?v=d1F_Ye3mSnE"  title="  John Wesley: les origines du méthodisme | Dans la lignée des héros de la foi par Ainsi parle l'éternel"&gt;de méthodisme&lt;/a&gt;.  Il combine une vaste culture (philosophie, langues, théologie) à une activité de prédication et de réforme. &lt;/p&gt; &lt;p&gt; Il étudie les lettres classiques à Oxford, apprend plusieurs langues et se destine à une vie religieuse dès 1725. Après un séjour d’évangélisation aux États-Unis, il revient marqué par la ferveur des moraves et, lors d’une  &lt;a href="https://www.youtube.com/watch?v=v-B6rEPbNQk"  title=" Qu’est ce qu’une expérience spirituelle par Numérologie &amp; Spiritualité"&gt;expérience spirituelle&lt;/a&gt; en 1738, affirme avoir trouvé l'assurance du salut – événement clé du méthodisme, qui repose sur le réveil personnel et l’expérience directe de la foi. Il se distingue par son opposition à la doctrine de la prédestination et par son attachement à l’arminianisme, qui valorise la responsabilité humaine et la conversion personnelle. Il insiste sur la « sanctification » : vivre selon l’amour du Christ et tendre vers une  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_2008_num_88_3_1347" title="Le Cheminement théologique de John Wesley (1703-1791) avec le catholicisme par Persée"&gt; perfection chrétienne&lt;/a&gt; dans la vie morale et sociale. Il combat aussi le déisme des Lumières, défendant un christianisme de révélation et d’engagement immédiat. &lt;/p&gt; &lt;p&gt; Il est aussi connu pour son engagement contre l’esclavage ; il considère la liberté comme un droit naturel et publie plusieurs écrits abolitionnistes. Il a influencé d’autres figures majeures du mouvement antiesclavagiste et prôné un christianisme impliqué dans la justice sociale. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F54" s="47" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="E55" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)"    title=" Wikipedia"&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href="https://www.youtube.com/watch?v=kbpEAw2gl40" title=" David Hartley par Crevoisier Philippe"&gt; développement de la psychologie &lt;/a&gt;  , en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt; - La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la "substance médullaire" (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt; - La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des "vibratiuncules" (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs "vibratiuncules" respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href="https://www.youtube.com/shorts/BuqpLB9V41c"  title=" David Hartley par timelinephilosopher"&gt;  le fondement des idées et des pensées &lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des "vibratiuncules" de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, "Observations on Man, his Frame, his Duty, and his Expectations", publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)"    title=" Wikipedia"&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href="https://www.youtube.com/watch?v=kbpEAw2gl40" title=" David Hartley par Crevoisier Philippe"&gt; développement de la psychologie&lt;/a&gt;, en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt; - La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la "substance médullaire" (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt; - La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des "vibratiuncules" (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs "vibratiuncules" respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href="https://www.youtube.com/shorts/BuqpLB9V41c"  title=" David Hartley par timelinephilosopher"&gt;  le fondement des idées et des pensées&lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des "vibratiuncules" de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, "Observations on Man, his Frame, his Duty, and his Expectations", publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt; 
 - L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt; 
 - Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; </t>
         </is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="E59" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau" title=" Wikipedia"&gt; Jean-Jacques ROUSSEAU&lt;/a&gt; était un philosophe &lt;a href="https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;ab_channel=LePr%C3%A9cepteur"  title="Les Lumières par le Précepteur "&gt; des lumières&lt;/a&gt; et écrivain suisse-français, défenseur de la liberté et de l'égalité. Il et est surtout connu pour son livre &lt;a href="https://www.youtube.com/watch?v=tToAS8pUXzU"   title="Le texte fondateur par Alain Bajomée "&gt;"Du contrat social"&lt;/a&gt; , dans lequel il développe sa théorie politique ainsi que &lt;a href="https://www.youtube.com/watch?v=3-mPXD5CkJc"  title="L'Emile par Librairie Vrin"&gt;"Emile" &lt;/a&gt;considéré comme un "traité d'écucation" ou sa théorie de l'homme. &lt;/p&gt; &lt;p&gt;
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau" title=" Wikipedia"&gt; Jean-Jacques ROUSSEAU&lt;/a&gt; était un philosophe &lt;a href="https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;ab_channel=LePr%C3%A9cepteur"  title="Les Lumières par le Précepteur "&gt; des lumières&lt;/a&gt; et écrivain suisse-français, défenseur de la liberté et de l'égalité. Il et est surtout connu pour son livre &lt;a href="https://www.youtube.com/watch?v=tToAS8pUXzU"   title="Le texte fondateur par Alain Bajomée "&gt;"Du contrat social"&lt;/a&gt;, dans lequel il développe sa théorie politique ainsi que &lt;a href="https://www.youtube.com/watch?v=3-mPXD5CkJc"  title="L'Emile par Librairie Vrin"&gt;"Emile" &lt;/a&gt;considéré comme un "traité d'écucation" ou sa théorie de l'homme. &lt;/p&gt; &lt;p&gt;
 Rousseau a également écrit sur la philosophie morale, la théorie de l'éducation et la nature humaine et  &lt;a href="https://www.youtube.com/watch?v=cUtO8U9QbZs&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Le désir par le Précepteur "&gt; le désir&lt;/a&gt;. Il croyait que &lt;a href="https://www.youtube.com/watch?v=FpXdTgerxiI&amp;ab_channel=LePr%C3%A9cepteur"   title="L''homme est naturellement bon par le Précepteur "&gt; l'homme est naturellement bon&lt;/a&gt;, mais corrompu par la société et la civilisation. Il a également affirmé que la liberté individuelle est essentielle à l'épanouissement humain et que les institutions politiques doivent être créées pour protéger les droits et les libertés des individus. &lt;/p&gt; &lt;p&gt;  Il est souvent considéré comme un précurseur du  &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1927_num_29_16_2482#"  title="La philosophie romantique par Persée "&gt; romantisme&lt;/a&gt; en raison de son accent mis sur les émotions, la nature, l'individualité et la subjectivité. Il a exprimé une méfiance envers la société civilisée et a prôné un retour à la nature et à la simplicité. Il a également souligné l'importance de l'émotion et de l'expérience personnelle dans la compréhension du monde, remettant en question l'approche rationnelle et scientifique des Lumières. Ses idées ont eu une influence significative sur les écrivains et les artistes romantiques ultérieurs, qui ont valorisé l'expression émotionnelle et l'expérience individuelle dans leurs œuvres.&lt;/p&gt; &lt;p&gt;
 En termes de théorie de l'éducation, Rousseau a proposé une approche de l'apprentissage basée sur l'observation et l'expérience plutôt que sur la mémorisation et l'étude académique et a souligné l'importance de la créativité et de l'expression personnelle dans l'éducation. &lt;/p&gt; &lt;p&gt; &lt;audio controls title="Rousseau, l'anti-économiste par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10081-28.12.2022-ITEMA_23239091-2022C29629E0022-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E63" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claude-Adrien_Helv%C3%A9tius" title=" Wikipedia"&gt;Claude-Adrien HELVÉTIUS&lt;/a&gt; était un philosophe français des Lumières, connu pour son matérialisme radical et son utilitarisme, qui a marqué le XVIIIe siècle par ses idées provocatrices sur l'esprit humain et la société. Il  fut fermier général, poète et mécène des philosophes, collaborant à l'Encyclopédie de Diderot. Son ouvrage  &lt;a href="https://fr.wikipedia.org/wiki/De_l%27esprit"  title="De l’esprit par Wikipedia"&gt;De l'esprit (1758) &lt;/a&gt; , publié anonymement, provoqua un scandale immense, fut condamné au feu par l'Église et le Parlement, mais diffusé en Hollande. &lt;/p&gt; &lt;p&gt; Influencé par Locke, il défend un sensualisme selon lequel toutes nos idées et connaissances proviennent des sensations physiques, sans innéisme ni libre arbitre clair. L'âme n'est que la faculté de sentir, et l'esprit en découle via la mémoire qui compare les impressions sensorielles .  &lt;/p&gt; &lt;p&gt; Pour lui, l'égoïsme personnel, motivé par le plaisir et la douleur, est la base de toute action vertueuse et sociale, transformé par l'éducation et les institutions en bonheur collectif. Il prône une société réformée par la raison, où lois et mœurs maximisent l'utilité commune sous une autorité éclairée. &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claude-Adrien_Helv%C3%A9tius" title=" Wikipedia"&gt;Claude-Adrien HELVÉTIUS&lt;/a&gt; était un philosophe français des Lumières, connu pour son matérialisme radical et son utilitarisme, qui a marqué le XVIIIe siècle par ses idées provocatrices sur l'esprit humain et la société. Il  fut fermier général, poète et mécène des philosophes, collaborant à l'Encyclopédie de Diderot. Son ouvrage  &lt;a href="https://fr.wikipedia.org/wiki/De_l%27esprit"  title="De l’esprit par Wikipedia"&gt;De l'esprit (1758)&lt;/a&gt;, publié anonymement, provoqua un scandale immense, fut condamné au feu par l'Église et le Parlement, mais diffusé en Hollande. &lt;/p&gt; &lt;p&gt; Influencé par Locke, il défend un sensualisme selon lequel toutes nos idées et connaissances proviennent des sensations physiques, sans innéisme ni libre arbitre clair. L'âme n'est que la faculté de sentir, et l'esprit en découle via la mémoire qui compare les impressions sensorielles.  &lt;/p&gt; &lt;p&gt; Pour lui, l'égoïsme personnel, motivé par le plaisir et la douleur, est la base de toute action vertueuse et sociale, transformé par l'éducation et les institutions en bonheur collectif. Il prône une société réformée par la raison, où lois et mœurs maximisent l'utilité commune sous une autorité éclairée. &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E65" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0f"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie,il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral &lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0f"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie,il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F65" s="47" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="E67" s="58" t="inlineStr">
         <is>
-          <t>&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant"  title=" Wikipedia"&gt; Emmanuel KANT&lt;/a&gt; était un philosophe &lt;a href="https://la-philosophie.com/philosophie-lumieres" style="color:#88A1E9"   title="La philosophie des Lumières par la-philosophie.com"&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant"  title="La philosophie pratique de Kant de l'encyclopédie Wikipédia"&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href="https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos"   title="C'est quoi la raison pure par Kosmos"&gt;"Critique de la raison pure"&lt;/a&gt; , publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href="https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos"  title="La loi morale par Kosmos"&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href="https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'impératif catégorique par le Précepteur"&gt;"Fondement de la métaphysique des moeurs"&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href="https://la-philosophie.com/espace-public-et-democratie"  title="Espace public par la-philosophie.com"&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les "Lumières" comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href="https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume"  title="Faculté de jugement par la-philosophie.com"&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title="Le monde: entre déterminisme et liberté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant"  title=" Wikipedia"&gt; Emmanuel KANT&lt;/a&gt; était un philosophe &lt;a href="https://la-philosophie.com/philosophie-lumieres" style="color:#88A1E9"   title="La philosophie des Lumières par la-philosophie.com"&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant"  title="La philosophie pratique de Kant de l'encyclopédie Wikipédia"&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href="https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos"   title="C'est quoi la raison pure par Kosmos"&gt;"Critique de la raison pure"&lt;/a&gt;, publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href="https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos"  title="La loi morale par Kosmos"&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href="https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'impératif catégorique par le Précepteur"&gt;"Fondement de la métaphysique des moeurs"&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href="https://la-philosophie.com/espace-public-et-democratie"  title="Espace public par la-philosophie.com"&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les "Lumières" comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href="https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume"  title="Faculté de jugement par la-philosophie.com"&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title="Le monde: entre déterminisme et liberté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F67" s="47" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E68" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Moses_Mendelssohn"   title=" Wikipedia"&gt;Moses MENDELSSOHN&lt;/a&gt;  était un philosophe &lt;a href="https://www.youtube.com/watch?v=AvucqmG4Alk" title="Moses Mendelssohn et l’invention des Juifs allemands par Instituter of Jewish Studies"&gt;juif allemand des Lumières &lt;/a&gt;, né à Dessau et mort à Berlin, souvent considéré comme le "premier Juif allemand moderne" et l’une des grandes figures de  &lt;a href="https://www.youtube.com/watch?v=AaS7z6uRwWc" title="Le mythe de Moïse Mendelssohn par Efraim Palvanov"&gt;la Haskala, &lt;/a&gt; l’Aufklärung juive qui cherche à concilier fidélité au judaïsme et ouverture à la culture et à la philosophie modernes. &lt;/p&gt; &lt;p&gt; Il milite pour l’égalité civile des Juifs, la reconnaissance de leur spécificité au sein d’un État majoritairement chrétien, et la fin des discriminations légales et défend l’idée que les Juifs peuvent être pleinement intégrés comme citoyens allemands sans renoncer à leur religion. Il travaille sur la coexistence entre raison et foi, en soutenant que les vérités fondamentales de la religion sont accessibles à la raison humaine. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : -  "Phédon ou sur l’immortalité de l’âme" paru en 1767 qui  présente, sous forme de dialogues inspirés de Socrate, une défense de l’immortalité de l’âme et contribue à son surnom de "Socrate allemand". &lt; /p&gt; &lt;p&gt;  - "Jérusalem ou pouvoir religieux et judaïsme" en 1783 expose sa théorie de la séparation de l’Église et de l’État et sa vision d’un judaïsme compatible avec la liberté moderne. &lt;/p&gt; &lt;p&gt; - &lt;a href="https://laviedesidees.fr/Mendelssohn-Heures-matinales" title="Le dernier métaphysicien par la vie des idées"&gt;"Morgenstunden" &lt;/a&gt;, recueil de leçons sur l’existence de Dieu, synthétise sa position philosophique dans ses dernières années
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Moses_Mendelssohn"   title=" Wikipedia"&gt;Moses MENDELSSOHN&lt;/a&gt;  était un philosophe &lt;a href="https://www.youtube.com/watch?v=AvucqmG4Alk" title="Moses Mendelssohn et l’invention des Juifs allemands par Instituter of Jewish Studies"&gt;juif allemand des Lumières&lt;/a&gt;, né à Dessau et mort à Berlin, souvent considéré comme le "premier Juif allemand moderne" et l’une des grandes figures de  &lt;a href="https://www.youtube.com/watch?v=AaS7z6uRwWc" title="Le mythe de Moïse Mendelssohn par Efraim Palvanov"&gt;la Haskala, &lt;/a&gt; l’Aufklärung juive qui cherche à concilier fidélité au judaïsme et ouverture à la culture et à la philosophie modernes. &lt;/p&gt; &lt;p&gt; Il milite pour l’égalité civile des Juifs, la reconnaissance de leur spécificité au sein d’un État majoritairement chrétien, et la fin des discriminations légales et défend l’idée que les Juifs peuvent être pleinement intégrés comme citoyens allemands sans renoncer à leur religion. Il travaille sur la coexistence entre raison et foi, en soutenant que les vérités fondamentales de la religion sont accessibles à la raison humaine. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : -  "Phédon ou sur l’immortalité de l’âme" paru en 1767 qui  présente, sous forme de dialogues inspirés de Socrate, une défense de l’immortalité de l’âme et contribue à son surnom de "Socrate allemand". &lt; /p&gt; &lt;p&gt;  - "Jérusalem ou pouvoir religieux et judaïsme" en 1783 expose sa théorie de la séparation de l’Église et de l’État et sa vision d’un judaïsme compatible avec la liberté moderne. &lt;/p&gt; &lt;p&gt; - &lt;a href="https://laviedesidees.fr/Mendelssohn-Heures-matinales" title="Le dernier métaphysicien par la vie des idées"&gt;"Morgenstunden"&lt;/a&gt;, recueil de leçons sur l’existence de Dieu, synthétise sa position philosophique dans ses dernières années
 . &lt;/p&gt; &lt;p&gt;  Il est l’un des pionniers du judaïsme libéral et un des fondateurs de la modernité juive européenne, en cherchant l’intégration sans assimilation forcée et a  eu une influence durablement la philosophie juive et la pensée allemande, préparant le terrain pour des figures comme Heinrich Heine, Hermann Cohen, Franz Rosenzweig, Walter Benjamin ou Hannah Arendt. &lt;/p&gt; </t>
         </is>
       </c>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="E71" s="49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donatien_Alphonse_Fran%C3%A7ois_de_Sade" title=" Wikipedia"&gt;Marquis François de SADE&lt;/a&gt; était un écrivain, philosophe Français surtout connu pour ses écrits provocateurs et controversés, qui abordent les thèmes de &lt;a href="https://www.youtube.com/watch?v=PJdCNc-0Ybk" title="Sade – justine ou les malheurs de la vertu par Kosmos"&gt;la sexualité, la violence et la morale &lt;/a&gt; . Il a passé une grande partie de sa vie en prison ou en exil en raison de ses opinions et de ses activités considérées comme immorales et illégales. &lt;/p&gt; &lt;p&gt;  Bien qu'il soit souvent associé à la pornographie et à la violence, il a exercé une influence importante sur la philosophie et la culture. Il a été considéré comme un précurseur du mouvement surréaliste, de &lt;a href="https://www.youtube.com/watch?v=KEh0vf7HCoI&amp;ab_channel=RayonPolar"   title="Donatien Alphonse François de Sade par RayonPolar"&gt; nombreux cinéastes&lt;/a&gt; tels que Brunel, Debordque, Bergma ont étaient inspirés et son travail qui a aussi été étudié par des philosophes tels que Michel Foucault et Gilles Deleuze. &lt;/p&gt; &lt;p&gt;  Sa pensée libertaire et sa critique de la société et de la religion ont également inspiré de nombreux mouvements politiques et sociaux.&lt;/p&gt; &lt;p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donatien_Alphonse_Fran%C3%A7ois_de_Sade" title=" Wikipedia"&gt;Marquis François de SADE&lt;/a&gt; était un écrivain, philosophe Français surtout connu pour ses écrits provocateurs et controversés, qui abordent les thèmes de &lt;a href="https://www.youtube.com/watch?v=PJdCNc-0Ybk" title="Sade – justine ou les malheurs de la vertu par Kosmos"&gt;la sexualité, la violence et la morale&lt;/a&gt;. Il a passé une grande partie de sa vie en prison ou en exil en raison de ses opinions et de ses activités considérées comme immorales et illégales. &lt;/p&gt; &lt;p&gt;  Bien qu'il soit souvent associé à la pornographie et à la violence, il a exercé une influence importante sur la philosophie et la culture. Il a été considéré comme un précurseur du mouvement surréaliste, de &lt;a href="https://www.youtube.com/watch?v=KEh0vf7HCoI&amp;ab_channel=RayonPolar"   title="Donatien Alphonse François de Sade par RayonPolar"&gt; nombreux cinéastes&lt;/a&gt; tels que Brunel, Debordque, Bergma ont étaient inspirés et son travail qui a aussi été étudié par des philosophes tels que Michel Foucault et Gilles Deleuze. &lt;/p&gt; &lt;p&gt;  Sa pensée libertaire et sa critique de la société et de la religion ont également inspiré de nombreux mouvements politiques et sociaux.&lt;/p&gt; &lt;p&gt; 
 Son œuvre la plus célèbre, &lt;a href="https://fr.wikisource.org/wiki/Les_120_Journ%C3%A9es_de_Sodome"  title="Les 120 jours de Sodome par source Wikisource"&gt; "Les 120 Journées de Sodome" &lt;/a&gt; (également connue sous le nom de "La Philosophie dans le Boudoir"), est considérée comme l'un des premiers exemples de littérature érotique. Ce livre est aujourd'hui considéré comme extrêmement choquant en raison de sa description explicite de pratiques sexuelles déviantes et violentes. &lt;/p&gt; &lt;p&gt;  Son travail &lt;a href="https://www.youtube.com/watch?v=Qwfqw51JaGY" title=""L'apologie du mal" par le Précepteur"&gt;provocateur et choquant &lt;/a&gt;  a soulevé des questions importantes sur la sexualité, la morale et la liberté individuelle, qui continuent d'être pertinents aujourd'hui et on utilise le terme de 'sadique' aujourd'hui dans la langue Française.&lt;/p&gt; &lt;audio controls title="La vie en infamie du marquis de Sade par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-14.01.2019-ITEMA_21950194-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="E74" s="50" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet"  title=" Wikipedia"&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe , mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet féministe ? par Sud Radio"&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote .  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet et l’éloge de l’instruction par Culture philo"&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href="https://www.youtube.com/watch?v=avTI9GHZX1I"  title="Condorcet le paradoxe par Diable Positif"&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la "mathématique sociale", Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title="Nicolas de Condorcet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet"  title=" Wikipedia"&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe, mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet féministe ? par Sud Radio"&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote.  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet et l’éloge de l’instruction par Culture philo"&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href="https://www.youtube.com/watch?v=avTI9GHZX1I"  title="Condorcet le paradoxe par Diable Positif"&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la "mathématique sociale", Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title="Nicolas de Condorcet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F74" s="47" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="E75" s="63" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi"  title=" Wikipedia"&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href="https://fr.wikipedia.org/wiki/Nihilisme"  title="Nihilisme par Wikipedia"&gt; nihilisme &lt;/a&gt; et au &lt;a href="https://fr.wikipedia.org/wiki/Panth%C3%A9isme"  title="Panthéisme par Wikipedia"&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse "querelle du panthéisme" en révélant que Lessing s'était  &lt;a href="https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321"  title="Jacobi et Spinoza par Persée"&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu . &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du "rien ne sort du néant") de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un "saut de la foi" hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. - David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. - Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi"  title=" Wikipedia"&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href="https://fr.wikipedia.org/wiki/Nihilisme"  title="Nihilisme par Wikipedia"&gt; nihilisme &lt;/a&gt; et au &lt;a href="https://fr.wikipedia.org/wiki/Panth%C3%A9isme"  title="Panthéisme par Wikipedia"&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse "querelle du panthéisme" en révélant que Lessing s'était  &lt;a href="https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321"  title="Jacobi et Spinoza par Persée"&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu. &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du "rien ne sort du néant") de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un "saut de la foi" hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. - David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. - Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E76" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Gottfried_von_Herder"  title=" Wikipedia"&gt;Johann Gottfried HERDER&lt;/a&gt; était un philosophe  et écrivain allemand souvent considéré comme l’un des pères de la philosophie de la culture et de &lt;a href="https://www.jdarriulat.net/Introductionphiloesth/PhiloModerne/Herder.html"  title="INTRODUCTION A LA PHILOSOPHIE ESTHETIQUE par jdarriulat"&gt;l’idée moderne &lt;/a&gt; de "nation". Son œuvre se situe à la croisée des Lumières et du premier romantisme allemand. Il refuse l’idée d’un progrès linéaire et uniforme de l’humanité vers une &lt;a href="https://www.youtube.com/watch?v=Y8l9aJhT76U" title="Johann Gottfried Herder par Greatest Minds in History"&gt;seule forme de civilisation &lt;/a&gt;, telle qu’on la trouve chez certains auteurs des Lumières. Chaque époque et chaque peuple possède, selon lui, une valeur propre qui doit être comprise de l’intérieur et non jugée à l’aune d’un modèle abstrait. Il propose une philosophie de l’histoire "humanitaire" : l’histoire est le développement de l’humanité en tant que telle, dans sa pluralité de formes, sous le signe de la culture, de la liberté et de la perfectibilité.  &lt;/p&gt; &lt;p&gt; Il attribue au langage un rôle constitutif dans la formation de la pensée humaine, contre l’idée d’une raison pure préexistante à toute expérience linguistique. La raison ne précède pas le langage, elle se forme à travers lui, si bien que connaître, c’est toujours déjà interpréter à l’aide de mots et de symboles historiques. Il s’intéresse à l’origine des langues et parle d’un "roman des langues" pour décrire l’histoire par laquelle les hommes passent d’un stade prélinguistique à des formes complexes de communication et de socialisation. &lt;/p&gt; &lt;p&gt; Son œuvre est très abondante, mais quelques titres structurent sa pensée. On cite notamment : "Auch eine Philosophie der Geschichte zur Bildung der Menschheit" paru en 1774 et surtout &lt;a href="https://de.wikipedia.org/wiki/Ideen_zur_Philosophie_der_Geschichte_der_Menschheit" title="Ideen zur Philosophie der Geschichte der Menschheit par wikipedia"&gt;"Ideen zur Philosophie der Geschichte der Menschheit"&lt;/a&gt; qui proposent une vaste vision historico‑culturelle de l’humanité. &lt;/p&gt; &lt;p&gt;   À la fin de sa vie, il polémique avec Kant dans la "Métacritique de la critique de la raison pure" et développe une esthétique originale dans "Kalligone".  Son insistance sur la culture, la langue et le peuple marquera durablement les théories de la nation, de l’anthropologie culturelle et de la philosophie de l’histoire. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Gottfried_von_Herder"  title=" Wikipedia"&gt;Johann Gottfried HERDER&lt;/a&gt; était un philosophe  et écrivain allemand souvent considéré comme l’un des pères de la philosophie de la culture et de &lt;a href="https://www.jdarriulat.net/Introductionphiloesth/PhiloModerne/Herder.html"  title="INTRODUCTION A LA PHILOSOPHIE ESTHETIQUE par jdarriulat"&gt;l’idée moderne &lt;/a&gt; de "nation". Son œuvre se situe à la croisée des Lumières et du premier romantisme allemand. Il refuse l’idée d’un progrès linéaire et uniforme de l’humanité vers une &lt;a href="https://www.youtube.com/watch?v=Y8l9aJhT76U" title="Johann Gottfried Herder par Greatest Minds in History"&gt;seule forme de civilisation&lt;/a&gt;, telle qu’on la trouve chez certains auteurs des Lumières. Chaque époque et chaque peuple possède, selon lui, une valeur propre qui doit être comprise de l’intérieur et non jugée à l’aune d’un modèle abstrait. Il propose une philosophie de l’histoire "humanitaire" : l’histoire est le développement de l’humanité en tant que telle, dans sa pluralité de formes, sous le signe de la culture, de la liberté et de la perfectibilité.  &lt;/p&gt; &lt;p&gt; Il attribue au langage un rôle constitutif dans la formation de la pensée humaine, contre l’idée d’une raison pure préexistante à toute expérience linguistique. La raison ne précède pas le langage, elle se forme à travers lui, si bien que connaître, c’est toujours déjà interpréter à l’aide de mots et de symboles historiques. Il s’intéresse à l’origine des langues et parle d’un "roman des langues" pour décrire l’histoire par laquelle les hommes passent d’un stade prélinguistique à des formes complexes de communication et de socialisation. &lt;/p&gt; &lt;p&gt; Son œuvre est très abondante, mais quelques titres structurent sa pensée. On cite notamment : "Auch eine Philosophie der Geschichte zur Bildung der Menschheit" paru en 1774 et surtout &lt;a href="https://de.wikipedia.org/wiki/Ideen_zur_Philosophie_der_Geschichte_der_Menschheit" title="Ideen zur Philosophie der Geschichte der Menschheit par wikipedia"&gt;"Ideen zur Philosophie der Geschichte der Menschheit"&lt;/a&gt; qui proposent une vaste vision historico‑culturelle de l’humanité. &lt;/p&gt; &lt;p&gt;   À la fin de sa vie, il polémique avec Kant dans la "Métacritique de la critique de la raison pure" et développe une esthétique originale dans "Kalligone".  Son insistance sur la culture, la langue et le peuple marquera durablement les théories de la nation, de l’anthropologie culturelle et de la philosophie de l’histoire. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F76" s="47" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="E78" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jeremy_Bentham"  title=" Wikipedia"&gt;Jérémy BENTHAM&lt;/a&gt; était un philosophe Anglais, économiste et réformateur social . &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs de &lt;a  href="https://www.youtube.com/watch?v=yCDOVcvNYpY&amp;t=2s&amp;ab_channel=AlainBajom%C3%A9e"  title="L'utilitarisme par Alain Bajomée"&gt;l'utilitarisme&lt;/a&gt;, une doctrine éthique qui affirme que la meilleure action est celle qui produit le plus grand bien-être pour le plus grand nombre de personnes possible. Selon lui, la nature humaine est motivée par la recherche du &lt;a  href="https://www.youtube.com/watch?v=2c6jMZr6-Jc&amp;ab_channel=LePr%C3%A9cepteur"  title="Sommes nous tous égoiste par Le Précepteur"&gt;plaisir personnel&lt;/a&gt; et l'évitement de la douleur, et donc la recherche du bonheur est la fin ultime de toute action. &lt;/p&gt; &lt;p&gt;  rejette les fondements moraux traditionnels (coutume, religion, devoir abstrait) au profit de l'utilité : une loi ou action est bonne si elle augmente le bonheur net de la société, somme des bonheurs individuels. Il distingue plaisirs quantifiables (sans hiérarchie entre supérieurs ou inférieurs) et prône un État interventionniste pour protéger les libertés, redistribuer les richesses (taxe progressive sur héritages) et encourager la croissance économique et démographique. &lt;/p&gt; &lt;p&gt; Il a également proposé le principe de l'égalité morale, selon lequel chaque individu compte pour un dans le calcul du bonheur global, ce qui signifie que chaque vie a la même importance morale. Cela a conduit Bentham à être un défenseur de l'égalité des  &lt;a  href="https://www.youtube.com/watch?v=xJDQu0OLwME&amp;ab_channel=MonsieurPhi"  title="L'homosexualité par Mr Phi"&gt;droits pour tous&lt;/a&gt;, y compris les femmes et les minorités. &lt;/p&gt; &lt;p&gt;Il a été un critique de la philosophie morale traditionnelle, qui était souvent basée sur des notions abstraites telles que la vertu et le devoir. Il a plutôt cherché à fonder &lt;a  href="https://www.youtube.com/watch?v=mvamwoVi1KE"  title="Bentham, qu’est ce l’utilitarisme par Le Précepteur"&gt; l'éthique sur des principes empiriques, &lt;/a&gt; en se basant sur des observations et des expériences concrètes. Il  appliqua sa philosophie à la réforme pénale (contre la peine de mort arbitraire), juridique (code pénal rationnel), économique (rôle de l'État dans sécurité et subsistance) et sociale (éducation, santé publique). Critiqué pour son hédonisme mécanique, il influença Mill, le libéralisme social et les politiques publiques modernes.    &lt;/p&gt;  &lt;audio controls title="Dans la peau de Jeremy Bentham par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10081-29.01.2018-ITEMA_21570270-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jeremy_Bentham"  title=" Wikipedia"&gt;Jérémy BENTHAM&lt;/a&gt; était un philosophe Anglais, économiste et réformateur social. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs de &lt;a  href="https://www.youtube.com/watch?v=yCDOVcvNYpY&amp;t=2s&amp;ab_channel=AlainBajom%C3%A9e"  title="L'utilitarisme par Alain Bajomée"&gt;l'utilitarisme&lt;/a&gt;, une doctrine éthique qui affirme que la meilleure action est celle qui produit le plus grand bien-être pour le plus grand nombre de personnes possible. Selon lui, la nature humaine est motivée par la recherche du &lt;a  href="https://www.youtube.com/watch?v=2c6jMZr6-Jc&amp;ab_channel=LePr%C3%A9cepteur"  title="Sommes nous tous égoiste par Le Précepteur"&gt;plaisir personnel&lt;/a&gt; et l'évitement de la douleur, et donc la recherche du bonheur est la fin ultime de toute action. &lt;/p&gt; &lt;p&gt; Bentham rejette les fondements moraux traditionnels (coutume, religion, devoir abstrait) au profit de l'utilité : une loi ou action est bonne si elle augmente le bonheur net de la société, somme des bonheurs individuels. Il distingue plaisirs quantifiables (sans hiérarchie entre supérieurs ou inférieurs) et prône un État interventionniste pour protéger les libertés, redistribuer les richesses (taxe progressive sur héritages) et encourager la croissance économique et démographique. &lt;/p&gt; &lt;p&gt; Il a également proposé le principe de l'égalité morale, selon lequel chaque individu compte pour un dans le calcul du bonheur global, ce qui signifie que chaque vie a la même importance morale. Cela a conduit Bentham à être un défenseur de l'égalité des  &lt;a  href="https://www.youtube.com/watch?v=xJDQu0OLwME&amp;ab_channel=MonsieurPhi"  title="L'homosexualité par Mr Phi"&gt;droits pour tous&lt;/a&gt;, y compris les femmes et les minorités. &lt;/p&gt; &lt;p&gt;Il a été un critique de la philosophie morale traditionnelle, qui était souvent basée sur des notions abstraites telles que la vertu et le devoir. Il a plutôt cherché à fonder &lt;a  href="https://www.youtube.com/watch?v=mvamwoVi1KE"  title="Bentham, qu’est ce l’utilitarisme par Le Précepteur"&gt; l'éthique sur des principes empiriques, &lt;/a&gt; en se basant sur des observations et des expériences concrètes. Il  appliqua sa philosophie à la réforme pénale (contre la peine de mort arbitraire), juridique (code pénal rationnel), économique (rôle de l'État dans sécurité et subsistance) et sociale (éducation, santé publique). Critiqué pour son hédonisme mécanique, il influença Mill, le libéralisme social et les politiques publiques modernes.    &lt;/p&gt;  &lt;audio controls title="Dans la peau de Jeremy Bentham par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10081-29.01.2018-ITEMA_21570270-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F78" s="47" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="E81" s="63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_de_Bonald"  title=" Wikipedia"&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href="https://fr.wikipedia.org/wiki/Tradition_primordiale"  title=" Tradition Primordiale de Maistre par Wikipedia "&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. - Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. - Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href="https://www.youtube.com/watch?v=WMB9kethTWIe"  title=" Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations "&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href="https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral"  title=" Maurrassisme par Wikipedia "&gt; maurrassisme, &lt;a&gt; voyant la France comme "nation-pilote" pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant . &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_de_Bonald"  title=" Wikipedia"&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href="https://fr.wikipedia.org/wiki/Tradition_primordiale"  title=" Tradition Primordiale de Maistre par Wikipedia "&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. - Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. - Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href="https://www.youtube.com/watch?v=WMB9kethTWIe"  title=" Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations "&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href="https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral"  title=" Maurrassisme par Wikipedia "&gt; maurrassisme, &lt;a&gt; voyant la France comme "nation-pilote" pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant. &lt;/p&gt;
 //</t>
         </is>
       </c>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="L23" s="46" t="inlineStr">
         <is>
-          <t>Empirisme</t>
+          <t xml:space="preserve">Empirisme ; Progressisme</t>
         </is>
       </c>
       <c r="M23" s="35" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="L29" s="46" t="inlineStr">
         <is>
-          <t>Eclectisme</t>
+          <t xml:space="preserve">Eclectisme ; Pansophisme</t>
         </is>
       </c>
       <c r="M29" s="35" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="L32" s="46" t="inlineStr">
         <is>
-          <t>Rationalisme ; Dualisme ; Anthropocentrisme</t>
+          <t xml:space="preserve">Rationalisme ; Dualisme ; Anthropocentrisme ; Méthodisme</t>
         </is>
       </c>
       <c r="M32" s="35" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="L40" s="46" t="inlineStr">
         <is>
-          <t>Empirisme ; Libéralisme</t>
+          <t xml:space="preserve">Empirisme ; Libéralisme ; Méthodisme ; Conceptualisme</t>
         </is>
       </c>
       <c r="M40" s="35" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="L41" s="46" t="inlineStr">
         <is>
-          <t>Occasionalisme ; Ontologisme</t>
+          <t xml:space="preserve">Occasionalisme ; Ontologisme ; Dualisme</t>
         </is>
       </c>
       <c r="M41" s="35" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="L42" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rationalisme ; Fatalisme ; Oecuménisme</t>
+          <t xml:space="preserve">Rationalisme ; Fatalisme ; Oecuménisme ; Pansophisme</t>
         </is>
       </c>
       <c r="M42" s="35" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="L45" s="46" t="inlineStr">
         <is>
-          <t>Matérialisme</t>
+          <t xml:space="preserve">Matérialisme ; Athéisme</t>
         </is>
       </c>
       <c r="M45" s="35" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="L48" s="46" t="inlineStr">
         <is>
-          <t>Rationalisme</t>
+          <t xml:space="preserve">Rationalisme ; Ontologie</t>
         </is>
       </c>
       <c r="M48" s="35" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="L54" s="46" t="inlineStr">
         <is>
-          <t>Spiritualisme ; Méthodisme</t>
+          <t xml:space="preserve">Spiritualisme</t>
         </is>
       </c>
       <c r="M54" s="35" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="L56" s="46" t="inlineStr">
         <is>
-          <t>Matérialisme ; Épiphénoménisme</t>
+          <t xml:space="preserve">Matérialisme ; Épiphénoménisme ; Athéisme</t>
         </is>
       </c>
       <c r="M56" s="35" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L57" s="46" t="inlineStr">
         <is>
-          <t>Empirisme</t>
+          <t xml:space="preserve">Empirisme ; Particularisme</t>
         </is>
       </c>
       <c r="M57" s="35" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="L58" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empirisme ; Scepticisme ; Agnosticisme ; Lumières</t>
+          <t xml:space="preserve">Empirisme ; Scepticisme ; Agnosticisme ; Lumières ; Méthodisme ; Phénoménisme</t>
         </is>
       </c>
       <c r="M58" s="35" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L60" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matérialisme ; Lumières</t>
+          <t xml:space="preserve">Matérialisme ; Lumières ; Athéisme</t>
         </is>
       </c>
       <c r="M60" s="35" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="L66" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matérialisme ; Athéisme ; Lumières</t>
+          <t xml:space="preserve">Matérialisme ; Athéisme ; Lumières ; Incompatibilisme</t>
         </is>
       </c>
       <c r="M66" s="35" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L72" s="46" t="inlineStr">
         <is>
-          <t>Spiritualisme ; Irrationalisme</t>
+          <t xml:space="preserve">Spiritualisme</t>
         </is>
       </c>
       <c r="M72" s="35" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L74" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme ; Lumières</t>
+          <t xml:space="preserve">Positivisme ; Lumières ; Progressisme</t>
         </is>
       </c>
       <c r="M74" s="35" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="L75" s="46" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t xml:space="preserve">Spiritualisme ; Irrationalisme</t>
         </is>
       </c>
       <c r="M75" s="35" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="L80" s="46" t="inlineStr">
         <is>
-          <t>Conservatisme</t>
+          <t xml:space="preserve">Conservatisme ; Martinisme</t>
         </is>
       </c>
       <c r="M80" s="35" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="L81" s="46" t="inlineStr">
         <is>
-          <t>Conservatisme ; Maurrassisme</t>
+          <t xml:space="preserve">Conservatisme</t>
         </is>
       </c>
       <c r="M81" s="35" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -7115,6 +7115,62 @@
         </is>
       </c>
       <c r="P98"/>
+    </row>
+    <row r="99" ht="130.5" customHeight="1" s="39">
+      <c r="A99" s="47">
+        <v>1680</v>
+      </c>
+      <c r="B99" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1732</t>
+        </is>
+      </c>
+      <c r="C99" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1680 – 1732</t>
+        </is>
+      </c>
+      <c r="D99" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arthur COLLIER</t>
+        </is>
+      </c>
+      <c r="E99" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Arthur_Collier" title=" Wikipedia (en)"&gt;Arthur COLLIER&lt;/a&gt; est un pasteur et philosophe anglais. Né en 1680 à Steeple Langford, dans le Wiltshire, dans une famille de pasteurs, il étudie à Oxford et succède à son père comme recteur de la paroisse de Langford Magna, où il passe toute sa vie. Lecteur de Descartes et surtout de Malebranche, il réfléchit dès 1703 à la question de l’existence du monde extérieur.&lt;/p&gt; &lt;p&gt;En 1713, il publie la &lt;em&gt;Clavis Universalis&lt;/em&gt;, « la clé universelle », sous-titrée « nouvelle recherche de la vérité, démonstration de la non-existence ou de l’impossibilité d’un monde extérieur ». Il y soutient, comme &lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley" title=" Wikipedia"&gt;Berkeley&lt;/a&gt; dans ses &lt;em&gt;Principes&lt;/em&gt; de 1710, l’&lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Wikipedia"&gt;immatérialisme&lt;/a&gt; : le monde visible n’existe que dans l’esprit qui le perçoit, et une matière extérieure, indépendante de toute perception, est une idée contradictoire. Il en donne plusieurs preuves : l’idée d’un monde extérieur conduit à dire qu’il est à la fois fini et infini, divisible à l’infini et pourtant composé de parties.&lt;/p&gt; &lt;p&gt;Collier affirme être arrivé à ces conclusions seul, sans avoir lu Berkeley, et les historiens le croient généralement : les deux auteurs partent de Malebranche, mais avec des arguments différents. Son livre passe presque inaperçu de son vivant. Il meurt en 1732. Redécouvert au XVIIIe siècle par Thomas Reid, puis réédité au XIXe siècle, il est aujourd’hui considéré comme le second fondateur de l’immatérialisme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/collier-mini.webp</t>
+        </is>
+      </c>
+      <c r="J99" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K99" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique</t>
+        </is>
+      </c>
+      <c r="L99" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Immatérialisme</t>
+        </is>
+      </c>
+      <c r="M99" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pasteur et philosophe anglais qui défendit l’immatérialisme en même temps que Berkeley.</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P99"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -7171,6 +7171,62 @@
         </is>
       </c>
       <c r="P99"/>
+    </row>
+    <row r="100" ht="130.5" customHeight="1" s="39">
+      <c r="A100" s="47">
+        <v>1657</v>
+      </c>
+      <c r="B100" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1757</t>
+        </is>
+      </c>
+      <c r="C100" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1657 – 1757</t>
+        </is>
+      </c>
+      <c r="D100" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernard Le Bouyer de FONTENELLE</t>
+        </is>
+      </c>
+      <c r="E100" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Le_Bouyer_de_Fontenelle" title=" Wikipedia"&gt;Bernard Le Bouyer de FONTENELLE&lt;/a&gt; est un écrivain et savant français, l’un des grands passeurs entre l’âge classique et les &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt;. Né à Rouen en 1657, neveu de Pierre et Thomas Corneille, il abandonne vite le barreau pour les lettres et le théâtre, sans grand succès, avant de trouver sa voie dans la diffusion des sciences. Dans les &lt;em&gt;Entretiens sur la pluralité des mondes&lt;/em&gt; (1686), un philosophe explique à une marquise, au cours de promenades nocturnes, le système de Copernic et les tourbillons de Descartes, et imagine des habitants sur les autres planètes.&lt;/p&gt; &lt;p&gt;Ce livre élégant, l’un des premiers grands succès de la vulgarisation scientifique, enlève à la Terre et à l’homme leur place au centre du monde. L’année suivante, l’&lt;em&gt;Histoire des oracles&lt;/em&gt; (1687) montre que les oracles païens n’étaient pas l’œuvre des démons, mais des tromperies des prêtres : sous couvert d’Antiquité, c’est toute la crédulité religieuse qui est visée. Dans la querelle des Anciens et des Modernes, sa &lt;em&gt;Digression&lt;/em&gt; de 1688 prend le parti des Modernes : la nature n’a pas changé, et les connaissances s’accumulent au fil des siècles, ce qui annonce l’idée de progrès.&lt;/p&gt; &lt;p&gt;Élu à l’Académie française en 1691, il est de 1697 à 1740 le secrétaire perpétuel de l’Académie royale des sciences, dont il rédige chaque année l’histoire et les éloges des savants disparus, rendant accessibles les travaux de Leibniz ou de Newton. Fidèle jusqu’au bout à la physique de &lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Descartes" title=" Wikipedia"&gt;Descartes&lt;/a&gt;, il défend encore les tourbillons contre l’attraction newtonienne. Il meurt à Paris en 1757, à presque cent ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fontenelle-mini.webp</t>
+        </is>
+      </c>
+      <c r="J100" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K100" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L100" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartésianisme ; Lumières</t>
+        </is>
+      </c>
+      <c r="M100" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain français, vulgarisateur de la science cartésienne et précurseur des Lumières.</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P100"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -2475,9 +2475,7 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Thomas_Hobbes"  title=" Wikipedia"&gt;Thomas HOBBES&lt;/a&gt; était un philosophe anglais et fondateur de la philosophie politique moderne connu pour son ouvrage majeur, &lt;a href="https://www.youtube.com/watch?v=8sYAaiDjf0U&amp;ab_channel=AlainBajom%C3%A9e" title="Le Léviathan par Alain Bajomé"&gt;"Léviathan"&lt;/a&gt;, publié en 1651, dans lequel il développe sa vision de la nature humaine et de la société. Il partait du constat que l'être humain est fondamentalement égoïste et cherchera toujours à obtenir ce qu'il désire, même si cela nuit aux autres, car &lt;a href="https://www.youtube.com/watch?v=isCVgDObx4c&amp;ab_channel=LePr%C3%A9cepteur"  title="L'homme est un loup pour l'homme par Le Précepteur"&gt;"L'homme est un loup pour l'homme"&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Pour lui, cette tendance naturelle à l'égoïsme et à la violence rendait impossible la coexistence pacifique entre les hommes, à moins qu'ils ne se soumettent tous volontairement à une autorité souveraine forte. C'est pourquoi, la société doit être gouvernée par un pouvoir absolu, représenté par un souverain, qui impose l'ordre et la sécurité. &lt;/p&gt; &lt;p&gt;  Pour lui, le contrat social est un moyen pour les individus de renoncer à leur liberté naturelle en échange de la sécurité que leur offre l'Etat. Le souverain est donc le garant de cette sécurité, et il doit être obéi sans réserve, même si cela signifie restreindre certaines libertés individuelles. &lt;/p&gt; &lt;p&gt; 
-Hobbes a également développé une théorie de l'Etat de nature, dans lequel les hommes vivraient dans un état de guerre perpétuelle, sans lois ni règles pour les protéger. Pour lui, l'Etat de nature était un état de violence, de peur et d'insécurité, et c'est pour échapper à cet état que les hommes ont créé la société. &lt;/p&gt;   &lt;audio controls title="Le pacte d'obéissance par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22060-04.04.2021-ITEMA_22630431-2012C12410E0123.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-&lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Hobbes"  title=" Wikipedia"&gt;Thomas HOBBES&lt;/a&gt; (1588-1679) est un philosophe anglais, fondateur de la philosophie politique moderne. Né, dit-il, prématurément de la peur de sa mère à l’approche de l’Invincible Armada espagnole, il affirmait : « la peur et moi sommes nés jumeaux. » Précepteur dans la grande famille Cavendish, il voyage en Europe, rencontre Galilée et fréquente à Paris le cercle de Mersenne. Pendant la guerre civile anglaise, il vit en exil en France, de 1640 à 1651.&lt;/p&gt; &lt;p&gt;Hobbes est matérialiste : tout ce qui existe est corps en mouvement, et l’homme lui-même est une mécanique mue par ses désirs et ses craintes. Dans le &lt;a href="https://www.youtube.com/watch?v=8sYAaiDjf0U&amp;ab_channel=AlainBajom%C3%A9e" title="Le Léviathan par Alain Bajomé"&gt;&lt;em&gt;Léviathan&lt;/em&gt;&lt;/a&gt; (1651), il imagine la vie sans État, dans l’« état de nature ». Les hommes y sont à peu près égaux, chacun pouvant tuer l’autre, et la concurrence, la méfiance et l’orgueil les poussent à une « guerre de chacun contre chacun ». La vie y est « solitaire, misérable, dangereuse, animale et brève » : &lt;a href="https://www.youtube.com/watch?v=isCVgDObx4c&amp;ab_channel=LePr%C3%A9cepteur"  title="L'homme est un loup pour l'homme par Le Précepteur"&gt;l’homme est un loup pour l’homme&lt;/a&gt;, selon la formule de Plaute qu’il reprend. Pour échapper à la peur de la mort violente, la raison conseille de rechercher la paix. Les hommes passent donc un contrat par lequel chacun renonce à son droit de tout faire et le transfère à un souverain, un homme ou une assemblée, qui reçoit un pouvoir absolu et indivisible. Ce « dieu mortel », le Léviathan, assure la sécurité de tous ; lui obéir est le prix de la paix. Seul le droit de défendre sa vie ne peut être aliéné.&lt;/p&gt; &lt;p&gt;Accusé d’athéisme, Hobbes fut très critiqué. Mais en fondant le pouvoir sur l’accord des individus plutôt que sur Dieu ou la tradition, il ouvre la voie à Locke et à Rousseau.&lt;/p&gt;  &lt;audio controls title="Le pacte d'obéissance par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22060-04.04.2021-ITEMA_22630431-2012C12410E0123.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F28" s="61" t="inlineStr">
@@ -3220,8 +3218,7 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza"  title=" Wikipedia"&gt; Baruch SPINOZA&lt;/a&gt; était un philosophe hollandais et un penseur influent en opposition à Descartes en son époque. &lt;/p&gt; &lt;p&gt; Sa philosophie &lt;a href="https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur"  title="Le déterminisme par le Précepteur"&gt;déterministe&lt;/a&gt; se caractérise par sa vision &lt;a href="https://fr.wikipedia.org/wiki/Monisme"    title="Le monisme est la position philosophique qui affirme l'unité indivisible de l'être"&gt;moniste&lt;/a&gt; de l'univers, selon laquelle tout ce qui existe est une expression de la même substance divine, qu'il appelle &lt;a href="https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur"  title="Dieu égale nature"&gt;Dieu ou Nature&lt;/a&gt; et elle est souvent associée au rationalisme, à l'athéisme et au panthéisme. &lt;/p&gt; &lt;p&gt; Pour lui, la raison est la clé de la liberté et du bonheur. Il affirme que  &lt;a href="https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos"  title="Les passions tristes par Kosmos"&gt;les passions&lt;/a&gt; peuvent nous éloigner de la vérité et nous rendre esclaves de nos désirs. &lt;/p&gt; &lt;p&gt;Pour être libre, l'homme doit comprendre la nature des choses et apprendre à contrôler ses passions. Cela implique une acceptation de la nécessité et de la causalité, car tout ce qui arrive est le résultat de la nature des choses et que, de ce fait, &lt;a  href="https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur"   title="Le libre arbitre n'est il qu'une illusion? par le Précepteur"&gt;le libre arbitre n'existe pas.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Dans sa célèbre œuvre "L'Éthique", il élabore une théorie éthique basée sur l'idée que la raison est la clé de la liberté et du bonheur avec sa notion de &lt;a href="https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur"   title="Le conatus par le Précepteur"&gt;"Conatus".&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; En politique, il est souvent associé à la défense de la liberté d'expression et de la tolérance religieuse. Il a écrit un ouvrage intitulé  &lt;a href="https://www.youtube.com/watch?v=Zqt0QZVrTkI"   title="Le Traité TP par PrepaUp"&gt;"Le Traité théologico-politique"&lt;/a&gt; dans lequel il soutient que la religion doit être séparée de l'État et que chacun doit être libre de pratiquer sa religion sans être persécuté.&lt;/p&gt;    &lt;audio controls title="Spinoza est il le philosophe du bonheur ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-&lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza"  title=" Wikipedia"&gt;Baruch SPINOZA&lt;/a&gt; (1632-1677) est un philosophe néerlandais, l’un des grands rationalistes du XVIIe siècle. Né à Amsterdam dans une famille de marchands juifs d’origine portugaise, il est exclu de sa communauté en 1656 pour ses opinions jugées hérétiques. Il vit ensuite modestement, polissant des verres d’optique, refuse une chaire à l’université de Heidelberg pour garder sa liberté, et meurt à quarante-quatre ans.&lt;/p&gt; &lt;p&gt;Son œuvre majeure, l’&lt;em&gt;Éthique&lt;/em&gt;, publiée après sa mort, est « démontrée selon l’ordre géométrique », comme un traité de mathématiques. Spinoza y défend une vision &lt;a href="https://fr.wikipedia.org/wiki/Monisme"    title="Le monisme est la position philosophique qui affirme l'unité indivisible de l'être"&gt;moniste&lt;/a&gt; : il n’existe qu’une seule substance, infinie, &lt;a href="https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur"  title="Dieu égale nature"&gt;« Dieu ou la Nature »&lt;/a&gt;. La pensée et l’étendue en sont deux attributs, et chaque corps, chaque esprit, en est une manière d’être. Dieu n’agit pas selon des fins : tout découle nécessairement de sa nature, d’où une philosophie &lt;a href="https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur"  title="Le déterminisme par le Précepteur"&gt;déterministe&lt;/a&gt;. &lt;a  href="https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur"   title="Le libre arbitre n'est il qu'une illusion? par le Précepteur"&gt;Le libre arbitre est une illusion&lt;/a&gt; : nous nous croyons libres parce que nous ignorons les causes qui nous déterminent. Chaque être s’efforce de persévérer dans son être : c’est le &lt;a href="https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur"   title="Le conatus par le Précepteur"&gt;&lt;em&gt;conatus&lt;/em&gt;&lt;/a&gt;, l’essence même de l’homme, son désir. Ce qui augmente notre puissance d’agir nous réjouit, ce qui la diminue nous attriste, et &lt;a href="https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos"  title="Les passions tristes par Kosmos"&gt;les passions&lt;/a&gt; tristes, la haine, la crainte, l’espoir, nous rendent esclaves. La liberté consiste à comprendre la nécessité des choses ; la plus haute joie est l’« amour intellectuel de Dieu ».&lt;/p&gt; &lt;p&gt;Dans le &lt;a href="https://www.youtube.com/watch?v=Zqt0QZVrTkI"   title="Le Traité TP par PrepaUp"&gt;&lt;em&gt;Traité théologico-politique&lt;/em&gt;&lt;/a&gt; (1670), il lit la Bible en historien et défend la liberté de penser, que l’État doit garantir. Accusé d’athéisme, il inspire les Lumières, Hegel, Nietzsche et Einstein.&lt;/p&gt;  &lt;audio controls title="Spinoza est il le philosophe du bonheur ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F39" s="47" t="inlineStr">
@@ -3295,10 +3292,7 @@
       </c>
       <c r="E40" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/John_Locke"  title=" Wikipedia"&gt;John LOCKE&lt;/a&gt; était un philosophe anglais connu pour ses contributions en philosophie politique, en épistémologie et en théorie de l'éducation. &lt;/p&gt; &lt;p&gt; L'une de ses idées les plus célèbres est celle de la tabula rasa, qui signifie "table rase" en latin. Selon lui, l'esprit humain est vide à la naissance, sans aucune connaissance innée ou idées préconçues. C'est seulement par l'expérience sensorielle et la réflexion que nous acquérons des connaissances et des idées.&lt;/p&gt; &lt;p&gt; 
-Dans son ouvrage majeur,  &lt;a href="https://fr.wikisource.org/wiki/Livre:Locke_-_Essai_sur_l%E2%80%99entendement_humain.djvu"  title="Essai sur l'entendement humain par Wikisource"&gt;"Essai sur l'entendement humain"&lt;/a&gt;, il élabore une théorie de la connaissance empirique, qui affirme que toute notre connaissance provient de l'expérience. Il soutient également que la raison humaine est limitée et que les connaissances les plus élevées ne peuvent être atteintes que par une observation attentive des faits et des phénomènes. &lt;/p&gt; &lt;p&gt; 
-En politique, il est connu pour sa théorie du &lt;a href="https://www.youtube.com/watch?v=lU_sAreHchQ&amp;ab_channel=Lespodcastsphilosophiques"  title="la liberté politique par Les podcasts philo"&gt;"contrat social"&lt;/a&gt;, qui stipule que le gouvernement tire sa légitimité du consentement des gouvernés. Selon lui, les individus ont des droits naturels inaliénables tels que la vie, la liberté et la propriété, que le gouvernement a pour tâche de protéger. &lt;/p&gt; &lt;p&gt; 
-Il a également plaidé pour la tolérance religieuse et la séparation de l'Église et de l'État et a soutenu que chaque individu devrait être libre de pratiquer sa religion sans crainte de persécution.  &lt;/p&gt;  &lt;audio controls title="L'invention de la conscience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21976-01.02.2021-ITEMA_22560721-2015C12410S0287.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Locke"  title=" Wikipedia"&gt;John LOCKE&lt;/a&gt; (1632-1704) est un philosophe anglais, fondateur de l’empirisme moderne et l’un des pères du libéralisme politique. Formé à Oxford, où il étudie aussi la médecine, il devient le médecin et le conseiller de Lord Shaftesbury, chef de l’opposition au roi. Exilé aux Pays-Bas en 1683, il ne revient en Angleterre qu’après la « Glorieuse Révolution » de 1688, qui établit une monarchie limitée, et publie alors ses grands livres.&lt;/p&gt; &lt;p&gt;Dans l’&lt;a href="https://fr.wikisource.org/wiki/Livre:Locke_-_Essai_sur_l%E2%80%99entendement_humain.djvu"  title="Essai sur l'entendement humain par Wikisource"&gt;&lt;em&gt;Essai sur l’entendement humain&lt;/em&gt;&lt;/a&gt; (1690), il combat la théorie des idées innées défendue par Descartes : à la naissance, l’esprit est comme une « table rase », une feuille blanche. Toutes nos idées viennent de l’expérience, soit de la sensation, qui nous fait connaître les choses extérieures, soit de la réflexion, qui nous fait connaître les opérations de notre esprit ; les idées simples se combinent ensuite en idées complexes. Locke définit aussi l’identité personnelle par la conscience et la mémoire. Dans le &lt;em&gt;Second Traité du gouvernement civil&lt;/em&gt; (1690), il imagine un état de nature où les hommes, libres et égaux, ont des droits naturels : la vie, la liberté et la propriété, qui naît du travail. Pour mieux les protéger, ils forment par un &lt;a href="https://www.youtube.com/watch?v=lU_sAreHchQ&amp;ab_channel=Lespodcastsphilosophiques"  title="la liberté politique par Les podcasts philo"&gt;contrat social&lt;/a&gt; un gouvernement qui ne tient son pouvoir que de leur consentement ; s’il viole ces droits, le peuple peut lui résister. Locke distingue enfin le pouvoir législatif et le pouvoir exécutif.&lt;/p&gt; &lt;p&gt;Dans sa &lt;em&gt;Lettre sur la tolérance&lt;/em&gt; (1689), il demande que l’État laisse chacun libre de sa religion. Ses idées inspirent Voltaire, Montesquieu et la Déclaration d’indépendance américaine.&lt;/p&gt;  &lt;audio controls title="L'invention de la conscience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21976-01.02.2021-ITEMA_22560721-2015C12410S0287.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F40" s="47" t="inlineStr">
@@ -3910,8 +3904,7 @@
       </c>
       <c r="E49" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley"    title=" Wikipedia"&gt;Georges BERKELEY&lt;/a&gt; était un philosophe, évêque anglican et scientifique anglo-irlandais, célèbre pour sa philosophie empiriste et idéaliste, souvent résumée par la formule latine &lt;a href="https://www.youtube.com/watch?v=gcyFtJ1ZtrA"  title=" Berkeley Être c'est être perçu ou percevoir par Coursitout"&gt;"Esse est percipi"&lt;/a&gt; (être, c'est être perçu).&lt;/p&gt; &lt;p&gt;L'Idéalisme  &lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Immatérialisme  par Wikipedia"&gt; immatérialiste&lt;/a&gt; est le cœur de sa philosophie. Il soutenait que la réalité ne consiste qu'en esprits et leurs idées. Pour lui, les objets physiques n'existent pas indépendamment d'être perçus. Quand nous ne percevons pas un objet, il continue d'exister parce que Dieu le perçoit constamment et il croit que toute connaissance provient de l'expérience sensorielle. Cependant, il pousse l'empirisme à sa conclusion logique en niant l'existence d'une "substance matérielle" indépendante des perceptions. Il affirme que toutes les qualités sont des perceptions. Il n'y a pas de matière "derrière" les qualités perçues.&lt;/p&gt; &lt;p&gt;Ses trois oeuvres principales sont "Essai sur une nouvelle théorie de la vision sortie en 1709,  &lt;a href="https://www.youtube.com/watch?v=wBivRdgKgd0"  title=" Berkeley pour les nuls  par Alexis Vildier"&gt;"Traité des principes de la connaissance humaine"&lt;/a&gt; en 1710 et "Trois dialogues entre Hylas et Philonous en 1713. Sa  pensée, bien que souvent considérée comme contre-intuitive, est très cohérente et a marqué l'histoire de la philosophie par son radicalisme et sa remise en question des conceptions traditionnelles de la réalité. &lt;/p&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley"    title=" Wikipedia"&gt;Georges BERKELEY&lt;/a&gt; (1685-1753) est un philosophe irlandais et évêque anglican, célèbre pour sa formule &lt;a href="https://www.youtube.com/watch?v=gcyFtJ1ZtrA"  title=" Berkeley Être c'est être perçu ou percevoir par Coursitout"&gt;&lt;em&gt;esse est percipi&lt;/em&gt;&lt;/a&gt;, « être, c’est être perçu ». Né près de Kilkenny, il étudie et enseigne au Trinity College de Dublin. Il séjourne en Amérique pour fonder un collège aux Bermudes, projet qui échoue, puis devient en 1734 évêque de Cloyne, en Irlande.&lt;/p&gt; &lt;p&gt;Dans l’&lt;em&gt;Essai pour une nouvelle théorie de la vision&lt;/em&gt; (1709), il montre que nous ne voyons pas directement la distance : nous l’apprenons en associant la vue au toucher. Dans le &lt;a href="https://www.youtube.com/watch?v=wBivRdgKgd0"  title=" Berkeley pour les nuls  par Alexis Vildier"&gt;&lt;em&gt;Traité des principes de la connaissance humaine&lt;/em&gt;&lt;/a&gt; (1710), puis dans les &lt;em&gt;Trois Dialogues entre Hylas et Philonous&lt;/em&gt; (1713), il défend une position &lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Immatérialisme  par Wikipedia"&gt;immatérialiste&lt;/a&gt;. Locke distinguait les qualités secondes des choses, couleurs, sons ou saveurs, qui n’existent que dans notre esprit, et leurs qualités premières, étendue, figure, mouvement, qui existeraient dans une matière extérieure. Berkeley montre que ces dernières sont aussi des idées : on ne peut concevoir une étendue sans couleur. Une chose n’est donc qu’un ensemble d’idées, et l’idée d’une « substance matérielle » cachée derrière nos perceptions est vide. Seuls existent les esprits et leurs idées. Si l’arbre du jardin continue d’exister quand personne ne le regarde, c’est que Dieu le perçoit toujours. Berkeley pense ainsi combattre le scepticisme et l’athéisme, que favorisait selon lui la croyance en une matière indépendante.&lt;/p&gt; &lt;p&gt;Sa doctrine, jugée paradoxale par ses contemporains, a marqué Hume et Kant. Une ville de Californie, siège d’une célèbre université, porte son nom.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F49" s="47" t="inlineStr">
@@ -5128,7 +5121,7 @@
       </c>
       <c r="E67" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant"  title=" Wikipedia"&gt; Emmanuel KANT&lt;/a&gt; était un philosophe &lt;a href="https://la-philosophie.com/philosophie-lumieres" style="color:#88A1E9"   title="La philosophie des Lumières par la-philosophie.com"&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant"  title="La philosophie pratique de Kant de l'encyclopédie Wikipédia"&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href="https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos"   title="C'est quoi la raison pure par Kosmos"&gt;"Critique de la raison pure"&lt;/a&gt;, publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href="https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos"  title="La loi morale par Kosmos"&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href="https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'impératif catégorique par le Précepteur"&gt;"Fondement de la métaphysique des moeurs"&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href="https://la-philosophie.com/espace-public-et-democratie"  title="Espace public par la-philosophie.com"&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les "Lumières" comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href="https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume"  title="Faculté de jugement par la-philosophie.com"&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title="Le monde: entre déterminisme et liberté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant"  title=" Wikipedia"&gt;Emmanuel KANT&lt;/a&gt; (1724-1804) est un philosophe allemand des &lt;a href="https://la-philosophie.com/philosophie-lumieres" style="color:#88A1E9"   title="La philosophie des Lumières par la-philosophie.com"&gt;Lumières&lt;/a&gt;, l’un des plus grands de l’histoire. Il passe toute sa vie à Königsberg, en Prusse orientale, où il enseigne à l’université. La lecture de Hume le « réveille de son sommeil dogmatique » et le conduit à examiner les pouvoirs et les limites de la raison.&lt;/p&gt; &lt;p&gt;Dans la &lt;a href="https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos"   title="C'est quoi la raison pure par Kosmos"&gt;&lt;em&gt;Critique de la raison pure&lt;/em&gt;&lt;/a&gt; (1781), il réconcilie le rationalisme et l’empirisme : toute connaissance commence avec l’expérience, mais n’en dérive pas tout entière. L’esprit impose ses propres formes, l’espace, le temps et des catégories comme la causalité, à ce qu’il perçoit : c’est sa « révolution copernicienne ». Nous ne connaissons donc que les phénomènes, non les choses en soi, et la raison ne peut démontrer ni l’existence de Dieu ni l’immortalité de l’âme. Dans les &lt;a href="https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'impératif catégorique par le Précepteur"&gt;&lt;em&gt;Fondements de la métaphysique des mœurs&lt;/em&gt;&lt;/a&gt; (1785), il fonde une &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant"  title="La philosophie pratique de Kant de l'encyclopédie Wikipédia"&gt;philosophie pratique&lt;/a&gt; sur le devoir. &lt;a href="https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos"  title="La loi morale par Kosmos"&gt;La loi morale&lt;/a&gt; ne dépend ni des circonstances ni des conséquences : c’est un impératif catégorique. « Agis uniquement d’après la maxime qui fait que tu peux vouloir en même temps qu’elle devienne une loi universelle », et traite toujours l’humanité, en toi et en autrui, comme une fin, jamais simplement comme un moyen. La &lt;em&gt;Critique de la faculté de juger&lt;/em&gt; (1790) analyse le &lt;a href="https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume"  title="Faculté de jugement par la-philosophie.com"&gt;jugement&lt;/a&gt; de goût : le beau plaît universellement, sans intérêt et sans concept.&lt;/p&gt; &lt;p&gt;Pour Kant, les Lumières sont « la sortie de l’homme hors de l’état de minorité » : « Ose savoir ! » Il réclame la liberté de l’usage public de la raison, qui fonde &lt;a href="https://la-philosophie.com/espace-public-et-democratie"  title="Espace public par la-philosophie.com"&gt;l’espace public&lt;/a&gt;, et rêve d’une paix perpétuelle entre les nations.&lt;/p&gt;  &lt;audio controls title="Le monde: entre déterminisme et liberté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F67" s="47" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -3614,26 +3614,92 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="207.75" customHeight="1" s="39">
-      <c r="A45" s="47" t="n">
+    <row r="45" ht="130.5" customHeight="1" s="39">
+      <c r="A45" s="47">
+        <v>1657</v>
+      </c>
+      <c r="B45" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1757</t>
+        </is>
+      </c>
+      <c r="C45" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1657 – 1757</t>
+        </is>
+      </c>
+      <c r="D45" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernard Le Bouyer de FONTENELLE</t>
+        </is>
+      </c>
+      <c r="E45" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Le_Bouyer_de_Fontenelle" title=" Wikipedia"&gt;Bernard Le Bouyer de FONTENELLE&lt;/a&gt; est un écrivain et savant français, l’un des grands passeurs entre l’âge classique et les &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt;. Né à Rouen et neveu de Pierre et Thomas Corneille, il abandonne vite le barreau pour les lettres et le théâtre, sans grand succès, avant de trouver sa voie dans la diffusion des sciences. Dans les&lt;a href="https://www.youtube.com/watch?v=5JsNkt5BWC4&amp;amp;list=PLzEKOeY60frzFBdwN_ieACocW0grgZsqS" title="&amp;quot;Entretien sur la pluralité des mondes&amp;quot; Bernard Le Bouyer de Fontenelle -PREMIER SOIR- par French_With_Kathlyne"&gt; &lt;em&gt;Entretiens sur la pluralité des mondes&lt;/em&gt; &lt;/a&gt;(1686), un philosophe explique à une marquise, au cours de promenades nocturnes, le &lt;a href="https://www.youtube.com/watch?v=V1yLZNI0B8s" title="Entretiens sur la pluralité des mondes - Bernard Le Bouyer de Fontenelle | Résumé animé  📚🎬 par Livres en Scène"&gt;système de Copernic&lt;/a&gt; et les tourbillons de Descartes, et imagine des habitants sur les autres planètes.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=MKV24MRfu4Y" title="Les Entretiens sur la Pluralité des Mondes de Fontenelle - Bac de Français par Coursitout"&gt;Ce livre élégant&lt;/a&gt;, l’un des premiers grands succès de la vulgarisation scientifique, enlève à la Terre et à l’homme leur place au centre du monde. L’année suivante, l’&lt;em&gt;Histoire des oracles&lt;/em&gt; (1687) montre que les oracles païens n’étaient pas l’œuvre des démons, mais des tromperies des prêtres : sous couvert d’Antiquité, c’est toute la crédulité religieuse qui est visée. Dans la querelle des Anciens et des Modernes, sa &lt;em&gt;Digression&lt;/em&gt; de 1688 prend le parti des Modernes : la nature n’a pas changé, et les connaissances s’accumulent au fil des siècles, ce qui annonce l’idée de progrès.&lt;/p&gt; &lt;p&gt;Élu à l’Académie française en 1691, il est de 1697 à 1740 le secrétaire perpétuel de l’Académie royale des sciences, dont il rédige chaque année l’histoire et les éloges des savants disparus, rendant accessibles les travaux de Leibniz ou de Newton. Fidèle jusqu’au bout à la physique de &lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Descartes" title=" Wikipedia"&gt;Descartes&lt;/a&gt;, il défend encore les tourbillons contre l’attraction newtonienne. Il meurt à Paris à presque cent ans.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YAYJ4udP4WA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Cours Bac Français | Fontenelle – Entretiens sur la pluralité des mondes" par MemoClasse</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fontenelle-mini.webp</t>
+        </is>
+      </c>
+      <c r="J45" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K45" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L45" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartésianisme ; Lumières</t>
+        </is>
+      </c>
+      <c r="M45" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">écrivain français, vulgarisateur de la science cartésienne et précurseur des Lumières.</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P45"/>
+    </row>
+    <row r="46" ht="207.75" customHeight="1" s="39">
+      <c r="A46" s="47" t="n">
         <v>1664</v>
       </c>
-      <c r="B45" s="47" t="inlineStr">
+      <c r="B46" s="47" t="inlineStr">
         <is>
           <t>1729</t>
         </is>
       </c>
-      <c r="C45" s="47" t="inlineStr">
+      <c r="C46" s="47" t="inlineStr">
         <is>
           <t>1664 - 1729</t>
         </is>
       </c>
-      <c r="D45" s="48" t="inlineStr">
+      <c r="D46" s="48" t="inlineStr">
         <is>
           <t>Jean MESLIER</t>
         </is>
       </c>
-      <c r="E45" s="49" t="inlineStr">
+      <c r="E46" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Meslier"  title=" Wikipedia"&gt;Jean MESLIER&lt;/a&gt; était un prêtre français connu pour son &lt;a href="https://www.youtube.com/watch?v=5s-nuRI6dKY&amp;ab_channel=AlainBajom%C3%A9e"   title="L'athéisme par Meslier par Alain Bajomée"&gt; athéisme radical&lt;/a&gt; et anticlérical. À sa mort, un manuscrit de plus de 200 pages, connu sous le nom de  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1971_num_69_2_5609_t1_0297_0000_1"  title="Oeuvre complète par le Persée"&gt; "Mémoire des Pensées et des Sentiments de Jean Meslier"&lt;/a&gt;, a été découvert et est considéré comme l'un des premiers manifestes de l'athéisme moderne en France car il remet en question la validité des dogmes religieux, dénonce l'injustice sociale, critique l'influence corruptrice de l'Église et prône une société égalitaire.  &lt;/p&gt;
   &lt;p&gt;   Quelques aspects de sa philosophie qui ont marqué l'histoire de la philosophie : &lt;/p&gt;&lt;dd&gt;&lt;a href="https://www.youtube.com/watch?v=0lQrBmCTD74"   title="La bonne parole du curé Meslier par Théatre poème"&gt; Athéisme radical&lt;/a&gt; - Il a argumenté de  manière virulente contre l'existence de Dieu et la validité des croyances religieuses. Il a utilisé des arguments rationalistes pour contester les dogmes religieux et a soutenu que la religion était une invention humaine visant à maintenir le pouvoir et la domination des élites religieuses et politiques. &lt;/dd&gt;
@@ -3643,106 +3709,40 @@
 </t>
         </is>
       </c>
-      <c r="F45" s="47" t="inlineStr">
+      <c r="F46" s="47" t="inlineStr">
         <is>
           <t>5s-nuRI6dKY</t>
         </is>
       </c>
-      <c r="G45" s="49" t="inlineStr">
+      <c r="G46" s="49" t="inlineStr">
         <is>
           <t>"Jean Meslier et l'atéisme " par Alain Bajomée</t>
         </is>
       </c>
-      <c r="H45" s="49" t="inlineStr">
+      <c r="H46" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/meslier-mini.webp</t>
-        </is>
-      </c>
-      <c r="I45" s="45" t="n"/>
-      <c r="J45" s="38" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K45" s="45" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="L45" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matérialisme ; Athéisme</t>
-        </is>
-      </c>
-      <c r="M45" s="35" t="inlineStr">
-        <is>
-          <t>philosophe et prêtre français connu pour son Athéisme radical.</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="147.75" customHeight="1" s="39">
-      <c r="A46" s="47" t="n">
-        <v>1668</v>
-      </c>
-      <c r="B46" s="47" t="inlineStr">
-        <is>
-          <t>1744</t>
-        </is>
-      </c>
-      <c r="C46" s="47" t="inlineStr">
-        <is>
-          <t>1668 – 1744</t>
-        </is>
-      </c>
-      <c r="D46" s="48" t="inlineStr">
-        <is>
-          <t>Giambattista VICO</t>
-        </is>
-      </c>
-      <c r="E46" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giambattista_Vico"  title=" Wikipedia"&gt;Giambattista VICO&lt;/a&gt; était un  philosophe, historien et pédagogue italien reconnu comme un pionnier de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_6790" style="color:#88A1E9" title=" La sagesse de l'histoire. Jean-Baptiste Vico et la philosophie pratique  par Persée"&gt; philosophie pratique&lt;/a&gt;, de l’histoire et des sciences humaines avec son ouvrage "La Science nouvelle" (paru en 1725), où il critique le rationalisme cartésien et propose une &lt;a href="https://www.youtube.com/watch?v=-OWc7ej_ixM" style="color:#88A1E9" title="Giambattista Vico: Consciousness and the Cycles of History par Spiritual Quest"&gt;approche alternative&lt;/a&gt;, centrée sur la complexité et l’historicité des sociétés humaines. Il y développe l’idée que la vérité n’est pas simplement découverte mais également construite. Selon lui, alors que Dieu connaît parfaitement la nature en tant que créateur, l’humain ne connaît parfaitement que ce qu’il crée lui-même, comme les mathématiques et les institutions humaines. &lt;/p&gt; &lt;p&gt; Il est aussi considéré comme le précurseur de la  &lt;a href="https://www.youtube.com/watch?v=vEYpuH4KdWM" style="color:#88A1E9" title=" Giambattista Vico, "The New Science" | A Philosophy of the History of Human Ideas and Institutions par Gavin Young Philosophy"&gt;philosophie de l’histoire&lt;/a&gt; et de l'épistémologie constructiviste, car il affirme que la connaissance humaine résulte essentiellement d’un processus collectif de création et d’invention. Sa critique du cartésianisme, son attention à la pluralité des formes de savoir (histoire, philologie, droit, rhétorique) et son intuition de la spécificité des sciences sociales l’inscrivent à contre-courant des philosophies réductionnistes de son époque. &lt;/p&gt; &lt;p&gt; Il élabore une théorie cyclique du développement des sociétés, fondée sur trois âges : l’âge des dieux, l’âge des héros et l’âge des hommes, chacun marquant une transformation des mœurs, du droit et de la politique. Il affirme que chaque peuple passe par ces étapes, de la mythologie religieuse à la raison civique, et que ce mouvement forme la trame de l’histoire humaine.  &lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F46" s="47" t="inlineStr">
-        <is>
-          <t>IohgI_XC3gI</t>
-        </is>
-      </c>
-      <c r="G46" s="49" t="inlineStr">
-        <is>
-          <t>"Vico : Une science de l'homme est-elle possible?" par Philo-Man</t>
-        </is>
-      </c>
-      <c r="H46" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/vico-mini.webp</t>
         </is>
       </c>
       <c r="I46" s="45" t="n"/>
       <c r="J46" s="38" t="inlineStr">
         <is>
-          <t>Italienne</t>
+          <t>Française</t>
         </is>
       </c>
       <c r="K46" s="45" t="inlineStr">
         <is>
-          <t>epistemologie ; politique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="L46" s="46" t="inlineStr">
         <is>
-          <t>Herméneutique</t>
+          <t xml:space="preserve">Matérialisme ; Athéisme</t>
         </is>
       </c>
       <c r="M46" s="35" t="inlineStr">
         <is>
-          <t>philosophe italien qui élabora une métaphysique et une philosophie de l'histoire.</t>
+          <t>philosophe et prêtre français connu pour son Athéisme radical.</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3751,64 +3751,64 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="126.75" customHeight="1" s="39">
+    <row r="47" ht="147.75" customHeight="1" s="39">
       <c r="A47" s="47" t="n">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="B47" s="47" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="C47" s="47" t="inlineStr">
         <is>
-          <t>1670 – 1733</t>
+          <t>1668 – 1744</t>
         </is>
       </c>
       <c r="D47" s="48" t="inlineStr">
         <is>
-          <t>Bernard MANDEVILLE</t>
+          <t>Giambattista VICO</t>
         </is>
       </c>
       <c r="E47" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Mandeville_(philosophe)"   title=" Wikipedia"&gt;Bernard MANDEVILLE&lt;/a&gt; était un médecin et philosophe moral d’origine hollandaise, installé à Londres, devenu célèbre par son ouvrage satirique  &lt;a href="https://www.youtube.com/watch?v=hDQB2N3FzJA"  title=" La Fable des Abeilles – Et si le vice faisait tourner le monde ? | Mandeville par Capsio"&gt;"La Fable des abeilles" &lt;/a&gt; paru en 1714. Il y propose une vision provocatrice de la société commerciale moderne, qui fera de lui un précurseur à la fois du libéralisme économique et d’un certain utilitarisme. &lt;/p&gt; &lt;p&gt; Dans cet ouvrage, une ruche prospère vit grâce aux   &lt;a href="https://www.youtube.com/watch?v=Gdc0G67brI0"  title=" L' ÉLOGE DU VICE en 6 minutes ! (Bernard MANDEVILLE - Vices privés, vertu publique) par Culture Philo"&gt;passions égoïstes  &lt;/a&gt; de ses habitants (vanité, luxe, cupidité.). Lorsque ces abeilles deviennent soudain vertueuses et frugales, la prospérité disparaît : le commerce se contracte, les métiers liés au luxe s’effondrent, et la ruche finit pauvre mais “vertueuse”. &lt;/p&gt; &lt;p&gt; Il  a une conception très sombre de la nature humaine : pour lui, nos passions naturelles sont toutes intéressées, donc égoïstes. Une action n’est vraiment vertueuse que si elle implique un véritable renoncement à soi, ce qui la rend extrêmement rare ; pratiquement toutes les actions ordinaires restent traversées par l’amour de soi. Il en conclut que la &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1983_num_67_1_2319" title="Bernard Mandeville, moraliste et métaphysicien par Persée"&gt;morale “civile” &lt;/a&gt; est en grande partie une invention politique : les gouvernants transforment les passions (amour de la gloire, désir de reconnaissance, peur de la honte) en vertus utiles à l’ordre social. &lt;/p&gt; &lt;p&gt; Ses analyses de la consommation de luxe montrent que les dépenses ostentatoires des riches font vivre de nombreux artisans et ouvriers : ce qui apparaît comme “vice” du point de vue moral classique devient moteur d’activité du point de vue économique. Cette lecture en fait un des inspirateurs lointains d’Adam Smith, de Hayek et, via l’idée de demande effective, de Keynes.&lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giambattista_Vico"  title=" Wikipedia"&gt;Giambattista VICO&lt;/a&gt; était un  philosophe, historien et pédagogue italien reconnu comme un pionnier de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_6790" style="color:#88A1E9" title=" La sagesse de l'histoire. Jean-Baptiste Vico et la philosophie pratique  par Persée"&gt; philosophie pratique&lt;/a&gt;, de l’histoire et des sciences humaines avec son ouvrage "La Science nouvelle" (paru en 1725), où il critique le rationalisme cartésien et propose une &lt;a href="https://www.youtube.com/watch?v=-OWc7ej_ixM" style="color:#88A1E9" title="Giambattista Vico: Consciousness and the Cycles of History par Spiritual Quest"&gt;approche alternative&lt;/a&gt;, centrée sur la complexité et l’historicité des sociétés humaines. Il y développe l’idée que la vérité n’est pas simplement découverte mais également construite. Selon lui, alors que Dieu connaît parfaitement la nature en tant que créateur, l’humain ne connaît parfaitement que ce qu’il crée lui-même, comme les mathématiques et les institutions humaines. &lt;/p&gt; &lt;p&gt; Il est aussi considéré comme le précurseur de la  &lt;a href="https://www.youtube.com/watch?v=vEYpuH4KdWM" style="color:#88A1E9" title=" Giambattista Vico, "The New Science" | A Philosophy of the History of Human Ideas and Institutions par Gavin Young Philosophy"&gt;philosophie de l’histoire&lt;/a&gt; et de l'épistémologie constructiviste, car il affirme que la connaissance humaine résulte essentiellement d’un processus collectif de création et d’invention. Sa critique du cartésianisme, son attention à la pluralité des formes de savoir (histoire, philologie, droit, rhétorique) et son intuition de la spécificité des sciences sociales l’inscrivent à contre-courant des philosophies réductionnistes de son époque. &lt;/p&gt; &lt;p&gt; Il élabore une théorie cyclique du développement des sociétés, fondée sur trois âges : l’âge des dieux, l’âge des héros et l’âge des hommes, chacun marquant une transformation des mœurs, du droit et de la politique. Il affirme que chaque peuple passe par ces étapes, de la mythologie religieuse à la raison civique, et que ce mouvement forme la trame de l’histoire humaine.  &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F47" s="47" t="inlineStr">
         <is>
-          <t>PWsYvPlzhC8</t>
+          <t>IohgI_XC3gI</t>
         </is>
       </c>
       <c r="G47" s="49" t="inlineStr">
         <is>
-          <t>"BERNARD MANDEVILLE UN SACRÉ APICULTEUR : LA FABLE DES ABEILLES" par ECRITAU MAG</t>
+          <t>"Vico : Une science de l'homme est-elle possible?" par Philo-Man</t>
         </is>
       </c>
       <c r="H47" s="49" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/mandeville-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/vico-mini.webp</t>
         </is>
       </c>
       <c r="I47" s="45" t="n"/>
       <c r="J47" s="38" t="inlineStr">
         <is>
-          <t>Néerlandaise</t>
+          <t>Italienne</t>
         </is>
       </c>
       <c r="K47" s="45" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>epistemologie ; politique</t>
         </is>
       </c>
       <c r="L47" s="46" t="inlineStr">
         <is>
-          <t>Libéralisme</t>
+          <t>Herméneutique</t>
         </is>
       </c>
       <c r="M47" s="35" t="inlineStr">
         <is>
-          <t>philosophe hollandais célèbre par son ouvrage satirique "La Fable des Abeilles".</t>
+          <t>philosophe italien qui élabora une métaphysique et une philosophie de l'histoire.</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3817,294 +3817,360 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="147.75" customHeight="1" s="39">
+    <row r="48" ht="126.75" customHeight="1" s="39">
       <c r="A48" s="47" t="n">
-        <v>1679</v>
+        <v>1670</v>
       </c>
       <c r="B48" s="47" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="C48" s="47" t="inlineStr">
         <is>
-          <t>1679 – 1754</t>
+          <t>1670 – 1733</t>
         </is>
       </c>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>Christian WOLFF</t>
+          <t>Bernard MANDEVILLE</t>
         </is>
       </c>
       <c r="E48" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Wolff_(philosophe)"   title=" Wikipedia"&gt;Christian WOLFF&lt;/a&gt;  était un philosophe, mathématicien et juriste allemand majeur de l'Aufklärung, &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1964_num_62_74_7932_t1_0360_0000_2" title="Christian Wolff, Philosophia prima sive Ontologia edidit et curavit Joannes Ecole par Persée"&gt;l'Éclairage allemand &lt;/a&gt; précoce. Disciple de Leibniz, il systématisa la philosophie rationnelle en allemand, influençant Kant et Baumgarten. Il étudia la théologie à l'université de Iéna en 1699, puis se tourna vers les mathématiques sous l'influence d'Erhard Weigel. &lt;/p&gt; &lt;p&gt; Il popularisa le rationalisme leibnizien via une œuvre encyclopédique : "Philosophia rationalis sive logica" paru en 1712, "Philosophia prima" en 1729 et "Philosophie pratique" en  1738. Il  &lt;a href="https://www.youtube.com/watch?v=vfmME7Qcgh4"  title="Christian Wolff (philosopher) par WikiReader"&gt;structura la philosophie &lt;/a&gt; en domaines (ontologie, cosmologie, psychologie rationnelle, théologie naturelle) et contribua à l'économie politique, au droit international et à la subsidiarité. &lt;/p&gt; &lt;p&gt; Son "wolffianisme" forma la philosophie allemande du XVIIIe siècle, faisant du langage allemand un outil philosophique majeur et favorisant les Lumières prussiennes. Kant le critiqua pour son dogmatisme excessif, mais reconnut sa rigueur systématique. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Mandeville_(philosophe)"   title=" Wikipedia"&gt;Bernard MANDEVILLE&lt;/a&gt; était un médecin et philosophe moral d’origine hollandaise, installé à Londres, devenu célèbre par son ouvrage satirique  &lt;a href="https://www.youtube.com/watch?v=hDQB2N3FzJA"  title=" La Fable des Abeilles – Et si le vice faisait tourner le monde ? | Mandeville par Capsio"&gt;"La Fable des abeilles" &lt;/a&gt; paru en 1714. Il y propose une vision provocatrice de la société commerciale moderne, qui fera de lui un précurseur à la fois du libéralisme économique et d’un certain utilitarisme. &lt;/p&gt; &lt;p&gt; Dans cet ouvrage, une ruche prospère vit grâce aux   &lt;a href="https://www.youtube.com/watch?v=Gdc0G67brI0"  title=" L' ÉLOGE DU VICE en 6 minutes ! (Bernard MANDEVILLE - Vices privés, vertu publique) par Culture Philo"&gt;passions égoïstes  &lt;/a&gt; de ses habitants (vanité, luxe, cupidité.). Lorsque ces abeilles deviennent soudain vertueuses et frugales, la prospérité disparaît : le commerce se contracte, les métiers liés au luxe s’effondrent, et la ruche finit pauvre mais “vertueuse”. &lt;/p&gt; &lt;p&gt; Il  a une conception très sombre de la nature humaine : pour lui, nos passions naturelles sont toutes intéressées, donc égoïstes. Une action n’est vraiment vertueuse que si elle implique un véritable renoncement à soi, ce qui la rend extrêmement rare ; pratiquement toutes les actions ordinaires restent traversées par l’amour de soi. Il en conclut que la &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1983_num_67_1_2319" title="Bernard Mandeville, moraliste et métaphysicien par Persée"&gt;morale “civile” &lt;/a&gt; est en grande partie une invention politique : les gouvernants transforment les passions (amour de la gloire, désir de reconnaissance, peur de la honte) en vertus utiles à l’ordre social. &lt;/p&gt; &lt;p&gt; Ses analyses de la consommation de luxe montrent que les dépenses ostentatoires des riches font vivre de nombreux artisans et ouvriers : ce qui apparaît comme “vice” du point de vue moral classique devient moteur d’activité du point de vue économique. Cette lecture en fait un des inspirateurs lointains d’Adam Smith, de Hayek et, via l’idée de demande effective, de Keynes.&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F48" s="47" t="inlineStr">
         <is>
-          <t>KWCHoM3ujTA</t>
+          <t>PWsYvPlzhC8</t>
         </is>
       </c>
       <c r="G48" s="49" t="inlineStr">
         <is>
-          <t>"CHRISTIAN WOLFF - The Genius Behind the Rationalism" par Few Minutes Knowledge</t>
+          <t>"BERNARD MANDEVILLE UN SACRÉ APICULTEUR : LA FABLE DES ABEILLES" par ECRITAU MAG</t>
         </is>
       </c>
       <c r="H48" s="49" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/wolff-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/mandeville-mini.webp</t>
         </is>
       </c>
       <c r="I48" s="45" t="n"/>
       <c r="J48" s="38" t="inlineStr">
         <is>
+          <t>Néerlandaise</t>
+        </is>
+      </c>
+      <c r="K48" s="45" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L48" s="46" t="inlineStr">
+        <is>
+          <t>Libéralisme</t>
+        </is>
+      </c>
+      <c r="M48" s="35" t="inlineStr">
+        <is>
+          <t>philosophe hollandais célèbre par son ouvrage satirique "La Fable des Abeilles".</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="147.75" customHeight="1" s="39">
+      <c r="A49" s="47" t="n">
+        <v>1679</v>
+      </c>
+      <c r="B49" s="47" t="inlineStr">
+        <is>
+          <t>1754</t>
+        </is>
+      </c>
+      <c r="C49" s="47" t="inlineStr">
+        <is>
+          <t>1679 – 1754</t>
+        </is>
+      </c>
+      <c r="D49" s="48" t="inlineStr">
+        <is>
+          <t>Christian WOLFF</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Wolff_(philosophe)"   title=" Wikipedia"&gt;Christian WOLFF&lt;/a&gt; (1679-1754) est un philosophe, mathématicien et juriste allemand, le grand représentant des débuts des Lumières en Allemagne, l’&lt;em&gt;Aufklärung&lt;/em&gt;. Né à Breslau, il étudie la théologie et les mathématiques à Iéna, puis enseigne à l’université de Halle à partir de 1706, sur la recommandation de Leibniz, avec qui il correspond.&lt;/p&gt; &lt;p&gt;Wolff veut construire un système complet de la philosophie, démontré avec la rigueur des mathématiques à partir du principe de contradiction et du principe de raison suffisante. Il reprend de nombreuses idées de Leibniz, d’où le nom de « philosophie leibnizo-wolffienne », mais les organise en un ensemble ordonné, qui &lt;a href="https://www.youtube.com/watch?v=vfmME7Qcgh4"  title="Christian Wolff (philosopher) par WikiReader"&gt;structure la philosophie&lt;/a&gt; en disciplines : la logique, l’ontologie, ou science de l’être en général, la cosmologie, la psychologie rationnelle, la théologie naturelle, puis l’éthique, le droit et la politique. Il écrit d’abord en allemand, ce qui contribue à faire de cette langue une langue philosophique, avec de nombreux termes qu’il crée, puis en latin, dans de grands traités comme son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1964_num_62_74_7932_t1_0360_0000_2" title="Christian Wolff, Philosophia prima sive Ontologia edidit et curavit Joannes Ecole par Persée"&gt;&lt;em&gt;Ontologie&lt;/em&gt;&lt;/a&gt; (1730). En 1721, un discours où il loue la morale des Chinois, fondée sur la raison sans recours à la révélation, provoque la colère des théologiens piétistes, qui l’accusent de fatalisme. En 1723, le roi Frédéric-Guillaume Ier le chasse de Prusse en quarante-huit heures, sous peine de pendaison. Il trouve refuge à Marbourg, où sa renommée devient européenne.&lt;/p&gt; &lt;p&gt;Rappelé à Halle en 1740 par Frédéric II, il domine l’enseignement universitaire allemand. Kant, formé dans sa tradition, critiquera son « dogmatisme », tout en saluant sa rigueur.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F49" s="47" t="inlineStr">
+        <is>
+          <t>KWCHoM3ujTA</t>
+        </is>
+      </c>
+      <c r="G49" s="49" t="inlineStr">
+        <is>
+          <t>"CHRISTIAN WOLFF - The Genius Behind the Rationalism" par Few Minutes Knowledge</t>
+        </is>
+      </c>
+      <c r="H49" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/wolff-mini.webp</t>
+        </is>
+      </c>
+      <c r="I49" s="45" t="n"/>
+      <c r="J49" s="38" t="inlineStr">
+        <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K48" s="45" t="inlineStr">
+      <c r="K49" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L48" s="46" t="inlineStr">
+      <c r="L49" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme ; Ontologie</t>
         </is>
       </c>
-      <c r="M48" s="35" t="inlineStr">
+      <c r="M49" s="35" t="inlineStr">
         <is>
           <t>philosophe allemand qui systématisa la philosophie rationnelle en allemand.</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="164.9" customHeight="1" s="39">
-      <c r="A49" s="47" t="n">
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="164.9" customHeight="1" s="39">
+      <c r="A50" s="47" t="n">
         <v>1685</v>
       </c>
-      <c r="B49" s="47" t="inlineStr">
+      <c r="B50" s="47" t="inlineStr">
         <is>
           <t>1753</t>
         </is>
       </c>
-      <c r="C49" s="47" t="inlineStr">
+      <c r="C50" s="47" t="inlineStr">
         <is>
           <t>1685 – 1753</t>
         </is>
       </c>
-      <c r="D49" s="48" t="inlineStr">
+      <c r="D50" s="48" t="inlineStr">
         <is>
           <t>Georges BERKELEY</t>
         </is>
       </c>
-      <c r="E49" s="49" t="inlineStr">
+      <c r="E50" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley"    title=" Wikipedia"&gt;Georges BERKELEY&lt;/a&gt; (1685-1753) est un philosophe irlandais et évêque anglican, célèbre pour sa formule &lt;a href="https://www.youtube.com/watch?v=gcyFtJ1ZtrA"  title=" Berkeley Être c'est être perçu ou percevoir par Coursitout"&gt;&lt;em&gt;esse est percipi&lt;/em&gt;&lt;/a&gt;, « être, c’est être perçu ». Né près de Kilkenny, il étudie et enseigne au Trinity College de Dublin. Il séjourne en Amérique pour fonder un collège aux Bermudes, projet qui échoue, puis devient en 1734 évêque de Cloyne, en Irlande.&lt;/p&gt; &lt;p&gt;Dans l’&lt;em&gt;Essai pour une nouvelle théorie de la vision&lt;/em&gt; (1709), il montre que nous ne voyons pas directement la distance : nous l’apprenons en associant la vue au toucher. Dans le &lt;a href="https://www.youtube.com/watch?v=wBivRdgKgd0"  title=" Berkeley pour les nuls  par Alexis Vildier"&gt;&lt;em&gt;Traité des principes de la connaissance humaine&lt;/em&gt;&lt;/a&gt; (1710), puis dans les &lt;em&gt;Trois Dialogues entre Hylas et Philonous&lt;/em&gt; (1713), il défend une position &lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Immatérialisme  par Wikipedia"&gt;immatérialiste&lt;/a&gt;. Locke distinguait les qualités secondes des choses, couleurs, sons ou saveurs, qui n’existent que dans notre esprit, et leurs qualités premières, étendue, figure, mouvement, qui existeraient dans une matière extérieure. Berkeley montre que ces dernières sont aussi des idées : on ne peut concevoir une étendue sans couleur. Une chose n’est donc qu’un ensemble d’idées, et l’idée d’une « substance matérielle » cachée derrière nos perceptions est vide. Seuls existent les esprits et leurs idées. Si l’arbre du jardin continue d’exister quand personne ne le regarde, c’est que Dieu le perçoit toujours. Berkeley pense ainsi combattre le scepticisme et l’athéisme, que favorisait selon lui la croyance en une matière indépendante.&lt;/p&gt; &lt;p&gt;Sa doctrine, jugée paradoxale par ses contemporains, a marqué Hume et Kant. Une ville de Californie, siège d’une célèbre université, porte son nom.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F49" s="47" t="inlineStr">
+      <c r="F50" s="47" t="inlineStr">
         <is>
           <t>x42AwlrUOII</t>
         </is>
       </c>
-      <c r="G49" s="49" t="inlineStr">
+      <c r="G50" s="49" t="inlineStr">
         <is>
           <t>"George Berkeley: Challenging Materialism" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H49" s="49" t="inlineStr">
+      <c r="H50" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/berkeley-mini.webp</t>
         </is>
       </c>
-      <c r="I49" s="45" t="n"/>
-      <c r="J49" s="55" t="inlineStr">
+      <c r="I50" s="45" t="n"/>
+      <c r="J50" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K49" s="45" t="inlineStr">
+      <c r="K50" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L49" s="46" t="inlineStr">
+      <c r="L50" s="46" t="inlineStr">
         <is>
           <t>Immatérialisme ; Phénoménisme</t>
         </is>
       </c>
-      <c r="M49" s="35" t="inlineStr">
+      <c r="M50" s="35" t="inlineStr">
         <is>
           <t>philosophe et évêque irlandais célèbre pour sa philosophie empiriste et idéaliste.</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P49">
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P50">
         <v>2</v>
       </c>
     </row>
-    <row r="50" ht="150" customHeight="1" s="39">
-      <c r="A50" s="47" t="n">
+    <row r="51" ht="150" customHeight="1" s="39">
+      <c r="A51" s="47" t="n">
         <v>1688</v>
       </c>
-      <c r="B50" s="47" t="inlineStr">
+      <c r="B51" s="47" t="inlineStr">
         <is>
           <t>1772</t>
         </is>
       </c>
-      <c r="C50" s="47" t="inlineStr">
+      <c r="C51" s="47" t="inlineStr">
         <is>
           <t>1688 – 1772</t>
         </is>
       </c>
-      <c r="D50" s="48" t="inlineStr">
+      <c r="D51" s="48" t="inlineStr">
         <is>
           <t>Emanuel SWEDENBORG</t>
         </is>
       </c>
-      <c r="E50" s="49" t="inlineStr">
+      <c r="E51" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emanuel_Swedenborg"  title=" Wikipedia"&gt;Emanuel SWEDENBORG&lt;/a&gt;   était  un scientifique, philosophe et théologien suédois connu pour son passage du rationalisme scientifique au mysticisme chrétien. Issu d'une famille luthérienne, il excella en sciences avant de vivre des visions spirituelles dès 1744, affirmant recevoir des &lt;a href="https://www.youtube.com/watch?v=w4oPoKLes1w" title="Emanuel Swedenborg – Le Savant devenu Visionnaire | Biographie Mystique par SoulNym"&gt;révélations divines &lt;/a&gt; sur l'interprétation des Écritures. Fils d'un théologien et recteur d'université, il étudia la philosophie, les mathématiques et l'ingénierie à Uppsala, puis voyagea en Europe pour approfondir ses connaissances auprès de figures comme Christian Wolff. &lt;/p&gt; &lt;p&gt; Nommé assesseur au Collège du Mines en 1716, il inventa des machines et publia sur la métallurgie, tout en siégeant au parlement suédois. Vers 1745, une crise spirituelle le poussa à abandonner ses fonctions scientifiques pour se &lt;a href="https://www.persee.fr/doc/caief_0571-5865_1963_num_15_1_2263"  title="Balzac et Swedenborg par Persée"&gt;consacrer à la théologie,&lt;/a&gt;  voyageant entre Stockholm, Londres et Amsterdam jusqu'à sa mort le 29 mars 1772 à Londres. &lt;/p&gt; &lt;p&gt; Ses premiers travaux, comme "Opera Philosophica et Mineralia" en 1734, explorent la philosophie de la nature, la géométrie et la métallurgie, cherchant à unir matière et esprit via une méthode inductive proche des sciences modernes. "Oeconomia Regni Animalis" paru en 1740 analyse l'anatomie et la physiologie, anticipant des découvertes sur les glandes endocrines et les fonctions cérébrales. &lt;/p&gt; &lt;p&gt; À partir de Arcana Cœlestia (1749-1756), il développe une exégèse symbolique de la Bible, introduisant la théorie des "correspondances" entre monde physique et spirituel, et une vision unitaire de Dieu (Trinité comme amour, sagesse et action). Ses écrits, comme La Vraie Religion Chrétienne (1771), fondèrent l'Église de la Nouvelle Jérusalem, influençant Blake, Kant et le romantisme. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F50" s="47" t="inlineStr">
+      <c r="F51" s="47" t="inlineStr">
         <is>
           <t>aO2eXURYpSQ</t>
         </is>
       </c>
-      <c r="G50" s="49" t="inlineStr">
+      <c r="G51" s="49" t="inlineStr">
         <is>
           <t>"Emanuel Swedenborg: The Mystic Scientist" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H50" s="49" t="inlineStr">
+      <c r="H51" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/swedenborg-mini.webp</t>
         </is>
       </c>
-      <c r="I50" s="45" t="n"/>
-      <c r="J50" s="38" t="inlineStr">
+      <c r="I51" s="45" t="n"/>
+      <c r="J51" s="38" t="inlineStr">
         <is>
           <t>Suédoise</t>
         </is>
       </c>
-      <c r="K50" s="45" t="inlineStr">
+      <c r="K51" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="L50" s="46" t="inlineStr">
+      <c r="L51" s="46" t="inlineStr">
         <is>
           <t>Mysticisme ; Spiritualisme</t>
         </is>
       </c>
-      <c r="M50" s="35" t="inlineStr">
+      <c r="M51" s="35" t="inlineStr">
         <is>
           <t>philosophe suédois qui est passé du rationalisme scientifique au mysticisme chrétien.</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="168" customHeight="1" s="39">
-      <c r="A51" s="47" t="n">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="168" customHeight="1" s="39">
+      <c r="A52" s="47" t="n">
         <v>1689</v>
       </c>
-      <c r="B51" s="47" t="inlineStr">
+      <c r="B52" s="47" t="inlineStr">
         <is>
           <t>1755</t>
         </is>
       </c>
-      <c r="C51" s="47" t="inlineStr">
+      <c r="C52" s="47" t="inlineStr">
         <is>
           <t>1689 – 1755</t>
         </is>
       </c>
-      <c r="D51" s="48" t="inlineStr">
+      <c r="D52" s="48" t="inlineStr">
         <is>
           <t>MONTESQUIEU</t>
         </is>
       </c>
-      <c r="E51" s="49" t="inlineStr">
+      <c r="E52" s="49" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Montesquieu"    title=" Wikipedia"&gt;MONTESTQUIEU&lt;/a&gt; était un grand philosophe et écrivain français  associé au mouvement des Lumières et connu pour sa théorie de la séparation des pouvoirs. Il s’appelle en réalité Charles‑Louis de Secondat, baron de La Brède et de Montesquieu, et naît  près de Bordeaux dans une famille de noblesse de robe. &lt;/p&gt; &lt;p&gt; Deux œuvres dominent sa postérité : &lt;a href="https://www.youtube.com/watch?v=e72jQdl52bM" title=" Les Lettres persanes, Montesquieu  par Les Bons Profs"&gt;"les Lettres persanes"&lt;/a&gt;, un roman épistolaire satirique où des voyageurs persans observent la société française et critiquent l’absolutisme, les mœurs et l’intolérance religieuse, en utilisant le regard extérieur comme miroir critique et &lt;a href="https://www.youtube.com/watch?v=IBc46RLZxe4" title=" L'ESPRIT DES LOIS en 8 minutes ! par Culture Philo"&gt;"De l’esprit des lois"&lt;/a&gt;, un vaste traité de science politique et sociale qui analyse les types de gouvernement, le rôle des lois, l’influence du climat et des mœurs, et propose une nouvelle manière “scientifique” d’étudier les sociétés.​ &lt;/p&gt; &lt;p&gt; Il est l’un des &lt;a href="https://expositions.bnf.fr/montesquieu/un-ecrivain-philosophe.htm" title=" un écrivain philosophe par BNF"&gt;grands théoriciens&lt;/a&gt; du libéralisme classique et de la limitation du pouvoir politique. Il distingue notamment trois grands types de gouvernement : républicain, monarchique et despotique, en fonction du principe qui les fait tenir. Il parle de séparation des pouvoirs : le pouvoir législatif, l’exécutif et le judiciaire doivent être confiés à des organes distincts afin d’empêcher la concentration du pouvoir et de garantir la liberté. &lt;/p&gt; &lt;p&gt; Il critique la monarchie absolue et met en garde contre le despotisme, qu’il considère comme le régime où la peur domine et où les lois se confondent avec le bon plaisir du souverain.​ Il défend la &lt;a href="https://www.youtube.com/watch?v=2Ye6LrpTq9g" title=" le père de la démocratie  par Portrait Historiques"&gt;liberté politique &lt;/a&gt; comme sécurité du citoyen, la tolérance religieuse et une certaine forme d’universalisme, positions qui en font un précurseur et un modèle pour d’autres philosophes des Lumières. &lt;/p&gt; 
  &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="L'esprit de Montesquieu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24812-04.07.2011-ITEMA_23734145-2011C12410E0183-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F51" s="47" t="inlineStr">
+      <c r="F52" s="47" t="inlineStr">
         <is>
           <t>mK7zNAqI_GQ</t>
         </is>
       </c>
-      <c r="G51" s="49" t="inlineStr">
+      <c r="G52" s="49" t="inlineStr">
         <is>
           <t>"Montesquieu - Grand Ecrivain " par Culture Tube</t>
         </is>
       </c>
-      <c r="H51" s="49" t="inlineStr">
+      <c r="H52" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/montesquieu-mini.webp</t>
         </is>
       </c>
-      <c r="I51" s="45" t="n"/>
-      <c r="J51" s="38" t="inlineStr">
+      <c r="I52" s="45" t="n"/>
+      <c r="J52" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K51" s="45" t="inlineStr">
+      <c r="K52" s="45" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="L51" s="46" t="inlineStr">
+      <c r="L52" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Libéralisme ; Lumières</t>
         </is>
       </c>
-      <c r="M51" s="35" t="inlineStr">
+      <c r="M52" s="35" t="inlineStr">
         <is>
           <t>philosophe penseur de l'organisation politique et sociale des sociétés modernes.</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="177" customHeight="1" s="39">
-      <c r="A52" s="47" t="n">
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="177" customHeight="1" s="39">
+      <c r="A53" s="47" t="n">
         <v>1694</v>
       </c>
-      <c r="B52" s="47" t="inlineStr">
+      <c r="B53" s="47" t="inlineStr">
         <is>
           <t>1778</t>
         </is>
       </c>
-      <c r="C52" s="47" t="inlineStr">
+      <c r="C53" s="47" t="inlineStr">
         <is>
           <t>1694 - 1778</t>
         </is>
       </c>
-      <c r="D52" s="48" t="inlineStr">
+      <c r="D53" s="48" t="inlineStr">
         <is>
           <t>VOLTAIRE</t>
         </is>
       </c>
-      <c r="E52" s="58" t="inlineStr">
+      <c r="E53" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Voltaire"   title=" Wikipedia"&gt; VOLTAIRE&lt;/a&gt;, de son vrai nom François-Marie Arouet, est un philosophe de l'époque des  &lt;a href="https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;t=380s&amp;ab_channel=LePr%C3%A9cepteur"  title=" La philosophie des lumières par le Précepteur "&gt;Lumières&lt;/a&gt; (ou Illuministe) en France. Il était aussi écrivain, poète, dramaturge et philosophe. &lt;/p&gt; &lt;p&gt;
 Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href="https://www.youtube.com/watch?v=XE1Z8jpVJUA" title=" la vie de Voltaire  par Portrait Historiques"&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation. Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;
@@ -4113,476 +4179,476 @@
 La contribution de Voltaire à la philosophie se caractérise par son engagement envers la raison, la liberté et la justice. Il a influencé de nombreux penseurs ultérieurs et a contribué à jeter les bases de la pensée libérale et humaniste qui a marqué les siècles suivants. Sa défense de la liberté d'expression reste une valeur fondamentale de nos sociétés démocratiques aujourd'hui. &lt;/p&gt; &lt;audio controls title="Voltaire et les Lumières par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-13.01.2021-ITEMA_22540842-2021C24632S0013.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F52" s="47" t="inlineStr">
+      <c r="F53" s="47" t="inlineStr">
         <is>
           <t>oUWrf3GUj0U</t>
         </is>
       </c>
-      <c r="G52" s="49" t="inlineStr">
+      <c r="G53" s="49" t="inlineStr">
         <is>
           <t>"Philosopher-Voltaire" par Guillaume Deloison</t>
         </is>
       </c>
-      <c r="H52" s="49" t="inlineStr">
+      <c r="H53" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/voltaire-mini.webp</t>
         </is>
       </c>
-      <c r="I52" s="45" t="n"/>
-      <c r="J52" s="38" t="inlineStr">
+      <c r="I53" s="45" t="n"/>
+      <c r="J53" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K52" s="45" t="inlineStr">
+      <c r="K53" s="45" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="L52" s="46" t="inlineStr">
+      <c r="L53" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Déisme ; Libéralisme ; Lumières</t>
         </is>
       </c>
-      <c r="M52" s="35" t="inlineStr">
+      <c r="M53" s="35" t="inlineStr">
         <is>
           <t>philosophe et écrivain français Déiste de l'époque des lumières.</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P52">
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P53">
         <v>3</v>
       </c>
     </row>
-    <row r="53" ht="147.75" customHeight="1" s="39">
-      <c r="A53" s="47" t="n">
+    <row r="54" ht="147.75" customHeight="1" s="39">
+      <c r="A54" s="47" t="n">
         <v>1694</v>
       </c>
-      <c r="B53" s="47" t="inlineStr">
+      <c r="B54" s="47" t="inlineStr">
         <is>
           <t>1746</t>
         </is>
       </c>
-      <c r="C53" s="47" t="inlineStr">
+      <c r="C54" s="47" t="inlineStr">
         <is>
           <t>1694 – 1746</t>
         </is>
       </c>
-      <c r="D53" s="48" t="inlineStr">
+      <c r="D54" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Francis HUTCHESON</t>
         </is>
       </c>
-      <c r="E53" s="62" t="inlineStr">
+      <c r="E54" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francis_Hutcheson_(philosophe)"   title=" Wikipedia"&gt;Francis HUTCHESON&lt;/a&gt;  était un philosophe irlando-écossais  majeur des Lumières écossaises, surtout connu pour sa théorie du sens moral et pour son influence sur Hume, Smith et Reid. Il a enseigné la philosophie morale à l’université de Glasgow et a contribué aussi à l’esthétique, à la psychologie morale et à la pensée politique. Sa thèse la plus célèbre est que &lt;a href="https://www.persee.fr/doc/dhs_0070-6760_1994_num_26_1_2013_t1_0566_0000_3"   title=" Two Texts on Human Nature par Persée "&gt;l’être humain &lt;/a&gt; possède une faculté morale innée, un « moral sense », qui nous fait approuver spontanément les actions vertueuses et désapprouver les actions vicieuses, sans passer d’abord par un long raisonnement. &lt;/p&gt; &lt;p&gt; Il s’oppose aux théories qui réduisent la morale à l’égoïsme, comme celles de Hobbes ou de Mandeville, et il insiste au contraire sur le rôle de la bienveillance dans l’action morale. Il est aussi souvent vu comme un précurseur de &lt;a href="https://fr.wikipedia.org/wiki/Utilitarisme"   title=" Utilitarisme par Wikipedia "&gt;l’utilitarisme, &lt;/a&gt; parce qu’il relie le bien moral au bien-être général et à l’idée du « plus grand bonheur du plus grand nombre ». &lt;/p&gt; &lt;p&gt; Parmi ses textes les plus connus, on trouve An Inquiry into the Original of Our Ideas of Beauty and Virtue (1725) et An Essay on the Nature and Conduct of the Passions and Affections (1728). Ces ouvrages ont joué un rôle important dans la naissance de la philosophie morale moderne en langue anglaise. &lt;/p&gt; &lt;p&gt; Il  a fortement influencé la philosophie morale écossaise et des penseurs comme Adam Smith et David Hume. On lui doit aussi d’avoir contribué à faire de l’esthétique un domaine philosophique à part entière, en montrant que le beau peut aussi être perçu par une forme de sens intérieur. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F53" s="47" t="inlineStr">
+      <c r="F54" s="47" t="inlineStr">
         <is>
           <t>ARi0h-Izi5U</t>
         </is>
       </c>
-      <c r="G53" s="49" t="inlineStr">
+      <c r="G54" s="49" t="inlineStr">
         <is>
           <t>"When Self Meets Society |How Hutcheson’s Philosophy Inspires True Motivation?" par Success Saga Stories</t>
         </is>
       </c>
-      <c r="H53" s="49" t="inlineStr">
+      <c r="H54" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fhutcheson-mini.webp</t>
         </is>
       </c>
-      <c r="I53" s="45" t="n"/>
-      <c r="J53" s="38" t="inlineStr">
+      <c r="I54" s="45" t="n"/>
+      <c r="J54" s="38" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K53" s="45" t="inlineStr">
+      <c r="K54" s="45" t="inlineStr">
         <is>
           <t>ethique</t>
         </is>
       </c>
-      <c r="L53" s="46" t="inlineStr">
+      <c r="L54" s="46" t="inlineStr">
         <is>
           <t>Empirisme</t>
         </is>
       </c>
-      <c r="M53" s="35" t="inlineStr">
+      <c r="M54" s="35" t="inlineStr">
         <is>
           <t>philosophe irlando-écossais  majeur des Lumières écossaises.</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="133.5" customHeight="1" s="39">
-      <c r="A54" s="47" t="n">
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="133.5" customHeight="1" s="39">
+      <c r="A55" s="47" t="n">
         <v>1703</v>
       </c>
-      <c r="B54" s="47" t="inlineStr">
+      <c r="B55" s="47" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="C54" s="47" t="inlineStr">
+      <c r="C55" s="47" t="inlineStr">
         <is>
           <t>1703 – 1791</t>
         </is>
       </c>
-      <c r="D54" s="48" t="inlineStr">
+      <c r="D55" s="48" t="inlineStr">
         <is>
           <t>John WESLEY</t>
         </is>
       </c>
-      <c r="E54" s="49" t="inlineStr">
+      <c r="E55" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Wesley"  title=" Wikipedia"&gt;John WESLEY&lt;/a&gt; était un philosophe, religieux, théologien et évangélisateur anglais qui fut le déclencheur d'un mouvement de réveil au sein de l'Église d'Angleterre, connu sous le nom &lt;a href="https://www.youtube.com/watch?v=d1F_Ye3mSnE"  title="  John Wesley: les origines du méthodisme | Dans la lignée des héros de la foi par Ainsi parle l'éternel"&gt;de méthodisme&lt;/a&gt;.  Il combine une vaste culture (philosophie, langues, théologie) à une activité de prédication et de réforme. &lt;/p&gt; &lt;p&gt; Il étudie les lettres classiques à Oxford, apprend plusieurs langues et se destine à une vie religieuse dès 1725. Après un séjour d’évangélisation aux États-Unis, il revient marqué par la ferveur des moraves et, lors d’une  &lt;a href="https://www.youtube.com/watch?v=v-B6rEPbNQk"  title=" Qu’est ce qu’une expérience spirituelle par Numérologie &amp; Spiritualité"&gt;expérience spirituelle&lt;/a&gt; en 1738, affirme avoir trouvé l'assurance du salut – événement clé du méthodisme, qui repose sur le réveil personnel et l’expérience directe de la foi. Il se distingue par son opposition à la doctrine de la prédestination et par son attachement à l’arminianisme, qui valorise la responsabilité humaine et la conversion personnelle. Il insiste sur la « sanctification » : vivre selon l’amour du Christ et tendre vers une  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_2008_num_88_3_1347" title="Le Cheminement théologique de John Wesley (1703-1791) avec le catholicisme par Persée"&gt; perfection chrétienne&lt;/a&gt; dans la vie morale et sociale. Il combat aussi le déisme des Lumières, défendant un christianisme de révélation et d’engagement immédiat. &lt;/p&gt; &lt;p&gt; Il est aussi connu pour son engagement contre l’esclavage ; il considère la liberté comme un droit naturel et publie plusieurs écrits abolitionnistes. Il a influencé d’autres figures majeures du mouvement antiesclavagiste et prôné un christianisme impliqué dans la justice sociale. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F54" s="47" t="inlineStr">
+      <c r="F55" s="47" t="inlineStr">
         <is>
           <t>N8El4zSIY9A</t>
         </is>
       </c>
-      <c r="G54" s="49" t="inlineStr">
+      <c r="G55" s="49" t="inlineStr">
         <is>
           <t>"Prédication John Wesley en Français Marcher par la Foi ou par la vue" par Grâce &amp; Justice en Lui</t>
         </is>
       </c>
-      <c r="H54" s="49" t="inlineStr">
+      <c r="H55" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/wesley-mini.webp</t>
         </is>
       </c>
-      <c r="I54" s="45" t="n"/>
-      <c r="J54" s="55" t="inlineStr">
+      <c r="I55" s="45" t="n"/>
+      <c r="J55" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K54" s="45" t="inlineStr">
+      <c r="K55" s="45" t="inlineStr">
         <is>
           <t>ethique ; spiritualite</t>
         </is>
       </c>
-      <c r="L54" s="46" t="inlineStr">
+      <c r="L55" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Spiritualisme</t>
         </is>
       </c>
-      <c r="M54" s="35" t="inlineStr">
+      <c r="M55" s="35" t="inlineStr">
         <is>
           <t>philosophe anglais déclencheur d'un réveil de l'Église d'Angleterre, le méthodisme.</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="166.5" customHeight="1" s="39">
-      <c r="A55" s="47" t="n">
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="166.5" customHeight="1" s="39">
+      <c r="A56" s="47" t="n">
         <v>1705</v>
       </c>
-      <c r="B55" s="47" t="inlineStr">
+      <c r="B56" s="47" t="inlineStr">
         <is>
           <t>1757</t>
         </is>
       </c>
-      <c r="C55" s="47" t="inlineStr">
+      <c r="C56" s="47" t="inlineStr">
         <is>
           <t>1705 – 1757</t>
         </is>
       </c>
-      <c r="D55" s="48" t="inlineStr">
+      <c r="D56" s="48" t="inlineStr">
         <is>
           <t>David HARTLEY</t>
         </is>
       </c>
-      <c r="E55" s="58" t="inlineStr">
+      <c r="E56" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)"    title=" Wikipedia"&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href="https://www.youtube.com/watch?v=kbpEAw2gl40" title=" David Hartley par Crevoisier Philippe"&gt; développement de la psychologie&lt;/a&gt;, en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt; - La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la "substance médullaire" (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt; - La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des "vibratiuncules" (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs "vibratiuncules" respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href="https://www.youtube.com/shorts/BuqpLB9V41c"  title=" David Hartley par timelinephilosopher"&gt;  le fondement des idées et des pensées&lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des "vibratiuncules" de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, "Observations on Man, his Frame, his Duty, and his Expectations", publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt; 
 - L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt; 
 - Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F55" s="47" t="inlineStr">
+      <c r="F56" s="47" t="inlineStr">
         <is>
           <t>zYRbpPFmSWM</t>
         </is>
       </c>
-      <c r="G55" s="49" t="inlineStr">
+      <c r="G56" s="49" t="inlineStr">
         <is>
           <t>"Reprogramming Life with Hartley’s Wisdom |Reflections in the Mind’s Mirror" par Sucess saga Stories</t>
         </is>
       </c>
-      <c r="H55" s="49" t="inlineStr">
+      <c r="H56" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/hartley-mini.webp</t>
         </is>
       </c>
-      <c r="I55" s="45" t="n"/>
-      <c r="J55" s="55" t="inlineStr">
+      <c r="I56" s="45" t="n"/>
+      <c r="J56" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K55" s="45" t="inlineStr">
+      <c r="K56" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L55" s="46" t="inlineStr">
+      <c r="L56" s="46" t="inlineStr">
         <is>
           <t>Empirisme</t>
         </is>
       </c>
-      <c r="M55" s="35" t="inlineStr">
+      <c r="M56" s="35" t="inlineStr">
         <is>
           <t>philosophe et psychologue anglais précurseur dans l'étude de l'esprit humain.</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="135" customHeight="1" s="39">
-      <c r="A56" s="47" t="n">
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="135" customHeight="1" s="39">
+      <c r="A57" s="47" t="n">
         <v>1709</v>
       </c>
-      <c r="B56" s="47" t="inlineStr">
+      <c r="B57" s="47" t="inlineStr">
         <is>
           <t>1751</t>
         </is>
       </c>
-      <c r="C56" s="47" t="inlineStr">
+      <c r="C57" s="47" t="inlineStr">
         <is>
           <t>1709 – 1751</t>
         </is>
       </c>
-      <c r="D56" s="48" t="inlineStr">
+      <c r="D57" s="48" t="inlineStr">
         <is>
           <t>Julien Offray de la METTRIE</t>
         </is>
       </c>
-      <c r="E56" s="63" t="inlineStr">
+      <c r="E57" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julien_Offray_de_La_Mettrie"    title=" Wikipedia"&gt;Julien Onfray de la METTRIE&lt;/a&gt;  était un philosophe et médecin français des Lumières, connu pour son &lt;a href="https://www.youtube.com/watch?v=ATn23C-jw1M"  title=" Traité du bonheur de la Mettrie par Voyage interieur"&gt; matérialisme radical &lt;/a&gt; et son athéisme provocateur. Médecin militaire, il fut exilé de France après la publication de ses idées controversées, avant de trouver refuge auprès de Frédéric II de Prusse à Potsdam. &lt;/p&gt; &lt;p&gt; Dans L’Homme machine (1747), il affirme que l’être humain est une machine purement matérielle : l’âme n’existe pas comme substance distincte, mais émerge des processus physiques du cerveau et du corps, sans besoin de Dieu ou d’esprit immatériel. Il s’inspire de Descartes, mais pousse le mécanisme jusqu’au bout en rejetant le dualisme corps-âme.  &lt;/p&gt; &lt;p&gt; Ses écrits, comme Histoire naturelle de l’âme (1745), scandalisèrent l’Église et les autorités : ses livres furent brûlés publiquement et il perdit son poste aux Gardes-Françaises. Défenseur d’un hédonisme sensualiste, il prône le  &lt;a href="https://www.youtube.com/watch?v=FH2TDimoh7Q"  title=" La Mettrie ou l’art de jouir par Parole de philosophe"&gt; plaisir comme seul bien moral,&lt;/a&gt;  sans morale transcendante. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés : - Histoire naturelle de l’âme (1745) : Critique du dualisme et fondement matérialiste. - L’Homme machine (1747) : Thèse principale sur l’automatisme humain. - L’Homme plante (1748) : Étend le mécanisme aux végétaux et animaux. &lt;/p&gt; &lt;p&gt; Précurseur du matérialisme moderne et de la philosophie de la vie, il influence Diderot et les Encyclopédistes, mais reste marginalisé pour son radicalisme. Il anticipe des idées sur l’évolution et la cybernétique en voyant l’humain comme un système organisé. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F56" s="47" t="inlineStr">
+      <c r="F57" s="47" t="inlineStr">
         <is>
           <t>kTzhhULUEtQ</t>
         </is>
       </c>
-      <c r="G56" s="49" t="inlineStr">
+      <c r="G57" s="49" t="inlineStr">
         <is>
           <t>"Julien Offray de La Mettrie : Défier l'âme" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H56" s="49" t="inlineStr">
+      <c r="H57" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jmettrie-mini.webp</t>
         </is>
       </c>
-      <c r="I56" s="45" t="n"/>
-      <c r="J56" s="38" t="inlineStr">
+      <c r="I57" s="45" t="n"/>
+      <c r="J57" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K56" s="45" t="inlineStr">
+      <c r="K57" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L56" s="46" t="inlineStr">
+      <c r="L57" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Matérialisme ; Épiphénoménisme ; Athéisme</t>
         </is>
       </c>
-      <c r="M56" s="35" t="inlineStr">
+      <c r="M57" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour son matérialisme radical et son athéisme.</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="120" customHeight="1" s="39">
-      <c r="A57" s="47" t="n">
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="120" customHeight="1" s="39">
+      <c r="A58" s="47" t="n">
         <v>1710</v>
       </c>
-      <c r="B57" s="47" t="inlineStr">
+      <c r="B58" s="47" t="inlineStr">
         <is>
           <t>1796</t>
         </is>
       </c>
-      <c r="C57" s="47" t="inlineStr">
+      <c r="C58" s="47" t="inlineStr">
         <is>
           <t>1710 – 1796</t>
         </is>
       </c>
-      <c r="D57" s="48" t="inlineStr">
+      <c r="D58" s="48" t="inlineStr">
         <is>
           <t>Thomas REID</t>
         </is>
       </c>
-      <c r="E57" s="62" t="inlineStr">
+      <c r="E58" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Reid"   title=" Wikipedia"&gt;Thomas REID&lt;/a&gt; était un philosophe écossais des Lumières écossaises, fondateur de l'école du sens commun. Contemporain et critique principal de David Hume, il enseigna à Aberdeen puis à Glasgow, où il succéda à Adam Smith. Il  défend le réalisme direct : nous percevons immédiatement les objets extérieurs eux-mêmes, sans passer par  &lt;a href="https://fr.wikisource.org/wiki/Grand_dictionnaire_universel_du_XIXe_si%C3%A8cle/Reid_(thomas)_(philosophe)"  title=" Reid philosophe par Wikisource"&gt; des "idées"  &lt;/a&gt; intermédiaires comme chez Locke ou Descartes. Le sens commun fournit des principes innés et indubitables (existence du monde, causalité, témoignage), que la philosophie doit respecter plutôt que miner. &lt;/p&gt; &lt;p&gt; Face au scepticisme humain, il argue que nier ces principes du sens commun mène à l'absurde : si nous doutons de tout, la philosophie devient inutilisable. Il réfute la "théorie des idées représentatives" qui, selon lui, engendre le doute hyperbolique. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Recherche sur l'entendement humain d'après les principes du sens commun (1764) : sa thèse majeure. - Principes de la philosophie morale : lie épistémologie et éthique pratique, inspirée du stoïcisme. &lt;/p&gt; &lt;p&gt; Comme Hutcheson, il valorise une  &lt;a href="https://www.youtube.com/watch?v=Nq9g-OYRLLQ"  title=" Reid’s commun sense design philosophy par Discovery Science"&gt; faculté innée &lt;/a&gt;  (sens moral chez l'un, sens commun chez l'autre), mais appliquée à la connaissance plutôt qu'à la morale pure. Tous deux s'opposent au scepticisme et à l'égoïsme hobbesien.https://encyclo-philo.fr/item/221 &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F57" s="47" t="inlineStr">
+      <c r="F58" s="47" t="inlineStr">
         <is>
           <t>D4l_YhfDN30</t>
         </is>
       </c>
-      <c r="G57" s="49" t="inlineStr">
+      <c r="G58" s="49" t="inlineStr">
         <is>
           <t>"Thomas Reid: Unraveling the Philosophical Mysteries" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H57" s="49" t="inlineStr">
+      <c r="H58" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/reid-mini.webp</t>
         </is>
       </c>
-      <c r="I57" s="45" t="n"/>
-      <c r="J57" s="55" t="inlineStr">
+      <c r="I58" s="45" t="n"/>
+      <c r="J58" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K57" s="45" t="inlineStr">
+      <c r="K58" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L57" s="46" t="inlineStr">
+      <c r="L58" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Empirisme ; Particularisme</t>
         </is>
       </c>
-      <c r="M57" s="35" t="inlineStr">
+      <c r="M58" s="35" t="inlineStr">
         <is>
           <t>philosophe des Lumières écossaises, fondateur de l'école du sens commun.</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="115.5" customHeight="1" s="39">
-      <c r="A58" s="47" t="n">
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="115.5" customHeight="1" s="39">
+      <c r="A59" s="47" t="n">
         <v>1711</v>
       </c>
-      <c r="B58" s="47" t="inlineStr">
+      <c r="B59" s="47" t="inlineStr">
         <is>
           <t>1776</t>
         </is>
       </c>
-      <c r="C58" s="47" t="inlineStr">
+      <c r="C59" s="47" t="inlineStr">
         <is>
           <t>1711 - 1776</t>
         </is>
       </c>
-      <c r="D58" s="48" t="inlineStr">
+      <c r="D59" s="48" t="inlineStr">
         <is>
           <t>David HUME</t>
         </is>
       </c>
-      <c r="E58" s="58" t="inlineStr">
+      <c r="E59" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/David_Hume"  title=" Wikipedia"&gt;David HUME&lt;/a&gt; était un philosophe, historien et économiste écossais de l'ère des Lumières. Il est surtout connu pour ses contributions à la philosophie empirique, la théorie de la connaissance, la métaphysique, l'éthique et l'esthétique. &lt;/p&gt; &lt;p&gt; Hume était un sceptique et a cherché à examiner de manière critique les idées préconçues et les &lt;a  href="https://www.youtube.com/watch?v=CLIoxw6TXuk&amp;ab_channel=LePr%C3%A9cepteur"  title="Tout n'est que croyance  par Le Précepteur"&gt;croyances reçues&lt;/a&gt;. Il a rejeté les arguments métaphysiques qui ne pouvaient pas être fondés sur l'expérience directe, et a affirmé que les connaissances humaines étaient basées sur les impressions et les idées que nous en avons. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de &lt;a  href="https://www.youtube.com/watch?v=ftd3vjw9lSU"  title=" la causalité par Skarblown Animations"&gt;la causalité&lt;/a&gt;, qui affirme que nous ne pouvons pas connaître la relation de cause à effet entre deux événements par simple observation, mais que nous sommes amenés à croire en une telle relation en raison de notre expérience passée.  &lt;/p&gt; &lt;p&gt; En éthique, il a affirmé que la morale était basée sur des sentiments plutôt que sur la raison et qu'elle ne peut pas être déduite de principes rationnels, mais doit être fondée sur l'empathie et la sympathie envers les autres.  &lt;/p&gt; &lt;p&gt; Il a également souligné l'importance du bonheur et du plaisir dans la vie, affirmant que ce sont des aspects essentiels de notre existence et de notre &lt;a  href="https://www.youtube.com/watch?v=52077nWSkPM&amp;t=11s&amp;ab_channel=LePr%C3%A9cepteur"   title="l'identité par le Précepteur"&gt;identité&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il a écrit sur la religion et a critiqué les arguments traditionnels pour l'existence de Dieu en affirmant que la religion était basée sur la superstition plutôt que sur la raison, et que la croyance en Dieu était fondée sur l'habitude plutôt que sur la preuve. &lt;/p&gt;  &lt;audio controls title="Pourquoi faut il lire David Hume par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22838-02.02.2022-ITEMA_22927004-2022C45539E0018-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F58" s="47" t="inlineStr">
+      <c r="F59" s="47" t="inlineStr">
         <is>
           <t>67YDDiB1Gms</t>
         </is>
       </c>
-      <c r="G58" s="49" t="inlineStr">
+      <c r="G59" s="49" t="inlineStr">
         <is>
           <t>David Hume par Bibiclo</t>
         </is>
       </c>
-      <c r="H58" s="49" t="inlineStr">
+      <c r="H59" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/hume-mini.webp</t>
         </is>
       </c>
-      <c r="I58" s="45" t="n"/>
-      <c r="J58" s="55" t="inlineStr">
+      <c r="I59" s="45" t="n"/>
+      <c r="J59" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K58" s="45" t="inlineStr">
+      <c r="K59" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; ethique</t>
         </is>
       </c>
-      <c r="L58" s="46" t="inlineStr">
+      <c r="L59" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Empirisme ; Scepticisme ; Agnosticisme ; Lumières ; Méthodisme ; Phénoménisme</t>
         </is>
       </c>
-      <c r="M58" s="35" t="inlineStr">
+      <c r="M59" s="35" t="inlineStr">
         <is>
           <t>philosophe écossais Sceptique et fondateur de l'Empirisme moderne.</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P58">
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P59">
         <v>3</v>
       </c>
     </row>
-    <row r="59" ht="126.75" customHeight="1" s="39">
-      <c r="A59" s="47" t="n">
+    <row r="60" ht="126.75" customHeight="1" s="39">
+      <c r="A60" s="47" t="n">
         <v>1712</v>
       </c>
-      <c r="B59" s="47" t="inlineStr">
+      <c r="B60" s="47" t="inlineStr">
         <is>
           <t>1778</t>
         </is>
       </c>
-      <c r="C59" s="47" t="inlineStr">
+      <c r="C60" s="47" t="inlineStr">
         <is>
           <t>1712 - 1778</t>
         </is>
       </c>
-      <c r="D59" s="48" t="inlineStr">
+      <c r="D60" s="48" t="inlineStr">
         <is>
           <t>Jean Jacques ROUSSEAU</t>
         </is>
       </c>
-      <c r="E59" s="58" t="inlineStr">
+      <c r="E60" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau" title=" Wikipedia"&gt; Jean-Jacques ROUSSEAU&lt;/a&gt; était un philosophe &lt;a href="https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;ab_channel=LePr%C3%A9cepteur"  title="Les Lumières par le Précepteur "&gt; des lumières&lt;/a&gt; et écrivain suisse-français, défenseur de la liberté et de l'égalité. Il et est surtout connu pour son livre &lt;a href="https://www.youtube.com/watch?v=tToAS8pUXzU"   title="Le texte fondateur par Alain Bajomée "&gt;"Du contrat social"&lt;/a&gt;, dans lequel il développe sa théorie politique ainsi que &lt;a href="https://www.youtube.com/watch?v=3-mPXD5CkJc"  title="L'Emile par Librairie Vrin"&gt;"Emile" &lt;/a&gt;considéré comme un "traité d'écucation" ou sa théorie de l'homme. &lt;/p&gt; &lt;p&gt;
 Rousseau a également écrit sur la philosophie morale, la théorie de l'éducation et la nature humaine et  &lt;a href="https://www.youtube.com/watch?v=cUtO8U9QbZs&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Le désir par le Précepteur "&gt; le désir&lt;/a&gt;. Il croyait que &lt;a href="https://www.youtube.com/watch?v=FpXdTgerxiI&amp;ab_channel=LePr%C3%A9cepteur"   title="L''homme est naturellement bon par le Précepteur "&gt; l'homme est naturellement bon&lt;/a&gt;, mais corrompu par la société et la civilisation. Il a également affirmé que la liberté individuelle est essentielle à l'épanouissement humain et que les institutions politiques doivent être créées pour protéger les droits et les libertés des individus. &lt;/p&gt; &lt;p&gt;  Il est souvent considéré comme un précurseur du  &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1927_num_29_16_2482#"  title="La philosophie romantique par Persée "&gt; romantisme&lt;/a&gt; en raison de son accent mis sur les émotions, la nature, l'individualité et la subjectivité. Il a exprimé une méfiance envers la société civilisée et a prôné un retour à la nature et à la simplicité. Il a également souligné l'importance de l'émotion et de l'expérience personnelle dans la compréhension du monde, remettant en question l'approche rationnelle et scientifique des Lumières. Ses idées ont eu une influence significative sur les écrivains et les artistes romantiques ultérieurs, qui ont valorisé l'expression émotionnelle et l'expérience individuelle dans leurs œuvres.&lt;/p&gt; &lt;p&gt;
@@ -4590,71 +4656,71 @@
 </t>
         </is>
       </c>
-      <c r="F59" s="47" t="inlineStr">
+      <c r="F60" s="47" t="inlineStr">
         <is>
           <t>NA0upIwMLSk</t>
         </is>
       </c>
-      <c r="G59" s="49" t="inlineStr">
+      <c r="G60" s="49" t="inlineStr">
         <is>
           <t>"Jean Jacques ROUSSEAU" par Culture Tube</t>
         </is>
       </c>
-      <c r="H59" s="49" t="inlineStr">
+      <c r="H60" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rousseau-mini.webp</t>
         </is>
       </c>
-      <c r="I59" s="45" t="n"/>
-      <c r="J59" s="38" t="inlineStr">
+      <c r="I60" s="45" t="n"/>
+      <c r="J60" s="38" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
       </c>
-      <c r="K59" s="45" t="inlineStr">
+      <c r="K60" s="45" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="L59" s="46" t="inlineStr">
+      <c r="L60" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Contractualisme ; Lumières</t>
         </is>
       </c>
-      <c r="M59" s="35" t="inlineStr">
+      <c r="M60" s="35" t="inlineStr">
         <is>
           <t>philosophe et écrivain franco-suisse de l'époque des lumières.</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P59">
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P60">
         <v>3</v>
       </c>
     </row>
-    <row r="60" ht="148.5" customHeight="1" s="39">
-      <c r="A60" s="47" t="n">
+    <row r="61" ht="148.5" customHeight="1" s="39">
+      <c r="A61" s="47" t="n">
         <v>1713</v>
       </c>
-      <c r="B60" s="47" t="inlineStr">
+      <c r="B61" s="47" t="inlineStr">
         <is>
           <t>1784</t>
         </is>
       </c>
-      <c r="C60" s="47" t="inlineStr">
+      <c r="C61" s="47" t="inlineStr">
         <is>
           <t>1713 - 1784</t>
         </is>
       </c>
-      <c r="D60" s="48" t="inlineStr">
+      <c r="D61" s="48" t="inlineStr">
         <is>
           <t>Denis DIDEROT</t>
         </is>
       </c>
-      <c r="E60" s="58" t="inlineStr">
+      <c r="E61" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Denis_Diderot"  title=" Wikipedia"&gt; Denis DIDEROT&lt;/a&gt; était un philosophe des Lumières français ainsi qu' un écrivain, éditeur et encyclopédiste influent.  Il est surtout connu pour son rôle de coéditeur et contributeur majeur de &lt;a href="https://www.youtube.com/watch?v=LuRI5zg7tJY"   title="Diderot 1750 Encyclopedia par OER Project "&gt;l'Encyclopédie, &lt;/a&gt; ou Dictionnaire raisonné des sciences, des arts et des métiers.&lt;/p&gt; &lt;p&gt;
 Il était un fervent défenseur de la raison et de l'esprit critique et il rejetait les dogmes et les traditions aveugles, encourageant à la place l'examen rationnel et la remise en question des croyances établies. Il croyait en la capacité de l'homme à comprendre le monde à travers la science, la philosophie et l'observation directe. &lt;/p&gt; &lt;p&gt;
@@ -4663,107 +4729,40 @@
    &lt;audio controls title="Le Neveu de Rameau par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/10/s40/RF_38A1D24B-FA10-43F4-8B19-8C4921845BD4_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F60" s="47" t="inlineStr">
+      <c r="F61" s="47" t="inlineStr">
         <is>
           <t>MwdE6ig1mVw</t>
         </is>
       </c>
-      <c r="G60" s="49" t="inlineStr">
+      <c r="G61" s="49" t="inlineStr">
         <is>
           <t>"Philosopher-Diderot " par Guillaume Deloison</t>
         </is>
       </c>
-      <c r="H60" s="49" t="inlineStr">
+      <c r="H61" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/diderot-mini.webp</t>
-        </is>
-      </c>
-      <c r="I60" s="45" t="n"/>
-      <c r="J60" s="38" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K60" s="45" t="inlineStr">
-        <is>
-          <t>epistemologie ; politique</t>
-        </is>
-      </c>
-      <c r="L60" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matérialisme ; Lumières ; Athéisme</t>
-        </is>
-      </c>
-      <c r="M60" s="35" t="inlineStr">
-        <is>
-          <t>philosophe et écrivain français des lumières qui rejetait les dogmes.</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="166.5" customHeight="1" s="39">
-      <c r="A61" s="47" t="n">
-        <v>1714</v>
-      </c>
-      <c r="B61" s="47" t="inlineStr">
-        <is>
-          <t>1762</t>
-        </is>
-      </c>
-      <c r="C61" s="47" t="inlineStr">
-        <is>
-          <t>1714 – 1762</t>
-        </is>
-      </c>
-      <c r="D61" s="48" t="inlineStr">
-        <is>
-          <t>Alexander  Gottlieb BAUMGARTEN</t>
-        </is>
-      </c>
-      <c r="E61" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Gottlieb_Baumgarten"  title=" Wikipedia"&gt;Alexander Gottlieb BAUMGARTEN&lt;/a&gt;  était un philosophe allemand considéré comme le père de l'esthétique en tant que discipline philosophique autonome. Il  a étudié à Halle sous l'influence de Christian Wolff et de la tradition leibnizienne. Professeur à Halle puis à Francfort, il a développé une pensée rationaliste tout en valorisant la connaissance sensible.  &lt;/p&gt; &lt;p&gt; Dans son œuvre majeure Aesthetica (1750-1758), il introduit le terme &lt;a href="https://www.youtube.com/watch?v=izQeXqAcTVo"  title="Qu’est ce que l’esthétique aujourd’hui par Esthete Esthete"&gt;« esthétique » &lt;/a&gt; (du grec aisthēsis, sensation) pour désigner la « science de la connaissance sensible ». Contrairement à la logique qui traite de la connaissance rationnelle, l'esthétique étudie la perfection sensible, c'est-à-dire le beau perçu par les sens comme une forme complète de savoir. &lt;/p&gt; &lt;p&gt; Il  défend l'autonomie des « facultés inférieures » (sens, imagination, mémoire) face à la suprématie de la raison, voyant dans le beau une perfection analogue à la vérité (rationnelle) et au bien (moral). Son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1992_num_90_87_6745"  title="De Baumgarten à Kant par Persée"&gt;travail a influencé Kant &lt;/a&gt; et l'idéalisme allemand en légitimant l'étude philosophique de l'art et de l'expérience esthétique. Il insiste sur le rôle créatif de l'artiste, qui doit embellir la nature par l'ajout d'éléments sensibles. &lt;/p&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F61" s="47" t="inlineStr">
-        <is>
-          <t>7If2WywcyME</t>
-        </is>
-      </c>
-      <c r="G61" s="49" t="inlineStr">
-        <is>
-          <t>"Alexander Gottlieb Baumgarten : Redéfinir l'esthétique " par VIS PHILO</t>
-        </is>
-      </c>
-      <c r="H61" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/abaumgarten-mini.webp</t>
         </is>
       </c>
       <c r="I61" s="45" t="n"/>
       <c r="J61" s="38" t="inlineStr">
         <is>
-          <t>Allemande</t>
+          <t>Française</t>
         </is>
       </c>
       <c r="K61" s="45" t="inlineStr">
         <is>
-          <t>esthetique ; epistemologie</t>
+          <t>epistemologie ; politique</t>
         </is>
       </c>
       <c r="L61" s="46" t="inlineStr">
         <is>
-          <t>Rationalisme</t>
+          <t xml:space="preserve">Matérialisme ; Lumières ; Athéisme</t>
         </is>
       </c>
       <c r="M61" s="35" t="inlineStr">
         <is>
-          <t>philosophe allemand considéré comme le père de l'esthétique.</t>
+          <t>philosophe et écrivain français des lumières qui rejetait les dogmes.</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4776,842 +4775,843 @@
       <c r="A62" s="47" t="n">
         <v>1714</v>
       </c>
-      <c r="B62" s="47" t="n">
+      <c r="B62" s="47" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="C62" s="47" t="inlineStr">
+        <is>
+          <t>1714 – 1762</t>
+        </is>
+      </c>
+      <c r="D62" s="48" t="inlineStr">
+        <is>
+          <t>Alexander  Gottlieb BAUMGARTEN</t>
+        </is>
+      </c>
+      <c r="E62" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Gottlieb_Baumgarten"  title=" Wikipedia"&gt;Alexander Gottlieb BAUMGARTEN&lt;/a&gt;  était un philosophe allemand considéré comme le père de l'esthétique en tant que discipline philosophique autonome. Il  a étudié à Halle sous l'influence de Christian Wolff et de la tradition leibnizienne. Professeur à Halle puis à Francfort, il a développé une pensée rationaliste tout en valorisant la connaissance sensible.  &lt;/p&gt; &lt;p&gt; Dans son œuvre majeure Aesthetica (1750-1758), il introduit le terme &lt;a href="https://www.youtube.com/watch?v=izQeXqAcTVo"  title="Qu’est ce que l’esthétique aujourd’hui par Esthete Esthete"&gt;« esthétique » &lt;/a&gt; (du grec aisthēsis, sensation) pour désigner la « science de la connaissance sensible ». Contrairement à la logique qui traite de la connaissance rationnelle, l'esthétique étudie la perfection sensible, c'est-à-dire le beau perçu par les sens comme une forme complète de savoir. &lt;/p&gt; &lt;p&gt; Il  défend l'autonomie des « facultés inférieures » (sens, imagination, mémoire) face à la suprématie de la raison, voyant dans le beau une perfection analogue à la vérité (rationnelle) et au bien (moral). Son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1992_num_90_87_6745"  title="De Baumgarten à Kant par Persée"&gt;travail a influencé Kant &lt;/a&gt; et l'idéalisme allemand en légitimant l'étude philosophique de l'art et de l'expérience esthétique. Il insiste sur le rôle créatif de l'artiste, qui doit embellir la nature par l'ajout d'éléments sensibles. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F62" s="47" t="inlineStr">
+        <is>
+          <t>7If2WywcyME</t>
+        </is>
+      </c>
+      <c r="G62" s="49" t="inlineStr">
+        <is>
+          <t>"Alexander Gottlieb Baumgarten : Redéfinir l'esthétique " par VIS PHILO</t>
+        </is>
+      </c>
+      <c r="H62" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/abaumgarten-mini.webp</t>
+        </is>
+      </c>
+      <c r="I62" s="45" t="n"/>
+      <c r="J62" s="38" t="inlineStr">
+        <is>
+          <t>Allemande</t>
+        </is>
+      </c>
+      <c r="K62" s="45" t="inlineStr">
+        <is>
+          <t>esthetique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L62" s="46" t="inlineStr">
+        <is>
+          <t>Rationalisme</t>
+        </is>
+      </c>
+      <c r="M62" s="35" t="inlineStr">
+        <is>
+          <t>philosophe allemand considéré comme le père de l'esthétique.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="166.5" customHeight="1" s="39">
+      <c r="A63" s="47" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B63" s="47" t="n">
         <v>1804</v>
       </c>
-      <c r="C62" s="47" t="inlineStr">
+      <c r="C63" s="47" t="inlineStr">
         <is>
           <t>1714 – 1804</t>
         </is>
       </c>
-      <c r="D62" s="48" t="inlineStr">
+      <c r="D63" s="48" t="inlineStr">
         <is>
           <t>Johann Joachim SPALDING</t>
         </is>
       </c>
-      <c r="E62" s="63" t="inlineStr">
+      <c r="E63" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Joachim_Spalding" title=" Wikipedia"&gt;Johann Joachim SPALDING&lt;/a&gt; était un théologien protestant allemand, souvent considéré comme l’un des grands représentants des Lumières religieuses en Allemagne. Sa pensée cherche à concilier foi chrétienne, raison et morale, dans un esprit de réforme modérée plutôt que de rupture. &lt;/p&gt; &lt;p&gt; Dans son œuvre la plus célèbre, Die Bestimmung des Menschen (1748), il réfléchit au sens de la vie humaine. Pour lui, l’être humain n’est pas fait seulement pour satisfaire ses besoins matériels, mais pour se développer intérieurement, moralement et spirituellement. &lt;/p&gt; &lt;p&gt; Sa philosophie religieuse défend l’idée d’une religion naturelle compatible avec la Révélation. Il refuse le dogmatisme rigide et l’orthodoxie autoritaire, et insiste sur une foi plus vivante, fondée sur la conscience, le bon sens et l’expérience intérieure. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande importance &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1979_num_92_88_18346"  title="problèmes de la théologie allemande par persée"&gt;au sentiment religieux. &lt;/a&gt;  Dans son ouvrage de 1789, il montre que les émotions et la vie intérieure ont une vraie place dans le christianisme, sans que cela supprime l’exigence morale. Il représente une forme de christianisme éclairé : une religion raisonnable, morale et personnelle, qui veut rendre la foi plus humaine et plus intelligible. Son influence a compté dans la théologie protestante allemande, notamment dans le courant appelé néologie. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F62" s="47" t="n"/>
-      <c r="G62" s="49" t="n"/>
-      <c r="H62" s="58" t="inlineStr">
+      <c r="F63" s="47" t="n"/>
+      <c r="G63" s="49" t="n"/>
+      <c r="H63" s="58" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jjspalding-mini.webp</t>
         </is>
       </c>
-      <c r="I62" s="45" t="inlineStr">
+      <c r="I63" s="45" t="inlineStr">
         <is>
           <t>https://laphilo.fr/photo/jjspalding.webp</t>
         </is>
       </c>
-      <c r="J62" s="38" t="inlineStr">
+      <c r="J63" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K62" s="45" t="inlineStr">
+      <c r="K63" s="45" t="inlineStr">
         <is>
           <t>spiritualite</t>
         </is>
       </c>
-      <c r="L62" s="46" t="inlineStr">
+      <c r="L63" s="46" t="inlineStr">
         <is>
           <t>Rationalisme</t>
         </is>
       </c>
-      <c r="M62" s="35" t="inlineStr">
+      <c r="M63" s="35" t="inlineStr">
         <is>
           <t>philosophe et théologien protestant allemand, représentant des Lumières religieuses.</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="153.75" customHeight="1" s="39">
-      <c r="A63" s="47" t="n">
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="153.75" customHeight="1" s="39">
+      <c r="A64" s="47" t="n">
         <v>1715</v>
       </c>
-      <c r="B63" s="47" t="inlineStr">
+      <c r="B64" s="47" t="inlineStr">
         <is>
           <t>1771</t>
         </is>
       </c>
-      <c r="C63" s="47" t="inlineStr">
+      <c r="C64" s="47" t="inlineStr">
         <is>
           <t>1715 – 1771</t>
         </is>
       </c>
-      <c r="D63" s="48" t="inlineStr">
+      <c r="D64" s="48" t="inlineStr">
         <is>
           <t>Claude-Adrien HELVÉTIUS</t>
         </is>
       </c>
-      <c r="E63" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claude-Adrien_Helv%C3%A9tius" title=" Wikipedia"&gt;Claude-Adrien HELVÉTIUS&lt;/a&gt; était un philosophe français des Lumières, connu pour son matérialisme radical et son utilitarisme, qui a marqué le XVIIIe siècle par ses idées provocatrices sur l'esprit humain et la société. Il  fut fermier général, poète et mécène des philosophes, collaborant à l'Encyclopédie de Diderot. Son ouvrage  &lt;a href="https://fr.wikipedia.org/wiki/De_l%27esprit"  title="De l’esprit par Wikipedia"&gt;De l'esprit (1758)&lt;/a&gt;, publié anonymement, provoqua un scandale immense, fut condamné au feu par l'Église et le Parlement, mais diffusé en Hollande. &lt;/p&gt; &lt;p&gt; Influencé par Locke, il défend un sensualisme selon lequel toutes nos idées et connaissances proviennent des sensations physiques, sans innéisme ni libre arbitre clair. L'âme n'est que la faculté de sentir, et l'esprit en découle via la mémoire qui compare les impressions sensorielles.  &lt;/p&gt; &lt;p&gt; Pour lui, l'égoïsme personnel, motivé par le plaisir et la douleur, est la base de toute action vertueuse et sociale, transformé par l'éducation et les institutions en bonheur collectif. Il prône une société réformée par la raison, où lois et mœurs maximisent l'utilité commune sous une autorité éclairée. &lt;/p&gt;
+      <c r="E64" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claude-Adrien_Helv%C3%A9tius" title=" Wikipedia"&gt;Claude-Adrien HELVÉTIUS&lt;/a&gt; était un philosophe français des Lumières, connu pour son matérialisme radical et son utilitarisme, qui a marqué le XVIIIe siècle par ses idées provocatrices sur l'esprit humain et la société. Il  fut fermier général, poète et mécène des philosophes, collaborant à l'Encyclopédie de Diderot. Son ouvrage  &lt;a href="https://fr.wikipedia.org/wiki/De_l%27esprit"  title="De l’esprit par Wikipedia"&gt;De l'esprit (1758)&lt;/a&gt;, publié anonymement, provoqua un scandale immense, fut condamné au feu par l'Église et le Parlement, mais diffusé en Hollande. &lt;/p&gt; &lt;p&gt; Influencé par Locke, il défend un sensualisme selon lequel toutes nos idées et connaissances proviennent des sensations physiques, sans innéisme ni libre arbitre clair. L'âme n'est que la faculté de sentir, et l'esprit en découle via la mémoire qui compare les impressions sensorielles.  &lt;/p&gt; &lt;p&gt; Pour lui, l'égoïsme personnel, motivé par le plaisir et la douleur, est la base de toute action vertueuse et sociale, transformé par l'éducation et les institutions en bonheur collectif. Il prône une société réformée par la raison, où lois et mœurs maximisent l'utilité commune sous une autorité éclairée. Il soutient aussi que les hommes naissent avec des capacités à peu près égales : les différences d’esprit viennent de l’éducation et des circonstances, d’où l’importance qu’il accorde à l’instruction publique. Il développe ces thèses dans &lt;em&gt;De l’homme&lt;/em&gt;, publié après sa mort. Sa pensée, qui fait de « l’utilité publique » le principe de la morale et des lois, inspire Bentham et l’utilitarisme anglais. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F63" s="47" t="inlineStr">
+      <c r="F64" s="47" t="inlineStr">
         <is>
           <t>DyvOZMOphM4</t>
         </is>
       </c>
-      <c r="G63" s="49" t="inlineStr">
+      <c r="G64" s="49" t="inlineStr">
         <is>
           <t>"Préface "De l'Homme" - C.A. Helvetius" par Paul Eymeric</t>
         </is>
       </c>
-      <c r="H63" s="49" t="inlineStr">
+      <c r="H64" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/helvetius-mini.webp</t>
-        </is>
-      </c>
-      <c r="I63" s="45" t="n"/>
-      <c r="J63" s="38" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K63" s="45" t="inlineStr">
-        <is>
-          <t>ethique ; politique</t>
-        </is>
-      </c>
-      <c r="L63" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matérialisme ; Utilitarisme ; Lumières</t>
-        </is>
-      </c>
-      <c r="M63" s="35" t="inlineStr">
-        <is>
-          <t>philosophe français connu pour son matérialisme radical et son utilitarisme.</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="88.5" customHeight="1" s="39">
-      <c r="A64" s="47" t="n">
-        <v>1720</v>
-      </c>
-      <c r="B64" s="47" t="inlineStr">
-        <is>
-          <t>1793</t>
-        </is>
-      </c>
-      <c r="C64" s="47" t="inlineStr">
-        <is>
-          <t>1720 – 1793</t>
-        </is>
-      </c>
-      <c r="D64" s="48" t="inlineStr">
-        <is>
-          <t>Charles BONNET</t>
-        </is>
-      </c>
-      <c r="E64" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Bonnet_(naturaliste)"  title=" Wikipedia"&gt;Charles BONNET&lt;/a&gt;  était un philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie et sa découverte de la &lt;a href="https://fr.wikipedia.org/wiki/Paling%C3%A9n%C3%A9sie"  title="palingénésie par Wikipedia"&gt;parthénogenèse. &lt;/a&gt; Il  étudie la botanique et l'entomologie dès sa jeunesse, influencé par Newton, Leibniz et Malebranche. Malgré des problèmes de vue et d'ouïe précoces, il devient membre du Conseil des Deux-Cents et correspondant de l'Académie des sciences de Paris. &lt;/p&gt; &lt;p&gt; Il démontre en 1745 la reproduction par parthénogenèse chez les pucerons, obtenant onze générations sans fécondation, et étudie la régénération des vers, des limaçons et des pattes d'écrevisse. Ses Recherches sur l'usage des feuilles (1754) préfigurent la photosynthèse, et il défend la théorie de la préformation, où les germes préexistent depuis la Création. &lt;/p&gt; &lt;p&gt; Dans Essai de psychologie (1754) et Essai analytique sur les facultés de l'âme (1760), il développe un sensualisme spiritualiste, voyant les idées naître des sensations via les fibres cérébrales. Sa Palingénésie philosophique (1769) postule l'immortalité des âmes humaines et animales dans une échelle continue des êtres. &lt;/p&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F64" s="47" t="inlineStr">
-        <is>
-          <t>UWf2B79U0O0</t>
-        </is>
-      </c>
-      <c r="G64" s="49" t="inlineStr">
-        <is>
-          <t>"Charles Bonnet: Exploring Nature's Patterns" par VIS PHILO</t>
-        </is>
-      </c>
-      <c r="H64" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/cbonnet-mini.webp</t>
         </is>
       </c>
       <c r="I64" s="45" t="n"/>
       <c r="J64" s="38" t="inlineStr">
         <is>
+          <t>Française</t>
+        </is>
+      </c>
+      <c r="K64" s="45" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L64" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matérialisme ; Utilitarisme ; Lumières</t>
+        </is>
+      </c>
+      <c r="M64" s="35" t="inlineStr">
+        <is>
+          <t>philosophe français connu pour son matérialisme radical et son utilitarisme.</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="88.5" customHeight="1" s="39">
+      <c r="A65" s="47" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B65" s="47" t="inlineStr">
+        <is>
+          <t>1793</t>
+        </is>
+      </c>
+      <c r="C65" s="47" t="inlineStr">
+        <is>
+          <t>1720 – 1793</t>
+        </is>
+      </c>
+      <c r="D65" s="48" t="inlineStr">
+        <is>
+          <t>Charles BONNET</t>
+        </is>
+      </c>
+      <c r="E65" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Bonnet_(naturaliste)"  title=" Wikipedia"&gt;Charles BONNET&lt;/a&gt;  était un philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie et sa découverte de la parthénogenèse. Il  étudie la botanique et l'entomologie dès sa jeunesse, influencé par Newton, Leibniz et Malebranche. Malgré des problèmes de vue et d'ouïe précoces, il devient membre du Conseil des Deux-Cents et correspondant de l'Académie des sciences de Paris. &lt;/p&gt; &lt;p&gt; Il démontre en 1745 la reproduction par parthénogenèse chez les pucerons, obtenant onze générations sans fécondation, et étudie la régénération des vers, des limaçons et des pattes d'écrevisse. Ses Recherches sur l'usage des feuilles (1754) préfigurent la photosynthèse, et il défend la théorie de la préformation, où les germes préexistent depuis la Création. &lt;/p&gt; &lt;p&gt; Dans Essai de psychologie (1754) et Essai analytique sur les facultés de l'âme (1760), il développe un sensualisme spiritualiste, voyant les idées naître des sensations via les fibres cérébrales. Sa &lt;a href="https://fr.wikipedia.org/wiki/Paling%C3%A9n%C3%A9sie"  title="palingénésie par Wikipedia"&gt;&lt;em&gt;Palingénésie philosophique&lt;/em&gt;&lt;/a&gt; (1769) postule l'immortalité des âmes humaines et animales dans une échelle continue des êtres. Pour lui, la nature forme une chaîne sans rupture, du minéral à l’homme, que décrit sa &lt;em&gt;Contemplation de la nature&lt;/em&gt; (1764), et chaque être y progressera après la mort. Devenu presque aveugle, il décrit les visions qu’éprouvait son grand-père, qui voyait des personnages et des objets imaginaires tout en sachant qu’ils n’existaient pas : ces hallucinations des personnes malvoyantes portent aujourd’hui le nom de « syndrome de Charles Bonnet ». &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F65" s="47" t="inlineStr">
+        <is>
+          <t>UWf2B79U0O0</t>
+        </is>
+      </c>
+      <c r="G65" s="49" t="inlineStr">
+        <is>
+          <t>"Charles Bonnet: Exploring Nature's Patterns" par VIS PHILO</t>
+        </is>
+      </c>
+      <c r="H65" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/cbonnet-mini.webp</t>
+        </is>
+      </c>
+      <c r="I65" s="45" t="n"/>
+      <c r="J65" s="38" t="inlineStr">
+        <is>
           <t>Suisse</t>
         </is>
       </c>
-      <c r="K64" s="45" t="inlineStr">
+      <c r="K65" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L64" s="46" t="inlineStr">
+      <c r="L65" s="46" t="inlineStr">
         <is>
           <t>Empirisme</t>
         </is>
       </c>
-      <c r="M64" s="35" t="inlineStr">
+      <c r="M65" s="35" t="inlineStr">
         <is>
           <t>philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie.</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="126" customHeight="1" s="39">
-      <c r="A65" s="47" t="n">
-        <v>1723</v>
-      </c>
-      <c r="B65" s="47" t="inlineStr">
-        <is>
-          <t>1790</t>
-        </is>
-      </c>
-      <c r="C65" s="47" t="inlineStr">
-        <is>
-          <t>1723 - 1790</t>
-        </is>
-      </c>
-      <c r="D65" s="48" t="inlineStr">
-        <is>
-          <t>Adam SMITH</t>
-        </is>
-      </c>
-      <c r="E65" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0f"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie,il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F65" s="47" t="inlineStr">
-        <is>
-          <t>6onxSBxmBXs</t>
-        </is>
-      </c>
-      <c r="G65" s="49" t="inlineStr">
-        <is>
-          <t>"Adam Smith : le pere de l’éconnomie moderne" par Portrait Historiques</t>
-        </is>
-      </c>
-      <c r="H65" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/smith-mini.webp</t>
-        </is>
-      </c>
-      <c r="I65" s="45" t="n"/>
-      <c r="J65" s="55" t="inlineStr">
-        <is>
-          <t>Britannique</t>
-        </is>
-      </c>
-      <c r="K65" s="45" t="inlineStr">
-        <is>
-          <t>ethique ; politique</t>
-        </is>
-      </c>
-      <c r="L65" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Lumières</t>
-        </is>
-      </c>
-      <c r="M65" s="35" t="inlineStr">
-        <is>
-          <t>philosophe écossais Libéraliste qui développa sa théorie de la 'main invisible'.</t>
-        </is>
-      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="101.25" customHeight="1" s="39">
+    <row r="66" ht="126" customHeight="1" s="39">
       <c r="A66" s="47" t="n">
         <v>1723</v>
       </c>
       <c r="B66" s="47" t="inlineStr">
         <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="C66" s="47" t="inlineStr">
+        <is>
+          <t>1723 - 1790</t>
+        </is>
+      </c>
+      <c r="D66" s="48" t="inlineStr">
+        <is>
+          <t>Adam SMITH</t>
+        </is>
+      </c>
+      <c r="E66" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0f"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie,il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F66" s="47" t="inlineStr">
+        <is>
+          <t>6onxSBxmBXs</t>
+        </is>
+      </c>
+      <c r="G66" s="49" t="inlineStr">
+        <is>
+          <t>"Adam Smith : le pere de l’éconnomie moderne" par Portrait Historiques</t>
+        </is>
+      </c>
+      <c r="H66" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/smith-mini.webp</t>
+        </is>
+      </c>
+      <c r="I66" s="45" t="n"/>
+      <c r="J66" s="55" t="inlineStr">
+        <is>
+          <t>Britannique</t>
+        </is>
+      </c>
+      <c r="K66" s="45" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L66" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Lumières</t>
+        </is>
+      </c>
+      <c r="M66" s="35" t="inlineStr">
+        <is>
+          <t>philosophe écossais Libéraliste qui développa sa théorie de la 'main invisible'.</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="101.25" customHeight="1" s="39">
+      <c r="A67" s="47" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B67" s="47" t="inlineStr">
+        <is>
           <t>1789</t>
         </is>
       </c>
-      <c r="C66" s="47" t="inlineStr">
+      <c r="C67" s="47" t="inlineStr">
         <is>
           <t>1723 – 1789</t>
         </is>
       </c>
-      <c r="D66" s="48" t="inlineStr">
+      <c r="D67" s="48" t="inlineStr">
         <is>
           <t>Paul Thiry d'HOLBACH</t>
         </is>
       </c>
-      <c r="E66" s="58" t="inlineStr">
+      <c r="E67" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Thiry_d%27Holbach"  title=" Wikipedia"&gt;Paul Thiry d'HOLBACH&lt;/a&gt;  était un philosophe allemand et devient encyclopédiste, traduit des œuvres scientifiques allemandes et anglaises pour l'Encyclopédie de Diderot. Hôte du célèbre "cénacle d'Holbach", salon fréquenté par Diderot, Rousseau, Helvétius et Adam Smith, il anime un foyer intellectuel anticlérical jusqu'à sa mort en 1789. &lt;/p&gt; &lt;p&gt; Il défend un matérialisme radical: l'univers se compose uniquement de matière et de mouvement, régi par des  &lt;a href="https://www.youtube.com/watch?v=x99DRdMAd08"  title="Essai sur l'art de ramper à l'usage des courtisans - D'Holbach" par Vox Plebeia"&gt;lois causales &lt;/a&gt; nécessaires, excluant Dieu ou toute intervention surnaturelle. Athée virulent, il combat les religions comme sources d'erreur, de peur et de superstition dans des pamphlets pseudonymes comme &lt;a href="https://www.youtube.com/watch?v=8Uohr5Y9xx0" title="Religions Are ROTTING ILLUSIONS | Baron d’Holbach par Unfiltered Philosophy"&gt;"Le Christianisme dévoilé" &lt;/a&gt; paru en 1761 ou "Le Système de la nature" (1770), bible de l'athéisme. &lt;/p&gt; &lt;p&gt; Sa morale est utilitariste et eudémoniste: la vertu réside dans l'utilité pour le bonheur individuel et collectif, fondée sur la raison et l'éducation, sans recours à la religion. Fataliste et déterministe, il prône la liberté sociale, l'égalité et une politique naturelle anti-despotique, influençant la Révolution française par sa critique des privilèges et du fanatisme. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F66" s="47" t="inlineStr">
+      <c r="F67" s="47" t="inlineStr">
         <is>
           <t>0t-kRccSANI</t>
         </is>
       </c>
-      <c r="G66" s="49" t="inlineStr">
+      <c r="G67" s="49" t="inlineStr">
         <is>
           <t>"Baron d'Holbach: Enlightening the World" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H66" s="49" t="inlineStr">
+      <c r="H67" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/holbach-mini.webp</t>
         </is>
       </c>
-      <c r="I66" s="45" t="n"/>
-      <c r="J66" s="38" t="inlineStr">
+      <c r="I67" s="45" t="n"/>
+      <c r="J67" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K66" s="45" t="inlineStr">
+      <c r="K67" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; politique</t>
         </is>
       </c>
-      <c r="L66" s="46" t="inlineStr">
+      <c r="L67" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Matérialisme ; Athéisme ; Lumières ; Incompatibilisme</t>
         </is>
       </c>
-      <c r="M66" s="35" t="inlineStr">
+      <c r="M67" s="35" t="inlineStr">
         <is>
           <t>philosophe matérialiste allemand athée des Lumières.</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="166.5" customHeight="1" s="39">
-      <c r="A67" s="47" t="n">
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="166.5" customHeight="1" s="39">
+      <c r="A68" s="47" t="n">
         <v>1724</v>
       </c>
-      <c r="B67" s="47" t="inlineStr">
+      <c r="B68" s="47" t="inlineStr">
         <is>
           <t>1804</t>
         </is>
       </c>
-      <c r="C67" s="47" t="inlineStr">
+      <c r="C68" s="47" t="inlineStr">
         <is>
           <t>1724 - 1804</t>
         </is>
       </c>
-      <c r="D67" s="48" t="inlineStr">
+      <c r="D68" s="48" t="inlineStr">
         <is>
           <t>Emmanuel KANT</t>
         </is>
       </c>
-      <c r="E67" s="58" t="inlineStr">
+      <c r="E68" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant"  title=" Wikipedia"&gt;Emmanuel KANT&lt;/a&gt; (1724-1804) est un philosophe allemand des &lt;a href="https://la-philosophie.com/philosophie-lumieres" style="color:#88A1E9"   title="La philosophie des Lumières par la-philosophie.com"&gt;Lumières&lt;/a&gt;, l’un des plus grands de l’histoire. Il passe toute sa vie à Königsberg, en Prusse orientale, où il enseigne à l’université. La lecture de Hume le « réveille de son sommeil dogmatique » et le conduit à examiner les pouvoirs et les limites de la raison.&lt;/p&gt; &lt;p&gt;Dans la &lt;a href="https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos"   title="C'est quoi la raison pure par Kosmos"&gt;&lt;em&gt;Critique de la raison pure&lt;/em&gt;&lt;/a&gt; (1781), il réconcilie le rationalisme et l’empirisme : toute connaissance commence avec l’expérience, mais n’en dérive pas tout entière. L’esprit impose ses propres formes, l’espace, le temps et des catégories comme la causalité, à ce qu’il perçoit : c’est sa « révolution copernicienne ». Nous ne connaissons donc que les phénomènes, non les choses en soi, et la raison ne peut démontrer ni l’existence de Dieu ni l’immortalité de l’âme. Dans les &lt;a href="https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'impératif catégorique par le Précepteur"&gt;&lt;em&gt;Fondements de la métaphysique des mœurs&lt;/em&gt;&lt;/a&gt; (1785), il fonde une &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant"  title="La philosophie pratique de Kant de l'encyclopédie Wikipédia"&gt;philosophie pratique&lt;/a&gt; sur le devoir. &lt;a href="https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos"  title="La loi morale par Kosmos"&gt;La loi morale&lt;/a&gt; ne dépend ni des circonstances ni des conséquences : c’est un impératif catégorique. « Agis uniquement d’après la maxime qui fait que tu peux vouloir en même temps qu’elle devienne une loi universelle », et traite toujours l’humanité, en toi et en autrui, comme une fin, jamais simplement comme un moyen. La &lt;em&gt;Critique de la faculté de juger&lt;/em&gt; (1790) analyse le &lt;a href="https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume"  title="Faculté de jugement par la-philosophie.com"&gt;jugement&lt;/a&gt; de goût : le beau plaît universellement, sans intérêt et sans concept.&lt;/p&gt; &lt;p&gt;Pour Kant, les Lumières sont « la sortie de l’homme hors de l’état de minorité » : « Ose savoir ! » Il réclame la liberté de l’usage public de la raison, qui fonde &lt;a href="https://la-philosophie.com/espace-public-et-democratie"  title="Espace public par la-philosophie.com"&gt;l’espace public&lt;/a&gt;, et rêve d’une paix perpétuelle entre les nations.&lt;/p&gt;  &lt;audio controls title="Le monde: entre déterminisme et liberté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F67" s="47" t="inlineStr">
+      <c r="F68" s="47" t="inlineStr">
         <is>
           <t>WwrEOuVOkjk</t>
         </is>
       </c>
-      <c r="G67" s="49" t="inlineStr">
+      <c r="G68" s="49" t="inlineStr">
         <is>
           <t>"Emmanuel Kant: transformer le monde sans quitter sa ville" par Essences des Livres</t>
         </is>
       </c>
-      <c r="H67" s="49" t="inlineStr">
+      <c r="H68" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/kant-mini.webp</t>
         </is>
       </c>
-      <c r="I67" s="49" t="n"/>
-      <c r="J67" s="38" t="inlineStr">
+      <c r="I68" s="49" t="n"/>
+      <c r="J68" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K67" s="45" t="inlineStr">
+      <c r="K68" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="L67" s="46" t="inlineStr">
+      <c r="L68" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Criticisme ; Agnosticisme ; Anthropocentrisme ; Constructivisme ; Lumières ; Déontologisme</t>
         </is>
       </c>
-      <c r="M67" s="35" t="inlineStr">
+      <c r="M68" s="35" t="inlineStr">
         <is>
           <t>philosophe allemand qui a développé une théorie appelée « éthique kantienne ».</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P67">
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P68">
         <v>3</v>
       </c>
     </row>
-    <row r="68" ht="140.25" customHeight="1" s="39">
-      <c r="A68" s="47" t="n">
+    <row r="69" ht="140.25" customHeight="1" s="39">
+      <c r="A69" s="47" t="n">
         <v>1729</v>
       </c>
-      <c r="B68" s="47" t="inlineStr">
+      <c r="B69" s="47" t="inlineStr">
         <is>
           <t>1786</t>
         </is>
       </c>
-      <c r="C68" s="47" t="inlineStr">
+      <c r="C69" s="47" t="inlineStr">
         <is>
           <t>1729 – 1786</t>
         </is>
       </c>
-      <c r="D68" s="48" t="inlineStr">
+      <c r="D69" s="48" t="inlineStr">
         <is>
           <t>Moses MENDELSSOHN</t>
         </is>
       </c>
-      <c r="E68" s="49" t="inlineStr">
+      <c r="E69" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Moses_Mendelssohn"   title=" Wikipedia"&gt;Moses MENDELSSOHN&lt;/a&gt;  était un philosophe &lt;a href="https://www.youtube.com/watch?v=AvucqmG4Alk" title="Moses Mendelssohn et l’invention des Juifs allemands par Instituter of Jewish Studies"&gt;juif allemand des Lumières&lt;/a&gt;, né à Dessau et mort à Berlin, souvent considéré comme le "premier Juif allemand moderne" et l’une des grandes figures de  &lt;a href="https://www.youtube.com/watch?v=AaS7z6uRwWc" title="Le mythe de Moïse Mendelssohn par Efraim Palvanov"&gt;la Haskala, &lt;/a&gt; l’Aufklärung juive qui cherche à concilier fidélité au judaïsme et ouverture à la culture et à la philosophie modernes. &lt;/p&gt; &lt;p&gt; Il milite pour l’égalité civile des Juifs, la reconnaissance de leur spécificité au sein d’un État majoritairement chrétien, et la fin des discriminations légales et défend l’idée que les Juifs peuvent être pleinement intégrés comme citoyens allemands sans renoncer à leur religion. Il travaille sur la coexistence entre raison et foi, en soutenant que les vérités fondamentales de la religion sont accessibles à la raison humaine. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : -  "Phédon ou sur l’immortalité de l’âme" paru en 1767 qui  présente, sous forme de dialogues inspirés de Socrate, une défense de l’immortalité de l’âme et contribue à son surnom de "Socrate allemand". &lt; /p&gt; &lt;p&gt;  - "Jérusalem ou pouvoir religieux et judaïsme" en 1783 expose sa théorie de la séparation de l’Église et de l’État et sa vision d’un judaïsme compatible avec la liberté moderne. &lt;/p&gt; &lt;p&gt; - &lt;a href="https://laviedesidees.fr/Mendelssohn-Heures-matinales" title="Le dernier métaphysicien par la vie des idées"&gt;"Morgenstunden"&lt;/a&gt;, recueil de leçons sur l’existence de Dieu, synthétise sa position philosophique dans ses dernières années
 . &lt;/p&gt; &lt;p&gt;  Il est l’un des pionniers du judaïsme libéral et un des fondateurs de la modernité juive européenne, en cherchant l’intégration sans assimilation forcée et a  eu une influence durablement la philosophie juive et la pensée allemande, préparant le terrain pour des figures comme Heinrich Heine, Hermann Cohen, Franz Rosenzweig, Walter Benjamin ou Hannah Arendt. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F68" s="47" t="inlineStr">
+      <c r="F69" s="47" t="inlineStr">
         <is>
           <t>TJbV6JSLUeE</t>
         </is>
       </c>
-      <c r="G68" s="49" t="inlineStr">
+      <c r="G69" s="49" t="inlineStr">
         <is>
           <t>"Moses Mendelssohn: Enlightenment Pioneer" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H68" s="49" t="inlineStr">
+      <c r="H69" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mendelssohn-mini.webp</t>
         </is>
       </c>
-      <c r="I68" s="49" t="n"/>
-      <c r="J68" s="38" t="inlineStr">
+      <c r="I69" s="49" t="n"/>
+      <c r="J69" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K68" s="45" t="inlineStr">
+      <c r="K69" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="L68" s="46" t="inlineStr">
+      <c r="L69" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme ; Lumières ; Haskala</t>
         </is>
       </c>
-      <c r="M68" s="35" t="inlineStr">
+      <c r="M69" s="35" t="inlineStr">
         <is>
           <t>philosophe juif allemand moderne &amp; figure de la Haskala.</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="127.5" customHeight="1" s="39">
-      <c r="A69" s="47" t="n">
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="127.5" customHeight="1" s="39">
+      <c r="A70" s="47" t="n">
         <v>1729</v>
       </c>
-      <c r="B69" s="47" t="inlineStr">
+      <c r="B70" s="47" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="C69" s="47" t="inlineStr">
+      <c r="C70" s="47" t="inlineStr">
         <is>
           <t>1729 – 1797</t>
         </is>
       </c>
-      <c r="D69" s="48" t="inlineStr">
+      <c r="D70" s="48" t="inlineStr">
         <is>
           <t>Edmund BURKE</t>
         </is>
       </c>
-      <c r="E69" s="63" t="inlineStr">
+      <c r="E70" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Edmund_Burke"   title=" Wikipedia"&gt;Edmund BURKE&lt;/a&gt; était un philosophe et homme politique anglo-irlandais, considéré comme l'un des fondateurs du conservatisme moderne. Il s'opposa farouchement à la Révolution française, défendant l'évolution graduelle des institutions plutôt que les ruptures radicales. Il étudia au Trinity College avant de s'installer à Londres pour exercer le droit et entrer en politique. Député whig à la Chambre des communes de 1766 à 1794, il soutint l'indépendance américaine tout en critiquant les excès fiscaux britanniques. Sa célèbre Réflexions sur la Révolution de France (1790) alerta sur les dangers de la "multitude perverse" et du rejet des traditions. &lt;/p&gt; &lt;p&gt; Il  voyait la société comme un "partenariat entre les vivants, les morts et ceux qui ne sont pas encore nés", valorisant les &lt;a href="https://www.youtube.com/watch?v=az1n7gSaKFE" title="La tradition permet elle le changement  par la chaine de Velours"&gt;préjugés hérités &lt;/a&gt; comme bank de sagesse collective supérieure à la raison individuelle. Dans Recherches philosophiques sur l'origine de nos idées du sublime et du beau (1757), il distingue le sublime (lié à la douleur, à la terreur et à Dieu) du beau (lié au plaisir et à la société), influençant l'esthétique romantique. Il prônait l'amélioration progressive de la nature humaine imparfaite, sans table rase. &lt;/p&gt; &lt;p&gt; Surnommé "conservateur des Lumières", il inspira des penseurs comme Roger Scruton et reste une référence contre les utopies rationalistes. En France, il fut parfois taxé de réactionnaire, mais son libéralisme tempéré et son sens de la responsabilité des élites résonnent encore. &lt;/p&gt;  &lt;audio controls title="Les britaniques ; Burke et ses héritiers par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-10.12.2024-ITEMA_23958056-2024C48904S0345-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F69" s="47" t="inlineStr">
+      <c r="F70" s="47" t="inlineStr">
         <is>
           <t>PazGgn9Bdsc</t>
         </is>
       </c>
-      <c r="G69" s="49" t="inlineStr">
+      <c r="G70" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">"Burke : la critique de la révolution" par Histoire sans complexe
 </t>
         </is>
       </c>
-      <c r="H69" s="49" t="inlineStr">
+      <c r="H70" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/burke-mini.webp</t>
         </is>
       </c>
-      <c r="I69" s="49" t="n"/>
-      <c r="J69" s="55" t="inlineStr">
+      <c r="I70" s="49" t="n"/>
+      <c r="J70" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K69" s="45" t="inlineStr">
+      <c r="K70" s="45" t="inlineStr">
         <is>
           <t>politique ; esthetique</t>
         </is>
       </c>
-      <c r="L69" s="46" t="inlineStr">
+      <c r="L70" s="46" t="inlineStr">
         <is>
           <t>Conservatisme</t>
         </is>
       </c>
-      <c r="M69" s="35" t="inlineStr">
+      <c r="M70" s="35" t="inlineStr">
         <is>
           <t>philosophe anglo-irlandais considéré comme l'un des fondateurs du conservatisme moderne.</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="143.25" customHeight="1" s="39">
-      <c r="A70" s="47" t="n">
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="143.25" customHeight="1" s="39">
+      <c r="A71" s="47" t="n">
         <v>1729</v>
       </c>
-      <c r="B70" s="47" t="n">
+      <c r="B71" s="47" t="n">
         <v>1781</v>
       </c>
-      <c r="C70" s="47" t="inlineStr">
+      <c r="C71" s="47" t="inlineStr">
         <is>
           <t>1729 – 1781</t>
         </is>
       </c>
-      <c r="D70" s="48" t="inlineStr">
+      <c r="D71" s="48" t="inlineStr">
         <is>
           <t>Gotthold Ephraim LESSING</t>
         </is>
       </c>
-      <c r="E70" s="62" t="inlineStr">
+      <c r="E71" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing"   title=" Wikipedia"&gt;Gotthold Ephraim LESSING&lt;/a&gt; était un écrivain, dramaturge et philosophe allemand, figure centrale des Lumières allemandes qui défendit la tolérance religieuse, la raison critique et un christianisme épuré de dogmes orthodoxes. Il rejeta l'interprétation littérale de la Bible au profit d'une révélation progressive de l'humanité via la raison, influencé par Spinoza et Leibniz, tout en prônant une harmonie entre foi et savoir. &lt;/p&gt; &lt;p&gt; Fils de pasteur luthérien à Kamenz (Saxe), Lessing étudia la théologie et la médecine avant de se consacrer à la littérature à Berlin et Leipzig. Critique théâtral virulent, il combattit l'imitation des modèles français dans la Hamburgische Dramaturgie (1767-1769), plaidant pour un théâtre national allemand réaliste. Directeur de bibliothèque à Wolfenbüttel, il noua des amitiés avec Mendelssohn et Jacobi, déclenchant la querelle du panthéisme par ses sympathies spinozistes. &lt;/p&gt; &lt;p&gt; Ses Œuvres théâtrales majeures : - Miss Sara Sampson (1755) : Première tragédie bourgeoise allemande, explorant culpabilité et pardon. - Minna von Barnhelm (1767) : Comédie sur la réconciliation post-Sept Ans. - Emilia Galotti (1772) : Drame sur l'honneur et l'hypocrisie sociale. -  &lt;a href="https://www.radiofrance.fr/franceculture/nathan-le-sage-de-gotthold-ephraim-lessing-8205672" title="Nathan le sage de Lessing  par Radio France"&gt;Nathan le Sage (1779) &lt;/a&gt;  : Parabole tolérante où juif, chrétien et musulman incarnent la fraternité humaine via les trois anneaux (foi égale). &lt;/p&gt; &lt;p&gt; Dans L'Éducation du genre humain (1780), il voit l'histoire comme un processus divin d'éducation progressive : la révélation biblique n'est pas figée mais s'affine par la raison, menant à un "christianisme de raison". Laocoon (1766) distingue poésie (temps, action) et peinture (espace, corps). Son "fossé de Lessing" questionne : miracles historiques ne prouvent pas vérités éternelles. Il inspira Herder, Goethe et le romantisme par son relativisme esthétique et moral. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F70" s="47" t="inlineStr">
+      <c r="F71" s="47" t="inlineStr">
         <is>
           <t>4q_hrrQvNtA</t>
         </is>
       </c>
-      <c r="G70" s="49" t="inlineStr">
+      <c r="G71" s="49" t="inlineStr">
         <is>
           <t>« what did Gotthold Ephraim Lessing believe ? » Par Chronicles of Legends</t>
         </is>
       </c>
-      <c r="H70" s="58" t="inlineStr">
+      <c r="H71" s="58" t="inlineStr">
         <is>
           <t>https://laphilo.fr/pho/ghlessing-mini.webp</t>
         </is>
       </c>
-      <c r="I70" s="49" t="n"/>
-      <c r="J70" s="38" t="inlineStr">
+      <c r="I71" s="49" t="n"/>
+      <c r="J71" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K70" s="45" t="inlineStr">
+      <c r="K71" s="45" t="inlineStr">
         <is>
           <t>ethique ; esthetique</t>
         </is>
       </c>
-      <c r="L70" s="46" t="inlineStr">
+      <c r="L71" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Déisme ; Lumières</t>
         </is>
       </c>
-      <c r="M70" s="35" t="inlineStr">
+      <c r="M71" s="35" t="inlineStr">
         <is>
           <t>philosophe allemand &amp; figure centrale des Lumières allemandes.</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="131.25" customHeight="1" s="39">
-      <c r="A71" s="47" t="n">
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="131.25" customHeight="1" s="39">
+      <c r="A72" s="47" t="n">
         <v>1740</v>
       </c>
-      <c r="B71" s="47" t="inlineStr">
+      <c r="B72" s="47" t="inlineStr">
         <is>
           <t>1814</t>
         </is>
       </c>
-      <c r="C71" s="47" t="inlineStr">
+      <c r="C72" s="47" t="inlineStr">
         <is>
           <t>1740 - 1814</t>
         </is>
       </c>
-      <c r="D71" s="48" t="inlineStr">
+      <c r="D72" s="48" t="inlineStr">
         <is>
           <t>François de SADE</t>
         </is>
       </c>
-      <c r="E71" s="49" t="inlineStr">
+      <c r="E72" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donatien_Alphonse_Fran%C3%A7ois_de_Sade" title=" Wikipedia"&gt;Marquis François de SADE&lt;/a&gt; était un écrivain, philosophe Français surtout connu pour ses écrits provocateurs et controversés, qui abordent les thèmes de &lt;a href="https://www.youtube.com/watch?v=PJdCNc-0Ybk" title="Sade – justine ou les malheurs de la vertu par Kosmos"&gt;la sexualité, la violence et la morale&lt;/a&gt;. Il a passé une grande partie de sa vie en prison ou en exil en raison de ses opinions et de ses activités considérées comme immorales et illégales. &lt;/p&gt; &lt;p&gt;  Bien qu'il soit souvent associé à la pornographie et à la violence, il a exercé une influence importante sur la philosophie et la culture. Il a été considéré comme un précurseur du mouvement surréaliste, de &lt;a href="https://www.youtube.com/watch?v=KEh0vf7HCoI&amp;ab_channel=RayonPolar"   title="Donatien Alphonse François de Sade par RayonPolar"&gt; nombreux cinéastes&lt;/a&gt; tels que Brunel, Debordque, Bergma ont étaient inspirés et son travail qui a aussi été étudié par des philosophes tels que Michel Foucault et Gilles Deleuze. &lt;/p&gt; &lt;p&gt;  Sa pensée libertaire et sa critique de la société et de la religion ont également inspiré de nombreux mouvements politiques et sociaux.&lt;/p&gt; &lt;p&gt; 
 Son œuvre la plus célèbre, &lt;a href="https://fr.wikisource.org/wiki/Les_120_Journ%C3%A9es_de_Sodome"  title="Les 120 jours de Sodome par source Wikisource"&gt; "Les 120 Journées de Sodome" &lt;/a&gt; (également connue sous le nom de "La Philosophie dans le Boudoir"), est considérée comme l'un des premiers exemples de littérature érotique. Ce livre est aujourd'hui considéré comme extrêmement choquant en raison de sa description explicite de pratiques sexuelles déviantes et violentes. &lt;/p&gt; &lt;p&gt;  Son travail &lt;a href="https://www.youtube.com/watch?v=Qwfqw51JaGY" title=""L'apologie du mal" par le Précepteur"&gt;provocateur et choquant &lt;/a&gt;  a soulevé des questions importantes sur la sexualité, la morale et la liberté individuelle, qui continuent d'être pertinents aujourd'hui et on utilise le terme de 'sadique' aujourd'hui dans la langue Française.&lt;/p&gt; &lt;audio controls title="La vie en infamie du marquis de Sade par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-14.01.2019-ITEMA_21950194-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F71" s="47" t="inlineStr">
+      <c r="F72" s="47" t="inlineStr">
         <is>
           <t>SSL6icGS7gg</t>
         </is>
       </c>
-      <c r="G71" s="49" t="inlineStr">
+      <c r="G72" s="49" t="inlineStr">
         <is>
           <t>"Marquis de sade : l’homme le plus dépravé de l’histoire" par Les Ombres de l’histoire</t>
         </is>
       </c>
-      <c r="H71" s="49" t="inlineStr">
+      <c r="H72" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/sade-mini.webp</t>
         </is>
       </c>
-      <c r="I71" s="49" t="n"/>
-      <c r="J71" s="38" t="inlineStr">
+      <c r="I72" s="49" t="n"/>
+      <c r="J72" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K71" s="45" t="inlineStr">
+      <c r="K72" s="45" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="L71" s="46" t="inlineStr">
+      <c r="L72" s="46" t="inlineStr">
         <is>
           <t>Matérialisme</t>
         </is>
       </c>
-      <c r="M71" s="35" t="inlineStr">
+      <c r="M72" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses écrits provocateurs et controversés.</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="116.25" customHeight="1" s="39">
-      <c r="A72" s="47" t="n">
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="116.25" customHeight="1" s="39">
+      <c r="A73" s="47" t="n">
         <v>1741</v>
       </c>
-      <c r="B72" s="47" t="inlineStr">
+      <c r="B73" s="47" t="inlineStr">
         <is>
           <t>1801</t>
         </is>
       </c>
-      <c r="C72" s="47" t="inlineStr">
+      <c r="C73" s="47" t="inlineStr">
         <is>
           <t>1741 – 1801</t>
         </is>
       </c>
-      <c r="D72" s="48" t="inlineStr">
+      <c r="D73" s="48" t="inlineStr">
         <is>
           <t>Johann Kaspar LAVATER</t>
         </is>
       </c>
-      <c r="E72" s="63" t="inlineStr">
+      <c r="E73" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Kaspar_Lavater"  title=" Wikipedia"&gt;Johann Kaspar LAVATER&lt;/a&gt;  était un théologien, poète et philosophe suisse, connu surtout comme pionnier de  &lt;a href="https://fr.wikipedia.org/wiki/Physiognomonie"  title="Physiognomonie par Wikipedia"&gt; "la physiognomonie, &lt;/a&gt;  une pseudoscience liant traits du visage et caractère moral. Pasteur réformé à Zurich, il mêla mysticisme chrétien, irrationalisme et influences des Lumières tardives dans ses écrits. Né à Zurich dans une famille bourgeoise, il étudia la théologie et la philosophie au Collegium Carolinum sous Johann Jakob Bodmer. Ordonné en 1762, il devint diacre puis pasteur à l'église St-Pierre, tout en s'engageant contre la corruption locale, ce qui l'exila brièvement à Berlin. Ami de Goethe (dont la relation se tendit) et de Moses Mendelssohn, il fut blessé lors de l'invasion française de 1799 et mourut de ses blessures. &lt;/p&gt; &lt;p&gt; Sa grande œuvre, Physiognomische Fragmente zur Beförderung der Menschenkenntnis und Menschenliebe (1775-1778), postule que le visage révèle l'âme divine en l'homme, reliant esthétique, vertu et théologie. Influencé par l'Empfindsamkeit et le Sturm und Drang, il valorisait le sentiment sur la raison pure, explorant prophétie, miracles et palingénésie (résurrection). Critiqué par Lichtenberg pour son subjectivisme, il inspira poésie mystique et débats sur  &lt;a href="https://www.youtube.com/watch?v=LUxSlXIY-Zk"  title="Johann Kaspar Lavater par Grow Wise"&gt; "l'intériorité humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il  incarna un pont entre piétisme, sentimentalisme et romantisme naissant, influençant esthétique et psychologie populaire en Europe. Ses idées déclinèrent avec les progrès scientifiques, mais sa quête d'une connaissance intuitive de l'homme reste débattue. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F72" s="47" t="inlineStr">
+      <c r="F73" s="47" t="inlineStr">
         <is>
           <t>bSAtDI9S6hU</t>
         </is>
       </c>
-      <c r="G72" s="49" t="inlineStr">
+      <c r="G73" s="49" t="inlineStr">
         <is>
           <t>Johann Kaspar Lavater par See Hear Say Learn</t>
         </is>
       </c>
-      <c r="H72" s="49" t="inlineStr">
+      <c r="H73" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jklavater-mini.webp</t>
         </is>
       </c>
-      <c r="I72" s="49" t="n"/>
-      <c r="J72" s="38" t="inlineStr">
+      <c r="I73" s="49" t="n"/>
+      <c r="J73" s="38" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
       </c>
-      <c r="K72" s="45" t="inlineStr">
+      <c r="K73" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; spiritualite</t>
         </is>
       </c>
-      <c r="L72" s="46" t="inlineStr">
+      <c r="L73" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Spiritualisme</t>
         </is>
       </c>
-      <c r="M72" s="35" t="inlineStr">
+      <c r="M73" s="35" t="inlineStr">
         <is>
           <t>théologien, poète et philosophe suisse, connu comme pionnier de la physiognomonie.</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="158.25" customHeight="1" s="39">
-      <c r="A73" s="47" t="n">
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="158.25" customHeight="1" s="39">
+      <c r="A74" s="47" t="n">
         <v>1743</v>
       </c>
-      <c r="B73" s="47" t="inlineStr">
+      <c r="B74" s="47" t="inlineStr">
         <is>
           <t>1803</t>
         </is>
       </c>
-      <c r="C73" s="47" t="inlineStr">
+      <c r="C74" s="47" t="inlineStr">
         <is>
           <t>1743 – 1803</t>
         </is>
       </c>
-      <c r="D73" s="48" t="inlineStr">
+      <c r="D74" s="48" t="inlineStr">
         <is>
           <t>Louis-Claude de ST-MARTIN</t>
         </is>
       </c>
-      <c r="E73" s="62" t="inlineStr">
+      <c r="E74" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis-Claude_de_Saint-Martin"  title=" Wikipedia"&gt;Louis-Claude de ST-MARTIN&lt;/a&gt; dit &lt;a href="https://www.persee.fr/doc/dhs_0070-6760_1972_num_4_1_998"  title="Un philosophe toujours inconnu par Persée"&gt;« le Philosophe inconnu », &lt;/a&gt; était un philosophe et théosophe français, figure majeure du mysticisme chrétien au XVIIIe siècle. Issu d’une famille noble tourangelle, il chercha une voie spirituelle intérieure, rejetant les pratiques magiques pour privilégier la prière et la connaissance de soi comme moyens de réintégration divine.  &lt;/p&gt; &lt;p&gt; Militaire de formation, il rencontra en 1768 Martinez de Pasqually, fondateur de l’Ordre des Élus-Cohën, dont il devint un disciple fervent, assistant à ses rituels théurgiques. Après la mort de son maître en 1774, il s’éloigna des opérations extérieures, publiant anonymement des œuvres comme Des erreurs et de la vérité (1775) et Le Tableau naturel (1782).  Il a composé en 1790  &lt;a href="https://www.youtube.com/watch?v=4MFZG5b-lbI"  title="Le nouvel homme de St martin par Hermes Books Omega"&gt;« le nouvel homme » &lt;/a&gt; qui constitue une oeuvre majeure pour tous ceux qui s'intéressent à la pensée saint-martinienne et en premier chef pour les Martinistes, Vivant modestement comme secrétaire d’un magistrat à Paris, puis à Aulnay-la-Malherbe, il entretint une correspondance spirituelle avec des adeptes, influencé par Jakob Böhme et Swedenborg. &lt;/p&gt; &lt;p&gt; Pour lui, l’homme, issu d’une chute originelle, porte en lui une « pensée de Dieu » à développer par le libre arbitre et l’amour universel, menant à l’unité primordiale. Il opposait la raison matérialiste des Lumières à une révélation intérieure, voyant la société et l’individu comme des miroirs déformés de la Divinité à restaurer par la grâce et la vertu. Ses écrits insistent sur l’équilibre entre devoir moral, fraternité et intuition prophétique, préfigurant un ésotérisme non dogmatique. &lt;/p&gt; &lt;p&gt; Influençant Joseph de Maistre, Schelling ou René Guénon, il fonda une « école mystique » centrée sur la voie cardiaque, sans rituels extérieurs. Son rejet des utopies rationalistes et son appel à une régénération spirituelle résonnent encore dans la franc-maçonnerie  &lt;a href="https://fr.wikipedia.org/wiki/Martinisme"  title="Martinisme par Wikipedia"&gt; martiniste &lt;/a&gt; et la théosophie moderne. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F73" s="47" t="inlineStr">
+      <c r="F74" s="47" t="inlineStr">
         <is>
           <t>SJuwC2Mj59U</t>
         </is>
       </c>
-      <c r="G73" s="49" t="inlineStr">
+      <c r="G74" s="49" t="inlineStr">
         <is>
           <t>"Louis-Claude de SAINT-MARTIN et le martinisme" par promethee moi</t>
         </is>
       </c>
-      <c r="H73" s="49" t="inlineStr">
+      <c r="H74" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/martin-mini.webp</t>
-        </is>
-      </c>
-      <c r="I73" s="49" t="n"/>
-      <c r="J73" s="38" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K73" s="45" t="inlineStr">
-        <is>
-          <t>metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L73" s="46" t="inlineStr">
-        <is>
-          <t>Martinisme</t>
-        </is>
-      </c>
-      <c r="M73" s="35" t="inlineStr">
-        <is>
-          <t>philosophe français figure du mysticisme chrétien au XVIIIe siècle.</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="187.5" customHeight="1" s="39">
-      <c r="A74" s="47" t="n">
-        <v>1743</v>
-      </c>
-      <c r="B74" s="47" t="inlineStr">
-        <is>
-          <t>1794</t>
-        </is>
-      </c>
-      <c r="C74" s="47" t="inlineStr">
-        <is>
-          <t>1743 – 1794</t>
-        </is>
-      </c>
-      <c r="D74" s="48" t="inlineStr">
-        <is>
-          <t>Nicolas de CONDORCET</t>
-        </is>
-      </c>
-      <c r="E74" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet"  title=" Wikipedia"&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe, mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet féministe ? par Sud Radio"&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote.  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet et l’éloge de l’instruction par Culture philo"&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href="https://www.youtube.com/watch?v=avTI9GHZX1I"  title="Condorcet le paradoxe par Diable Positif"&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la "mathématique sociale", Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title="Nicolas de Condorcet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F74" s="47" t="inlineStr">
-        <is>
-          <t>2Acb4hqvw54</t>
-        </is>
-      </c>
-      <c r="G74" s="49" t="inlineStr">
-        <is>
-          <t>"Condorcet - Laissez-faire français " par Ecole de la Liberté</t>
-        </is>
-      </c>
-      <c r="H74" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/condorcet-mini.webp</t>
         </is>
       </c>
       <c r="I74" s="49" t="n"/>
@@ -5622,17 +5622,17 @@
       </c>
       <c r="K74" s="45" t="inlineStr">
         <is>
-          <t>politique ; epistemologie</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L74" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme ; Lumières ; Progressisme</t>
+          <t>Martinisme</t>
         </is>
       </c>
       <c r="M74" s="35" t="inlineStr">
         <is>
-          <t>philosophe français figure des Lumières et défenseur du progrès humain indéfini.</t>
+          <t>philosophe français figure du mysticisme chrétien au XVIIIe siècle.</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5641,110 +5641,110 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="148.5" customHeight="1" s="39">
+    <row r="75" ht="187.5" customHeight="1" s="39">
       <c r="A75" s="47" t="n">
         <v>1743</v>
       </c>
       <c r="B75" s="47" t="inlineStr">
         <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="C75" s="47" t="inlineStr">
+        <is>
+          <t>1743 – 1794</t>
+        </is>
+      </c>
+      <c r="D75" s="48" t="inlineStr">
+        <is>
+          <t>Nicolas de CONDORCET</t>
+        </is>
+      </c>
+      <c r="E75" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet"  title=" Wikipedia"&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe, mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet féministe ? par Sud Radio"&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote.  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet et l’éloge de l’instruction par Culture philo"&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href="https://www.youtube.com/watch?v=avTI9GHZX1I"  title="Condorcet le paradoxe par Diable Positif"&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la "mathématique sociale", Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title="Nicolas de Condorcet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F75" s="47" t="inlineStr">
+        <is>
+          <t>2Acb4hqvw54</t>
+        </is>
+      </c>
+      <c r="G75" s="49" t="inlineStr">
+        <is>
+          <t>"Condorcet - Laissez-faire français " par Ecole de la Liberté</t>
+        </is>
+      </c>
+      <c r="H75" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/condorcet-mini.webp</t>
+        </is>
+      </c>
+      <c r="I75" s="49" t="n"/>
+      <c r="J75" s="38" t="inlineStr">
+        <is>
+          <t>Française</t>
+        </is>
+      </c>
+      <c r="K75" s="45" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L75" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme ; Lumières ; Progressisme</t>
+        </is>
+      </c>
+      <c r="M75" s="35" t="inlineStr">
+        <is>
+          <t>philosophe français figure des Lumières et défenseur du progrès humain indéfini.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="148.5" customHeight="1" s="39">
+      <c r="A76" s="47" t="n">
+        <v>1743</v>
+      </c>
+      <c r="B76" s="47" t="inlineStr">
+        <is>
           <t>1819</t>
         </is>
       </c>
-      <c r="C75" s="47" t="inlineStr">
+      <c r="C76" s="47" t="inlineStr">
         <is>
           <t>1743 – 1819</t>
         </is>
       </c>
-      <c r="D75" s="48" t="inlineStr">
+      <c r="D76" s="48" t="inlineStr">
         <is>
           <t>Friedrich Heinrich JACOBI</t>
         </is>
       </c>
-      <c r="E75" s="63" t="inlineStr">
+      <c r="E76" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi"  title=" Wikipedia"&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href="https://fr.wikipedia.org/wiki/Nihilisme"  title="Nihilisme par Wikipedia"&gt; nihilisme &lt;/a&gt; et au &lt;a href="https://fr.wikipedia.org/wiki/Panth%C3%A9isme"  title="Panthéisme par Wikipedia"&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse "querelle du panthéisme" en révélant que Lessing s'était  &lt;a href="https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321"  title="Jacobi et Spinoza par Persée"&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu. &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du "rien ne sort du néant") de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un "saut de la foi" hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. - David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. - Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F75" s="47" t="inlineStr">
+      <c r="F76" s="47" t="inlineStr">
         <is>
           <t>1omDmffUbaw</t>
         </is>
       </c>
-      <c r="G75" s="49" t="inlineStr">
+      <c r="G76" s="49" t="inlineStr">
         <is>
           <t>"Friedrich Heinrich Jacobi: Challenging Enlightenment Ideas" par VISPHILO</t>
         </is>
       </c>
-      <c r="H75" s="49" t="inlineStr">
+      <c r="H76" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fhjacobi-mini.webp</t>
-        </is>
-      </c>
-      <c r="I75" s="49" t="n"/>
-      <c r="J75" s="38" t="inlineStr">
-        <is>
-          <t>Allemande</t>
-        </is>
-      </c>
-      <c r="K75" s="45" t="inlineStr">
-        <is>
-          <t>metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L75" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spiritualisme ; Irrationalisme</t>
-        </is>
-      </c>
-      <c r="M75" s="35" t="inlineStr">
-        <is>
-          <t>philosophe juif allemand critique majeur du rationalisme des Lumières.</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="155.25" customHeight="1" s="39">
-      <c r="A76" s="47" t="n">
-        <v>1744</v>
-      </c>
-      <c r="B76" s="47" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="C76" s="47" t="inlineStr">
-        <is>
-          <t>1744 – 1803</t>
-        </is>
-      </c>
-      <c r="D76" s="48" t="inlineStr">
-        <is>
-          <t>Johann Gottfried HERDER</t>
-        </is>
-      </c>
-      <c r="E76" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Gottfried_von_Herder"  title=" Wikipedia"&gt;Johann Gottfried HERDER&lt;/a&gt; était un philosophe  et écrivain allemand souvent considéré comme l’un des pères de la philosophie de la culture et de &lt;a href="https://www.jdarriulat.net/Introductionphiloesth/PhiloModerne/Herder.html"  title="INTRODUCTION A LA PHILOSOPHIE ESTHETIQUE par jdarriulat"&gt;l’idée moderne &lt;/a&gt; de "nation". Son œuvre se situe à la croisée des Lumières et du premier romantisme allemand. Il refuse l’idée d’un progrès linéaire et uniforme de l’humanité vers une &lt;a href="https://www.youtube.com/watch?v=Y8l9aJhT76U" title="Johann Gottfried Herder par Greatest Minds in History"&gt;seule forme de civilisation&lt;/a&gt;, telle qu’on la trouve chez certains auteurs des Lumières. Chaque époque et chaque peuple possède, selon lui, une valeur propre qui doit être comprise de l’intérieur et non jugée à l’aune d’un modèle abstrait. Il propose une philosophie de l’histoire "humanitaire" : l’histoire est le développement de l’humanité en tant que telle, dans sa pluralité de formes, sous le signe de la culture, de la liberté et de la perfectibilité.  &lt;/p&gt; &lt;p&gt; Il attribue au langage un rôle constitutif dans la formation de la pensée humaine, contre l’idée d’une raison pure préexistante à toute expérience linguistique. La raison ne précède pas le langage, elle se forme à travers lui, si bien que connaître, c’est toujours déjà interpréter à l’aide de mots et de symboles historiques. Il s’intéresse à l’origine des langues et parle d’un "roman des langues" pour décrire l’histoire par laquelle les hommes passent d’un stade prélinguistique à des formes complexes de communication et de socialisation. &lt;/p&gt; &lt;p&gt; Son œuvre est très abondante, mais quelques titres structurent sa pensée. On cite notamment : "Auch eine Philosophie der Geschichte zur Bildung der Menschheit" paru en 1774 et surtout &lt;a href="https://de.wikipedia.org/wiki/Ideen_zur_Philosophie_der_Geschichte_der_Menschheit" title="Ideen zur Philosophie der Geschichte der Menschheit par wikipedia"&gt;"Ideen zur Philosophie der Geschichte der Menschheit"&lt;/a&gt; qui proposent une vaste vision historico‑culturelle de l’humanité. &lt;/p&gt; &lt;p&gt;   À la fin de sa vie, il polémique avec Kant dans la "Métacritique de la critique de la raison pure" et développe une esthétique originale dans "Kalligone".  Son insistance sur la culture, la langue et le peuple marquera durablement les théories de la nation, de l’anthropologie culturelle et de la philosophie de l’histoire. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F76" s="47" t="inlineStr">
-        <is>
-          <t>AWvhAGgW1v8</t>
-        </is>
-      </c>
-      <c r="G76" s="49" t="inlineStr">
-        <is>
-          <t>"Johann Gottfried Herder: Revolutionizing Political Thought" par VIS PHILO</t>
-        </is>
-      </c>
-      <c r="H76" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/herder-mini.webp</t>
         </is>
       </c>
       <c r="I76" s="49" t="n"/>
@@ -5755,17 +5755,17 @@
       </c>
       <c r="K76" s="45" t="inlineStr">
         <is>
-          <t>epistemologie ; esthetique</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L76" s="46" t="inlineStr">
         <is>
-          <t>Romantisme</t>
+          <t xml:space="preserve">Spiritualisme ; Irrationalisme</t>
         </is>
       </c>
       <c r="M76" s="35" t="inlineStr">
         <is>
-          <t>philosophe allemand père de la philosophie de la culture et de l’idée moderne de nation.</t>
+          <t>philosophe juif allemand critique majeur du rationalisme des Lumières.</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5774,9 +5774,9 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="112.5" customHeight="1" s="39">
+    <row r="77" ht="155.25" customHeight="1" s="39">
       <c r="A77" s="47" t="n">
-        <v>1747</v>
+        <v>1744</v>
       </c>
       <c r="B77" s="47" t="inlineStr">
         <is>
@@ -5785,32 +5785,32 @@
       </c>
       <c r="C77" s="47" t="inlineStr">
         <is>
-          <t>1747 – 1803</t>
+          <t>1744 – 1803</t>
         </is>
       </c>
       <c r="D77" s="48" t="inlineStr">
         <is>
-          <t>Marcus HERZ</t>
-        </is>
-      </c>
-      <c r="E77" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcus_Herz"  title=" Wikipedia"&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Emmanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2" title="Kant, Lettre à Marcus Herz du 21 février 1772 par Persée"&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la "révolution copernicienne"), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent "Betrachtungen aus der spekulativen Weltweisheit"  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et "Versuch über den Geschmack" en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; </t>
+          <t>Johann Gottfried HERDER</t>
+        </is>
+      </c>
+      <c r="E77" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Gottfried_von_Herder"  title=" Wikipedia"&gt;Johann Gottfried HERDER&lt;/a&gt; était un philosophe  et écrivain allemand souvent considéré comme l’un des pères de la philosophie de la culture et de &lt;a href="https://www.jdarriulat.net/Introductionphiloesth/PhiloModerne/Herder.html"  title="INTRODUCTION A LA PHILOSOPHIE ESTHETIQUE par jdarriulat"&gt;l’idée moderne &lt;/a&gt; de "nation". Son œuvre se situe à la croisée des Lumières et du premier romantisme allemand. Il refuse l’idée d’un progrès linéaire et uniforme de l’humanité vers une &lt;a href="https://www.youtube.com/watch?v=Y8l9aJhT76U" title="Johann Gottfried Herder par Greatest Minds in History"&gt;seule forme de civilisation&lt;/a&gt;, telle qu’on la trouve chez certains auteurs des Lumières. Chaque époque et chaque peuple possède, selon lui, une valeur propre qui doit être comprise de l’intérieur et non jugée à l’aune d’un modèle abstrait. Il propose une philosophie de l’histoire "humanitaire" : l’histoire est le développement de l’humanité en tant que telle, dans sa pluralité de formes, sous le signe de la culture, de la liberté et de la perfectibilité.  &lt;/p&gt; &lt;p&gt; Il attribue au langage un rôle constitutif dans la formation de la pensée humaine, contre l’idée d’une raison pure préexistante à toute expérience linguistique. La raison ne précède pas le langage, elle se forme à travers lui, si bien que connaître, c’est toujours déjà interpréter à l’aide de mots et de symboles historiques. Il s’intéresse à l’origine des langues et parle d’un "roman des langues" pour décrire l’histoire par laquelle les hommes passent d’un stade prélinguistique à des formes complexes de communication et de socialisation. &lt;/p&gt; &lt;p&gt; Son œuvre est très abondante, mais quelques titres structurent sa pensée. On cite notamment : "Auch eine Philosophie der Geschichte zur Bildung der Menschheit" paru en 1774 et surtout &lt;a href="https://de.wikipedia.org/wiki/Ideen_zur_Philosophie_der_Geschichte_der_Menschheit" title="Ideen zur Philosophie der Geschichte der Menschheit par wikipedia"&gt;"Ideen zur Philosophie der Geschichte der Menschheit"&lt;/a&gt; qui proposent une vaste vision historico‑culturelle de l’humanité. &lt;/p&gt; &lt;p&gt;   À la fin de sa vie, il polémique avec Kant dans la "Métacritique de la critique de la raison pure" et développe une esthétique originale dans "Kalligone".  Son insistance sur la culture, la langue et le peuple marquera durablement les théories de la nation, de l’anthropologie culturelle et de la philosophie de l’histoire. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F77" s="47" t="inlineStr">
         <is>
-          <t>vKkBVZaoOs4</t>
+          <t>AWvhAGgW1v8</t>
         </is>
       </c>
       <c r="G77" s="49" t="inlineStr">
         <is>
-          <t>"Marcus HERZ" par WikiTubia</t>
+          <t>"Johann Gottfried Herder: Revolutionizing Political Thought" par VIS PHILO</t>
         </is>
       </c>
       <c r="H77" s="49" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/herz-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/herder-mini.webp</t>
         </is>
       </c>
       <c r="I77" s="49" t="n"/>
@@ -5821,726 +5821,739 @@
       </c>
       <c r="K77" s="45" t="inlineStr">
         <is>
+          <t>epistemologie ; esthetique</t>
+        </is>
+      </c>
+      <c r="L77" s="46" t="inlineStr">
+        <is>
+          <t>Romantisme</t>
+        </is>
+      </c>
+      <c r="M77" s="35" t="inlineStr">
+        <is>
+          <t>philosophe allemand père de la philosophie de la culture et de l’idée moderne de nation.</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="112.5" customHeight="1" s="39">
+      <c r="A78" s="47" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B78" s="47" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="C78" s="47" t="inlineStr">
+        <is>
+          <t>1747 – 1803</t>
+        </is>
+      </c>
+      <c r="D78" s="48" t="inlineStr">
+        <is>
+          <t>Marcus HERZ</t>
+        </is>
+      </c>
+      <c r="E78" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcus_Herz"  title=" Wikipedia"&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Emmanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2" title="Kant, Lettre à Marcus Herz du 21 février 1772 par Persée"&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la "révolution copernicienne"), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent "Betrachtungen aus der spekulativen Weltweisheit"  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et "Versuch über den Geschmack" en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F78" s="47" t="inlineStr">
+        <is>
+          <t>vKkBVZaoOs4</t>
+        </is>
+      </c>
+      <c r="G78" s="49" t="inlineStr">
+        <is>
+          <t>"Marcus HERZ" par WikiTubia</t>
+        </is>
+      </c>
+      <c r="H78" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/herz-mini.webp</t>
+        </is>
+      </c>
+      <c r="I78" s="49" t="n"/>
+      <c r="J78" s="38" t="inlineStr">
+        <is>
+          <t>Allemande</t>
+        </is>
+      </c>
+      <c r="K78" s="45" t="inlineStr">
+        <is>
           <t>epistemologie ; metaphysique</t>
         </is>
       </c>
-      <c r="L77" s="46" t="inlineStr">
+      <c r="L78" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Criticisme ; Haskala</t>
         </is>
       </c>
-      <c r="M77" s="35" t="inlineStr">
+      <c r="M78" s="35" t="inlineStr">
         <is>
           <t>philosophe juif allemand, disciple de Kant &amp; figure des Lumières berlinoises.</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="178.5" customHeight="1" s="39">
-      <c r="A78" s="47" t="n">
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="178.5" customHeight="1" s="39">
+      <c r="A79" s="47" t="n">
         <v>1748</v>
       </c>
-      <c r="B78" s="47" t="inlineStr">
+      <c r="B79" s="47" t="inlineStr">
         <is>
           <t>1832</t>
         </is>
       </c>
-      <c r="C78" s="47" t="inlineStr">
+      <c r="C79" s="47" t="inlineStr">
         <is>
           <t>1748 - 1832</t>
         </is>
       </c>
-      <c r="D78" s="48" t="inlineStr">
+      <c r="D79" s="48" t="inlineStr">
         <is>
           <t>Jérémy BENTHAM</t>
         </is>
       </c>
-      <c r="E78" s="60" t="inlineStr">
+      <c r="E79" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jeremy_Bentham"  title=" Wikipedia"&gt;Jérémy BENTHAM&lt;/a&gt; était un philosophe Anglais, économiste et réformateur social. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs de &lt;a  href="https://www.youtube.com/watch?v=yCDOVcvNYpY&amp;t=2s&amp;ab_channel=AlainBajom%C3%A9e"  title="L'utilitarisme par Alain Bajomée"&gt;l'utilitarisme&lt;/a&gt;, une doctrine éthique qui affirme que la meilleure action est celle qui produit le plus grand bien-être pour le plus grand nombre de personnes possible. Selon lui, la nature humaine est motivée par la recherche du &lt;a  href="https://www.youtube.com/watch?v=2c6jMZr6-Jc&amp;ab_channel=LePr%C3%A9cepteur"  title="Sommes nous tous égoiste par Le Précepteur"&gt;plaisir personnel&lt;/a&gt; et l'évitement de la douleur, et donc la recherche du bonheur est la fin ultime de toute action. &lt;/p&gt; &lt;p&gt; Bentham rejette les fondements moraux traditionnels (coutume, religion, devoir abstrait) au profit de l'utilité : une loi ou action est bonne si elle augmente le bonheur net de la société, somme des bonheurs individuels. Il distingue plaisirs quantifiables (sans hiérarchie entre supérieurs ou inférieurs) et prône un État interventionniste pour protéger les libertés, redistribuer les richesses (taxe progressive sur héritages) et encourager la croissance économique et démographique. &lt;/p&gt; &lt;p&gt; Il a également proposé le principe de l'égalité morale, selon lequel chaque individu compte pour un dans le calcul du bonheur global, ce qui signifie que chaque vie a la même importance morale. Cela a conduit Bentham à être un défenseur de l'égalité des  &lt;a  href="https://www.youtube.com/watch?v=xJDQu0OLwME&amp;ab_channel=MonsieurPhi"  title="L'homosexualité par Mr Phi"&gt;droits pour tous&lt;/a&gt;, y compris les femmes et les minorités. &lt;/p&gt; &lt;p&gt;Il a été un critique de la philosophie morale traditionnelle, qui était souvent basée sur des notions abstraites telles que la vertu et le devoir. Il a plutôt cherché à fonder &lt;a  href="https://www.youtube.com/watch?v=mvamwoVi1KE"  title="Bentham, qu’est ce l’utilitarisme par Le Précepteur"&gt; l'éthique sur des principes empiriques, &lt;/a&gt; en se basant sur des observations et des expériences concrètes. Il  appliqua sa philosophie à la réforme pénale (contre la peine de mort arbitraire), juridique (code pénal rationnel), économique (rôle de l'État dans sécurité et subsistance) et sociale (éducation, santé publique). Critiqué pour son hédonisme mécanique, il influença Mill, le libéralisme social et les politiques publiques modernes.    &lt;/p&gt;  &lt;audio controls title="Dans la peau de Jeremy Bentham par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10081-29.01.2018-ITEMA_21570270-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F78" s="47" t="inlineStr">
+      <c r="F79" s="47" t="inlineStr">
         <is>
           <t>mvamwoVi1KE</t>
         </is>
       </c>
-      <c r="G78" s="49" t="inlineStr">
+      <c r="G79" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">"L'utilitarisme" par Le Précepteur</t>
         </is>
       </c>
-      <c r="H78" s="49" t="inlineStr">
+      <c r="H79" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bentham-mini.webp</t>
         </is>
       </c>
-      <c r="I78" s="49" t="n"/>
-      <c r="J78" s="55" t="inlineStr">
+      <c r="I79" s="49" t="n"/>
+      <c r="J79" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K78" s="45" t="inlineStr">
+      <c r="K79" s="45" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="L78" s="46" t="inlineStr">
+      <c r="L79" s="46" t="inlineStr">
         <is>
           <t>Utilitarisme ; Conséquentialisme</t>
         </is>
       </c>
-      <c r="M78" s="35" t="inlineStr">
+      <c r="M79" s="35" t="inlineStr">
         <is>
           <t>philosophe et économiste anglais considéré comme fondateur de l'Utilitarisme.</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="141.75" customHeight="1" s="39">
-      <c r="A79" s="47" t="n">
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="141.75" customHeight="1" s="39">
+      <c r="A80" s="47" t="n">
         <v>1750</v>
       </c>
-      <c r="B79" s="47" t="inlineStr">
+      <c r="B80" s="47" t="inlineStr">
         <is>
           <t>1834</t>
         </is>
       </c>
-      <c r="C79" s="47" t="inlineStr">
+      <c r="C80" s="47" t="inlineStr">
         <is>
           <t>1750 – 1834</t>
         </is>
       </c>
-      <c r="D79" s="48" t="inlineStr">
+      <c r="D80" s="48" t="inlineStr">
         <is>
           <t>David FRIEDLÄNDER</t>
         </is>
       </c>
-      <c r="E79" s="63" t="inlineStr">
+      <c r="E80" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Friedl%C3%A4nder"  title=" Wikipedia"&gt;David FRIEDLÄNDER&lt;/a&gt;  était un intellectuel, marchand et réformateur juif allemand, disciple de Moses Mendelssohn, plus connu comme pionnier de l'Haskalah (Lumières juives) et de la  &lt;a  href="https://www.persee.fr/doc/reval_0035-0974_1973_num_5_3_1989"  title="D Friedlander et la réforme des communaités juives de prusse par Persée"&gt; réforme religieuse &lt;/a&gt; que comme philosophe académique strict. Il prôna l'émancipation des Juifs par l'assimilation culturelle et une dédogmatisation du judaïsme, fusionnant rationalisme des Lumières et monothéisme mosaïque originel contre les rituels "superstitieux". &lt;/p&gt; &lt;p&gt; Né à Königsberg, il s'installa à Berlin en 1770, fonda une usine de soie et intégra l'élite juive éclairée via son mariage avec la fille du banquier Daniel Itzig. Après la mort de Mendelssohn (1786), il mena la Haskalah berlinoise : création de la Chevrat Chinuch Ne’arim (école juive libre en 1778), traductions de prières en allemand, et plaidoyers pour l'égalité civile. Premier conseiller municipal juif à Berlin, il lutta contre les discriminations prussiennes. &lt;/p&gt; &lt;p&gt; Il rejetait le Talmud et les rites comme "œuvres de sainteté, verbiage et futilités", défendant un judaïsme "pur" : monothéisme rationnel commun aux religions abrahamiques, sans dogmes christologiques ni observances contraignantes. Dans son Sendschreiben anonyme (1799) à l'ecclésiastique Wilhelm Teller, il proposa une union judéo-protestante déiste – baptême symbolique sans trinité, en échange d'émancipation –, vu comme opportuniste mais innovant pour le judaïsme réformé naissant. Il resta juif par fidélité au "monothéisme mosaïque idéal", contrairement à sa famille convertie. &lt;/p&gt; &lt;p&gt; Précurseur du judaïsme réformé et de l'assimilation prussienne, Friedländer incarna le dilemme post-mendelssohnien : identité juive face à l'universalisme. Critiqué pour pragmatisme, il influença les réformes liturgiques et débats sur l'émancipation, bien que son projet fusionnel échouât face au romantisme montant. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F79" s="47" t="n"/>
-      <c r="G79" s="49" t="n"/>
-      <c r="H79" s="49" t="inlineStr">
+      <c r="F80" s="47" t="n"/>
+      <c r="G80" s="49" t="n"/>
+      <c r="H80" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/dfriedlander-mini.webp</t>
         </is>
       </c>
-      <c r="I79" s="58" t="inlineStr">
+      <c r="I80" s="58" t="inlineStr">
         <is>
           <t>https://laphilo.fr/photo/dfriedlander.webp</t>
         </is>
       </c>
-      <c r="J79" s="38" t="inlineStr">
+      <c r="J80" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K79" s="45" t="inlineStr">
+      <c r="K80" s="45" t="inlineStr">
         <is>
           <t>ethique ; spiritualite</t>
         </is>
       </c>
-      <c r="L79" s="46" t="inlineStr">
+      <c r="L80" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme ; Haskala</t>
         </is>
       </c>
-      <c r="M79" s="35" t="inlineStr">
+      <c r="M80" s="35" t="inlineStr">
         <is>
           <t>philosophe juif allemand plus connu comme pionnier de l'Haskalah.</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="157.5" customHeight="1" s="39">
-      <c r="A80" s="47" t="n">
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="157.5" customHeight="1" s="39">
+      <c r="A81" s="47" t="n">
         <v>1753</v>
       </c>
-      <c r="B80" s="47" t="inlineStr">
+      <c r="B81" s="47" t="inlineStr">
         <is>
           <t>1821</t>
         </is>
       </c>
-      <c r="C80" s="47" t="inlineStr">
+      <c r="C81" s="47" t="inlineStr">
         <is>
           <t>1753 – 1821</t>
         </is>
       </c>
-      <c r="D80" s="48" t="inlineStr">
+      <c r="D81" s="48" t="inlineStr">
         <is>
           <t>Joseph de MAISTRE</t>
         </is>
       </c>
-      <c r="E80" s="58" t="inlineStr">
+      <c r="E81" s="58" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joseph_de_Maistre"  title=" Wikipedia"&gt;Joseph de MAISTRE&lt;/a&gt; était un philosophe, écrivain et diplomate savoyard, figure majeure de la contre-révolution et critique virulent des Lumières et de la Révolution française. Considéré comme un père de la pensée conservatrice moderne, il défend une vision organique de la société, hiérarchique et divinement ordonnée, où l'autorité monarchique et religieuse prime sur les idées contractualistes et individualistes. &lt;/p&gt; &lt;p&gt;  Pour lui, la Révolution française est un &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1989_num_1_2_1393" title="Sacré et sacrifice dans la pensée de Joseph de Maistre par Persée"&gt;châtiment providentiel &lt;/a&gt; des excès des philosophes des Lumières, punissant l'athéisme et le rationalisme par la Terreur. Les sociétés ne naissent pas d'un contrat rationnel (comme chez Rousseau), mais d'une autorité divine imposée d'en haut; l'individu abstrait n'existe pas, il est façonné par la tradition et l'État.  Il prône une monarchie absolue et l'autorité suprême du Pape pour unifier l'Europe spirituellement et temporellement. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures sont : - "Considérations sur la France" paru en 1797 : Interprétation providentialiste de la Révolution comme mission divine de la France. - "Essai sur le principe générateur des constitutions" paru en 1809 :  &lt;a href="https://www.youtube.com/watch?v=oPEzOiEdrNE"  title=" L'oecuménisme de Joseph de Maistre par BAGLIS TV"&gt;Les constitutions &lt;/a&gt; viennent de Dieu, non de la raison humaine et - "Soirées de Saint-Pétersbourg"  en1821, posthume : Théodicée justifiant le mal (guerre, sacrifice) comme partie du plan divin. &lt;/p&gt; &lt;p&gt; Il a eu une influence durablement le conservatisme, le romantisme contre-révolutionnaire et des penseurs comme Donoso Cortés, tout en étant critiqué pour son apologie de la violence. Sa pensée hiérarchique et anti-individualiste reste débattue face aux idéaux démocratiques modernes. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Troisième penseur, Joseph de Maistre. par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-26.10.2011-ITEMA_20317797-2011C12410S0299-NET_F022382B-0B64-4C5C-B335-284B201C884D_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F80" s="47" t="inlineStr">
+      <c r="F81" s="47" t="inlineStr">
         <is>
           <t>suyM7vu194w</t>
         </is>
       </c>
-      <c r="G80" s="49" t="inlineStr">
+      <c r="G81" s="49" t="inlineStr">
         <is>
           <t>"La défense des préjugés contre l’universalisme abstrait (Joseph de Maistre)" par Ego Non</t>
         </is>
       </c>
-      <c r="H80" s="49" t="inlineStr">
+      <c r="H81" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/maistre-mini.webp</t>
         </is>
       </c>
-      <c r="I80" s="49" t="n"/>
-      <c r="J80" s="38" t="inlineStr">
+      <c r="I81" s="49" t="n"/>
+      <c r="J81" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K80" s="45" t="inlineStr">
+      <c r="K81" s="45" t="inlineStr">
         <is>
           <t>politique ; spiritualite</t>
         </is>
       </c>
-      <c r="L80" s="46" t="inlineStr">
+      <c r="L81" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Conservatisme ; Martinisme</t>
         </is>
       </c>
-      <c r="M80" s="35" t="inlineStr">
+      <c r="M81" s="35" t="inlineStr">
         <is>
           <t>philosophe français figure de la contre-révolution &amp; critique des Lumières.</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="148.5" customHeight="1" s="39">
-      <c r="A81" s="47" t="n">
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="148.5" customHeight="1" s="39">
+      <c r="A82" s="47" t="n">
         <v>1754</v>
       </c>
-      <c r="B81" s="47" t="inlineStr">
+      <c r="B82" s="47" t="inlineStr">
         <is>
           <t>1840</t>
         </is>
       </c>
-      <c r="C81" s="47" t="inlineStr">
+      <c r="C82" s="47" t="inlineStr">
         <is>
           <t>1754 – 1840</t>
         </is>
       </c>
-      <c r="D81" s="48" t="inlineStr">
+      <c r="D82" s="48" t="inlineStr">
         <is>
           <t>Louis BONALD</t>
         </is>
       </c>
-      <c r="E81" s="63" t="inlineStr">
+      <c r="E82" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_de_Bonald"  title=" Wikipedia"&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href="https://fr.wikipedia.org/wiki/Tradition_primordiale"  title=" Tradition Primordiale de Maistre par Wikipedia "&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. - Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. - Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href="https://www.youtube.com/watch?v=WMB9kethTWIe"  title=" Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations "&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href="https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral"  title=" Maurrassisme par Wikipedia "&gt; maurrassisme, &lt;a&gt; voyant la France comme "nation-pilote" pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant. &lt;/p&gt;
 //</t>
         </is>
       </c>
-      <c r="F81" s="47" t="inlineStr">
+      <c r="F82" s="47" t="inlineStr">
         <is>
           <t>zJeETVwu1Zo</t>
         </is>
       </c>
-      <c r="G81" s="49" t="inlineStr">
+      <c r="G82" s="49" t="inlineStr">
         <is>
           <t>"L'Homme et la Société (Louis de Bonald)" par Ego Non</t>
         </is>
       </c>
-      <c r="H81" s="49" t="inlineStr">
+      <c r="H82" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bonald-mini.webp</t>
         </is>
       </c>
-      <c r="I81" s="49" t="n"/>
-      <c r="J81" s="38" t="inlineStr">
+      <c r="I82" s="49" t="n"/>
+      <c r="J82" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K81" s="45" t="inlineStr">
+      <c r="K82" s="45" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="L81" s="46" t="inlineStr">
+      <c r="L82" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Conservatisme</t>
         </is>
       </c>
-      <c r="M81" s="35" t="inlineStr">
+      <c r="M82" s="35" t="inlineStr">
         <is>
           <t>philosophe et théoricien contre-révolutionnaire français, chef de file du traditionalisme.</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="135" customHeight="1" s="39">
-      <c r="A82" s="34" t="n">
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="135" customHeight="1" s="39">
+      <c r="A83" s="34" t="n">
         <v>1754</v>
       </c>
-      <c r="B82" s="34" t="n">
+      <c r="B83" s="34" t="n">
         <v>1836</v>
       </c>
-      <c r="C82" s="34" t="inlineStr">
+      <c r="C83" s="34" t="inlineStr">
         <is>
           <t>1754 – 1836</t>
         </is>
       </c>
-      <c r="D82" s="35" t="inlineStr">
+      <c r="D83" s="35" t="inlineStr">
         <is>
           <t>Destutt de TRACY</t>
         </is>
       </c>
-      <c r="E82" s="35" t="inlineStr">
+      <c r="E83" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine_Destutt_de_Tracy"  title=" Wikipedia"&gt;Destutt de TRACY&lt;/a&gt; était un philosophe et idéologue français, fondateur et théoricien principal du courant philosophique des Idéologues. Né Antoine Louis Claude Destutt, comte de Tracy, dans une famille noble auvergnate, il fit une carrière militaire avant de se consacrer à la philosophie après son emprisonnement pendant la Terreur. Membre de l'Institut national et de l'Académie française, il joua un rôle central dans la vie intellectuelle française sous le Directoire et le Consulat. &lt;/p&gt; &lt;p&gt; Sa contribution majeure est la création de l'« idéologie » comme science des idées. Dans ses &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=DAz6QsBdeyg"  title="Destrutt de DRACYi par Wikipedia Fan"&gt;Éléments d'idéologie &lt;/a&gt; &lt;/em&gt; (5 volumes, 1801-1815), il cherche à fonder une science générale des idées qui analyserait leur formation à partir des sensations et des signes. S'inscrivant dans la tradition sensualiste de Condillac, il développe une sémiologie et une grammaire générale visant à purifier le langage de ses ambiguïtés et à fonder les sciences humaines sur des bases empiriques solides. Son projet était d'édifier une « science des sciences » qui servirait de fondement à l'enseignement et à la réforme sociale. &lt;/p&gt; &lt;p&gt; Sa &lt;em&gt;Logique&lt;/em&gt; et son &lt;em&gt;Commentaire sur l'Esprit des Lois de Montesquieu&lt;/em&gt; (1811) témoignent de son intérêt pour la philosophie politique libérale. Jefferson, qui admirait sa pensée, fit traduire son &lt;em&gt;Traité de la volonté&lt;/em&gt; en anglais. Ironiquement, le terme même d'« idéologie » qu'il avait forgé fut retourné contre lui par Napoléon, qui qualifiait les Idéologues d'esprits abstraits et dangereux. Marx reprit ensuite ce terme dans un sens radicalement différent. Destutt de Tracy reste une figure essentielle pour comprendre l'émergence des sciences humaines en France. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F82" s="47" t="inlineStr">
+      <c r="F83" s="47" t="inlineStr">
         <is>
           <t>n69ITkX9DMU</t>
         </is>
       </c>
-      <c r="G82" s="49" t="inlineStr">
+      <c r="G83" s="49" t="inlineStr">
         <is>
           <t>« l’influence de Destutt de Tracy » par Ecole de la Liberté</t>
         </is>
       </c>
-      <c r="H82" s="35" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/destuttdetracy-mini.webp</t>
         </is>
       </c>
-      <c r="J82" s="38" t="inlineStr">
+      <c r="J83" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K82" s="45" t="inlineStr">
+      <c r="K83" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L82" s="46" t="inlineStr">
+      <c r="L83" s="46" t="inlineStr">
         <is>
           <t>Positivisme</t>
         </is>
       </c>
-      <c r="M82" s="35" t="inlineStr">
+      <c r="M83" s="35" t="inlineStr">
         <is>
           <t>philosophe français fondateur du courant philosophique des Idéologues.</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="104.25" customHeight="1" s="39">
-      <c r="A83" s="34" t="n">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="104.25" customHeight="1" s="39">
+      <c r="A84" s="34" t="n">
         <v>1756</v>
       </c>
-      <c r="B83" s="34" t="n">
+      <c r="B84" s="34" t="n">
         <v>1837</v>
       </c>
-      <c r="C83" s="34" t="inlineStr">
+      <c r="C84" s="34" t="inlineStr">
         <is>
           <t>1756 – 1837</t>
         </is>
       </c>
-      <c r="D83" s="35" t="inlineStr">
+      <c r="D84" s="35" t="inlineStr">
         <is>
           <t>Pierre LAROMIGUIÈRE</t>
         </is>
       </c>
-      <c r="E83" s="35" t="inlineStr">
+      <c r="E84" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Laromigui%C3%A8re"  title=" Wikipedia"&gt;Pierre LAROMIGUIÈRE&lt;/a&gt; était un philosophe français, l'une des figures transitoires entre le sensualisme des Lumières et la philosophie spiritualiste du XIXe siècle. Né à Livinhac-le-Haut dans l'Aveyron, il fut d'abord prêtre avant la Révolution, puis professeur de philosophie à l'École centrale des arts et manufactures et enfin à la Sorbonne. Ses cours, qui attirèrent un public nombreux et enthousiaste dans les premières décennies du XIXe siècle, contribuèrent à renouveler l'enseignement de la philosophie en France. &lt;/p&gt; &lt;p&gt; Sa philosophie part du sensualisme de Condillac mais s'en écarte sur un point décisif : là où Condillac réduisait toutes les opérations de l'esprit à des sensations transformées, Laromiguière distingue soigneusement les sensations des opérations actives de l'attention, de la comparaison et du jugement. Cette distinction entre les facultés passives et les facultés actives de l'esprit ouvre la voie à une conception plus riche de la vie psychique, qui reconnaît la spécificité de l'activité intellectuelle irréductible à la simple réception sensorielle. &lt;/p&gt; &lt;p&gt; Dans ses &lt;em&gt;Leçons de philosophie&lt;/em&gt; (1815-1818), dont la clarté et l'agrément du style lui valurent un succès durable, il développe cette psychologie des facultés dans un cadre pédagogique accessible. Bien que sa pensée ait été éclipsée par le courant spiritualiste de Cousin et par le positivisme de Comte, Laromiguière représente une étape importante dans la constitution de la psychologie philosophique française. Sa manière de corriger Condillac par une attention accrue à l'activité de l'esprit préfigure les développements du spiritualisme ultérieur. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F83" s="47" t="inlineStr">
+      <c r="F84" s="47" t="inlineStr">
         <is>
           <t>STOo4oShj2g</t>
         </is>
       </c>
-      <c r="G83" s="49" t="inlineStr">
+      <c r="G84" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Pierre LAROMIGUIERE  par VIS PHILO </t>
         </is>
       </c>
-      <c r="H83" s="35" t="inlineStr">
+      <c r="H84" s="35" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/laromiguiere-mini.webp</t>
         </is>
       </c>
-      <c r="J83" s="38" t="inlineStr">
+      <c r="J84" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K83" s="45" t="inlineStr">
+      <c r="K84" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L83" s="46" t="inlineStr">
+      <c r="L84" s="46" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="M83" s="35" t="inlineStr">
+      <c r="M84" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour avoir réformé la psychologie rationnelle.</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="109.5" customHeight="1" s="39">
-      <c r="A84" s="34" t="n">
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="109.5" customHeight="1" s="39">
+      <c r="A85" s="34" t="n">
         <v>1757</v>
       </c>
-      <c r="B84" s="34" t="n">
+      <c r="B85" s="34" t="n">
         <v>1808</v>
       </c>
-      <c r="C84" s="34" t="inlineStr">
+      <c r="C85" s="34" t="inlineStr">
         <is>
           <t>1757 – 1808</t>
         </is>
       </c>
-      <c r="D84" s="35" t="inlineStr">
+      <c r="D85" s="35" t="inlineStr">
         <is>
           <t>Pierre CABANIS</t>
         </is>
       </c>
-      <c r="E84" s="65" t="inlineStr">
+      <c r="E85" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Jean_Georges_Cabanis" title=" Wikipedia"&gt;Pierre CABANIS&lt;/a&gt; était un médecin et philosophe français, figure majeure du groupe des Idéologues et pionnier d'une approche naturaliste de la vie psychique. Né à Cosnac en Corrèze, il fut introduit dans les cercles intellectuels parisiens par Turgot et fréquenta le salon d'Helvétius. Ami intime de Mirabeau dont il soigna les derniers jours, il participa activement à la vie politique de la Révolution et du Directoire, siégeant au Conseil des Cinq-Cents. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;Rapports du physique et du moral de l'homme&lt;/em&gt; (1802), est un essai audacieux pour fonder une science de l'homme sur des bases physiologiques. Cabanis y soutient que les phénomènes psychiques sont intimement liés aux processus organiques du corps : le cerveau secrète la pensée comme le foie sécrète la bile. Cette formule provocatrice, souvent mal comprise, visait en réalité à établir une méthode empirique pour l'étude de l'âme, refusant tout recours à des entités métaphysiques abstraites. &lt;/p&gt; &lt;p&gt; Médecin réformateur, il œuvra à la réorganisation des hôpitaux parisiens et milita pour une médecine fondée sur l'observation clinique plutôt que sur les théories scolastiques. Ses travaux contribuèrent à l'essor de l'hygiénisme et de la médecine sociale. Sa pensée, qui anticipe certains aspects du matérialisme médical du XIXe siècle, représente une étape importante dans la constitution des sciences humaines. Bien que les Idéologues aient été rabroués par Napoléon qui les rendait responsables des « idéologues abstraits », l'influence de Cabanis sur la médecine et la psychologie françaises fut durable. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F84" s="34" t="inlineStr">
+      <c r="F85" s="34" t="inlineStr">
         <is>
           <t>7JWvo6-4cjA</t>
         </is>
       </c>
-      <c r="G84" s="64" t="inlineStr">
+      <c r="G85" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">« Pierre Jean Georges Cabanis » par  Everything Philosophers </t>
         </is>
       </c>
-      <c r="H84" s="35" t="inlineStr">
+      <c r="H85" s="35" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cabanis-mini.webp</t>
         </is>
       </c>
-      <c r="J84" s="38" t="inlineStr">
+      <c r="J85" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K84" s="45" t="inlineStr">
+      <c r="K85" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L84" s="46" t="inlineStr">
+      <c r="L85" s="46" t="inlineStr">
         <is>
           <t>Matérialisme ; Épiphénoménisme</t>
         </is>
       </c>
-      <c r="M84" s="35" t="inlineStr">
+      <c r="M85" s="35" t="inlineStr">
         <is>
           <t>philosophe figure majeure du matérialisme et de l'idéologie de la Révolution française.</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="135.75" customHeight="1" s="39">
-      <c r="A85" s="47" t="n">
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="135.75" customHeight="1" s="39">
+      <c r="A86" s="47" t="n">
         <v>1763</v>
       </c>
-      <c r="B85" s="47" t="inlineStr">
+      <c r="B86" s="47" t="inlineStr">
         <is>
           <t>1845</t>
         </is>
       </c>
-      <c r="C85" s="47" t="inlineStr">
+      <c r="C86" s="47" t="inlineStr">
         <is>
           <t>1763 – 1845</t>
         </is>
       </c>
-      <c r="D85" s="48" t="inlineStr">
+      <c r="D86" s="48" t="inlineStr">
         <is>
           <t>Pierre-Paul ROYER-COLLARD</t>
         </is>
       </c>
-      <c r="E85" s="50" t="inlineStr">
+      <c r="E86" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre-Paul_Royer-Collard"  title=" Wikipedia"&gt;Pierre-Paul ROYER-COLLARD&lt;/a&gt;  était un philosophe et homme politique français, figure majeure du libéralisme modéré sous la Restauration et chef des Doctrinaires. Né en Champagne, il commence comme avocat au Parlement de Paris avant de s'engager politiquement. Pendant la Révolution, il soutient les Girondins et fuit la Terreur, se retirant dans ses terres. Sous la Restauration, il devient député de la Marne et préside la Chambre des députés (1828–1830), tout en enseignant l'histoire de la philosophie moderne à la Sorbonne. &lt;/p&gt; &lt;p&gt; Sa philosophie se présente comme un rejet du sensualisme de Condillac qui dominait le XVIIIᵉ siècle français. Il s'inspire du philosophe écossais Thomas Reid et introduit en France la doctrine du sens commun. Contrairement aux sensualistes, il distingue clairement la sensation (subjective, plaisir ou peine) de la perception (appréhension d'un objet externe). Pour lui, la perception implique un jugement spontané de l'esprit actif, non déductible des seuls sens. &lt;/p&gt; &lt;p&gt; Il développe un spiritualisme rigoureux : l'esprit humain est actif et capable de jugements autonomes. Le sens commun – cette faculté naturelle de distinguer le bien du mal, le vrai du faux – fonde la vie communautaire et remplace l'autorité surnaturelle. Par les principes de causalité et d'induction, la raison conduit nécessairement à l'idée d'une Première Cause (Dieu). Il affirme la supériorité irréductible de la personne humaine sur l'État, les personnes étant &lt;a  href="https://www.youtube.com/watch?v=15bNqKMiW_w"  title="R Collard ou l’ambilalence des restaurations par Collège st Germain"&gt;« faites à l'image de Dieu et douées d'immortalité ».&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Politiquement, il est un royaliste libéral qui considère la Révolution de 1789 comme irréversible. Il cherche à fonder une monarchie constitutionnelle stable entre l'Ancien Régime (les Ultras) et le totalitarisme napoléonien, puis la démocratisation trop rapide sous Louis-Philippe. Il incarne la « philosophie de la Charte » et influence profondément François Guizot. N'a presque rien publié de son vivant : ses écrits philosophiques ont été rassemblés après coup par son admirateur Théodore Jouffroy.  &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F85" s="66" t="inlineStr">
+      <c r="F86" s="66" t="inlineStr">
         <is>
           <t>_6oY2zBA5lQ</t>
         </is>
       </c>
-      <c r="G85" s="67" t="inlineStr">
+      <c r="G86" s="67" t="inlineStr">
         <is>
           <t>"Pierre Paul Royer-Collard: Unleashing Mathematical Genius" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H85" s="58" t="inlineStr">
+      <c r="H86" s="58" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/pcollard-mini.webp</t>
         </is>
       </c>
-      <c r="I85" s="49" t="n"/>
-      <c r="J85" s="38" t="inlineStr">
+      <c r="I86" s="49" t="n"/>
+      <c r="J86" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K85" s="45" t="inlineStr">
+      <c r="K86" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; politique</t>
         </is>
       </c>
-      <c r="L85" s="46" t="inlineStr">
+      <c r="L86" s="46" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="M85" s="35" t="inlineStr">
+      <c r="M86" s="35" t="inlineStr">
         <is>
           <t>philosophe français figure majeure du libéralisme modéré.</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="317.25" customFormat="1" customHeight="1" s="38">
-      <c r="A86" s="38" t="n">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="317.25" customFormat="1" customHeight="1" s="38">
+      <c r="A87" s="38" t="n">
         <v>1760</v>
       </c>
-      <c r="B86" s="38" t="n">
+      <c r="B87" s="38" t="n">
         <v>1825</v>
       </c>
-      <c r="C86" s="38" t="inlineStr">
+      <c r="C87" s="38" t="inlineStr">
         <is>
           <t>1760 – 1825</t>
         </is>
       </c>
-      <c r="D86" s="38" t="inlineStr">
+      <c r="D87" s="38" t="inlineStr">
         <is>
           <t>Henri de SAINT-SIMON</t>
         </is>
       </c>
-      <c r="E86" s="45" t="inlineStr">
+      <c r="E87" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claude-Henri_de_Rouvroy_de_Saint-Simon" title=" Wikipedia"&gt;Claude-Henri de ROUVROY, comte de SAINT-SIMON&lt;/a&gt; est un penseur et réformateur social français, issu d’une famille aristocratique qui revendiquait une lointaine parenté avec Charlemagne. Volontaire dans l’armée française envoyée soutenir l’indépendance américaine, il participe au siège de Yorktown avant de renoncer, sous la Révolution, à son titre de noblesse.  &lt;a href="https://maitron.fr/saint-simon-claude-henri-claude-henri-de-rouvroy-comte-de-saint-simon/" title="saint simon par le maitron"&gt;Spéculateur &lt;/a&gt; sur les biens nationaux, emprisonné pendant la Terreur, il connaît ensuite une vie mouvementée, tour à tour fortunée et misérable, entièrement vouée à la recherche d’une science nouvelle de la société. &lt;/p&gt; &lt;p&gt; Convaincu que la Révolution a détruit l’ancien ordre théologique et féodal sans encore bâtir l’ordre qui doit lui succéder, Saint-Simon appelle à fonder une organisation sociale confiée non plus aux militaires, aux juristes ou aux rentiers, mais aux savants, aux industriels et aux producteurs. Dans des ouvrages comme &lt;em&gt;L’Industrie&lt;/em&gt; ou &lt;em&gt;Du système industriel&lt;/em&gt;, il défend l’idée que le pouvoir politique doit être subordonné à la production utile : gouverner, pour lui, revient d’abord à administrer les choses et à organiser le travail, plutôt qu’à commander les hommes. &lt;/p&gt; &lt;p&gt; Il élabore ainsi une &lt;a href="https://fr.wikipedia.org/wiki/Saint-simonisme" title="Saint-simonisme par Wikipedia"&gt;philosophie de l’histoire&lt;/a&gt; fondée sur l’alternance de périodes « organiques » et « critiques », et annonce l’avènement d’un âge industriel où la science et la technique remplaceraient la théologie comme principe d’unité sociale. Son dernier livre, &lt;em&gt;Le Nouveau Christianisme&lt;/em&gt; (1825), publié l’année de sa mort, prône une religion de la fraternité entièrement tournée vers l’amélioration du sort des classes les plus pauvres, qu’il présente comme la fin ultime de toute organisation sociale et politique légitime. &lt;/p&gt; &lt;p&gt; Bien que ses écrits soient souvent fragmentaires et inachevés, Saint-Simon laisse une postérité considérable : ses disciples, réunis après sa mort en une école puis en une véritable Église saint-simonienne, diffusent et systématisent sa pensée sous le nom de saint-simonisme. Ce courant influencera profondément le socialisme utopique du XIXe siècle, la sociologie naissante d’Auguste Comte (un temps son secrétaire), ainsi que les grandes entreprises industrielles et financières du Second Empire, qui reprendront à leur compte son culte du progrès technique et de l’organisation rationnelle de la production. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F86" s="38" t="inlineStr">
+      <c r="F87" s="38" t="inlineStr">
         <is>
           <t>82O6eO6UQqY</t>
         </is>
       </c>
-      <c r="G86" s="45" t="inlineStr">
+      <c r="G87" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">saint simon – transformer la société par Thérence Carvalho</t>
         </is>
       </c>
-      <c r="H86" s="45" t="inlineStr">
+      <c r="H87" s="45" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/hssimon-mini.webp</t>
         </is>
       </c>
-      <c r="J86" s="45" t="inlineStr">
+      <c r="J87" s="45" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K86" s="45" t="inlineStr">
+      <c r="K87" s="45" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="L86" s="45" t="inlineStr">
+      <c r="L87" s="45" t="inlineStr">
         <is>
           <t>Saint-Simonisme</t>
         </is>
       </c>
-      <c r="M86" s="45" t="inlineStr">
+      <c r="M87" s="45" t="inlineStr">
         <is>
           <t>penseur et réformateur social français, fondateur du saint-simonisme.</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="130.5" customHeight="1" s="39">
-      <c r="A87" s="47" t="n">
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="130.5" customHeight="1" s="39">
+      <c r="A88" s="47" t="n">
         <v>1766</v>
       </c>
-      <c r="B87" s="47" t="inlineStr">
+      <c r="B88" s="47" t="inlineStr">
         <is>
           <t>1824</t>
         </is>
       </c>
-      <c r="C87" s="47" t="inlineStr">
+      <c r="C88" s="47" t="inlineStr">
         <is>
           <t>1766 – 1824</t>
         </is>
       </c>
-      <c r="D87" s="48" t="inlineStr">
+      <c r="D88" s="48" t="inlineStr">
         <is>
           <t>Maine de BIRAN</t>
         </is>
       </c>
-      <c r="E87" s="68" t="inlineStr">
+      <c r="E88" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maine_de_Biran"  title=" Wikipedia"&gt;Maine de BIRAN&lt;/a&gt; était un philosophe français, considéré comme l'un des fondateurs de la philosophie de l'intériorité et du spiritualisme français. Né François-Pierre Gonthier de Biran à Bergerac en Dordogne, il commença sa carrière comme officier de la garde du roi, avant de se consacrer à la philosophie et à la vie politique locale en Périgord. Administrateur apprécié sous plusieurs régimes successifs, il fut député et sous-préfet, mais c'est à travers ses journaux intimes et ses &lt;a  href="https://www.youtube.com/watch?v=ayhmQ5WQfJk"  title="Maine de Biran spiritualité &amp; phénoménologie par ICP"&gt;essais philosophiques &lt;/a&gt; que son originalité s'exprima pleinement. &lt;/p&gt; &lt;p&gt; Sa pensée prend pour point de départ l'expérience immédiate de l'effort : c'est dans l'acte volontaire par lequel le moi exerce une résistance contre le corps propre que la conscience se saisit elle-même comme force et comme liberté. Contre le sensualisme de Condillac qui réduisait l'âme à la sensation passive, il soutient que l'activité volontaire constitue le fait primitif de la conscience. Cette découverte du « moi voulant » comme donnée irréductible de l'intériorité marque une rupture décisive dans la philosophie française. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;t &lt;a  href="https://www.persee.fr/doc/bupsy_0007-4403_1963_num_17_224_9102"  title="Maine de Biran fondateur de la psychologie française par Persée"&gt;Essai sur les fondements de la psychologie &lt;/a&gt; &lt;/em&gt; (1812) et ses nombreux &lt;em&gt;Mémoires&lt;/em&gt; rédigés pour les concours de l'Institut, développent une psychologie de l'effort qui distingue trois ordres d'existence : la vie animale (sensations), la vie humaine (volonté et conscience) et la vie de l'esprit (grâce et amour mystique). Cette trilogie, d'inspiration néo-platonicienne et chrétienne dans sa dernière phase, influença profondément Ravaisson, Bergson et tout le courant spiritualiste français. Ses &lt;em&gt;Journal&lt;/em&gt; et &lt;em&gt;Mémoire sur les perceptions obscures&lt;/em&gt; témoignent d'une introspection d'une subtilité et d'une profondeur rares. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F87" s="66" t="inlineStr">
+      <c r="F88" s="66" t="inlineStr">
         <is>
           <t>e6lHF0weqtA</t>
         </is>
       </c>
-      <c r="G87" s="67" t="inlineStr">
+      <c r="G88" s="67" t="inlineStr">
         <is>
           <t>"Maine de Biran: Exploring the Human Mind" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H87" s="49" t="inlineStr">
+      <c r="H88" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mbiran-mini.webp</t>
         </is>
       </c>
-      <c r="I87" s="49" t="n"/>
-      <c r="J87" s="38" t="inlineStr">
+      <c r="I88" s="49" t="n"/>
+      <c r="J88" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K87" s="45" t="inlineStr">
+      <c r="K88" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L87" s="46" t="inlineStr">
+      <c r="L88" s="46" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="M87" s="35" t="inlineStr">
+      <c r="M88" s="35" t="inlineStr">
         <is>
           <t>philosophe français fondateur de la philosophie de l'intériorité et du spiritualisme.</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="130.5" customHeight="1" s="39">
-      <c r="A88" s="47">
-        <v>1565</v>
-      </c>
-      <c r="B88" s="47">
-        <v>1645</v>
-      </c>
-      <c r="C88" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1565 - 1645</t>
-        </is>
-      </c>
-      <c r="D88" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marie de GOURNAY</t>
-        </is>
-      </c>
-      <c r="E88" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marie_de_Gournay"  title=" Wikipedia"&gt;Marie de GOURNAY&lt;/a&gt; (1565-1645) est une femme de lettres et philosophe française. Autodidacte, elle apprit seule le latin et découvrit adolescente les &lt;em&gt;Essais&lt;/em&gt; de Montaigne, qui la bouleversèrent. Elle rencontra l'auteur en 1588 et devint sa « fille d'alliance », une amitié intellectuelle profonde.&lt;/p&gt; &lt;p&gt;Après la mort de Montaigne, sa veuve lui confia le manuscrit annoté des &lt;em&gt;Essais&lt;/em&gt;. Marie de Gournay consacra une grande partie de sa vie à en préparer les éditions, dont celle de 1595, qui a fait autorité pendant des siècles. Elle vécut de sa plume, chose très rare pour une femme de son époque, et fréquenta les milieux savants de Paris, où elle fut souvent moquée pour son indépendance.&lt;/p&gt; &lt;p&gt;Marie de Gournay s'intéressa aussi à la langue française, qu'elle défendit contre les réformes de Malherbe qui voulaient l'appauvrir selon elle, et publia un recueil de ses œuvres sous le titre &lt;em&gt;L'Ombre de la demoiselle de Gournay&lt;/em&gt; (1626), puis &lt;em&gt;Les Advis ou les Présens&lt;/em&gt; (1634). Elle y traite de l'éducation des princes, de la poésie, de la calomnie et de la condition des femmes savantes, qu'on ridiculisait pour mieux les écarter.&lt;/p&gt; &lt;p&gt;Elle est surtout connue pour deux textes pionniers : &lt;em&gt;Égalité des hommes et des femmes&lt;/em&gt; (1622) et &lt;em&gt;Grief des dames&lt;/em&gt; (1626). Elle y soutient que la différence entre hommes et femmes ne tient pas à la nature mais à l'éducation, et que « l'animal humain n'est ni homme ni femme » par l'âme. Elle s'appuie sur la Bible, les Pères de l'Église et les philosophes antiques pour montrer que rien ne justifie l'exclusion des femmes du savoir. Elle est considérée comme l'une des premières penseuses de l'égalité des sexes.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J88" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Française</t>
-        </is>
-      </c>
-      <c r="K88" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique ; politique</t>
-        </is>
-      </c>
-      <c r="L88" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Humanisme ; Féminisme</t>
-        </is>
-      </c>
-      <c r="M88" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme de lettres française, « fille d'alliance » de Montaigne et pionnière de la défense de l'égalité des sexes.</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6551,44 +6564,44 @@
     </row>
     <row r="89" ht="130.5" customHeight="1" s="39">
       <c r="A89" s="47">
-        <v>1618</v>
+        <v>1565</v>
       </c>
       <c r="B89" s="47">
-        <v>1680</v>
+        <v>1645</v>
       </c>
       <c r="C89" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618 - 1680</t>
+          <t xml:space="preserve">1565 - 1645</t>
         </is>
       </c>
       <c r="D89" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ÉLISABETH de Bohême</t>
+          <t xml:space="preserve">Marie de GOURNAY</t>
         </is>
       </c>
       <c r="E89" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Élisabeth_de_Bohême_(1618-1680)"  title=" Wikipedia"&gt;ÉLISABETH de Bohême&lt;/a&gt; (1618-1680), princesse palatine, était la fille de Frédéric V, l'éphémère « roi d'hiver » de Bohême, chassé de son trône au début de la guerre de Trente Ans. Elle grandit en exil aux Pays-Bas, où elle reçut une éducation très poussée en langues, mathématiques et philosophie.&lt;/p&gt; &lt;p&gt;Elle est célèbre pour sa correspondance avec René Descartes, commencée en 1643. Dès sa première lettre, elle lui pose une question redoutable : si l'âme est une substance pensante, sans étendue, comment peut-elle mettre en mouvement le corps, qui est une chose étendue ? Descartes eut beaucoup de mal à lui répondre, et cette objection reste au cœur de ce que l'on appelle aujourd'hui le problème de l'esprit et du corps.&lt;/p&gt; &lt;p&gt;La correspondance entre Élisabeth et Descartes, qui dura jusqu'à la mort du philosophe en 1650, compte une soixantaine de lettres. On y voit la princesse contester, avec politesse mais fermeté, plusieurs points de la doctrine cartésienne, et proposer ses propres solutions, par exemple sur la manière dont l'âme peut être affectée par la maladie du corps. Descartes lui-même reconnaissait qu'elle était la personne qui comprenait le mieux sa philosophie.&lt;/p&gt; &lt;p&gt;Leurs échanges portèrent aussi sur les passions, la vertu, le bonheur et la politique : c'est pour elle que Descartes écrivit son &lt;em&gt;Traité des passions de l'âme&lt;/em&gt;, et il lui dédia ses &lt;em&gt;Principes de la philosophie&lt;/em&gt;. Élisabeth y défend une morale attentive aux réalités de la vie et du corps. Elle devint ensuite abbesse de l'abbaye protestante de Herford, en Allemagne, où elle accueillit des penseurs persécutés. Elle est aujourd'hui reconnue comme une philosophe à part entière, et non plus seulement comme une correspondante de Descartes.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marie_de_Gournay"  title=" Wikipedia"&gt;Marie de GOURNAY&lt;/a&gt; (1565-1645) est une femme de lettres et philosophe française. Autodidacte, elle apprit seule le latin et découvrit adolescente les &lt;em&gt;Essais&lt;/em&gt; de Montaigne, qui la bouleversèrent. Elle rencontra l'auteur en 1588 et devint sa « fille d'alliance », une amitié intellectuelle profonde.&lt;/p&gt; &lt;p&gt;Après la mort de Montaigne, sa veuve lui confia le manuscrit annoté des &lt;em&gt;Essais&lt;/em&gt;. Marie de Gournay consacra une grande partie de sa vie à en préparer les éditions, dont celle de 1595, qui a fait autorité pendant des siècles. Elle vécut de sa plume, chose très rare pour une femme de son époque, et fréquenta les milieux savants de Paris, où elle fut souvent moquée pour son indépendance.&lt;/p&gt; &lt;p&gt;Marie de Gournay s'intéressa aussi à la langue française, qu'elle défendit contre les réformes de Malherbe qui voulaient l'appauvrir selon elle, et publia un recueil de ses œuvres sous le titre &lt;em&gt;L'Ombre de la demoiselle de Gournay&lt;/em&gt; (1626), puis &lt;em&gt;Les Advis ou les Présens&lt;/em&gt; (1634). Elle y traite de l'éducation des princes, de la poésie, de la calomnie et de la condition des femmes savantes, qu'on ridiculisait pour mieux les écarter.&lt;/p&gt; &lt;p&gt;Elle est surtout connue pour deux textes pionniers : &lt;em&gt;Égalité des hommes et des femmes&lt;/em&gt; (1622) et &lt;em&gt;Grief des dames&lt;/em&gt; (1626). Elle y soutient que la différence entre hommes et femmes ne tient pas à la nature mais à l'éducation, et que « l'animal humain n'est ni homme ni femme » par l'âme. Elle s'appuie sur la Bible, les Pères de l'Église et les philosophes antiques pour montrer que rien ne justifie l'exclusion des femmes du savoir. Elle est considérée comme l'une des premières penseuses de l'égalité des sexes.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J89" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allemande</t>
+          <t xml:space="preserve">Française</t>
         </is>
       </c>
       <c r="K89" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; ethique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L89" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartésianisme</t>
+          <t xml:space="preserve">Humanisme ; Féminisme</t>
         </is>
       </c>
       <c r="M89" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">princesse palatine dont la correspondance avec Descartes pose le problème de l'union de l'âme et du corps.</t>
+          <t xml:space="preserve">femme de lettres française, « fille d'alliance » de Montaigne et pionnière de la défense de l'égalité des sexes.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6600,51 +6613,48 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
-      </c>
-      <c r="P89">
-        <v>2</v>
       </c>
     </row>
     <row r="90" ht="130.5" customHeight="1" s="39">
       <c r="A90" s="47">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="B90" s="47">
-        <v>1673</v>
+        <v>1680</v>
       </c>
       <c r="C90" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623 - 1673</t>
+          <t xml:space="preserve">1618 - 1680</t>
         </is>
       </c>
       <c r="D90" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margaret CAVENDISH</t>
+          <t xml:space="preserve">ÉLISABETH de Bohême</t>
         </is>
       </c>
       <c r="E90" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Margaret_Cavendish"  title=" Wikipedia"&gt;Margaret CAVENDISH&lt;/a&gt; (1623-1673), duchesse de Newcastle, est une philosophe, poétesse et romancière anglaise. Pendant la guerre civile anglaise, elle suivit la reine en exil à Paris, où elle épousa William Cavendish et fréquenta, grâce à lui, des penseurs comme Hobbes, Descartes et Gassendi.&lt;/p&gt; &lt;p&gt;Elle publia sous son propre nom une douzaine d'ouvrages de philosophie naturelle, ce qui était presque impensable pour une femme de son temps. Elle y développe une philosophie matérialiste et vitaliste : la nature entière est faite d'une seule matière, mais cette matière est douée de mouvement, de perception et même de raison. Elle critique à la fois le mécanisme de Descartes et de Hobbes, et la science expérimentale de la Royal Society, qui prétendait connaître la nature grâce aux microscopes.&lt;/p&gt; &lt;p&gt;Cavendish réfléchit aussi à la condition des femmes, qu'elle juge tenues à l'écart du savoir et du pouvoir par la coutume plutôt que par la nature. Dans ses préfaces, elle revendique ouvertement le désir de gloire et de reconnaissance, ce qui choquait ses contemporains. Ses &lt;em&gt;Observations sur la philosophie expérimentale&lt;/em&gt; (1666) contiennent l'une des premières critiques philosophiques de la confiance aveugle dans les instruments scientifiques.&lt;/p&gt; &lt;p&gt;En 1667, elle fut la première femme invitée à assister à une séance de la Royal Society de Londres. Son récit &lt;em&gt;Le Monde glorieux&lt;/em&gt; (&lt;em&gt;The Blazing World&lt;/em&gt;, 1666), où une femme devient impératrice d'un monde imaginaire peuplé de savants animaux, est souvent considéré comme l'un des premiers romans de science-fiction. Surnommée « Mad Madge » par ses contemporains, elle est aujourd'hui redécouverte comme une philosophe originale et audacieuse.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Élisabeth_de_Bohême_(1618-1680)"  title=" Wikipedia"&gt;ÉLISABETH de Bohême&lt;/a&gt; (1618-1680), princesse palatine, était la fille de Frédéric V, l'éphémère « roi d'hiver » de Bohême, chassé de son trône au début de la guerre de Trente Ans. Elle grandit en exil aux Pays-Bas, où elle reçut une éducation très poussée en langues, mathématiques et philosophie.&lt;/p&gt; &lt;p&gt;Elle est célèbre pour sa correspondance avec René Descartes, commencée en 1643. Dès sa première lettre, elle lui pose une question redoutable : si l'âme est une substance pensante, sans étendue, comment peut-elle mettre en mouvement le corps, qui est une chose étendue ? Descartes eut beaucoup de mal à lui répondre, et cette objection reste au cœur de ce que l'on appelle aujourd'hui le problème de l'esprit et du corps.&lt;/p&gt; &lt;p&gt;La correspondance entre Élisabeth et Descartes, qui dura jusqu'à la mort du philosophe en 1650, compte une soixantaine de lettres. On y voit la princesse contester, avec politesse mais fermeté, plusieurs points de la doctrine cartésienne, et proposer ses propres solutions, par exemple sur la manière dont l'âme peut être affectée par la maladie du corps. Descartes lui-même reconnaissait qu'elle était la personne qui comprenait le mieux sa philosophie.&lt;/p&gt; &lt;p&gt;Leurs échanges portèrent aussi sur les passions, la vertu, le bonheur et la politique : c'est pour elle que Descartes écrivit son &lt;em&gt;Traité des passions de l'âme&lt;/em&gt;, et il lui dédia ses &lt;em&gt;Principes de la philosophie&lt;/em&gt;. Élisabeth y défend une morale attentive aux réalités de la vie et du corps. Elle devint ensuite abbesse de l'abbaye protestante de Herford, en Allemagne, où elle accueillit des penseurs persécutés. Elle est aujourd'hui reconnue comme une philosophe à part entière, et non plus seulement comme une correspondante de Descartes.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J90" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britannique</t>
+          <t xml:space="preserve">Allemande</t>
         </is>
       </c>
       <c r="K90" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">metaphysique ; ethique</t>
         </is>
       </c>
       <c r="L90" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matérialisme</t>
+          <t xml:space="preserve">Cartésianisme</t>
         </is>
       </c>
       <c r="M90" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe anglaise, penseuse matérialiste de la nature et autrice de l'un des premiers romans de science-fiction.</t>
+          <t xml:space="preserve">princesse palatine dont la correspondance avec Descartes pose le problème de l'union de l'âme et du corps.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6656,28 +6666,31 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
+      </c>
+      <c r="P90">
+        <v>2</v>
       </c>
     </row>
     <row r="91" ht="130.5" customHeight="1" s="39">
       <c r="A91" s="47">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="B91" s="47">
-        <v>1679</v>
+        <v>1673</v>
       </c>
       <c r="C91" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631 - 1679</t>
+          <t xml:space="preserve">1623 - 1673</t>
         </is>
       </c>
       <c r="D91" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne CONWAY</t>
+          <t xml:space="preserve">Margaret CAVENDISH</t>
         </is>
       </c>
       <c r="E91" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Conway"  title=" Wikipedia"&gt;Anne CONWAY&lt;/a&gt; (1631-1679) est une philosophe anglaise, proche du groupe des platoniciens de Cambridge. Souffrant toute sa vie de violentes migraines, elle reçut une éducation principalement par correspondance, notamment avec le philosophe Henry More, qui devint son ami et son maître.&lt;/p&gt; &lt;p&gt;Son unique ouvrage, les &lt;em&gt;Principes de la plus ancienne et de la plus moderne philosophie&lt;/em&gt;, fut publié après sa mort, en latin en 1690, puis en anglais. Elle y rejette le dualisme de Descartes, qui sépare l'esprit et la matière, et le matérialisme de Hobbes et de Spinoza. Pour elle, tout ce qui existe est à la fois esprit et corps à des degrés divers : la matière n'est qu'un esprit « épaissi », et toutes les créatures, même les pierres, sont vivantes et capables de se perfectionner.&lt;/p&gt; &lt;p&gt;Sa philosophie répond aussi à une question personnelle : comment donner un sens à la douleur ? Pour Anne Conway, la souffrance n'est pas un châtiment arbitraire mais un moyen de purification, qui permet à chaque créature de se rapprocher de Dieu. Aucune créature n'est condamnée pour toujours : toutes sont appelées à progresser vers le bien, ce qui fait de sa pensée l'une des plus optimistes de son temps.&lt;/p&gt; &lt;p&gt;Anne Conway propose une vision d'un monde en constante évolution vers le bien, où la souffrance a un sens puisqu'elle aide les êtres à progresser. Influencée par la kabbale et par les quakers, qu'elle rejoignit à la fin de sa vie, elle eut une influence directe sur Leibniz, qui la cite et lui emprunta sans doute l'idée de « monade ». Longtemps oubliée, elle est aujourd'hui considérée comme l'une des philosophes les plus originales du XVIIe siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Margaret_Cavendish"  title=" Wikipedia"&gt;Margaret CAVENDISH&lt;/a&gt; (1623-1673), duchesse de Newcastle, est une philosophe, poétesse et romancière anglaise. Pendant la guerre civile anglaise, elle suivit la reine en exil à Paris, où elle épousa William Cavendish et fréquenta, grâce à lui, des penseurs comme Hobbes, Descartes et Gassendi.&lt;/p&gt; &lt;p&gt;Elle publia sous son propre nom une douzaine d'ouvrages de philosophie naturelle, ce qui était presque impensable pour une femme de son temps. Elle y développe une philosophie matérialiste et vitaliste : la nature entière est faite d'une seule matière, mais cette matière est douée de mouvement, de perception et même de raison. Elle critique à la fois le mécanisme de Descartes et de Hobbes, et la science expérimentale de la Royal Society, qui prétendait connaître la nature grâce aux microscopes.&lt;/p&gt; &lt;p&gt;Cavendish réfléchit aussi à la condition des femmes, qu'elle juge tenues à l'écart du savoir et du pouvoir par la coutume plutôt que par la nature. Dans ses préfaces, elle revendique ouvertement le désir de gloire et de reconnaissance, ce qui choquait ses contemporains. Ses &lt;em&gt;Observations sur la philosophie expérimentale&lt;/em&gt; (1666) contiennent l'une des premières critiques philosophiques de la confiance aveugle dans les instruments scientifiques.&lt;/p&gt; &lt;p&gt;En 1667, elle fut la première femme invitée à assister à une séance de la Royal Society de Londres. Son récit &lt;em&gt;Le Monde glorieux&lt;/em&gt; (&lt;em&gt;The Blazing World&lt;/em&gt;, 1666), où une femme devient impératrice d'un monde imaginaire peuplé de savants animaux, est souvent considéré comme l'un des premiers romans de science-fiction. Surnommée « Mad Madge » par ses contemporains, elle est aujourd'hui redécouverte comme une philosophe originale et audacieuse.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J91" s="38" t="inlineStr">
@@ -6687,17 +6700,17 @@
       </c>
       <c r="K91" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="L91" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Néoplatonisme</t>
+          <t xml:space="preserve">Matérialisme</t>
         </is>
       </c>
       <c r="M91" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe anglaise, penseuse d'un monde fait d'un seul esprit vivant, qui influença Leibniz.</t>
+          <t xml:space="preserve">philosophe anglaise, penseuse matérialiste de la nature et autrice de l'un des premiers romans de science-fiction.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6713,24 +6726,24 @@
     </row>
     <row r="92" ht="130.5" customHeight="1" s="39">
       <c r="A92" s="47">
-        <v>1666</v>
+        <v>1631</v>
       </c>
       <c r="B92" s="47">
-        <v>1731</v>
+        <v>1679</v>
       </c>
       <c r="C92" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666 - 1731</t>
+          <t xml:space="preserve">1631 - 1679</t>
         </is>
       </c>
       <c r="D92" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mary ASTELL</t>
+          <t xml:space="preserve">Anne CONWAY</t>
         </is>
       </c>
       <c r="E92" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Astell"  title=" Wikipedia"&gt;Mary ASTELL&lt;/a&gt; (1666-1731) est une philosophe et écrivaine anglaise, souvent présentée comme la première féministe anglaise. Fille d'un marchand de charbon de Newcastle, elle fut instruite par son oncle, puis s'installa seule à Londres, où elle vécut de sa plume grâce au soutien de protectrices aristocratiques.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Une proposition sérieuse aux dames&lt;/em&gt; (1694), elle propose de créer une sorte d'institution où les femmes pourraient se consacrer à l'étude et à la réflexion, loin des futilités auxquelles la société les condamne. Disciple de Descartes et du philosophe Malebranche, elle affirme que les femmes ont la même raison que les hommes et que leur prétendue infériorité vient uniquement de leur manque d'éducation.&lt;/p&gt; &lt;p&gt;Mary Astell fut aussi une polémiste redoutée, qui débattit avec les penseurs les plus en vue de son temps, dont John Locke et le philosophe John Norris, avec qui elle échangea des lettres sur l'amour de Dieu. Elle fonda à Chelsea une école de charité pour les filles pauvres, qu'elle soutint jusqu'à sa mort. Son idée d'une communauté de femmes consacrée à l'étude, jugée trop proche des couvents catholiques, ne vit jamais le jour, mais elle inspira de nombreuses féministes après elle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Réflexions sur le mariage&lt;/em&gt; (1700), elle critique avec ironie la condition des épouses, soumises à un pouvoir absolu de leur mari. Elle retourne contre ses adversaires les idées de John Locke : « si tous les hommes naissent libres, comment se fait-il que toutes les femmes naissent esclaves ? ». Anglicane conservatrice en politique, elle n'en fut pas moins l'une des premières à penser la domination des femmes comme une question philosophique et politique.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Conway"  title=" Wikipedia"&gt;Anne CONWAY&lt;/a&gt; (1631-1679) est une philosophe anglaise, proche du groupe des platoniciens de Cambridge. Souffrant toute sa vie de violentes migraines, elle reçut une éducation principalement par correspondance, notamment avec le philosophe Henry More, qui devint son ami et son maître.&lt;/p&gt; &lt;p&gt;Son unique ouvrage, les &lt;em&gt;Principes de la plus ancienne et de la plus moderne philosophie&lt;/em&gt;, fut publié après sa mort, en latin en 1690, puis en anglais. Elle y rejette le dualisme de Descartes, qui sépare l'esprit et la matière, et le matérialisme de Hobbes et de Spinoza. Pour elle, tout ce qui existe est à la fois esprit et corps à des degrés divers : la matière n'est qu'un esprit « épaissi », et toutes les créatures, même les pierres, sont vivantes et capables de se perfectionner.&lt;/p&gt; &lt;p&gt;Sa philosophie répond aussi à une question personnelle : comment donner un sens à la douleur ? Pour Anne Conway, la souffrance n'est pas un châtiment arbitraire mais un moyen de purification, qui permet à chaque créature de se rapprocher de Dieu. Aucune créature n'est condamnée pour toujours : toutes sont appelées à progresser vers le bien, ce qui fait de sa pensée l'une des plus optimistes de son temps.&lt;/p&gt; &lt;p&gt;Anne Conway propose une vision d'un monde en constante évolution vers le bien, où la souffrance a un sens puisqu'elle aide les êtres à progresser. Influencée par la kabbale et par les quakers, qu'elle rejoignit à la fin de sa vie, elle eut une influence directe sur Leibniz, qui la cite et lui emprunta sans doute l'idée de « monade ». Longtemps oubliée, elle est aujourd'hui considérée comme l'une des philosophes les plus originales du XVIIe siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J92" s="38" t="inlineStr">
@@ -6740,17 +6753,17 @@
       </c>
       <c r="K92" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L92" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rationalisme ; Féminisme</t>
+          <t xml:space="preserve">Néoplatonisme</t>
         </is>
       </c>
       <c r="M92" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe anglaise, considérée comme l'une des premières féministes, qui défendit l'éducation des femmes.</t>
+          <t xml:space="preserve">philosophe anglaise, penseuse d'un monde fait d'un seul esprit vivant, qui influença Leibniz.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6766,44 +6779,44 @@
     </row>
     <row r="93" ht="130.5" customHeight="1" s="39">
       <c r="A93" s="47">
-        <v>1706</v>
+        <v>1666</v>
       </c>
       <c r="B93" s="47">
-        <v>1749</v>
+        <v>1731</v>
       </c>
       <c r="C93" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1706 - 1749</t>
+          <t xml:space="preserve">1666 - 1731</t>
         </is>
       </c>
       <c r="D93" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Émilie du CHÂTELET</t>
+          <t xml:space="preserve">Mary ASTELL</t>
         </is>
       </c>
       <c r="E93" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Émilie_du_Châtelet"  title=" Wikipedia"&gt;Émilie du CHÂTELET&lt;/a&gt; (1706-1749) est une mathématicienne, physicienne et philosophe française des Lumières. Issue de l'aristocratie, elle reçut une éducation rare pour une fille, en latin, en mathématiques et en sciences. Compagne de Voltaire pendant quinze ans, elle fit de leur château de Cirey un véritable centre d'étude, où ils travaillaient côte à côte.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Institutions de physique&lt;/em&gt; (1740) tentent de concilier la physique de Newton et la métaphysique de Leibniz, en particulier le principe de raison suffisante. Elle participa à la grande controverse sur la notion de « force vive », en montrant que l'énergie d'un corps en mouvement dépend du carré de sa vitesse, une idée essentielle pour la physique moderne.&lt;/p&gt; &lt;p&gt;Elle entretint une correspondance avec les plus grands savants de son temps, comme les mathématiciens Maupertuis et Clairaut, et fut la première femme dont un mémoire scientifique, sur la nature du feu, fut publié par l'Académie des sciences de Paris en 1738. Elle ne pouvait pourtant pas en être membre, et il lui arriva de se déguiser en homme pour entrer dans les cafés où se retrouvaient les savants.&lt;/p&gt; &lt;p&gt;Son œuvre majeure est la traduction commentée en français des &lt;em&gt;Principes mathématiques de la philosophie naturelle&lt;/em&gt; de Newton, achevée juste avant sa mort en couches, à 42 ans. Elle reste aujourd'hui la seule traduction française complète de ce texte fondateur. Dans son &lt;em&gt;Discours sur le bonheur&lt;/em&gt;, elle fait de l'étude et de la passion du savoir une source de bonheur indépendante des autres, notamment pour les femmes, exclues de tant d'autres chemins de la gloire.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Astell"  title=" Wikipedia"&gt;Mary ASTELL&lt;/a&gt; (1666-1731) est une philosophe et écrivaine anglaise, souvent présentée comme la première féministe anglaise. Fille d'un marchand de charbon de Newcastle, elle fut instruite par son oncle, puis s'installa seule à Londres, où elle vécut de sa plume grâce au soutien de protectrices aristocratiques.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Une proposition sérieuse aux dames&lt;/em&gt; (1694), elle propose de créer une sorte d'institution où les femmes pourraient se consacrer à l'étude et à la réflexion, loin des futilités auxquelles la société les condamne. Disciple de Descartes et du philosophe Malebranche, elle affirme que les femmes ont la même raison que les hommes et que leur prétendue infériorité vient uniquement de leur manque d'éducation.&lt;/p&gt; &lt;p&gt;Mary Astell fut aussi une polémiste redoutée, qui débattit avec les penseurs les plus en vue de son temps, dont John Locke et le philosophe John Norris, avec qui elle échangea des lettres sur l'amour de Dieu. Elle fonda à Chelsea une école de charité pour les filles pauvres, qu'elle soutint jusqu'à sa mort. Son idée d'une communauté de femmes consacrée à l'étude, jugée trop proche des couvents catholiques, ne vit jamais le jour, mais elle inspira de nombreuses féministes après elle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Réflexions sur le mariage&lt;/em&gt; (1700), elle critique avec ironie la condition des épouses, soumises à un pouvoir absolu de leur mari. Elle retourne contre ses adversaires les idées de John Locke : « si tous les hommes naissent libres, comment se fait-il que toutes les femmes naissent esclaves ? ». Anglicane conservatrice en politique, elle n'en fut pas moins l'une des premières à penser la domination des femmes comme une question philosophique et politique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J93" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Française</t>
+          <t xml:space="preserve">Britannique</t>
         </is>
       </c>
       <c r="K93" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; metaphysique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L93" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rationalisme ; Lumières</t>
+          <t xml:space="preserve">Rationalisme ; Féminisme</t>
         </is>
       </c>
       <c r="M93" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">mathématicienne et philosophe française des Lumières, traductrice de Newton et penseuse du bonheur.</t>
+          <t xml:space="preserve">philosophe anglaise, considérée comme l'une des premières féministes, qui défendit l'éducation des femmes.</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6815,31 +6828,28 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
-      </c>
-      <c r="P93">
-        <v>2</v>
       </c>
     </row>
     <row r="94" ht="130.5" customHeight="1" s="39">
       <c r="A94" s="47">
-        <v>1748</v>
+        <v>1706</v>
       </c>
       <c r="B94" s="47">
-        <v>1793</v>
+        <v>1749</v>
       </c>
       <c r="C94" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748 - 1793</t>
+          <t xml:space="preserve">1706 - 1749</t>
         </is>
       </c>
       <c r="D94" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olympe de GOUGES</t>
+          <t xml:space="preserve">Émilie du CHÂTELET</t>
         </is>
       </c>
       <c r="E94" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympe_de_Gouges"  title=" Wikipedia"&gt;Olympe de GOUGES&lt;/a&gt; (1748-1793), de son vrai nom Marie Gouze, est une femme de lettres et une femme politique française. Née à Montauban dans un milieu modeste, veuve très jeune, elle s'installa à Paris où elle écrivit des pièces de théâtre, dont une dénonçant l'esclavage des Noirs, qui fit scandale.&lt;/p&gt; &lt;p&gt;Pendant la Révolution française, elle publia de nombreuses brochures sur les questions sociales et politiques : aide aux pauvres, divorce, protection des enfants nés hors mariage. En 1791, elle rédigea la &lt;em&gt;Déclaration des droits de la femme et de la citoyenne&lt;/em&gt;, qui reprend article par article la Déclaration de 1789 pour montrer qu'elle exclut la moitié de l'humanité. Elle y écrit : « La femme a le droit de monter sur l'échafaud ; elle doit avoir également celui de monter à la tribune ».&lt;/p&gt; &lt;p&gt;Olympe de Gouges réclamait aussi l'accès des femmes à toutes les fonctions publiques, le droit de vote, le partage des biens entre époux et le droit de rechercher la paternité. Dans le postambule de sa Déclaration, elle appelle les femmes à se réveiller et à reconnaître leurs droits. Sa pensée associe l'égalité des sexes, l'abolition de l'esclavage et la justice sociale, bien avant que ces combats soient reconnus.&lt;/p&gt; &lt;p&gt;Proche des Girondins, elle critiqua ouvertement Robespierre et la Terreur. Arrêtée pour ses écrits, elle fut condamnée à mort et guillotinée le 3 novembre 1793. Longtemps caricaturée, elle est aujourd'hui considérée comme une pionnière du féminisme et de la défense des droits humains.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Émilie_du_Châtelet"  title=" Wikipedia"&gt;Émilie du CHÂTELET&lt;/a&gt; (1706-1749) est une mathématicienne, physicienne et philosophe française des Lumières. Issue de l'aristocratie, elle reçut une éducation rare pour une fille, en latin, en mathématiques et en sciences. Compagne de Voltaire pendant quinze ans, elle fit de leur château de Cirey un véritable centre d'étude, où ils travaillaient côte à côte.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Institutions de physique&lt;/em&gt; (1740) tentent de concilier la physique de Newton et la métaphysique de Leibniz, en particulier le principe de raison suffisante. Elle participa à la grande controverse sur la notion de « force vive », en montrant que l'énergie d'un corps en mouvement dépend du carré de sa vitesse, une idée essentielle pour la physique moderne.&lt;/p&gt; &lt;p&gt;Elle entretint une correspondance avec les plus grands savants de son temps, comme les mathématiciens Maupertuis et Clairaut, et fut la première femme dont un mémoire scientifique, sur la nature du feu, fut publié par l'Académie des sciences de Paris en 1738. Elle ne pouvait pourtant pas en être membre, et il lui arriva de se déguiser en homme pour entrer dans les cafés où se retrouvaient les savants.&lt;/p&gt; &lt;p&gt;Son œuvre majeure est la traduction commentée en français des &lt;em&gt;Principes mathématiques de la philosophie naturelle&lt;/em&gt; de Newton, achevée juste avant sa mort en couches, à 42 ans. Elle reste aujourd'hui la seule traduction française complète de ce texte fondateur. Dans son &lt;em&gt;Discours sur le bonheur&lt;/em&gt;, elle fait de l'étude et de la passion du savoir une source de bonheur indépendante des autres, notamment pour les femmes, exclues de tant d'autres chemins de la gloire.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J94" s="38" t="inlineStr">
@@ -6849,17 +6859,17 @@
       </c>
       <c r="K94" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
         </is>
       </c>
       <c r="L94" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Féminisme ; Lumières</t>
+          <t xml:space="preserve">Rationalisme ; Lumières</t>
         </is>
       </c>
       <c r="M94" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">femme de lettres et révolutionnaire française, autrice de la Déclaration des droits de la femme et de la citoyenne.</t>
+          <t xml:space="preserve">mathématicienne et philosophe française des Lumières, traductrice de Newton et penseuse du bonheur.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -6878,56 +6888,49 @@
     </row>
     <row r="95" ht="130.5" customHeight="1" s="39">
       <c r="A95" s="47">
-        <v>1550</v>
-      </c>
-      <c r="B95" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1623</t>
-        </is>
+        <v>1748</v>
+      </c>
+      <c r="B95" s="47">
+        <v>1793</v>
       </c>
       <c r="C95" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550 – 1623</t>
+          <t xml:space="preserve">1748 - 1793</t>
         </is>
       </c>
       <c r="D95" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisco SANCHES</t>
+          <t xml:space="preserve">Olympe de GOUGES</t>
         </is>
       </c>
       <c r="E95" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Sanchez" title=" Wikipedia"&gt;Francisco SANCHES&lt;/a&gt; est un médecin et philosophe d’origine portugaise, l’un des grands sceptiques de la Renaissance. Né vers 1550, à Braga ou à Tui, dans une famille de juifs convertis, que la menace de l’Inquisition pousse à quitter la péninsule Ibérique, il grandit à Bordeaux. Il étudie la médecine à Montpellier, séjourne en Italie, puis s’installe à Toulouse, où il exerce la médecine à l’hôpital et enseigne la philosophie et la médecine à l’université jusqu’à sa mort en 1623. Il serait un parent de &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne" title=" Wikipedia"&gt;Montaigne&lt;/a&gt;, par la mère de celui-ci.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Que rien ne se sait&lt;/em&gt; (&lt;em&gt;Quod nihil scitur&lt;/em&gt;), publié à Lyon en 1581, attaque la science des écoles, fondée sur Aristote : ses définitions ne sont que des mots, ses syllogismes ne font que répéter ce qu’on savait déjà, et l’on croit savoir quand on ne fait que nommer. La connaissance parfaite d’une chose supposerait de la connaître dans toutes ses causes et ses relations avec tout le reste, ce qui est impossible à un esprit fini. Il commence chaque argument par une question et termine son livre par un « Quoi ? » ironique.&lt;/p&gt; &lt;p&gt;Mais son &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_%28philosophie%29" title=" Wikipedia"&gt;scepticisme&lt;/a&gt; n’est pas un renoncement. Faute de savoir parfait, il faut s’en remettre à l’observation attentive et à l’expérience, comme le fait le médecin au chevet des malades, et avancer prudemment de jugement en jugement. Il annonce ainsi, avant Bacon et Descartes, l’esprit de la méthode expérimentale. Son œuvre, contemporaine des &lt;em&gt;Essais&lt;/em&gt; de Montaigne, a été redécouverte au XXe siècle comme un moment important du doute moderne.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/sanches-mini.webp</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympe_de_Gouges"  title=" Wikipedia"&gt;Olympe de GOUGES&lt;/a&gt; (1748-1793), de son vrai nom Marie Gouze, est une femme de lettres et une femme politique française. Née à Montauban dans un milieu modeste, veuve très jeune, elle s'installa à Paris où elle écrivit des pièces de théâtre, dont une dénonçant l'esclavage des Noirs, qui fit scandale.&lt;/p&gt; &lt;p&gt;Pendant la Révolution française, elle publia de nombreuses brochures sur les questions sociales et politiques : aide aux pauvres, divorce, protection des enfants nés hors mariage. En 1791, elle rédigea la &lt;em&gt;Déclaration des droits de la femme et de la citoyenne&lt;/em&gt;, qui reprend article par article la Déclaration de 1789 pour montrer qu'elle exclut la moitié de l'humanité. Elle y écrit : « La femme a le droit de monter sur l'échafaud ; elle doit avoir également celui de monter à la tribune ».&lt;/p&gt; &lt;p&gt;Olympe de Gouges réclamait aussi l'accès des femmes à toutes les fonctions publiques, le droit de vote, le partage des biens entre époux et le droit de rechercher la paternité. Dans le postambule de sa Déclaration, elle appelle les femmes à se réveiller et à reconnaître leurs droits. Sa pensée associe l'égalité des sexes, l'abolition de l'esclavage et la justice sociale, bien avant que ces combats soient reconnus.&lt;/p&gt; &lt;p&gt;Proche des Girondins, elle critiqua ouvertement Robespierre et la Terreur. Arrêtée pour ses écrits, elle fut condamnée à mort et guillotinée le 3 novembre 1793. Longtemps caricaturée, elle est aujourd'hui considérée comme une pionnière du féminisme et de la défense des droits humains.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J95" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portugaise</t>
+          <t xml:space="preserve">Française</t>
         </is>
       </c>
       <c r="K95" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L95" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scepticisme</t>
+          <t xml:space="preserve">Féminisme ; Lumières</t>
         </is>
       </c>
       <c r="M95" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">médecin et philosophe sceptique d’origine portugaise, auteur de Que rien ne se sait.</t>
+          <t xml:space="preserve">femme de lettres et révolutionnaire française, autrice de la Déclaration des droits de la femme et de la citoyenne.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -6941,31 +6944,31 @@
     </row>
     <row r="96" ht="130.5" customHeight="1" s="39">
       <c r="A96" s="47">
-        <v>1608</v>
+        <v>1550</v>
       </c>
       <c r="B96" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697</t>
+          <t xml:space="preserve">1623</t>
         </is>
       </c>
       <c r="C96" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608 – 1697</t>
+          <t xml:space="preserve">1550 – 1623</t>
         </is>
       </c>
       <c r="D96" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">António VIEIRA</t>
+          <t xml:space="preserve">Francisco SANCHES</t>
         </is>
       </c>
       <c r="E96" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ant%C3%B3nio_Vieira" title=" Wikipedia"&gt;António VIEIRA&lt;/a&gt; est un prêtre jésuite portugais, prédicateur, diplomate et écrivain, l’un des plus grands prosateurs de la langue portugaise. Né à Lisbonne, il part enfant pour le Brésil, à Bahia, où il entre chez les jésuites et apprend les langues indiennes. Ses sermons, d’une éloquence baroque éblouissante, le rendent célèbre : il en a laissé plus de deux cents. Conseiller du roi Jean IV après la restauration de l’indépendance portugaise en 1640, il est chargé de missions diplomatiques en France, en Hollande et à Rome.&lt;/p&gt; &lt;p&gt;Il prend la défense des Indiens d’Amazonie, réduits en esclavage par les colons, et se fait de puissants ennemis : son &lt;em&gt;Sermon de saint Antoine aux poissons&lt;/em&gt; (1654), où il prêche aux poissons faute d’être écouté des hommes, est une satire célèbre des colons. Ses adversaires obtiennent son expulsion du Maranhão en 1661. Dans plusieurs sermons, il dénonce aussi la souffrance des esclaves africains, tout en restant prisonnier des idées de son temps. Il plaide enfin pour les « nouveaux chrétiens », juifs convertis persécutés au Portugal, et demande que l’&lt;a href="https://fr.wikipedia.org/wiki/Inquisition_portugaise" title=" Wikipedia"&gt;Inquisition&lt;/a&gt; cesse de les poursuivre et que leurs capitaux servent au royaume.&lt;/p&gt; &lt;p&gt;Ses rêves prophétiques d’un &lt;a href="https://fr.wikipedia.org/wiki/Quint-Empire" title=" Wikipedia"&gt;Cinquième Empire&lt;/a&gt;, un règne universel de paix et de justice dont le Portugal serait l’instrument, lui valent d’être poursuivi par l’Inquisition, qui l’emprisonne de 1665 à 1667. Libéré, il obtient du pape une protection contre elle. Il passe ses dernières années à Bahia, où il meurt en 1697. Le poète Fernando Pessoa l’appelait « l’empereur de la langue portugaise ».&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Sanchez" title=" Wikipedia"&gt;Francisco SANCHES&lt;/a&gt; est un médecin et philosophe d’origine portugaise, l’un des grands sceptiques de la Renaissance. Né vers 1550, à Braga ou à Tui, dans une famille de juifs convertis, que la menace de l’Inquisition pousse à quitter la péninsule Ibérique, il grandit à Bordeaux. Il étudie la médecine à Montpellier, séjourne en Italie, puis s’installe à Toulouse, où il exerce la médecine à l’hôpital et enseigne la philosophie et la médecine à l’université jusqu’à sa mort en 1623. Il serait un parent de &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne" title=" Wikipedia"&gt;Montaigne&lt;/a&gt;, par la mère de celui-ci.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Que rien ne se sait&lt;/em&gt; (&lt;em&gt;Quod nihil scitur&lt;/em&gt;), publié à Lyon en 1581, attaque la science des écoles, fondée sur Aristote : ses définitions ne sont que des mots, ses syllogismes ne font que répéter ce qu’on savait déjà, et l’on croit savoir quand on ne fait que nommer. La connaissance parfaite d’une chose supposerait de la connaître dans toutes ses causes et ses relations avec tout le reste, ce qui est impossible à un esprit fini. Il commence chaque argument par une question et termine son livre par un « Quoi ? » ironique.&lt;/p&gt; &lt;p&gt;Mais son &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_%28philosophie%29" title=" Wikipedia"&gt;scepticisme&lt;/a&gt; n’est pas un renoncement. Faute de savoir parfait, il faut s’en remettre à l’observation attentive et à l’expérience, comme le fait le médecin au chevet des malades, et avancer prudemment de jugement en jugement. Il annonce ainsi, avant Bacon et Descartes, l’esprit de la méthode expérimentale. Son œuvre, contemporaine des &lt;em&gt;Essais&lt;/em&gt; de Montaigne, a été redécouverte au XXe siècle comme un moment important du doute moderne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/vieira-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sanches-mini.webp</t>
         </is>
       </c>
       <c r="J96" s="38" t="inlineStr">
@@ -6975,17 +6978,22 @@
       </c>
       <c r="K96" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">epistemologie</t>
         </is>
       </c>
       <c r="L96" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme</t>
+          <t xml:space="preserve">Scepticisme</t>
         </is>
       </c>
       <c r="M96" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">jésuite portugais, prédicateur baroque, défenseur des Indiens du Brésil et des nouveaux chrétiens.</t>
+          <t xml:space="preserve">médecin et philosophe sceptique d’origine portugaise, auteur de Que rien ne se sait.</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6999,51 +7007,51 @@
     </row>
     <row r="97" ht="130.5" customHeight="1" s="39">
       <c r="A97" s="47">
-        <v>1530</v>
+        <v>1608</v>
       </c>
       <c r="B97" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1596</t>
+          <t xml:space="preserve">1697</t>
         </is>
       </c>
       <c r="C97" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">vers 1530 – 1596</t>
+          <t xml:space="preserve">1608 – 1697</t>
         </is>
       </c>
       <c r="D97" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jean BODIN</t>
+          <t xml:space="preserve">António VIEIRA</t>
         </is>
       </c>
       <c r="E97" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Bodin" title=" Wikipedia"&gt;Jean BODIN&lt;/a&gt; est un juriste, philosophe et économiste français de la Renaissance, le grand théoricien de la &lt;a href="https://fr.wikipedia.org/wiki/Souverainet%C3%A9" title=" Wikipedia"&gt;souveraineté&lt;/a&gt;. Né à Angers vers 1530, il est d’abord moine carme, puis étudie et enseigne le droit à Toulouse avant de devenir avocat au Parlement de Paris. Il vit les guerres de Religion qui déchirent la France. Député du tiers état aux états généraux de Blois en 1576, il s’oppose à la reprise de la guerre contre les protestants et à la vente du domaine royal. Il finit procureur du roi à Laon, où il meurt de la peste en 1596.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Six Livres de la République&lt;/em&gt; (1576), il définit l’État par la souveraineté, « puissance absolue et perpétuelle d’une République ». Elle est indivisible, et son premier attribut est de « donner et casser la loi » sans le consentement de personne. Le souverain reste pourtant soumis aux lois de Dieu et de la nature : il doit respecter la propriété de ses sujets et ne peut lever d’impôt sans leur accord. Écrite contre l’anarchie des guerres civiles, cette théorie prépare la monarchie absolue et toute la pensée moderne de l’État, de Hobbes à Rousseau. Bodin y expose aussi une théorie des climats que reprendra Montesquieu.&lt;/p&gt; &lt;p&gt;Il est aussi l’un des premiers économistes. Dans sa &lt;em&gt;Réponse aux paradoxes de M. de Malestroit&lt;/em&gt; (1568), il explique la hausse des prix qui frappe l’Europe par l’afflux de l’or et de l’argent d’Amérique : c’est une première forme de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_quantitative_de_la_monnaie" title=" Wikipedia"&gt;théorie quantitative de la monnaie&lt;/a&gt;. Partisan d’un commerce actif et de la protection des manufactures, il annonce le &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt;. Son &lt;em&gt;Colloque des sept sages&lt;/em&gt; fait dialoguer un catholique, un luthérien, un calviniste, un juif, un musulman, un partisan de la religion naturelle et un sceptique, sans désigner de vainqueur : un plaidoyer pour la tolérance. Mais le même Bodin publie en 1580 une &lt;em&gt;Démonomanie des sorciers&lt;/em&gt; qui encourage leur persécution.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ant%C3%B3nio_Vieira" title=" Wikipedia"&gt;António VIEIRA&lt;/a&gt; est un prêtre jésuite portugais, prédicateur, diplomate et écrivain, l’un des plus grands prosateurs de la langue portugaise. Né à Lisbonne, il part enfant pour le Brésil, à Bahia, où il entre chez les jésuites et apprend les langues indiennes. Ses sermons, d’une éloquence baroque éblouissante, le rendent célèbre : il en a laissé plus de deux cents. Conseiller du roi Jean IV après la restauration de l’indépendance portugaise en 1640, il est chargé de missions diplomatiques en France, en Hollande et à Rome.&lt;/p&gt; &lt;p&gt;Il prend la défense des Indiens d’Amazonie, réduits en esclavage par les colons, et se fait de puissants ennemis : son &lt;em&gt;Sermon de saint Antoine aux poissons&lt;/em&gt; (1654), où il prêche aux poissons faute d’être écouté des hommes, est une satire célèbre des colons. Ses adversaires obtiennent son expulsion du Maranhão en 1661. Dans plusieurs sermons, il dénonce aussi la souffrance des esclaves africains, tout en restant prisonnier des idées de son temps. Il plaide enfin pour les « nouveaux chrétiens », juifs convertis persécutés au Portugal, et demande que l’&lt;a href="https://fr.wikipedia.org/wiki/Inquisition_portugaise" title=" Wikipedia"&gt;Inquisition&lt;/a&gt; cesse de les poursuivre et que leurs capitaux servent au royaume.&lt;/p&gt; &lt;p&gt;Ses rêves prophétiques d’un &lt;a href="https://fr.wikipedia.org/wiki/Quint-Empire" title=" Wikipedia"&gt;Cinquième Empire&lt;/a&gt;, un règne universel de paix et de justice dont le Portugal serait l’instrument, lui valent d’être poursuivi par l’Inquisition, qui l’emprisonne de 1665 à 1667. Libéré, il obtient du pape une protection contre elle. Il passe ses dernières années à Bahia, où il meurt en 1697. Le poète Fernando Pessoa l’appelait « l’empereur de la langue portugaise ».&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/bodin-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vieira-mini.webp</t>
         </is>
       </c>
       <c r="J97" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Française</t>
+          <t xml:space="preserve">Portugaise</t>
         </is>
       </c>
       <c r="K97" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; spiritualite</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L97" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Mercantilisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="M97" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">juriste et philosophe français, théoricien de la souveraineté et pionnier de la pensée économique.</t>
+          <t xml:space="preserve">jésuite portugais, prédicateur baroque, défenseur des Indiens du Brésil et des nouveaux chrétiens.</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7051,35 +7059,37 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P97"/>
+      <c r="P97">
+        <v>2</v>
+      </c>
     </row>
     <row r="98" ht="130.5" customHeight="1" s="39">
       <c r="A98" s="47">
-        <v>1575</v>
+        <v>1530</v>
       </c>
       <c r="B98" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1621</t>
+          <t xml:space="preserve">1596</t>
         </is>
       </c>
       <c r="C98" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">vers 1575 – 1621</t>
+          <t xml:space="preserve">vers 1530 – 1596</t>
         </is>
       </c>
       <c r="D98" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antoine de MONTCHRESTIEN</t>
+          <t xml:space="preserve">Jean BODIN</t>
         </is>
       </c>
       <c r="E98" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine_de_Montchrestien" title=" Wikipedia"&gt;Antoine de MONTCHRESTIEN&lt;/a&gt; est un dramaturge et économiste français, l’inventeur de l’expression « &lt;a href="https://fr.wikipedia.org/wiki/%C3%89conomie_politique" title=" Wikipedia"&gt;économie politique&lt;/a&gt; ». Né à Falaise, en Normandie, vers 1575, fils d’un apothicaire, il se fait d’abord connaître comme poète tragique : sa tragédie &lt;em&gt;L’Écossaise&lt;/em&gt;, sur la mort de Marie Stuart, est l’une des premières pièces françaises consacrées à l’histoire récente. Après avoir tué un adversaire en duel, il s’exile en Angleterre et aux Pays-Bas, où il observe l’essor du commerce et des manufactures.&lt;/p&gt; &lt;p&gt;Revenu en France, il fonde une fabrique de couteaux et d’outils, et publie en 1615 son &lt;em&gt;Traité de l’économie politique&lt;/em&gt;, dédié au jeune Louis XIII et à sa mère Marie de Médicis. Le titre est nouveau : l’« économie », qui désignait chez Aristote la gestion de la maison, devient la science de la richesse de tout le royaume. Pour Montchrestien, la vraie richesse n’est pas seulement l’or, mais le travail des hommes et l’abondance des choses nécessaires. Le roi doit développer les manufactures, mettre les oisifs au travail, réserver le marché national aux produits français, protéger la marine et fonder des colonies. Il dénonce les marchands étrangers qui s’enrichissent aux dépens de la France.&lt;/p&gt; &lt;p&gt;Ces idées font de lui l’un des grands auteurs du &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt; français, que la politique de Colbert mettra en œuvre un demi-siècle plus tard. Protestant, Montchrestien prend part au soulèvement huguenot de 1621 ; il est tué dans une embuscade près de Domfront, et son corps est jugé, puis brûlé. Son traité, longtemps oublié, a été redécouvert au XIXe siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Bodin" title=" Wikipedia"&gt;Jean BODIN&lt;/a&gt; est un juriste, philosophe et économiste français de la Renaissance, le grand théoricien de la &lt;a href="https://fr.wikipedia.org/wiki/Souverainet%C3%A9" title=" Wikipedia"&gt;souveraineté&lt;/a&gt;. Né à Angers vers 1530, il est d’abord moine carme, puis étudie et enseigne le droit à Toulouse avant de devenir avocat au Parlement de Paris. Il vit les guerres de Religion qui déchirent la France. Député du tiers état aux états généraux de Blois en 1576, il s’oppose à la reprise de la guerre contre les protestants et à la vente du domaine royal. Il finit procureur du roi à Laon, où il meurt de la peste en 1596.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Six Livres de la République&lt;/em&gt; (1576), il définit l’État par la souveraineté, « puissance absolue et perpétuelle d’une République ». Elle est indivisible, et son premier attribut est de « donner et casser la loi » sans le consentement de personne. Le souverain reste pourtant soumis aux lois de Dieu et de la nature : il doit respecter la propriété de ses sujets et ne peut lever d’impôt sans leur accord. Écrite contre l’anarchie des guerres civiles, cette théorie prépare la monarchie absolue et toute la pensée moderne de l’État, de Hobbes à Rousseau. Bodin y expose aussi une théorie des climats que reprendra Montesquieu.&lt;/p&gt; &lt;p&gt;Il est aussi l’un des premiers économistes. Dans sa &lt;em&gt;Réponse aux paradoxes de M. de Malestroit&lt;/em&gt; (1568), il explique la hausse des prix qui frappe l’Europe par l’afflux de l’or et de l’argent d’Amérique : c’est une première forme de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_quantitative_de_la_monnaie" title=" Wikipedia"&gt;théorie quantitative de la monnaie&lt;/a&gt;. Partisan d’un commerce actif et de la protection des manufactures, il annonce le &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt;. Son &lt;em&gt;Colloque des sept sages&lt;/em&gt; fait dialoguer un catholique, un luthérien, un calviniste, un juif, un musulman, un partisan de la religion naturelle et un sceptique, sans désigner de vainqueur : un plaidoyer pour la tolérance. Mais le même Bodin publie en 1580 une &lt;em&gt;Démonomanie des sorciers&lt;/em&gt; qui encourage leur persécution.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/montchrestien-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/bodin-mini.webp</t>
         </is>
       </c>
       <c r="J98" s="38" t="inlineStr">
@@ -7089,17 +7099,17 @@
       </c>
       <c r="K98" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique</t>
+          <t xml:space="preserve">politique ; spiritualite</t>
         </is>
       </c>
       <c r="L98" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercantilisme</t>
+          <t xml:space="preserve">Humanisme ; Mercantilisme</t>
         </is>
       </c>
       <c r="M98" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">dramaturge et économiste français, inventeur de l’expression « économie politique ».</t>
+          <t xml:space="preserve">juriste et philosophe français, théoricien de la souveraineté et pionnier de la pensée économique.</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7111,51 +7121,51 @@
     </row>
     <row r="99" ht="130.5" customHeight="1" s="39">
       <c r="A99" s="47">
-        <v>1680</v>
+        <v>1575</v>
       </c>
       <c r="B99" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1732</t>
+          <t xml:space="preserve">1621</t>
         </is>
       </c>
       <c r="C99" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680 – 1732</t>
+          <t xml:space="preserve">vers 1575 – 1621</t>
         </is>
       </c>
       <c r="D99" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arthur COLLIER</t>
+          <t xml:space="preserve">Antoine de MONTCHRESTIEN</t>
         </is>
       </c>
       <c r="E99" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Arthur_Collier" title=" Wikipedia (en)"&gt;Arthur COLLIER&lt;/a&gt; est un pasteur et philosophe anglais. Né en 1680 à Steeple Langford, dans le Wiltshire, dans une famille de pasteurs, il étudie à Oxford et succède à son père comme recteur de la paroisse de Langford Magna, où il passe toute sa vie. Lecteur de Descartes et surtout de Malebranche, il réfléchit dès 1703 à la question de l’existence du monde extérieur.&lt;/p&gt; &lt;p&gt;En 1713, il publie la &lt;em&gt;Clavis Universalis&lt;/em&gt;, « la clé universelle », sous-titrée « nouvelle recherche de la vérité, démonstration de la non-existence ou de l’impossibilité d’un monde extérieur ». Il y soutient, comme &lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley" title=" Wikipedia"&gt;Berkeley&lt;/a&gt; dans ses &lt;em&gt;Principes&lt;/em&gt; de 1710, l’&lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Wikipedia"&gt;immatérialisme&lt;/a&gt; : le monde visible n’existe que dans l’esprit qui le perçoit, et une matière extérieure, indépendante de toute perception, est une idée contradictoire. Il en donne plusieurs preuves : l’idée d’un monde extérieur conduit à dire qu’il est à la fois fini et infini, divisible à l’infini et pourtant composé de parties.&lt;/p&gt; &lt;p&gt;Collier affirme être arrivé à ces conclusions seul, sans avoir lu Berkeley, et les historiens le croient généralement : les deux auteurs partent de Malebranche, mais avec des arguments différents. Son livre passe presque inaperçu de son vivant. Il meurt en 1732. Redécouvert au XVIIIe siècle par Thomas Reid, puis réédité au XIXe siècle, il est aujourd’hui considéré comme le second fondateur de l’immatérialisme.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine_de_Montchrestien" title=" Wikipedia"&gt;Antoine de MONTCHRESTIEN&lt;/a&gt; est un dramaturge et économiste français, l’inventeur de l’expression « &lt;a href="https://fr.wikipedia.org/wiki/%C3%89conomie_politique" title=" Wikipedia"&gt;économie politique&lt;/a&gt; ». Né à Falaise, en Normandie, vers 1575, fils d’un apothicaire, il se fait d’abord connaître comme poète tragique : sa tragédie &lt;em&gt;L’Écossaise&lt;/em&gt;, sur la mort de Marie Stuart, est l’une des premières pièces françaises consacrées à l’histoire récente. Après avoir tué un adversaire en duel, il s’exile en Angleterre et aux Pays-Bas, où il observe l’essor du commerce et des manufactures.&lt;/p&gt; &lt;p&gt;Revenu en France, il fonde une fabrique de couteaux et d’outils, et publie en 1615 son &lt;em&gt;Traité de l’économie politique&lt;/em&gt;, dédié au jeune Louis XIII et à sa mère Marie de Médicis. Le titre est nouveau : l’« économie », qui désignait chez Aristote la gestion de la maison, devient la science de la richesse de tout le royaume. Pour Montchrestien, la vraie richesse n’est pas seulement l’or, mais le travail des hommes et l’abondance des choses nécessaires. Le roi doit développer les manufactures, mettre les oisifs au travail, réserver le marché national aux produits français, protéger la marine et fonder des colonies. Il dénonce les marchands étrangers qui s’enrichissent aux dépens de la France.&lt;/p&gt; &lt;p&gt;Ces idées font de lui l’un des grands auteurs du &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt; français, que la politique de Colbert mettra en œuvre un demi-siècle plus tard. Protestant, Montchrestien prend part au soulèvement huguenot de 1621 ; il est tué dans une embuscade près de Domfront, et son corps est jugé, puis brûlé. Son traité, longtemps oublié, a été redécouvert au XIXe siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/collier-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/montchrestien-mini.webp</t>
         </is>
       </c>
       <c r="J99" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britannique</t>
+          <t xml:space="preserve">Française</t>
         </is>
       </c>
       <c r="K99" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique</t>
+          <t xml:space="preserve">politique</t>
         </is>
       </c>
       <c r="L99" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Immatérialisme</t>
+          <t xml:space="preserve">Mercantilisme</t>
         </is>
       </c>
       <c r="M99" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">pasteur et philosophe anglais qui défendit l’immatérialisme en même temps que Berkeley.</t>
+          <t xml:space="preserve">dramaturge et économiste français, inventeur de l’expression « économie politique ».</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7167,51 +7177,51 @@
     </row>
     <row r="100" ht="130.5" customHeight="1" s="39">
       <c r="A100" s="47">
-        <v>1657</v>
+        <v>1680</v>
       </c>
       <c r="B100" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1757</t>
+          <t xml:space="preserve">1732</t>
         </is>
       </c>
       <c r="C100" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1657 – 1757</t>
+          <t xml:space="preserve">1680 – 1732</t>
         </is>
       </c>
       <c r="D100" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernard Le Bouyer de FONTENELLE</t>
+          <t xml:space="preserve">Arthur COLLIER</t>
         </is>
       </c>
       <c r="E100" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Le_Bouyer_de_Fontenelle" title=" Wikipedia"&gt;Bernard Le Bouyer de FONTENELLE&lt;/a&gt; est un écrivain et savant français, l’un des grands passeurs entre l’âge classique et les &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt;. Né à Rouen en 1657, neveu de Pierre et Thomas Corneille, il abandonne vite le barreau pour les lettres et le théâtre, sans grand succès, avant de trouver sa voie dans la diffusion des sciences. Dans les &lt;em&gt;Entretiens sur la pluralité des mondes&lt;/em&gt; (1686), un philosophe explique à une marquise, au cours de promenades nocturnes, le système de Copernic et les tourbillons de Descartes, et imagine des habitants sur les autres planètes.&lt;/p&gt; &lt;p&gt;Ce livre élégant, l’un des premiers grands succès de la vulgarisation scientifique, enlève à la Terre et à l’homme leur place au centre du monde. L’année suivante, l’&lt;em&gt;Histoire des oracles&lt;/em&gt; (1687) montre que les oracles païens n’étaient pas l’œuvre des démons, mais des tromperies des prêtres : sous couvert d’Antiquité, c’est toute la crédulité religieuse qui est visée. Dans la querelle des Anciens et des Modernes, sa &lt;em&gt;Digression&lt;/em&gt; de 1688 prend le parti des Modernes : la nature n’a pas changé, et les connaissances s’accumulent au fil des siècles, ce qui annonce l’idée de progrès.&lt;/p&gt; &lt;p&gt;Élu à l’Académie française en 1691, il est de 1697 à 1740 le secrétaire perpétuel de l’Académie royale des sciences, dont il rédige chaque année l’histoire et les éloges des savants disparus, rendant accessibles les travaux de Leibniz ou de Newton. Fidèle jusqu’au bout à la physique de &lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Descartes" title=" Wikipedia"&gt;Descartes&lt;/a&gt;, il défend encore les tourbillons contre l’attraction newtonienne. Il meurt à Paris en 1757, à presque cent ans.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Arthur_Collier" title=" Wikipedia (en)"&gt;Arthur COLLIER&lt;/a&gt; est un pasteur et philosophe anglais. Né en 1680 à Steeple Langford, dans le Wiltshire, dans une famille de pasteurs, il étudie à Oxford et succède à son père comme recteur de la paroisse de Langford Magna, où il passe toute sa vie. Lecteur de Descartes et surtout de Malebranche, il réfléchit dès 1703 à la question de l’existence du monde extérieur.&lt;/p&gt; &lt;p&gt;En 1713, il publie la &lt;em&gt;Clavis Universalis&lt;/em&gt;, « la clé universelle », sous-titrée « nouvelle recherche de la vérité, démonstration de la non-existence ou de l’impossibilité d’un monde extérieur ». Il y soutient, comme &lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley" title=" Wikipedia"&gt;Berkeley&lt;/a&gt; dans ses &lt;em&gt;Principes&lt;/em&gt; de 1710, l’&lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Wikipedia"&gt;immatérialisme&lt;/a&gt; : le monde visible n’existe que dans l’esprit qui le perçoit, et une matière extérieure, indépendante de toute perception, est une idée contradictoire. Il en donne plusieurs preuves : l’idée d’un monde extérieur conduit à dire qu’il est à la fois fini et infini, divisible à l’infini et pourtant composé de parties.&lt;/p&gt; &lt;p&gt;Collier affirme être arrivé à ces conclusions seul, sans avoir lu Berkeley, et les historiens le croient généralement : les deux auteurs partent de Malebranche, mais avec des arguments différents. Son livre passe presque inaperçu de son vivant. Il meurt en 1732. Redécouvert au XVIIIe siècle par Thomas Reid, puis réédité au XIXe siècle, il est aujourd’hui considéré comme le second fondateur de l’immatérialisme.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/fontenelle-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/collier-mini.webp</t>
         </is>
       </c>
       <c r="J100" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Française</t>
+          <t xml:space="preserve">Britannique</t>
         </is>
       </c>
       <c r="K100" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; metaphysique</t>
+          <t xml:space="preserve">metaphysique</t>
         </is>
       </c>
       <c r="L100" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartésianisme ; Lumières</t>
+          <t xml:space="preserve">Immatérialisme</t>
         </is>
       </c>
       <c r="M100" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">écrivain français, vulgarisateur de la science cartésienne et précurseur des Lumières.</t>
+          <t xml:space="preserve">pasteur et philosophe anglais qui défendit l’immatérialisme en même temps que Berkeley.</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7247,37 +7257,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" display="https://www.laphilo.fr/pho/pnicole-mini.webp" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baruch_Spinoza&quot;  title=&quot; Wikipedia&quot;&gt; Baruch SPINOZA&lt;/a&gt; était un philosophe hollandais et un penseur influent en opposition à Descartes en son époque. &lt;/p&gt; &lt;p&gt; Sa philosophie &lt;a href=&quot;https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le déterminisme par le Précepteur&quot;&gt;Déterministe.&lt;/a&gt; se caractérise par sa vision &lt;a href=&quot;https://fr.wikipedia.org/wiki/Monisme&quot;    title=&quot;Le monisme est la position philosophique qui affirme l'unité indivisible de l'être&quot;&gt;moniste&lt;/a&gt; de l'univers, selon laquelle tout ce qui existe est une expression de la même substance divine, qu'il appelle &lt;a href=&quot;https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Dieu égale nature&quot;&gt;Dieu ou Nature&lt;/a&gt; et elle est souvent associée au rationalisme, à l'athéisme et au panthéisme. &lt;/p&gt; &lt;p&gt; Pour lui, la raison est la clé de la liberté et du bonheur. Il affirme que  &lt;a href=&quot;https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos&quot;  title=&quot;Les passions tristes par Kosmos&quot;&gt;les passions.&lt;/a&gt; peuvent nous éloigner de la vérité et nous rendre esclaves de nos désirs. &lt;/p&gt; &lt;p&gt;Pour être libre, l'homme doit comprendre la nature des choses et apprendre à contrôler ses passions. Cela implique une acceptation de la nécessité et de la causalité, car tout ce qui arrive est le résultat de la nature des choses et que, de ce fait, &lt;a  href=&quot;https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;Le libre arbitre n'est il qu'une illusion? par le Précepteur&quot;&gt;le libre arbitre n'existe pas.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Dans sa célèbre œuvre &quot;L'Éthique&quot;, il élabore une théorie éthique basée sur l'idée que la raison est la clé de la liberté et du bonheur avec sa notion de &lt;a href=&quot;https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;Le conatus par le Précepteur&quot;&gt;&quot;Conatus&quot;.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; En politique, il est souvent associé à la défense de la liberté d'expression et de la tolérance religieuse. Il a écrit un ouvrage intitulé  &lt;a href=&quot;https://www.youtube.com/watch?v=Zqt0QZVrTkI&quot;   title=&quot;Le Traité TP par PrepaUp&quot;&gt;&quot;Le Traité théologico-politique&quot;&lt;/a&gt; dans lequel il soutient que la religion doit être séparée de l'État et que chacun doit être libre de pratiquer sa religion sans être persécuté.&lt;/p&gt;    &lt;audio controls title=&quot;Spinoza est il le philosophe du bonheur ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&lt;p&gt; &lt;/p&gt;" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nicolas_Malebranche&quot; title=&quot; Wikipedia&quot;&gt;Nicolas MALEBRANCHE&lt;/a&gt; était un philosophe et théologien français, connu pour ses travaux en métaphysique, en épistémologie et en philosophie de la religion. En 1660, il rejoint l'Oratoire, une congrégation religieuse catholique, où il se consacre à l'étude de la philosophie et de la théologie et il découvre les travaux de Descartes, qui auront une influence majeure sur sa pensée. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de  &lt;a href=&quot;https://www.youtube.com/watch?v=3YvitSjZ2_4&amp;t=326s&quot; title=&quot;Malebranche : Occasionalism par Leevark&quot;&gt;l'occasionalisme&lt;/a&gt;, qu'il développe dans son ouvrage majeur &quot; De la recherche de la vérité&quot;. Selon lui, les idées que nous avons des objets existent dans l'entendement divin, et c'est par la médiation de Dieu que nous accédons à ces idées. Cette théorie s'oppose à l'empirisme et à l'idée que nos perceptions sont directement causées par les objets eux-mêmes.  Il rejette l'interaction directe entre l'âme et le corps, une idée défendue par Descartes. Selon lui, l'âme et le corps ne peuvent pas agir l'un sur l'autre directement. Au lieu de cela, Dieu coordonne les états de l'âme et les états du corps de manière harmonieuse, sans qu'il y ait de causalité directe entre eux. Il a développé une théorie selon laquelle Dieu agit selon des &quot;lois générales&quot; plutôt que par des interventions particulières, ce qui laisse une place à la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Libert%C3%A9_(philosophie)&quot;  title=&quot;La liberté par Wikipedia&quot;&gt;liberté humaine&lt;/a&gt; tout en maintenant la souveraineté divine. &lt;/p&gt; &lt;p&gt;Ses oeuvres principales : &lt;/p&gt; &#10;&lt;dd&gt; -De la recherche de la vérité : Théories sur la perception, la causalité et la métaphysique.  &lt;/dd&gt; &#10;&lt;dd&gt; - Traité de la nature et de la grâce : Relation entre la grâce divine et les lois de la nature. &lt;/dd&gt;&#10;&lt;dd&gt; - Entretiens sur la métaphysique et la religion : Un dialogue qui résume et défend ses idées. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il reste une figure importante dans l'histoire de la philosophie, notamment pour sa tentative de concilier la pensée cartésienne avec une vision profondément théocentrique du monde. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;   &lt;audio controls title=&quot; L’imagination selon Descartes et Malebranche par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-16.01.2024-ITEMA_23616134-2024C48904S0016-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Voltaire&quot;   title=&quot; Wikipedia&quot;&gt; VOLTAIRE&lt;/a&gt;, de son vrai nom François-Marie Arouet, est un philosophe de l'époque des  &lt;a href=&quot;https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;t=380s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot; La philosophie des lumières par le Précepteur &quot;&gt;Lumières&lt;/a&gt; (ou Illuministe) en France. Il était aussi écrivain, poète, dramaturge et philosophe. &lt;/p&gt; &lt;p&gt;&#10;Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href=&quot;https://www.youtube.com/watch?v=XE1Z8jpVJUA&quot; title=&quot; la vie de Voltaire  par Portrait Historiques&quot;&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation . Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;&#10;Voltaire, qui était &lt;a href=&quot;https://www.youtube.com/watch?v=RO_aeh1cBgA&amp;ab_channel=Kurious&quot;   title=&quot; Regard critique sur le déîsme par Kurious &quot;&gt;déiste&lt;/a&gt; s'est opposé aux abus de l'Église catholique et a plaidé en faveur de la tolérance envers les minorités religieuses. Dans son ouvrage &lt;a href=&quot;https://www.youtube.com/watch?v=1RlS8GKL7SU&quot;  title=&quot; Voltaire-Tolérence par Culture Philo &quot;&gt;&quot;Traité sur la tolérance&quot;&lt;/a&gt;, (1763) il a condamné les persécutions religieuses et a défendu le principe selon lequel chaque individu devait être libre de pratiquer sa religion sans être inquiété. &lt;/p&gt; &lt;p&gt;&#10;Son ouvrage le plus connu est  &lt;a href=&quot;https://www.youtube.com/watch?v=kom2zFvrj5I&amp;ab_channel=T%C3%A9l%C3%A9Crayon&quot;  title=&quot; Candide de Voltaire par TéléCrayon &quot;&gt;&quot;Candide&quot;&lt;/a&gt; (1759), un conte philosophique qui critique les idées optimistes de l'époque et souligne les absurdités et les injustices du monde. &lt;/p&gt; &lt;p&gt;&#10;La contribution de Voltaire à la philosophie se caractérise par son engagement envers la raison, la liberté et la justice. Il a influencé de nombreux penseurs ultérieurs et a contribué à jeter les bases de la pensée libérale et humaniste qui a marqué les siècles suivants. Sa défense de la liberté d'expression reste une valeur fondamentale de nos sociétés démocratiques aujourd'hui. &lt;/p&gt; &lt;audio controls title=&quot;Voltaire et les Lumières par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15537-13.01.2021-ITEMA_22540842-2021C24632S0013.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)&quot;    title=&quot; Wikipedia&quot;&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href=&quot;https://www.youtube.com/watch?v=kbpEAw2gl40&quot; title=&quot; David Hartley par Crevoisier Philippe&quot;&gt; développement de la psychologie &lt;/a&gt;  , en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt; - La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la &quot;substance médullaire&quot; (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt; - La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des &quot;vibratiuncules&quot; (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs &quot;vibratiuncules&quot; respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href=&quot;https://www.youtube.com/shorts/BuqpLB9V41c&quot;  title=&quot; David Hartley par timelinephilosopher&quot;&gt;  le fondement des idées et des pensées &lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des &quot;vibratiuncules&quot; de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &quot;Observations on Man, his Frame, his Duty, and his Expectations&quot;, publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt; &#10;- L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt; &#10;- Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; " r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Julien_Offray_de_La_Mettrie&quot;    title=&quot; Wikipedia&quot;&gt;Julien Onfray de la METTRIE&lt;/a&gt;  était un philosophe et médecin français des Lumières, connu pour son &lt;a href=&quot;https://www.youtube.com/watch?v=ATn23C-jw1M&quot;  title=&quot; Traité du bonheur de la Mettrie par Voyage interieur&quot;&gt; matérialisme radical &lt;/a&gt; et son athéisme provocateur. Médecin militaire, il fut exilé de France après la publication de ses idées controversées, avant de trouver refuge auprès de Frédéric II de Prusse à Potsdam. &lt;/p&gt; &lt;p&gt; Dans L’Homme machine (1747), il affirme que l’être humain est une machine purement matérielle : l’âme n’existe pas comme substance distincte, mais émerge des processus physiques du cerveau et du corps, sans besoin de Dieu ou d’esprit immatériel. Il s’inspire de Descartes, mais pousse le mécanisme jusqu’au bout en rejetant le dualisme corps-âme.  &lt;/p&gt; &lt;p&gt; Ses écrits, comme Histoire naturelle de l’âme (1745), scandalisèrent l’Église et les autorités : ses livres furent brûlés publiquement et il perdit son poste aux Gardes-Françaises. Défenseur d’un hédonisme sensualiste, il prône le  &lt;a href=&quot;https://www.youtube.com/watch?v=FH2TDimoh7Q&quot;  title=&quot; La Mettrie ou l’art de jouir par Parole de philosophe&quot;&gt; plaisir comme seul bien moral,&lt;/a&gt;  sans morale transcendante. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés : - Histoire naturelle de l’âme (1745) : Critique du dualisme et fondement matérialiste. - L’Homme machine (1747) : Thèse principale sur l’automatisme humain. - L’Homme plante (1748) : Étend le mécanisme aux végétaux et animaux. &lt;/p&gt; &lt;p&gt; Précurseur du matérialisme moderne et de la philosophie de la vie, il influence Diderot et les Encyclopédistes, mais reste marginalisé pour son radicalisme. Il anticipe des idées sur l’évolution et la cybernétique en voyant l’humain comme un système organisé. &lt;/p&gt; &#10;" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Hume&quot;  title=&quot; Wikipedia&quot;&gt;David HUME&lt;/a&gt; était un philosophe, historien et économiste écossais de l'ère des Lumières. Il est surtout connu pour ses contributions à la philosophie empirique, la théorie de la connaissance, la métaphysique, l'éthique et l'esthétique. &lt;/p&gt; &lt;p&gt; Hume était un sceptique et a cherché à examiner de manière critique les idées préconçues et les &lt;a  href=&quot;https://www.youtube.com/watch?v=CLIoxw6TXuk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Tout n'est que croyance  par Le Précepteur&quot;&gt;croyances reçues&lt;/a&gt;. Il a rejeté les arguments métaphysiques qui ne pouvaient pas être fondés sur l'expérience directe, et a affirmé que les connaissances humaines étaient basées sur les impressions et les idées que nous en avons. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de &lt;a  href=&quot;https://www.youtube.com/watch?v=ftd3vjw9lSU&quot;  title=&quot; la causalité par Skarblown Animations&quot;&gt;la causalité&lt;/a&gt;, qui affirme que nous ne pouvons pas connaître la relation de cause à effet entre deux événements par simple observation, mais que nous sommes amenés à croire en une telle relation en raison de notre expérience passée.  &lt;/p&gt; &lt;p&gt; En éthique, il a affirmé que la morale était basée sur des sentiments plutôt que sur la raison et qu'elle ne peut pas être déduite de principes rationnels, mais doit être fondée sur l'empathie et la sympathie envers les autres.  &lt;/p&gt; &lt;p&gt; Il a également souligné l'importance du bonheur et du plaisir dans la vie, affirmant que ce sont des aspects essentiels de notre existence et de notre &lt;a  href=&quot;https://www.youtube.com/watch?v=52077nWSkPM&amp;t=11s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;l'identité par le Précepteur&quot;&gt;identité&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il a écrit sur la religion et a critiqué les arguments traditionnels pour l'existence de Dieu en affirmant que la religion était basée sur la superstition plutôt que sur la raison, et que la croyance en Dieu était fondée sur l'habitude plutôt que sur la preuve. &lt;/p&gt;  &lt;audio controls title=&quot;Pourquoi faut il lire David Hume par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22838-02.02.2022-ITEMA_22927004-2022C45539E0018-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;&#10;" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau&quot; title=&quot; Wikipedia&quot;&gt; Jean-Jacques ROUSSEAU&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Les Lumières par le Précepteur &quot;&gt; des lumières&lt;/a&gt; et écrivain suisse-français, défenseur de la liberté et de l'égalité. Il et est surtout connu pour son livre &lt;a href=&quot;https://www.youtube.com/watch?v=tToAS8pUXzU&quot;   title=&quot;Le texte fondateur par Alain Bajomée &quot;&gt;&quot;Du contrat social&quot;&lt;/a&gt; , dans lequel il développe sa théorie politique ainsi que &lt;a href=&quot;https://www.youtube.com/watch?v=3-mPXD5CkJc&quot;  title=&quot;L'Emile par Librairie Vrin&quot;&gt;&quot;Emile&quot; &lt;/a&gt;considéré comme un &quot;traité d'écucation&quot; ou sa théorie de l'homme. &lt;/p&gt; &lt;p&gt;&#10;Rousseau a également écrit sur la philosophie morale, la théorie de l'éducation et la nature humaine et  &lt;a href=&quot;https://www.youtube.com/watch?v=cUtO8U9QbZs&amp;ab_channel=LePr%C3%A9cepteur&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Le désir par le Précepteur &quot;&gt; le désir&lt;/a&gt;. Il croyait que &lt;a href=&quot;https://www.youtube.com/watch?v=FpXdTgerxiI&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L''homme est naturellement bon par le Précepteur &quot;&gt; l'homme est naturellement bon&lt;/a&gt;, mais corrompu par la société et la civilisation. Il a également affirmé que la liberté individuelle est essentielle à l'épanouissement humain et que les institutions politiques doivent être créées pour protéger les droits et les libertés des individus. &lt;/p&gt; &lt;p&gt;  Il est souvent considéré comme un précurseur du  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0776-555x_1927_num_29_16_2482#&quot;  title=&quot;La philosophie romantique par Persée &quot;&gt; romantisme&lt;/a&gt; en raison de son accent mis sur les émotions, la nature, l'individualité et la subjectivité. Il a exprimé une méfiance envers la société civilisée et a prôné un retour à la nature et à la simplicité. Il a également souligné l'importance de l'émotion et de l'expérience personnelle dans la compréhension du monde, remettant en question l'approche rationnelle et scientifique des Lumières. Ses idées ont eu une influence significative sur les écrivains et les artistes romantiques ultérieurs, qui ont valorisé l'expression émotionnelle et l'expérience individuelle dans leurs œuvres.&lt;/p&gt; &lt;p&gt;&#10;En termes de théorie de l'éducation, Rousseau a proposé une approche de l'apprentissage basée sur l'observation et l'expérience plutôt que sur la mémorisation et l'étude académique et a souligné l'importance de la créativité et de l'expression personnelle dans l'éducation. &lt;/p&gt; &lt;p&gt; &lt;audio controls title=&quot;Rousseau, l'anti-économiste par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10081-28.12.2022-ITEMA_23239091-2022C29629E0022-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Denis_Diderot&quot;  title=&quot; Wikipedia&quot;&gt; Denis DIDEROT&lt;/a&gt; était un philosophe des Lumières français ainsi qu' un écrivain, éditeur et encyclopédiste influent.  Il est surtout connu pour son rôle de coéditeur et contributeur majeur de &lt;a href=&quot;https://www.youtube.com/watch?v=LuRI5zg7tJY&quot;   title=&quot;Diderot 1750 Encyclopedia par OER Project &quot;&gt;l'Encyclopédie, &lt;/a&gt; ou Dictionnaire raisonné des sciences, des arts et des métiers.&lt;/p&gt; &lt;p&gt;&#10;Il était un fervent défenseur de la raison et de l'esprit critique et il rejetait les dogmes et les traditions aveugles, encourageant à la place l'examen rationnel et la remise en question des croyances établies. Il croyait en la capacité de l'homme à comprendre le monde à travers la science, la philosophie et l'observation directe. &lt;/p&gt; &lt;p&gt;&#10;Il était un matérialiste convaincu et soutenait que l'univers était composé de matière en mouvement constant et rejetait l'idée d'une entité divine créatrice. Il écrit &lt;a href=&quot;https://www.youtube.com/watch?v=vkBC-MDLH_A&amp;ab_channel=BouillondeCulture&quot;  title=&quot;Le rêve d'Alembert  par Bouillon de culture&quot;&gt;Le Rêve de D’Alembert&lt;/a&gt;, un ensemble de trois dialogues philosophiques ou il expose sa théorie sur la vie et la nature. Sa vision matérialiste était étroitement liée à sa pensée scientifique et à son intérêt pour les sciences naturelles. &lt;/p&gt; &lt;p&gt; Il écrit aussi un roman (ou plutôt un anti-roman) &lt;a href=&quot;https://www.youtube.com/watch?v=NtxGWQ89g_k&quot; title=&quot;Jacques le Fataliste  par Kosmos&quot;&gt;&quot;Jacques le Fataliste et son maître&quot;&lt;/a&gt; où il refuse le cloisonnement et se positionne en rupture avec les conventions et invente une liberté à l'égard des pratiques existantes en France au XVIIIe siècle. &lt;/p&gt; &lt;p&gt;&#10;Il était un défenseur des libertés de pensée, d'expression et de la presse. Il critiquait les institutions religieuses et politiques oppressives de son époque et plaidait en faveur de l'égalité sociale et de la justice. Il croyait en l'éducation comme moyen d'émancipation et de progrès social, et il pensait que les individus devaient être libres de remettre en question les traditions et les dogmes établis. &lt;/p&gt; &#10;   &lt;audio controls title=&quot;Le Neveu de Rameau par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/10/s40/RF_38A1D24B-FA10-43F4-8B19-8C4921845BD4_GENE.MP3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Johann_Joachim_Spalding&quot; title=&quot; Wikipedia&quot;&gt;Johann Joachim SPALDING&lt;/a&gt; était un théologien protestant allemand, souvent considéré comme l’un des grands représentants des Lumières religieuses en Allemagne. Sa pensée cherche à concilier foi chrétienne, raison et morale, dans un esprit de réforme modérée plutôt que de rupture. &lt;/p&gt; &lt;p&gt; Dans son œuvre la plus célèbre, Die Bestimmung des Menschen (1748), il réfléchit au sens de la vie humaine. Pour lui, l’être humain n’est pas fait seulement pour satisfaire ses besoins matériels, mais pour se développer intérieurement, moralement et spirituellement. &lt;/p&gt; &lt;p&gt; Sa philosophie religieuse défend l’idée d’une religion naturelle compatible avec la Révélation. Il refuse le dogmatisme rigide et l’orthodoxie autoritaire, et insiste sur une foi plus vivante, fondée sur la conscience, le bon sens et l’expérience intérieure. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande importance &lt;a href=&quot;https://www.persee.fr/doc/ephe_0000-0002_1979_num_92_88_18346&quot;  title=&quot;problèmes de la théologie allemande par persée&quot;&gt;au sentiment religieux. &lt;/a&gt;  Dans son ouvrage de 1789, il montre que les émotions et la vie intérieure ont une vraie place dans le christianisme, sans que cela supprime l’exigence morale. Il représente une forme de christianisme éclairé : une religion raisonnable, morale et personnelle, qui veut rendre la foi plus humaine et plus intelligible. Son influence a compté dans la théologie protestante allemande, notamment dans le courant appelé néologie. &lt;/p&gt; &#10;" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" display="https://www.laphilo.fr/pho/jjspalding-mini.webp" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" display="https://laphilo.fr/photo/jjspalding.webp" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Bonnet_(naturaliste)&quot;  title=&quot; Wikipedia&quot;&gt;Charles BONNET&lt;/a&gt;  était un philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie et sa découverte de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Paling%C3%A9n%C3%A9sie&quot;  title=&quot;palingénésie par Wikipedia&quot;&gt;parthénogenèse. &lt;/a&gt; Il  étudie la botanique et l'entomologie dès sa jeunesse, influencé par Newton, Leibniz et Malebranche. Malgré des problèmes de vue et d'ouïe précoces, il devient membre du Conseil des Deux-Cents et correspondant de l'Académie des sciences de Paris. &lt;/p&gt; &lt;p&gt; Il démontre en 1745 la reproduction par parthénogenèse chez les pucerons, obtenant onze générations sans fécondation, et étudie la régénération des vers, des limaçons et des pattes d'écrevisse. Ses Recherches sur l'usage des feuilles (1754) préfigurent la photosynthèse, et il défend la théorie de la préformation, où les germes préexistent depuis la Création. &lt;/p&gt; &lt;p&gt; Dans Essai de psychologie (1754) et Essai analytique sur les facultés de l'âme (1760), il développe un sensualisme spiritualiste, voyant les idées naître des sensations via les fibres cérébrales. Sa Palingénésie philosophique (1769) postule l'immortalité des âmes humaines et animales dans une échelle continue des êtres. &lt;/p&gt; &#10;" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Thiry_d%27Holbach&quot;  title=&quot; Wikipedia&quot;&gt;Paul Thiry d'HOLBACH&lt;/a&gt;  était un philosophe allemand et devient encyclopédiste, traduit des œuvres scientifiques allemandes et anglaises pour l'Encyclopédie de Diderot. Hôte du célèbre &quot;cénacle d'Holbach&quot;, salon fréquenté par Diderot, Rousseau, Helvétius et Adam Smith, il anime un foyer intellectuel anticlérical jusqu'à sa mort en 1789. &lt;/p&gt; &lt;p&gt; Il défend un matérialisme radical: l'univers se compose uniquement de matière et de mouvement, régi par des  &lt;a href=&quot;https://www.youtube.com/watch?v=x99DRdMAd08&quot;  title=&quot;Essai sur l'art de ramper à l'usage des courtisans - D'Holbach&quot; par Vox Plebeia&quot;&gt;lois causales &lt;/a&gt; nécessaires, excluant Dieu ou toute intervention surnaturelle. Athée virulent, il combat les religions comme sources d'erreur, de peur et de superstition dans des pamphlets pseudonymes comme &lt;a href=&quot;https://www.youtube.com/watch?v=8Uohr5Y9xx0&quot; title=&quot;Religions Are ROTTING ILLUSIONS | Baron d’Holbach par Unfiltered Philosophy&quot;&gt;&quot;Le Christianisme dévoilé&quot; &lt;/a&gt; paru en 1761 ou &quot;Le Système de la nature&quot; (1770), bible de l'athéisme. &lt;/p&gt; &lt;p&gt; Sa morale est utilitariste et eudémoniste: la vertu réside dans l'utilité pour le bonheur individuel et collectif, fondée sur la raison et l'éducation, sans recours à la religion. Fataliste et déterministe, il prône la liberté sociale, l'égalité et une politique naturelle anti-despotique, influençant la Révolution française par sa critique des privilèges et du fanatisme. &lt;/p&gt; &#10;&#10;" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" display="&lt;a href=&quot;https://fr.wikipedia.org/wiki/Emmanuel_Kant&quot;  title=&quot; Wikipedia&quot;&gt; Immanuel KANT&lt;/a&gt; était un philosophe &lt;a href=&quot;https://la-philosophie.com/philosophie-lumieres&quot; style=&quot;color:#88A1E9&quot;   title=&quot;La philosophie des Lumières par la-philosophie.com&quot;&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant&quot;  title=&quot;La philosophie pratique de Kant de l'encyclopédie Wikipédia&quot;&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href=&quot;https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos&quot;   title=&quot;C'est quoi la raison pure par Kosmos&quot;&gt;&quot;Critique de la raison pure&quot;&lt;/a&gt; , publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href=&quot;https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos&quot;  title=&quot;La loi morale par Kosmos&quot;&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href=&quot;https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'impératif catégorique par le Précepteur&quot;&gt;&quot;Fondement de la métaphysique des moeurs&quot;&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href=&quot;https://la-philosophie.com/espace-public-et-democratie&quot;  title=&quot;Espace public par la-philosophie.com&quot;&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les &quot;Lumières&quot; comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href=&quot;https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume&quot;  title=&quot;Faculté de jugement par la-philosophie.com&quot;&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title=&quot;Le monde: entre déterminisme et liberté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edmund_Burke&quot;   title=&quot; Wikipedia&quot;&gt;Edmund BURKE&lt;/a&gt; était un philosophe et homme politique anglo-irlandais, considéré comme l'un des fondateurs du conservatisme moderne. Il s'opposa farouchement à la Révolution française, défendant l'évolution graduelle des institutions plutôt que les ruptures radicales. Il étudia au Trinity College avant de s'installer à Londres pour exercer le droit et entrer en politique. Député whig à la Chambre des communes de 1766 à 1794, il soutint l'indépendance américaine tout en critiquant les excès fiscaux britanniques. Sa célèbre Réflexions sur la Révolution de France (1790) alerta sur les dangers de la &quot;multitude perverse&quot; et du rejet des traditions. &lt;/p&gt; &lt;p&gt; Il  voyait la société comme un &quot;partenariat entre les vivants, les morts et ceux qui ne sont pas encore nés&quot;, valorisant les &lt;a href=&quot;https://www.youtube.com/watch?v=az1n7gSaKFE&quot; title=&quot;La tradition permet elle le changement  par la chaine de Velours&quot;&gt;préjugés hérités &lt;/a&gt; comme bank de sagesse collective supérieure à la raison individuelle. Dans Recherches philosophiques sur l'origine de nos idées du sublime et du beau (1757), il distingue le sublime (lié à la douleur, à la terreur et à Dieu) du beau (lié au plaisir et à la société), influençant l'esthétique romantique. Il prônait l'amélioration progressive de la nature humaine imparfaite, sans table rase. &lt;/p&gt; &lt;p&gt; Surnommé &quot;conservateur des Lumières&quot;, il inspira des penseurs comme Roger Scruton et reste une référence contre les utopies rationalistes. En France, il fut parfois taxé de réactionnaire, mais son libéralisme tempéré et son sens de la responsabilité des élites résonnent encore. &lt;/p&gt;  &lt;audio controls title=&quot;Les britaniques ; Burke et ses héritiers par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-10.12.2024-ITEMA_23958056-2024C48904S0345-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;&#10;&#10;" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" display="https://laphilo.fr/pho/ghlessing-mini.webp" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Johann_Kaspar_Lavater&quot;  title=&quot; Wikipedia&quot;&gt;Johann Kaspar LAVATER&lt;/a&gt;  était un théologien, poète et philosophe suisse, connu surtout comme pionnier de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Physiognomonie&quot;  title=&quot;Physiognomonie par Wikipedia&quot;&gt; &quot;la physiognomonie, &lt;/a&gt;  une pseudoscience liant traits du visage et caractère moral. Pasteur réformé à Zurich, il mêla mysticisme chrétien, irrationalisme et influences des Lumières tardives dans ses écrits. Né à Zurich dans une famille bourgeoise, il étudia la théologie et la philosophie au Collegium Carolinum sous Johann Jakob Bodmer. Ordonné en 1762, il devint diacre puis pasteur à l'église St-Pierre, tout en s'engageant contre la corruption locale, ce qui l'exila brièvement à Berlin. Ami de Goethe (dont la relation se tendit) et de Moses Mendelssohn, il fut blessé lors de l'invasion française de 1799 et mourut de ses blessures. &lt;/p&gt; &lt;p&gt; Sa grande œuvre, Physiognomische Fragmente zur Beförderung der Menschenkenntnis und Menschenliebe (1775-1778), postule que le visage révèle l'âme divine en l'homme, reliant esthétique, vertu et théologie. Influencé par l'Empfindsamkeit et le Sturm und Drang, il valorisait le sentiment sur la raison pure, explorant prophétie, miracles et palingénésie (résurrection). Critiqué par Lichtenberg pour son subjectivisme, il inspira poésie mystique et débats sur  &lt;a href=&quot;https://www.youtube.com/watch?v=LUxSlXIY-Zk&quot;  title=&quot;Johann Kaspar Lavater par Grow Wise&quot;&gt; &quot;l'intériorité humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il  incarna un pont entre piétisme, sentimentalisme et romantisme naissant, influençant esthétique et psychologie populaire en Europe. Ses idées déclinèrent avec les progrès scientifiques, mais sa quête d'une connaissance intuitive de l'homme reste débattue. &lt;/p&gt; &#10;" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet&quot;  title=&quot; Wikipedia&quot;&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe , mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href=&quot;https://www.youtube.com/watch?v=3G3kVl0GbA8&quot;  title=&quot;Condorcet féministe ? par Sud Radio&quot;&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote .  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href=&quot;https://www.youtube.com/watch?v=3G3kVl0GbA8&quot;  title=&quot;Condorcet et l’éloge de l’instruction par Culture philo&quot;&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href=&quot;https://www.youtube.com/watch?v=avTI9GHZX1I&quot;  title=&quot;Condorcet le paradoxe par Diable Positif&quot;&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la &quot;mathématique sociale&quot;, Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title=&quot;Nicolas de Condorcet par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nihilisme&quot;  title=&quot;Nihilisme par Wikipedia&quot;&gt; nihilisme &lt;/a&gt; et au &lt;a href=&quot;https://fr.wikipedia.org/wiki/Panth%C3%A9isme&quot;  title=&quot;Panthéisme par Wikipedia&quot;&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse &quot;querelle du panthéisme&quot; en révélant que Lessing s'était  &lt;a href=&quot;https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321&quot;  title=&quot;Jacobi et Spinoza par Persée&quot;&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu . &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du &quot;rien ne sort du néant&quot;) de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un &quot;saut de la foi&quot; hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. - David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. - Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; &#10;&#10;&#10;" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marcus_Herz&quot;  title=&quot; Wikipedia&quot;&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Immanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2&quot; title=&quot;Kant, Lettre à Marcus Herz du 21 février 1772 par Persée&quot;&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la &quot;révolution copernicienne&quot;), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent &quot;Betrachtungen aus der spekulativen Weltweisheit&quot;  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et &quot;Versuch über den Geschmack&quot; en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; " r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Friedl%C3%A4nder&quot;  title=&quot; Wikipedia&quot;&gt;David FRIEDLÄNDER&lt;/a&gt;  était un intellectuel, marchand et réformateur juif allemand, disciple de Moses Mendelssohn, plus connu comme pionnier de l'Haskalah (Lumières juives) et de la  &lt;a  href=&quot;https://www.persee.fr/doc/reval_0035-0974_1973_num_5_3_1989&quot;  title=&quot;D Friedlander et la réforme des communaités juives de prusse par Persée&quot;&gt; réforme religieuse &lt;/a&gt; que comme philosophe académique strict. Il prôna l'émancipation des Juifs par l'assimilation culturelle et une dédogmatisation du judaïsme, fusionnant rationalisme des Lumières et monothéisme mosaïque originel contre les rituels &quot;superstitieux&quot;. &lt;/p&gt; &lt;p&gt; Né à Königsberg, il s'installa à Berlin en 1770, fonda une usine de soie et intégra l'élite juive éclairée via son mariage avec la fille du banquier Daniel Itzig. Après la mort de Mendelssohn (1786), il mena la Haskalah berlinoise : création de la Chevrat Chinuch Ne’arim (école juive libre en 1778), traductions de prières en allemand, et plaidoyers pour l'égalité civile. Premier conseiller municipal juif à Berlin, il lutta contre les discriminations prussiennes. &lt;/p&gt; &lt;p&gt; Il rejetait le Talmud et les rites comme &quot;œuvres de sainteté, verbiage et futilités&quot;, défendant un judaïsme &quot;pur&quot; : monothéisme rationnel commun aux religions abrahamiques, sans dogmes christologiques ni observances contraignantes. Dans son Sendschreiben anonyme (1799) à l'ecclésiastique Wilhelm Teller, il proposa une union judéo-protestante déiste – baptême symbolique sans trinité, en échange d'émancipation –, vu comme opportuniste mais innovant pour le judaïsme réformé naissant. Il resta juif par fidélité au &quot;monothéisme mosaïque idéal&quot;, contrairement à sa famille convertie. &lt;/p&gt; &lt;p&gt; Précurseur du judaïsme réformé et de l'assimilation prussienne, Friedländer incarna le dilemme post-mendelssohnien : identité juive face à l'universalisme. Critiqué pour pragmatisme, il influença les réformes liturgiques et débats sur l'émancipation, bien que son projet fusionnel échouât face au romantisme montant. &lt;/p&gt; &#10;&#10;" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" display="https://laphilo.fr/photo/dfriedlander.webp" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joseph_de_Maistre&quot;  title=&quot; Wikipedia&quot;&gt;Joseph de MAISTRE&lt;/a&gt; était un philosophe, écrivain et diplomate savoyard, figure majeure de la contre-révolution et critique virulent des Lumières et de la Révolution française. Considéré comme un père de la pensée conservatrice moderne, il défend une vision organique de la société, hiérarchique et divinement ordonnée, où l'autorité monarchique et religieuse prime sur les idées contractualistes et individualistes. &lt;/p&gt; &lt;p&gt;  Pour lui, la Révolution française est un &lt;a href=&quot;https://www.persee.fr/doc/bude_0004-5527_1989_num_1_2_1393&quot; title=&quot;Sacré et sacrifice dans la pensée de Joseph de Maistre par Persée&quot;&gt;châtiment providentiel &lt;/a&gt; des excès des philosophes des Lumières, punissant l'athéisme et le rationalisme par la Terreur. Les sociétés ne naissent pas d'un contrat rationnel (comme chez Rousseau), mais d'une autorité divine imposée d'en haut; l'individu abstrait n'existe pas, il est façonné par la tradition et l'État.  Il prône une monarchie absolue et l'autorité suprême du Pape pour unifier l'Europe spirituellement et temporellement. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures sont : - &quot;Considérations sur la France&quot; paru en 1797 : Interprétation providentialiste de la Révolution comme mission divine de la France. - &quot;Essai sur le principe générateur des constitutions&quot; paru en 1809 :  &lt;a href=&quot;https://www.youtube.com/watch?v=oPEzOiEdrNE&quot;  title=&quot; L'oecuménisme de Joseph de Maistre par BAGLIS TV&quot;&gt;Les constitutions &lt;/a&gt; viennent de Dieu, non de la raison humaine et - &quot;Soirées de Saint-Pétersbourg&quot;  en1821, posthume : Théodicée justifiant le mal (guerre, sacrifice) comme partie du plan divin. &lt;/p&gt; &lt;p&gt; Il a eu une influence durablement le conservatisme, le romantisme contre-révolutionnaire et des penseurs comme Donoso Cortés, tout en étant critiqué pour son apologie de la violence. Sa pensée hiérarchique et anti-individualiste reste débattue face aux idéaux démocratiques modernes. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Troisième penseur, Joseph de Maistre. par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-26.10.2011-ITEMA_20317797-2011C12410S0299-NET_F022382B-0B64-4C5C-B335-284B201C884D_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Louis_de_Bonald&quot;  title=&quot; Wikipedia&quot;&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Tradition_primordiale&quot;  title=&quot; Tradition Primordiale de Maistre par Wikipedia &quot;&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. - Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. - Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href=&quot;https://www.youtube.com/watch?v=WMB9kethTWIe&quot;  title=&quot; Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations &quot;&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral&quot;  title=&quot; Maurrassisme par Wikipedia &quot;&gt; maurrassisme, &lt;a&gt; voyant la France comme &quot;nation-pilote&quot; pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant . &lt;/p&gt;&#10; &#10;&#10;//" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Antoine_Destutt_de_Tracy&quot;  title=&quot; Wikipedia&quot;&gt;Destutt de TRACY&lt;/a&gt; était un philosophe et idéologue français, fondateur et théoricien principal du courant philosophique des Idéologues. Né Antoine Louis Claude Destutt, comte de Tracy, dans une famille noble auvergnate, il fit une carrière militaire avant de se consacrer à la philosophie après son emprisonnement pendant la Terreur. Membre de l'Institut national et de l'Académie française, il joua un rôle central dans la vie intellectuelle française sous le Directoire et le Consulat. &lt;/p&gt; &lt;p&gt; Sa contribution majeure est la création de l'« idéologie » comme science des idées. Dans ses &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=DAz6QsBdeyg&quot;  title=&quot;Destrutt de DRACYi par Wikipedia Fan&quot;&gt;Éléments d'idéologie &lt;/a&gt; &lt;/em&gt; (5 volumes, 1801-1815), il cherche à fonder une science générale des idées qui analyserait leur formation à partir des sensations et des signes. S'inscrivant dans la tradition sensualiste de Condillac, il développe une sémiologie et une grammaire générale visant à purifier le langage de ses ambiguïtés et à fonder les sciences humaines sur des bases empiriques solides. Son projet était d'édifier une « science des sciences » qui servirait de fondement à l'enseignement et à la réforme sociale. &lt;/p&gt; &lt;p&gt; Sa &lt;em&gt;Logique&lt;/em&gt; et son &lt;em&gt;Commentaire sur l'Esprit des Lois de Montesquieu&lt;/em&gt; (1811) témoignent de son intérêt pour la philosophie politique libérale. Jefferson, qui admirait sa pensée, fit traduire son &lt;em&gt;Traité de la volonté&lt;/em&gt; en anglais. Ironiquement, le terme même d'« idéologie » qu'il avait forgé fut retourné contre lui par Napoléon, qui qualifiait les Idéologues d'esprits abstraits et dangereux. Marx reprit ensuite ce terme dans un sens radicalement différent. Destutt de Tracy reste une figure essentielle pour comprendre l'émergence des sciences humaines en France. &lt;/p&gt;" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Laromigui%C3%A8re&quot;  title=&quot; Wikipedia&quot;&gt;Pierre LAROMIGUIÈRE&lt;/a&gt; était un philosophe français, l'une des figures transitoires entre le sensualisme des Lumières et la philosophie spiritualiste du XIXe siècle. Né à Livinhac-le-Haut dans l'Aveyron, il fut d'abord prêtre avant la Révolution, puis professeur de philosophie à l'École centrale des arts et manufactures et enfin à la Sorbonne. Ses cours, qui attirèrent un public nombreux et enthousiaste dans les premières décennies du XIXe siècle, contribuèrent à renouveler l'enseignement de la philosophie en France. &lt;/p&gt; &lt;p&gt; Sa philosophie part du sensualisme de Condillac mais s'en écarte sur un point décisif : là où Condillac réduisait toutes les opérations de l'esprit à des sensations transformées, Laromiguière distingue soigneusement les sensations des opérations actives de l'attention, de la comparaison et du jugement. Cette distinction entre les facultés passives et les facultés actives de l'esprit ouvre la voie à une conception plus riche de la vie psychique, qui reconnaît la spécificité de l'activité intellectuelle irréductible à la simple réception sensorielle. &lt;/p&gt; &lt;p&gt; Dans ses &lt;em&gt;Leçons de philosophie&lt;/em&gt; (1815-1818), dont la clarté et l'agrément du style lui valurent un succès durable, il développe cette psychologie des facultés dans un cadre pédagogique accessible. Bien que sa pensée ait été éclipsée par le courant spiritualiste de Cousin et par le positivisme de Comte, Laromiguière représente une étape importante dans la constitution de la psychologie philosophique française. Sa manière de corriger Condillac par une attention accrue à l'activité de l'esprit préfigure les développements du spiritualisme ultérieur. &lt;/p&gt;" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Jean_Georges_Cabanis&quot; title=&quot; Wikipedia&quot;&gt;Pierre CABANIS&lt;/a&gt; était un médecin et philosophe français, figure majeure du groupe des Idéologues et pionnier d'une approche naturaliste de la vie psychique. Né à Cosnac en Corrèze, il fut introduit dans les cercles intellectuels parisiens par Turgot et fréquenta le salon d'Helvétius. Ami intime de Mirabeau dont il soigna les derniers jours, il participa activement à la vie politique de la Révolution et du Directoire, siégeant au Conseil des Cinq-Cents. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;Rapports du physique et du moral de l'homme&lt;/em&gt; (1802), est un essai audacieux pour fonder une science de l'homme sur des bases physiologiques. Cabanis y soutient que les phénomènes psychiques sont intimement liés aux processus organiques du corps : le cerveau secrète la pensée comme le foie sécrète la bile. Cette formule provocatrice, souvent mal comprise, visait en réalité à établir une méthode empirique pour l'étude de l'âme, refusant tout recours à des entités métaphysiques abstraites. &lt;/p&gt; &lt;p&gt; Médecin réformateur, il œuvra à la réorganisation des hôpitaux parisiens et milita pour une médecine fondée sur l'observation clinique plutôt que sur les théories scolastiques. Ses travaux contribuèrent à l'essor de l'hygiénisme et de la médecine sociale. Sa pensée, qui anticipe certains aspects du matérialisme médical du XIXe siècle, représente une étape importante dans la constitution des sciences humaines. Bien que les Idéologues aient été rabroués par Napoléon qui les rendait responsables des « idéologues abstraits », l'influence de Cabanis sur la médecine et la psychologie françaises fut durable. &lt;/p&gt;" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" display="https://www.laphilo.fr/pho/cabanis-mini.webp" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre-Paul_Royer-Collard&quot;  title=&quot; Wikipedia&quot;&gt;Pierre-Paul ROYER-COLLARD&lt;/a&gt;  était un philosophe et homme politique français, figure majeure du libéralisme modéré sous la Restauration et chef des Doctrinaires. Né en Champagne, il commence comme avocat au Parlement de Paris avant de s'engager politiquement. Pendant la Révolution, il soutient les Girondins et fuit la Terreur, se retirant dans ses terres. Sous la Restauration, il devient député de la Marne et préside la Chambre des députés (1828–1830), tout en enseignant l'histoire de la philosophie moderne à la Sorbonne. &lt;/p&gt; &lt;p&gt; Sa philosophie se présente comme un rejet du sensualisme de Condillac qui dominait le XVIIIᵉ siècle français. Il s'inspire du philosophe écossais Thomas Reid et introduit en France la doctrine du sens commun. Contrairement aux sensualistes, il distingue clairement la sensation (subjective, plaisir ou peine) de la perception (appréhension d'un objet externe). Pour lui, la perception implique un jugement spontané de l'esprit actif, non déductible des seuls sens. &lt;/p&gt; &lt;p&gt; Il développe un spiritualisme rigoureux : l'esprit humain est actif et capable de jugements autonomes. Le sens commun – cette faculté naturelle de distinguer le bien du mal, le vrai du faux – fonde la vie communautaire et remplace l'autorité surnaturelle. Par les principes de causalité et d'induction, la raison conduit nécessairement à l'idée d'une Première Cause (Dieu). Il affirme la supériorité irréductible de la personne humaine sur l'État, les personnes étant &lt;a  href=&quot;https://www.youtube.com/watch?v=15bNqKMiW_w&quot;  title=&quot;R Collard ou l’ambilalence des restaurations par Collège st Germain&quot;&gt;« faites à l'image de Dieu et douées d'immortalité ».&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Politiquement, il est un royaliste libéral qui considère la Révolution de 1789 comme irréversible. Il cherche à fonder une monarchie constitutionnelle stable entre l'Ancien Régime (les Ultras) et le totalitarisme napoléonien, puis la démocratisation trop rapide sous Louis-Philippe. Il incarne la « philosophie de la Charte » et influence profondément François Guizot. N'a presque rien publié de son vivant : ses écrits philosophiques ont été rassemblés après coup par son admirateur Théodore Jouffroy.  &lt;/p&gt; " r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" display="https://www.laphilo.fr/pho/pcollard-mini.webp" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Claude-Henri_de_Rouvroy_de_Saint-Simon&quot; title=&quot; Wikipedia&quot;&gt;Claude-Henri de ROUVROY, comte de SAINT-SIMON&lt;/a&gt; est un penseur et réformateur social français, issu d’une famille aristocratique qui revendiquait une lointaine parenté avec Charlemagne. Volontaire dans l’armée française envoyée soutenir l’indépendance américaine, il participe au siège de Yorktown avant de renoncer, sous la Révolution, à son titre de noblesse.  &lt;a href=&quot;https://maitron.fr/saint-simon-claude-henri-claude-henri-de-rouvroy-comte-de-saint-simon/&quot; title=&quot;saint simon par le maitron&quot;&gt;Spéculateur &lt;/a&gt; sur les biens nationaux, emprisonné pendant la Terreur, il connaît ensuite une vie mouvementée, tour à tour fortunée et misérable, entièrement vouée à la recherche d’une science nouvelle de la société. &lt;/p&gt; &lt;p&gt; Convaincu que la Révolution a détruit l’ancien ordre théologique et féodal sans encore bâtir l’ordre qui doit lui succéder, Saint-Simon appelle à fonder une organisation sociale confiée non plus aux militaires, aux juristes ou aux rentiers, mais aux savants, aux industriels et aux producteurs. Dans des ouvrages comme &lt;em&gt;L’Industrie&lt;/em&gt; ou &lt;em&gt;Du système industriel&lt;/em&gt;, il défend l’idée que le pouvoir politique doit être subordonné à la production utile : gouverner, pour lui, revient d’abord à administrer les choses et à organiser le travail, plutôt qu’à commander les hommes. &lt;/p&gt; &lt;p&gt; Il élabore ainsi une &lt;a href=&quot;https://fr.wikipedia.org/wiki/Saint-simonisme&quot; title=&quot;Saint-simonisme par Wikipedia&quot;&gt;philosophie de l’histoire&lt;/a&gt; fondée sur l’alternance de périodes « organiques » et « critiques », et annonce l’avènement d’un âge industriel où la science et la technique remplaceraient la théologie comme principe d’unité sociale. Son dernier livre, &lt;em&gt;Le Nouveau Christianisme&lt;/em&gt; (1825), publié l’année de sa mort, prône une religion de la fraternité entièrement tournée vers l’amélioration du sort des classes les plus pauvres, qu’il présente comme la fin ultime de toute organisation sociale et politique légitime. &lt;/p&gt; &lt;p&gt; Bien que ses écrits soient souvent fragmentaires et inachevés, Saint-Simon laisse une postérité considérable : ses disciples, réunis après sa mort en une école puis en une véritable Église saint-simonienne, diffusent et systématisent sa pensée sous le nom de saint-simonisme. Ce courant influencera profondément le socialisme utopique du XIXe siècle, la sociologie naissante d’Auguste Comte (un temps son secrétaire), ainsi que les grandes entreprises industrielles et financières du Second Empire, qui reprendront à leur compte son culte du progrès technique et de l’organisation rationnelle de la production. &lt;/p&gt;" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" display="https://www.laphilo.fr/pho/hssimon-mini.webp" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Maine_de_Biran&quot;  title=&quot; Wikipedia&quot;&gt;Maine de BIRAN&lt;/a&gt; était un philosophe français, considéré comme l'un des fondateurs de la philosophie de l'intériorité et du spiritualisme français. Né François-Pierre Gonthier de Biran à Bergerac en Dordogne, il commença sa carrière comme officier de la garde du roi, avant de se consacrer à la philosophie et à la vie politique locale en Périgord. Administrateur apprécié sous plusieurs régimes successifs, il fut député et sous-préfet, mais c'est à travers ses journaux intimes et ses &lt;a  href=&quot;https://www.youtube.com/watch?v=ayhmQ5WQfJk&quot;  title=&quot;Maine de Biran spiritualité &amp; phénoménologie par ICP&quot;&gt;essais philosophiques &lt;/a&gt; que son originalité s'exprima pleinement. &lt;/p&gt; &lt;p&gt; Sa pensée prend pour point de départ l'expérience immédiate de l'effort : c'est dans l'acte volontaire par lequel le moi exerce une résistance contre le corps propre que la conscience se saisit elle-même comme force et comme liberté. Contre le sensualisme de Condillac qui réduisait l'âme à la sensation passive, il soutient que l'activité volontaire constitue le fait primitif de la conscience. Cette découverte du « moi voulant » comme donnée irréductible de l'intériorité marque une rupture décisive dans la philosophie française. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;t &lt;a  href=&quot;https://www.persee.fr/doc/bupsy_0007-4403_1963_num_17_224_9102&quot;  title=&quot;Maine de Biran fondateur de la psychologie française par Persée&quot;&gt;Essai sur les fondements de la psychologie &lt;/a&gt; &lt;/em&gt; (1812) et ses nombreux &lt;em&gt;Mémoires&lt;/em&gt; rédigés pour les concours de l'Institut, développent une psychologie de l'effort qui distingue trois ordres d'existence : la vie animale (sensations), la vie humaine (volonté et conscience) et la vie de l'esprit (grâce et amour mystique). Cette trilogie, d'inspiration néo-platonicienne et chrétienne dans sa dernière phase, influença profondément Ravaisson, Bergson et tout le courant spiritualiste français. Ses &lt;em&gt;Journal&lt;/em&gt; et &lt;em&gt;Mémoire sur les perceptions obscures&lt;/em&gt; témoignent d'une introspection d'une subtilité et d'une profondeur rares. &lt;/p&gt;" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Voltaire&quot;   title=&quot; Wikipedia&quot;&gt; VOLTAIRE&lt;/a&gt;, de son vrai nom François-Marie Arouet, est un philosophe de l'époque des  &lt;a href=&quot;https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;t=380s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot; La philosophie des lumières par le Précepteur &quot;&gt;Lumières&lt;/a&gt; (ou Illuministe) en France. Il était aussi écrivain, poète, dramaturge et philosophe. &lt;/p&gt; &lt;p&gt;&#10;Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href=&quot;https://www.youtube.com/watch?v=XE1Z8jpVJUA&quot; title=&quot; la vie de Voltaire  par Portrait Historiques&quot;&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation . Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;&#10;Voltaire, qui était &lt;a href=&quot;https://www.youtube.com/watch?v=RO_aeh1cBgA&amp;ab_channel=Kurious&quot;   title=&quot; Regard critique sur le déîsme par Kurious &quot;&gt;déiste&lt;/a&gt; s'est opposé aux abus de l'Église catholique et a plaidé en faveur de la tolérance envers les minorités religieuses. Dans son ouvrage &lt;a href=&quot;https://www.youtube.com/watch?v=1RlS8GKL7SU&quot;  title=&quot; Voltaire-Tolérence par Culture Philo &quot;&gt;&quot;Traité sur la tolérance&quot;&lt;/a&gt;, (1763) il a condamné les persécutions religieuses et a défendu le principe selon lequel chaque individu devait être libre de pratiquer sa religion sans être inquiété. &lt;/p&gt; &lt;p&gt;&#10;Son ouvrage le plus connu est  &lt;a href=&quot;https://www.youtube.com/watch?v=kom2zFvrj5I&amp;ab_channel=T%C3%A9l%C3%A9Crayon&quot;  title=&quot; Candide de Voltaire par TéléCrayon &quot;&gt;&quot;Candide&quot;&lt;/a&gt; (1759), un conte philosophique qui critique les idées optimistes de l'époque et souligne les absurdités et les injustices du monde. &lt;/p&gt; &lt;p&gt;&#10;La contribution de Voltaire à la philosophie se caractérise par son engagement envers la raison, la liberté et la justice. Il a influencé de nombreux penseurs ultérieurs et a contribué à jeter les bases de la pensée libérale et humaniste qui a marqué les siècles suivants. Sa défense de la liberté d'expression reste une valeur fondamentale de nos sociétés démocratiques aujourd'hui. &lt;/p&gt; &lt;audio controls title=&quot;Voltaire et les Lumières par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15537-13.01.2021-ITEMA_22540842-2021C24632S0013.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)&quot;    title=&quot; Wikipedia&quot;&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href=&quot;https://www.youtube.com/watch?v=kbpEAw2gl40&quot; title=&quot; David Hartley par Crevoisier Philippe&quot;&gt; développement de la psychologie &lt;/a&gt;  , en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt; - La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la &quot;substance médullaire&quot; (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt; - La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des &quot;vibratiuncules&quot; (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs &quot;vibratiuncules&quot; respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href=&quot;https://www.youtube.com/shorts/BuqpLB9V41c&quot;  title=&quot; David Hartley par timelinephilosopher&quot;&gt;  le fondement des idées et des pensées &lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des &quot;vibratiuncules&quot; de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &quot;Observations on Man, his Frame, his Duty, and his Expectations&quot;, publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt; &#10;- L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt; &#10;- Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; " r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Julien_Offray_de_La_Mettrie&quot;    title=&quot; Wikipedia&quot;&gt;Julien Onfray de la METTRIE&lt;/a&gt;  était un philosophe et médecin français des Lumières, connu pour son &lt;a href=&quot;https://www.youtube.com/watch?v=ATn23C-jw1M&quot;  title=&quot; Traité du bonheur de la Mettrie par Voyage interieur&quot;&gt; matérialisme radical &lt;/a&gt; et son athéisme provocateur. Médecin militaire, il fut exilé de France après la publication de ses idées controversées, avant de trouver refuge auprès de Frédéric II de Prusse à Potsdam. &lt;/p&gt; &lt;p&gt; Dans L’Homme machine (1747), il affirme que l’être humain est une machine purement matérielle : l’âme n’existe pas comme substance distincte, mais émerge des processus physiques du cerveau et du corps, sans besoin de Dieu ou d’esprit immatériel. Il s’inspire de Descartes, mais pousse le mécanisme jusqu’au bout en rejetant le dualisme corps-âme.  &lt;/p&gt; &lt;p&gt; Ses écrits, comme Histoire naturelle de l’âme (1745), scandalisèrent l’Église et les autorités : ses livres furent brûlés publiquement et il perdit son poste aux Gardes-Françaises. Défenseur d’un hédonisme sensualiste, il prône le  &lt;a href=&quot;https://www.youtube.com/watch?v=FH2TDimoh7Q&quot;  title=&quot; La Mettrie ou l’art de jouir par Parole de philosophe&quot;&gt; plaisir comme seul bien moral,&lt;/a&gt;  sans morale transcendante. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés : - Histoire naturelle de l’âme (1745) : Critique du dualisme et fondement matérialiste. - L’Homme machine (1747) : Thèse principale sur l’automatisme humain. - L’Homme plante (1748) : Étend le mécanisme aux végétaux et animaux. &lt;/p&gt; &lt;p&gt; Précurseur du matérialisme moderne et de la philosophie de la vie, il influence Diderot et les Encyclopédistes, mais reste marginalisé pour son radicalisme. Il anticipe des idées sur l’évolution et la cybernétique en voyant l’humain comme un système organisé. &lt;/p&gt; &#10;" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Hume&quot;  title=&quot; Wikipedia&quot;&gt;David HUME&lt;/a&gt; était un philosophe, historien et économiste écossais de l'ère des Lumières. Il est surtout connu pour ses contributions à la philosophie empirique, la théorie de la connaissance, la métaphysique, l'éthique et l'esthétique. &lt;/p&gt; &lt;p&gt; Hume était un sceptique et a cherché à examiner de manière critique les idées préconçues et les &lt;a  href=&quot;https://www.youtube.com/watch?v=CLIoxw6TXuk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Tout n'est que croyance  par Le Précepteur&quot;&gt;croyances reçues&lt;/a&gt;. Il a rejeté les arguments métaphysiques qui ne pouvaient pas être fondés sur l'expérience directe, et a affirmé que les connaissances humaines étaient basées sur les impressions et les idées que nous en avons. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de &lt;a  href=&quot;https://www.youtube.com/watch?v=ftd3vjw9lSU&quot;  title=&quot; la causalité par Skarblown Animations&quot;&gt;la causalité&lt;/a&gt;, qui affirme que nous ne pouvons pas connaître la relation de cause à effet entre deux événements par simple observation, mais que nous sommes amenés à croire en une telle relation en raison de notre expérience passée.  &lt;/p&gt; &lt;p&gt; En éthique, il a affirmé que la morale était basée sur des sentiments plutôt que sur la raison et qu'elle ne peut pas être déduite de principes rationnels, mais doit être fondée sur l'empathie et la sympathie envers les autres.  &lt;/p&gt; &lt;p&gt; Il a également souligné l'importance du bonheur et du plaisir dans la vie, affirmant que ce sont des aspects essentiels de notre existence et de notre &lt;a  href=&quot;https://www.youtube.com/watch?v=52077nWSkPM&amp;t=11s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;l'identité par le Précepteur&quot;&gt;identité&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il a écrit sur la religion et a critiqué les arguments traditionnels pour l'existence de Dieu en affirmant que la religion était basée sur la superstition plutôt que sur la raison, et que la croyance en Dieu était fondée sur l'habitude plutôt que sur la preuve. &lt;/p&gt;  &lt;audio controls title=&quot;Pourquoi faut il lire David Hume par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22838-02.02.2022-ITEMA_22927004-2022C45539E0018-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;&#10;" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau&quot; title=&quot; Wikipedia&quot;&gt; Jean-Jacques ROUSSEAU&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Les Lumières par le Précepteur &quot;&gt; des lumières&lt;/a&gt; et écrivain suisse-français, défenseur de la liberté et de l'égalité. Il et est surtout connu pour son livre &lt;a href=&quot;https://www.youtube.com/watch?v=tToAS8pUXzU&quot;   title=&quot;Le texte fondateur par Alain Bajomée &quot;&gt;&quot;Du contrat social&quot;&lt;/a&gt; , dans lequel il développe sa théorie politique ainsi que &lt;a href=&quot;https://www.youtube.com/watch?v=3-mPXD5CkJc&quot;  title=&quot;L'Emile par Librairie Vrin&quot;&gt;&quot;Emile&quot; &lt;/a&gt;considéré comme un &quot;traité d'écucation&quot; ou sa théorie de l'homme. &lt;/p&gt; &lt;p&gt;&#10;Rousseau a également écrit sur la philosophie morale, la théorie de l'éducation et la nature humaine et  &lt;a href=&quot;https://www.youtube.com/watch?v=cUtO8U9QbZs&amp;ab_channel=LePr%C3%A9cepteur&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Le désir par le Précepteur &quot;&gt; le désir&lt;/a&gt;. Il croyait que &lt;a href=&quot;https://www.youtube.com/watch?v=FpXdTgerxiI&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L''homme est naturellement bon par le Précepteur &quot;&gt; l'homme est naturellement bon&lt;/a&gt;, mais corrompu par la société et la civilisation. Il a également affirmé que la liberté individuelle est essentielle à l'épanouissement humain et que les institutions politiques doivent être créées pour protéger les droits et les libertés des individus. &lt;/p&gt; &lt;p&gt;  Il est souvent considéré comme un précurseur du  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0776-555x_1927_num_29_16_2482#&quot;  title=&quot;La philosophie romantique par Persée &quot;&gt; romantisme&lt;/a&gt; en raison de son accent mis sur les émotions, la nature, l'individualité et la subjectivité. Il a exprimé une méfiance envers la société civilisée et a prôné un retour à la nature et à la simplicité. Il a également souligné l'importance de l'émotion et de l'expérience personnelle dans la compréhension du monde, remettant en question l'approche rationnelle et scientifique des Lumières. Ses idées ont eu une influence significative sur les écrivains et les artistes romantiques ultérieurs, qui ont valorisé l'expression émotionnelle et l'expérience individuelle dans leurs œuvres.&lt;/p&gt; &lt;p&gt;&#10;En termes de théorie de l'éducation, Rousseau a proposé une approche de l'apprentissage basée sur l'observation et l'expérience plutôt que sur la mémorisation et l'étude académique et a souligné l'importance de la créativité et de l'expression personnelle dans l'éducation. &lt;/p&gt; &lt;p&gt; &lt;audio controls title=&quot;Rousseau, l'anti-économiste par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10081-28.12.2022-ITEMA_23239091-2022C29629E0022-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Denis_Diderot&quot;  title=&quot; Wikipedia&quot;&gt; Denis DIDEROT&lt;/a&gt; était un philosophe des Lumières français ainsi qu' un écrivain, éditeur et encyclopédiste influent.  Il est surtout connu pour son rôle de coéditeur et contributeur majeur de &lt;a href=&quot;https://www.youtube.com/watch?v=LuRI5zg7tJY&quot;   title=&quot;Diderot 1750 Encyclopedia par OER Project &quot;&gt;l'Encyclopédie, &lt;/a&gt; ou Dictionnaire raisonné des sciences, des arts et des métiers.&lt;/p&gt; &lt;p&gt;&#10;Il était un fervent défenseur de la raison et de l'esprit critique et il rejetait les dogmes et les traditions aveugles, encourageant à la place l'examen rationnel et la remise en question des croyances établies. Il croyait en la capacité de l'homme à comprendre le monde à travers la science, la philosophie et l'observation directe. &lt;/p&gt; &lt;p&gt;&#10;Il était un matérialiste convaincu et soutenait que l'univers était composé de matière en mouvement constant et rejetait l'idée d'une entité divine créatrice. Il écrit &lt;a href=&quot;https://www.youtube.com/watch?v=vkBC-MDLH_A&amp;ab_channel=BouillondeCulture&quot;  title=&quot;Le rêve d'Alembert  par Bouillon de culture&quot;&gt;Le Rêve de D’Alembert&lt;/a&gt;, un ensemble de trois dialogues philosophiques ou il expose sa théorie sur la vie et la nature. Sa vision matérialiste était étroitement liée à sa pensée scientifique et à son intérêt pour les sciences naturelles. &lt;/p&gt; &lt;p&gt; Il écrit aussi un roman (ou plutôt un anti-roman) &lt;a href=&quot;https://www.youtube.com/watch?v=NtxGWQ89g_k&quot; title=&quot;Jacques le Fataliste  par Kosmos&quot;&gt;&quot;Jacques le Fataliste et son maître&quot;&lt;/a&gt; où il refuse le cloisonnement et se positionne en rupture avec les conventions et invente une liberté à l'égard des pratiques existantes en France au XVIIIe siècle. &lt;/p&gt; &lt;p&gt;&#10;Il était un défenseur des libertés de pensée, d'expression et de la presse. Il critiquait les institutions religieuses et politiques oppressives de son époque et plaidait en faveur de l'égalité sociale et de la justice. Il croyait en l'éducation comme moyen d'émancipation et de progrès social, et il pensait que les individus devaient être libres de remettre en question les traditions et les dogmes établis. &lt;/p&gt; &#10;   &lt;audio controls title=&quot;Le Neveu de Rameau par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/10/s40/RF_38A1D24B-FA10-43F4-8B19-8C4921845BD4_GENE.MP3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Johann_Joachim_Spalding&quot; title=&quot; Wikipedia&quot;&gt;Johann Joachim SPALDING&lt;/a&gt; était un théologien protestant allemand, souvent considéré comme l’un des grands représentants des Lumières religieuses en Allemagne. Sa pensée cherche à concilier foi chrétienne, raison et morale, dans un esprit de réforme modérée plutôt que de rupture. &lt;/p&gt; &lt;p&gt; Dans son œuvre la plus célèbre, Die Bestimmung des Menschen (1748), il réfléchit au sens de la vie humaine. Pour lui, l’être humain n’est pas fait seulement pour satisfaire ses besoins matériels, mais pour se développer intérieurement, moralement et spirituellement. &lt;/p&gt; &lt;p&gt; Sa philosophie religieuse défend l’idée d’une religion naturelle compatible avec la Révélation. Il refuse le dogmatisme rigide et l’orthodoxie autoritaire, et insiste sur une foi plus vivante, fondée sur la conscience, le bon sens et l’expérience intérieure. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande importance &lt;a href=&quot;https://www.persee.fr/doc/ephe_0000-0002_1979_num_92_88_18346&quot;  title=&quot;problèmes de la théologie allemande par persée&quot;&gt;au sentiment religieux. &lt;/a&gt;  Dans son ouvrage de 1789, il montre que les émotions et la vie intérieure ont une vraie place dans le christianisme, sans que cela supprime l’exigence morale. Il représente une forme de christianisme éclairé : une religion raisonnable, morale et personnelle, qui veut rendre la foi plus humaine et plus intelligible. Son influence a compté dans la théologie protestante allemande, notamment dans le courant appelé néologie. &lt;/p&gt; &#10;" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" display="https://www.laphilo.fr/pho/jjspalding-mini.webp" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" display="https://laphilo.fr/photo/jjspalding.webp" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Bonnet_(naturaliste)&quot;  title=&quot; Wikipedia&quot;&gt;Charles BONNET&lt;/a&gt;  était un philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie et sa découverte de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Paling%C3%A9n%C3%A9sie&quot;  title=&quot;palingénésie par Wikipedia&quot;&gt;parthénogenèse. &lt;/a&gt; Il  étudie la botanique et l'entomologie dès sa jeunesse, influencé par Newton, Leibniz et Malebranche. Malgré des problèmes de vue et d'ouïe précoces, il devient membre du Conseil des Deux-Cents et correspondant de l'Académie des sciences de Paris. &lt;/p&gt; &lt;p&gt; Il démontre en 1745 la reproduction par parthénogenèse chez les pucerons, obtenant onze générations sans fécondation, et étudie la régénération des vers, des limaçons et des pattes d'écrevisse. Ses Recherches sur l'usage des feuilles (1754) préfigurent la photosynthèse, et il défend la théorie de la préformation, où les germes préexistent depuis la Création. &lt;/p&gt; &lt;p&gt; Dans Essai de psychologie (1754) et Essai analytique sur les facultés de l'âme (1760), il développe un sensualisme spiritualiste, voyant les idées naître des sensations via les fibres cérébrales. Sa Palingénésie philosophique (1769) postule l'immortalité des âmes humaines et animales dans une échelle continue des êtres. &lt;/p&gt; &#10;" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Thiry_d%27Holbach&quot;  title=&quot; Wikipedia&quot;&gt;Paul Thiry d'HOLBACH&lt;/a&gt;  était un philosophe allemand et devient encyclopédiste, traduit des œuvres scientifiques allemandes et anglaises pour l'Encyclopédie de Diderot. Hôte du célèbre &quot;cénacle d'Holbach&quot;, salon fréquenté par Diderot, Rousseau, Helvétius et Adam Smith, il anime un foyer intellectuel anticlérical jusqu'à sa mort en 1789. &lt;/p&gt; &lt;p&gt; Il défend un matérialisme radical: l'univers se compose uniquement de matière et de mouvement, régi par des  &lt;a href=&quot;https://www.youtube.com/watch?v=x99DRdMAd08&quot;  title=&quot;Essai sur l'art de ramper à l'usage des courtisans - D'Holbach&quot; par Vox Plebeia&quot;&gt;lois causales &lt;/a&gt; nécessaires, excluant Dieu ou toute intervention surnaturelle. Athée virulent, il combat les religions comme sources d'erreur, de peur et de superstition dans des pamphlets pseudonymes comme &lt;a href=&quot;https://www.youtube.com/watch?v=8Uohr5Y9xx0&quot; title=&quot;Religions Are ROTTING ILLUSIONS | Baron d’Holbach par Unfiltered Philosophy&quot;&gt;&quot;Le Christianisme dévoilé&quot; &lt;/a&gt; paru en 1761 ou &quot;Le Système de la nature&quot; (1770), bible de l'athéisme. &lt;/p&gt; &lt;p&gt; Sa morale est utilitariste et eudémoniste: la vertu réside dans l'utilité pour le bonheur individuel et collectif, fondée sur la raison et l'éducation, sans recours à la religion. Fataliste et déterministe, il prône la liberté sociale, l'égalité et une politique naturelle anti-despotique, influençant la Révolution française par sa critique des privilèges et du fanatisme. &lt;/p&gt; &#10;&#10;" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" display="&lt;a href=&quot;https://fr.wikipedia.org/wiki/Emmanuel_Kant&quot;  title=&quot; Wikipedia&quot;&gt; Immanuel KANT&lt;/a&gt; était un philosophe &lt;a href=&quot;https://la-philosophie.com/philosophie-lumieres&quot; style=&quot;color:#88A1E9&quot;   title=&quot;La philosophie des Lumières par la-philosophie.com&quot;&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant&quot;  title=&quot;La philosophie pratique de Kant de l'encyclopédie Wikipédia&quot;&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href=&quot;https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos&quot;   title=&quot;C'est quoi la raison pure par Kosmos&quot;&gt;&quot;Critique de la raison pure&quot;&lt;/a&gt; , publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href=&quot;https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos&quot;  title=&quot;La loi morale par Kosmos&quot;&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href=&quot;https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'impératif catégorique par le Précepteur&quot;&gt;&quot;Fondement de la métaphysique des moeurs&quot;&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href=&quot;https://la-philosophie.com/espace-public-et-democratie&quot;  title=&quot;Espace public par la-philosophie.com&quot;&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les &quot;Lumières&quot; comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href=&quot;https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume&quot;  title=&quot;Faculté de jugement par la-philosophie.com&quot;&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title=&quot;Le monde: entre déterminisme et liberté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edmund_Burke&quot;   title=&quot; Wikipedia&quot;&gt;Edmund BURKE&lt;/a&gt; était un philosophe et homme politique anglo-irlandais, considéré comme l'un des fondateurs du conservatisme moderne. Il s'opposa farouchement à la Révolution française, défendant l'évolution graduelle des institutions plutôt que les ruptures radicales. Il étudia au Trinity College avant de s'installer à Londres pour exercer le droit et entrer en politique. Député whig à la Chambre des communes de 1766 à 1794, il soutint l'indépendance américaine tout en critiquant les excès fiscaux britanniques. Sa célèbre Réflexions sur la Révolution de France (1790) alerta sur les dangers de la &quot;multitude perverse&quot; et du rejet des traditions. &lt;/p&gt; &lt;p&gt; Il  voyait la société comme un &quot;partenariat entre les vivants, les morts et ceux qui ne sont pas encore nés&quot;, valorisant les &lt;a href=&quot;https://www.youtube.com/watch?v=az1n7gSaKFE&quot; title=&quot;La tradition permet elle le changement  par la chaine de Velours&quot;&gt;préjugés hérités &lt;/a&gt; comme bank de sagesse collective supérieure à la raison individuelle. Dans Recherches philosophiques sur l'origine de nos idées du sublime et du beau (1757), il distingue le sublime (lié à la douleur, à la terreur et à Dieu) du beau (lié au plaisir et à la société), influençant l'esthétique romantique. Il prônait l'amélioration progressive de la nature humaine imparfaite, sans table rase. &lt;/p&gt; &lt;p&gt; Surnommé &quot;conservateur des Lumières&quot;, il inspira des penseurs comme Roger Scruton et reste une référence contre les utopies rationalistes. En France, il fut parfois taxé de réactionnaire, mais son libéralisme tempéré et son sens de la responsabilité des élites résonnent encore. &lt;/p&gt;  &lt;audio controls title=&quot;Les britaniques ; Burke et ses héritiers par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-10.12.2024-ITEMA_23958056-2024C48904S0345-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;&#10;&#10;" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" display="https://laphilo.fr/pho/ghlessing-mini.webp" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Johann_Kaspar_Lavater&quot;  title=&quot; Wikipedia&quot;&gt;Johann Kaspar LAVATER&lt;/a&gt;  était un théologien, poète et philosophe suisse, connu surtout comme pionnier de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Physiognomonie&quot;  title=&quot;Physiognomonie par Wikipedia&quot;&gt; &quot;la physiognomonie, &lt;/a&gt;  une pseudoscience liant traits du visage et caractère moral. Pasteur réformé à Zurich, il mêla mysticisme chrétien, irrationalisme et influences des Lumières tardives dans ses écrits. Né à Zurich dans une famille bourgeoise, il étudia la théologie et la philosophie au Collegium Carolinum sous Johann Jakob Bodmer. Ordonné en 1762, il devint diacre puis pasteur à l'église St-Pierre, tout en s'engageant contre la corruption locale, ce qui l'exila brièvement à Berlin. Ami de Goethe (dont la relation se tendit) et de Moses Mendelssohn, il fut blessé lors de l'invasion française de 1799 et mourut de ses blessures. &lt;/p&gt; &lt;p&gt; Sa grande œuvre, Physiognomische Fragmente zur Beförderung der Menschenkenntnis und Menschenliebe (1775-1778), postule que le visage révèle l'âme divine en l'homme, reliant esthétique, vertu et théologie. Influencé par l'Empfindsamkeit et le Sturm und Drang, il valorisait le sentiment sur la raison pure, explorant prophétie, miracles et palingénésie (résurrection). Critiqué par Lichtenberg pour son subjectivisme, il inspira poésie mystique et débats sur  &lt;a href=&quot;https://www.youtube.com/watch?v=LUxSlXIY-Zk&quot;  title=&quot;Johann Kaspar Lavater par Grow Wise&quot;&gt; &quot;l'intériorité humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il  incarna un pont entre piétisme, sentimentalisme et romantisme naissant, influençant esthétique et psychologie populaire en Europe. Ses idées déclinèrent avec les progrès scientifiques, mais sa quête d'une connaissance intuitive de l'homme reste débattue. &lt;/p&gt; &#10;" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet&quot;  title=&quot; Wikipedia&quot;&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe , mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href=&quot;https://www.youtube.com/watch?v=3G3kVl0GbA8&quot;  title=&quot;Condorcet féministe ? par Sud Radio&quot;&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote .  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href=&quot;https://www.youtube.com/watch?v=3G3kVl0GbA8&quot;  title=&quot;Condorcet et l’éloge de l’instruction par Culture philo&quot;&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href=&quot;https://www.youtube.com/watch?v=avTI9GHZX1I&quot;  title=&quot;Condorcet le paradoxe par Diable Positif&quot;&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la &quot;mathématique sociale&quot;, Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title=&quot;Nicolas de Condorcet par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nihilisme&quot;  title=&quot;Nihilisme par Wikipedia&quot;&gt; nihilisme &lt;/a&gt; et au &lt;a href=&quot;https://fr.wikipedia.org/wiki/Panth%C3%A9isme&quot;  title=&quot;Panthéisme par Wikipedia&quot;&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse &quot;querelle du panthéisme&quot; en révélant que Lessing s'était  &lt;a href=&quot;https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321&quot;  title=&quot;Jacobi et Spinoza par Persée&quot;&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu . &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du &quot;rien ne sort du néant&quot;) de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un &quot;saut de la foi&quot; hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. - David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. - Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; &#10;&#10;&#10;" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marcus_Herz&quot;  title=&quot; Wikipedia&quot;&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Immanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2&quot; title=&quot;Kant, Lettre à Marcus Herz du 21 février 1772 par Persée&quot;&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la &quot;révolution copernicienne&quot;), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent &quot;Betrachtungen aus der spekulativen Weltweisheit&quot;  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et &quot;Versuch über den Geschmack&quot; en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; " r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Friedl%C3%A4nder&quot;  title=&quot; Wikipedia&quot;&gt;David FRIEDLÄNDER&lt;/a&gt;  était un intellectuel, marchand et réformateur juif allemand, disciple de Moses Mendelssohn, plus connu comme pionnier de l'Haskalah (Lumières juives) et de la  &lt;a  href=&quot;https://www.persee.fr/doc/reval_0035-0974_1973_num_5_3_1989&quot;  title=&quot;D Friedlander et la réforme des communaités juives de prusse par Persée&quot;&gt; réforme religieuse &lt;/a&gt; que comme philosophe académique strict. Il prôna l'émancipation des Juifs par l'assimilation culturelle et une dédogmatisation du judaïsme, fusionnant rationalisme des Lumières et monothéisme mosaïque originel contre les rituels &quot;superstitieux&quot;. &lt;/p&gt; &lt;p&gt; Né à Königsberg, il s'installa à Berlin en 1770, fonda une usine de soie et intégra l'élite juive éclairée via son mariage avec la fille du banquier Daniel Itzig. Après la mort de Mendelssohn (1786), il mena la Haskalah berlinoise : création de la Chevrat Chinuch Ne’arim (école juive libre en 1778), traductions de prières en allemand, et plaidoyers pour l'égalité civile. Premier conseiller municipal juif à Berlin, il lutta contre les discriminations prussiennes. &lt;/p&gt; &lt;p&gt; Il rejetait le Talmud et les rites comme &quot;œuvres de sainteté, verbiage et futilités&quot;, défendant un judaïsme &quot;pur&quot; : monothéisme rationnel commun aux religions abrahamiques, sans dogmes christologiques ni observances contraignantes. Dans son Sendschreiben anonyme (1799) à l'ecclésiastique Wilhelm Teller, il proposa une union judéo-protestante déiste – baptême symbolique sans trinité, en échange d'émancipation –, vu comme opportuniste mais innovant pour le judaïsme réformé naissant. Il resta juif par fidélité au &quot;monothéisme mosaïque idéal&quot;, contrairement à sa famille convertie. &lt;/p&gt; &lt;p&gt; Précurseur du judaïsme réformé et de l'assimilation prussienne, Friedländer incarna le dilemme post-mendelssohnien : identité juive face à l'universalisme. Critiqué pour pragmatisme, il influença les réformes liturgiques et débats sur l'émancipation, bien que son projet fusionnel échouât face au romantisme montant. &lt;/p&gt; &#10;&#10;" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" display="https://laphilo.fr/photo/dfriedlander.webp" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joseph_de_Maistre&quot;  title=&quot; Wikipedia&quot;&gt;Joseph de MAISTRE&lt;/a&gt; était un philosophe, écrivain et diplomate savoyard, figure majeure de la contre-révolution et critique virulent des Lumières et de la Révolution française. Considéré comme un père de la pensée conservatrice moderne, il défend une vision organique de la société, hiérarchique et divinement ordonnée, où l'autorité monarchique et religieuse prime sur les idées contractualistes et individualistes. &lt;/p&gt; &lt;p&gt;  Pour lui, la Révolution française est un &lt;a href=&quot;https://www.persee.fr/doc/bude_0004-5527_1989_num_1_2_1393&quot; title=&quot;Sacré et sacrifice dans la pensée de Joseph de Maistre par Persée&quot;&gt;châtiment providentiel &lt;/a&gt; des excès des philosophes des Lumières, punissant l'athéisme et le rationalisme par la Terreur. Les sociétés ne naissent pas d'un contrat rationnel (comme chez Rousseau), mais d'une autorité divine imposée d'en haut; l'individu abstrait n'existe pas, il est façonné par la tradition et l'État.  Il prône une monarchie absolue et l'autorité suprême du Pape pour unifier l'Europe spirituellement et temporellement. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures sont : - &quot;Considérations sur la France&quot; paru en 1797 : Interprétation providentialiste de la Révolution comme mission divine de la France. - &quot;Essai sur le principe générateur des constitutions&quot; paru en 1809 :  &lt;a href=&quot;https://www.youtube.com/watch?v=oPEzOiEdrNE&quot;  title=&quot; L'oecuménisme de Joseph de Maistre par BAGLIS TV&quot;&gt;Les constitutions &lt;/a&gt; viennent de Dieu, non de la raison humaine et - &quot;Soirées de Saint-Pétersbourg&quot;  en1821, posthume : Théodicée justifiant le mal (guerre, sacrifice) comme partie du plan divin. &lt;/p&gt; &lt;p&gt; Il a eu une influence durablement le conservatisme, le romantisme contre-révolutionnaire et des penseurs comme Donoso Cortés, tout en étant critiqué pour son apologie de la violence. Sa pensée hiérarchique et anti-individualiste reste débattue face aux idéaux démocratiques modernes. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Troisième penseur, Joseph de Maistre. par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-26.10.2011-ITEMA_20317797-2011C12410S0299-NET_F022382B-0B64-4C5C-B335-284B201C884D_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Louis_de_Bonald&quot;  title=&quot; Wikipedia&quot;&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Tradition_primordiale&quot;  title=&quot; Tradition Primordiale de Maistre par Wikipedia &quot;&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. - Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. - Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href=&quot;https://www.youtube.com/watch?v=WMB9kethTWIe&quot;  title=&quot; Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations &quot;&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral&quot;  title=&quot; Maurrassisme par Wikipedia &quot;&gt; maurrassisme, &lt;a&gt; voyant la France comme &quot;nation-pilote&quot; pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant . &lt;/p&gt;&#10; &#10;&#10;//" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Antoine_Destutt_de_Tracy&quot;  title=&quot; Wikipedia&quot;&gt;Destutt de TRACY&lt;/a&gt; était un philosophe et idéologue français, fondateur et théoricien principal du courant philosophique des Idéologues. Né Antoine Louis Claude Destutt, comte de Tracy, dans une famille noble auvergnate, il fit une carrière militaire avant de se consacrer à la philosophie après son emprisonnement pendant la Terreur. Membre de l'Institut national et de l'Académie française, il joua un rôle central dans la vie intellectuelle française sous le Directoire et le Consulat. &lt;/p&gt; &lt;p&gt; Sa contribution majeure est la création de l'« idéologie » comme science des idées. Dans ses &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=DAz6QsBdeyg&quot;  title=&quot;Destrutt de DRACYi par Wikipedia Fan&quot;&gt;Éléments d'idéologie &lt;/a&gt; &lt;/em&gt; (5 volumes, 1801-1815), il cherche à fonder une science générale des idées qui analyserait leur formation à partir des sensations et des signes. S'inscrivant dans la tradition sensualiste de Condillac, il développe une sémiologie et une grammaire générale visant à purifier le langage de ses ambiguïtés et à fonder les sciences humaines sur des bases empiriques solides. Son projet était d'édifier une « science des sciences » qui servirait de fondement à l'enseignement et à la réforme sociale. &lt;/p&gt; &lt;p&gt; Sa &lt;em&gt;Logique&lt;/em&gt; et son &lt;em&gt;Commentaire sur l'Esprit des Lois de Montesquieu&lt;/em&gt; (1811) témoignent de son intérêt pour la philosophie politique libérale. Jefferson, qui admirait sa pensée, fit traduire son &lt;em&gt;Traité de la volonté&lt;/em&gt; en anglais. Ironiquement, le terme même d'« idéologie » qu'il avait forgé fut retourné contre lui par Napoléon, qui qualifiait les Idéologues d'esprits abstraits et dangereux. Marx reprit ensuite ce terme dans un sens radicalement différent. Destutt de Tracy reste une figure essentielle pour comprendre l'émergence des sciences humaines en France. &lt;/p&gt;" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Laromigui%C3%A8re&quot;  title=&quot; Wikipedia&quot;&gt;Pierre LAROMIGUIÈRE&lt;/a&gt; était un philosophe français, l'une des figures transitoires entre le sensualisme des Lumières et la philosophie spiritualiste du XIXe siècle. Né à Livinhac-le-Haut dans l'Aveyron, il fut d'abord prêtre avant la Révolution, puis professeur de philosophie à l'École centrale des arts et manufactures et enfin à la Sorbonne. Ses cours, qui attirèrent un public nombreux et enthousiaste dans les premières décennies du XIXe siècle, contribuèrent à renouveler l'enseignement de la philosophie en France. &lt;/p&gt; &lt;p&gt; Sa philosophie part du sensualisme de Condillac mais s'en écarte sur un point décisif : là où Condillac réduisait toutes les opérations de l'esprit à des sensations transformées, Laromiguière distingue soigneusement les sensations des opérations actives de l'attention, de la comparaison et du jugement. Cette distinction entre les facultés passives et les facultés actives de l'esprit ouvre la voie à une conception plus riche de la vie psychique, qui reconnaît la spécificité de l'activité intellectuelle irréductible à la simple réception sensorielle. &lt;/p&gt; &lt;p&gt; Dans ses &lt;em&gt;Leçons de philosophie&lt;/em&gt; (1815-1818), dont la clarté et l'agrément du style lui valurent un succès durable, il développe cette psychologie des facultés dans un cadre pédagogique accessible. Bien que sa pensée ait été éclipsée par le courant spiritualiste de Cousin et par le positivisme de Comte, Laromiguière représente une étape importante dans la constitution de la psychologie philosophique française. Sa manière de corriger Condillac par une attention accrue à l'activité de l'esprit préfigure les développements du spiritualisme ultérieur. &lt;/p&gt;" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Jean_Georges_Cabanis&quot; title=&quot; Wikipedia&quot;&gt;Pierre CABANIS&lt;/a&gt; était un médecin et philosophe français, figure majeure du groupe des Idéologues et pionnier d'une approche naturaliste de la vie psychique. Né à Cosnac en Corrèze, il fut introduit dans les cercles intellectuels parisiens par Turgot et fréquenta le salon d'Helvétius. Ami intime de Mirabeau dont il soigna les derniers jours, il participa activement à la vie politique de la Révolution et du Directoire, siégeant au Conseil des Cinq-Cents. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;Rapports du physique et du moral de l'homme&lt;/em&gt; (1802), est un essai audacieux pour fonder une science de l'homme sur des bases physiologiques. Cabanis y soutient que les phénomènes psychiques sont intimement liés aux processus organiques du corps : le cerveau secrète la pensée comme le foie sécrète la bile. Cette formule provocatrice, souvent mal comprise, visait en réalité à établir une méthode empirique pour l'étude de l'âme, refusant tout recours à des entités métaphysiques abstraites. &lt;/p&gt; &lt;p&gt; Médecin réformateur, il œuvra à la réorganisation des hôpitaux parisiens et milita pour une médecine fondée sur l'observation clinique plutôt que sur les théories scolastiques. Ses travaux contribuèrent à l'essor de l'hygiénisme et de la médecine sociale. Sa pensée, qui anticipe certains aspects du matérialisme médical du XIXe siècle, représente une étape importante dans la constitution des sciences humaines. Bien que les Idéologues aient été rabroués par Napoléon qui les rendait responsables des « idéologues abstraits », l'influence de Cabanis sur la médecine et la psychologie françaises fut durable. &lt;/p&gt;" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" display="https://www.laphilo.fr/pho/cabanis-mini.webp" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre-Paul_Royer-Collard&quot;  title=&quot; Wikipedia&quot;&gt;Pierre-Paul ROYER-COLLARD&lt;/a&gt;  était un philosophe et homme politique français, figure majeure du libéralisme modéré sous la Restauration et chef des Doctrinaires. Né en Champagne, il commence comme avocat au Parlement de Paris avant de s'engager politiquement. Pendant la Révolution, il soutient les Girondins et fuit la Terreur, se retirant dans ses terres. Sous la Restauration, il devient député de la Marne et préside la Chambre des députés (1828–1830), tout en enseignant l'histoire de la philosophie moderne à la Sorbonne. &lt;/p&gt; &lt;p&gt; Sa philosophie se présente comme un rejet du sensualisme de Condillac qui dominait le XVIIIᵉ siècle français. Il s'inspire du philosophe écossais Thomas Reid et introduit en France la doctrine du sens commun. Contrairement aux sensualistes, il distingue clairement la sensation (subjective, plaisir ou peine) de la perception (appréhension d'un objet externe). Pour lui, la perception implique un jugement spontané de l'esprit actif, non déductible des seuls sens. &lt;/p&gt; &lt;p&gt; Il développe un spiritualisme rigoureux : l'esprit humain est actif et capable de jugements autonomes. Le sens commun – cette faculté naturelle de distinguer le bien du mal, le vrai du faux – fonde la vie communautaire et remplace l'autorité surnaturelle. Par les principes de causalité et d'induction, la raison conduit nécessairement à l'idée d'une Première Cause (Dieu). Il affirme la supériorité irréductible de la personne humaine sur l'État, les personnes étant &lt;a  href=&quot;https://www.youtube.com/watch?v=15bNqKMiW_w&quot;  title=&quot;R Collard ou l’ambilalence des restaurations par Collège st Germain&quot;&gt;« faites à l'image de Dieu et douées d'immortalité ».&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Politiquement, il est un royaliste libéral qui considère la Révolution de 1789 comme irréversible. Il cherche à fonder une monarchie constitutionnelle stable entre l'Ancien Régime (les Ultras) et le totalitarisme napoléonien, puis la démocratisation trop rapide sous Louis-Philippe. Il incarne la « philosophie de la Charte » et influence profondément François Guizot. N'a presque rien publié de son vivant : ses écrits philosophiques ont été rassemblés après coup par son admirateur Théodore Jouffroy.  &lt;/p&gt; " r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" display="https://www.laphilo.fr/pho/pcollard-mini.webp" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Claude-Henri_de_Rouvroy_de_Saint-Simon&quot; title=&quot; Wikipedia&quot;&gt;Claude-Henri de ROUVROY, comte de SAINT-SIMON&lt;/a&gt; est un penseur et réformateur social français, issu d’une famille aristocratique qui revendiquait une lointaine parenté avec Charlemagne. Volontaire dans l’armée française envoyée soutenir l’indépendance américaine, il participe au siège de Yorktown avant de renoncer, sous la Révolution, à son titre de noblesse.  &lt;a href=&quot;https://maitron.fr/saint-simon-claude-henri-claude-henri-de-rouvroy-comte-de-saint-simon/&quot; title=&quot;saint simon par le maitron&quot;&gt;Spéculateur &lt;/a&gt; sur les biens nationaux, emprisonné pendant la Terreur, il connaît ensuite une vie mouvementée, tour à tour fortunée et misérable, entièrement vouée à la recherche d’une science nouvelle de la société. &lt;/p&gt; &lt;p&gt; Convaincu que la Révolution a détruit l’ancien ordre théologique et féodal sans encore bâtir l’ordre qui doit lui succéder, Saint-Simon appelle à fonder une organisation sociale confiée non plus aux militaires, aux juristes ou aux rentiers, mais aux savants, aux industriels et aux producteurs. Dans des ouvrages comme &lt;em&gt;L’Industrie&lt;/em&gt; ou &lt;em&gt;Du système industriel&lt;/em&gt;, il défend l’idée que le pouvoir politique doit être subordonné à la production utile : gouverner, pour lui, revient d’abord à administrer les choses et à organiser le travail, plutôt qu’à commander les hommes. &lt;/p&gt; &lt;p&gt; Il élabore ainsi une &lt;a href=&quot;https://fr.wikipedia.org/wiki/Saint-simonisme&quot; title=&quot;Saint-simonisme par Wikipedia&quot;&gt;philosophie de l’histoire&lt;/a&gt; fondée sur l’alternance de périodes « organiques » et « critiques », et annonce l’avènement d’un âge industriel où la science et la technique remplaceraient la théologie comme principe d’unité sociale. Son dernier livre, &lt;em&gt;Le Nouveau Christianisme&lt;/em&gt; (1825), publié l’année de sa mort, prône une religion de la fraternité entièrement tournée vers l’amélioration du sort des classes les plus pauvres, qu’il présente comme la fin ultime de toute organisation sociale et politique légitime. &lt;/p&gt; &lt;p&gt; Bien que ses écrits soient souvent fragmentaires et inachevés, Saint-Simon laisse une postérité considérable : ses disciples, réunis après sa mort en une école puis en une véritable Église saint-simonienne, diffusent et systématisent sa pensée sous le nom de saint-simonisme. Ce courant influencera profondément le socialisme utopique du XIXe siècle, la sociologie naissante d’Auguste Comte (un temps son secrétaire), ainsi que les grandes entreprises industrielles et financières du Second Empire, qui reprendront à leur compte son culte du progrès technique et de l’organisation rationnelle de la production. &lt;/p&gt;" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" display="https://www.laphilo.fr/pho/hssimon-mini.webp" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Maine_de_Biran&quot;  title=&quot; Wikipedia&quot;&gt;Maine de BIRAN&lt;/a&gt; était un philosophe français, considéré comme l'un des fondateurs de la philosophie de l'intériorité et du spiritualisme français. Né François-Pierre Gonthier de Biran à Bergerac en Dordogne, il commença sa carrière comme officier de la garde du roi, avant de se consacrer à la philosophie et à la vie politique locale en Périgord. Administrateur apprécié sous plusieurs régimes successifs, il fut député et sous-préfet, mais c'est à travers ses journaux intimes et ses &lt;a  href=&quot;https://www.youtube.com/watch?v=ayhmQ5WQfJk&quot;  title=&quot;Maine de Biran spiritualité &amp; phénoménologie par ICP&quot;&gt;essais philosophiques &lt;/a&gt; que son originalité s'exprima pleinement. &lt;/p&gt; &lt;p&gt; Sa pensée prend pour point de départ l'expérience immédiate de l'effort : c'est dans l'acte volontaire par lequel le moi exerce une résistance contre le corps propre que la conscience se saisit elle-même comme force et comme liberté. Contre le sensualisme de Condillac qui réduisait l'âme à la sensation passive, il soutient que l'activité volontaire constitue le fait primitif de la conscience. Cette découverte du « moi voulant » comme donnée irréductible de l'intériorité marque une rupture décisive dans la philosophie française. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;t &lt;a  href=&quot;https://www.persee.fr/doc/bupsy_0007-4403_1963_num_17_224_9102&quot;  title=&quot;Maine de Biran fondateur de la psychologie française par Persée&quot;&gt;Essai sur les fondements de la psychologie &lt;/a&gt; &lt;/em&gt; (1812) et ses nombreux &lt;em&gt;Mémoires&lt;/em&gt; rédigés pour les concours de l'Institut, développent une psychologie de l'effort qui distingue trois ordres d'existence : la vie animale (sensations), la vie humaine (volonté et conscience) et la vie de l'esprit (grâce et amour mystique). Cette trilogie, d'inspiration néo-platonicienne et chrétienne dans sa dernière phase, influença profondément Ravaisson, Bergson et tout le courant spiritualiste français. Ses &lt;em&gt;Journal&lt;/em&gt; et &lt;em&gt;Mémoire sur les perceptions obscures&lt;/em&gt; témoignent d'une introspection d'une subtilité et d'une profondeur rares. &lt;/p&gt;" r:id="rId51"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -925,9 +925,7 @@
       </c>
       <c r="E5" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/%C3%89rasme"  title=" Wikipedia"&gt;ÉRASME de Rotterdam&lt;/a&gt; était un philosophe et Humaniste, un mouvement &lt;a href="https://www.youtube.com/watch?v=yIz5ltk3lJA&amp;ab_channel=Rienneveutriendire"  title="Portrait d'un intellectuel par Rien ne veut rien dire"&gt;intellectuel&lt;/a&gt; qui a émergé pendant la Renaissance en Europe et qui a mis l'accent sur l'importance de l'individu, de la raison et de l'éducation. Il croyait que l'éducation était la clé pour améliorer la vie humaine et promouvoir le progrès social. &lt;/p&gt; &lt;p&gt; Il a écrit de nombreux livres, notamment &lt;a href="https://www.youtube.com/watch?v=bwZbMqs9F1w&amp;ab_channel=%C3%89ditionsDianedeSelliers"  title="l'Eloge de la folie illustré par les peintres de la Renaissance du Nord par Diane de Selliers"&gt;"L'Éloge de la Folie"&lt;/a&gt; où il présente la Folie comme une divinité qui, par son pouvoir, rend supportable la vie humaine et les faiblesses de l'humanité, et "Le Manuel du Chrétien", qui ont été largement lus et influents à l'époque. &lt;/p&gt; &lt;p&gt; Érasme a également travaillé à la réforme de l'Église catholique et a critiqué les abus et les excès de l'Église de son époque. Il a plaidé pour un retour aux sources du christianisme, en se basant sur les textes originaux de la Bible, plutôt que sur les traditions et les dogmes de l'Église. Il avait un grand intérêt pour la musique, qu'il considérait comme un moyen important pour les gens de se rapprocher de Dieu et d'atteindre un état de bien-être spirituel.&lt;/p&gt; &lt;p&gt;
-Il a lui-même joué de plusieurs instruments de musique, dont le luth et l'orgue et a également &lt;a href="https://www.youtube.com/watch?v=byUyM3fwf5Y&amp;ab_channel=KARLMORE"   title="Marche guérrière ottomane par Karl More"&gt;écrit sur la musique&lt;/a&gt;  dans plusieurs de ses œuvres, y compris dans "De ratione studii puerilis".   &lt;/p&gt;   &lt;audio controls title="Erasme, l'Européen par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-27.07.2019-ITEMA_22116176-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89rasme"  title=" Wikipedia"&gt;ÉRASME de Rotterdam&lt;/a&gt; (vers 1466-1536) est le plus célèbre des humanistes de la Renaissance, un &lt;a href="https://www.youtube.com/watch?v=yIz5ltk3lJA&amp;ab_channel=Rienneveutriendire"  title="Portrait d'un intellectuel par Rien ne veut rien dire"&gt;intellectuel&lt;/a&gt; européen avant la lettre. Fils illégitime d’un prêtre, il devient chanoine, étudie à Paris, puis voyage sans cesse à travers l’Europe, d’Angleterre en Italie et de Louvain à Bâle, où il meurt. Ami de l’Anglais Thomas More, il correspond avec les savants, les princes et les papes de son temps.&lt;/p&gt; &lt;p&gt;Érasme veut unir la culture antique et la foi chrétienne. Ses &lt;em&gt;Adages&lt;/em&gt;, recueil de milliers de proverbes grecs et latins commentés, font connaître à toute l’Europe la sagesse des Anciens. Dans le &lt;em&gt;Manuel du soldat chrétien&lt;/em&gt; (1503), il défend un christianisme intérieur, fondé sur l’imitation du Christ plutôt que sur les cérémonies. En 1516, il publie la première édition imprimée du Nouveau Testament en grec, accompagnée d’une nouvelle traduction latine, pour revenir aux sources mêmes de la foi. Dans &lt;a href="https://www.youtube.com/watch?v=bwZbMqs9F1w&amp;ab_channel=%C3%89ditionsDianedeSelliers"  title="l'Eloge de la folie illustré par les peintres de la Renaissance du Nord par Diane de Selliers"&gt;&lt;em&gt;L’Éloge de la folie&lt;/em&gt;&lt;/a&gt; (1511), la Folie prend la parole et se moque des théologiens, des moines, des princes et des savants, montrant combien la vie humaine repose sur des illusions. Pacifiste convaincu, il dénonce la guerre dans la &lt;em&gt;Complainte de la paix&lt;/em&gt; : « la guerre est douce à qui ne l’a pas faite ». Il ne s’y résigne qu’avec réticence face à la menace ottomane, dans un traité sur &lt;a href="https://www.youtube.com/watch?v=byUyM3fwf5Y&amp;ab_channel=KARLMORE"   title="Marche guérrière ottomane par Karl More"&gt;la guerre contre les Turcs&lt;/a&gt; (1530). Il critique aussi les abus de l’Église, mais refuse de suivre Luther, avec qui il se brouille en 1524 sur la question du libre arbitre, qu’il défend.&lt;/p&gt; &lt;p&gt;Son nom désigne aujourd’hui le programme européen d’échanges d’étudiants, fidèle à son idéal d’une culture commune.&lt;/p&gt;  &lt;audio controls title="Erasme, l'Européen par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16278-27.07.2019-ITEMA_22116176-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F5" s="47" t="inlineStr">
@@ -1190,7 +1188,7 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_de_Bovelles"  title=" Wikipedia"&gt;CHARLES de Bovelles&lt;/a&gt;   était un philosophe, mathématicien et humaniste français de la Renaissance. Élève de Jacques Lefèvre d'Étaples au collège du Cardinal-Lemoine, il enseigna la philosophie, la logique et l'arithmétique, et fut chanoine à Noyon et Saint-Quentin. &lt;/p&gt; &lt;p&gt; Issu d'une famille picarde, il étudia à Paris dès 1495, voyagea en Italie et en Espagne, et embrassa l'état ecclésiastique pour obtenir des bénéfices canoniaux. Professeur influent, il eut pour élève Beatus Rhenanus et contribua à la pédagogie mathématique en publiant la première Géométrie en françoys en 1511.  &lt;a href="https://www.persee.fr/doc/rhren_0181-6799_1983_num_17_1_1383" title=" Charles de Bovelles en son cinquième centenaire 1479-1979. Actes du colloque international tenu à Noyon les 14 - 15 - 16 septembre 1979  par Persée"&gt;Sa carrière &lt;/a&gt; mêla érudition humaniste, théologie et sciences, sous la protection d'évêques locaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique, il publia des traités philosophiques comme le "Liber de Sapiente" paru en 1509 et explorant la sagesse comme harmonie entre raison, vertu et cosmos, où l'homme est un microcosme reflétant l'univers. Ses écrits sur l'extase "De raptu divi Pauli" paru en 1531 et les visions prophétiques analysent l'élévation spirituelle au-delà des sens. Influencé par Nicolas de Cues, il synthétisa scolastique médiévale et humanisme renaissant, insistant sur la coincidentia oppositorum et la connaissance de soi. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_de_Bovelles"  title=" Wikipedia"&gt;CHARLES de Bovelles&lt;/a&gt;   était un philosophe, mathématicien et humaniste français de la Renaissance. Élève de Jacques Lefèvre d'Étaples au collège du Cardinal-Lemoine, il enseigna la philosophie, la logique et l'arithmétique, et fut chanoine à Noyon et Saint-Quentin. &lt;/p&gt; &lt;p&gt; Issu d'une famille picarde, il étudia à Paris dès 1495, voyagea en Italie et en Espagne, et embrassa l'état ecclésiastique pour obtenir des bénéfices canoniaux. Professeur influent, il eut pour élève Beatus Rhenanus et contribua à la pédagogie mathématique en publiant la première Géométrie en françoys en 1511.  &lt;a href="https://www.persee.fr/doc/rhren_0181-6799_1983_num_17_1_1383" title=" Charles de Bovelles en son cinquième centenaire 1479-1979. Actes du colloque international tenu à Noyon les 14 - 15 - 16 septembre 1979  par Persée"&gt;Sa carrière &lt;/a&gt; mêla érudition humaniste, théologie et sciences, sous la protection d'évêques locaux. &lt;/p&gt; &lt;p&gt; Auteur prolifique, il publia des traités philosophiques comme le "Liber de Sapiente" paru en 1509 et explorant la sagesse comme harmonie entre raison, vertu et cosmos, où l'homme est un microcosme reflétant l'univers. Ses écrits sur l'extase "De raptu divi Pauli" paru en 1531 et les visions prophétiques analysent l'élévation spirituelle au-delà des sens. Influencé par Nicolas de Cues, il synthétisa scolastique médiévale et humanisme renaissant, insistant sur la coincidentia oppositorum et la connaissance de soi. Dans le &lt;em&gt;Livre du sage&lt;/em&gt;, il décrit l’homme comme un être qui n’a pas de place fixe dans l’univers : il est un miroir du monde, et c’est par la connaissance qu’il se construit lui-même et devient pleinement homme. Il consacre aussi un traité étonnant au néant, &lt;em&gt;Du néant&lt;/em&gt;,. Le philosophe Ernst Cassirer a vu en lui l’une des expressions les plus nettes de l’idée renaissante de l’homme. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F9" s="51" t="inlineStr">
@@ -1317,7 +1315,7 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_de_Vitoria"  title=" Wikipedia"&gt;FRANCISCO de Victoria&lt;/a&gt;  était un théologien, philosophe et juriste espagnol. Membre de l'ordre dominicain, il est une figure majeure de &lt;a href="https://www.persee.fr/doc/carav_0008-0152_1987_num_48_1_2318_t1_0201_0000_2" title="Francisco de Vitoria y la Escuela de Salamanca par Persée"&gt;l'École de Salamanque&lt;/a&gt;, un mouvement intellectuel qui a joué un rôle crucial dans le développement de la pensée économique, juridique et éthique à la Renaissance. Après ses études, il enseigne à Paris, puis retourne en Espagne où il devient professeur de théologie à l'Université de Salamanque où il réforme l'enseignement de la théologie en introduisant une approche plus humaniste et en mettant l'accent sur les questions éthiques et juridiques. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme le père du droit international moderne. Il développe une théorie du jus gentium (droit des gens), qui s'applique à tous les peuples, indépendamment de leur culture ou de leur religion. Il affirme que les nations sont souveraines, mais qu'elles sont liées par des principes universels de justice et de moralité. Il est l'un des  &lt;a href="https://www.youtube.com/watch?v=3hg8CqfyDFI&amp;list=PL0rFKbIsatLHwWCB-7gMpbOVNO3JT8xBd" style="color:#88A1E9" title="Francisco de Vitoria par Filosofia Apuntes"&gt;premiers penseurs&lt;/a&gt;  à défendre les droits des peuples indigènes des Amériques. Dans ses conférences De Indis, il critique la colonisation espagnole et affirme que les Amérindiens sont des êtres rationnels dotés de droits naturels. &lt;/p&gt; &lt;p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_de_Vitoria"  title=" Wikipedia"&gt;Francisco de VITORIA&lt;/a&gt;  était un théologien, philosophe et juriste espagnol. Membre de l'ordre dominicain, il est une figure majeure de &lt;a href="https://www.persee.fr/doc/carav_0008-0152_1987_num_48_1_2318_t1_0201_0000_2" title="Francisco de Vitoria y la Escuela de Salamanca par Persée"&gt;l'École de Salamanque&lt;/a&gt;, un mouvement intellectuel qui a joué un rôle crucial dans le développement de la pensée économique, juridique et éthique à la Renaissance. Après ses études, il enseigne à Paris, puis retourne en Espagne où il devient professeur de théologie à l'Université de Salamanque où il réforme l'enseignement de la théologie en introduisant une approche plus humaniste et en mettant l'accent sur les questions éthiques et juridiques. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme le père du droit international moderne. Il développe une théorie du jus gentium (droit des gens), qui s'applique à tous les peuples, indépendamment de leur culture ou de leur religion. Il affirme que les nations sont souveraines, mais qu'elles sont liées par des principes universels de justice et de moralité. Il est l'un des  &lt;a href="https://www.youtube.com/watch?v=3hg8CqfyDFI&amp;list=PL0rFKbIsatLHwWCB-7gMpbOVNO3JT8xBd" style="color:#88A1E9" title="Francisco de Vitoria par Filosofia Apuntes"&gt;premiers penseurs&lt;/a&gt;  à défendre les droits des peuples indigènes des Amériques. Dans ses conférences De Indis, il critique la colonisation espagnole et affirme que les Amérindiens sont des êtres rationnels dotés de droits naturels. &lt;/p&gt; Né à Burgos vers 1483, il remplace à Salamanque l’étude des &lt;em&gt;Sentences&lt;/em&gt; de Pierre Lombard par celle de la &lt;em&gt;Somme théologique&lt;/em&gt; de Thomas d’Aquin. Dans ses leçons &lt;em&gt;Sur les Indiens&lt;/em&gt; (1539), il soutient qu’ils sont les vrais propriétaires de leurs terres, et que ni le pape ni l’empereur ne sont les maîtres du monde ; il admet pourtant un droit de circuler, de commercer et de prêcher, qui a pu servir à justifier la conquête. &lt;p&gt; </t>
         </is>
       </c>
       <c r="F11" s="51" t="inlineStr">
@@ -2611,7 +2609,7 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Gassendi"  title=" Wikipedia"&gt; Pierre GASSENDI&lt;/a&gt;  était un philosophe, scientifique, astronome et mathématicien français, connu pour &lt;a href="https://www.gassendi.fr/index.php" style="color:#88A1E9" title="Pierre GASSENDI par gassendi.fr "&gt;ses contributions&lt;/a&gt; à la philosophie naturelle, à la renaissance de l'épicurisme et pour ses critiques des philosophies de Descartes et d'Aristote. Il  a été un observateur attentif des phénomènes célestes. Il est notamment connu pour avoir été le premier à observer le transit de Mercure devant le Soleil en 1631, confirmant ainsi les prédictions de Kepler. &lt;/p&gt; &lt;p&gt; Il  a joué un &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1958_num_154_2_8873" title="Pierre GASSENDI par Persée "&gt;rôle clé &lt;/a&gt; dans la réhabilitation de la philosophie d'Épicure, qu'il a adaptée à un contexte chrétien. Il a défendu une vision atomiste de la nature, mais a rejeté les aspects matérialistes et athées de l'épicurisme antique. Il a plaidé pour une approche empirique de la connaissance, insistant sur l'importance de l'observation et de l'expérience. &lt;/p&gt; &lt;p&gt; Il a influencé des penseurs ultérieurs tels que John Locke et Isaac Newton. Son empirisme et son atomisme ont contribué au développement de la philosophie naturelle moderne tout en cherchant à concilier la science naissante avec la foi chrétienne, montrant que les découvertes scientifiques pouvaient être compatibles avec une vision religieuse du monde. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Gassendi"  title=" Wikipedia"&gt; Pierre GASSENDI&lt;/a&gt;  était un philosophe, scientifique, astronome et mathématicien français, connu pour &lt;a href="https://www.gassendi.fr/index.php" style="color:#88A1E9" title="Pierre GASSENDI par gassendi.fr "&gt;ses contributions&lt;/a&gt; à la philosophie naturelle, à la renaissance de l'épicurisme et pour ses critiques des philosophies de Descartes et d'Aristote. Il  a été un observateur attentif des phénomènes célestes. Il est notamment connu pour avoir été le premier à observer le transit de Mercure devant le Soleil en 1631, confirmant ainsi les prédictions de Kepler. &lt;/p&gt; &lt;p&gt; Il  a joué un &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1958_num_154_2_8873" title="Pierre GASSENDI par Persée "&gt;rôle clé &lt;/a&gt; dans la réhabilitation de la philosophie d'Épicure, qu'il a adaptée à un contexte chrétien. Il a défendu une vision atomiste de la nature, mais a rejeté les aspects matérialistes et athées de l'épicurisme antique. Il a plaidé pour une approche empirique de la connaissance, insistant sur l'importance de l'observation et de l'expérience. &lt;/p&gt; &lt;p&gt; Il a influencé des penseurs ultérieurs tels que John Locke et Isaac Newton. Son empirisme et son atomisme ont contribué au développement de la philosophie naturelle moderne tout en cherchant à concilier la science naissante avec la foi chrétienne, montrant que les découvertes scientifiques pouvaient être compatibles avec une vision religieuse du monde. Né en Provence en 1592, prêtre, professeur de philosophie à Aix puis de mathématiques au Collège royal de Paris, il est l’ami de Mersenne. Il rédige les cinquièmes &lt;em&gt;Objections&lt;/em&gt; aux &lt;em&gt;Méditations&lt;/em&gt; de Descartes, auquel il reproche de s’éloigner de l’expérience : Descartes l’appelle « Ô chair », Gassendi lui répond « Ô esprit ». Pour lui, les atomes ont été créés par Dieu en nombre fini, et l’âme raisonnable reste immatérielle. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -3499,7 +3497,7 @@
       </c>
       <c r="E43" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Poullain_de_La_Barre" title=" Wikipedia"&gt;François POULLAIN de la Barre&lt;/a&gt; était un  philosophe et écrivain français, connu comme un pionnier du  &lt;a href="https://www.youtube.com/watch?v=ddRMNFWa0lk"  title=" Un philosophe féministe à l'époque de Louis XIV par Citéphilo"&gt;féminisme moderne &lt;/a&gt; et un disciple de Descartes. Initialement étudiant en théologie et prêtre, il adopte la philosophie cartésienne et se convertit au protestantisme, s'exilant à Genève où il enseigne la philosophie. &lt;/p&gt; &lt;p&gt;  Il applique la méthode cartésienne pour démontrer que la prétendue infériorité des femmes n'a pas de fondement naturel, mais résulte de préjugés culturels. Dans son ouvrage anonyme de 1673,  &lt;a href="https://www.les-philosophes.fr/feminisme/de-l-egalite-des-deux-sexes.html"  title="De l'égalité des deux sexes, de l'éducation des dames, de l'excellence des hommes par Les Philosophes.fr"&gt; "De l’égalité des deux sexes"&lt;/a&gt;, il critique les idées patriarcales qui justifient les discriminations contre les femmes et revendique leur droit à une véritable éducation et à l'accès aux mêmes carrières que les hommes, y compris les sciences. Il publie également "De l’éducation des dames pour la conduite des esprits dans les sciences et dans les mœurs" en 1674 et plus tard, ironiquement, "De l’excellence des hommes contre l’égalité des sexes"  en 1675 dans le but de ridiculiser les arguments sexistes de son époque. Sa thèse centrale est que l'esprit, la raison, n'a pas de sexe, et que les différences sociales tiennent à l'éducation et aux préjugés. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Poullain_de_La_Barre" title=" Wikipedia"&gt;François POULLAIN de la Barre&lt;/a&gt; était un  philosophe et écrivain français, connu comme un pionnier du  &lt;a href="https://www.youtube.com/watch?v=ddRMNFWa0lk"  title=" Un philosophe féministe à l'époque de Louis XIV par Citéphilo"&gt;féminisme moderne &lt;/a&gt; et un disciple de Descartes. Initialement étudiant en théologie et prêtre, il adopte la philosophie cartésienne et se convertit au protestantisme, s'exilant à Genève où il enseigne la philosophie. &lt;/p&gt; &lt;p&gt;  Il applique la méthode cartésienne pour démontrer que la prétendue infériorité des femmes n'a pas de fondement naturel, mais résulte de préjugés culturels. Dans son ouvrage anonyme de 1673,  &lt;a href="https://www.les-philosophes.fr/feminisme/de-l-egalite-des-deux-sexes.html"  title="De l'égalité des deux sexes, de l'éducation des dames, de l'excellence des hommes par Les Philosophes.fr"&gt; "De l’égalité des deux sexes"&lt;/a&gt;, il critique les idées patriarcales qui justifient les discriminations contre les femmes et revendique leur droit à une véritable éducation et à l'accès aux mêmes carrières que les hommes, y compris les sciences. Il publie également "De l’éducation des dames pour la conduite des esprits dans les sciences et dans les mœurs" en 1674 et plus tard, ironiquement, "De l’excellence des hommes contre l’égalité des sexes"  en 1675 dans le but de ridiculiser les arguments sexistes de son époque. Sa thèse centrale est que l'esprit, la raison, n'a pas de sexe, et que les différences sociales tiennent à l'éducation et aux préjugés. Sa formule « l’esprit n’a point de sexe » résume cette position : la raison étant la même chez tous, rien ne justifie d’exclure les femmes des savoirs, des métiers ou des fonctions publiques. Il invite aussi à se méfier de ce que les hommes ont écrit sur les femmes, puisqu’ils y sont à la fois juges et parties ; Simone de Beauvoir placera cette idée en exergue du &lt;em&gt;Deuxième Sexe&lt;/em&gt;. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F43" s="47" t="inlineStr">
@@ -4513,7 +4511,7 @@
       </c>
       <c r="E58" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Reid"   title=" Wikipedia"&gt;Thomas REID&lt;/a&gt; était un philosophe écossais des Lumières écossaises, fondateur de l'école du sens commun. Contemporain et critique principal de David Hume, il enseigna à Aberdeen puis à Glasgow, où il succéda à Adam Smith. Il  défend le réalisme direct : nous percevons immédiatement les objets extérieurs eux-mêmes, sans passer par  &lt;a href="https://fr.wikisource.org/wiki/Grand_dictionnaire_universel_du_XIXe_si%C3%A8cle/Reid_(thomas)_(philosophe)"  title=" Reid philosophe par Wikisource"&gt; des "idées"  &lt;/a&gt; intermédiaires comme chez Locke ou Descartes. Le sens commun fournit des principes innés et indubitables (existence du monde, causalité, témoignage), que la philosophie doit respecter plutôt que miner. &lt;/p&gt; &lt;p&gt; Face au scepticisme humain, il argue que nier ces principes du sens commun mène à l'absurde : si nous doutons de tout, la philosophie devient inutilisable. Il réfute la "théorie des idées représentatives" qui, selon lui, engendre le doute hyperbolique. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Recherche sur l'entendement humain d'après les principes du sens commun (1764) : sa thèse majeure. - Principes de la philosophie morale : lie épistémologie et éthique pratique, inspirée du stoïcisme. &lt;/p&gt; &lt;p&gt; Comme Hutcheson, il valorise une  &lt;a href="https://www.youtube.com/watch?v=Nq9g-OYRLLQ"  title=" Reid’s commun sense design philosophy par Discovery Science"&gt; faculté innée &lt;/a&gt;  (sens moral chez l'un, sens commun chez l'autre), mais appliquée à la connaissance plutôt qu'à la morale pure. Tous deux s'opposent au scepticisme et à l'égoïsme hobbesien.https://encyclo-philo.fr/item/221 &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Reid"   title=" Wikipedia"&gt;Thomas REID&lt;/a&gt; était un philosophe écossais des Lumières écossaises, fondateur de l'école du sens commun. Contemporain et critique principal de David Hume, il enseigna à Aberdeen puis à Glasgow, où il succéda à Adam Smith. Il  défend le réalisme direct : nous percevons immédiatement les objets extérieurs eux-mêmes, sans passer par  &lt;a href="https://fr.wikisource.org/wiki/Grand_dictionnaire_universel_du_XIXe_si%C3%A8cle/Reid_(thomas)_(philosophe)"  title=" Reid philosophe par Wikisource"&gt; des "idées"  &lt;/a&gt; intermédiaires comme chez Locke ou Descartes. Le sens commun fournit des principes innés et indubitables (existence du monde, causalité, témoignage), que la philosophie doit respecter plutôt que miner. &lt;/p&gt; &lt;p&gt; Face au scepticisme humain, il argue que nier ces principes du sens commun mène à l'absurde : si nous doutons de tout, la philosophie devient inutilisable. Il réfute la "théorie des idées représentatives" qui, selon lui, engendre le doute hyperbolique. &lt;/p&gt; &lt;p&gt; Il expose sa pensée dans les &lt;em&gt;Recherches sur l'entendement humain d'après les principes du sens commun&lt;/em&gt; (1764), puis dans les &lt;em&gt;Essais sur les facultés intellectuelles&lt;/em&gt; (1785) et &lt;em&gt;sur les facultés actives&lt;/em&gt; de l'homme (1788), où il défend la liberté humaine contre le déterminisme. &lt;/p&gt; &lt;p&gt; Comme Hutcheson, il valorise une  &lt;a href="https://www.youtube.com/watch?v=Nq9g-OYRLLQ"  title=" Reid’s commun sense design philosophy par Discovery Science"&gt; faculté innée &lt;/a&gt;  (sens moral chez l'un, sens commun chez l'autre), mais appliquée à la connaissance plutôt qu'à la morale pure. Tous deux s'opposent au scepticisme et à l'égoïsme hobbesien. Sa philosophie du sens commun a dominé l’enseignement en Écosse et aux États-Unis, et en France, Royer-Collard et Victor Cousin s’en sont inspirés. Elle a été redécouverte au XXe siècle par G. E. Moore et par les épistémologues contemporains. &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -4792,7 +4790,7 @@
       </c>
       <c r="E62" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Gottlieb_Baumgarten"  title=" Wikipedia"&gt;Alexander Gottlieb BAUMGARTEN&lt;/a&gt;  était un philosophe allemand considéré comme le père de l'esthétique en tant que discipline philosophique autonome. Il  a étudié à Halle sous l'influence de Christian Wolff et de la tradition leibnizienne. Professeur à Halle puis à Francfort, il a développé une pensée rationaliste tout en valorisant la connaissance sensible.  &lt;/p&gt; &lt;p&gt; Dans son œuvre majeure Aesthetica (1750-1758), il introduit le terme &lt;a href="https://www.youtube.com/watch?v=izQeXqAcTVo"  title="Qu’est ce que l’esthétique aujourd’hui par Esthete Esthete"&gt;« esthétique » &lt;/a&gt; (du grec aisthēsis, sensation) pour désigner la « science de la connaissance sensible ». Contrairement à la logique qui traite de la connaissance rationnelle, l'esthétique étudie la perfection sensible, c'est-à-dire le beau perçu par les sens comme une forme complète de savoir. &lt;/p&gt; &lt;p&gt; Il  défend l'autonomie des « facultés inférieures » (sens, imagination, mémoire) face à la suprématie de la raison, voyant dans le beau une perfection analogue à la vérité (rationnelle) et au bien (moral). Son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1992_num_90_87_6745"  title="De Baumgarten à Kant par Persée"&gt;travail a influencé Kant &lt;/a&gt; et l'idéalisme allemand en légitimant l'étude philosophique de l'art et de l'expérience esthétique. Il insiste sur le rôle créatif de l'artiste, qui doit embellir la nature par l'ajout d'éléments sensibles. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Gottlieb_Baumgarten"  title=" Wikipedia"&gt;Alexander Gottlieb BAUMGARTEN&lt;/a&gt;  était un philosophe allemand considéré comme le père de l'esthétique en tant que discipline philosophique autonome. Il  a étudié à Halle sous l'influence de Christian Wolff et de la tradition leibnizienne. Professeur à Halle puis à Francfort, il a développé une pensée rationaliste tout en valorisant la connaissance sensible.  &lt;/p&gt; &lt;p&gt; Dans son œuvre majeure Aesthetica (1750-1758), il introduit le terme &lt;a href="https://www.youtube.com/watch?v=izQeXqAcTVo"  title="Qu’est ce que l’esthétique aujourd’hui par Esthete Esthete"&gt;« esthétique » &lt;/a&gt; (du grec aisthēsis, sensation) pour désigner la « science de la connaissance sensible ». Contrairement à la logique qui traite de la connaissance rationnelle, l'esthétique étudie la perfection sensible, c'est-à-dire le beau perçu par les sens comme une forme complète de savoir. &lt;/p&gt; &lt;p&gt; Il  défend l'autonomie des « facultés inférieures » (sens, imagination, mémoire) face à la suprématie de la raison, voyant dans le beau une perfection analogue à la vérité (rationnelle) et au bien (moral). Son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1992_num_90_87_6745"  title="De Baumgarten à Kant par Persée"&gt;travail a influencé Kant &lt;/a&gt; et l'idéalisme allemand en légitimant l'étude philosophique de l'art et de l'expérience esthétique. Né à Berlin en 1714, il emploie le mot pour la première fois dès 1735, dans sa thèse sur la poésie. Pour lui, la connaissance sensible est un « analogue de la raison » : elle saisit les choses de manière confuse mais riche, comme le fait le poète, là où la raison les saisit de manière claire mais abstraite. Sa &lt;em&gt;Métaphysique&lt;/em&gt; (1739), manuel de la philosophie de Wolff, a servi de support aux cours de Kant pendant plusieurs décennies. Il insiste sur le rôle créatif de l'artiste, qui doit embellir la nature par l'ajout d'éléments sensibles. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -5120,8 +5118,7 @@
       </c>
       <c r="E67" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Thiry_d%27Holbach"  title=" Wikipedia"&gt;Paul Thiry d'HOLBACH&lt;/a&gt;  était un philosophe allemand et devient encyclopédiste, traduit des œuvres scientifiques allemandes et anglaises pour l'Encyclopédie de Diderot. Hôte du célèbre "cénacle d'Holbach", salon fréquenté par Diderot, Rousseau, Helvétius et Adam Smith, il anime un foyer intellectuel anticlérical jusqu'à sa mort en 1789. &lt;/p&gt; &lt;p&gt; Il défend un matérialisme radical: l'univers se compose uniquement de matière et de mouvement, régi par des  &lt;a href="https://www.youtube.com/watch?v=x99DRdMAd08"  title="Essai sur l'art de ramper à l'usage des courtisans - D'Holbach" par Vox Plebeia"&gt;lois causales &lt;/a&gt; nécessaires, excluant Dieu ou toute intervention surnaturelle. Athée virulent, il combat les religions comme sources d'erreur, de peur et de superstition dans des pamphlets pseudonymes comme &lt;a href="https://www.youtube.com/watch?v=8Uohr5Y9xx0" title="Religions Are ROTTING ILLUSIONS | Baron d’Holbach par Unfiltered Philosophy"&gt;"Le Christianisme dévoilé" &lt;/a&gt; paru en 1761 ou "Le Système de la nature" (1770), bible de l'athéisme. &lt;/p&gt; &lt;p&gt; Sa morale est utilitariste et eudémoniste: la vertu réside dans l'utilité pour le bonheur individuel et collectif, fondée sur la raison et l'éducation, sans recours à la religion. Fataliste et déterministe, il prône la liberté sociale, l'égalité et une politique naturelle anti-despotique, influençant la Révolution française par sa critique des privilèges et du fanatisme. &lt;/p&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Thiry_d%27Holbach"  title=" Wikipedia"&gt;Paul Thiry d’HOLBACH&lt;/a&gt; (1723-1789) est un philosophe des Lumières, d’origine allemande et naturalisé français, l’un des penseurs les plus radicaux de son siècle. Né dans le Palatinat, élevé à Paris par un oncle dont il hérite la fortune et le titre de baron, il étudie à Leyde, puis s’installe à Paris. Il écrit pour l’&lt;em&gt;Encyclopédie&lt;/em&gt; de Diderot plusieurs centaines d’articles, surtout de chimie et de minéralogie.&lt;/p&gt; &lt;p&gt;Son salon de la rue Royale, que l’abbé Galiani appelait « le maître d’hôtel de la philosophie », réunit deux fois par semaine Diderot, Grimm, Helvétius, Raynal et les étrangers de passage, comme Hume, Adam Smith ou Beccaria. D’Holbach publie sous de faux noms une série d’ouvrages contre la religion, dont &lt;a href="https://www.youtube.com/watch?v=8Uohr5Y9xx0" title="Religions Are ROTTING ILLUSIONS | Baron d’Holbach par Unfiltered Philosophy"&gt;&lt;em&gt;Le Christianisme dévoilé&lt;/em&gt;&lt;/a&gt; (1766), et surtout le &lt;em&gt;Système de la nature&lt;/em&gt; (1770), attribué à un auteur mort, qui fait scandale et est condamné au feu. Il y défend un matérialisme intégral : l’univers n’est que matière en mouvement, régie par des lois nécessaires ; il n’y a ni Dieu, ni âme immortelle, ni liberté au sens d’un libre arbitre. La religion naît de l’ignorance et de la peur, et les prêtres et les rois s’appuient l’un sur l’autre pour asservir les peuples. La morale doit donc être fondée sur la nature humaine, qui recherche le bonheur, et sur l’utilité sociale : l’homme vertueux est celui qui contribue au bonheur des autres. Dans son pamphlet &lt;a href="https://www.youtube.com/watch?v=x99DRdMAd08"  title="Essai sur l'art de ramper à l'usage des courtisans - D'Holbach par Vox Plebeia"&gt;&lt;em&gt;Essai sur l’art de ramper, à l’usage des courtisans&lt;/em&gt;&lt;/a&gt;, il raille la servilité des grands.&lt;/p&gt; &lt;p&gt;Mort en 1789, quelques mois avant la Révolution, il a inspiré les matérialistes du XIXe siècle et la critique moderne de la religion.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F67" s="47" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -856,10 +856,10 @@
       </c>
       <c r="E4" s="49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Pic_de_la_Mirandole"   title=" Wikipedia"&gt;Jean PIC de la Mirandole&lt;/a&gt; était un penseur humaniste italien célèbre pour son érudition exceptionnelle, son projet ambitieux d’unifier toutes les formes de pensée philosophique et religieuse et sa défense de la dignité humaine avec son célèbre  &lt;a href="https://www.youtube.com/watch?v=1YJMpWsx9UI" style="color:#88A1E9" title="Discours sur la dignité de l'homme par Adrien Bouhours "&gt;"Discours sur la dignité de l'homme"&lt;/a&gt;, où il défend l'idée que l'homme est libre de se façonner lui-même et de s'élever vers Dieu. &lt;/p&gt;   &lt;p&gt;Il s’intéresse autant à la pensée classique qu’à la théologie chrétienne, à la kabbale juive et aux mysticismes orientaux.  En 1486, il entreprend un projet d’une ampleur inédite : il rédige 900 thèses, qu’il propose de défendre publiquement à Rome. Ces thèses abordent des sujets variés : philosophie, théologie, mysticisme, magie, kabbale, alchimie… Son but est de démontrer que toutes les traditions philosophiques et religieuses partagent une vérité commune. &lt;/p&gt;
-&lt;p&gt;-  "L'Oratio de hominis dignitate" : Il préface ces thèses avec un texte célèbre, l’Oratio de hominis dignitate, souvent considéré comme un manifeste de l’humanisme. Il y défend l’idée que l’homme est un être libre, doté d’un potentiel infini, capable de s’élever par le savoir et la contemplation. &lt;/p&gt;
-&lt;p&gt;-  L’échec du débat Le pape Innocent VIII voit ces thèses d’un mauvais œil, suspectant certaines d’entre elles d’hérésie. L’Église condamne 13 de ses propositions et interdit la tenue du débat. Accusé d’hérésie, Pic doit s’enfuir et est brièvement emprisonné en France avant d’être libéré grâce à l’intervention de Laurent de Médicis. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Décédé à 31 ans, probablement empoisonné, peut-être sur ordre de Pierre de Médicis, son œuvre a eu une influence durable, notamment dans la pensée humaniste et ésotérique. Son idéal d’une synthèse universelle des savoirs reste un modèle pour la philosophie moderne. &lt;/p&gt;
-&lt;p&gt; &lt;/p&gt;&lt;audio controls title="Pic de la Marandole par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10344-19.02.2023-ITEMA_23292733-2023C5010E0006-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Pic_de_la_Mirandole"   title=" Wikipedia"&gt;Jean PIC de la Mirandole&lt;/a&gt; était un penseur humaniste italien célèbre pour son érudition exceptionnelle, son projet ambitieux d’unifier toutes les formes de pensée philosophique et religieuse et sa défense de la dignité humaine avec son célèbre  &lt;a href="https://www.youtube.com/watch?v=1YJMpWsx9UI" style="color:#88A1E9" title="Discours sur la dignité de l'homme par Adrien Bouhours "&gt;"Discours sur la dignité de l'homme"&lt;/a&gt;, où il défend l'idée que l'homme est libre de se façonner lui-même et de s'élever vers Dieu. &lt;/p&gt; &lt;p&gt;Il s’intéresse autant à la pensée classique qu’à la théologie chrétienne, à la kabbale juive et aux mysticismes orientaux.  En 1486, il entreprend un projet d’une ampleur inédite : il rédige 900 thèses, qu’il propose de défendre publiquement à Rome. Ces thèses abordent des sujets variés : philosophie, théologie, mysticisme, magie, kabbale, alchimie… Son but est de démontrer que toutes les traditions philosophiques et religieuses partagent une vérité commune. &lt;/p&gt;
+&lt;p&gt;"L'Oratio de hominis dignitate" : Il préface ces thèses avec un texte célèbre, l’Oratio de hominis dignitate, souvent considéré comme un manifeste de l’humanisme. Il y défend l’idée que l’homme est un être libre, doté d’un potentiel infini, capable de s’élever par le savoir et la contemplation. &lt;/p&gt;
+&lt;p&gt;L’échec du débat Le pape Innocent VIII voit ces thèses d’un mauvais œil, suspectant certaines d’entre elles d’hérésie. L’Église condamne 13 de ses propositions et interdit la tenue du débat. Accusé d’hérésie, Pic doit s’enfuir et est brièvement emprisonné en France avant d’être libéré grâce à l’intervention de Laurent de Médicis. &lt;/p&gt; &lt;p&gt; Décédé à 31 ans, probablement empoisonné, peut-être sur ordre de Pierre de Médicis, son œuvre a eu une influence durable, notamment dans la pensée humaniste et ésotérique. Son idéal d’une synthèse universelle des savoirs reste un modèle pour la philosophie moderne. &lt;/p&gt;
+&lt;audio controls title="Pic de la Marandole par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10344-19.02.2023-ITEMA_23292733-2023C5010E0006-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F4" s="47" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E6" s="50" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Machiavel" title=" Wikipedia"&gt;Nicolas MACHIAVEL&lt;/a&gt; était un philosophe italien connu pour son livre &lt;a href="https://www.youtube.com/watch?v=x4z-TLoOQ5Q&amp;ab_channel=AlainBajom%C3%A9ef"    title="Le Prince par Alain Bajomée"&gt; "Le Prince"&lt;/a&gt;, publié en 1532, qui aborde les thèmes de la politique et de la tactique politique ou &lt;a href="https://www.youtube.com/watch?v=9tt12zMrx3M&amp;ab_channel=LePr%C3%A9cepteur"  title="L'art de gouverner par le Précepteur"&gt; "l'Art de Gouverner" &lt;/a&gt; et où il  plaide en faveur de la raison d'État, une approche selon laquelle les dirigeants doivent faire des choix politiques en fonction des intérêts de l'État, même si cela signifie enfreindre les normes éthiques ou morales.&lt;/p&gt;  &lt;p&gt; Cet ouvrage  est un traité pragmatique sur l'art de gouverner, prônant l'usage de la ruse, de la force et de la virtù (énergie audacieuse) pour maintenir le pouvoir, où la fin justifie les moyens. Il écrit aussi les Discours sur la première décade de Tite-Live (favorisant les républiques), L'Art de la guerre et la comédie &lt;a href="https://www.youtube.com/watch?v=mN425No69K4"  title="La philosophie de Machiavel par Parole de philosophes"&gt; La Mandragore&lt;/a&gt;. Ces textes analysent l'histoire romaine pour en tirer des leçons politiques concrètes.   &lt;p&gt;  Il sépare la politique de la morale et de la religion, la fondant sur l'expérience historique et le réalisme : le dirigeant doit inspirer la crainte plus que l'amour si nécessaire, et s'adapter aux circonstances (fortuna) par la virtù. Pour lui, la politique repose sur le mouvement, le conflit et la rhétorique persuasive, préfigurant une science laïque &lt;a href="https://www.youtube.com/watch?v=QP_o9y1B1nw"  title="Machiavel c’est quoi le pouvoir par Kosmos"&gt; du pouvoir&lt;/a&gt;. Son nom a donné l'adjectif "machiavélique", connotant ruse et cynisme, bien qu'il visait surtout l'unité italienne face aux divisions de l'époque.https://www.youtube.com/watch?v=YoYshBzpaqY   Il soutient également que les dirigeants doivent être prêts à utiliser la force pour maintenir le pouvoir et la stabilité de l'État. Il inspirera tous les grands hommes d'Etat, de Mitterrand à De Gaulle en passant par Churchill et Napoléon. &lt;/p&gt; &lt;p&gt;  En raison de ses idées controversées, il a souvent été considéré comme un théoricien de la tyrannie et de la manipulation politique.&lt;/p&gt; &lt;p&gt;  Malgré les accusations de cruauté et de déshumanisation, ses pensées continuent d'être étudiées et on utilise le terme de 'machiavélique' aujourd'hui dans la langue Française. &lt;/&gt;  &lt;audio controls title="Machiavel, le précurseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21877-15.03.2022-ITEMA_22963725-2022C42575E0002-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Machiavel" title=" Wikipedia"&gt;Nicolas MACHIAVEL&lt;/a&gt; était un philosophe italien connu pour son livre &lt;a href="https://www.youtube.com/watch?v=x4z-TLoOQ5Q&amp;ab_channel=AlainBajom%C3%A9ef"    title="Le Prince par Alain Bajomée"&gt; "Le Prince"&lt;/a&gt;, publié en 1532, qui aborde les thèmes de la politique et de la tactique politique ou &lt;a href="https://www.youtube.com/watch?v=9tt12zMrx3M&amp;ab_channel=LePr%C3%A9cepteur"  title="L'art de gouverner par le Précepteur"&gt; "l'Art de Gouverner" &lt;/a&gt; et où il  plaide en faveur de la raison d'État, une approche selon laquelle les dirigeants doivent faire des choix politiques en fonction des intérêts de l'État, même si cela signifie enfreindre les normes éthiques ou morales.&lt;/p&gt; &lt;p&gt; Cet ouvrage  est un traité pragmatique sur l'art de gouverner, prônant l'usage de la ruse, de la force et de la virtù (énergie audacieuse) pour maintenir le pouvoir, où la fin justifie les moyens. Il écrit aussi les Discours sur la première décade de Tite-Live (favorisant les républiques), L'Art de la guerre et la comédie &lt;a href="https://www.youtube.com/watch?v=mN425No69K4"  title="La philosophie de Machiavel par Parole de philosophes"&gt; La Mandragore&lt;/a&gt;. Ces textes analysent l'histoire romaine pour en tirer des leçons politiques concrètes.   &lt;p&gt;  Il sépare la politique de la morale et de la religion, la fondant sur l'expérience historique et le réalisme : le dirigeant doit inspirer la crainte plus que l'amour si nécessaire, et s'adapter aux circonstances (fortuna) par la virtù. Pour lui, la politique repose sur le mouvement, le conflit et la rhétorique persuasive, préfigurant une science laïque &lt;a href="https://www.youtube.com/watch?v=QP_o9y1B1nw"  title="Machiavel c’est quoi le pouvoir par Kosmos"&gt; du pouvoir&lt;/a&gt;. Son nom a donné l'adjectif "machiavélique", connotant ruse et cynisme, bien qu'il visait surtout l'unité italienne face aux divisions de l'époque.   Il soutient également que les dirigeants doivent être prêts à utiliser la force pour maintenir le pouvoir et la stabilité de l'État. Il inspirera tous les grands hommes d'Etat, de Mitterrand à De Gaulle en passant par Churchill et Napoléon. &lt;/p&gt; &lt;p&gt;  En raison de ses idées controversées, il a souvent été considéré comme un théoricien de la tyrannie et de la manipulation politique.&lt;/p&gt; &lt;p&gt;  Malgré les accusations de cruauté et de déshumanisation, ses pensées continuent d'être étudiées et on utilise le terme de 'machiavélique' aujourd'hui dans la langue Française. &lt;/&gt;  &lt;audio controls title="Machiavel, le précurseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21877-15.03.2022-ITEMA_22963725-2022C42575E0002-25.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F6" s="47" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_More"  title=" Wikipedia"&gt;Thomas MORE&lt;/a&gt;  est une figure majeure de la Renaissance anglaise, connue pour son érudition, ses écrits et son engagement politique. Il est surtout célèbre pour son ouvrage  &lt;a href="https://fr.wikipedia.org/wiki/L%27Utopie" style="color:#88A1E9" title="Utopia par Wikipedia "&gt;Utopia&lt;/a&gt;, mais son refus de reconnaître Henri VIII comme chef suprême de l'Église d'Angleterre lui valut d'être persécuté et exécuté. &lt;/p&gt;  &lt;p&gt; Il  est nommé Lord Chancelier d'Angleterre, devenant ainsi l'un des hommes les plus puissants du royaume. Cependant, sa carrière politique est marquée par des tensions croissantes avec Henri VIII, notamment sur la question du divorce du roi avec Catherine d'Aragon et de la rupture avec l'Église catholique. &lt;/p&gt; &lt;p&gt; Son œuvre la plus célèbre est Utopia (titre complet : De optimo rei publicae statu deque nova insula Utopia). Publiée en latin en 1516, elle décrit une société imaginaire située sur une île appelée Utopia, où règnent l'égalité, la justice et la prospérité. Les habitants vivent dans un système communautaire, sans propriété privée, et travaillent pour le bien commun. &lt;a href="https://www.youtube.com/watch?v=fvA0IBRWCso"  title="Utopie par Alain Bajomé "&gt;Utopia&lt;/a&gt; est à la fois une critique des maux de la société européenne de l'époque (pauvreté, corruption, inégalités) et une réflexion sur les possibilités d'une organisation sociale plus juste. Le terme "utopie" est entré dans le langage courant pour désigner un idéal inaccessible ou une société parfaite. &lt;/p&gt; &lt;p&gt; Il  est décapité le 6 juillet 1535 puis canonisé par l'Église catholique en 1935. Il reste une figure complexe et fascinante, à la fois homme d'État, écrivain visionnaire et martyr de la foi. Son héritage continue d'inspirer des débats sur la justice, la liberté de conscience et la quête d'une société meilleure. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;   &lt;audio controls title="Thomas MORE, l'utopie et nous par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11739-18.10.2016-ITEMA_21107818-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_More"  title=" Wikipedia"&gt;Thomas MORE&lt;/a&gt;  est une figure majeure de la Renaissance anglaise, connue pour son érudition, ses écrits et son engagement politique. Il est surtout célèbre pour son ouvrage  &lt;a href="https://fr.wikipedia.org/wiki/L%27Utopie" style="color:#88A1E9" title="Utopia par Wikipedia "&gt;Utopia&lt;/a&gt;, mais son refus de reconnaître Henri VIII comme chef suprême de l'Église d'Angleterre lui valut d'être persécuté et exécuté. &lt;/p&gt; &lt;p&gt; Il  est nommé Lord Chancelier d'Angleterre, devenant ainsi l'un des hommes les plus puissants du royaume. Cependant, sa carrière politique est marquée par des tensions croissantes avec Henri VIII, notamment sur la question du divorce du roi avec Catherine d'Aragon et de la rupture avec l'Église catholique. &lt;/p&gt; &lt;p&gt; Son œuvre la plus célèbre est Utopia (titre complet : De optimo rei publicae statu deque nova insula Utopia). Publiée en latin en 1516, elle décrit une société imaginaire située sur une île appelée Utopia, où règnent l'égalité, la justice et la prospérité. Les habitants vivent dans un système communautaire, sans propriété privée, et travaillent pour le bien commun. &lt;a href="https://www.youtube.com/watch?v=fvA0IBRWCso"  title="Utopie par Alain Bajomé "&gt;Utopia&lt;/a&gt; est à la fois une critique des maux de la société européenne de l'époque (pauvreté, corruption, inégalités) et une réflexion sur les possibilités d'une organisation sociale plus juste. Le terme "utopie" est entré dans le langage courant pour désigner un idéal inaccessible ou une société parfaite. &lt;/p&gt; &lt;p&gt; Il  est décapité le 6 juillet 1535 puis canonisé par l'Église catholique en 1935. Il reste une figure complexe et fascinante, à la fois homme d'État, écrivain visionnaire et martyr de la foi. Son héritage continue d'inspirer des débats sur la justice, la liberté de conscience et la quête d'une société meilleure. &lt;/p&gt;    &lt;audio controls title="Thomas MORE, l'utopie et nous par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11739-18.10.2016-ITEMA_21107818-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F8" s="51" t="inlineStr">
@@ -1381,12 +1381,9 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martin_Luther"  title=" Wikipedia"&gt;Matin LUTHER&lt;/a&gt; est connu pour avoir initié la Réforme protestante au XVIe siècle, un mouvement religieux qui a profondément transformé le christianisme et l'Europe. &lt;/p&gt; &lt;p&gt; Le déclencheur de la Réforme est la publication par Luther de ses &lt;a href="https://www.persee.fr/doc/ether_0014-2239_1968_num_43_1_1846" style="color:#88A1E9" title="95 thèses du 31 octobre 1517 par Persée"&gt;95 thèses&lt;/a&gt; en 1517. Ces thèses critiquent ouvertement les pratiques de l'Église catholique, en particulier la vente des indulgences (des pardons monnayés pour réduire le temps passé au purgatoire). &lt;/p&gt; 
-&lt;dd&gt; - Sola Scriptura : La Bible est la seule autorité en matière de foi, rejetant la tradition et l'autorité du pape. &lt;/dd&gt; 
-&lt;dd&gt; - Sola Fide : Le salut s'obtient par la foi en Jésus-Christ, et non par les œuvres ou les indulgences. &lt;/dd&gt;
-&lt;dd&gt; - Sola Gratia : Le salut est un don gratuit de Dieu, et non le résultat des efforts humains. &lt;/dd&gt;
-&lt;dd&gt; - Sacerdoce universel : Les croyants sont égaux devant Dieu, et il n'y a pas besoin d'un clergé intermédiaire. &lt;/dd&gt; 
-&lt;dd&gt; - Nombre de sacrements de sept à deux (le baptême et la Cène), rejetant ceux qu'il considère comme des ajouts humains. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=IcM8dGc1kXM" title="La réforme Martin Luther par Yannick Rub"&gt;La Réforme&lt;/a&gt;  a conduit à la création du protestantisme, qui se divise en plusieurs branches (luthéranisme, calvinisme, anglicanisme, etc.).  Les tensions entre catholiques et protestants ont déclenché des conflits, comme la guerre de Trente Ans (1618–1648). Il a encouragé l'éducation pour tous, y compris les femmes, et a influencé la culture européenne, notamment la musique. &lt;/p&gt; &lt;p&gt; En 1525, il épouse Katharina von Bora, une ancienne nonne. Leur mariage symbolise la rupture avec le célibat des prêtres catholiques. Ils ont six enfants et leur foyer devient un modèle pour la famille protestante. Il a profondément marqué l'histoire religieuse, culturelle et politique de l'Europe. Ses idées ont influencé non seulement la théologie, mais aussi des concepts modernes comme la liberté de conscience et la séparation de l'Église et de l'État. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martin_Luther"  title=" Wikipedia"&gt;Matin LUTHER&lt;/a&gt; est connu pour avoir initié la Réforme protestante au XVIe siècle, un mouvement religieux qui a profondément transformé le christianisme et l'Europe. &lt;/p&gt; &lt;p&gt; Le déclencheur de la Réforme est la publication par Luther de ses &lt;a href="https://www.persee.fr/doc/ether_0014-2239_1968_num_43_1_1846" style="color:#88A1E9" title="95 thèses du 31 octobre 1517 par Persée"&gt;95 thèses&lt;/a&gt; en 1517. Ces thèses critiquent ouvertement les pratiques de l'Église catholique, en particulier la vente des indulgences (des pardons monnayés pour réduire le temps passé au purgatoire). &lt;/p&gt; &lt;p&gt;Sola Scriptura : La Bible est la seule autorité en matière de foi, rejetant la tradition et l'autorité du pape. &lt;/p&gt; &lt;p&gt;Sola Fide : Le salut s'obtient par la foi en Jésus-Christ, et non par les œuvres ou les indulgences. &lt;/p&gt;
+&lt;p&gt;Sola Gratia : Le salut est un don gratuit de Dieu, et non le résultat des efforts humains. &lt;/p&gt;
+&lt;p&gt;Sacerdoce universel : Les croyants sont égaux devant Dieu, et il n'y a pas besoin d'un clergé intermédiaire. &lt;/p&gt; &lt;p&gt;Nombre de sacrements de sept à deux (le baptême et la Cène), rejetant ceux qu'il considère comme des ajouts humains. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=IcM8dGc1kXM" title="La réforme Martin Luther par Yannick Rub"&gt;La Réforme&lt;/a&gt;  a conduit à la création du protestantisme, qui se divise en plusieurs branches (luthéranisme, calvinisme, anglicanisme, etc.).  Les tensions entre catholiques et protestants ont déclenché des conflits, comme la guerre de Trente Ans (1618–1648). Il a encouragé l'éducation pour tous, y compris les femmes, et a influencé la culture européenne, notamment la musique. &lt;/p&gt; &lt;p&gt; En 1525, il épouse Katharina von Bora, une ancienne nonne. Leur mariage symbolise la rupture avec le célibat des prêtres catholiques. Ils ont six enfants et leur foyer devient un modèle pour la famille protestante. Il a profondément marqué l'histoire religieuse, culturelle et politique de l'Europe. Ses idées ont influencé non seulement la théologie, mais aussi des concepts modernes comme la liberté de conscience et la séparation de l'Église et de l'État. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -1519,11 +1516,11 @@
       </c>
       <c r="E14" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Calvin"   title=" Wikipedia"&gt;Jean CALVIN&lt;/a&gt; était un théologien, pasteur et réformateur français qui a joué un rôle central dans le développement du protestantisme, en particulier de la branche réformée, mouvement de contestation de l'autorité de l'Église catholique romaine et de retour aux sources bibliques. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus importante est  &lt;a href="https://www.youtube.com/watch?v=O1w5GbNMX0Y"  title="L'institution de la religion par Musée protestant "&gt;"L'Institution de la religion chrétienne"&lt;/a&gt; (1536). Elle expose de manière systématique les principes de la foi réformée. Voici les idées clés de cette œuvre : &lt;/p&gt;
-&lt;dd&gt; - La souveraineté de Dieu : Il insiste sur la toute-puissance et la souveraineté absolue de Dieu. Tout ce qui arrive est selon la volonté divine. &lt;/dd&gt;
-&lt;dd&gt; -  La prédestination : Il développe la doctrine de la prédestination, selon laquelle Dieu a choisi de toute éternité ceux qui seront sauvés (les élus) et ceux qui seront damnés (les réprouvés). &lt;/dd&gt;
-&lt;dd&gt; -  L'autorité des Écritures : Pour lui, la Bible est la seule autorité en matière de foi et de pratique religieuse. Il rejette les traditions et les dogmes de l'Église qui ne sont pas explicitement fondés sur les Écritures. &lt;/dd&gt;
-&lt;dd&gt; -  La justification par la foi : Comme Luther, il enseigne que le salut est un don gratuit de Dieu, reçu par la foi seule, et non par les œuvres. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il met en place un système de discipline rigoureuse à Genève, visant à maintenir la pureté morale et doctrinale de la communauté. &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_2013_num_93_4_1801_t8_0586_0000_2"  title="Le Consistoire au temps de Calvin par Persée "&gt;Le Consistoire&lt;/a&gt;, un tribunal ecclésiastique, surveille les comportements et punit les infractions. Il attache une grande importance à l'éducation. &lt;/p&gt; &lt;p&gt;Il  distingue clairement les rôles de l'Église et de l'État, bien qu'il considère que les deux doivent collaborer pour maintenir l'ordre et la piété. &lt;/p&gt; &lt;p&gt; Sa pensée   a influencé le développement de la démocratie républicaine, en particulier l'idée que les gouvernants doivent être soumis à la loi et responsables devant Dieu et le peuple.  &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Calvin"   title=" Wikipedia"&gt;Jean CALVIN&lt;/a&gt; était un théologien, pasteur et réformateur français qui a joué un rôle central dans le développement du protestantisme, en particulier de la branche réformée, mouvement de contestation de l'autorité de l'Église catholique romaine et de retour aux sources bibliques. &lt;/p&gt; &lt;p&gt;  Son œuvre la plus importante est  &lt;a href="https://www.youtube.com/watch?v=O1w5GbNMX0Y"  title="L'institution de la religion par Musée protestant "&gt;"L'Institution de la religion chrétienne"&lt;/a&gt; (1536). Elle expose de manière systématique les principes de la foi réformée. &lt;/p&gt;
+&lt;p&gt;La souveraineté de Dieu : Il insiste sur la toute-puissance et la souveraineté absolue de Dieu. Tout ce qui arrive est selon la volonté divine. &lt;/p&gt;
+&lt;p&gt;La prédestination : Il développe la doctrine de la prédestination, selon laquelle Dieu a choisi de toute éternité ceux qui seront sauvés (les élus) et ceux qui seront damnés (les réprouvés). &lt;/p&gt;
+&lt;p&gt;L'autorité des Écritures : Pour lui, la Bible est la seule autorité en matière de foi et de pratique religieuse. Il rejette les traditions et les dogmes de l'Église qui ne sont pas explicitement fondés sur les Écritures. &lt;/p&gt;
+&lt;p&gt;La justification par la foi : Comme Luther, il enseigne que le salut est un don gratuit de Dieu, reçu par la foi seule, et non par les œuvres. &lt;/p&gt; &lt;p&gt; Il met en place un système de discipline rigoureuse à Genève, visant à maintenir la pureté morale et doctrinale de la communauté. &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_2013_num_93_4_1801_t8_0586_0000_2"  title="Le Consistoire au temps de Calvin par Persée "&gt;Le Consistoire&lt;/a&gt;, un tribunal ecclésiastique, surveille les comportements et punit les infractions. Il attache une grande importance à l'éducation. &lt;/p&gt; &lt;p&gt;Il  distingue clairement les rôles de l'Église et de l'État, bien qu'il considère que les deux doivent collaborer pour maintenir l'ordre et la piété. &lt;/p&gt; &lt;p&gt; Sa pensée   a influencé le développement de la démocratie républicaine, en particulier l'idée que les gouvernants doivent être soumis à la loi et responsables devant Dieu et le peuple.  &lt;/p&gt;   </t>
         </is>
       </c>
       <c r="F14" s="47" t="inlineStr">
@@ -1589,7 +1586,7 @@
       </c>
       <c r="E15" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.universalis.fr/encyclopedie/bernardino-telesio/"   title=" Wikipedia"&gt;Bernardino TELESIO&lt;/a&gt; était  un philosophe italien de la Renaissance, considéré comme l’un des principaux critiques de l’aristotélisme médiéval et un pionnier de la pensée empirique et naturaliste. Son approche révolutionnaire de la philosophie naturelle a influencé des penseurs comme Francis Bacon, Campanella et Bruno, ouvrant la voie à la méthode scientifique moderne.  Il  s’oppose à la physique d’Aristote et à la scolastique médiévale, proposant une philosophie basée sur : &lt;/p&gt; &lt;p&gt; - L’observation directe de la nature (empirisme naissant).  -  Une explication mécaniste et matérialiste des phénomènes naturels.  -  Le rejet des formes substantielles et des causes finales aristotéliciennes.&lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans le naturalisme renaissant, préfigurant le mécanisme de Galilée et Descartes. Ses oeuvres principales : &lt;/p&gt; &lt;p&gt; -   &lt;a href="https://archive.org/details/dererumnaturaiux00tele/mode/2up"  title=" De rerum natura iuxta propria principia par Internet Archive "&gt;"De rerum natura iuxta propria principia"&lt;/a&gt; : Critique d’Aristote et rejet des quatre éléments (terre, eau, air, feu) et des qualités occultes. Refus de la physique qualitative d’Aristote au profit d’une approche quantitative.  Il voyait la Chaleur (calor) et le froid (frigus) comme forces fondamentales expliquant tous les phénomènes naturels. &lt;/p&gt; &lt;p&gt;  - "De his quae in aere fiunt"  : Sur les phénomènes météorologiques. &lt;/p&gt; &lt;p&gt; - "De mari" : Étude sur la mer et les marées. &lt;/p&gt; &lt;p&gt; -  "De cometis et lacteo circulo" : Sur les comètes et la Voie lactée. &lt;/p&gt; &lt;p&gt; - "Varii de &lt;a href="https://www.youtube.com/watch?v=z736KDAH_s0" title=" Bernardino Telesio - La natura secondo i propri principi par Scorribande Filosofiche "&gt;naturalibus &lt;/a&gt; rebus libelli" : Recueil de petits traités sur des sujets naturels. &lt;/p&gt; &lt;p&gt; Il  rompt avec la tradition scolastique en proposant une philosophie naturelle basée sur l’observation, annonçant la révolution scientifique du XVIIe siècle.  Son influence sur l’empirisme et le mécanisme est majeure. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://www.universalis.fr/encyclopedie/bernardino-telesio/"   title=" Wikipedia"&gt;Bernardino TELESIO&lt;/a&gt; était  un philosophe italien de la Renaissance, considéré comme l’un des principaux critiques de l’aristotélisme médiéval et un pionnier de la pensée empirique et naturaliste. Son approche révolutionnaire de la philosophie naturelle a influencé des penseurs comme Francis Bacon, Campanella et Bruno, ouvrant la voie à la méthode scientifique moderne.  Il  s’oppose à la physique d’Aristote et à la scolastique médiévale, proposant une philosophie basée sur : &lt;/p&gt; &lt;p&gt;L’observation directe de la nature (empirisme naissant). Une explication mécaniste et matérialiste des phénomènes naturels. Le rejet des formes substantielles et des causes finales aristotéliciennes.&lt;/p&gt; &lt;p&gt; Sa pensée s’inscrit dans le naturalisme renaissant, préfigurant le mécanisme de Galilée et Descartes. Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;&lt;a href="https://archive.org/details/dererumnaturaiux00tele/mode/2up"  title=" De rerum natura iuxta propria principia par Internet Archive "&gt;"De rerum natura iuxta propria principia"&lt;/a&gt; : Critique d’Aristote et rejet des quatre éléments (terre, eau, air, feu) et des qualités occultes. Refus de la physique qualitative d’Aristote au profit d’une approche quantitative.  Il voyait la Chaleur (calor) et le froid (frigus) comme forces fondamentales expliquant tous les phénomènes naturels. &lt;/p&gt; &lt;p&gt;"De his quae in aere fiunt"  : Sur les phénomènes météorologiques. &lt;/p&gt; &lt;p&gt;"De mari" : Étude sur la mer et les marées. &lt;/p&gt; &lt;p&gt;"De cometis et lacteo circulo" : Sur les comètes et la Voie lactée. &lt;/p&gt; &lt;p&gt;"Varii de &lt;a href="https://www.youtube.com/watch?v=z736KDAH_s0" title=" Bernardino Telesio - La natura secondo i propri principi par Scorribande Filosofiche "&gt;naturalibus &lt;/a&gt; rebus libelli" : Recueil de petits traités sur des sujets naturels. &lt;/p&gt; &lt;p&gt; Il  rompt avec la tradition scolastique en proposant une philosophie naturelle basée sur l’observation, annonçant la révolution scientifique du XVIIe siècle.  Son influence sur l’empirisme et le mécanisme est majeure. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -1721,9 +1718,8 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francesco_Patrizi" title=" Wikipedia"&gt;Francesco PATRIZI&lt;/a&gt; était un philosophe et humaniste italien connu pour son rejet de l'aristotélisme et sa promotion d'une philosophie inspirée par Platon et les néoplatoniciens comme Plotin et Proclus. Il a cherché à revitaliser la philosophie naturelle en intégrant des éléments mystiques et hermétiques, ce qui l'a conduit à développer une vision du monde panthéiste et dynamique. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt; - "Nova de universis philosophia" : C'est son œuvre majeure où il expose sa vision d'une nouvelle philosophie universelle. Il y critique sévèrement Aristote et propose une métaphysique fondée sur la lumière comme principe premier de l'univers. &lt;/p&gt; 
-&lt;p&gt; - "Discussiones peripateticae" : Il attaque la philosophie aristotélicienne, qu'il juge dépassée et incompatible avec les découvertes scientifiques de son époque. Il plaide pour un retour à Platon et aux traditions pré-aristotéliciennes. &lt;p&gt; 
-&lt;p&gt; - "Della poetica" : Il s'intéresse également à l'esthétique et à la littérature. Il explore la nature de la poésie et son rôle dans la connaissance et l'expression de la vérité. &lt;/p&gt; &lt;p&gt; Considéré comme un précurseur de certaines idées modernes, notamment en ce qui concerne la nature de la lumière et son rôle dans l'univers, sa tentative de dépasser l'aristotélisme et de proposer une nouvelle philosophie universelle fondée sur la lumière et l'harmonie cosmique en fait une figure importante dans l'histoire de la pensée occidentale. Bien que ses idées aient été parfois marginalisées, elles témoignent de la richesse et de la diversité de la philosophie de la Renaissance. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francesco_Patrizi" title=" Wikipedia"&gt;Francesco PATRIZI&lt;/a&gt; était un philosophe et humaniste italien connu pour son rejet de l'aristotélisme et sa promotion d'une philosophie inspirée par Platon et les néoplatoniciens comme Plotin et Proclus. Il a cherché à revitaliser la philosophie naturelle en intégrant des éléments mystiques et hermétiques, ce qui l'a conduit à développer une vision du monde panthéiste et dynamique. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt;"Nova de universis philosophia" : C'est son œuvre majeure où il expose sa vision d'une nouvelle philosophie universelle. Il y critique sévèrement Aristote et propose une métaphysique fondée sur la lumière comme principe premier de l'univers. &lt;/p&gt; &lt;p&gt;"Discussiones peripateticae" : Il attaque la philosophie aristotélicienne, qu'il juge dépassée et incompatible avec les découvertes scientifiques de son époque. Il plaide pour un retour à Platon et aux traditions pré-aristotéliciennes. &lt;p&gt; 
+&lt;p&gt;"Della poetica" : Il s'intéresse également à l'esthétique et à la littérature. Il explore la nature de la poésie et son rôle dans la connaissance et l'expression de la vérité. &lt;/p&gt; &lt;p&gt; Considéré comme un précurseur de certaines idées modernes, notamment en ce qui concerne la nature de la lumière et son rôle dans l'univers, sa tentative de dépasser l'aristotélisme et de proposer une nouvelle philosophie universelle fondée sur la lumière et l'harmonie cosmique en fait une figure importante dans l'histoire de la pensée occidentale. Bien que ses idées aient été parfois marginalisées, elles témoignent de la richesse et de la diversité de la philosophie de la Renaissance. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F17" s="47" t="inlineStr">
@@ -1789,7 +1785,7 @@
       </c>
       <c r="E18" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne"  title=" Wikipedia"&gt; Michel de MONTAIGNE&lt;/a&gt; était un philosophe, écrivain français qui naquit près de Bordeaux, issu d’une famille de la petite noblesse terrienne. Après des études de droit, il exerce des fonctions de magistrat au Parlement de Bordeaux de 1557 à 1571, puis se retire de la vie publique pour se consacrer à la réflexion et à l’écriture. &lt;/p&gt; &lt;p&gt; Son œuvre majeure est &lt;a href="https://www.youtube.com/watch?v=qKXwK8Sj-24&amp;ab_channel=Kosmos" title="Les Essais par Kosmos"&gt; &lt;en&gt; Les Essais&lt;/em&gt;&lt;/a&gt;, publiés en trois livres entre 1580 et 1588, qu’il réécrit et enrichit tout au long de sa vie. Il livre aussi une traduction de la Théologie naturelle de Raymond Sebond (1569) et un Journal de voyage en Italie publié après sa mort, qui montre son goût pour l’observation concrète du monde. Il part de son expérience personnelle (sa santé, ses habitudes, ses lectures, ses voyages) pour &gt;&lt;a href="https://www.youtube.com/watch?v=dIH-Pg1q1pE"  title=" La Philosophie de Montaigne par Paroles de philosophe"&gt;interroger l’homme&lt;/a&gt;, la connaissance, la mort, l’amitié ou l’éducation, en adoptant un ton très libre et décousu. Il met en doute les certitudes de la science ou de la religion de son époque, prône la curiosité, la tolérance et la connaissance de soi, et ouvre la voie au relativisme et au scepticisme moderne. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs du &lt;a href="https://www.youtube.com/watch?v=IcW1ZnRUoGI"  title="Le scepticisme de Montaigne par Le Prisme Humain"&gt;scepticisme moderne&lt;/a&gt;, une approche philosophique qui remet en question la capacité de la raison humaine à atteindre une vérité absolue. Il est également connu pour sa conception de la philosophie comme une pratique personnelle de l'auto-examen et de la réflexion sur soi. Il croyait que la sagesse ne pouvait pas être trouvée dans les livres ou les enseignements des autres, mais devait être découverte à travers l'expérience de la vie et la contemplation de soi. &lt;/p&gt; &lt;p&gt; Il pronait la tolérance religieuse et la coexistence pacifique des différentes religions. Il était aussi un défenseur de la liberté de pensée et d'expression car les individus devaient être libres de penser et de s'exprimer sans crainte de persécution. &lt;/p&gt; &lt;p&gt; Il est important d'accepter notre nature humaine et ne pas essayer de nous conformer à des normes artificielles ou idéalisées. Il a écrit sur &lt;a href="https://preo.u-bourgogne.fr/shc/index.php?id=78" title="La vanité par Ed LETS"&gt;la vanité &lt;/a&gt; de l'homme et la nécessité de reconnaître nos faiblesses et nos imperfections.  &lt;/p&gt; &lt;audio controls title="La fable de l'identité  par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/03/s11/RF_B993FBEB-CED3-4D8B-A48F-2D502E485A89_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne"  title=" Wikipedia"&gt; Michel de MONTAIGNE&lt;/a&gt; était un philosophe, écrivain français qui naquit près de Bordeaux, issu d’une famille de la petite noblesse terrienne. Après des études de droit, il exerce des fonctions de magistrat au Parlement de Bordeaux de 1557 à 1571, puis se retire de la vie publique pour se consacrer à la réflexion et à l’écriture. &lt;/p&gt; &lt;p&gt; Son œuvre majeure est &lt;a href="https://www.youtube.com/watch?v=qKXwK8Sj-24&amp;ab_channel=Kosmos" title="Les Essais par Kosmos"&gt; &lt;en&gt; Les Essais&lt;/em&gt;&lt;/a&gt;, publiés en trois livres entre 1580 et 1588, qu’il réécrit et enrichit tout au long de sa vie. Il livre aussi une traduction de la Théologie naturelle de Raymond Sebond (1569) et un Journal de voyage en Italie publié après sa mort, qui montre son goût pour l’observation concrète du monde. Il part de son expérience personnelle (sa santé, ses habitudes, ses lectures, ses voyages) pour &gt;&lt;a href="https://www.youtube.com/watch?v=dIH-Pg1q1pE"  title=" La Philosophie de Montaigne par Paroles de philosophe"&gt;interroger l’homme&lt;/a&gt;, la connaissance, la mort, l’amitié ou l’éducation, en adoptant un ton très libre et décousu. Il met en doute les certitudes de la science ou de la religion de son époque, prône la curiosité, la tolérance et la connaissance de soi, et ouvre la voie au relativisme et au scepticisme moderne. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs du &lt;a href="https://www.youtube.com/watch?v=IcW1ZnRUoGI"  title="Le scepticisme de Montaigne par Le Prisme Humain"&gt;scepticisme moderne&lt;/a&gt;, une approche philosophique qui remet en question la capacité de la raison humaine à atteindre une vérité absolue. Il est également connu pour sa conception de la philosophie comme une pratique personnelle de l'auto-examen et de la réflexion sur soi. Il croyait que la sagesse ne pouvait pas être trouvée dans les livres ou les enseignements des autres, mais devait être découverte à travers l'expérience de la vie et la contemplation de soi. &lt;/p&gt; &lt;p&gt; Il pronait la tolérance religieuse et la coexistence pacifique des différentes religions. Il était aussi un défenseur de la liberté de pensée et d'expression car les individus devaient être libres de penser et de s'exprimer sans crainte de persécution. &lt;/p&gt; &lt;p&gt; Il est important d'accepter notre nature humaine et ne pas essayer de nous conformer à des normes artificielles ou idéalisées. Il a écrit sur &lt;a href="https://preo.u-bourgogne.fr/shc/index.php?id=78" title="La vanité par Ed LETS"&gt;la vanité &lt;/a&gt; de l'homme et la nécessité de reconnaître nos faiblesses et nos imperfections.  &lt;/p&gt; &lt;audio controls title="La fable de l'identité  par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/03/s11/RF_B993FBEB-CED3-4D8B-A48F-2D502E485A89_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F18" s="47" t="inlineStr">
@@ -1858,10 +1854,7 @@
       </c>
       <c r="E19" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacopo_Zabarella"  title=" Wikipedia"&gt;Jacopo ZABARELLA&lt;/a&gt; était un philosophe italien, connu pour ses contributions à la logique, à l'épistémologie et à la philosophie naturelle. Il est souvent associé à &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Padoue"  title="Ecole de Padoue par Wikipedia"&gt;l’aristotélisme padouan&lt;/a&gt;, un courant philosophique influent qui a dominé l’Université de Padoue où il enseigna toute sa vie. Son approche se caractérise par un retour rigoureux aux textes aristotéliciens, en opposition aux interprétations néoplatoniciennes, scolastiques ou humanistes plus libres. &lt;/p&gt; &lt;p&gt;Il est célèbre pour sa réflexion sur la méthodologie scientifique, en particulier dans ses œuvres  importantes, principalement en latin dont les plus notables sont : &lt;/p&gt; &lt;p&gt; 
-- &lt;"Opera Logica"  : Une œuvre majeure dans laquelle il expose une théorie logique influencée par Aristote, mais aussi enrichie par sa propre réflexion méthodologique. &lt;/p&gt; &lt;p&gt; 
--  "De Methodis" : Texte fondamental sur la question des méthodes scientifiques, dans lequel il distingue deux types de raisonnements scientifiques : la méthode résolutive (anagogique, qui va de l’effet à la cause) et la méthode compositive (déductive, qui va de la cause à l’effet). Ces deux méthodes inspireront plus tard la pensée scientifique moderne. &lt;/p&gt; 
-&lt;p&gt; - "De Rebus Naturalibus" : Traité sur la philosophie naturelle aristotélicienne. &lt;/p&gt; &lt;p&gt; Il  est un des premiers à penser la science comme un système de démonstrations fondé sur des principes sûrs, mais qui doivent être établis par l’observation et la réflexion logique. Il reste fidèle à Aristote, mais développe des outils logiques sophistiqués pour fonder une science naturelle rigoureuse. Son œuvre est un pont entre la scolastique médiévale et les débuts de la révolution scientifique. Il a influencé plusieurs générations de penseurs, non seulement en Italie, mais aussi dans le monde germanique, où ses textes ont été largement diffusés. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacopo_Zabarella"  title=" Wikipedia"&gt;Jacopo ZABARELLA&lt;/a&gt; était un philosophe italien, connu pour ses contributions à la logique, à l'épistémologie et à la philosophie naturelle. Il est souvent associé à &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Padoue"  title="Ecole de Padoue par Wikipedia"&gt;l’aristotélisme padouan&lt;/a&gt;, un courant philosophique influent qui a dominé l’Université de Padoue où il enseigna toute sa vie. Son approche se caractérise par un retour rigoureux aux textes aristotéliciens, en opposition aux interprétations néoplatoniciennes, scolastiques ou humanistes plus libres. &lt;/p&gt; &lt;p&gt;Il est célèbre pour sa réflexion sur la méthodologie scientifique, en particulier dans ses œuvres  importantes, principalement en latin dont les plus notables sont : &lt;/p&gt; &lt;p&gt;&lt;"Opera Logica"  : Une œuvre majeure dans laquelle il expose une théorie logique influencée par Aristote, mais aussi enrichie par sa propre réflexion méthodologique. &lt;/p&gt; &lt;p&gt;"De Methodis" : Texte fondamental sur la question des méthodes scientifiques, dans lequel il distingue deux types de raisonnements scientifiques : la méthode résolutive (anagogique, qui va de l’effet à la cause) et la méthode compositive (déductive, qui va de la cause à l’effet). Ces deux méthodes inspireront plus tard la pensée scientifique moderne. &lt;/p&gt; &lt;p&gt;"De Rebus Naturalibus" : Traité sur la philosophie naturelle aristotélicienne. &lt;/p&gt; &lt;p&gt; Il  est un des premiers à penser la science comme un système de démonstrations fondé sur des principes sûrs, mais qui doivent être établis par l’observation et la réflexion logique. Il reste fidèle à Aristote, mais développe des outils logiques sophistiqués pour fonder une science naturelle rigoureuse. Son œuvre est un pont entre la scolastique médiévale et les débuts de la révolution scientifique. Il a influencé plusieurs générations de penseurs, non seulement en Italie, mais aussi dans le monde germanique, où ses textes ont été largement diffusés. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -1994,14 +1987,10 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giordano_Bruno"  title=" Wikipedia"&gt; Giordano BRUNO&lt;/a&gt; était un philosophe et penseur italien, connue pour ses  &lt;a href="https://www.youtube.com/watch?v=21dM3ZJtYY0&amp;t=11s" style="color:#88A1E9" title="Giordano BRUNO de Calvin par Le Pro Presente "&gt;idées cosmologiques&lt;/a&gt; et philosophiques radicales dont voici quelques-uns de ses concepts clés : &lt;/p&gt; &lt;p&gt; &lt;/p&gt;
-&lt;p&gt; - L'univers infini : et peuplé d'une infinité de mondes habités. Cette vision s'opposait à la conception géocentrique de l'univers, qui plaçait la Terre au centre de tout.  &lt;/p&gt;
-&lt;p&gt; -  L'unité de la matière et de l'esprit : vision panthéiste de l'univers, où il croyait que la matière et l'esprit étaient inséparables et que l'univers était animé par une force vitale universelle. &lt;/p&gt;
-&lt;p&gt;  - La relativité du mouvement : le mouvement est relatif et qu'il n'y a pas de point de référence absolu dans l'univers. &lt;/p&gt;
-&lt;p&gt; - La liberté de pensée : la liberté de pensée et d'expression, s'opposant à l'autorité dogmatique de l'Église. Il croyait que la vérité ne pouvait être découverte que par la raison et l'expérience, et non par la révélation divine. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; En raison de  &lt;a href="https://nospensees.fr/les-meilleures-phrases-de-giordano-bruno/" title="Giordano BRUNO par nospensees "&gt;ses idées controversées&lt;/a&gt;, il a été contraint de quitter l'Italie et de voyager à travers l'Europe, dans des villes comme Genève, Paris, Londres et Prague, où il a enseigné et publié  &lt;a href="https://www.willeime.com/bruno.htm" title="Giordano BRUNO par willeime "&gt;ses œuvres&lt;/a&gt;. Il a été arrêté par l'Inquisition vénitienne et extradé à Rome. Après 8 ans de procès, il a été accusé d'hérésie pour ses idées et condamné à mort. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus importantes, on peut citer : &lt;/p&gt; &lt;p&gt; &lt;/p&gt;
-&lt;p&gt; -  &lt;a href="https://www.youtube.com/watch?v=vHfEKwAmhAQ"  title="Giordano BRUNO par Filosofia"&gt;"De l'infinito, universo e mondi"&lt;/a&gt;: Théorie de l'univers infini et des mondes multiples. &lt;/p&gt; 
-&lt;p&gt; -" La cena de le ceneri" : Critique la philosophie aristotélicienne et défend les idées coperniciennes.&lt;/p&gt; 
-&lt;p&gt; - "De la causa, principio e uno" : Nature de l'univers et l'unité de la matière et de l'esprit.&lt;/p&gt;  &lt;p&gt; &lt;/p&gt; &lt;p&gt;   &lt;p&gt; &lt;/p&gt;     &lt;audio controls title=" Giordano BRUNO par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-16.11.2022-ITEMA_23198161-2015C3372E1085-NET_MFC_367A1BA4-BD9E-4C79-A1B2-C57FCE8CB809-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giordano_Bruno"  title=" Wikipedia"&gt; Giordano BRUNO&lt;/a&gt; était un philosophe et penseur italien, connue pour ses  &lt;a href="https://www.youtube.com/watch?v=21dM3ZJtYY0&amp;t=11s" style="color:#88A1E9" title="Giordano BRUNO de Calvin par Le Pro Presente "&gt;idées cosmologiques&lt;/a&gt; et philosophiques radicales dont voici quelques-uns de ses concepts clés : &lt;/p&gt; &lt;p&gt;L'univers infini : et peuplé d'une infinité de mondes habités. Cette vision s'opposait à la conception géocentrique de l'univers, qui plaçait la Terre au centre de tout.  &lt;/p&gt;
+&lt;p&gt;L'unité de la matière et de l'esprit : vision panthéiste de l'univers, où il croyait que la matière et l'esprit étaient inséparables et que l'univers était animé par une force vitale universelle. &lt;/p&gt;
+&lt;p&gt;La relativité du mouvement : le mouvement est relatif et qu'il n'y a pas de point de référence absolu dans l'univers. &lt;/p&gt;
+&lt;p&gt;La liberté de pensée : la liberté de pensée et d'expression, s'opposant à l'autorité dogmatique de l'Église. Il croyait que la vérité ne pouvait être découverte que par la raison et l'expérience, et non par la révélation divine. &lt;/p&gt; &lt;p&gt; En raison de  &lt;a href="https://nospensees.fr/les-meilleures-phrases-de-giordano-bruno/" title="Giordano BRUNO par nospensees "&gt;ses idées controversées&lt;/a&gt;, il a été contraint de quitter l'Italie et de voyager à travers l'Europe, dans des villes comme Genève, Paris, Londres et Prague, où il a enseigné et publié  &lt;a href="https://www.willeime.com/bruno.htm" title="Giordano BRUNO par willeime "&gt;ses œuvres&lt;/a&gt;. Il a été arrêté par l'Inquisition vénitienne et extradé à Rome. Après 8 ans de procès, il a été accusé d'hérésie pour ses idées et condamné à mort. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus importantes, on peut citer : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=vHfEKwAmhAQ"  title="Giordano BRUNO par Filosofia"&gt;"De l'infinito, universo e mondi"&lt;/a&gt;: Théorie de l'univers infini et des mondes multiples. &lt;/p&gt; &lt;p&gt;" La cena de le ceneri" : Critique la philosophie aristotélicienne et défend les idées coperniciennes.&lt;/p&gt; &lt;p&gt;"De la causa, principio e uno" : Nature de l'univers et l'unité de la matière et de l'esprit.&lt;/p&gt; &lt;p&gt;        &lt;audio controls title=" Giordano BRUNO par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-16.11.2022-ITEMA_23198161-2015C3372E1085-NET_MFC_367A1BA4-BD9E-4C79-A1B2-C57FCE8CB809-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F21" s="47" t="inlineStr">
@@ -2199,9 +2188,7 @@
       </c>
       <c r="E24" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tommaso_Campanella" title=" Wikipedia"&gt;Tommaso CAMPANELLA&lt;/a&gt; était  un philosophe, théologien et moine dominicain italien, connu pour ses   &lt;a href="https://www.youtube.com/watch?v=wAl4GvGSVJM" style="color:#88A1E9" title="Jean Delumeau : Le mystère Campanella par Canal Academies "&gt;idées utopiques&lt;/a&gt;, sa pensée politique audacieuse et son engagement en faveur d’une réforme sociale et religieuse.  Il sera marqué par la pensée d’Aristote, mais aussi par les idées novatrices de Bernardino Telesio, un philosophe naturaliste qui rejette l’aristotélisme traditionnel. &lt;/p&gt; &lt;p&gt; Il  s’oppose à l’autorité espagnole en Italie et participe à un complot visant à établir une république mais le projet échoue. Il est arrêté, torturé et condamné à mort, il simule la folie pour éviter l’exécution et passera 27 ans en prison, où il écrit son œuvre majeure : &lt;/p&gt; &lt;p&gt; -  &lt;a href="https://www.persee.fr/doc/barb_0001-4133_1992_num_3_1_38762" title="Tommaso Campanella, « La Cité du Soleil » par Persée "&gt;La Cité du Soleil&lt;/a&gt; : Utopie politique et sociale, inspirée de La République de Platon et de L'Utopie de Thomas More. Une société idéale gouvernée par des savants, où la propriété privée est abolie, les biens sont communs, et l’éducation est centralisée. &lt;/p&gt; &lt;p&gt; - Philosophia sensibus demonstrata : Il s’inspire de Telesio pour promouvoir une philosophie basée sur l’observation de la nature, rejetant la scolastique aristotélicienne.&lt;/p&gt; 
-&lt;p&gt; - Atheismus triumphatus : Critique de l’athéisme, mais aussi des dogmatismes religieux. Il prédit une réforme universelle de l’Église et de la société, influencé par le millénarisme (âge d’or futur). &lt;/p&gt; 
-&lt;p&gt; - Monarchie d'Espagne : Projet politique pour une monarchie universelle sous domination espagnole.  Il rejette la séparation de la morale et de la politique, prônant un État vertueux. &lt;/p&gt; &lt;p&gt; Il  reste une figure complexe, à mi-chemin entre mysticisme et rationalisme, dont les idées résonnent encore dans les débats sur la justice sociale et le rôle de la science. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tommaso_Campanella" title=" Wikipedia"&gt;Tommaso CAMPANELLA&lt;/a&gt; était  un philosophe, théologien et moine dominicain italien, connu pour ses   &lt;a href="https://www.youtube.com/watch?v=wAl4GvGSVJM" style="color:#88A1E9" title="Jean Delumeau : Le mystère Campanella par Canal Academies "&gt;idées utopiques&lt;/a&gt;, sa pensée politique audacieuse et son engagement en faveur d’une réforme sociale et religieuse.  Il sera marqué par la pensée d’Aristote, mais aussi par les idées novatrices de Bernardino Telesio, un philosophe naturaliste qui rejette l’aristotélisme traditionnel. &lt;/p&gt; &lt;p&gt; Il  s’oppose à l’autorité espagnole en Italie et participe à un complot visant à établir une république mais le projet échoue. Il est arrêté, torturé et condamné à mort, il simule la folie pour éviter l’exécution et passera 27 ans en prison, où il écrit son œuvre majeure : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/barb_0001-4133_1992_num_3_1_38762" title="Tommaso Campanella, « La Cité du Soleil » par Persée "&gt;La Cité du Soleil&lt;/a&gt; : Utopie politique et sociale, inspirée de La République de Platon et de L'Utopie de Thomas More. Une société idéale gouvernée par des savants, où la propriété privée est abolie, les biens sont communs, et l’éducation est centralisée. &lt;/p&gt; &lt;p&gt;Philosophia sensibus demonstrata : Il s’inspire de Telesio pour promouvoir une philosophie basée sur l’observation de la nature, rejetant la scolastique aristotélicienne.&lt;/p&gt; &lt;p&gt;Atheismus triumphatus : Critique de l’athéisme, mais aussi des dogmatismes religieux. Il prédit une réforme universelle de l’Église et de la société, influencé par le millénarisme (âge d’or futur). &lt;/p&gt; &lt;p&gt;Monarchie d'Espagne : Projet politique pour une monarchie universelle sous domination espagnole.  Il rejette la séparation de la morale et de la politique, prônant un État vertueux. &lt;/p&gt; &lt;p&gt; Il  reste une figure complexe, à mi-chemin entre mysticisme et rationalisme, dont les idées résonnent encore dans les débats sur la justice sociale et le rôle de la science. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -2335,8 +2322,8 @@
       <c r="E26" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugo_Grotius" title=" Wikipedia"&gt;Hugo GROTUIS&lt;/a&gt; était une figure majeure de l'histoire intellectuelle Néerlandaise, juridique et politique, il est souvent considéré comme l'un des fondateurs du droit international moderne.  Il a vécu à une époque marquée par des conflits religieux et politiques intenses, notamment la guerre de Quatre-Vingts Ans entre les Pays-Bas et l'Espagne, ainsi que la guerre de Trente Ans en Europe. Ces conflits ont influencé sa pensée, notamment en ce qui concerne la nécessité d'un &lt;a href="https://www.youtube.com/watch?v=BoTTE8ohmJ0" style="color:#88A1E9" title="Le droit des gens et le droit international par Radio J "&gt;système juridique&lt;/a&gt; pour réguler les relations entre États. &lt;/p&gt; &lt;p&gt; Ses contributions majeures en droit international : &lt;/p&gt;
-&lt;dd&gt; - &lt;a href="https://www.persee.fr/doc/ridc_0035-3337_1954_num_6_4_9126"  title="H Grotius par Persée "&gt;"De jure belli ac pacis"&lt;/a&gt;  (Du droit de la guerre et de la paix, 1625) : œuvres fondatrices du droit international. Il y développe l'idée que les relations entre États devraient être régies par des principes juridiques plutôt que par la force brute. Il introduit le concept de "droit naturel", qui est universel et immuable, et qui s'applique à tous les êtres humains, indépendamment de leur nationalité ou de leur religion. &lt;/dd&gt;
-&lt;dd&gt; - "Mare Liberum"   (La mer libre, 1609) : les mers doivent être libres d'accès pour tous les États, une idée qui a eu un impact sur le droit maritime international. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt;  Il a défendu l'idée que la souveraineté de l'État est limitée par le droit naturel et que les gouvernements ont des obligations envers leurs citoyens. Il a plaidé pour la tolérance religieuse et a cherché à réconcilier les différentes confessions chrétiennes. Son ouvrage &lt;a href="https://www.penseesdepascal.fr/General/Grotius.php" title="De veritate religionis christianae par penseesdepascal "&gt;"De veritate religionis Christianae" &lt;/a&gt; (Sur la vérité de la religion chrétienne) est une défense rationnelle du christianisme.&lt;/p&gt; &lt;p&gt; Il est souvent appelé le "père du droit international" et ses idées ont jeté les bases de nombreuses institutions internationales modernes, comme les Nations Unies. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; </t>
+&lt;p&gt;&lt;a href="https://www.persee.fr/doc/ridc_0035-3337_1954_num_6_4_9126"  title="H Grotius par Persée "&gt;"De jure belli ac pacis"&lt;/a&gt;  (Du droit de la guerre et de la paix, 1625) : œuvres fondatrices du droit international. Il y développe l'idée que les relations entre États devraient être régies par des principes juridiques plutôt que par la force brute. Il introduit le concept de "droit naturel", qui est universel et immuable, et qui s'applique à tous les êtres humains, indépendamment de leur nationalité ou de leur religion. &lt;/p&gt;
+&lt;p&gt;"Mare Liberum"   (La mer libre, 1609) : les mers doivent être libres d'accès pour tous les États, une idée qui a eu un impact sur le droit maritime international. &lt;/p&gt; &lt;p&gt;  Il a défendu l'idée que la souveraineté de l'État est limitée par le droit naturel et que les gouvernements ont des obligations envers leurs citoyens. Il a plaidé pour la tolérance religieuse et a cherché à réconcilier les différentes confessions chrétiennes. Son ouvrage &lt;a href="https://www.penseesdepascal.fr/General/Grotius.php" title="De veritate religionis christianae par penseesdepascal "&gt;"De veritate religionis Christianae" &lt;/a&gt; (Sur la vérité de la religion chrétienne) est une défense rationnelle du christianisme.&lt;/p&gt; &lt;p&gt; Il est souvent appelé le "père du droit international" et ses idées ont jeté les bases de nombreuses institutions internationales modernes, comme les Nations Unies. &lt;/p&gt;  </t>
         </is>
       </c>
       <c r="F26" s="47" t="inlineStr">
@@ -2402,11 +2389,8 @@
       </c>
       <c r="E27" s="49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giulio_Cesare_Vanini"  title=" Wikipedia"&gt;Giulo Cesare VANINI&lt;/a&gt; était  un philosophe et libre-penseur italien, précurseur des Lumières et un représentant radical du naturalisme et de l'athéisme. Il s'inscrit dans la &lt;a href="https://www.youtube.com/watch?v=6oiQSoSK8-I" style="color:#88A1E9" title=" 1619, Vanini, un libertin sur le bûcher par Librairie Ombres Blanches "&gt;tradition libertine&lt;/a&gt; et sceptique de la Renaissance, influencé par des auteurs comme Pomponazzi et peut-être par les  &lt;a href="https://www.persee.fr/doc/horma_0984-2616_1999_num_40_1_1801" style="color:#88A1E9" title=" Au déclin de l'averroïsme latin : Giulio Cesare Vanini par Persée"&gt;courants averroïstes&lt;/a&gt; ou épicuriens clandestins. Ses idées marquantes incluent : &lt;/p&gt;
-&lt;p&gt;  - Naturalisme radical : Il affirme que la nature se suffit à elle-même et qu'il n'est pas nécessaire de recourir à Dieu pour expliquer les phénomènes et suggère que le monde pourrait être éternel et que les religions sont des inventions humaines. &lt;/p&gt; 
-&lt;p&gt;  - Critique des miracles : Dans De Admirandis, il explique les "miracles" par des causes naturelles ou des supercheries, une position extrêmement dangereuse à l'époque. &lt;/p&gt; 
-&lt;p&gt; - Athéisme voilé : Bien qu'il utilise parfois un langage déiste pour se protéger, ses contemporains (comme le philosophe Mersenne) l'ont accusé de promouvoir l'athéisme. Certains passages de ses livres laissent penser qu'il considérait Dieu comme une métaphore de la Nature. &lt;/p&gt; 
-&lt;p&gt;  - Influence sur le matérialisme : Il anticipe des thèmes qu'on retrouvera chez Spinoza (le Dieu-Nature) ou chez les matérialistes du XVIIIe siècle (comme Diderot). &lt;/p&gt; &lt;p&gt;  
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giulio_Cesare_Vanini"  title=" Wikipedia"&gt;Giulo Cesare VANINI&lt;/a&gt; était  un philosophe et libre-penseur italien, précurseur des Lumières et un représentant radical du naturalisme et de l'athéisme. Il s'inscrit dans la &lt;a href="https://www.youtube.com/watch?v=6oiQSoSK8-I" style="color:#88A1E9" title=" 1619, Vanini, un libertin sur le bûcher par Librairie Ombres Blanches "&gt;tradition libertine&lt;/a&gt; et sceptique de la Renaissance, influencé par des auteurs comme Pomponazzi et peut-être par les  &lt;a href="https://www.persee.fr/doc/horma_0984-2616_1999_num_40_1_1801" style="color:#88A1E9" title=" Au déclin de l'averroïsme latin : Giulio Cesare Vanini par Persée"&gt;courants averroïstes&lt;/a&gt; ou épicuriens clandestins. Ses idées marquantes incluent : &lt;/p&gt;
+&lt;p&gt;Naturalisme radical : Il affirme que la nature se suffit à elle-même et qu'il n'est pas nécessaire de recourir à Dieu pour expliquer les phénomènes et suggère que le monde pourrait être éternel et que les religions sont des inventions humaines. &lt;/p&gt; &lt;p&gt;Critique des miracles : Dans De Admirandis, il explique les "miracles" par des causes naturelles ou des supercheries, une position extrêmement dangereuse à l'époque. &lt;/p&gt; &lt;p&gt;Athéisme voilé : Bien qu'il utilise parfois un langage déiste pour se protéger, ses contemporains (comme le philosophe Mersenne) l'ont accusé de promouvoir l'athéisme. Certains passages de ses livres laissent penser qu'il considérait Dieu comme une métaphore de la Nature. &lt;/p&gt; &lt;p&gt;Influence sur le matérialisme : Il anticipe des thèmes qu'on retrouvera chez Spinoza (le Dieu-Nature) ou chez les matérialistes du XVIIIe siècle (comme Diderot). &lt;/p&gt; &lt;p&gt;  
 En 1615, il publie à Lyon "Amphitheatrum Æternæ Providentiæ Divino-Magicum" où il adopte encore une position déiste et, en 1616, son ouvrage "De Admirandis Naturæ Reginæ Deæque Mortalium Arcanis" suscite la controverse : il y développe une &lt;a href="https://www.youtube.com/watch?v=lfSxoWIDe0I" style="color:#88A1E9" title=" "Vanini, 400 ans : liberté de conscience et conscience de la liberté" par Association Item"&gt;philosophie naturaliste&lt;/a&gt;, voire matérialiste, qui nie l'immortalité de l'âme et remet en cause les miracles.&lt;/p&gt; &lt;p&gt;   Arrêté à Toulouse en 1618, il est jugé pour blasphème et athéisme. Refusant d'abjurer, il est condamné à avoir la langue arrachée et à être brûlé vif en place publique en février 1619. &lt;/p&gt;</t>
         </is>
       </c>
@@ -2542,7 +2526,7 @@
       </c>
       <c r="E29" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Heinrich_Alsted"  title=" Wikipedia"&gt;Johann Heinrich ALSTED&lt;/a&gt; était un théologien, philosophe et encyclopédiste protestant calviniste allemand, connu comme un polyhistor et un pionnier des encyclopédies modernes. Né à Ballersbach près d'Herborn, il enseigna la philosophie et la théologie à l'académie calviniste de Herborn, puis à Weissenburg en Transylvanie. Professeur influent, il fut impliqué dans la Synode de Dort et émigra en Transylvanie pour fuir les troubles religieux. Son élève Johann Amos Comenius diffusa largement ses idées en pédagogie et en réformes universelles. Il mourut en 1638, laissant une œuvre marquée par le ramisme, le lullisme et un chiliasme calviniste, &lt;/p&gt; &lt;p&gt; Il distinguait philosophie (raison, foedus naturae) et théologie (révélation, foedus gratiae), tout en cherchant une synthèse universelle des savoirs. Il intégrait logique ramiste, art de la mémoire lulliste et aristotélisme pour ordonner tout le savoir humain, visant une "réforme générale" hermétique et alchimique. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : - Encyclopaedia septem tomis distincta (1630) : Son chef-d'œuvre, un "système de tous les systèmes" résumant les disciplines (logique, physique, théologie), loué par ses contemporains. - Logicae Systema Harmonicum (1614) : Traité de logique appliquée à l'ensemble des connaissances. - Prodromus (1635) : Défense calviniste de la Trinité contre les anti-trinitariens.  Ses encyclopédies influencèrent la pédagogie européenne et les réformateurs du XVIIe siècle.  &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Heinrich_Alsted"  title=" Wikipedia"&gt;Johann Heinrich ALSTED&lt;/a&gt; était un théologien, philosophe et encyclopédiste protestant calviniste allemand, connu comme un polyhistor et un pionnier des encyclopédies modernes. Né à Ballersbach près d'Herborn, il enseigna la philosophie et la théologie à l'académie calviniste de Herborn, puis à Weissenburg en Transylvanie. Professeur influent, il fut impliqué dans la Synode de Dort et émigra en Transylvanie pour fuir les troubles religieux. Son élève Johann Amos Comenius diffusa largement ses idées en pédagogie et en réformes universelles. Il mourut en 1638, laissant une œuvre marquée par le ramisme, le lullisme et un chiliasme calviniste, &lt;/p&gt; &lt;p&gt; Il distinguait philosophie (raison, foedus naturae) et théologie (révélation, foedus gratiae), tout en cherchant une synthèse universelle des savoirs. Il intégrait logique ramiste, art de la mémoire lulliste et aristotélisme pour ordonner tout le savoir humain, visant une "réforme générale" hermétique et alchimique. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : Encyclopaedia septem tomis distincta (1630) : Son chef-d'œuvre, un "système de tous les systèmes" résumant les disciplines (logique, physique, théologie), loué par ses contemporains. Logicae Systema Harmonicum (1614) : Traité de logique appliquée à l'ensemble des connaissances. Prodromus (1635) : Défense calviniste de la Trinité contre les anti-trinitariens.  Ses encyclopédies influencèrent la pédagogie européenne et les réformateurs du XVIIe siècle.  &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -2676,7 +2660,7 @@
       </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Comenius"  title=" Wikipedia"&gt;COMENIUS&lt;/a&gt;   de son nom tchèque Jan Amos Komenský, était un philosophe, théologien et pédagogue tchèque, considéré comme le père de la pédagogie moderne. Évêque des Frères moraves, il fuit les persécutions religieuses et erra en Europe, promouvant une éducation universelle &lt;a href="https://www.youtube.com/watch?v=oGscXWKpLAA"  title="comment donner accès à tous les savoirs par Benoit Urgelli"&gt;accessible à tous, &lt;/a&gt; y compris aux filles et aux pauvres. &lt;/p&gt; &lt;p&gt; Orphelin jeune, il étudie à l’université de Heidelberg et devient enseignant dans les écoles moraves. Exilé après la bataille de la Montagne Blanche (1620), il enseigne à Lissa, Amsterdam et ailleurs, influencé par Alsted dont il fut l’élève. Il meurt à Naarden aux Pays-Bas, rêvant d’une restauration de son pays. &lt;/p&gt; &lt;p&gt; Il  prône une "pansophie" : une sagesse universelle enseignant tout à tous via la nature, la raison et la révélation divine. Il rejette les châtiments corporels, favorise l’apprentissage naturel, ludique et progressif (du sensoriel à l’abstrait), avec &lt;a href="https://www.youtube.com/watch?v=CMFh0seMZUg"  title="The dramatic story on education par Czech the History"&gt;des écoles pour tous &lt;/a&gt; les âges et sexes. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : - Didactica Magna (1657) : Traité sur l’art  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1969_num_49_1_3943"  title="Jean Amos COMENIUS par Persée"&gt; d’enseigner universellement, &lt;/a&gt; sans violence. - Orbis Sensualium Pictus (1658) : Premier manuel illustré bilingue pour enfants, associant mots et images.https://fr.wikipedia.org/wiki/Comenius - De Rerum Humanarum Emendatione : Consultation catholique pour une réforme mondiale du savoir et de la paix. Ses idées inspirèrent l’éducation européenne et l’UNESCO le nomme "Père de l’éducation". &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Comenius"  title=" Wikipedia"&gt;COMENIUS&lt;/a&gt;   de son nom tchèque Jan Amos Komenský, était un philosophe, théologien et pédagogue tchèque, considéré comme le père de la pédagogie moderne. Évêque des Frères moraves, il fuit les persécutions religieuses et erra en Europe, promouvant une éducation universelle &lt;a href="https://www.youtube.com/watch?v=oGscXWKpLAA"  title="comment donner accès à tous les savoirs par Benoit Urgelli"&gt;accessible à tous, &lt;/a&gt; y compris aux filles et aux pauvres. &lt;/p&gt; &lt;p&gt; Orphelin jeune, il étudie à l’université de Heidelberg et devient enseignant dans les écoles moraves. Exilé après la bataille de la Montagne Blanche (1620), il enseigne à Lissa, Amsterdam et ailleurs, influencé par Alsted dont il fut l’élève. Il meurt à Naarden aux Pays-Bas, rêvant d’une restauration de son pays. &lt;/p&gt; &lt;p&gt; Il  prône une "pansophie" : une sagesse universelle enseignant tout à tous via la nature, la raison et la révélation divine. Il rejette les châtiments corporels, favorise l’apprentissage naturel, ludique et progressif (du sensoriel à l’abstrait), avec &lt;a href="https://www.youtube.com/watch?v=CMFh0seMZUg"  title="The dramatic story on education par Czech the History"&gt;des écoles pour tous &lt;/a&gt; les âges et sexes. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : Didactica Magna (1657) : Traité sur l’art  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1969_num_49_1_3943"  title="Jean Amos COMENIUS par Persée"&gt; d’enseigner universellement, &lt;/a&gt; sans violence. Orbis Sensualium Pictus (1658) : Premier manuel illustré bilingue pour enfants, associant mots et images. De Rerum Humanarum Emendatione : Consultation catholique pour une réforme mondiale du savoir et de la paix. Ses idées inspirèrent l’éducation européenne et l’UNESCO le nomme "Père de l’éducation". &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -2813,7 +2797,7 @@
       </c>
       <c r="E33" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baltasar_Graci%C3%A1n" title=" Wikipedia"&gt;Baltazar GRACIAN&lt;/a&gt;  était un philosophe, moraliste, écrivain et jésuite espagnol du Siècle d’or, célèbre pour son style très dense et pour sa réflexion sur &lt;a href="https://www.youtube.com/watch?v=mo8tYs5W_MA"  title="L’art de la prudence par le Mental Parfait"&gt; la prudence, &lt;/a&gt; la conduite de la vie et la lucidité face au monde. On le considère comme l’un des grands représentants du conceptisme, un art de l’écriture qui concentre beaucoup d’idées en très peu de mots. Il entre chez les jésuites à 18 ans, devient prêtre, puis enseigne et exerce diverses fonctions dans la Compagnie de Jésus. Sa carrière fut parfois tendue avec ses supérieurs, car il publia plusieurs œuvres sans toujours respecter la discipline de l’ordre. &lt;/p&gt; &lt;p&gt; Il  voit la société comme un espace difficile où il faut apprendre à se défendre, à juger vite et à agir avec finesse. Sa philosophie est souvent sombre et réaliste : il insiste sur l’intelligence pratique, la discrétion, le tact et la capacité à lire les intentions des autres. &lt;/p&gt; &lt;p&gt; Ses Œuvres importantes : - El héroe (1637) : réflexion sur le modèle du héros capable de réussir dans la vie sociale. - El político don Fernando el Católico (1640) : traité sur l’art de gouverner.https://fr.wikipedia.org/wiki/Baltasar_Gracián - El discreto (1646) : idéal de l’homme accompli et prudent.https://fr.wikipedia.org/wiki/Baltasar_Gracián - Oráculo manual y arte de prudencia (1647) : son livre le plus célèbre, composé de maximes sur l’art de vivre. -  &lt;a href="https://www.youtube.com/watch?v=qD8Ji701jrU"  title="l’homme de cours par VoixLibris"&gt;El Criticón &lt;/a&gt; (1651-1657) : son grand roman philosophique, très critique envers la société humaine. &lt;/p&gt; &lt;p&gt; Il  a marqué durablement la pensée morale européenne par son mélange de philosophie, de littérature et de stratégie sociale. Son influence a été reconnue bien plus tard par des penseurs comme Schopenhauer, qui admirait particulièrement El Criticón.  &lt;/p&gt;  &lt;audio controls title="Baltazar Grancian ou l’art du travestissement par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.05.2016-ITEMA_20975945-2016C12410S0124-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baltasar_Graci%C3%A1n" title=" Wikipedia"&gt;Baltazar GRACIAN&lt;/a&gt;  était un philosophe, moraliste, écrivain et jésuite espagnol du Siècle d’or, célèbre pour son style très dense et pour sa réflexion sur &lt;a href="https://www.youtube.com/watch?v=mo8tYs5W_MA"  title="L’art de la prudence par le Mental Parfait"&gt; la prudence, &lt;/a&gt; la conduite de la vie et la lucidité face au monde. On le considère comme l’un des grands représentants du conceptisme, un art de l’écriture qui concentre beaucoup d’idées en très peu de mots. Il entre chez les jésuites à 18 ans, devient prêtre, puis enseigne et exerce diverses fonctions dans la Compagnie de Jésus. Sa carrière fut parfois tendue avec ses supérieurs, car il publia plusieurs œuvres sans toujours respecter la discipline de l’ordre. &lt;/p&gt; &lt;p&gt; Il  voit la société comme un espace difficile où il faut apprendre à se défendre, à juger vite et à agir avec finesse. Sa philosophie est souvent sombre et réaliste : il insiste sur l’intelligence pratique, la discrétion, le tact et la capacité à lire les intentions des autres. &lt;/p&gt; &lt;p&gt; Ses Œuvres importantes : El héroe (1637) : réflexion sur le modèle du héros capable de réussir dans la vie sociale. El político don Fernando el Católico (1640) : traité sur l’art de gouverner. El discreto (1646) : idéal de l’homme accompli et prudent. Oráculo manual y arte de prudencia (1647) : son livre le plus célèbre, composé de maximes sur l’art de vivre. &lt;a href="https://www.youtube.com/watch?v=qD8Ji701jrU"  title="l’homme de cours par VoixLibris"&gt;El Criticón &lt;/a&gt; (1651-1657) : son grand roman philosophique, très critique envers la société humaine. &lt;/p&gt; &lt;p&gt; Il  a marqué durablement la pensée morale européenne par son mélange de philosophie, de littérature et de stratégie sociale. Son influence a été reconnue bien plus tard par des penseurs comme Schopenhauer, qui admirait particulièrement El Criticón.  &lt;/p&gt;  &lt;audio controls title="Baltazar Grancian ou l’art du travestissement par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.05.2016-ITEMA_20975945-2016C12410S0124-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -2945,11 +2929,11 @@
       <c r="E35" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Blaise_Pascal" title="Blaise PASCAL par Wikipédia"&gt; Blaise PASCAL&lt;/a&gt;  était un mathématicien, philosophe et écrivain français. Il a inventé à 19 ans, la première calculatrice mécanique, connue sous le nom de "machine de Pascal". Il fut ensuite célèbre pour son &lt;a href="https://blaisepascal.bibliotheques-clermontmetropole.eu/son-oeuvre/pascal-savant/mathematiques/le-triangle-arithmetique"  title="Le triangle arithmétique par Clermont metropole"&gt; "Triangle de Pascal"&lt;/a&gt;, un arrangement de nombres qui est devenu un élément fondamental de la théorie des probabilités et de l'algèbre combinatoire. Il a aussi étudié la pression atmosphérique et a contribué à la compréhension de la manière dont la pression varie avec l'altitude. L'unité de pression "pascal" (Pa) porte son nom.  &lt;/p&gt; &lt;p&gt;
-Il était un chrétien dévot, et sa philosophie a été profondément influencée par sa foi. Il a écrit &lt;a href="https://www.youtube.com/watch?v=3uIjGv6jfSE&amp;ab_channel=Kosmos"   title="Pensées par Kosmos"&gt; "Pensées"&lt;/a&gt;, ce recueil de pensées, d'aphorismes et de réflexions où  Il a développé l'argument connu sous le nom de &lt;a href="https://www.youtube.com/watch?v=FoWFLpm8eX0&amp;ab_channel=AlainBajom%C3%A9e"  title="Le pari de Pascal par Alain Bajomée"&gt; "pari de Pascal,"&lt;/a&gt; qui suggère que, même en l'absence de preuves rationnelles concluantes de l'existence de Dieu, il est plus raisonnable de &lt;a href="https://www.youtube.com/watch?v=6KLWy3dWFMw&amp;ab_channel=LePr%C3%A9cepteur"   title="le pari par Le Précepteur"&gt;parier sur son existence&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;   Voici quelques-unes des contributions les plus importantes : &lt;p&gt;
-&lt;dd&gt;  &lt;a href="https://www.youtube.com/watch?v=OL4fFfld9Pw&amp;ab_channel=Kosmos"  title="le pouvoir par Kosmos"&gt;- La condition humaine :&lt;/a&gt;  Il l'aborde avec une perspective réaliste et parfois pessimiste. Il explore la vulnérabilité de l'homme, sa nature pécheresse et sa tendance à la vanité. Il souligne également l'incertitude de la vie humaine et la fragilité de l'existence. &lt;/dd&gt;
-&lt;dd&gt;  - Le désespoir et l'angoisse : Il a exploré le sentiment de vide et de malaise que les êtres humains peuvent ressentir lorsqu'ils sont confrontés à l'absurdité de la vie. Il a suggéré que la quête de sens et de bonheur peut être trouvée dans une relation personnelle avec Dieu.  &lt;/dd&gt;
-&lt;dd&gt; &lt;a href="https://www.youtube.com/watch?v=CNr84ZlVfVY&amp;t=668s&amp;ab_channel=LePr%C3%A9cepteur" title="le coeur à ses raisons par Le Précepteur"&gt;La pensée et le cœur :&lt;/a&gt; Il a fait une distinction entre la "raison du cœur" et la "raison de l'esprit." Il a soutenu que certaines vérités, en particulier celles liées à la foi et à la spiritualité, ne peuvent pas être pleinement saisies par la seule raison intellectuelle, mais nécessitent une approche du cœur et de l'émotion. &lt;/dd&gt;
-&lt;dd&gt; - La critique du rationalisme excessif :  qui réduisait toute connaissance à la raison et à la logique. Il croyait que la raison seule ne pouvait pas répondre à toutes les questions importantes de la vie et que l'expérience émotionnelle et spirituelle était tout aussi cruciale. &lt;/dd&gt;  &lt;audio controls title="Blaise Pascal, vers l'infini et au-delà par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.09.2018-ITEMA_21822263-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+Il était un chrétien dévot, et sa philosophie a été profondément influencée par sa foi. Il a écrit &lt;a href="https://www.youtube.com/watch?v=3uIjGv6jfSE&amp;ab_channel=Kosmos"   title="Pensées par Kosmos"&gt; "Pensées"&lt;/a&gt;, ce recueil de pensées, d'aphorismes et de réflexions où  Il a développé l'argument connu sous le nom de &lt;a href="https://www.youtube.com/watch?v=FoWFLpm8eX0&amp;ab_channel=AlainBajom%C3%A9e"  title="Le pari de Pascal par Alain Bajomée"&gt; "pari de Pascal,"&lt;/a&gt; qui suggère que, même en l'absence de preuves rationnelles concluantes de l'existence de Dieu, il est plus raisonnable de &lt;a href="https://www.youtube.com/watch?v=6KLWy3dWFMw&amp;ab_channel=LePr%C3%A9cepteur"   title="le pari par Le Précepteur"&gt;parier sur son existence&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;   &lt;p&gt;
+&lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=OL4fFfld9Pw&amp;ab_channel=Kosmos"  title="le pouvoir par Kosmos"&gt;- La condition humaine :&lt;/a&gt;  Il l'aborde avec une perspective réaliste et parfois pessimiste. Il explore la vulnérabilité de l'homme, sa nature pécheresse et sa tendance à la vanité. Il souligne également l'incertitude de la vie humaine et la fragilité de l'existence. &lt;/p&gt;
+&lt;p&gt;Le désespoir et l'angoisse : Il a exploré le sentiment de vide et de malaise que les êtres humains peuvent ressentir lorsqu'ils sont confrontés à l'absurdité de la vie. Il a suggéré que la quête de sens et de bonheur peut être trouvée dans une relation personnelle avec Dieu.  &lt;/p&gt;
+&lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=CNr84ZlVfVY&amp;t=668s&amp;ab_channel=LePr%C3%A9cepteur" title="le coeur à ses raisons par Le Précepteur"&gt;La pensée et le cœur :&lt;/a&gt; Il a fait une distinction entre la "raison du cœur" et la "raison de l'esprit." Il a soutenu que certaines vérités, en particulier celles liées à la foi et à la spiritualité, ne peuvent pas être pleinement saisies par la seule raison intellectuelle, mais nécessitent une approche du cœur et de l'émotion. &lt;/p&gt;
+&lt;p&gt;La critique du rationalisme excessif :  qui réduisait toute connaissance à la raison et à la logique. Il croyait que la raison seule ne pouvait pas répondre à toutes les questions importantes de la vie et que l'expérience émotionnelle et spirituelle était tout aussi cruciale. &lt;/p&gt;  &lt;audio controls title="Blaise Pascal, vers l'infini et au-delà par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.09.2018-ITEMA_21822263-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F35" s="47" t="inlineStr">
@@ -3018,7 +3002,7 @@
       </c>
       <c r="E36" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arnold_Geulincx"  style="color:#6A142A"  title=" Wikipedia"&gt;Arnold GEULINCX&lt;/a&gt;  était un philosophe flamand, disciple radical de Descartes et pionnier de  &lt;a href="https://fr.wikipedia.org/wiki/Occasionnalisme" title="occasionnalisme par Wikipedia"&gt;l'occasionnalisme, &lt;/a&gt; une doctrine niant toute causalité entre l'âme et le corps. Né à Anvers, il enseigna à Louvain avant d'être destitué pour sympathies jansénistes, puis à Leyde où il mourut de la peste à 45 ans. Étudiant en &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1910_num_17_65_4252" title="Arnold Geulincx et le procès de la philosophie par Persée"&gt;philosophie et théologie &lt;/a&gt; à Louvain, il devint professeur mais fut exilé pour hérésie présumée. À Leyde dès 1665, il développa sa pensée dans l'ombre de Descartes, influençant plus tard des auteurs comme Samuel Beckett avec sa maxime "Ubi nihil vales, ibi nihil velis" ("Là où tu ne vaux rien, là ne veuille rien"). &lt;/p&gt; &lt;p&gt; Il  radicalise le dualisme cartésien : l'esprit (res cogitans) et le corps (res extensa) sont deux substances séparées sans interaction causale directe, synchronisées par Dieu comme deux horloges divinement accordées. Principe clé : "Quod nescis quomodo fiat, id non facis" ("Ce que tu ignores comment ça se fait, tu ne le fais pas") – nous ne causons rien, car nous ignorons les mécanismes ; Dieu est la seule cause universelle. Son éthique repose sur l'"inspectio sui" (auto-examen humble) et une soumission joyeuse à l'impuissance humaine face à la volonté divine. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : - Disputatio ethica de furore (1665) : Sur la fureur et la maîtrise de soi. – Gnothi seauton ou Ethica (1675, posth.) : Éthique centrée sur l'humilité et la vertu, &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arnold_Geulincx"  style="color:#6A142A"  title=" Wikipedia"&gt;Arnold GEULINCX&lt;/a&gt;  était un philosophe flamand, disciple radical de Descartes et pionnier de  &lt;a href="https://fr.wikipedia.org/wiki/Occasionnalisme" title="occasionnalisme par Wikipedia"&gt;l'occasionnalisme, &lt;/a&gt; une doctrine niant toute causalité entre l'âme et le corps. Né à Anvers, il enseigna à Louvain avant d'être destitué pour sympathies jansénistes, puis à Leyde où il mourut de la peste à 45 ans. Étudiant en &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1910_num_17_65_4252" title="Arnold Geulincx et le procès de la philosophie par Persée"&gt;philosophie et théologie &lt;/a&gt; à Louvain, il devint professeur mais fut exilé pour hérésie présumée. À Leyde dès 1665, il développa sa pensée dans l'ombre de Descartes, influençant plus tard des auteurs comme Samuel Beckett avec sa maxime "Ubi nihil vales, ibi nihil velis" ("Là où tu ne vaux rien, là ne veuille rien"). &lt;/p&gt; &lt;p&gt; Il  radicalise le dualisme cartésien : l'esprit (res cogitans) et le corps (res extensa) sont deux substances séparées sans interaction causale directe, synchronisées par Dieu comme deux horloges divinement accordées. Principe clé : "Quod nescis quomodo fiat, id non facis" ("Ce que tu ignores comment ça se fait, tu ne le fais pas") – nous ne causons rien, car nous ignorons les mécanismes ; Dieu est la seule cause universelle. Son éthique repose sur l'"inspectio sui" (auto-examen humble) et une soumission joyeuse à l'impuissance humaine face à la volonté divine. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : Disputatio ethica de furore (1665) : Sur la fureur et la maîtrise de soi. – Gnothi seauton ou Ethica (1675, posth.) : Éthique centrée sur l'humilité et la vertu, &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -3085,7 +3069,7 @@
       </c>
       <c r="E37" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Erhard_Weigel" title=" Wikipedia"&gt;Erhard WEIGEL&lt;/a&gt;  était un mathématicien, philosophe et astronome allemand, professeur à l'université de Iéna, connu pour ses tentatives de fonder une &lt;a href="https://fr.wikipedia.org/wiki/Pansophisme" title="Pansophisme par Wikipedia"&gt; "pansophie universelle" &lt;/a&gt; en intégrant mathématiques, aristotélisme et sciences pratiques. Polymath prolifique, il cherchait à réformer l'éducation et la philosophie via une méthode géométrique, influençant Leibniz parmi ses élèves. Il étudie à Leipzig puis à Iéna où il obtient son doctorat en 1653 et devient professeur de mathématiques et de métaphysique dès 1662. Inventeur de dispositifs pédagogiques (comme des machines à enseigner l'astronomie), il défend des thèses controversées, frôlant l'interdiction de ses écrits pour hérésie philosophique. &lt;/p&gt; &lt;p&gt; Il vise une "restitutio" d'Aristote via Euclide : une science universelle structurant toute connaissance – philosophie, théologie, morale, politique – sur des principes mathématiques clairs et rationnels. Sa morale arithmétique divise le bien en "tetractys pythagoricienne" pour atteindre le bonheur ; sa socialphilosophie analyse les relations humaines comme des équations pratiques au service du bien commun. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : - Analysis Aristotelica ex Euclide restituta (1658) : Réinterprétation mathématique d'Aristote. - Arithmetische Beschreibung der Moral-Weißheit (1674) : Morale en termes numériques et pythagoriciens. - Universi Corporis Pansophici Caput Summum (1673) : Exposé de sa pansophie cosmologique.&lt;/p&gt; &lt;p&gt; Ses "Kunst-Erfindungen" (inventions artistiques) démocratisent la science, préfigurant une pédagogie universelle à la Comenius. &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Erhard_Weigel" title=" Wikipedia"&gt;Erhard WEIGEL&lt;/a&gt;  était un mathématicien, philosophe et astronome allemand, professeur à l'université de Iéna, connu pour ses tentatives de fonder une &lt;a href="https://fr.wikipedia.org/wiki/Pansophisme" title="Pansophisme par Wikipedia"&gt; "pansophie universelle" &lt;/a&gt; en intégrant mathématiques, aristotélisme et sciences pratiques. Polymath prolifique, il cherchait à réformer l'éducation et la philosophie via une méthode géométrique, influençant Leibniz parmi ses élèves. Il étudie à Leipzig puis à Iéna où il obtient son doctorat en 1653 et devient professeur de mathématiques et de métaphysique dès 1662. Inventeur de dispositifs pédagogiques (comme des machines à enseigner l'astronomie), il défend des thèses controversées, frôlant l'interdiction de ses écrits pour hérésie philosophique. &lt;/p&gt; &lt;p&gt; Il vise une "restitutio" d'Aristote via Euclide : une science universelle structurant toute connaissance – philosophie, théologie, morale, politique – sur des principes mathématiques clairs et rationnels. Sa morale arithmétique divise le bien en "tetractys pythagoricienne" pour atteindre le bonheur ; sa socialphilosophie analyse les relations humaines comme des équations pratiques au service du bien commun. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : Analysis Aristotelica ex Euclide restituta (1658) : Réinterprétation mathématique d'Aristote. Arithmetische Beschreibung der Moral-Weißheit (1674) : Morale en termes numériques et pythagoriciens. Universi Corporis Pansophici Caput Summum (1673) : Exposé de sa pansophie cosmologique.&lt;/p&gt; &lt;p&gt; Ses "Kunst-Erfindungen" (inventions artistiques) démocratisent la science, préfigurant une pédagogie universelle à la Comenius. &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -3359,10 +3343,8 @@
       </c>
       <c r="E41" s="58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Malebranche" title=" Wikipedia"&gt;Nicolas MALEBRANCHE&lt;/a&gt; était un philosophe et théologien français, connu pour ses travaux en métaphysique, en épistémologie et en philosophie de la religion. En 1660, il rejoint l'Oratoire, une congrégation religieuse catholique, où il se consacre à l'étude de la philosophie et de la théologie et il découvre les travaux de Descartes, qui auront une influence majeure sur sa pensée. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de  &lt;a href="https://www.youtube.com/watch?v=3YvitSjZ2_4&amp;t=326s" title="Malebranche : Occasionalism par Leevark"&gt;l'occasionalisme&lt;/a&gt;, qu'il développe dans son ouvrage majeur " De la recherche de la vérité". Selon lui, les idées que nous avons des objets existent dans l'entendement divin, et c'est par la médiation de Dieu que nous accédons à ces idées. Cette théorie s'oppose à l'empirisme et à l'idée que nos perceptions sont directement causées par les objets eux-mêmes.  Il rejette l'interaction directe entre l'âme et le corps, une idée défendue par Descartes. Selon lui, l'âme et le corps ne peuvent pas agir l'un sur l'autre directement. Au lieu de cela, Dieu coordonne les états de l'âme et les états du corps de manière harmonieuse, sans qu'il y ait de causalité directe entre eux. Il a développé une théorie selon laquelle Dieu agit selon des "lois générales" plutôt que par des interventions particulières, ce qui laisse une place à la &lt;a href="https://fr.wikipedia.org/wiki/Libert%C3%A9_(philosophie)"  title="La liberté par Wikipedia"&gt;liberté humaine&lt;/a&gt; tout en maintenant la souveraineté divine. &lt;/p&gt; &lt;p&gt;Ses oeuvres principales : &lt;/p&gt; 
-&lt;dd&gt; -De la recherche de la vérité : Théories sur la perception, la causalité et la métaphysique.  &lt;/dd&gt; 
-&lt;dd&gt; - Traité de la nature et de la grâce : Relation entre la grâce divine et les lois de la nature. &lt;/dd&gt;
-&lt;dd&gt; - Entretiens sur la métaphysique et la religion : Un dialogue qui résume et défend ses idées. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il reste une figure importante dans l'histoire de la philosophie, notamment pour sa tentative de concilier la pensée cartésienne avec une vision profondément théocentrique du monde. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;   &lt;audio controls title=" L’imagination selon Descartes et Malebranche par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-16.01.2024-ITEMA_23616134-2024C48904S0016-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Malebranche" title=" Wikipedia"&gt;Nicolas MALEBRANCHE&lt;/a&gt; était un philosophe et théologien français, connu pour ses travaux en métaphysique, en épistémologie et en philosophie de la religion. En 1660, il rejoint l'Oratoire, une congrégation religieuse catholique, où il se consacre à l'étude de la philosophie et de la théologie et il découvre les travaux de Descartes, qui auront une influence majeure sur sa pensée. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de  &lt;a href="https://www.youtube.com/watch?v=3YvitSjZ2_4&amp;t=326s" title="Malebranche : Occasionalism par Leevark"&gt;l'occasionalisme&lt;/a&gt;, qu'il développe dans son ouvrage majeur " De la recherche de la vérité". Selon lui, les idées que nous avons des objets existent dans l'entendement divin, et c'est par la médiation de Dieu que nous accédons à ces idées. Cette théorie s'oppose à l'empirisme et à l'idée que nos perceptions sont directement causées par les objets eux-mêmes.  Il rejette l'interaction directe entre l'âme et le corps, une idée défendue par Descartes. Selon lui, l'âme et le corps ne peuvent pas agir l'un sur l'autre directement. Au lieu de cela, Dieu coordonne les états de l'âme et les états du corps de manière harmonieuse, sans qu'il y ait de causalité directe entre eux. Il a développé une théorie selon laquelle Dieu agit selon des "lois générales" plutôt que par des interventions particulières, ce qui laisse une place à la &lt;a href="https://fr.wikipedia.org/wiki/Libert%C3%A9_(philosophie)"  title="La liberté par Wikipedia"&gt;liberté humaine&lt;/a&gt; tout en maintenant la souveraineté divine. &lt;/p&gt; &lt;p&gt;Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;De la recherche de la vérité : Théories sur la perception, la causalité et la métaphysique.  &lt;/p&gt; &lt;p&gt;Traité de la nature et de la grâce : Relation entre la grâce divine et les lois de la nature. &lt;/p&gt;
+&lt;p&gt;Entretiens sur la métaphysique et la religion : Un dialogue qui résume et défend ses idées. &lt;/p&gt; &lt;p&gt; Il reste une figure importante dans l'histoire de la philosophie, notamment pour sa tentative de concilier la pensée cartésienne avec une vision profondément théocentrique du monde. &lt;/p&gt;    &lt;audio controls title=" L’imagination selon Descartes et Malebranche par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-16.01.2024-ITEMA_23616134-2024C48904S0016-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F41" s="47" t="inlineStr">
@@ -3431,7 +3413,7 @@
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gottfried_Wilhelm_Leibniz"  title=" Wikipedia"&gt;Gottfried Wilhelm LEIBNIZ&lt;/a&gt; était un philosophe allemand très &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme"  title=""éclectisme par Wikipedia"&gt;éclectique&lt;/a&gt;, de la théologie en passant par les mathématiques, la logique et la philosophie politique ou encore la métaphysique où il est connu pour sa théorie des monades, selon laquelle l'univers est composé d'un nombre infini d'entités individuelles et autonomes appelées monades. Chaque monade est une substance simple, sans parties, qui possède une perception et une appétition, c'est-à-dire une tendance à rechercher le bien et à &lt;a href="https://www.youtube.com/watch?v=ZJKr-vJt3NE&amp;ab_channel=LePr%C3%A9cepteur"  title="Le mal n'existe pas par le Précepteur"&gt; éviter le mal&lt;/a&gt;. Les monades ne peuvent pas interagir directement les unes avec les autres, mais leur perception et leur appétition sont harmonisées par Dieu, qui a créé l'univers de manière à ce qu'il soit le meilleur des mondes possibles. &lt;/p&gt; &lt;p&gt;
 La théorie a des implications dans de nombreux domaines, y compris la métaphysique, la théologie, l'épistémologie et l'éthique. Elle implique que la connaissance de chaque monade est limitée à sa propre perspective, ce qui soulève des questions intéressantes sur la nature de la vérité et de la connaissance.&lt;/p&gt; &lt;p&gt; 
 En mathématiques, il est connu pour avoir inventé le calcul infinitésimal, une méthode qui permet de manipuler des quantités infiniment petites. Cette découverte a été réalisée de manière indépendante par Leibniz et Isaac Newton, et les deux hommes ont été impliqués dans une longue querelle pour savoir qui était le véritable inventeur.&lt;/p&gt; &lt;p&gt; 
-En philosophie politique, Leibniz a soutenu que le pouvoir politique devrait être détenu par une élite instruite, qui gouvernerait de manière éclairée et rationnelle. &lt;/p&gt;  &lt;audio controls title="La Monadologie par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/11/s47/RF_F56A3AEF-9E04-487F-89BF-2C4FBCA2B21D_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+En philosophie politique, Leibniz a soutenu que le pouvoir politique devrait être détenu par une élite instruite, qui gouvernerait de manière éclairée et rationnelle. &lt;/p&gt;  &lt;audio controls title="La Monadologie par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/11/s47/RF_F56A3AEF-9E04-487F-89BF-2C4FBCA2B21D_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F42" s="47" t="inlineStr">
@@ -3565,9 +3547,9 @@
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Bayle"   title=" Wikipedia"&gt;Pierre BAYLE&lt;/a&gt; était un philosophe français connu pour son scepticisme, sa défense de  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1965_num_39_2_2413" title="Pierre Bayle précurseur des théologies modernes de la liberté religieuse  par Persée"&gt;la tolérance religieuse &lt;/a&gt; et son monumental Dictionnaire historique et critique, qui en fait un précurseur majeur des Lumières. Sa pensée mêle critique radicale des dogmes religieux, exigence de rigueur historique et réflexion sur les limites de la raison. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un sceptique : il met en évidence les contradictions de la raison, notamment quand elle prétend démontrer les dogmes religieux (Trinité, providence, miracle, etc.). Il aime exposer des opinions paradoxales, voire scandaleuses, et les renforcer par des arguments rigoureux, sans dire clairement s’il les adopte lui‑même, ce qui déroutait ses contemporains. Concernant le problème du mal, il montre que la raison ne parvient pas à concilier l’existence du mal avec celle d’un Dieu tout‑puissant et parfaitement bon.
  &lt;/p&gt; &lt;p&gt; Il défend la tolérance civile : l’État ne doit pas persécuter pour des motifs religieux et doit protéger la liberté de conscience de toutes les confessions, y compris juifs, musulmans et athées. Il soutient qu’une société composée d’athées pourrait être ordonnée et morale, anticipant l’idée moderne d’une morale indépendante de la religion.  &lt;/p&gt; &lt;p&gt; 
-Le &lt;a href="https://fr.wikipedia.org/wiki/Dictionnaire_historique_et_critique" title=" Pierre Bayle : Dictionnaire historique et critique par Wikipedia"&gt;Dictionnaire historique et critique &lt;/a&gt; est un véritable "labyrinthe" de textes et de notes, où la partie la plus subversive se trouve souvent dans les renvois et les commentaires en marge. Il y pratique une critique érudite des sources, confrontant témoignages, chronologies et récits, et affaiblissant ainsi l’autorité de la tradition dogmatique. Les philosophes des Lumières (Voltaire, Diderot, etc.) lisent et l'utilisent, qu’ils voient comme un précurseur par son antifanatisme, son scepticisme et son exigence critique. &lt;/p&gt; &lt;p&gt; Ses autes ouvrages : - "Pensées diverses sur la comète" paru 1682 : partant de la comète de 1680, il y dénonce les superstitions qui associent phénomènes célestes et malheurs terrestres, et y formule le fameux paradoxe de "l’athée vertueux".  - "Ce que c’est que la France toute catholique sous le règne de Louis‑le‑Grand" paru en 1686 : critique ironique de la politique religieuse de Louis XIV et de la persécution des protestants. - Commentaire philosophique sur ces paroles de Jésus‑Christ : “Contrains‑les d’entrer” en 1686 : texte majeur pour la &lt;a href="https://www.youtube.com/watch?v=ew4sBCkUseA" title=" Pierre Bayle : tolérance et liberté religieuse  par Institut Coppet"&gt;théorie moderne de la tolérance&lt;/a&gt;, il argumente contre toute coercition en matière de foi, y compris envers les hérétiques et les athées. &lt;/p&gt; 
+Le &lt;a href="https://fr.wikipedia.org/wiki/Dictionnaire_historique_et_critique" title=" Pierre Bayle : Dictionnaire historique et critique par Wikipedia"&gt;Dictionnaire historique et critique &lt;/a&gt; est un véritable "labyrinthe" de textes et de notes, où la partie la plus subversive se trouve souvent dans les renvois et les commentaires en marge. Il y pratique une critique érudite des sources, confrontant témoignages, chronologies et récits, et affaiblissant ainsi l’autorité de la tradition dogmatique. Les philosophes des Lumières (Voltaire, Diderot, etc.) lisent et l'utilisent, qu’ils voient comme un précurseur par son antifanatisme, son scepticisme et son exigence critique. &lt;/p&gt; &lt;p&gt; Ses autes ouvrages : "Pensées diverses sur la comète" paru 1682 : partant de la comète de 1680, il y dénonce les superstitions qui associent phénomènes célestes et malheurs terrestres, et y formule le fameux paradoxe de "l’athée vertueux". "Ce que c’est que la France toute catholique sous le règne de Louis‑le‑Grand" paru en 1686 : critique ironique de la politique religieuse de Louis XIV et de la persécution des protestants. Commentaire philosophique sur ces paroles de Jésus‑Christ : “Contrains‑les d’entrer” en 1686 : texte majeur pour la &lt;a href="https://www.youtube.com/watch?v=ew4sBCkUseA" title=" Pierre Bayle : tolérance et liberté religieuse  par Institut Coppet"&gt;théorie moderne de la tolérance&lt;/a&gt;, il argumente contre toute coercition en matière de foi, y compris envers les hérétiques et les athées. &lt;/p&gt; 
 ​
-&lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Le scandaleux Pierre Bayle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-04.04.2008-ITEMA_20118105-2008C6409S0095-NET_66658CCB-7933-4384-84A0-F0495954D09D_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+ &lt;p&gt;  &lt;audio controls title="Le scandaleux Pierre Bayle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-04.04.2008-ITEMA_20118105-2008C6409S0095-NET_66658CCB-7933-4384-84A0-F0495954D09D_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F44" s="47" t="inlineStr">
@@ -3699,11 +3681,10 @@
       </c>
       <c r="E46" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Meslier"  title=" Wikipedia"&gt;Jean MESLIER&lt;/a&gt; était un prêtre français connu pour son &lt;a href="https://www.youtube.com/watch?v=5s-nuRI6dKY&amp;ab_channel=AlainBajom%C3%A9e"   title="L'athéisme par Meslier par Alain Bajomée"&gt; athéisme radical&lt;/a&gt; et anticlérical. À sa mort, un manuscrit de plus de 200 pages, connu sous le nom de  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1971_num_69_2_5609_t1_0297_0000_1"  title="Oeuvre complète par le Persée"&gt; "Mémoire des Pensées et des Sentiments de Jean Meslier"&lt;/a&gt;, a été découvert et est considéré comme l'un des premiers manifestes de l'athéisme moderne en France car il remet en question la validité des dogmes religieux, dénonce l'injustice sociale, critique l'influence corruptrice de l'Église et prône une société égalitaire.  &lt;/p&gt;
-  &lt;p&gt;   Quelques aspects de sa philosophie qui ont marqué l'histoire de la philosophie : &lt;/p&gt;&lt;dd&gt;&lt;a href="https://www.youtube.com/watch?v=0lQrBmCTD74"   title="La bonne parole du curé Meslier par Théatre poème"&gt; Athéisme radical&lt;/a&gt; - Il a argumenté de  manière virulente contre l'existence de Dieu et la validité des croyances religieuses. Il a utilisé des arguments rationalistes pour contester les dogmes religieux et a soutenu que la religion était une invention humaine visant à maintenir le pouvoir et la domination des élites religieuses et politiques. &lt;/dd&gt;
-&lt;dd&gt;&lt;a href="https://www.youtube.com/watch?v=p8r9BYjZ7SQ"   title="Le matérialisme par Culture philo"&gt;  - Matérialisme : &lt;/a&gt; Il croyait que le monde était constitué de matière et que la conscience humaine découlait de processus matériels dans le cerveau. Ce point de vue était en accord avec les idées des philosophes matérialistes ultérieurs des Lumières. &lt;/dd&gt;
-&lt;dd&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89galitarisme"   title="L’égalitarisme par Wikipedia"&gt; - Égalitarisme social :&lt;/a&gt; Il a critiqué l'injustice sociale et économique ainsi que le pouvoir de l'Église et de la noblesse. Il a plaidé en faveur de l'égalité sociale, de la répartition des richesses et de la fin des privilèges de la classe dirigeante. &lt;/dd&gt;
-&lt;dd&gt;- Influence sur les Lumières françaises :&lt;/a&gt; Les idées de Meslier ont eu un impact considérable sur les philosophes des Lumières en France, qui ont poursuivi la critique de la religion, de l'injustice sociale et du despotisme politique. Ses écrits ont été lus et discutés par des figures importantes comme Voltaire, Diderot et d'Alembert, contribuant ainsi à l'émergence de la pensée laïque et de l'athéisme dans la France du XVIIIe siècle. &lt;/dd&gt;  &lt;audio controls title="prêtre catholique et philosophe athée par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24171-31.07.2023-ITEMA_23450279-2023C51253S0212-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Meslier"  title=" Wikipedia"&gt;Jean MESLIER&lt;/a&gt; était un prêtre français connu pour son &lt;a href="https://www.youtube.com/watch?v=5s-nuRI6dKY&amp;ab_channel=AlainBajom%C3%A9e"   title="L'athéisme par Meslier par Alain Bajomée"&gt; athéisme radical&lt;/a&gt; et anticlérical. À sa mort, un manuscrit de plus de 200 pages, connu sous le nom de  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1971_num_69_2_5609_t1_0297_0000_1"  title="Oeuvre complète par le Persée"&gt; "Mémoire des Pensées et des Sentiments de Jean Meslier"&lt;/a&gt;, a été découvert et est considéré comme l'un des premiers manifestes de l'athéisme moderne en France car il remet en question la validité des dogmes religieux, dénonce l'injustice sociale, critique l'influence corruptrice de l'Église et prône une société égalitaire.  &lt;/p&gt; &lt;p&gt;   Quelques aspects de sa philosophie qui ont marqué l'histoire de la philosophie : &lt;/p&gt;&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=0lQrBmCTD74"   title="La bonne parole du curé Meslier par Théatre poème"&gt; Athéisme radical&lt;/a&gt; - Il a argumenté de  manière virulente contre l'existence de Dieu et la validité des croyances religieuses. Il a utilisé des arguments rationalistes pour contester les dogmes religieux et a soutenu que la religion était une invention humaine visant à maintenir le pouvoir et la domination des élites religieuses et politiques. &lt;/p&gt;
+&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=p8r9BYjZ7SQ"   title="Le matérialisme par Culture philo"&gt;  - Matérialisme : &lt;/a&gt; Il croyait que le monde était constitué de matière et que la conscience humaine découlait de processus matériels dans le cerveau. Ce point de vue était en accord avec les idées des philosophes matérialistes ultérieurs des Lumières. &lt;/p&gt;
+&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89galitarisme"   title="L’égalitarisme par Wikipedia"&gt; - Égalitarisme social :&lt;/a&gt; Il a critiqué l'injustice sociale et économique ainsi que le pouvoir de l'Église et de la noblesse. Il a plaidé en faveur de l'égalité sociale, de la répartition des richesses et de la fin des privilèges de la classe dirigeante. &lt;/p&gt;
+&lt;p&gt;Influence sur les Lumières françaises :&lt;/a&gt; Les idées de Meslier ont eu un impact considérable sur les philosophes des Lumières en France, qui ont poursuivi la critique de la religion, de l'injustice sociale et du despotisme politique. Ses écrits ont été lus et discutés par des figures importantes comme Voltaire, Diderot et d'Alembert, contribuant ainsi à l'émergence de la pensée laïque et de l'athéisme dans la France du XVIIIe siècle. &lt;/p&gt;  &lt;audio controls title="prêtre catholique et philosophe athée par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24171-31.07.2023-ITEMA_23450279-2023C51253S0212-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -4103,8 +4084,7 @@
       </c>
       <c r="E52" s="49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Montesquieu"    title=" Wikipedia"&gt;MONTESTQUIEU&lt;/a&gt; était un grand philosophe et écrivain français  associé au mouvement des Lumières et connu pour sa théorie de la séparation des pouvoirs. Il s’appelle en réalité Charles‑Louis de Secondat, baron de La Brède et de Montesquieu, et naît  près de Bordeaux dans une famille de noblesse de robe. &lt;/p&gt; &lt;p&gt; Deux œuvres dominent sa postérité : &lt;a href="https://www.youtube.com/watch?v=e72jQdl52bM" title=" Les Lettres persanes, Montesquieu  par Les Bons Profs"&gt;"les Lettres persanes"&lt;/a&gt;, un roman épistolaire satirique où des voyageurs persans observent la société française et critiquent l’absolutisme, les mœurs et l’intolérance religieuse, en utilisant le regard extérieur comme miroir critique et &lt;a href="https://www.youtube.com/watch?v=IBc46RLZxe4" title=" L'ESPRIT DES LOIS en 8 minutes ! par Culture Philo"&gt;"De l’esprit des lois"&lt;/a&gt;, un vaste traité de science politique et sociale qui analyse les types de gouvernement, le rôle des lois, l’influence du climat et des mœurs, et propose une nouvelle manière “scientifique” d’étudier les sociétés.​ &lt;/p&gt; &lt;p&gt; Il est l’un des &lt;a href="https://expositions.bnf.fr/montesquieu/un-ecrivain-philosophe.htm" title=" un écrivain philosophe par BNF"&gt;grands théoriciens&lt;/a&gt; du libéralisme classique et de la limitation du pouvoir politique. Il distingue notamment trois grands types de gouvernement : républicain, monarchique et despotique, en fonction du principe qui les fait tenir. Il parle de séparation des pouvoirs : le pouvoir législatif, l’exécutif et le judiciaire doivent être confiés à des organes distincts afin d’empêcher la concentration du pouvoir et de garantir la liberté. &lt;/p&gt; &lt;p&gt; Il critique la monarchie absolue et met en garde contre le despotisme, qu’il considère comme le régime où la peur domine et où les lois se confondent avec le bon plaisir du souverain.​ Il défend la &lt;a href="https://www.youtube.com/watch?v=2Ye6LrpTq9g" title=" le père de la démocratie  par Portrait Historiques"&gt;liberté politique &lt;/a&gt; comme sécurité du citoyen, la tolérance religieuse et une certaine forme d’universalisme, positions qui en font un précurseur et un modèle pour d’autres philosophes des Lumières. &lt;/p&gt; 
- &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="L'esprit de Montesquieu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24812-04.07.2011-ITEMA_23734145-2011C12410E0183-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Montesquieu"    title=" Wikipedia"&gt;MONTESTQUIEU&lt;/a&gt; était un grand philosophe et écrivain français  associé au mouvement des Lumières et connu pour sa théorie de la séparation des pouvoirs. Il s’appelle en réalité Charles‑Louis de Secondat, baron de La Brède et de Montesquieu, et naît  près de Bordeaux dans une famille de noblesse de robe. &lt;/p&gt; &lt;p&gt; Deux œuvres dominent sa postérité : &lt;a href="https://www.youtube.com/watch?v=e72jQdl52bM" title=" Les Lettres persanes, Montesquieu  par Les Bons Profs"&gt;"les Lettres persanes"&lt;/a&gt;, un roman épistolaire satirique où des voyageurs persans observent la société française et critiquent l’absolutisme, les mœurs et l’intolérance religieuse, en utilisant le regard extérieur comme miroir critique et &lt;a href="https://www.youtube.com/watch?v=IBc46RLZxe4" title=" L'ESPRIT DES LOIS en 8 minutes ! par Culture Philo"&gt;"De l’esprit des lois"&lt;/a&gt;, un vaste traité de science politique et sociale qui analyse les types de gouvernement, le rôle des lois, l’influence du climat et des mœurs, et propose une nouvelle manière “scientifique” d’étudier les sociétés.​ &lt;/p&gt; &lt;p&gt; Il est l’un des &lt;a href="https://expositions.bnf.fr/montesquieu/un-ecrivain-philosophe.htm" title=" un écrivain philosophe par BNF"&gt;grands théoriciens&lt;/a&gt; du libéralisme classique et de la limitation du pouvoir politique. Il distingue notamment trois grands types de gouvernement : républicain, monarchique et despotique, en fonction du principe qui les fait tenir. Il parle de séparation des pouvoirs : le pouvoir législatif, l’exécutif et le judiciaire doivent être confiés à des organes distincts afin d’empêcher la concentration du pouvoir et de garantir la liberté. &lt;/p&gt; &lt;p&gt; Il critique la monarchie absolue et met en garde contre le despotisme, qu’il considère comme le régime où la peur domine et où les lois se confondent avec le bon plaisir du souverain.​ Il défend la &lt;a href="https://www.youtube.com/watch?v=2Ye6LrpTq9g" title=" le père de la démocratie  par Portrait Historiques"&gt;liberté politique &lt;/a&gt; comme sécurité du citoyen, la tolérance religieuse et une certaine forme d’universalisme, positions qui en font un précurseur et un modèle pour d’autres philosophes des Lumières. &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="L'esprit de Montesquieu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24812-04.07.2011-ITEMA_23734145-2011C12410E0183-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F52" s="47" t="inlineStr">
@@ -4376,9 +4356,7 @@
       </c>
       <c r="E56" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)"    title=" Wikipedia"&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href="https://www.youtube.com/watch?v=kbpEAw2gl40" title=" David Hartley par Crevoisier Philippe"&gt; développement de la psychologie&lt;/a&gt;, en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt; - La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la "substance médullaire" (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt; - La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des "vibratiuncules" (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs "vibratiuncules" respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href="https://www.youtube.com/shorts/BuqpLB9V41c"  title=" David Hartley par timelinephilosopher"&gt;  le fondement des idées et des pensées&lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des "vibratiuncules" de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, "Observations on Man, his Frame, his Duty, and his Expectations", publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt; 
-- L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt; 
-- Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)"    title=" Wikipedia"&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href="https://www.youtube.com/watch?v=kbpEAw2gl40" title=" David Hartley par Crevoisier Philippe"&gt; développement de la psychologie&lt;/a&gt;, en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt;La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la "substance médullaire" (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt;La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des "vibratiuncules" (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs "vibratiuncules" respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href="https://www.youtube.com/shorts/BuqpLB9V41c"  title=" David Hartley par timelinephilosopher"&gt;  le fondement des idées et des pensées&lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des "vibratiuncules" de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, "Observations on Man, his Frame, his Duty, and his Expectations", publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt;L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt;Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F56" s="47" t="inlineStr">
@@ -4444,7 +4422,7 @@
       </c>
       <c r="E57" s="63" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julien_Offray_de_La_Mettrie"    title=" Wikipedia"&gt;Julien Onfray de la METTRIE&lt;/a&gt;  était un philosophe et médecin français des Lumières, connu pour son &lt;a href="https://www.youtube.com/watch?v=ATn23C-jw1M"  title=" Traité du bonheur de la Mettrie par Voyage interieur"&gt; matérialisme radical &lt;/a&gt; et son athéisme provocateur. Médecin militaire, il fut exilé de France après la publication de ses idées controversées, avant de trouver refuge auprès de Frédéric II de Prusse à Potsdam. &lt;/p&gt; &lt;p&gt; Dans L’Homme machine (1747), il affirme que l’être humain est une machine purement matérielle : l’âme n’existe pas comme substance distincte, mais émerge des processus physiques du cerveau et du corps, sans besoin de Dieu ou d’esprit immatériel. Il s’inspire de Descartes, mais pousse le mécanisme jusqu’au bout en rejetant le dualisme corps-âme.  &lt;/p&gt; &lt;p&gt; Ses écrits, comme Histoire naturelle de l’âme (1745), scandalisèrent l’Église et les autorités : ses livres furent brûlés publiquement et il perdit son poste aux Gardes-Françaises. Défenseur d’un hédonisme sensualiste, il prône le  &lt;a href="https://www.youtube.com/watch?v=FH2TDimoh7Q"  title=" La Mettrie ou l’art de jouir par Parole de philosophe"&gt; plaisir comme seul bien moral,&lt;/a&gt;  sans morale transcendante. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés : - Histoire naturelle de l’âme (1745) : Critique du dualisme et fondement matérialiste. - L’Homme machine (1747) : Thèse principale sur l’automatisme humain. - L’Homme plante (1748) : Étend le mécanisme aux végétaux et animaux. &lt;/p&gt; &lt;p&gt; Précurseur du matérialisme moderne et de la philosophie de la vie, il influence Diderot et les Encyclopédistes, mais reste marginalisé pour son radicalisme. Il anticipe des idées sur l’évolution et la cybernétique en voyant l’humain comme un système organisé. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julien_Offray_de_La_Mettrie"    title=" Wikipedia"&gt;Julien Onfray de la METTRIE&lt;/a&gt;  était un philosophe et médecin français des Lumières, connu pour son &lt;a href="https://www.youtube.com/watch?v=ATn23C-jw1M"  title=" Traité du bonheur de la Mettrie par Voyage interieur"&gt; matérialisme radical &lt;/a&gt; et son athéisme provocateur. Médecin militaire, il fut exilé de France après la publication de ses idées controversées, avant de trouver refuge auprès de Frédéric II de Prusse à Potsdam. &lt;/p&gt; &lt;p&gt; Dans L’Homme machine (1747), il affirme que l’être humain est une machine purement matérielle : l’âme n’existe pas comme substance distincte, mais émerge des processus physiques du cerveau et du corps, sans besoin de Dieu ou d’esprit immatériel. Il s’inspire de Descartes, mais pousse le mécanisme jusqu’au bout en rejetant le dualisme corps-âme.  &lt;/p&gt; &lt;p&gt; Ses écrits, comme Histoire naturelle de l’âme (1745), scandalisèrent l’Église et les autorités : ses livres furent brûlés publiquement et il perdit son poste aux Gardes-Françaises. Défenseur d’un hédonisme sensualiste, il prône le  &lt;a href="https://www.youtube.com/watch?v=FH2TDimoh7Q"  title=" La Mettrie ou l’art de jouir par Parole de philosophe"&gt; plaisir comme seul bien moral,&lt;/a&gt;  sans morale transcendante. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés : Histoire naturelle de l’âme (1745) : Critique du dualisme et fondement matérialiste. L’Homme machine (1747) : Thèse principale sur l’automatisme humain. L’Homme plante (1748) : Étend le mécanisme aux végétaux et animaux. &lt;/p&gt; &lt;p&gt; Précurseur du matérialisme moderne et de la philosophie de la vie, il influence Diderot et les Encyclopédistes, mais reste marginalisé pour son radicalisme. Il anticipe des idées sur l’évolution et la cybernétique en voyant l’humain comme un système organisé. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -5253,7 +5231,7 @@
       </c>
       <c r="E69" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Moses_Mendelssohn"   title=" Wikipedia"&gt;Moses MENDELSSOHN&lt;/a&gt;  était un philosophe &lt;a href="https://www.youtube.com/watch?v=AvucqmG4Alk" title="Moses Mendelssohn et l’invention des Juifs allemands par Instituter of Jewish Studies"&gt;juif allemand des Lumières&lt;/a&gt;, né à Dessau et mort à Berlin, souvent considéré comme le "premier Juif allemand moderne" et l’une des grandes figures de  &lt;a href="https://www.youtube.com/watch?v=AaS7z6uRwWc" title="Le mythe de Moïse Mendelssohn par Efraim Palvanov"&gt;la Haskala, &lt;/a&gt; l’Aufklärung juive qui cherche à concilier fidélité au judaïsme et ouverture à la culture et à la philosophie modernes. &lt;/p&gt; &lt;p&gt; Il milite pour l’égalité civile des Juifs, la reconnaissance de leur spécificité au sein d’un État majoritairement chrétien, et la fin des discriminations légales et défend l’idée que les Juifs peuvent être pleinement intégrés comme citoyens allemands sans renoncer à leur religion. Il travaille sur la coexistence entre raison et foi, en soutenant que les vérités fondamentales de la religion sont accessibles à la raison humaine. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : -  "Phédon ou sur l’immortalité de l’âme" paru en 1767 qui  présente, sous forme de dialogues inspirés de Socrate, une défense de l’immortalité de l’âme et contribue à son surnom de "Socrate allemand". &lt; /p&gt; &lt;p&gt;  - "Jérusalem ou pouvoir religieux et judaïsme" en 1783 expose sa théorie de la séparation de l’Église et de l’État et sa vision d’un judaïsme compatible avec la liberté moderne. &lt;/p&gt; &lt;p&gt; - &lt;a href="https://laviedesidees.fr/Mendelssohn-Heures-matinales" title="Le dernier métaphysicien par la vie des idées"&gt;"Morgenstunden"&lt;/a&gt;, recueil de leçons sur l’existence de Dieu, synthétise sa position philosophique dans ses dernières années
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Moses_Mendelssohn"   title=" Wikipedia"&gt;Moses MENDELSSOHN&lt;/a&gt;  était un philosophe &lt;a href="https://www.youtube.com/watch?v=AvucqmG4Alk" title="Moses Mendelssohn et l’invention des Juifs allemands par Instituter of Jewish Studies"&gt;juif allemand des Lumières&lt;/a&gt;, né à Dessau et mort à Berlin, souvent considéré comme le "premier Juif allemand moderne" et l’une des grandes figures de  &lt;a href="https://www.youtube.com/watch?v=AaS7z6uRwWc" title="Le mythe de Moïse Mendelssohn par Efraim Palvanov"&gt;la Haskala, &lt;/a&gt; l’Aufklärung juive qui cherche à concilier fidélité au judaïsme et ouverture à la culture et à la philosophie modernes. &lt;/p&gt; &lt;p&gt; Il milite pour l’égalité civile des Juifs, la reconnaissance de leur spécificité au sein d’un État majoritairement chrétien, et la fin des discriminations légales et défend l’idée que les Juifs peuvent être pleinement intégrés comme citoyens allemands sans renoncer à leur religion. Il travaille sur la coexistence entre raison et foi, en soutenant que les vérités fondamentales de la religion sont accessibles à la raison humaine. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : "Phédon ou sur l’immortalité de l’âme" paru en 1767 qui  présente, sous forme de dialogues inspirés de Socrate, une défense de l’immortalité de l’âme et contribue à son surnom de "Socrate allemand". &lt; /p&gt; &lt;p&gt;"Jérusalem ou pouvoir religieux et judaïsme" en 1783 expose sa théorie de la séparation de l’Église et de l’État et sa vision d’un judaïsme compatible avec la liberté moderne. &lt;/p&gt; &lt;p&gt;&lt;a href="https://laviedesidees.fr/Mendelssohn-Heures-matinales" title="Le dernier métaphysicien par la vie des idées"&gt;"Morgenstunden"&lt;/a&gt;, recueil de leçons sur l’existence de Dieu, synthétise sa position philosophique dans ses dernières années
 . &lt;/p&gt; &lt;p&gt;  Il est l’un des pionniers du judaïsme libéral et un des fondateurs de la modernité juive européenne, en cherchant l’intégration sans assimilation forcée et a  eu une influence durablement la philosophie juive et la pensée allemande, préparant le terrain pour des figures comme Heinrich Heine, Hermann Cohen, Franz Rosenzweig, Walter Benjamin ou Hannah Arendt. &lt;/p&gt; </t>
         </is>
       </c>
@@ -5325,7 +5303,7 @@
       </c>
       <c r="E70" s="63" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Edmund_Burke"   title=" Wikipedia"&gt;Edmund BURKE&lt;/a&gt; était un philosophe et homme politique anglo-irlandais, considéré comme l'un des fondateurs du conservatisme moderne. Il s'opposa farouchement à la Révolution française, défendant l'évolution graduelle des institutions plutôt que les ruptures radicales. Il étudia au Trinity College avant de s'installer à Londres pour exercer le droit et entrer en politique. Député whig à la Chambre des communes de 1766 à 1794, il soutint l'indépendance américaine tout en critiquant les excès fiscaux britanniques. Sa célèbre Réflexions sur la Révolution de France (1790) alerta sur les dangers de la "multitude perverse" et du rejet des traditions. &lt;/p&gt; &lt;p&gt; Il  voyait la société comme un "partenariat entre les vivants, les morts et ceux qui ne sont pas encore nés", valorisant les &lt;a href="https://www.youtube.com/watch?v=az1n7gSaKFE" title="La tradition permet elle le changement  par la chaine de Velours"&gt;préjugés hérités &lt;/a&gt; comme bank de sagesse collective supérieure à la raison individuelle. Dans Recherches philosophiques sur l'origine de nos idées du sublime et du beau (1757), il distingue le sublime (lié à la douleur, à la terreur et à Dieu) du beau (lié au plaisir et à la société), influençant l'esthétique romantique. Il prônait l'amélioration progressive de la nature humaine imparfaite, sans table rase. &lt;/p&gt; &lt;p&gt; Surnommé "conservateur des Lumières", il inspira des penseurs comme Roger Scruton et reste une référence contre les utopies rationalistes. En France, il fut parfois taxé de réactionnaire, mais son libéralisme tempéré et son sens de la responsabilité des élites résonnent encore. &lt;/p&gt;  &lt;audio controls title="Les britaniques ; Burke et ses héritiers par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-10.12.2024-ITEMA_23958056-2024C48904S0345-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Edmund_Burke"   title=" Wikipedia"&gt;Edmund BURKE&lt;/a&gt; était un philosophe et homme politique anglo-irlandais, considéré comme l'un des fondateurs du conservatisme moderne. Il s'opposa farouchement à la Révolution française, défendant l'évolution graduelle des institutions plutôt que les ruptures radicales. Il étudia au Trinity College avant de s'installer à Londres pour exercer le droit et entrer en politique. Député whig à la Chambre des communes de 1766 à 1794, il soutint l'indépendance américaine tout en critiquant les excès fiscaux britanniques. Sa célèbre Réflexions sur la Révolution de France (1790) alerta sur les dangers de la "multitude perverse" et du rejet des traditions. &lt;/p&gt; &lt;p&gt; Il  voyait la société comme un "partenariat entre les vivants, les morts et ceux qui ne sont pas encore nés", valorisant les &lt;a href="https://www.youtube.com/watch?v=az1n7gSaKFE" title="La tradition permet elle le changement  par la chaine de Velours"&gt;préjugés hérités &lt;/a&gt; comme bank de sagesse collective supérieure à la raison individuelle. Dans Recherches philosophiques sur l'origine de nos idées du sublime et du beau (1757), il distingue le sublime (lié à la douleur, à la terreur et à Dieu) du beau (lié au plaisir et à la société), influençant l'esthétique romantique. Il prônait l'amélioration progressive de la nature humaine imparfaite, sans table rase. &lt;/p&gt; &lt;p&gt; Surnommé "conservateur des Lumières", il inspira des penseurs comme Roger Scruton et reste une référence contre les utopies rationalistes. En France, il fut parfois taxé de réactionnaire, mais son libéralisme tempéré et son sens de la responsabilité des élites résonnent encore. &lt;/p&gt;  &lt;audio controls title="Les britaniques ; Burke et ses héritiers par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-10.12.2024-ITEMA_23958056-2024C48904S0345-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
@@ -5391,7 +5369,7 @@
       </c>
       <c r="E71" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing"   title=" Wikipedia"&gt;Gotthold Ephraim LESSING&lt;/a&gt; était un écrivain, dramaturge et philosophe allemand, figure centrale des Lumières allemandes qui défendit la tolérance religieuse, la raison critique et un christianisme épuré de dogmes orthodoxes. Il rejeta l'interprétation littérale de la Bible au profit d'une révélation progressive de l'humanité via la raison, influencé par Spinoza et Leibniz, tout en prônant une harmonie entre foi et savoir. &lt;/p&gt; &lt;p&gt; Fils de pasteur luthérien à Kamenz (Saxe), Lessing étudia la théologie et la médecine avant de se consacrer à la littérature à Berlin et Leipzig. Critique théâtral virulent, il combattit l'imitation des modèles français dans la Hamburgische Dramaturgie (1767-1769), plaidant pour un théâtre national allemand réaliste. Directeur de bibliothèque à Wolfenbüttel, il noua des amitiés avec Mendelssohn et Jacobi, déclenchant la querelle du panthéisme par ses sympathies spinozistes. &lt;/p&gt; &lt;p&gt; Ses Œuvres théâtrales majeures : - Miss Sara Sampson (1755) : Première tragédie bourgeoise allemande, explorant culpabilité et pardon. - Minna von Barnhelm (1767) : Comédie sur la réconciliation post-Sept Ans. - Emilia Galotti (1772) : Drame sur l'honneur et l'hypocrisie sociale. -  &lt;a href="https://www.radiofrance.fr/franceculture/nathan-le-sage-de-gotthold-ephraim-lessing-8205672" title="Nathan le sage de Lessing  par Radio France"&gt;Nathan le Sage (1779) &lt;/a&gt;  : Parabole tolérante où juif, chrétien et musulman incarnent la fraternité humaine via les trois anneaux (foi égale). &lt;/p&gt; &lt;p&gt; Dans L'Éducation du genre humain (1780), il voit l'histoire comme un processus divin d'éducation progressive : la révélation biblique n'est pas figée mais s'affine par la raison, menant à un "christianisme de raison". Laocoon (1766) distingue poésie (temps, action) et peinture (espace, corps). Son "fossé de Lessing" questionne : miracles historiques ne prouvent pas vérités éternelles. Il inspira Herder, Goethe et le romantisme par son relativisme esthétique et moral. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing"   title=" Wikipedia"&gt;Gotthold Ephraim LESSING&lt;/a&gt; était un écrivain, dramaturge et philosophe allemand, figure centrale des Lumières allemandes qui défendit la tolérance religieuse, la raison critique et un christianisme épuré de dogmes orthodoxes. Il rejeta l'interprétation littérale de la Bible au profit d'une révélation progressive de l'humanité via la raison, influencé par Spinoza et Leibniz, tout en prônant une harmonie entre foi et savoir. &lt;/p&gt; &lt;p&gt; Fils de pasteur luthérien à Kamenz (Saxe), Lessing étudia la théologie et la médecine avant de se consacrer à la littérature à Berlin et Leipzig. Critique théâtral virulent, il combattit l'imitation des modèles français dans la Hamburgische Dramaturgie (1767-1769), plaidant pour un théâtre national allemand réaliste. Directeur de bibliothèque à Wolfenbüttel, il noua des amitiés avec Mendelssohn et Jacobi, déclenchant la querelle du panthéisme par ses sympathies spinozistes. &lt;/p&gt; &lt;p&gt; Ses Œuvres théâtrales majeures : Miss Sara Sampson (1755) : Première tragédie bourgeoise allemande, explorant culpabilité et pardon. Minna von Barnhelm (1767) : Comédie sur la réconciliation post-Sept Ans. Emilia Galotti (1772) : Drame sur l'honneur et l'hypocrisie sociale. &lt;a href="https://www.radiofrance.fr/franceculture/nathan-le-sage-de-gotthold-ephraim-lessing-8205672" title="Nathan le sage de Lessing  par Radio France"&gt;Nathan le Sage (1779) &lt;/a&gt;  : Parabole tolérante où juif, chrétien et musulman incarnent la fraternité humaine via les trois anneaux (foi égale). &lt;/p&gt; &lt;p&gt; Dans L'Éducation du genre humain (1780), il voit l'histoire comme un processus divin d'éducation progressive : la révélation biblique n'est pas figée mais s'affine par la raison, menant à un "christianisme de raison". Laocoon (1766) distingue poésie (temps, action) et peinture (espace, corps). Son "fossé de Lessing" questionne : miracles historiques ne prouvent pas vérités éternelles. Il inspira Herder, Goethe et le romantisme par son relativisme esthétique et moral. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -5459,7 +5437,7 @@
       <c r="E72" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donatien_Alphonse_Fran%C3%A7ois_de_Sade" title=" Wikipedia"&gt;Marquis François de SADE&lt;/a&gt; était un écrivain, philosophe Français surtout connu pour ses écrits provocateurs et controversés, qui abordent les thèmes de &lt;a href="https://www.youtube.com/watch?v=PJdCNc-0Ybk" title="Sade – justine ou les malheurs de la vertu par Kosmos"&gt;la sexualité, la violence et la morale&lt;/a&gt;. Il a passé une grande partie de sa vie en prison ou en exil en raison de ses opinions et de ses activités considérées comme immorales et illégales. &lt;/p&gt; &lt;p&gt;  Bien qu'il soit souvent associé à la pornographie et à la violence, il a exercé une influence importante sur la philosophie et la culture. Il a été considéré comme un précurseur du mouvement surréaliste, de &lt;a href="https://www.youtube.com/watch?v=KEh0vf7HCoI&amp;ab_channel=RayonPolar"   title="Donatien Alphonse François de Sade par RayonPolar"&gt; nombreux cinéastes&lt;/a&gt; tels que Brunel, Debordque, Bergma ont étaient inspirés et son travail qui a aussi été étudié par des philosophes tels que Michel Foucault et Gilles Deleuze. &lt;/p&gt; &lt;p&gt;  Sa pensée libertaire et sa critique de la société et de la religion ont également inspiré de nombreux mouvements politiques et sociaux.&lt;/p&gt; &lt;p&gt; 
-Son œuvre la plus célèbre, &lt;a href="https://fr.wikisource.org/wiki/Les_120_Journ%C3%A9es_de_Sodome"  title="Les 120 jours de Sodome par source Wikisource"&gt; "Les 120 Journées de Sodome" &lt;/a&gt; (également connue sous le nom de "La Philosophie dans le Boudoir"), est considérée comme l'un des premiers exemples de littérature érotique. Ce livre est aujourd'hui considéré comme extrêmement choquant en raison de sa description explicite de pratiques sexuelles déviantes et violentes. &lt;/p&gt; &lt;p&gt;  Son travail &lt;a href="https://www.youtube.com/watch?v=Qwfqw51JaGY" title=""L'apologie du mal" par le Précepteur"&gt;provocateur et choquant &lt;/a&gt;  a soulevé des questions importantes sur la sexualité, la morale et la liberté individuelle, qui continuent d'être pertinents aujourd'hui et on utilise le terme de 'sadique' aujourd'hui dans la langue Française.&lt;/p&gt; &lt;audio controls title="La vie en infamie du marquis de Sade par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-14.01.2019-ITEMA_21950194-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+Son œuvre la plus célèbre, &lt;a href="https://fr.wikisource.org/wiki/Les_120_Journ%C3%A9es_de_Sodome"  title="Les 120 jours de Sodome par source Wikisource"&gt; "Les 120 Journées de Sodome" &lt;/a&gt; (également connue sous le nom de "La Philosophie dans le Boudoir"), est considérée comme l'un des premiers exemples de littérature érotique. Ce livre est aujourd'hui considéré comme extrêmement choquant en raison de sa description explicite de pratiques sexuelles déviantes et violentes. &lt;/p&gt; &lt;p&gt;  Son travail &lt;a href="https://www.youtube.com/watch?v=Qwfqw51JaGY" title=""L'apologie du mal" par le Précepteur"&gt;provocateur et choquant &lt;/a&gt;  a soulevé des questions importantes sur la sexualité, la morale et la liberté individuelle, qui continuent d'être pertinents aujourd'hui et on utilise le terme de 'sadique' aujourd'hui dans la langue Française.&lt;/p&gt; &lt;audio controls title="La vie en infamie du marquis de Sade par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-14.01.2019-ITEMA_21950194-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F72" s="47" t="inlineStr">
@@ -5725,7 +5703,7 @@
       </c>
       <c r="E76" s="63" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi"  title=" Wikipedia"&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href="https://fr.wikipedia.org/wiki/Nihilisme"  title="Nihilisme par Wikipedia"&gt; nihilisme &lt;/a&gt; et au &lt;a href="https://fr.wikipedia.org/wiki/Panth%C3%A9isme"  title="Panthéisme par Wikipedia"&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse "querelle du panthéisme" en révélant que Lessing s'était  &lt;a href="https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321"  title="Jacobi et Spinoza par Persée"&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu. &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du "rien ne sort du néant") de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un "saut de la foi" hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. - David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. - Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi"  title=" Wikipedia"&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href="https://fr.wikipedia.org/wiki/Nihilisme"  title="Nihilisme par Wikipedia"&gt; nihilisme &lt;/a&gt; et au &lt;a href="https://fr.wikipedia.org/wiki/Panth%C3%A9isme"  title="Panthéisme par Wikipedia"&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse "querelle du panthéisme" en révélant que Lessing s'était  &lt;a href="https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321"  title="Jacobi et Spinoza par Persée"&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu. &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du "rien ne sort du néant") de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un "saut de la foi" hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -6063,7 +6041,7 @@
       </c>
       <c r="E81" s="58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joseph_de_Maistre"  title=" Wikipedia"&gt;Joseph de MAISTRE&lt;/a&gt; était un philosophe, écrivain et diplomate savoyard, figure majeure de la contre-révolution et critique virulent des Lumières et de la Révolution française. Considéré comme un père de la pensée conservatrice moderne, il défend une vision organique de la société, hiérarchique et divinement ordonnée, où l'autorité monarchique et religieuse prime sur les idées contractualistes et individualistes. &lt;/p&gt; &lt;p&gt;  Pour lui, la Révolution française est un &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1989_num_1_2_1393" title="Sacré et sacrifice dans la pensée de Joseph de Maistre par Persée"&gt;châtiment providentiel &lt;/a&gt; des excès des philosophes des Lumières, punissant l'athéisme et le rationalisme par la Terreur. Les sociétés ne naissent pas d'un contrat rationnel (comme chez Rousseau), mais d'une autorité divine imposée d'en haut; l'individu abstrait n'existe pas, il est façonné par la tradition et l'État.  Il prône une monarchie absolue et l'autorité suprême du Pape pour unifier l'Europe spirituellement et temporellement. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures sont : - "Considérations sur la France" paru en 1797 : Interprétation providentialiste de la Révolution comme mission divine de la France. - "Essai sur le principe générateur des constitutions" paru en 1809 :  &lt;a href="https://www.youtube.com/watch?v=oPEzOiEdrNE"  title=" L'oecuménisme de Joseph de Maistre par BAGLIS TV"&gt;Les constitutions &lt;/a&gt; viennent de Dieu, non de la raison humaine et - "Soirées de Saint-Pétersbourg"  en1821, posthume : Théodicée justifiant le mal (guerre, sacrifice) comme partie du plan divin. &lt;/p&gt; &lt;p&gt; Il a eu une influence durablement le conservatisme, le romantisme contre-révolutionnaire et des penseurs comme Donoso Cortés, tout en étant critiqué pour son apologie de la violence. Sa pensée hiérarchique et anti-individualiste reste débattue face aux idéaux démocratiques modernes. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Troisième penseur, Joseph de Maistre. par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-26.10.2011-ITEMA_20317797-2011C12410S0299-NET_F022382B-0B64-4C5C-B335-284B201C884D_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joseph_de_Maistre"  title=" Wikipedia"&gt;Joseph de MAISTRE&lt;/a&gt; était un philosophe, écrivain et diplomate savoyard, figure majeure de la contre-révolution et critique virulent des Lumières et de la Révolution française. Considéré comme un père de la pensée conservatrice moderne, il défend une vision organique de la société, hiérarchique et divinement ordonnée, où l'autorité monarchique et religieuse prime sur les idées contractualistes et individualistes. &lt;/p&gt; &lt;p&gt;  Pour lui, la Révolution française est un &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1989_num_1_2_1393" title="Sacré et sacrifice dans la pensée de Joseph de Maistre par Persée"&gt;châtiment providentiel &lt;/a&gt; des excès des philosophes des Lumières, punissant l'athéisme et le rationalisme par la Terreur. Les sociétés ne naissent pas d'un contrat rationnel (comme chez Rousseau), mais d'une autorité divine imposée d'en haut; l'individu abstrait n'existe pas, il est façonné par la tradition et l'État.  Il prône une monarchie absolue et l'autorité suprême du Pape pour unifier l'Europe spirituellement et temporellement. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures sont : "Considérations sur la France" paru en 1797 : Interprétation providentialiste de la Révolution comme mission divine de la France. "Essai sur le principe générateur des constitutions" paru en 1809 :  &lt;a href="https://www.youtube.com/watch?v=oPEzOiEdrNE"  title=" L'oecuménisme de Joseph de Maistre par BAGLIS TV"&gt;Les constitutions &lt;/a&gt; viennent de Dieu, non de la raison humaine et "Soirées de Saint-Pétersbourg"  en1821, posthume : Théodicée justifiant le mal (guerre, sacrifice) comme partie du plan divin. &lt;/p&gt; &lt;p&gt; Il a eu une influence durablement le conservatisme, le romantisme contre-révolutionnaire et des penseurs comme Donoso Cortés, tout en étant critiqué pour son apologie de la violence. Sa pensée hiérarchique et anti-individualiste reste débattue face aux idéaux démocratiques modernes. &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Troisième penseur, Joseph de Maistre. par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-26.10.2011-ITEMA_20317797-2011C12410S0299-NET_F022382B-0B64-4C5C-B335-284B201C884D_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F81" s="47" t="inlineStr">
@@ -6129,7 +6107,7 @@
       </c>
       <c r="E82" s="63" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_de_Bonald"  title=" Wikipedia"&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href="https://fr.wikipedia.org/wiki/Tradition_primordiale"  title=" Tradition Primordiale de Maistre par Wikipedia "&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. - Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. - Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href="https://www.youtube.com/watch?v=WMB9kethTWIe"  title=" Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations "&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href="https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral"  title=" Maurrassisme par Wikipedia "&gt; maurrassisme, &lt;a&gt; voyant la France comme "nation-pilote" pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant. &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_de_Bonald"  title=" Wikipedia"&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href="https://fr.wikipedia.org/wiki/Tradition_primordiale"  title=" Tradition Primordiale de Maistre par Wikipedia "&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href="https://www.youtube.com/watch?v=WMB9kethTWIe"  title=" Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations "&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href="https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral"  title=" Maurrassisme par Wikipedia "&gt; maurrassisme, &lt;a&gt; voyant la France comme "nation-pilote" pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant. &lt;/p&gt;
 //</t>
         </is>
       </c>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E7" s="53" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Cranston" title=" Wikipedia"&gt;David CRANSTON&lt;/a&gt; est un logicien et philosophe écossais, formé à Paris au sein du milieu intellectuel bouillonnant du tournant du XVIe siècle. Élève et proche collaborateur de &lt;a href="https://fr.wikipedia.org/wiki/John_Mair"  title=" Wikipedia"&gt;Jean Major&lt;/a&gt;, il s'inscrit dans le réseau écossais qui gravite autour du &lt;a href="https://fr.wikipedia.org/wiki/Coll%C3%A8ge_de_Montaigu" title=" Wikipedia"&gt;Collège de Montaigu&lt;/a&gt; et des institutions universitaires parisiennes. Mort prématurément à moins de quarante ans, il laisse une œuvre brève mais techniquement remarquable, qui témoigne de la vitalité d'une scolastique logique tardive au moment où l'humanisme renaissant commence à en contester la légitimité.&lt;/p&gt; &lt;p&gt;L'œuvre de Cranston se concentre sur la logique et les questions de langage, dans la tradition de la logique terministe héritée d'Ockham et de Buridan. Son traité principal porte sur les &lt;em&gt;suppositiones&lt;/em&gt; — la théorie médiévale de la référence des termes dans le contexte des propositions — et sur les conséquences logiques, raffinant des outils conceptuels élaborés depuis le XIIIe siècle. Il s'intéresse également aux &lt;a href="https://fr.wikipedia.org/wiki/Sophisme" style="color:#6A142A" title=" Wikipedia"&gt;sophismes&lt;/a&gt; et aux &lt;em&gt;insolubilia&lt;/em&gt; — paradoxes logiques comme le Menteur — terrain d'exercice privilégié de la logique universitaire de son temps.&lt;/p&gt; &lt;p&gt;Cranston appartient au courant du &lt;a href="https://fr.wikipedia.org/wiki/Nominalisme" style="color:#6A142A" title=" Wikipedia"&gt;nominalisme&lt;/a&gt; parisien, héritier de la &lt;em&gt;via moderna&lt;/em&gt; ockhamiste, qu'il pratique avec une technicité remarquable. Son œuvre s'inscrit dans le dialogue tendu avec l'&lt;a href="https://fr.wikipedia.org/wiki/Humanisme_de_la_Renaissance" style="color:#6A142A" title=" Wikipedia"&gt;humanisme de la Renaissance&lt;/a&gt;, qui reproche à la scolastique son jargon barbare, tandis que des logiciens comme Cranston défendent la fécondité d'une analyse précise du langage que les humanistes abandonnent pour le beau style.&lt;/p&gt; &lt;p&gt;La postérité de Cranston est limitée par sa mort précoce et par le déclin général de la logique scolastique face à la marée montante de l'humanisme et de la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9forme_protestante" style="color:#6A142A" title=" Wikipedia"&gt;Réforme protestante&lt;/a&gt;. Néanmoins, ses travaux s'inscrivent dans une tradition qui, via Port-Royal et Leibniz, contribue à l'émergence de la &lt;a href="https://fr.wikipedia.org/wiki/Logique_formelle" style="color:#6A142A" title=" Wikipedia"&gt;logique formelle&lt;/a&gt; moderne. Les historiens de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" style="color:#6A142A" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; voient dans la logique terministe médiévale, dont Cranston est l'un des derniers représentants parisiens, une anticipation remarquable des problématiques de référence et de vérité qui dominent la philosophie du langage contemporaine.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/David_Cranston_(philosopher)" title=" Wikipedia"&gt;David CRANSTON&lt;/a&gt; est un logicien et philosophe écossais, formé à Paris au sein du milieu intellectuel bouillonnant du tournant du XVIe siècle. Élève et proche collaborateur de &lt;a href="https://fr.wikipedia.org/wiki/John_Mair"  title=" Wikipedia"&gt;Jean Major&lt;/a&gt;, il s'inscrit dans le réseau écossais qui gravite autour du &lt;a href="https://fr.wikipedia.org/wiki/Coll%C3%A8ge_de_Montaigu" title=" Wikipedia"&gt;Collège de Montaigu&lt;/a&gt; et des institutions universitaires parisiennes. Mort prématurément à moins de quarante ans, il laisse une œuvre brève mais techniquement remarquable, qui témoigne de la vitalité d'une scolastique logique tardive au moment où l'humanisme renaissant commence à en contester la légitimité.&lt;/p&gt; &lt;p&gt;L'œuvre de Cranston se concentre sur la logique et les questions de langage, dans la tradition de la logique terministe héritée d'Ockham et de Buridan. Son traité principal porte sur les &lt;em&gt;suppositiones&lt;/em&gt; — la théorie médiévale de la référence des termes dans le contexte des propositions — et sur les conséquences logiques, raffinant des outils conceptuels élaborés depuis le XIIIe siècle. Il s'intéresse également aux &lt;a href="https://fr.wikipedia.org/wiki/Sophisme" style="color:#6A142A" title=" Wikipedia"&gt;sophismes&lt;/a&gt; et aux &lt;em&gt;insolubilia&lt;/em&gt; — paradoxes logiques comme le Menteur — terrain d'exercice privilégié de la logique universitaire de son temps.&lt;/p&gt; &lt;p&gt;Cranston appartient au courant du &lt;a href="https://fr.wikipedia.org/wiki/Nominalisme" style="color:#6A142A" title=" Wikipedia"&gt;nominalisme&lt;/a&gt; parisien, héritier de la &lt;em&gt;via moderna&lt;/em&gt; ockhamiste, qu'il pratique avec une technicité remarquable. Son œuvre s'inscrit dans le dialogue tendu avec l'&lt;a href="https://fr.wikipedia.org/wiki/Humanisme_de_la_Renaissance" style="color:#6A142A" title=" Wikipedia"&gt;humanisme de la Renaissance&lt;/a&gt;, qui reproche à la scolastique son jargon barbare, tandis que des logiciens comme Cranston défendent la fécondité d'une analyse précise du langage que les humanistes abandonnent pour le beau style.&lt;/p&gt; &lt;p&gt;La postérité de Cranston est limitée par sa mort précoce et par le déclin général de la logique scolastique face à la marée montante de l'humanisme et de la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9forme_protestante" style="color:#6A142A" title=" Wikipedia"&gt;Réforme protestante&lt;/a&gt;. Néanmoins, ses travaux s'inscrivent dans une tradition qui, via Port-Royal et Leibniz, contribue à l'émergence de la &lt;a href="https://fr.wikipedia.org/wiki/Logique_formelle" style="color:#6A142A" title=" Wikipedia"&gt;logique formelle&lt;/a&gt; moderne. Les historiens de la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_analytique" style="color:#6A142A" title=" Wikipedia"&gt;philosophie analytique&lt;/a&gt; voient dans la logique terministe médiévale, dont Cranston est l'un des derniers représentants parisiens, une anticipation remarquable des problématiques de référence et de vérité qui dominent la philosophie du langage contemporaine.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F7" s="51" t="n"/>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="E63" s="63" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Joachim_Spalding" title=" Wikipedia"&gt;Johann Joachim SPALDING&lt;/a&gt; était un théologien protestant allemand, souvent considéré comme l’un des grands représentants des Lumières religieuses en Allemagne. Sa pensée cherche à concilier foi chrétienne, raison et morale, dans un esprit de réforme modérée plutôt que de rupture. &lt;/p&gt; &lt;p&gt; Dans son œuvre la plus célèbre, Die Bestimmung des Menschen (1748), il réfléchit au sens de la vie humaine. Pour lui, l’être humain n’est pas fait seulement pour satisfaire ses besoins matériels, mais pour se développer intérieurement, moralement et spirituellement. &lt;/p&gt; &lt;p&gt; Sa philosophie religieuse défend l’idée d’une religion naturelle compatible avec la Révélation. Il refuse le dogmatisme rigide et l’orthodoxie autoritaire, et insiste sur une foi plus vivante, fondée sur la conscience, le bon sens et l’expérience intérieure. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande importance &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1979_num_92_88_18346"  title="problèmes de la théologie allemande par persée"&gt;au sentiment religieux. &lt;/a&gt;  Dans son ouvrage de 1789, il montre que les émotions et la vie intérieure ont une vraie place dans le christianisme, sans que cela supprime l’exigence morale. Il représente une forme de christianisme éclairé : une religion raisonnable, morale et personnelle, qui veut rendre la foi plus humaine et plus intelligible. Son influence a compté dans la théologie protestante allemande, notamment dans le courant appelé néologie. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Joachim_Spalding" title=" Wikipedia"&gt;Johann Joachim SPALDING&lt;/a&gt; était un théologien protestant allemand, souvent considéré comme l’un des grands représentants des Lumières religieuses en Allemagne. Sa pensée cherche à concilier foi chrétienne, raison et morale, dans un esprit de réforme modérée plutôt que de rupture. Né en Poméranie suédoise, fils de pasteur, il traduit Shaftesbury, puis devient en 1764 prévôt de l’église Saint-Nicolas de Berlin. &lt;/p&gt; &lt;p&gt; Dans son œuvre la plus célèbre, &lt;em&gt;Die Bestimmung des Menschen&lt;/em&gt; (« La Destination de l’homme », 1748), il réfléchit au sens de la vie humaine. Pour lui, l’être humain n’est pas fait seulement pour satisfaire ses besoins matériels, mais pour se développer intérieurement, moralement et spirituellement. &lt;/p&gt; &lt;p&gt; Sa philosophie religieuse défend l’idée d’une religion naturelle compatible avec la Révélation. Il refuse le dogmatisme rigide et l’orthodoxie autoritaire, et insiste sur une foi plus vivante, fondée sur la conscience, le bon sens et l’expérience intérieure. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande importance &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1979_num_92_88_18346"  title="problèmes de la théologie allemande par persée"&gt;au sentiment religieux. &lt;/a&gt;  Dans ses &lt;em&gt;Pensées sur la valeur des sentiments dans le christianisme&lt;/em&gt; (1761), il montre que les émotions et la vie intérieure ont une vraie place dans le christianisme, sans que cela supprime l’exigence morale. Il représente une forme de christianisme éclairé : une religion raisonnable, morale et personnelle, qui veut rendre la foi plus humaine et plus intelligible. Son influence a compté dans la théologie protestante allemande, notamment dans le courant appelé néologie. En 1788, il renonce à prêcher après l’édit de Wöllner, qui impose aux pasteurs l’orthodoxie luthérienne. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="E66" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0f"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie,il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie,il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F66" s="47" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="E82" s="63" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_de_Bonald"  title=" Wikipedia"&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href="https://fr.wikipedia.org/wiki/Tradition_primordiale"  title=" Tradition Primordiale de Maistre par Wikipedia "&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href="https://www.youtube.com/watch?v=WMB9kethTWIe"  title=" Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations "&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href="https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral"  title=" Maurrassisme par Wikipedia "&gt; maurrassisme, &lt;a&gt; voyant la France comme "nation-pilote" pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant. &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_de_Bonald"  title=" Wikipedia"&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href="https://fr.wikipedia.org/wiki/Tradition_primordiale"  title=" Tradition Primordiale de Maistre par Wikipedia "&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href="https://www.youtube.com/watch?v=WMB9kethTWI"  title=" Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations "&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href="https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral"  title=" Maurrassisme par Wikipedia "&gt; maurrassisme, &lt;a&gt; voyant la France comme "nation-pilote" pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant. &lt;/p&gt;
 //</t>
         </is>
       </c>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -2255,7 +2255,7 @@
       </c>
       <c r="E25" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jakob_B%C3%B6hme" title=" Wikipedia"&gt;Jacob BÖEHME&lt;/a&gt; était un philosophe mystique allemand  surnommé le  &lt;a href="https://www.youtube.com/watch?v=MZA137IGPB0&amp;t=761s" style="color:#88A1E9" title=" Jacob Boehme par Carmel de Saint-Elie"&gt; "Philosophus Teutonicus" &lt;/a&gt; et simple cordonnier sans éducation formelle. Pourtant, il a développé une pensée théosophique et philosophique d'une profondeur et d'une complexité   &lt;a href="https://livres-mystiques.com/partieTEXTES/Besson/Articles/boehm.html"  title="  Jacob BOEHME par Livres mystiques"&gt; remarquables&lt;/a&gt;, qu'il disait avoir reçue par des illuminations divines.&lt;/p&gt; &lt;p&gt;  L'une de ses idées les plus connues est celle de  &lt;a href="https://www.youtube.com/watch?v=krUTxK9Adks" title="  L’Ungrund, le sans-fond de Jacob Böhme par BAGLIS TV"&gt;  l'Ungrund&lt;/a&gt;, le "sans-fond"  où Dieu n'est pas un être statique, mais une réalité dynamique, insondable, d'où émergent les oppositions et la création. Cette dialectique entre le "oui" et le "non", la lumière et l'obscurité, le bien et le mal, est centrale à sa pensée. &lt;/p&gt; &lt;p&gt;  Il  s'est penché sur l'épineux problème de l'existence du mal dans un monde créé par un Dieu bon. Contrairement à d'autres théologiens qui le réduisaient à une simple absence du bien, il voyait le mal comme une composante nécessaire du processus divin de manifestation et de la liberté humaine. &lt;/p&gt; &lt;p&gt;  Parmi ses œuvres les plus importantes, on peut citer  &lt;a href="https://www.youtube.com/watch?v=hNRrhozhNSE"  title="  Le royaume Angelique par Dominique Debray"&gt; "L'Aurore naissante"&lt;/a&gt;, "Des trois principes de l'essence divine", "De la signature des choses"  et "De l'élection de la grâce" mais sa pensée non conventionnelle lui a valu d'être en butte aux critiques et aux persécutions de l'orthodoxie luthérienne de son temps, le forçant parfois à cesser d'écrire pendant un certain temps.&lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jakob_B%C3%B6hme" title=" Wikipedia"&gt;Jacob BOEHME&lt;/a&gt; était un philosophe mystique allemand  surnommé le  &lt;a href="https://www.youtube.com/watch?v=MZA137IGPB0&amp;t=761s" style="color:#88A1E9" title=" Jacob Boehme par Carmel de Saint-Elie"&gt; "Philosophus Teutonicus" &lt;/a&gt; et simple cordonnier sans éducation formelle. Pourtant, il a développé une pensée théosophique et philosophique d'une profondeur et d'une complexité   &lt;a href="https://livres-mystiques.com/partieTEXTES/Besson/Articles/boehm.html"  title="  Jacob BOEHME par Livres mystiques"&gt; remarquables&lt;/a&gt;, qu'il disait avoir reçue par des illuminations divines.&lt;/p&gt; &lt;p&gt;  L'une de ses idées les plus connues est celle de  &lt;a href="https://www.youtube.com/watch?v=krUTxK9Adks" title="  L’Ungrund, le sans-fond de Jacob Böhme par BAGLIS TV"&gt;  l'Ungrund&lt;/a&gt;, le "sans-fond"  où Dieu n'est pas un être statique, mais une réalité dynamique, insondable, d'où émergent les oppositions et la création. Cette dialectique entre le "oui" et le "non", la lumière et l'obscurité, le bien et le mal, est centrale à sa pensée. &lt;/p&gt; &lt;p&gt;  Il  s'est penché sur l'épineux problème de l'existence du mal dans un monde créé par un Dieu bon. Contrairement à d'autres théologiens qui le réduisaient à une simple absence du bien, il voyait le mal comme une composante nécessaire du processus divin de manifestation et de la liberté humaine. &lt;/p&gt; &lt;p&gt;  Parmi ses œuvres les plus importantes, on peut citer  &lt;a href="https://www.youtube.com/watch?v=hNRrhozhNSE"  title="  Le royaume Angelique par Dominique Debray"&gt; "L'Aurore naissante"&lt;/a&gt;, "Des trois principes de l'essence divine", "De la signature des choses"  et "De l'élection de la grâce" mais sa pensée non conventionnelle lui a valu d'être en butte aux critiques et aux persécutions de l'orthodoxie luthérienne de son temps, le forçant parfois à cesser d'écrire pendant un certain temps. Après &lt;em&gt;L’Aurore naissante&lt;/em&gt; (1612), le pasteur de Görlitz, Gregor Richter, le fait condamner au silence, et il ne reprend la plume qu’en 1619. Sa pensée a marqué Louis-Claude de Saint-Martin, qui le traduit en français, puis Schelling et Hegel, qui voyait en lui « le premier philosophe allemand ».&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F25" s="47" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -2660,7 +2660,7 @@
       </c>
       <c r="E31" s="60" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Comenius"  title=" Wikipedia"&gt;COMENIUS&lt;/a&gt;   de son nom tchèque Jan Amos Komenský, était un philosophe, théologien et pédagogue tchèque, considéré comme le père de la pédagogie moderne. Évêque des Frères moraves, il fuit les persécutions religieuses et erra en Europe, promouvant une éducation universelle &lt;a href="https://www.youtube.com/watch?v=oGscXWKpLAA"  title="comment donner accès à tous les savoirs par Benoit Urgelli"&gt;accessible à tous, &lt;/a&gt; y compris aux filles et aux pauvres. &lt;/p&gt; &lt;p&gt; Orphelin jeune, il étudie à l’université de Heidelberg et devient enseignant dans les écoles moraves. Exilé après la bataille de la Montagne Blanche (1620), il enseigne à Lissa, Amsterdam et ailleurs, influencé par Alsted dont il fut l’élève. Il meurt à Naarden aux Pays-Bas, rêvant d’une restauration de son pays. &lt;/p&gt; &lt;p&gt; Il  prône une "pansophie" : une sagesse universelle enseignant tout à tous via la nature, la raison et la révélation divine. Il rejette les châtiments corporels, favorise l’apprentissage naturel, ludique et progressif (du sensoriel à l’abstrait), avec &lt;a href="https://www.youtube.com/watch?v=CMFh0seMZUg"  title="The dramatic story on education par Czech the History"&gt;des écoles pour tous &lt;/a&gt; les âges et sexes. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : Didactica Magna (1657) : Traité sur l’art  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1969_num_49_1_3943"  title="Jean Amos COMENIUS par Persée"&gt; d’enseigner universellement, &lt;/a&gt; sans violence. Orbis Sensualium Pictus (1658) : Premier manuel illustré bilingue pour enfants, associant mots et images. De Rerum Humanarum Emendatione : Consultation catholique pour une réforme mondiale du savoir et de la paix. Ses idées inspirèrent l’éducation européenne et l’UNESCO le nomme "Père de l’éducation". &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Comenius"  title=" Wikipedia"&gt;COMENIUS&lt;/a&gt;   de son nom tchèque Jan Amos Komenský, était un philosophe, théologien et pédagogue tchèque, considéré comme le père de la pédagogie moderne. Évêque des Frères moraves, il fuit les persécutions religieuses et erra en Europe, promouvant une éducation universelle &lt;a href="https://www.youtube.com/watch?v=oGscXWKpLAA"  title="comment donner accès à tous les savoirs par Benoit Urgelli"&gt;accessible à tous, &lt;/a&gt; y compris aux filles et aux pauvres. &lt;/p&gt; &lt;p&gt; Orphelin jeune, il étudie à Herborn, puis à l’université de Heidelberg et devient enseignant dans les écoles moraves. Exilé après la bataille de la Montagne Blanche (1620), il enseigne à Lissa, Amsterdam et ailleurs, influencé par Alsted dont il fut l’élève. Il meurt à Naarden aux Pays-Bas, rêvant d’une restauration de son pays. Sa &lt;em&gt;Porte des langues ouverte&lt;/em&gt; (1631), méthode qui enseigne le latin à partir des choses, est traduite dans de nombreuses langues et le rend célèbre dans toute l’Europe ; il est appelé en Angleterre, en Suède et en Transylvanie pour réformer les écoles. &lt;/p&gt; &lt;p&gt; Il  prône une "pansophie" : une sagesse universelle enseignant tout à tous via la nature, la raison et la révélation divine. Il rejette les châtiments corporels, favorise l’apprentissage naturel, ludique et progressif (du sensoriel à l’abstrait), avec &lt;a href="https://www.youtube.com/watch?v=CMFh0seMZUg"  title="The dramatic story on education par Czech the History"&gt;des écoles pour tous &lt;/a&gt; les âges et sexes. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : &lt;em&gt;Didactica Magna&lt;/em&gt; (1657) : Traité sur l’art  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1969_num_49_1_3943"  title="Jean Amos COMENIUS par Persée"&gt; d’enseigner universellement, &lt;/a&gt; sans violence. &lt;em&gt;Orbis sensualium pictus&lt;/em&gt; (1658) : Premier manuel illustré bilingue pour enfants, associant mots et images. De Rerum Humanarum Emendatione : Consultation catholique pour une réforme mondiale du savoir et de la paix. Ses idées inspirèrent l’éducation européenne et l’UNESCO le nomme "Père de l’éducation". &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="E66" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie,il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. Né à Kirkcaldy, professeur de philosophie morale à l’université de Glasgow et ami de David Hume, il publie ce livre en 1776. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie, il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. C’est l’objet de sa &lt;em&gt;Théorie des sentiments moraux&lt;/em&gt; (1759) : nous jugeons nos propres actes en imaginant le regard d’un « spectateur impartial ». &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F66" s="47" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E100" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Arthur_Collier" title=" Wikipedia (en)"&gt;Arthur COLLIER&lt;/a&gt; est un pasteur et philosophe anglais. Né en 1680 à Steeple Langford, dans le Wiltshire, dans une famille de pasteurs, il étudie à Oxford et succède à son père comme recteur de la paroisse de Langford Magna, où il passe toute sa vie. Lecteur de Descartes et surtout de Malebranche, il réfléchit dès 1703 à la question de l’existence du monde extérieur.&lt;/p&gt; &lt;p&gt;En 1713, il publie la &lt;em&gt;Clavis Universalis&lt;/em&gt;, « la clé universelle », sous-titrée « nouvelle recherche de la vérité, démonstration de la non-existence ou de l’impossibilité d’un monde extérieur ». Il y soutient, comme &lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley" title=" Wikipedia"&gt;Berkeley&lt;/a&gt; dans ses &lt;em&gt;Principes&lt;/em&gt; de 1710, l’&lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Wikipedia"&gt;immatérialisme&lt;/a&gt; : le monde visible n’existe que dans l’esprit qui le perçoit, et une matière extérieure, indépendante de toute perception, est une idée contradictoire. Il en donne plusieurs preuves : l’idée d’un monde extérieur conduit à dire qu’il est à la fois fini et infini, divisible à l’infini et pourtant composé de parties.&lt;/p&gt; &lt;p&gt;Collier affirme être arrivé à ces conclusions seul, sans avoir lu Berkeley, et les historiens le croient généralement : les deux auteurs partent de Malebranche, mais avec des arguments différents. Son livre passe presque inaperçu de son vivant. Il meurt en 1732. Redécouvert au XVIIIe siècle par Thomas Reid, puis réédité au XIXe siècle, il est aujourd’hui considéré comme le second fondateur de l’immatérialisme.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Arthur_Collier" title=" Wikipedia (en)"&gt;Arthur COLLIER&lt;/a&gt; est un pasteur et philosophe anglais. Né en 1680 à Steeple Langford, dans le Wiltshire, dans une famille de pasteurs, il étudie à Oxford et succède à son père comme recteur de la paroisse de Langford Magna, où il passe toute sa vie. Lecteur de Descartes et surtout de Malebranche, il réfléchit dès 1703 à la question de l’existence du monde extérieur.&lt;/p&gt; &lt;p&gt;En 1713, il publie la &lt;em&gt;Clavis Universalis&lt;/em&gt;, « la clé universelle », sous-titrée « nouvelle recherche de la vérité, démonstration de la non-existence ou de l’impossibilité d’un monde extérieur ». Il y soutient, comme &lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley" title=" Wikipedia"&gt;Berkeley&lt;/a&gt; dans ses &lt;em&gt;Principes&lt;/em&gt; de 1710, l’&lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Wikipedia"&gt;immatérialisme&lt;/a&gt; : le monde visible n’existe que dans l’esprit qui le perçoit, et une matière extérieure, indépendante de toute perception, est une idée contradictoire. Il en donne plusieurs preuves : l’idée d’un monde extérieur conduit à dire qu’il est à la fois fini et infini, divisible à l’infini et pourtant composé de parties.&lt;/p&gt; &lt;p&gt;Collier affirme être arrivé à ces conclusions seul, sans avoir lu Berkeley, et les historiens le croient généralement : les deux auteurs partent de Malebranche, mais avec des arguments différents. Son livre passe presque inaperçu de son vivant. Il publie encore deux essais de théologie, &lt;em&gt;A Specimen of True Philosophy&lt;/em&gt; (1730) et &lt;em&gt;Logology&lt;/em&gt; (1732), consacré au Verbe divin. Il meurt en 1732. Redécouvert au XVIIIe siècle par Thomas Reid, puis réédité au XIXe siècle, il est aujourd’hui considéré comme le second fondateur de l’immatérialisme.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -4152,7 +4152,7 @@
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Voltaire"   title=" Wikipedia"&gt; VOLTAIRE&lt;/a&gt;, de son vrai nom François-Marie Arouet, est un philosophe de l'époque des  &lt;a href="https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;t=380s&amp;ab_channel=LePr%C3%A9cepteur"  title=" La philosophie des lumières par le Précepteur "&gt;Lumières&lt;/a&gt; (ou Illuministe) en France. Il était aussi écrivain, poète, dramaturge et philosophe. &lt;/p&gt; &lt;p&gt;
 Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href="https://www.youtube.com/watch?v=XE1Z8jpVJUA" title=" la vie de Voltaire  par Portrait Historiques"&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation. Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;
-Voltaire, qui était &lt;a href="https://www.youtube.com/watch?v=RO_aeh1cBgA&amp;ab_channel=Kurious"   title=" Regard critique sur le déîsme par Kurious "&gt;déiste&lt;/a&gt; s'est opposé aux abus de l'Église catholique et a plaidé en faveur de la tolérance envers les minorités religieuses. Dans son ouvrage &lt;a href="https://www.youtube.com/watch?v=1RlS8GKL7SU"  title=" Voltaire-Tolérence par Culture Philo "&gt;"Traité sur la tolérance"&lt;/a&gt;, (1763) il a condamné les persécutions religieuses et a défendu le principe selon lequel chaque individu devait être libre de pratiquer sa religion sans être inquiété. &lt;/p&gt; &lt;p&gt;
+Voltaire, qui était &lt;a href="https://www.youtube.com/watch?v=RO_aeh1cBgA&amp;ab_channel=Kurious"   title=" Regard critique sur le déîsme par Kurious "&gt;déiste&lt;/a&gt; s'est opposé aux abus de l'Église catholique et a plaidé en faveur de la tolérance envers les minorités religieuses. Dans son ouvrage "Traité sur la tolérance", (1763) il a condamné les persécutions religieuses et a défendu le principe selon lequel chaque individu devait être libre de pratiquer sa religion sans être inquiété. &lt;/p&gt; &lt;p&gt;
 Son ouvrage le plus connu est  &lt;a href="https://www.youtube.com/watch?v=kom2zFvrj5I&amp;ab_channel=T%C3%A9l%C3%A9Crayon"  title=" Candide de Voltaire par TéléCrayon "&gt;"Candide"&lt;/a&gt; (1759), un conte philosophique qui critique les idées optimistes de l'époque et souligne les absurdités et les injustices du monde. &lt;/p&gt; &lt;p&gt;
 La contribution de Voltaire à la philosophie se caractérise par son engagement envers la raison, la liberté et la justice. Il a influencé de nombreux penseurs ultérieurs et a contribué à jeter les bases de la pensée libérale et humaniste qui a marqué les siècles suivants. Sa défense de la liberté d'expression reste une valeur fondamentale de nos sociétés démocratiques aujourd'hui. &lt;/p&gt; &lt;audio controls title="Voltaire et les Lumières par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-13.01.2021-ITEMA_22540842-2021C24632S0013.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -1764,64 +1764,63 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="183.75" customHeight="1" s="39">
-      <c r="A18" s="47" t="n">
-        <v>1533</v>
+    <row r="18" ht="130.5" customHeight="1" s="39">
+      <c r="A18" s="47">
+        <v>1530</v>
       </c>
       <c r="B18" s="47" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t xml:space="preserve">1596</t>
         </is>
       </c>
       <c r="C18" s="47" t="inlineStr">
         <is>
-          <t>1533 - 1592</t>
+          <t xml:space="preserve">vers 1530 – 1596</t>
         </is>
       </c>
       <c r="D18" s="48" t="inlineStr">
         <is>
-          <t>Michel de MONTAIGNE</t>
-        </is>
-      </c>
-      <c r="E18" s="60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne"  title=" Wikipedia"&gt; Michel de MONTAIGNE&lt;/a&gt; était un philosophe, écrivain français qui naquit près de Bordeaux, issu d’une famille de la petite noblesse terrienne. Après des études de droit, il exerce des fonctions de magistrat au Parlement de Bordeaux de 1557 à 1571, puis se retire de la vie publique pour se consacrer à la réflexion et à l’écriture. &lt;/p&gt; &lt;p&gt; Son œuvre majeure est &lt;a href="https://www.youtube.com/watch?v=qKXwK8Sj-24&amp;ab_channel=Kosmos" title="Les Essais par Kosmos"&gt; &lt;en&gt; Les Essais&lt;/em&gt;&lt;/a&gt;, publiés en trois livres entre 1580 et 1588, qu’il réécrit et enrichit tout au long de sa vie. Il livre aussi une traduction de la Théologie naturelle de Raymond Sebond (1569) et un Journal de voyage en Italie publié après sa mort, qui montre son goût pour l’observation concrète du monde. Il part de son expérience personnelle (sa santé, ses habitudes, ses lectures, ses voyages) pour &gt;&lt;a href="https://www.youtube.com/watch?v=dIH-Pg1q1pE"  title=" La Philosophie de Montaigne par Paroles de philosophe"&gt;interroger l’homme&lt;/a&gt;, la connaissance, la mort, l’amitié ou l’éducation, en adoptant un ton très libre et décousu. Il met en doute les certitudes de la science ou de la religion de son époque, prône la curiosité, la tolérance et la connaissance de soi, et ouvre la voie au relativisme et au scepticisme moderne. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs du &lt;a href="https://www.youtube.com/watch?v=IcW1ZnRUoGI"  title="Le scepticisme de Montaigne par Le Prisme Humain"&gt;scepticisme moderne&lt;/a&gt;, une approche philosophique qui remet en question la capacité de la raison humaine à atteindre une vérité absolue. Il est également connu pour sa conception de la philosophie comme une pratique personnelle de l'auto-examen et de la réflexion sur soi. Il croyait que la sagesse ne pouvait pas être trouvée dans les livres ou les enseignements des autres, mais devait être découverte à travers l'expérience de la vie et la contemplation de soi. &lt;/p&gt; &lt;p&gt; Il pronait la tolérance religieuse et la coexistence pacifique des différentes religions. Il était aussi un défenseur de la liberté de pensée et d'expression car les individus devaient être libres de penser et de s'exprimer sans crainte de persécution. &lt;/p&gt; &lt;p&gt; Il est important d'accepter notre nature humaine et ne pas essayer de nous conformer à des normes artificielles ou idéalisées. Il a écrit sur &lt;a href="https://preo.u-bourgogne.fr/shc/index.php?id=78" title="La vanité par Ed LETS"&gt;la vanité &lt;/a&gt; de l'homme et la nécessité de reconnaître nos faiblesses et nos imperfections.  &lt;/p&gt; &lt;audio controls title="La fable de l'identité  par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/03/s11/RF_B993FBEB-CED3-4D8B-A48F-2D502E485A89_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F18" s="47" t="inlineStr">
-        <is>
-          <t>it1SGoGdpCw</t>
-        </is>
-      </c>
-      <c r="G18" s="49" t="inlineStr">
-        <is>
-          <t>"Montaigne l’homme qui transforma le doute en sagesse " par Voyages Endormis</t>
-        </is>
-      </c>
-      <c r="H18" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/montaigne-mini.webp</t>
-        </is>
-      </c>
-      <c r="I18" s="45" t="n"/>
+          <t xml:space="preserve">Jean BODIN</t>
+        </is>
+      </c>
+      <c r="E18" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Bodin" title=" Wikipedia"&gt;Jean BODIN&lt;/a&gt; est un juriste, philosophe et économiste français de la Renaissance, le grand théoricien de la &lt;a href="https://fr.wikipedia.org/wiki/Souverainet%C3%A9" title=" Wikipedia"&gt;souveraineté&lt;/a&gt;. Né à Angers vers 1530, il est d’abord moine carme, puis étudie et &lt;a href="https://classiques.uqam.ca/classiques/bodin_jean/bodin_jean_photo/bodin_jean_photo.html" title="jean Bodin par université du québec"&gt;enseigne le droit&lt;/a&gt; à Toulouse avant de devenir avocat au Parlement de Paris. Il vit les guerres de Religion qui déchirent la France. Député du tiers état aux états généraux de Blois en 1576, il s’oppose à la reprise de la guerre contre les protestants et à la vente du domaine royal. Il finit procureur du roi à Laon, où il meurt de la peste en 1596.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Six Livres de la République&lt;/em&gt; (1576), il définit l’État par la souveraineté, « puissance absolue et perpétuelle d’une République ». Elle est indivisible, et son premier attribut est de « donner et casser la loi » sans le consentement de personne. Le souverain reste pourtant soumis aux lois de Dieu et de la nature : il doit respecter la propriété de ses sujets et ne peut lever d’impôt sans leur accord. Écrite contre l’anarchie des guerres civiles, cette théorie prépare la monarchie absolue et toute la pensée moderne de l’État, de Hobbes à Rousseau. Bodin y expose aussi une théorie des climats que reprendra Montesquieu.&lt;/p&gt; &lt;p&gt;Il est aussi l’un des premiers économistes. Dans sa &lt;em&gt;Réponse aux paradoxes de M. de Malestroit&lt;/em&gt; (1568), il explique la hausse des prix qui frappe l’Europe par l’afflux de l’or et de l’argent d’Amérique : c’est une première forme de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_quantitative_de_la_monnaie" title=" Wikipedia"&gt;théorie quantitative de la monnaie&lt;/a&gt;. Partisan d’un commerce actif et de la protection des manufactures, il annonce le &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt;. Son &lt;em&gt;Colloque des sept sages&lt;/em&gt; fait dialoguer un catholique, un luthérien, un calviniste, un juif, un musulman, un partisan de la religion naturelle et un sceptique, sans désigner de vainqueur : un plaidoyer pour la tolérance. Mais le même Bodin publie en 1580 une &lt;em&gt;Démonomanie des sorciers&lt;/em&gt; qui encourage leur persécution.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hVuz1FyDJmQ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"BODIN - L'inventeur de la souveraineté moderne" par Thérence Carvalho</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/bodin-mini.webp</t>
+        </is>
+      </c>
       <c r="J18" s="38" t="inlineStr">
         <is>
-          <t>Française</t>
+          <t xml:space="preserve">Française</t>
         </is>
       </c>
       <c r="K18" s="45" t="inlineStr">
         <is>
-          <t>ethique ; epistemologie</t>
+          <t xml:space="preserve">politique ; spiritualite</t>
         </is>
       </c>
       <c r="L18" s="46" t="inlineStr">
         <is>
-          <t>Scepticisme ; Humanisme</t>
+          <t xml:space="preserve">Humanisme ; Mercantilisme</t>
         </is>
       </c>
       <c r="M18" s="35" t="inlineStr">
         <is>
-          <t>philosophe et écrivain français, l'un des fondateurs du Scepticisme moderne.</t>
+          <t xml:space="preserve">juriste et philosophe français, théoricien de la souveraineté et pionnier de la pensée économique.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1829,163 +1828,230 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" ht="139.5" customHeight="1" s="39">
+      <c r="P18"/>
+    </row>
+    <row r="19" ht="183.75" customHeight="1" s="39">
       <c r="A19" s="47" t="n">
         <v>1533</v>
       </c>
       <c r="B19" s="47" t="inlineStr">
         <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>1533 - 1592</t>
+        </is>
+      </c>
+      <c r="D19" s="48" t="inlineStr">
+        <is>
+          <t>Michel de MONTAIGNE</t>
+        </is>
+      </c>
+      <c r="E19" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne"  title=" Wikipedia"&gt; Michel de MONTAIGNE&lt;/a&gt; était un philosophe, écrivain français qui naquit près de Bordeaux, issu d’une famille de la petite noblesse terrienne. Après des études de droit, il exerce des fonctions de magistrat au Parlement de Bordeaux de 1557 à 1571, puis se retire de la vie publique pour se consacrer à la réflexion et à l’écriture. &lt;/p&gt; &lt;p&gt; Son œuvre majeure est &lt;a href="https://www.youtube.com/watch?v=qKXwK8Sj-24&amp;ab_channel=Kosmos" title="Les Essais par Kosmos"&gt; &lt;en&gt; Les Essais&lt;/em&gt;&lt;/a&gt;, publiés en trois livres entre 1580 et 1588, qu’il réécrit et enrichit tout au long de sa vie. Il livre aussi une traduction de la Théologie naturelle de Raymond Sebond (1569) et un Journal de voyage en Italie publié après sa mort, qui montre son goût pour l’observation concrète du monde. Il part de son expérience personnelle (sa santé, ses habitudes, ses lectures, ses voyages) pour &gt;&lt;a href="https://www.youtube.com/watch?v=dIH-Pg1q1pE"  title=" La Philosophie de Montaigne par Paroles de philosophe"&gt;interroger l’homme&lt;/a&gt;, la connaissance, la mort, l’amitié ou l’éducation, en adoptant un ton très libre et décousu. Il met en doute les certitudes de la science ou de la religion de son époque, prône la curiosité, la tolérance et la connaissance de soi, et ouvre la voie au relativisme et au scepticisme moderne. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs du &lt;a href="https://www.youtube.com/watch?v=IcW1ZnRUoGI"  title="Le scepticisme de Montaigne par Le Prisme Humain"&gt;scepticisme moderne&lt;/a&gt;, une approche philosophique qui remet en question la capacité de la raison humaine à atteindre une vérité absolue. Il est également connu pour sa conception de la philosophie comme une pratique personnelle de l'auto-examen et de la réflexion sur soi. Il croyait que la sagesse ne pouvait pas être trouvée dans les livres ou les enseignements des autres, mais devait être découverte à travers l'expérience de la vie et la contemplation de soi. &lt;/p&gt; &lt;p&gt; Il pronait la tolérance religieuse et la coexistence pacifique des différentes religions. Il était aussi un défenseur de la liberté de pensée et d'expression car les individus devaient être libres de penser et de s'exprimer sans crainte de persécution. &lt;/p&gt; &lt;p&gt; Il est important d'accepter notre nature humaine et ne pas essayer de nous conformer à des normes artificielles ou idéalisées. Il a écrit sur &lt;a href="https://preo.u-bourgogne.fr/shc/index.php?id=78" title="La vanité par Ed LETS"&gt;la vanité &lt;/a&gt; de l'homme et la nécessité de reconnaître nos faiblesses et nos imperfections.  &lt;/p&gt; &lt;audio controls title="La fable de l'identité  par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2011/03/s11/RF_B993FBEB-CED3-4D8B-A48F-2D502E485A89_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F19" s="47" t="inlineStr">
+        <is>
+          <t>it1SGoGdpCw</t>
+        </is>
+      </c>
+      <c r="G19" s="49" t="inlineStr">
+        <is>
+          <t>"Montaigne l’homme qui transforma le doute en sagesse " par Voyages Endormis</t>
+        </is>
+      </c>
+      <c r="H19" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/montaigne-mini.webp</t>
+        </is>
+      </c>
+      <c r="I19" s="45" t="n"/>
+      <c r="J19" s="38" t="inlineStr">
+        <is>
+          <t>Française</t>
+        </is>
+      </c>
+      <c r="K19" s="45" t="inlineStr">
+        <is>
+          <t>ethique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L19" s="46" t="inlineStr">
+        <is>
+          <t>Scepticisme ; Humanisme</t>
+        </is>
+      </c>
+      <c r="M19" s="35" t="inlineStr">
+        <is>
+          <t>philosophe et écrivain français, l'un des fondateurs du Scepticisme moderne.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" ht="139.5" customHeight="1" s="39">
+      <c r="A20" s="47" t="n">
+        <v>1533</v>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>1533 – 1589</t>
         </is>
       </c>
-      <c r="D19" s="48" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>Jacopo ZABARELLA</t>
         </is>
       </c>
-      <c r="E19" s="49" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacopo_Zabarella"  title=" Wikipedia"&gt;Jacopo ZABARELLA&lt;/a&gt; était un philosophe italien, connu pour ses contributions à la logique, à l'épistémologie et à la philosophie naturelle. Il est souvent associé à &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Padoue"  title="Ecole de Padoue par Wikipedia"&gt;l’aristotélisme padouan&lt;/a&gt;, un courant philosophique influent qui a dominé l’Université de Padoue où il enseigna toute sa vie. Son approche se caractérise par un retour rigoureux aux textes aristotéliciens, en opposition aux interprétations néoplatoniciennes, scolastiques ou humanistes plus libres. &lt;/p&gt; &lt;p&gt;Il est célèbre pour sa réflexion sur la méthodologie scientifique, en particulier dans ses œuvres  importantes, principalement en latin dont les plus notables sont : &lt;/p&gt; &lt;p&gt;&lt;"Opera Logica"  : Une œuvre majeure dans laquelle il expose une théorie logique influencée par Aristote, mais aussi enrichie par sa propre réflexion méthodologique. &lt;/p&gt; &lt;p&gt;"De Methodis" : Texte fondamental sur la question des méthodes scientifiques, dans lequel il distingue deux types de raisonnements scientifiques : la méthode résolutive (anagogique, qui va de l’effet à la cause) et la méthode compositive (déductive, qui va de la cause à l’effet). Ces deux méthodes inspireront plus tard la pensée scientifique moderne. &lt;/p&gt; &lt;p&gt;"De Rebus Naturalibus" : Traité sur la philosophie naturelle aristotélicienne. &lt;/p&gt; &lt;p&gt; Il  est un des premiers à penser la science comme un système de démonstrations fondé sur des principes sûrs, mais qui doivent être établis par l’observation et la réflexion logique. Il reste fidèle à Aristote, mais développe des outils logiques sophistiqués pour fonder une science naturelle rigoureuse. Son œuvre est un pont entre la scolastique médiévale et les débuts de la révolution scientifique. Il a influencé plusieurs générations de penseurs, non seulement en Italie, mais aussi dans le monde germanique, où ses textes ont été largement diffusés. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F19" s="47" t="inlineStr">
+      <c r="F20" s="47" t="inlineStr">
         <is>
           <t>YX7eKSD-X2M</t>
         </is>
       </c>
-      <c r="G19" s="49" t="inlineStr">
+      <c r="G20" s="49" t="inlineStr">
         <is>
           <t>"Jacopo Zabarella: Renaissance Scholar" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H19" s="49" t="inlineStr">
+      <c r="H20" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/zabarella-mini.webp</t>
-        </is>
-      </c>
-      <c r="I19" s="45" t="n"/>
-      <c r="J19" s="38" t="inlineStr">
-        <is>
-          <t>Italienne</t>
-        </is>
-      </c>
-      <c r="K19" s="45" t="inlineStr">
-        <is>
-          <t>logique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="L19" s="46" t="inlineStr">
-        <is>
-          <t>Aristotélisme</t>
-        </is>
-      </c>
-      <c r="M19" s="35" t="inlineStr">
-        <is>
-          <t>philosophe humaniste italien commentateur latin d'Aristote le plus réputé.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="137.25" customHeight="1" s="39">
-      <c r="A20" s="47" t="n">
-        <v>1541</v>
-      </c>
-      <c r="B20" s="47" t="inlineStr">
-        <is>
-          <t>1603</t>
-        </is>
-      </c>
-      <c r="C20" s="47" t="inlineStr">
-        <is>
-          <t>1541 – 1603</t>
-        </is>
-      </c>
-      <c r="D20" s="48" t="inlineStr">
-        <is>
-          <t>Pierre CHARRON</t>
-        </is>
-      </c>
-      <c r="E20" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Charron"  title=" Wikipedia"&gt;Pierre CHARRON&lt;/a&gt; était un philosophe, orateur et moraliste français dont   &lt;a href="https://revuecorpus.com/pdf/CORPUS%20N%C2%B055.pdf" style="color:#88A1E9" title=" n°55  Charron par Corpus"&gt; l'œuvre&lt;/a&gt; est profondément marquée par le contexte religieux et intellectuel de son époque, notamment les guerres de religion et l'humanisme renaissant. &lt;/p&gt; &lt;p&gt;  Son ouvrage "Les Trois Vérités" est une apologie de la religion catholique, rédigée en réponse aux arguments protestants. Elle vise à défendre la foi contre les athées, idolâtres, juifs, mahométans, hérétiques et schismatiques. Il est présenté comme un fervent défenseur de l'orthodoxie catholique, &lt;/p&gt; &lt;p&gt; Son 2ème ouvrage "De la Sagesse" est sans doute le plus célèbre et le plus influent. Ce &lt;a href="https://www.youtube.com/watch?v=6n3OmEeVudo" title=" Charron et l'invention d'une sagesse laîque par Photon"&gt; traité de morale &lt;/a&gt;  et de philosophie, divisé en trois livres, expose une conception de la sagesse humaine qui sera très commentée et parfois critiquée pour ses implications jugées irréligieuses par certains car il révèle une pensée plus nuancée, imprégnée de scepticisme et d'une forme de moralisme laïque. &lt;/p&gt; &lt;p&gt; Il est profondément influencé par le scepticisme des  &lt;a href="https://fr.wikipedia.org/wiki/Essais_(Montaigne)" title=" Essais de Montaigne par Wikipedia"&gt; Essais de Montaigne&lt;/a&gt; et partage l'idée de la faiblesse de la raison humaine et l'incertitude des connaissances. Pour lui, il faut "commencer" par le doute, reconnaître "l'ignorance, faiblesse, incertitude" de la condition humaine. Ce  &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_(philosophie)" title="  scepticisme par Wikipedia"&gt; scepticisme&lt;/a&gt; initial n'est pas une fin en soi, mais un point de départ pour l'acquisition de la sagesse. &lt;/p&gt; &lt;p&gt;  Il est l'un des penseurs qui contribuent à la séparation de la sphère morale de la sphère théologique. Il cherche à établir une éthique autonome, fondée sur la raison et la nature humaine, sans la subordonner entièrement à la foi. Il  invite à fuir la "contagion du monde" et à rechercher la solitude comme moyen d'amender l'intellect par rapport aux erreurs populaires. Il insiste sur la capacité de l'homme à être maître de sa volonté et à s'affermir dans la raison, ce qui peut être vu comme un précurseur de l'individualisme moderne. &lt;/p&gt; &lt;p&gt; Il  a joué un rôle important dans la transition de l'humanisme vers le rationalisme, en ouvrant la voie à une réflexion morale et philosophique plus autonome par rapport à la théologie. Son œuvre est un témoignage précieux des tensions intellectuelles et religieuses de son époque. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F20" s="47" t="inlineStr">
-        <is>
-          <t>RZBdYMma2gc</t>
-        </is>
-      </c>
-      <c r="G20" s="49" t="inlineStr">
-        <is>
-          <t>"Pierre CHARRON" par See Hear Say Learn</t>
-        </is>
-      </c>
-      <c r="H20" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/charron-mini.webp</t>
         </is>
       </c>
       <c r="I20" s="45" t="n"/>
       <c r="J20" s="38" t="inlineStr">
         <is>
+          <t>Italienne</t>
+        </is>
+      </c>
+      <c r="K20" s="45" t="inlineStr">
+        <is>
+          <t>logique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L20" s="46" t="inlineStr">
+        <is>
+          <t>Aristotélisme</t>
+        </is>
+      </c>
+      <c r="M20" s="35" t="inlineStr">
+        <is>
+          <t>philosophe humaniste italien commentateur latin d'Aristote le plus réputé.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="137.25" customHeight="1" s="39">
+      <c r="A21" s="47" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>1603</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>1541 – 1603</t>
+        </is>
+      </c>
+      <c r="D21" s="48" t="inlineStr">
+        <is>
+          <t>Pierre CHARRON</t>
+        </is>
+      </c>
+      <c r="E21" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Charron"  title=" Wikipedia"&gt;Pierre CHARRON&lt;/a&gt; était un philosophe, orateur et moraliste français dont   &lt;a href="https://revuecorpus.com/pdf/CORPUS%20N%C2%B055.pdf" style="color:#88A1E9" title=" n°55  Charron par Corpus"&gt; l'œuvre&lt;/a&gt; est profondément marquée par le contexte religieux et intellectuel de son époque, notamment les guerres de religion et l'humanisme renaissant. &lt;/p&gt; &lt;p&gt;  Son ouvrage "Les Trois Vérités" est une apologie de la religion catholique, rédigée en réponse aux arguments protestants. Elle vise à défendre la foi contre les athées, idolâtres, juifs, mahométans, hérétiques et schismatiques. Il est présenté comme un fervent défenseur de l'orthodoxie catholique, &lt;/p&gt; &lt;p&gt; Son 2ème ouvrage "De la Sagesse" est sans doute le plus célèbre et le plus influent. Ce &lt;a href="https://www.youtube.com/watch?v=6n3OmEeVudo" title=" Charron et l'invention d'une sagesse laîque par Photon"&gt; traité de morale &lt;/a&gt;  et de philosophie, divisé en trois livres, expose une conception de la sagesse humaine qui sera très commentée et parfois critiquée pour ses implications jugées irréligieuses par certains car il révèle une pensée plus nuancée, imprégnée de scepticisme et d'une forme de moralisme laïque. &lt;/p&gt; &lt;p&gt; Il est profondément influencé par le scepticisme des  &lt;a href="https://fr.wikipedia.org/wiki/Essais_(Montaigne)" title=" Essais de Montaigne par Wikipedia"&gt; Essais de Montaigne&lt;/a&gt; et partage l'idée de la faiblesse de la raison humaine et l'incertitude des connaissances. Pour lui, il faut "commencer" par le doute, reconnaître "l'ignorance, faiblesse, incertitude" de la condition humaine. Ce  &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_(philosophie)" title="  scepticisme par Wikipedia"&gt; scepticisme&lt;/a&gt; initial n'est pas une fin en soi, mais un point de départ pour l'acquisition de la sagesse. &lt;/p&gt; &lt;p&gt;  Il est l'un des penseurs qui contribuent à la séparation de la sphère morale de la sphère théologique. Il cherche à établir une éthique autonome, fondée sur la raison et la nature humaine, sans la subordonner entièrement à la foi. Il  invite à fuir la "contagion du monde" et à rechercher la solitude comme moyen d'amender l'intellect par rapport aux erreurs populaires. Il insiste sur la capacité de l'homme à être maître de sa volonté et à s'affermir dans la raison, ce qui peut être vu comme un précurseur de l'individualisme moderne. &lt;/p&gt; &lt;p&gt; Il  a joué un rôle important dans la transition de l'humanisme vers le rationalisme, en ouvrant la voie à une réflexion morale et philosophique plus autonome par rapport à la théologie. Son œuvre est un témoignage précieux des tensions intellectuelles et religieuses de son époque. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F21" s="47" t="inlineStr">
+        <is>
+          <t>RZBdYMma2gc</t>
+        </is>
+      </c>
+      <c r="G21" s="49" t="inlineStr">
+        <is>
+          <t>"Pierre CHARRON" par See Hear Say Learn</t>
+        </is>
+      </c>
+      <c r="H21" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/charron-mini.webp</t>
+        </is>
+      </c>
+      <c r="I21" s="45" t="n"/>
+      <c r="J21" s="38" t="inlineStr">
+        <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K20" s="45" t="inlineStr">
+      <c r="K21" s="45" t="inlineStr">
         <is>
           <t>ethique ; epistemologie</t>
         </is>
       </c>
-      <c r="L20" s="46" t="inlineStr">
+      <c r="L21" s="46" t="inlineStr">
         <is>
           <t>Scepticisme</t>
         </is>
       </c>
-      <c r="M20" s="35" t="inlineStr">
+      <c r="M21" s="35" t="inlineStr">
         <is>
           <t>philosophe et moraliste français sceptique qui défendait la tolérance religieuse.</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="105.75" customHeight="1" s="39">
-      <c r="A21" s="47" t="n">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="105.75" customHeight="1" s="39">
+      <c r="A22" s="47" t="n">
         <v>1548</v>
       </c>
-      <c r="B21" s="47" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>1548 – 1600</t>
         </is>
       </c>
-      <c r="D21" s="48" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Giordano BRUNO</t>
         </is>
       </c>
-      <c r="E21" s="58" t="inlineStr">
+      <c r="E22" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giordano_Bruno"  title=" Wikipedia"&gt; Giordano BRUNO&lt;/a&gt; était un philosophe et penseur italien, connue pour ses  &lt;a href="https://www.youtube.com/watch?v=21dM3ZJtYY0&amp;t=11s" style="color:#88A1E9" title="Giordano BRUNO de Calvin par Le Pro Presente "&gt;idées cosmologiques&lt;/a&gt; et philosophiques radicales dont voici quelques-uns de ses concepts clés : &lt;/p&gt; &lt;p&gt;L'univers infini : et peuplé d'une infinité de mondes habités. Cette vision s'opposait à la conception géocentrique de l'univers, qui plaçait la Terre au centre de tout.  &lt;/p&gt;
 &lt;p&gt;L'unité de la matière et de l'esprit : vision panthéiste de l'univers, où il croyait que la matière et l'esprit étaient inséparables et que l'univers était animé par une force vitale universelle. &lt;/p&gt;
@@ -1993,940 +2059,940 @@
 &lt;p&gt;La liberté de pensée : la liberté de pensée et d'expression, s'opposant à l'autorité dogmatique de l'Église. Il croyait que la vérité ne pouvait être découverte que par la raison et l'expérience, et non par la révélation divine. &lt;/p&gt; &lt;p&gt; En raison de  &lt;a href="https://nospensees.fr/les-meilleures-phrases-de-giordano-bruno/" title="Giordano BRUNO par nospensees "&gt;ses idées controversées&lt;/a&gt;, il a été contraint de quitter l'Italie et de voyager à travers l'Europe, dans des villes comme Genève, Paris, Londres et Prague, où il a enseigné et publié  &lt;a href="https://www.willeime.com/bruno.htm" title="Giordano BRUNO par willeime "&gt;ses œuvres&lt;/a&gt;. Il a été arrêté par l'Inquisition vénitienne et extradé à Rome. Après 8 ans de procès, il a été accusé d'hérésie pour ses idées et condamné à mort. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus importantes, on peut citer : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=vHfEKwAmhAQ"  title="Giordano BRUNO par Filosofia"&gt;"De l'infinito, universo e mondi"&lt;/a&gt;: Théorie de l'univers infini et des mondes multiples. &lt;/p&gt; &lt;p&gt;" La cena de le ceneri" : Critique la philosophie aristotélicienne et défend les idées coperniciennes.&lt;/p&gt; &lt;p&gt;"De la causa, principio e uno" : Nature de l'univers et l'unité de la matière et de l'esprit.&lt;/p&gt; &lt;p&gt;        &lt;audio controls title=" Giordano BRUNO par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-16.11.2022-ITEMA_23198161-2015C3372E1085-NET_MFC_367A1BA4-BD9E-4C79-A1B2-C57FCE8CB809-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F21" s="47" t="inlineStr">
+      <c r="F22" s="47" t="inlineStr">
         <is>
           <t>24dXLNyq6D4</t>
         </is>
       </c>
-      <c r="G21" s="49" t="inlineStr">
+      <c r="G22" s="49" t="inlineStr">
         <is>
           <t>"Giordano BRUNO" par Histoire &amp; mythologie en BD</t>
         </is>
       </c>
-      <c r="H21" s="49" t="inlineStr">
+      <c r="H22" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bruno-mini.webp</t>
-        </is>
-      </c>
-      <c r="I21" s="45" t="n"/>
-      <c r="J21" s="38" t="inlineStr">
-        <is>
-          <t>Italienne</t>
-        </is>
-      </c>
-      <c r="K21" s="45" t="inlineStr">
-        <is>
-          <t>metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L21" s="46" t="inlineStr">
-        <is>
-          <t>Néoplatonisme ; Panthéisme</t>
-        </is>
-      </c>
-      <c r="M21" s="35" t="inlineStr">
-        <is>
-          <t>philosophe et scientifique italien de la renaissance qui croyait en d'autres mondes.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="178.5" customHeight="1" s="39">
-      <c r="A22" s="47" t="n">
-        <v>1548</v>
-      </c>
-      <c r="B22" s="47" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
-      <c r="C22" s="47" t="inlineStr">
-        <is>
-          <t>1548 – 1617</t>
-        </is>
-      </c>
-      <c r="D22" s="48" t="inlineStr">
-        <is>
-          <t>Francisco SUAREZ</t>
-        </is>
-      </c>
-      <c r="E22" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Su%C3%A1rez"  title=" Wikipedia"&gt;Francisco SUAREZ&lt;/a&gt; était un philosophe et théologien jésuite espagnol, considéré comme l'une des figures majeures de la scolastique tardive et de la philosophie du droit naturel. Il est surtout connu pour son ouvrage Disputationes Metaphysicae, une synthèse magistrale de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1999_num_97_1_7140_t1_0138_0000_2"  title="Francisco Suarez, Disputes métaphysiques par Persée"&gt;métaphysique&lt;/a&gt; scolastique. Il y explore des concepts comme l'être, l'existence, la substance et la causalité. Il développe une conception de l'être comme ce qui est « réellement existant » ou « apte à exister », insistant sur la distinction entre essence et existence. &lt;/p&gt; &lt;p&gt; Il est un pionnier du droit international moderne. Dans son ouvrage De Legibus, il développe une théorie du droit naturel basée sur la raison et la loi divine. Il affirme que l'autorité politique vient de Dieu, mais qu'elle est exercée par le consentement du peuple. Suárez critique l'absolutisme royal et soutient que le pouvoir politique est délégué par la communauté. Cette idée préfigure les théories du contrat social.  Il rejette la théorie du droit divin des rois, affirmant que même les monarques sont soumis à la loi morale et divine. &lt;/p&gt; &lt;p&gt; Dans De Bello, Suárez développe une théorie de la guerre juste, insistant sur les conditions morales qui doivent être remplies pour qu'une guerre soit légitime (par exemple, une cause juste, une intention droite et une autorité légitime). Il met l'accent sur la dignité de l'individu et sur le rôle de la communauté dans la réalisation  &lt;a href="https://www.persee.fr/doc/afdi_0066-3085_2017_num_63_1_5362"  title="Le droit des gens chez Francisco Suarez par Persée"&gt;du bien commun&lt;/a&gt;. Il insiste sur l'importance de la justice et de l'équité dans les relations sociales. &lt;/p&gt; &lt;p&gt; Sa théorie du droit naturel et de la souveraineté populaire inspire les penseurs des Lumières et les fondateurs du droit international. Il est reconnu comme l'un des plus grands théologiens de la Contre-Réforme. Ses idées sur la grâce et le libre arbitre sont largement discutées dans les débats théologiques. &lt;/p&gt; &lt;p&gt; Il s'intéresse également aux questions économiques, notamment à l'usure et au commerce. Il défend l'idée que les activités économiques doivent être régies par des principes éthiques et que le bien commun doit primer sur les intérêts individuels. Il est considéré comme un précurseur du droit international moderne. Ses idées sur la souveraineté, les droits des peuples et la guerre juste influenceront des penseurs comme Hugo Grotius, souvent appelé le « père du droit international ». Son œuvre reste d'une grande actualité pour les questions de justice globale et de relations internationales.&lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F22" s="47" t="inlineStr">
-        <is>
-          <t>uMxpw34VJzQ</t>
-        </is>
-      </c>
-      <c r="G22" s="49" t="inlineStr">
-        <is>
-          <t>"Francisco SUAREZ" par VIS PHILO</t>
-        </is>
-      </c>
-      <c r="H22" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/suarez-mini.webp</t>
         </is>
       </c>
       <c r="I22" s="45" t="n"/>
       <c r="J22" s="38" t="inlineStr">
         <is>
+          <t>Italienne</t>
+        </is>
+      </c>
+      <c r="K22" s="45" t="inlineStr">
+        <is>
+          <t>metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L22" s="46" t="inlineStr">
+        <is>
+          <t>Néoplatonisme ; Panthéisme</t>
+        </is>
+      </c>
+      <c r="M22" s="35" t="inlineStr">
+        <is>
+          <t>philosophe et scientifique italien de la renaissance qui croyait en d'autres mondes.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="178.5" customHeight="1" s="39">
+      <c r="A23" s="47" t="n">
+        <v>1548</v>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
+        <is>
+          <t>1548 – 1617</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>Francisco SUAREZ</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francisco_Su%C3%A1rez"  title=" Wikipedia"&gt;Francisco SUAREZ&lt;/a&gt; était un philosophe et théologien jésuite espagnol, considéré comme l'une des figures majeures de la scolastique tardive et de la philosophie du droit naturel. Il est surtout connu pour son ouvrage Disputationes Metaphysicae, une synthèse magistrale de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1999_num_97_1_7140_t1_0138_0000_2"  title="Francisco Suarez, Disputes métaphysiques par Persée"&gt;métaphysique&lt;/a&gt; scolastique. Il y explore des concepts comme l'être, l'existence, la substance et la causalité. Il développe une conception de l'être comme ce qui est « réellement existant » ou « apte à exister », insistant sur la distinction entre essence et existence. &lt;/p&gt; &lt;p&gt; Il est un pionnier du droit international moderne. Dans son ouvrage De Legibus, il développe une théorie du droit naturel basée sur la raison et la loi divine. Il affirme que l'autorité politique vient de Dieu, mais qu'elle est exercée par le consentement du peuple. Suárez critique l'absolutisme royal et soutient que le pouvoir politique est délégué par la communauté. Cette idée préfigure les théories du contrat social.  Il rejette la théorie du droit divin des rois, affirmant que même les monarques sont soumis à la loi morale et divine. &lt;/p&gt; &lt;p&gt; Dans De Bello, Suárez développe une théorie de la guerre juste, insistant sur les conditions morales qui doivent être remplies pour qu'une guerre soit légitime (par exemple, une cause juste, une intention droite et une autorité légitime). Il met l'accent sur la dignité de l'individu et sur le rôle de la communauté dans la réalisation  &lt;a href="https://www.persee.fr/doc/afdi_0066-3085_2017_num_63_1_5362"  title="Le droit des gens chez Francisco Suarez par Persée"&gt;du bien commun&lt;/a&gt;. Il insiste sur l'importance de la justice et de l'équité dans les relations sociales. &lt;/p&gt; &lt;p&gt; Sa théorie du droit naturel et de la souveraineté populaire inspire les penseurs des Lumières et les fondateurs du droit international. Il est reconnu comme l'un des plus grands théologiens de la Contre-Réforme. Ses idées sur la grâce et le libre arbitre sont largement discutées dans les débats théologiques. &lt;/p&gt; &lt;p&gt; Il s'intéresse également aux questions économiques, notamment à l'usure et au commerce. Il défend l'idée que les activités économiques doivent être régies par des principes éthiques et que le bien commun doit primer sur les intérêts individuels. Il est considéré comme un précurseur du droit international moderne. Ses idées sur la souveraineté, les droits des peuples et la guerre juste influenceront des penseurs comme Hugo Grotius, souvent appelé le « père du droit international ». Son œuvre reste d'une grande actualité pour les questions de justice globale et de relations internationales.&lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F23" s="47" t="inlineStr">
+        <is>
+          <t>uMxpw34VJzQ</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>"Francisco SUAREZ" par VIS PHILO</t>
+        </is>
+      </c>
+      <c r="H23" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/suarez-mini.webp</t>
+        </is>
+      </c>
+      <c r="I23" s="45" t="n"/>
+      <c r="J23" s="38" t="inlineStr">
+        <is>
           <t>Espagnole</t>
         </is>
       </c>
-      <c r="K22" s="45" t="inlineStr">
+      <c r="K23" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="L22" s="46" t="inlineStr">
+      <c r="L23" s="46" t="inlineStr">
         <is>
           <t>Néothomisme</t>
         </is>
       </c>
-      <c r="M22" s="35" t="inlineStr">
+      <c r="M23" s="35" t="inlineStr">
         <is>
           <t>philosophe espagnol pionnier du droit international moderne.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="157.5" customHeight="1" s="39">
-      <c r="A23" s="47" t="n">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="157.5" customHeight="1" s="39">
+      <c r="A24" s="47" t="n">
         <v>1561</v>
       </c>
-      <c r="B23" s="47" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>1626</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C24" s="47" t="inlineStr">
         <is>
           <t>1561 - 1626</t>
         </is>
       </c>
-      <c r="D23" s="48" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>Francis BACON</t>
         </is>
       </c>
-      <c r="E23" s="60" t="inlineStr">
+      <c r="E24" s="60" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francis_Bacon_(philosophe)"   title=" Wikipedia"&gt;Francis BACON&lt;/a&gt; était un philosophe, scientifique et homme politique britannique considéré comme l'un des pères fondateurs de &lt;a href="https://www.youtube.com/watch?v=20uVwCu5xyg&amp;ab_channel=CulturePhilo%2FAlainBajom%C3%A9e"   title="l'empirisme par Alain Bajomé"&gt;l'Empirisme&lt;/a&gt;   et de la méthode scientifique moderne. Né à Londres, il occupa des postes élevés comme chancelier d'Angleterre sous Jacques Ier, tout en critiquant la scolastique traditionnelle pour promouvoir une science basée sur l'observation et l'expérience. Fils de Sir Nicholas Bacon, il étudia au Trinity College de Cambridge et voyagea en Europe avant d'entrer en politique. Accusé de corruption en 1621, il fut destitué mais se consacra ensuite pleinement à la philosophie et aux sciences jusqu'à sa mort à Highgate.   . &lt;/p&gt; &lt;p&gt;Il  rejeta les préjugés humains, qu'il nomma "idoles de l'esprit" (tribu, caverne, forum, théâtre), pour défendre une logique inductive et expérimentale. Il voyait la connaissance comme un pouvoir ("scientia potentia est") visant à améliorer la condition humaine via des inventions pratiques.    Il est surtout connu pour son ouvrage &lt;a href="https://fr.wikipedia.org/wiki/Novum_organum"    title="Nouvel organon par Wikikipedia"&gt;"Nouvel organon"&lt;/a&gt;, publié en 1620 ou il plaide en faveur d'une approche scientifique basée sur l'observation et l'expérimentation pour acquérir des connaissances sur le monde et que les théories scientifiques doivent être testées par des méthodes expérimentales rigoureuses afin d'être considérées comme valides. &lt;/p&gt; &lt;p&gt; Il soutient que l'objectif de la science doit être de fournir des &lt;a href="https://www.youtube.com/watch?v=gUqmVJ7Wd0A"   title="Francis Bacon par MecaniqueUniverselle"&gt;connaissances pratiques &lt;/a&gt; pour améliorer la vie humaine et d'augmenter la puissance et la domination de l'humanité sur la nature. &lt;/p&gt; &lt;p&gt; De nos jours, il est considéré comme l'un des fondateurs de la science moderne et sa pensée continue d'influencer les scientifiques, les philosophes et les penseurs politiques à travers le monde.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F23" s="47" t="inlineStr">
+      <c r="F24" s="47" t="inlineStr">
         <is>
           <t>VTSNSe4xHV8</t>
         </is>
       </c>
-      <c r="G23" s="49" t="inlineStr">
+      <c r="G24" s="49" t="inlineStr">
         <is>
           <t>"Les citations qui changeront votre vie par Grandes Citations"</t>
         </is>
       </c>
-      <c r="H23" s="49" t="inlineStr">
+      <c r="H24" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bacon-mini.webp</t>
         </is>
       </c>
-      <c r="I23" s="45" t="n"/>
-      <c r="J23" s="55" t="inlineStr">
+      <c r="I24" s="45" t="n"/>
+      <c r="J24" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K23" s="45" t="inlineStr">
+      <c r="K24" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L23" s="46" t="inlineStr">
+      <c r="L24" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Empirisme ; Progressisme</t>
         </is>
       </c>
-      <c r="M23" s="35" t="inlineStr">
+      <c r="M24" s="35" t="inlineStr">
         <is>
           <t>philosophe anglais qui fut l'un des premiers adeptes de l'Empirisme.</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="147.75" customHeight="1" s="39">
-      <c r="A24" s="47" t="n">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="147.75" customHeight="1" s="39">
+      <c r="A25" s="47" t="n">
         <v>1568</v>
       </c>
-      <c r="B24" s="47" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>1639</t>
         </is>
       </c>
-      <c r="C24" s="47" t="inlineStr">
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>1568 – 1639</t>
         </is>
       </c>
-      <c r="D24" s="48" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>Tommaso CAMPANELLA</t>
         </is>
       </c>
-      <c r="E24" s="49" t="inlineStr">
+      <c r="E25" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tommaso_Campanella" title=" Wikipedia"&gt;Tommaso CAMPANELLA&lt;/a&gt; était  un philosophe, théologien et moine dominicain italien, connu pour ses   &lt;a href="https://www.youtube.com/watch?v=wAl4GvGSVJM" style="color:#88A1E9" title="Jean Delumeau : Le mystère Campanella par Canal Academies "&gt;idées utopiques&lt;/a&gt;, sa pensée politique audacieuse et son engagement en faveur d’une réforme sociale et religieuse.  Il sera marqué par la pensée d’Aristote, mais aussi par les idées novatrices de Bernardino Telesio, un philosophe naturaliste qui rejette l’aristotélisme traditionnel. &lt;/p&gt; &lt;p&gt; Il  s’oppose à l’autorité espagnole en Italie et participe à un complot visant à établir une république mais le projet échoue. Il est arrêté, torturé et condamné à mort, il simule la folie pour éviter l’exécution et passera 27 ans en prison, où il écrit son œuvre majeure : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/barb_0001-4133_1992_num_3_1_38762" title="Tommaso Campanella, « La Cité du Soleil » par Persée "&gt;La Cité du Soleil&lt;/a&gt; : Utopie politique et sociale, inspirée de La République de Platon et de L'Utopie de Thomas More. Une société idéale gouvernée par des savants, où la propriété privée est abolie, les biens sont communs, et l’éducation est centralisée. &lt;/p&gt; &lt;p&gt;Philosophia sensibus demonstrata : Il s’inspire de Telesio pour promouvoir une philosophie basée sur l’observation de la nature, rejetant la scolastique aristotélicienne.&lt;/p&gt; &lt;p&gt;Atheismus triumphatus : Critique de l’athéisme, mais aussi des dogmatismes religieux. Il prédit une réforme universelle de l’Église et de la société, influencé par le millénarisme (âge d’or futur). &lt;/p&gt; &lt;p&gt;Monarchie d'Espagne : Projet politique pour une monarchie universelle sous domination espagnole.  Il rejette la séparation de la morale et de la politique, prônant un État vertueux. &lt;/p&gt; &lt;p&gt; Il  reste une figure complexe, à mi-chemin entre mysticisme et rationalisme, dont les idées résonnent encore dans les débats sur la justice sociale et le rôle de la science. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F24" s="47" t="inlineStr">
+      <c r="F25" s="47" t="inlineStr">
         <is>
           <t>ZMqb8fBTVqA</t>
         </is>
       </c>
-      <c r="G24" s="49" t="inlineStr">
+      <c r="G25" s="49" t="inlineStr">
         <is>
           <t>"Tommaso Campanella" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H24" s="49" t="inlineStr">
+      <c r="H25" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/campanella-mini.webp</t>
         </is>
       </c>
-      <c r="I24" s="45" t="n"/>
-      <c r="J24" s="38" t="inlineStr">
+      <c r="I25" s="45" t="n"/>
+      <c r="J25" s="38" t="inlineStr">
         <is>
           <t>Italienne</t>
         </is>
       </c>
-      <c r="K24" s="45" t="inlineStr">
+      <c r="K25" s="45" t="inlineStr">
         <is>
           <t>politique ; metaphysique</t>
         </is>
       </c>
-      <c r="L24" s="46" t="inlineStr">
+      <c r="L25" s="46" t="inlineStr">
         <is>
           <t>Utopisme ; Naturalisme</t>
         </is>
       </c>
-      <c r="M24" s="35" t="inlineStr">
+      <c r="M25" s="35" t="inlineStr">
         <is>
           <t>philosophe dominicain italien connu pour ses idées utopiques.</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="135" customHeight="1" s="39">
-      <c r="A25" s="47" t="n">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="135" customHeight="1" s="39">
+      <c r="A26" s="47" t="n">
         <v>1575</v>
       </c>
-      <c r="B25" s="47" t="inlineStr">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>1624</t>
         </is>
       </c>
-      <c r="C25" s="47" t="inlineStr">
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>1575 – 1624</t>
         </is>
       </c>
-      <c r="D25" s="48" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>Jacob BOEHME</t>
         </is>
       </c>
-      <c r="E25" s="49" t="inlineStr">
+      <c r="E26" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jakob_B%C3%B6hme" title=" Wikipedia"&gt;Jacob BOEHME&lt;/a&gt; était un philosophe mystique allemand  surnommé le  &lt;a href="https://www.youtube.com/watch?v=MZA137IGPB0&amp;t=761s" style="color:#88A1E9" title=" Jacob Boehme par Carmel de Saint-Elie"&gt; "Philosophus Teutonicus" &lt;/a&gt; et simple cordonnier sans éducation formelle. Pourtant, il a développé une pensée théosophique et philosophique d'une profondeur et d'une complexité   &lt;a href="https://livres-mystiques.com/partieTEXTES/Besson/Articles/boehm.html"  title="  Jacob BOEHME par Livres mystiques"&gt; remarquables&lt;/a&gt;, qu'il disait avoir reçue par des illuminations divines.&lt;/p&gt; &lt;p&gt;  L'une de ses idées les plus connues est celle de  &lt;a href="https://www.youtube.com/watch?v=krUTxK9Adks" title="  L’Ungrund, le sans-fond de Jacob Böhme par BAGLIS TV"&gt;  l'Ungrund&lt;/a&gt;, le "sans-fond"  où Dieu n'est pas un être statique, mais une réalité dynamique, insondable, d'où émergent les oppositions et la création. Cette dialectique entre le "oui" et le "non", la lumière et l'obscurité, le bien et le mal, est centrale à sa pensée. &lt;/p&gt; &lt;p&gt;  Il  s'est penché sur l'épineux problème de l'existence du mal dans un monde créé par un Dieu bon. Contrairement à d'autres théologiens qui le réduisaient à une simple absence du bien, il voyait le mal comme une composante nécessaire du processus divin de manifestation et de la liberté humaine. &lt;/p&gt; &lt;p&gt;  Parmi ses œuvres les plus importantes, on peut citer  &lt;a href="https://www.youtube.com/watch?v=hNRrhozhNSE"  title="  Le royaume Angelique par Dominique Debray"&gt; "L'Aurore naissante"&lt;/a&gt;, "Des trois principes de l'essence divine", "De la signature des choses"  et "De l'élection de la grâce" mais sa pensée non conventionnelle lui a valu d'être en butte aux critiques et aux persécutions de l'orthodoxie luthérienne de son temps, le forçant parfois à cesser d'écrire pendant un certain temps. Après &lt;em&gt;L’Aurore naissante&lt;/em&gt; (1612), le pasteur de Görlitz, Gregor Richter, le fait condamner au silence, et il ne reprend la plume qu’en 1619. Sa pensée a marqué Louis-Claude de Saint-Martin, qui le traduit en français, puis Schelling et Hegel, qui voyait en lui « le premier philosophe allemand ».&lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F25" s="47" t="inlineStr">
+      <c r="F26" s="47" t="inlineStr">
         <is>
           <t>J0PQRsOLfKc</t>
         </is>
       </c>
-      <c r="G25" s="49" t="inlineStr">
+      <c r="G26" s="49" t="inlineStr">
         <is>
           <t>"Jacob Boehme - " L' Aurore naissante "" par Dominique Debray</t>
         </is>
       </c>
-      <c r="H25" s="49" t="inlineStr">
+      <c r="H26" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/boehme-mini.webp</t>
         </is>
       </c>
-      <c r="I25" s="57" t="n"/>
-      <c r="J25" s="38" t="inlineStr">
+      <c r="I26" s="57" t="n"/>
+      <c r="J26" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K25" s="45" t="inlineStr">
+      <c r="K26" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="L25" s="46" t="inlineStr">
+      <c r="L26" s="46" t="inlineStr">
         <is>
           <t>Mysticisme</t>
         </is>
       </c>
-      <c r="M25" s="35" t="inlineStr">
+      <c r="M26" s="35" t="inlineStr">
         <is>
           <t>philosophe mystique allemand surnommé le "Philosophus Teutonicus".</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="168" customHeight="1" s="39">
-      <c r="A26" s="47" t="n">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="168" customHeight="1" s="39">
+      <c r="A27" s="47" t="n">
         <v>1583</v>
       </c>
-      <c r="B26" s="47" t="inlineStr">
+      <c r="B27" s="47" t="inlineStr">
         <is>
           <t>1645</t>
         </is>
       </c>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="C27" s="47" t="inlineStr">
         <is>
           <t>1583 – 1645</t>
         </is>
       </c>
-      <c r="D26" s="48" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>Hugo GROTIUS</t>
         </is>
       </c>
-      <c r="E26" s="49" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugo_Grotius" title=" Wikipedia"&gt;Hugo GROTUIS&lt;/a&gt; était une figure majeure de l'histoire intellectuelle Néerlandaise, juridique et politique, il est souvent considéré comme l'un des fondateurs du droit international moderne.  Il a vécu à une époque marquée par des conflits religieux et politiques intenses, notamment la guerre de Quatre-Vingts Ans entre les Pays-Bas et l'Espagne, ainsi que la guerre de Trente Ans en Europe. Ces conflits ont influencé sa pensée, notamment en ce qui concerne la nécessité d'un &lt;a href="https://www.youtube.com/watch?v=BoTTE8ohmJ0" style="color:#88A1E9" title="Le droit des gens et le droit international par Radio J "&gt;système juridique&lt;/a&gt; pour réguler les relations entre États. &lt;/p&gt; &lt;p&gt; Ses contributions majeures en droit international : &lt;/p&gt;
 &lt;p&gt;&lt;a href="https://www.persee.fr/doc/ridc_0035-3337_1954_num_6_4_9126"  title="H Grotius par Persée "&gt;"De jure belli ac pacis"&lt;/a&gt;  (Du droit de la guerre et de la paix, 1625) : œuvres fondatrices du droit international. Il y développe l'idée que les relations entre États devraient être régies par des principes juridiques plutôt que par la force brute. Il introduit le concept de "droit naturel", qui est universel et immuable, et qui s'applique à tous les êtres humains, indépendamment de leur nationalité ou de leur religion. &lt;/p&gt;
 &lt;p&gt;"Mare Liberum"   (La mer libre, 1609) : les mers doivent être libres d'accès pour tous les États, une idée qui a eu un impact sur le droit maritime international. &lt;/p&gt; &lt;p&gt;  Il a défendu l'idée que la souveraineté de l'État est limitée par le droit naturel et que les gouvernements ont des obligations envers leurs citoyens. Il a plaidé pour la tolérance religieuse et a cherché à réconcilier les différentes confessions chrétiennes. Son ouvrage &lt;a href="https://www.penseesdepascal.fr/General/Grotius.php" title="De veritate religionis christianae par penseesdepascal "&gt;"De veritate religionis Christianae" &lt;/a&gt; (Sur la vérité de la religion chrétienne) est une défense rationnelle du christianisme.&lt;/p&gt; &lt;p&gt; Il est souvent appelé le "père du droit international" et ses idées ont jeté les bases de nombreuses institutions internationales modernes, comme les Nations Unies. &lt;/p&gt;  </t>
         </is>
       </c>
-      <c r="F26" s="47" t="inlineStr">
+      <c r="F27" s="47" t="inlineStr">
         <is>
           <t>uu5jJua_J-0</t>
         </is>
       </c>
-      <c r="G26" s="49" t="inlineStr">
+      <c r="G27" s="49" t="inlineStr">
         <is>
           <t>"Hugo GROTIUS par VIS PHILO</t>
         </is>
       </c>
-      <c r="H26" s="49" t="inlineStr">
+      <c r="H27" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/grotius-mini.webp</t>
         </is>
       </c>
-      <c r="I26" s="45" t="n"/>
-      <c r="J26" s="38" t="inlineStr">
+      <c r="I27" s="45" t="n"/>
+      <c r="J27" s="38" t="inlineStr">
         <is>
           <t>Néerlandaise</t>
         </is>
       </c>
-      <c r="K26" s="45" t="inlineStr">
+      <c r="K27" s="45" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="L26" s="46" t="inlineStr">
+      <c r="L27" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme ; Oecuménisme</t>
         </is>
       </c>
-      <c r="M26" s="35" t="inlineStr">
+      <c r="M27" s="35" t="inlineStr">
         <is>
           <t>humaniste hollandais fondateur du droit international moderne.</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="173.25" customHeight="1" s="39">
-      <c r="A27" s="47" t="n">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="173.25" customHeight="1" s="39">
+      <c r="A28" s="47" t="n">
         <v>1585</v>
       </c>
-      <c r="B27" s="47" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
         <is>
           <t>1619</t>
         </is>
       </c>
-      <c r="C27" s="47" t="inlineStr">
+      <c r="C28" s="47" t="inlineStr">
         <is>
           <t>1585 – 1619</t>
         </is>
       </c>
-      <c r="D27" s="48" t="inlineStr">
+      <c r="D28" s="48" t="inlineStr">
         <is>
           <t>Giulo Cesare VANINI</t>
         </is>
       </c>
-      <c r="E27" s="49" t="inlineStr">
+      <c r="E28" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giulio_Cesare_Vanini"  title=" Wikipedia"&gt;Giulo Cesare VANINI&lt;/a&gt; était  un philosophe et libre-penseur italien, précurseur des Lumières et un représentant radical du naturalisme et de l'athéisme. Il s'inscrit dans la &lt;a href="https://www.youtube.com/watch?v=6oiQSoSK8-I" style="color:#88A1E9" title=" 1619, Vanini, un libertin sur le bûcher par Librairie Ombres Blanches "&gt;tradition libertine&lt;/a&gt; et sceptique de la Renaissance, influencé par des auteurs comme Pomponazzi et peut-être par les  &lt;a href="https://www.persee.fr/doc/horma_0984-2616_1999_num_40_1_1801" style="color:#88A1E9" title=" Au déclin de l'averroïsme latin : Giulio Cesare Vanini par Persée"&gt;courants averroïstes&lt;/a&gt; ou épicuriens clandestins. Ses idées marquantes incluent : &lt;/p&gt;
 &lt;p&gt;Naturalisme radical : Il affirme que la nature se suffit à elle-même et qu'il n'est pas nécessaire de recourir à Dieu pour expliquer les phénomènes et suggère que le monde pourrait être éternel et que les religions sont des inventions humaines. &lt;/p&gt; &lt;p&gt;Critique des miracles : Dans De Admirandis, il explique les "miracles" par des causes naturelles ou des supercheries, une position extrêmement dangereuse à l'époque. &lt;/p&gt; &lt;p&gt;Athéisme voilé : Bien qu'il utilise parfois un langage déiste pour se protéger, ses contemporains (comme le philosophe Mersenne) l'ont accusé de promouvoir l'athéisme. Certains passages de ses livres laissent penser qu'il considérait Dieu comme une métaphore de la Nature. &lt;/p&gt; &lt;p&gt;Influence sur le matérialisme : Il anticipe des thèmes qu'on retrouvera chez Spinoza (le Dieu-Nature) ou chez les matérialistes du XVIIIe siècle (comme Diderot). &lt;/p&gt; &lt;p&gt;  
 En 1615, il publie à Lyon "Amphitheatrum Æternæ Providentiæ Divino-Magicum" où il adopte encore une position déiste et, en 1616, son ouvrage "De Admirandis Naturæ Reginæ Deæque Mortalium Arcanis" suscite la controverse : il y développe une &lt;a href="https://www.youtube.com/watch?v=lfSxoWIDe0I" style="color:#88A1E9" title=" "Vanini, 400 ans : liberté de conscience et conscience de la liberté" par Association Item"&gt;philosophie naturaliste&lt;/a&gt;, voire matérialiste, qui nie l'immortalité de l'âme et remet en cause les miracles.&lt;/p&gt; &lt;p&gt;   Arrêté à Toulouse en 1618, il est jugé pour blasphème et athéisme. Refusant d'abjurer, il est condamné à avoir la langue arrachée et à être brûlé vif en place publique en février 1619. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F27" s="47" t="inlineStr">
+      <c r="F28" s="47" t="inlineStr">
         <is>
           <t>jzNjugfduE8</t>
         </is>
       </c>
-      <c r="G27" s="49" t="inlineStr">
+      <c r="G28" s="49" t="inlineStr">
         <is>
           <t>"Cesare VANINI" par Victorio Cuirlia</t>
         </is>
       </c>
-      <c r="H27" s="49" t="inlineStr">
+      <c r="H28" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/vanini-mini.webp</t>
         </is>
       </c>
-      <c r="I27" s="57" t="n"/>
-      <c r="J27" s="38" t="inlineStr">
+      <c r="I28" s="57" t="n"/>
+      <c r="J28" s="38" t="inlineStr">
         <is>
           <t>Italienne</t>
         </is>
       </c>
-      <c r="K27" s="45" t="inlineStr">
+      <c r="K28" s="45" t="inlineStr">
         <is>
           <t>metaphysique</t>
         </is>
       </c>
-      <c r="L27" s="46" t="inlineStr">
+      <c r="L28" s="46" t="inlineStr">
         <is>
           <t>Naturalisme</t>
         </is>
       </c>
-      <c r="M27" s="35" t="inlineStr">
+      <c r="M28" s="35" t="inlineStr">
         <is>
           <t>philosophe et libre-penseur italien représentant radical du naturalisme.</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="137.25" customHeight="1" s="39">
-      <c r="A28" s="47" t="n">
-        <v>1588</v>
-      </c>
-      <c r="B28" s="47" t="inlineStr">
-        <is>
-          <t>1679</t>
-        </is>
-      </c>
-      <c r="C28" s="47" t="inlineStr">
-        <is>
-          <t>1588 - 1679</t>
-        </is>
-      </c>
-      <c r="D28" s="48" t="inlineStr">
-        <is>
-          <t>Thomas HOBBES</t>
-        </is>
-      </c>
-      <c r="E28" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Hobbes"  title=" Wikipedia"&gt;Thomas HOBBES&lt;/a&gt; (1588-1679) est un philosophe anglais, fondateur de la philosophie politique moderne. Né, dit-il, prématurément de la peur de sa mère à l’approche de l’Invincible Armada espagnole, il affirmait : « la peur et moi sommes nés jumeaux. » Précepteur dans la grande famille Cavendish, il voyage en Europe, rencontre Galilée et fréquente à Paris le cercle de Mersenne. Pendant la guerre civile anglaise, il vit en exil en France, de 1640 à 1651.&lt;/p&gt; &lt;p&gt;Hobbes est matérialiste : tout ce qui existe est corps en mouvement, et l’homme lui-même est une mécanique mue par ses désirs et ses craintes. Dans le &lt;a href="https://www.youtube.com/watch?v=8sYAaiDjf0U&amp;ab_channel=AlainBajom%C3%A9e" title="Le Léviathan par Alain Bajomé"&gt;&lt;em&gt;Léviathan&lt;/em&gt;&lt;/a&gt; (1651), il imagine la vie sans État, dans l’« état de nature ». Les hommes y sont à peu près égaux, chacun pouvant tuer l’autre, et la concurrence, la méfiance et l’orgueil les poussent à une « guerre de chacun contre chacun ». La vie y est « solitaire, misérable, dangereuse, animale et brève » : &lt;a href="https://www.youtube.com/watch?v=isCVgDObx4c&amp;ab_channel=LePr%C3%A9cepteur"  title="L'homme est un loup pour l'homme par Le Précepteur"&gt;l’homme est un loup pour l’homme&lt;/a&gt;, selon la formule de Plaute qu’il reprend. Pour échapper à la peur de la mort violente, la raison conseille de rechercher la paix. Les hommes passent donc un contrat par lequel chacun renonce à son droit de tout faire et le transfère à un souverain, un homme ou une assemblée, qui reçoit un pouvoir absolu et indivisible. Ce « dieu mortel », le Léviathan, assure la sécurité de tous ; lui obéir est le prix de la paix. Seul le droit de défendre sa vie ne peut être aliéné.&lt;/p&gt; &lt;p&gt;Accusé d’athéisme, Hobbes fut très critiqué. Mais en fondant le pouvoir sur l’accord des individus plutôt que sur Dieu ou la tradition, il ouvre la voie à Locke et à Rousseau.&lt;/p&gt;  &lt;audio controls title="Le pacte d'obéissance par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22060-04.04.2021-ITEMA_22630431-2012C12410E0123.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F28" s="61" t="inlineStr">
-        <is>
-          <t>jdbtbrJ0jMw</t>
-        </is>
-      </c>
-      <c r="G28" s="49" t="inlineStr">
-        <is>
-          <t>"Thomas Hobbes : le philosophe qui pensait que l’homme est un loup " par Ames profondes</t>
-        </is>
-      </c>
-      <c r="H28" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/hobbes-mini.webp</t>
-        </is>
-      </c>
-      <c r="I28" s="45" t="n"/>
-      <c r="J28" s="55" t="inlineStr">
-        <is>
-          <t>Britannique</t>
-        </is>
-      </c>
-      <c r="K28" s="45" t="inlineStr">
-        <is>
-          <t>politique ; epistemologie</t>
-        </is>
-      </c>
-      <c r="L28" s="46" t="inlineStr">
-        <is>
-          <t>Matérialisme ; Compatibilisme</t>
-        </is>
-      </c>
-      <c r="M28" s="35" t="inlineStr">
-        <is>
-          <t>philosophe anglais qui a eu une grande influence sur la politique moderne.</t>
-        </is>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" ht="157.5" customHeight="1" s="39">
+    </row>
+    <row r="29" ht="137.25" customHeight="1" s="39">
       <c r="A29" s="47" t="n">
         <v>1588</v>
       </c>
       <c r="B29" s="47" t="inlineStr">
         <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>1588 - 1679</t>
+        </is>
+      </c>
+      <c r="D29" s="48" t="inlineStr">
+        <is>
+          <t>Thomas HOBBES</t>
+        </is>
+      </c>
+      <c r="E29" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Hobbes"  title=" Wikipedia"&gt;Thomas HOBBES&lt;/a&gt; (1588-1679) est un philosophe anglais, fondateur de la philosophie politique moderne. Né, dit-il, prématurément de la peur de sa mère à l’approche de l’Invincible Armada espagnole, il affirmait : « la peur et moi sommes nés jumeaux. » Précepteur dans la grande famille Cavendish, il voyage en Europe, rencontre Galilée et fréquente à Paris le cercle de Mersenne. Pendant la guerre civile anglaise, il vit en exil en France, de 1640 à 1651.&lt;/p&gt; &lt;p&gt;Hobbes est matérialiste : tout ce qui existe est corps en mouvement, et l’homme lui-même est une mécanique mue par ses désirs et ses craintes. Dans le &lt;a href="https://www.youtube.com/watch?v=8sYAaiDjf0U&amp;ab_channel=AlainBajom%C3%A9e" title="Le Léviathan par Alain Bajomé"&gt;&lt;em&gt;Léviathan&lt;/em&gt;&lt;/a&gt; (1651), il imagine la vie sans État, dans l’« état de nature ». Les hommes y sont à peu près égaux, chacun pouvant tuer l’autre, et la concurrence, la méfiance et l’orgueil les poussent à une « guerre de chacun contre chacun ». La vie y est « solitaire, misérable, dangereuse, animale et brève » : &lt;a href="https://www.youtube.com/watch?v=isCVgDObx4c&amp;ab_channel=LePr%C3%A9cepteur"  title="L'homme est un loup pour l'homme par Le Précepteur"&gt;l’homme est un loup pour l’homme&lt;/a&gt;, selon la formule de Plaute qu’il reprend. Pour échapper à la peur de la mort violente, la raison conseille de rechercher la paix. Les hommes passent donc un contrat par lequel chacun renonce à son droit de tout faire et le transfère à un souverain, un homme ou une assemblée, qui reçoit un pouvoir absolu et indivisible. Ce « dieu mortel », le Léviathan, assure la sécurité de tous ; lui obéir est le prix de la paix. Seul le droit de défendre sa vie ne peut être aliéné.&lt;/p&gt; &lt;p&gt;Accusé d’athéisme, Hobbes fut très critiqué. Mais en fondant le pouvoir sur l’accord des individus plutôt que sur Dieu ou la tradition, il ouvre la voie à Locke et à Rousseau.&lt;/p&gt;  &lt;audio controls title="Le pacte d'obéissance par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22060-04.04.2021-ITEMA_22630431-2012C12410E0123.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F29" s="61" t="inlineStr">
+        <is>
+          <t>jdbtbrJ0jMw</t>
+        </is>
+      </c>
+      <c r="G29" s="49" t="inlineStr">
+        <is>
+          <t>"Thomas Hobbes : le philosophe qui pensait que l’homme est un loup " par Ames profondes</t>
+        </is>
+      </c>
+      <c r="H29" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/hobbes-mini.webp</t>
+        </is>
+      </c>
+      <c r="I29" s="45" t="n"/>
+      <c r="J29" s="55" t="inlineStr">
+        <is>
+          <t>Britannique</t>
+        </is>
+      </c>
+      <c r="K29" s="45" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L29" s="46" t="inlineStr">
+        <is>
+          <t>Matérialisme ; Compatibilisme</t>
+        </is>
+      </c>
+      <c r="M29" s="35" t="inlineStr">
+        <is>
+          <t>philosophe anglais qui a eu une grande influence sur la politique moderne.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" ht="157.5" customHeight="1" s="39">
+      <c r="A30" s="47" t="n">
+        <v>1588</v>
+      </c>
+      <c r="B30" s="47" t="inlineStr">
+        <is>
           <t>1638</t>
         </is>
       </c>
-      <c r="C29" s="47" t="inlineStr">
+      <c r="C30" s="47" t="inlineStr">
         <is>
           <t>1588 – 1638</t>
         </is>
       </c>
-      <c r="D29" s="48" t="inlineStr">
+      <c r="D30" s="48" t="inlineStr">
         <is>
           <t>Johann Heinrich ALSTED</t>
         </is>
       </c>
-      <c r="E29" s="62" t="inlineStr">
+      <c r="E30" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Heinrich_Alsted"  title=" Wikipedia"&gt;Johann Heinrich ALSTED&lt;/a&gt; était un théologien, philosophe et encyclopédiste protestant calviniste allemand, connu comme un polyhistor et un pionnier des encyclopédies modernes. Né à Ballersbach près d'Herborn, il enseigna la philosophie et la théologie à l'académie calviniste de Herborn, puis à Weissenburg en Transylvanie. Professeur influent, il fut impliqué dans la Synode de Dort et émigra en Transylvanie pour fuir les troubles religieux. Son élève Johann Amos Comenius diffusa largement ses idées en pédagogie et en réformes universelles. Il mourut en 1638, laissant une œuvre marquée par le ramisme, le lullisme et un chiliasme calviniste, &lt;/p&gt; &lt;p&gt; Il distinguait philosophie (raison, foedus naturae) et théologie (révélation, foedus gratiae), tout en cherchant une synthèse universelle des savoirs. Il intégrait logique ramiste, art de la mémoire lulliste et aristotélisme pour ordonner tout le savoir humain, visant une "réforme générale" hermétique et alchimique. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : Encyclopaedia septem tomis distincta (1630) : Son chef-d'œuvre, un "système de tous les systèmes" résumant les disciplines (logique, physique, théologie), loué par ses contemporains. Logicae Systema Harmonicum (1614) : Traité de logique appliquée à l'ensemble des connaissances. Prodromus (1635) : Défense calviniste de la Trinité contre les anti-trinitariens.  Ses encyclopédies influencèrent la pédagogie européenne et les réformateurs du XVIIe siècle.  &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F29" s="47" t="inlineStr">
+      <c r="F30" s="47" t="inlineStr">
         <is>
           <t>lgwdzHapX0I</t>
         </is>
       </c>
-      <c r="G29" s="49" t="inlineStr">
+      <c r="G30" s="49" t="inlineStr">
         <is>
           <t>"Horacio the handsnake - Johann Heinrich Alsted" par Eriq Smith</t>
         </is>
       </c>
-      <c r="H29" s="49" t="inlineStr">
+      <c r="H30" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jhalsted-mini.webp</t>
         </is>
       </c>
-      <c r="I29" s="45" t="n"/>
-      <c r="J29" s="38" t="inlineStr">
+      <c r="I30" s="45" t="n"/>
+      <c r="J30" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K29" s="45" t="inlineStr">
+      <c r="K30" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L29" s="46" t="inlineStr">
+      <c r="L30" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Eclectisme ; Pansophisme</t>
         </is>
       </c>
-      <c r="M29" s="35" t="inlineStr">
+      <c r="M30" s="35" t="inlineStr">
         <is>
           <t>philosophe et encyclopédiste protestant calviniste allemand.</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="102.75" customHeight="1" s="39">
-      <c r="A30" s="47" t="n">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="102.75" customHeight="1" s="39">
+      <c r="A31" s="47" t="n">
         <v>1592</v>
       </c>
-      <c r="B30" s="47" t="inlineStr">
+      <c r="B31" s="47" t="inlineStr">
         <is>
           <t>1655</t>
         </is>
       </c>
-      <c r="C30" s="47" t="inlineStr">
+      <c r="C31" s="47" t="inlineStr">
         <is>
           <t>1592 – 1655</t>
         </is>
       </c>
-      <c r="D30" s="48" t="inlineStr">
+      <c r="D31" s="48" t="inlineStr">
         <is>
           <t>Pierre GASSENDI</t>
         </is>
       </c>
-      <c r="E30" s="58" t="inlineStr">
+      <c r="E31" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Gassendi"  title=" Wikipedia"&gt; Pierre GASSENDI&lt;/a&gt;  était un philosophe, scientifique, astronome et mathématicien français, connu pour &lt;a href="https://www.gassendi.fr/index.php" style="color:#88A1E9" title="Pierre GASSENDI par gassendi.fr "&gt;ses contributions&lt;/a&gt; à la philosophie naturelle, à la renaissance de l'épicurisme et pour ses critiques des philosophies de Descartes et d'Aristote. Il  a été un observateur attentif des phénomènes célestes. Il est notamment connu pour avoir été le premier à observer le transit de Mercure devant le Soleil en 1631, confirmant ainsi les prédictions de Kepler. &lt;/p&gt; &lt;p&gt; Il  a joué un &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1958_num_154_2_8873" title="Pierre GASSENDI par Persée "&gt;rôle clé &lt;/a&gt; dans la réhabilitation de la philosophie d'Épicure, qu'il a adaptée à un contexte chrétien. Il a défendu une vision atomiste de la nature, mais a rejeté les aspects matérialistes et athées de l'épicurisme antique. Il a plaidé pour une approche empirique de la connaissance, insistant sur l'importance de l'observation et de l'expérience. &lt;/p&gt; &lt;p&gt; Il a influencé des penseurs ultérieurs tels que John Locke et Isaac Newton. Son empirisme et son atomisme ont contribué au développement de la philosophie naturelle moderne tout en cherchant à concilier la science naissante avec la foi chrétienne, montrant que les découvertes scientifiques pouvaient être compatibles avec une vision religieuse du monde. Né en Provence en 1592, prêtre, professeur de philosophie à Aix puis de mathématiques au Collège royal de Paris, il est l’ami de Mersenne. Il rédige les cinquièmes &lt;em&gt;Objections&lt;/em&gt; aux &lt;em&gt;Méditations&lt;/em&gt; de Descartes, auquel il reproche de s’éloigner de l’expérience : Descartes l’appelle « Ô chair », Gassendi lui répond « Ô esprit ». Pour lui, les atomes ont été créés par Dieu en nombre fini, et l’âme raisonnable reste immatérielle. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F30" s="47" t="inlineStr">
+      <c r="F31" s="47" t="inlineStr">
         <is>
           <t>Y4u4YMwcs-E</t>
         </is>
       </c>
-      <c r="G30" s="49" t="inlineStr">
+      <c r="G31" s="49" t="inlineStr">
         <is>
           <t>"Pierre GASSENDI" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H30" s="49" t="inlineStr">
+      <c r="H31" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/gassendi-mini.webp</t>
         </is>
       </c>
-      <c r="I30" s="45" t="n"/>
-      <c r="J30" s="38" t="inlineStr">
+      <c r="I31" s="45" t="n"/>
+      <c r="J31" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K30" s="45" t="inlineStr">
+      <c r="K31" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; metaphysique</t>
         </is>
       </c>
-      <c r="L30" s="46" t="inlineStr">
+      <c r="L31" s="46" t="inlineStr">
         <is>
           <t>Empirisme ; Epicurisme</t>
         </is>
       </c>
-      <c r="M30" s="35" t="inlineStr">
+      <c r="M31" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour avoir réintroduit la notion d'atome et défendu le vide.</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="132" customHeight="1" s="39">
-      <c r="A31" s="47" t="n">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="132" customHeight="1" s="39">
+      <c r="A32" s="47" t="n">
         <v>1592</v>
       </c>
-      <c r="B31" s="47" t="inlineStr">
+      <c r="B32" s="47" t="inlineStr">
         <is>
           <t>1670</t>
         </is>
       </c>
-      <c r="C31" s="47" t="inlineStr">
+      <c r="C32" s="47" t="inlineStr">
         <is>
           <t>1592 – 1670</t>
         </is>
       </c>
-      <c r="D31" s="48" t="inlineStr">
+      <c r="D32" s="48" t="inlineStr">
         <is>
           <t>COMENIUS</t>
         </is>
       </c>
-      <c r="E31" s="60" t="inlineStr">
+      <c r="E32" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Comenius"  title=" Wikipedia"&gt;COMENIUS&lt;/a&gt;   de son nom tchèque Jan Amos Komenský, était un philosophe, théologien et pédagogue tchèque, considéré comme le père de la pédagogie moderne. Évêque des Frères moraves, il fuit les persécutions religieuses et erra en Europe, promouvant une éducation universelle &lt;a href="https://www.youtube.com/watch?v=oGscXWKpLAA"  title="comment donner accès à tous les savoirs par Benoit Urgelli"&gt;accessible à tous, &lt;/a&gt; y compris aux filles et aux pauvres. &lt;/p&gt; &lt;p&gt; Orphelin jeune, il étudie à Herborn, puis à l’université de Heidelberg et devient enseignant dans les écoles moraves. Exilé après la bataille de la Montagne Blanche (1620), il enseigne à Lissa, Amsterdam et ailleurs, influencé par Alsted dont il fut l’élève. Il meurt à Naarden aux Pays-Bas, rêvant d’une restauration de son pays. Sa &lt;em&gt;Porte des langues ouverte&lt;/em&gt; (1631), méthode qui enseigne le latin à partir des choses, est traduite dans de nombreuses langues et le rend célèbre dans toute l’Europe ; il est appelé en Angleterre, en Suède et en Transylvanie pour réformer les écoles. &lt;/p&gt; &lt;p&gt; Il  prône une "pansophie" : une sagesse universelle enseignant tout à tous via la nature, la raison et la révélation divine. Il rejette les châtiments corporels, favorise l’apprentissage naturel, ludique et progressif (du sensoriel à l’abstrait), avec &lt;a href="https://www.youtube.com/watch?v=CMFh0seMZUg"  title="The dramatic story on education par Czech the History"&gt;des écoles pour tous &lt;/a&gt; les âges et sexes. &lt;/p&gt; &lt;p&gt; Ses œuvres majeures : &lt;em&gt;Didactica Magna&lt;/em&gt; (1657) : Traité sur l’art  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1969_num_49_1_3943"  title="Jean Amos COMENIUS par Persée"&gt; d’enseigner universellement, &lt;/a&gt; sans violence. &lt;em&gt;Orbis sensualium pictus&lt;/em&gt; (1658) : Premier manuel illustré bilingue pour enfants, associant mots et images. De Rerum Humanarum Emendatione : Consultation catholique pour une réforme mondiale du savoir et de la paix. Ses idées inspirèrent l’éducation européenne et l’UNESCO le nomme "Père de l’éducation". &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F31" s="47" t="inlineStr">
+      <c r="F32" s="47" t="inlineStr">
         <is>
           <t>oGscXWKpLAA</t>
         </is>
       </c>
-      <c r="G31" s="49" t="inlineStr">
+      <c r="G32" s="49" t="inlineStr">
         <is>
           <t>"Comment donner accès à tous les savoirs du monde ? Jan Amos KOMENSKY - COMENIUS - selon P. Meirieu" par Benoit Urgelli</t>
         </is>
       </c>
-      <c r="H31" s="49" t="inlineStr">
+      <c r="H32" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/comenius-mini.webp</t>
         </is>
       </c>
-      <c r="I31" s="57" t="n"/>
-      <c r="J31" s="38" t="inlineStr">
+      <c r="I32" s="57" t="n"/>
+      <c r="J32" s="38" t="inlineStr">
         <is>
           <t>Tchèque</t>
         </is>
       </c>
-      <c r="K31" s="45" t="inlineStr">
+      <c r="K32" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; ethique</t>
         </is>
       </c>
-      <c r="L31" s="46" t="inlineStr">
+      <c r="L32" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Humanisme ; Pansophisme ; Oecuménisme</t>
         </is>
       </c>
-      <c r="M31" s="35" t="inlineStr">
+      <c r="M32" s="35" t="inlineStr">
         <is>
           <t>philosophe, théologien tchèque, considéré comme le père de la pédagogie moderne.</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="223.5" customHeight="1" s="39">
-      <c r="A32" s="47" t="n">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="223.5" customHeight="1" s="39">
+      <c r="A33" s="47" t="n">
         <v>1596</v>
       </c>
-      <c r="B32" s="47" t="inlineStr">
+      <c r="B33" s="47" t="inlineStr">
         <is>
           <t>1650</t>
         </is>
       </c>
-      <c r="C32" s="47" t="inlineStr">
+      <c r="C33" s="47" t="inlineStr">
         <is>
           <t>1596 - 1650</t>
         </is>
       </c>
-      <c r="D32" s="48" t="inlineStr">
+      <c r="D33" s="48" t="inlineStr">
         <is>
           <t>René DESCARTES</t>
         </is>
       </c>
-      <c r="E32" s="63" t="inlineStr">
+      <c r="E33" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Descartes"  title=" Wikipedia"&gt;René DESCARTES&lt;/a&gt; était un philosophe et marthématicien Français considéré comme un pionnier de la philosophie &lt;a href="https://la-philosophie.com/philosophie-lumieres"  title="La philosophie des Lumières par la-philosophie.com"&gt;des lumières&lt;/a&gt;  et de la science moderne.&lt;/p&gt; &lt;p&gt; Il est surtout connu pour sa phrase célèbre &lt;a href="https://www.youtube.com/watch?v=OjKY5Okx9wQ&amp;ab_channel=LePr%C3%A9cepteur"  title="Je pense donc je suis par le Précepteur"&gt;"Je pense, donc je suis"&lt;/a&gt; (en latin "Cogito, ergo sum"), qui a été prononcée dans son œuvre phare  &lt;a href="https://www.youtube.com/watch?v=cGrhiO0CECs"  title="Le Discours de la méthode par Essences des Livres"&gt;"Discours de la méthode"&lt;/a&gt; écrite en 1637.  Issu d'une famille noble, il étudie au collège jésuite de La Flèche, puis à Poitiers où il obtient une licence en droit en 1616. Il voyage en Europe, sert dans l'armée, vit à Amsterdam en exil volontaire pour la liberté de pensée, et meurt à Stockholm invité par la reine Christine de Suède, probablement d'une pneumonie due au froid.  &lt;/p&gt;&lt;p&gt; &lt;a href="https://www.youtube.com/@paroledephilosophe/search?query=descartes"  title="La philosophie de Descartes par Parole de philosophe"&gt;Sa pensée &lt;/a&gt; est basée sur l'idée que la connaissance doit être fondée sur la raison et la logique, plutôt que sur la tradition ou l'autorité et que la science doit être basée sur des mathématiques rigoureuses, ce qui a conduit à l'adoption de la géométrie dans les sciences naturelles. &lt;/p&gt; &lt;p&gt;Il a également formulé une théorie de la dualité de la nature, selon laquelle l'univers est divisé en deux parties distinctes : la matière et l'esprit. Selon cette théorie, la matière est soumise aux lois de la physique, tandis que l'esprit est libre et capable de penser par lui-même. Il applique le doute hyperbolique (sur les sens, le rêve, un "malin génie") pour atteindre l'évidence : "Je pense, donc je suis", prouvant l'existence de l'ego cogitans (esprit pensant). Il distingue res cogitans (pensée immatérielle) et res extensa (matière étendue), fondant le dualisme cartésien, et conçoit Dieu comme garant de la vérité claire et distincte. Sa physique mécaniste voit l'univers comme une machine divine, préfigurant la science moderne. /p&gt; &lt;p&gt;En plus de ses contributions à la philosophie et à la science, il  a également écrit sur de nombreux autres sujets, notamment la métaphysique, &lt;a href="https://www.youtube.com/watch?v=BFFa7fHv_1I&amp;ab_channel=LePr%C3%A9cepteur"  title="Sommes nous vraimant libre par le Précepteur"&gt;la liberté&lt;/a&gt;,  &lt;a href="https://www.youtube.com/watch?v=dykLwHWB7qk&amp;ab_channel=LePr%C3%A9cepteur"  title="Peut on prouver l'existence de Dieu par le Précepteur"&gt;l'existence de Dieu&lt;/a&gt;, la théologie et la politique. &lt;/p&gt; &lt;p&gt;Il était en opposition totale avec la pensée de Spinoza car ils conçoivent l'union de l'âme et du corps de manière très différente. Tandis que Descartes voit deux substances qui agissent l'une sur l'autre, pour Spinoza, c'est une seule et même chose, vue sous deux aspects différents.&lt;/p&gt;  
  &lt;audio controls title="meditations metaphysiques rené Descartes  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22789-31.10.2025-ITEMA_24296808-2025C53456E0008-NET_MFC_2769CAD8-FF20-4C7A-AB24-4D8965BD8B85-21-07dab51b3250d9a22eaab62a5c04edeb.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F32" s="47" t="inlineStr">
+      <c r="F33" s="47" t="inlineStr">
         <is>
           <t>lG70S2cOGJ0</t>
         </is>
       </c>
-      <c r="G32" s="49" t="inlineStr">
+      <c r="G33" s="49" t="inlineStr">
         <is>
           <t>"Le genie qui doutait de tout: l'incroyable histoire de Descartes" par Essence des Livres</t>
         </is>
       </c>
-      <c r="H32" s="49" t="inlineStr">
+      <c r="H33" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/descarte-mini.webp</t>
         </is>
       </c>
-      <c r="I32" s="45" t="n"/>
-      <c r="J32" s="38" t="inlineStr">
+      <c r="I33" s="45" t="n"/>
+      <c r="J33" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K32" s="45" t="inlineStr">
+      <c r="K33" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L32" s="46" t="inlineStr">
+      <c r="L33" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme ; Dualisme ; Anthropocentrisme ; Méthodisme</t>
         </is>
       </c>
-      <c r="M32" s="35" t="inlineStr">
+      <c r="M33" s="35" t="inlineStr">
         <is>
           <t>philosophe français qui proposa d'atteindre la vérité par la raison.</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P32">
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P33">
         <v>3</v>
       </c>
     </row>
-    <row r="33" ht="220.5" customHeight="1" s="39">
-      <c r="A33" s="47" t="n">
+    <row r="34" ht="220.5" customHeight="1" s="39">
+      <c r="A34" s="47" t="n">
         <v>1604</v>
       </c>
-      <c r="B33" s="47" t="inlineStr">
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>1658</t>
         </is>
       </c>
-      <c r="C33" s="47" t="inlineStr">
+      <c r="C34" s="47" t="inlineStr">
         <is>
           <t>1604 – 1658</t>
         </is>
       </c>
-      <c r="D33" s="48" t="inlineStr">
+      <c r="D34" s="48" t="inlineStr">
         <is>
           <t>Baltazar GRACIAN</t>
         </is>
       </c>
-      <c r="E33" s="62" t="inlineStr">
+      <c r="E34" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baltasar_Graci%C3%A1n" title=" Wikipedia"&gt;Baltazar GRACIAN&lt;/a&gt;  était un philosophe, moraliste, écrivain et jésuite espagnol du Siècle d’or, célèbre pour son style très dense et pour sa réflexion sur &lt;a href="https://www.youtube.com/watch?v=mo8tYs5W_MA"  title="L’art de la prudence par le Mental Parfait"&gt; la prudence, &lt;/a&gt; la conduite de la vie et la lucidité face au monde. On le considère comme l’un des grands représentants du conceptisme, un art de l’écriture qui concentre beaucoup d’idées en très peu de mots. Il entre chez les jésuites à 18 ans, devient prêtre, puis enseigne et exerce diverses fonctions dans la Compagnie de Jésus. Sa carrière fut parfois tendue avec ses supérieurs, car il publia plusieurs œuvres sans toujours respecter la discipline de l’ordre. &lt;/p&gt; &lt;p&gt; Il  voit la société comme un espace difficile où il faut apprendre à se défendre, à juger vite et à agir avec finesse. Sa philosophie est souvent sombre et réaliste : il insiste sur l’intelligence pratique, la discrétion, le tact et la capacité à lire les intentions des autres. &lt;/p&gt; &lt;p&gt; Ses Œuvres importantes : El héroe (1637) : réflexion sur le modèle du héros capable de réussir dans la vie sociale. El político don Fernando el Católico (1640) : traité sur l’art de gouverner. El discreto (1646) : idéal de l’homme accompli et prudent. Oráculo manual y arte de prudencia (1647) : son livre le plus célèbre, composé de maximes sur l’art de vivre. &lt;a href="https://www.youtube.com/watch?v=qD8Ji701jrU"  title="l’homme de cours par VoixLibris"&gt;El Criticón &lt;/a&gt; (1651-1657) : son grand roman philosophique, très critique envers la société humaine. &lt;/p&gt; &lt;p&gt; Il  a marqué durablement la pensée morale européenne par son mélange de philosophie, de littérature et de stratégie sociale. Son influence a été reconnue bien plus tard par des penseurs comme Schopenhauer, qui admirait particulièrement El Criticón.  &lt;/p&gt;  &lt;audio controls title="Baltazar Grancian ou l’art du travestissement par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.05.2016-ITEMA_20975945-2016C12410S0124-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F33" s="47" t="inlineStr">
+      <c r="F34" s="47" t="inlineStr">
         <is>
           <t>Y24lm4leVXU</t>
         </is>
       </c>
-      <c r="G33" s="49" t="inlineStr">
+      <c r="G34" s="49" t="inlineStr">
         <is>
           <t>"comment les gens intelligents contrôlent leur image Baltasar Gracián " par Le Prince</t>
         </is>
       </c>
-      <c r="H33" s="49" t="inlineStr">
+      <c r="H34" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bgracian-mini.webp</t>
-        </is>
-      </c>
-      <c r="I33" s="45" t="n"/>
-      <c r="J33" s="38" t="inlineStr">
-        <is>
-          <t>Espagnole</t>
-        </is>
-      </c>
-      <c r="K33" s="45" t="inlineStr">
-        <is>
-          <t>ethique</t>
-        </is>
-      </c>
-      <c r="L33" s="46" t="inlineStr">
-        <is>
-          <t>Humanisme</t>
-        </is>
-      </c>
-      <c r="M33" s="35" t="inlineStr">
-        <is>
-          <t>philosophe espagnol connu pour sa réflexion sur la prudence et la lucidité.</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="346.5" customHeight="1" s="39">
-      <c r="A34" s="47" t="n">
-        <v>1612</v>
-      </c>
-      <c r="B34" s="47" t="n">
-        <v>1694</v>
-      </c>
-      <c r="C34" s="47" t="inlineStr">
-        <is>
-          <t>1612 – 1694</t>
-        </is>
-      </c>
-      <c r="D34" s="48" t="inlineStr">
-        <is>
-          <t>Antoine ARNAULD</t>
-        </is>
-      </c>
-      <c r="E34" s="60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine_Arnauld_(1612-1694)" title=" Wikipedia"&gt;Antoine ARNAULD&lt;/a&gt; surnommé le « Grand Arnauld », était un philosophe, théologien, logicien et mathématicien français, l’une des principales figures de Port-Royal et du jansénisme, courant catholique fortement marqué par la pensée de saint Augustin. Il défendait l’idée que l’être humain, affaibli par le péché, ne peut parvenir au salut par ses seules forces : la grâce divine est indispensable et ne dépend pas simplement du mérite humain. Cette position l’opposa notamment aux jésuites et au molinisme, qui accordaient une place plus importante à la liberté humaine. &lt;/p&gt; &lt;p&gt; Sa philosophie est généralement rattachée au cartésianisme, même s’il ne fut pas un disciple passif de Descartes. Il partageait avec lui l’importance  &lt;a href="https://www.youtube.com/watch?v=EehtChJtFV0"  title="Arnaud et Nicole , la logique ou l’art de pensée par Sobrecrate"&gt; accordée à la raison, &lt;/a&gt; à la clarté des idées et à la recherche de certitudes premières. Il intervint d’ailleurs dans les débats suscités par les Méditations métaphysiques, en formulant la célèbre objection du « cercle cartésien » : comment Descartes peut-il garantir la vérité des idées claires et distinctes par Dieu, si la preuve de l’existence de Dieu repose elle-même sur ces idées ? Cette critique témoigne de son exigence logique et de son attention aux fondements de la connaissance. &lt;/p&gt; &lt;p&gt; Son œuvre la plus célèbre est la Logique ou l’art de penser, publiée en 1662 avec Pierre Nicole et souvent appelée « Logique de Port-Royal ». Ce livre ne se contente pas de présenter des règles formelles : il cherche à apprendre à bien penser, à bien juger et à éviter les erreurs du raisonnement. La logique y est ainsi conçue comme une discipline de l’esprit, liée à la psychologie de la connaissance et à la morale intellectuelle. Les auteurs analysent les idées, les propositions et les raisonnements, tout en soulignant que le langage doit exprimer correctement la pensée. L’ouvrage connut une influence considérable dans l’enseignement européen pendant près de deux siècles. &lt;/p&gt; &lt;p&gt; Il développa également une &lt;a href="https://encyclo-philo.fr/antoine-arnauld-a"  title="Arnaud par l’encyclopédie philosophique"&gt;théorie des idées &lt;/a&gt;  et de la perception, notamment dans sa polémique avec Malebranche. Il refusa l’idée selon laquelle nous connaîtrions directement les choses uniquement à travers des idées présentes dans l’esprit ou en Dieu. Il soutenait davantage une conception réaliste : nos idées peuvent nous mettre en rapport avec des objets extérieurs, même si cette connaissance doit être examinée avec prudence. Cette position l’amena à défendre le rôle de l’expérience et du sens commun contre certaines formes de rationalisme métaphysique qu’il jugeait excessives. Il participa ainsi aux débats qui allaient conduire, plus tard, aux philosophies modernes de la connaissance. &lt;/p&gt; &lt;p&gt; Sa pensée se caractérise donc par l’alliance de trois exigences : la fidélité à l’augustinisme chrétien, la confiance dans la raison cartésienne et le souci d’une méthode rigoureuse du jugement. Il ne sépare pas complètement philosophie, théologie et logique : la raison doit rechercher la vérité, mais elle doit aussi reconnaître ses limites et la dépendance de l’homme à l’égard de la grâce. Il apparaît ainsi comme une figure majeure du rationalisme religieux du XVIIᵉ siècle, située entre Descartes, Pascal, Malebranche et Leibniz, et comme l’un des grands artisans de la culture intellectuelle de Port-Royal. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F34" s="47" t="inlineStr">
-        <is>
-          <t>n6-KA6Q9J0g</t>
-        </is>
-      </c>
-      <c r="G34" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Antoine Arnauld par VIS PHILO</t>
-        </is>
-      </c>
-      <c r="H34" s="58" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/aarnauld-mini.webp</t>
         </is>
       </c>
       <c r="I34" s="45" t="n"/>
       <c r="J34" s="38" t="inlineStr">
         <is>
+          <t>Espagnole</t>
+        </is>
+      </c>
+      <c r="K34" s="45" t="inlineStr">
+        <is>
+          <t>ethique</t>
+        </is>
+      </c>
+      <c r="L34" s="46" t="inlineStr">
+        <is>
+          <t>Humanisme</t>
+        </is>
+      </c>
+      <c r="M34" s="35" t="inlineStr">
+        <is>
+          <t>philosophe espagnol connu pour sa réflexion sur la prudence et la lucidité.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="346.5" customHeight="1" s="39">
+      <c r="A35" s="47" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B35" s="47" t="n">
+        <v>1694</v>
+      </c>
+      <c r="C35" s="47" t="inlineStr">
+        <is>
+          <t>1612 – 1694</t>
+        </is>
+      </c>
+      <c r="D35" s="48" t="inlineStr">
+        <is>
+          <t>Antoine ARNAULD</t>
+        </is>
+      </c>
+      <c r="E35" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine_Arnauld_(1612-1694)" title=" Wikipedia"&gt;Antoine ARNAULD&lt;/a&gt; surnommé le « Grand Arnauld », était un philosophe, théologien, logicien et mathématicien français, l’une des principales figures de Port-Royal et du jansénisme, courant catholique fortement marqué par la pensée de saint Augustin. Il défendait l’idée que l’être humain, affaibli par le péché, ne peut parvenir au salut par ses seules forces : la grâce divine est indispensable et ne dépend pas simplement du mérite humain. Cette position l’opposa notamment aux jésuites et au molinisme, qui accordaient une place plus importante à la liberté humaine. &lt;/p&gt; &lt;p&gt; Sa philosophie est généralement rattachée au cartésianisme, même s’il ne fut pas un disciple passif de Descartes. Il partageait avec lui l’importance  &lt;a href="https://www.youtube.com/watch?v=EehtChJtFV0"  title="Arnaud et Nicole , la logique ou l’art de pensée par Sobrecrate"&gt; accordée à la raison, &lt;/a&gt; à la clarté des idées et à la recherche de certitudes premières. Il intervint d’ailleurs dans les débats suscités par les Méditations métaphysiques, en formulant la célèbre objection du « cercle cartésien » : comment Descartes peut-il garantir la vérité des idées claires et distinctes par Dieu, si la preuve de l’existence de Dieu repose elle-même sur ces idées ? Cette critique témoigne de son exigence logique et de son attention aux fondements de la connaissance. &lt;/p&gt; &lt;p&gt; Son œuvre la plus célèbre est la Logique ou l’art de penser, publiée en 1662 avec Pierre Nicole et souvent appelée « Logique de Port-Royal ». Ce livre ne se contente pas de présenter des règles formelles : il cherche à apprendre à bien penser, à bien juger et à éviter les erreurs du raisonnement. La logique y est ainsi conçue comme une discipline de l’esprit, liée à la psychologie de la connaissance et à la morale intellectuelle. Les auteurs analysent les idées, les propositions et les raisonnements, tout en soulignant que le langage doit exprimer correctement la pensée. L’ouvrage connut une influence considérable dans l’enseignement européen pendant près de deux siècles. &lt;/p&gt; &lt;p&gt; Il développa également une &lt;a href="https://encyclo-philo.fr/antoine-arnauld-a"  title="Arnaud par l’encyclopédie philosophique"&gt;théorie des idées &lt;/a&gt;  et de la perception, notamment dans sa polémique avec Malebranche. Il refusa l’idée selon laquelle nous connaîtrions directement les choses uniquement à travers des idées présentes dans l’esprit ou en Dieu. Il soutenait davantage une conception réaliste : nos idées peuvent nous mettre en rapport avec des objets extérieurs, même si cette connaissance doit être examinée avec prudence. Cette position l’amena à défendre le rôle de l’expérience et du sens commun contre certaines formes de rationalisme métaphysique qu’il jugeait excessives. Il participa ainsi aux débats qui allaient conduire, plus tard, aux philosophies modernes de la connaissance. &lt;/p&gt; &lt;p&gt; Sa pensée se caractérise donc par l’alliance de trois exigences : la fidélité à l’augustinisme chrétien, la confiance dans la raison cartésienne et le souci d’une méthode rigoureuse du jugement. Il ne sépare pas complètement philosophie, théologie et logique : la raison doit rechercher la vérité, mais elle doit aussi reconnaître ses limites et la dépendance de l’homme à l’égard de la grâce. Il apparaît ainsi comme une figure majeure du rationalisme religieux du XVIIᵉ siècle, située entre Descartes, Pascal, Malebranche et Leibniz, et comme l’un des grands artisans de la culture intellectuelle de Port-Royal. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F35" s="47" t="inlineStr">
+        <is>
+          <t>n6-KA6Q9J0g</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antoine Arnauld par VIS PHILO</t>
+        </is>
+      </c>
+      <c r="H35" s="58" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/aarnauld-mini.webp</t>
+        </is>
+      </c>
+      <c r="I35" s="45" t="n"/>
+      <c r="J35" s="38" t="inlineStr">
+        <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K34" s="45" t="inlineStr">
+      <c r="K35" s="45" t="inlineStr">
         <is>
           <t>spiritualite</t>
         </is>
       </c>
-      <c r="L34" s="46" t="inlineStr">
+      <c r="L35" s="46" t="inlineStr">
         <is>
           <t>Jansénisme ; Cartésianisme ; Rationalisme</t>
         </is>
       </c>
-      <c r="M34" s="59" t="inlineStr">
+      <c r="M35" s="59" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe, théologien, logicien et mathématicien français, figure du jansénisme.</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="228" customHeight="1" s="39">
-      <c r="A35" s="47" t="n">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="228" customHeight="1" s="39">
+      <c r="A36" s="47" t="n">
         <v>1623</v>
       </c>
-      <c r="B35" s="47" t="inlineStr">
+      <c r="B36" s="47" t="inlineStr">
         <is>
           <t>1662</t>
         </is>
       </c>
-      <c r="C35" s="47" t="inlineStr">
+      <c r="C36" s="47" t="inlineStr">
         <is>
           <t>1623 - 1662</t>
         </is>
       </c>
-      <c r="D35" s="48" t="inlineStr">
+      <c r="D36" s="48" t="inlineStr">
         <is>
           <t>Blaise PASCAL</t>
         </is>
       </c>
-      <c r="E35" s="58" t="inlineStr">
+      <c r="E36" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Blaise_Pascal" title="Blaise PASCAL par Wikipédia"&gt; Blaise PASCAL&lt;/a&gt;  était un mathématicien, philosophe et écrivain français. Il a inventé à 19 ans, la première calculatrice mécanique, connue sous le nom de "machine de Pascal". Il fut ensuite célèbre pour son &lt;a href="https://blaisepascal.bibliotheques-clermontmetropole.eu/son-oeuvre/pascal-savant/mathematiques/le-triangle-arithmetique"  title="Le triangle arithmétique par Clermont metropole"&gt; "Triangle de Pascal"&lt;/a&gt;, un arrangement de nombres qui est devenu un élément fondamental de la théorie des probabilités et de l'algèbre combinatoire. Il a aussi étudié la pression atmosphérique et a contribué à la compréhension de la manière dont la pression varie avec l'altitude. L'unité de pression "pascal" (Pa) porte son nom.  &lt;/p&gt; &lt;p&gt;
 Il était un chrétien dévot, et sa philosophie a été profondément influencée par sa foi. Il a écrit &lt;a href="https://www.youtube.com/watch?v=3uIjGv6jfSE&amp;ab_channel=Kosmos"   title="Pensées par Kosmos"&gt; "Pensées"&lt;/a&gt;, ce recueil de pensées, d'aphorismes et de réflexions où  Il a développé l'argument connu sous le nom de &lt;a href="https://www.youtube.com/watch?v=FoWFLpm8eX0&amp;ab_channel=AlainBajom%C3%A9e"  title="Le pari de Pascal par Alain Bajomée"&gt; "pari de Pascal,"&lt;/a&gt; qui suggère que, même en l'absence de preuves rationnelles concluantes de l'existence de Dieu, il est plus raisonnable de &lt;a href="https://www.youtube.com/watch?v=6KLWy3dWFMw&amp;ab_channel=LePr%C3%A9cepteur"   title="le pari par Le Précepteur"&gt;parier sur son existence&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;   &lt;p&gt;
@@ -2936,381 +3002,312 @@
 &lt;p&gt;La critique du rationalisme excessif :  qui réduisait toute connaissance à la raison et à la logique. Il croyait que la raison seule ne pouvait pas répondre à toutes les questions importantes de la vie et que l'expérience émotionnelle et spirituelle était tout aussi cruciale. &lt;/p&gt;  &lt;audio controls title="Blaise Pascal, vers l'infini et au-delà par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-24.09.2018-ITEMA_21822263-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F35" s="47" t="inlineStr">
+      <c r="F36" s="47" t="inlineStr">
         <is>
           <t>QGCu4dlNII4</t>
         </is>
       </c>
-      <c r="G35" s="49" t="inlineStr">
+      <c r="G36" s="49" t="inlineStr">
         <is>
           <t>"Pascal: le génie qui eut peur de sa propre raison" par Voyages Endormis</t>
         </is>
       </c>
-      <c r="H35" s="49" t="inlineStr">
+      <c r="H36" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/pascal-mini.webp</t>
         </is>
       </c>
-      <c r="I35" s="45" t="n"/>
-      <c r="J35" s="38" t="inlineStr">
+      <c r="I36" s="45" t="n"/>
+      <c r="J36" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K35" s="45" t="inlineStr">
+      <c r="K36" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="L35" s="46" t="inlineStr">
+      <c r="L36" s="46" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="M35" s="35" t="inlineStr">
+      <c r="M36" s="35" t="inlineStr">
         <is>
           <t>philosophe et mathématicien français pris entre pessimisme et scepticisme.</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P35">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P36">
         <v>3</v>
       </c>
     </row>
-    <row r="36" ht="180" customHeight="1" s="39">
-      <c r="A36" s="47" t="n">
+    <row r="37" ht="180" customHeight="1" s="39">
+      <c r="A37" s="47" t="n">
         <v>1624</v>
       </c>
-      <c r="B36" s="47" t="inlineStr">
+      <c r="B37" s="47" t="inlineStr">
         <is>
           <t>1669</t>
         </is>
       </c>
-      <c r="C36" s="47" t="inlineStr">
+      <c r="C37" s="47" t="inlineStr">
         <is>
           <t>1624 – 1669</t>
         </is>
       </c>
-      <c r="D36" s="48" t="inlineStr">
+      <c r="D37" s="48" t="inlineStr">
         <is>
           <t>Arnold GEULINCX</t>
         </is>
       </c>
-      <c r="E36" s="62" t="inlineStr">
+      <c r="E37" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Arnold_Geulincx"  style="color:#6A142A"  title=" Wikipedia"&gt;Arnold GEULINCX&lt;/a&gt;  était un philosophe flamand, disciple radical de Descartes et pionnier de  &lt;a href="https://fr.wikipedia.org/wiki/Occasionnalisme" title="occasionnalisme par Wikipedia"&gt;l'occasionnalisme, &lt;/a&gt; une doctrine niant toute causalité entre l'âme et le corps. Né à Anvers, il enseigna à Louvain avant d'être destitué pour sympathies jansénistes, puis à Leyde où il mourut de la peste à 45 ans. Étudiant en &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1910_num_17_65_4252" title="Arnold Geulincx et le procès de la philosophie par Persée"&gt;philosophie et théologie &lt;/a&gt; à Louvain, il devint professeur mais fut exilé pour hérésie présumée. À Leyde dès 1665, il développa sa pensée dans l'ombre de Descartes, influençant plus tard des auteurs comme Samuel Beckett avec sa maxime "Ubi nihil vales, ibi nihil velis" ("Là où tu ne vaux rien, là ne veuille rien"). &lt;/p&gt; &lt;p&gt; Il  radicalise le dualisme cartésien : l'esprit (res cogitans) et le corps (res extensa) sont deux substances séparées sans interaction causale directe, synchronisées par Dieu comme deux horloges divinement accordées. Principe clé : "Quod nescis quomodo fiat, id non facis" ("Ce que tu ignores comment ça se fait, tu ne le fais pas") – nous ne causons rien, car nous ignorons les mécanismes ; Dieu est la seule cause universelle. Son éthique repose sur l'"inspectio sui" (auto-examen humble) et une soumission joyeuse à l'impuissance humaine face à la volonté divine. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : Disputatio ethica de furore (1665) : Sur la fureur et la maîtrise de soi. – Gnothi seauton ou Ethica (1675, posth.) : Éthique centrée sur l'humilité et la vertu, &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F36" s="47" t="inlineStr">
+      <c r="F37" s="47" t="inlineStr">
         <is>
           <t>Ex6xuUYwlIk</t>
         </is>
       </c>
-      <c r="G36" s="49" t="inlineStr">
+      <c r="G37" s="49" t="inlineStr">
         <is>
           <t>"Arnold Geulincx: Unraveling the Mind-Body Mystery" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H36" s="49" t="inlineStr">
+      <c r="H37" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/geulincx-mini.webp</t>
         </is>
       </c>
-      <c r="I36" s="45" t="n"/>
-      <c r="J36" s="38" t="inlineStr">
+      <c r="I37" s="45" t="n"/>
+      <c r="J37" s="38" t="inlineStr">
         <is>
           <t>Belge</t>
         </is>
       </c>
-      <c r="K36" s="45" t="inlineStr">
+      <c r="K37" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="L36" s="46" t="inlineStr">
+      <c r="L37" s="46" t="inlineStr">
         <is>
           <t>Occasionalisme</t>
         </is>
       </c>
-      <c r="M36" s="35" t="inlineStr">
+      <c r="M37" s="35" t="inlineStr">
         <is>
           <t>philosophe flamand disciple radical de Descartes et pionnier de l'occasionnalisme.</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="199.5" customHeight="1" s="39">
-      <c r="A37" s="47" t="n">
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="199.5" customHeight="1" s="39">
+      <c r="A38" s="47" t="n">
         <v>1625</v>
       </c>
-      <c r="B37" s="47" t="inlineStr">
+      <c r="B38" s="47" t="inlineStr">
         <is>
           <t>1699</t>
         </is>
       </c>
-      <c r="C37" s="47" t="inlineStr">
+      <c r="C38" s="47" t="inlineStr">
         <is>
           <t>1625 – 1699</t>
         </is>
       </c>
-      <c r="D37" s="48" t="inlineStr">
+      <c r="D38" s="48" t="inlineStr">
         <is>
           <t>Erhard WEIGEL</t>
         </is>
       </c>
-      <c r="E37" s="62" t="inlineStr">
+      <c r="E38" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Erhard_Weigel" title=" Wikipedia"&gt;Erhard WEIGEL&lt;/a&gt;  était un mathématicien, philosophe et astronome allemand, professeur à l'université de Iéna, connu pour ses tentatives de fonder une &lt;a href="https://fr.wikipedia.org/wiki/Pansophisme" title="Pansophisme par Wikipedia"&gt; "pansophie universelle" &lt;/a&gt; en intégrant mathématiques, aristotélisme et sciences pratiques. Polymath prolifique, il cherchait à réformer l'éducation et la philosophie via une méthode géométrique, influençant Leibniz parmi ses élèves. Il étudie à Leipzig puis à Iéna où il obtient son doctorat en 1653 et devient professeur de mathématiques et de métaphysique dès 1662. Inventeur de dispositifs pédagogiques (comme des machines à enseigner l'astronomie), il défend des thèses controversées, frôlant l'interdiction de ses écrits pour hérésie philosophique. &lt;/p&gt; &lt;p&gt; Il vise une "restitutio" d'Aristote via Euclide : une science universelle structurant toute connaissance – philosophie, théologie, morale, politique – sur des principes mathématiques clairs et rationnels. Sa morale arithmétique divise le bien en "tetractys pythagoricienne" pour atteindre le bonheur ; sa socialphilosophie analyse les relations humaines comme des équations pratiques au service du bien commun. &lt;/p&gt; &lt;p&gt; Ses Œuvres majeures : Analysis Aristotelica ex Euclide restituta (1658) : Réinterprétation mathématique d'Aristote. Arithmetische Beschreibung der Moral-Weißheit (1674) : Morale en termes numériques et pythagoriciens. Universi Corporis Pansophici Caput Summum (1673) : Exposé de sa pansophie cosmologique.&lt;/p&gt; &lt;p&gt; Ses "Kunst-Erfindungen" (inventions artistiques) démocratisent la science, préfigurant une pédagogie universelle à la Comenius. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F37" s="47" t="inlineStr">
+      <c r="F38" s="47" t="inlineStr">
         <is>
           <t>CYSmoiVNO6g</t>
         </is>
       </c>
-      <c r="G37" s="49" t="inlineStr">
+      <c r="G38" s="49" t="inlineStr">
         <is>
           <t>"Wissenschaft zum Wohle aller! Erhard Weigel zum 400. Geburtstag" par Geschichten aus und über Thüringen</t>
         </is>
       </c>
-      <c r="H37" s="49" t="inlineStr">
+      <c r="H38" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/eweigel-mini.webp</t>
-        </is>
-      </c>
-      <c r="I37" s="57" t="n"/>
-      <c r="J37" s="38" t="inlineStr">
-        <is>
-          <t>Allemande</t>
-        </is>
-      </c>
-      <c r="K37" s="45" t="inlineStr">
-        <is>
-          <t>epistemologie ; logique</t>
-        </is>
-      </c>
-      <c r="L37" s="46" t="inlineStr">
-        <is>
-          <t>Rationalisme</t>
-        </is>
-      </c>
-      <c r="M37" s="35" t="inlineStr">
-        <is>
-          <t>philosophe allemand connu pour ses tentatives de fonder une "pansophie universelle".</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="265.5" customHeight="1" s="39">
-      <c r="A38" s="47" t="n">
-        <v>1625</v>
-      </c>
-      <c r="B38" s="47" t="n">
-        <v>1695</v>
-      </c>
-      <c r="C38" s="47" t="inlineStr">
-        <is>
-          <t>1625 – 1695</t>
-        </is>
-      </c>
-      <c r="D38" s="48" t="inlineStr">
-        <is>
-          <t>Pierre NICOLE</t>
-        </is>
-      </c>
-      <c r="E38" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Nicole" title=" Wikipedia"&gt;Pierre NICOLE&lt;/a&gt; était un philosophe, théologien, logicien et polémiste français, proche de Port-Royal et du mouvement janséniste. Né à Chartres, il enseigna la littérature et la philosophie à Port-Royal des Champs, où il collabora étroitement avec Antoine Arnauld. Il participa également à la défense des thèses jansénistes et fut lié au milieu intellectuel de Pascal. Son œuvre est toutefois plus diverse que celle d’un simple polémiste religieux : elle comprend des écrits de logique, de théologie, de morale et de politique. &lt;/p&gt; &lt;p&gt; Il est surtout connu comme le coauteur, avec Arnauld, de &lt;a href="https://www.youtube.com/watch?v=Gt4zoFWEKLM" title="arnauld et Nicole, la logique ou l’art de penser par Sobrecrate"&gt; la Logique ou l’art de penser,&lt;/a&gt;  publiée en 1662. Cet ouvrage, appelé communément « Logique de Port-Royal », présente la logique non seulement comme un ensemble de règles abstraites, mais comme un art pratique destiné à former le jugement. Il étudie successivement les idées, les jugements, les raisonnements et la méthode. Pour lui, bien penser suppose de lutter contre les préjugés, les passions et les habitudes intellectuelles qui déforment notre rapport à la vérité. &lt;/p&gt; &lt;p&gt;  Mais sa contribution la plus personnelle se trouve probablement dans  &lt;a href="https://www.fabula.org/revue/document1063.php" title="la morale à l’essai par fabula"&gt; les Essais de morale, &lt;/a&gt; dont la publication commence en 1671. Il y analyse les comportements humains, les relations sociales, l’éducation, la politique et les devoirs religieux. Sa morale est profondément augustinienne : l’homme naturel est dominé par l’amour-propre, c’est-à-dire par la tendance à rechercher son intérêt, son prestige et l’approbation des autres. Même les actions qui semblent généreuses peuvent donc être motivées par une recherche cachée de reconnaissance. &lt;/p&gt; &lt;p&gt;  Cette analyse le conduit à une vision assez pessimiste de la nature humaine. Il se méfie des prétendues vertus héroïques et montre que la société repose souvent sur des intérêts dissimulés, des conventions et des compromis. Cependant, il ne conclut pas qu’il est impossible de vivre moralement : ses Essais de morale ont précisément pour objectif d’enseigner une conduite plus lucide, plus modeste et plus charitable. La morale doit commencer par la connaissance de notre faiblesse, car celui qui ignore son amour-propre risque de prendre ses intérêts personnels pour de véritables exigences morales. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F38" s="47" t="inlineStr">
-        <is>
-          <t>vMiObfmHyaQ</t>
-        </is>
-      </c>
-      <c r="G38" s="49" t="inlineStr">
-        <is>
-          <t>Pierre NICOLE par See Hear Say Learn</t>
-        </is>
-      </c>
-      <c r="H38" s="58" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/pnicole-mini.webp</t>
         </is>
       </c>
       <c r="I38" s="57" t="n"/>
       <c r="J38" s="38" t="inlineStr">
         <is>
+          <t>Allemande</t>
+        </is>
+      </c>
+      <c r="K38" s="45" t="inlineStr">
+        <is>
+          <t>epistemologie ; logique</t>
+        </is>
+      </c>
+      <c r="L38" s="46" t="inlineStr">
+        <is>
+          <t>Rationalisme</t>
+        </is>
+      </c>
+      <c r="M38" s="35" t="inlineStr">
+        <is>
+          <t>philosophe allemand connu pour ses tentatives de fonder une "pansophie universelle".</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="265.5" customHeight="1" s="39">
+      <c r="A39" s="47" t="n">
+        <v>1625</v>
+      </c>
+      <c r="B39" s="47" t="n">
+        <v>1695</v>
+      </c>
+      <c r="C39" s="47" t="inlineStr">
+        <is>
+          <t>1625 – 1695</t>
+        </is>
+      </c>
+      <c r="D39" s="48" t="inlineStr">
+        <is>
+          <t>Pierre NICOLE</t>
+        </is>
+      </c>
+      <c r="E39" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Nicole" title=" Wikipedia"&gt;Pierre NICOLE&lt;/a&gt; était un philosophe, théologien, logicien et polémiste français, proche de Port-Royal et du mouvement janséniste. Né à Chartres, il enseigna la littérature et la philosophie à Port-Royal des Champs, où il collabora étroitement avec Antoine Arnauld. Il participa également à la défense des thèses jansénistes et fut lié au milieu intellectuel de Pascal. Son œuvre est toutefois plus diverse que celle d’un simple polémiste religieux : elle comprend des écrits de logique, de théologie, de morale et de politique. &lt;/p&gt; &lt;p&gt; Il est surtout connu comme le coauteur, avec Arnauld, de &lt;a href="https://www.youtube.com/watch?v=Gt4zoFWEKLM" title="arnauld et Nicole, la logique ou l’art de penser par Sobrecrate"&gt; la Logique ou l’art de penser,&lt;/a&gt;  publiée en 1662. Cet ouvrage, appelé communément « Logique de Port-Royal », présente la logique non seulement comme un ensemble de règles abstraites, mais comme un art pratique destiné à former le jugement. Il étudie successivement les idées, les jugements, les raisonnements et la méthode. Pour lui, bien penser suppose de lutter contre les préjugés, les passions et les habitudes intellectuelles qui déforment notre rapport à la vérité. &lt;/p&gt; &lt;p&gt;  Mais sa contribution la plus personnelle se trouve probablement dans  &lt;a href="https://www.fabula.org/revue/document1063.php" title="la morale à l’essai par fabula"&gt; les Essais de morale, &lt;/a&gt; dont la publication commence en 1671. Il y analyse les comportements humains, les relations sociales, l’éducation, la politique et les devoirs religieux. Sa morale est profondément augustinienne : l’homme naturel est dominé par l’amour-propre, c’est-à-dire par la tendance à rechercher son intérêt, son prestige et l’approbation des autres. Même les actions qui semblent généreuses peuvent donc être motivées par une recherche cachée de reconnaissance. &lt;/p&gt; &lt;p&gt;  Cette analyse le conduit à une vision assez pessimiste de la nature humaine. Il se méfie des prétendues vertus héroïques et montre que la société repose souvent sur des intérêts dissimulés, des conventions et des compromis. Cependant, il ne conclut pas qu’il est impossible de vivre moralement : ses Essais de morale ont précisément pour objectif d’enseigner une conduite plus lucide, plus modeste et plus charitable. La morale doit commencer par la connaissance de notre faiblesse, car celui qui ignore son amour-propre risque de prendre ses intérêts personnels pour de véritables exigences morales. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F39" s="47" t="inlineStr">
+        <is>
+          <t>vMiObfmHyaQ</t>
+        </is>
+      </c>
+      <c r="G39" s="49" t="inlineStr">
+        <is>
+          <t>Pierre NICOLE par See Hear Say Learn</t>
+        </is>
+      </c>
+      <c r="H39" s="58" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/pnicole-mini.webp</t>
+        </is>
+      </c>
+      <c r="I39" s="57" t="n"/>
+      <c r="J39" s="38" t="inlineStr">
+        <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K38" s="45" t="inlineStr">
+      <c r="K39" s="45" t="inlineStr">
         <is>
           <t>logique</t>
         </is>
       </c>
-      <c r="L38" s="46" t="inlineStr">
+      <c r="L39" s="46" t="inlineStr">
         <is>
           <t>Jansénisme ; Augustinisme</t>
         </is>
       </c>
-      <c r="M38" s="64" t="inlineStr">
+      <c r="M39" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve"> philosophe, théologien, logicien et polémiste français, proche de Port-Royal et du mouvement janséniste.</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="168" customHeight="1" s="39">
-      <c r="A39" s="47" t="n">
-        <v>1632</v>
-      </c>
-      <c r="B39" s="47" t="inlineStr">
-        <is>
-          <t>1677</t>
-        </is>
-      </c>
-      <c r="C39" s="47" t="inlineStr">
-        <is>
-          <t>1632 - 1677</t>
-        </is>
-      </c>
-      <c r="D39" s="48" t="inlineStr">
-        <is>
-          <t>Baruch SPINOZA</t>
-        </is>
-      </c>
-      <c r="E39" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza"  title=" Wikipedia"&gt;Baruch SPINOZA&lt;/a&gt; (1632-1677) est un philosophe néerlandais, l’un des grands rationalistes du XVIIe siècle. Né à Amsterdam dans une famille de marchands juifs d’origine portugaise, il est exclu de sa communauté en 1656 pour ses opinions jugées hérétiques. Il vit ensuite modestement, polissant des verres d’optique, refuse une chaire à l’université de Heidelberg pour garder sa liberté, et meurt à quarante-quatre ans.&lt;/p&gt; &lt;p&gt;Son œuvre majeure, l’&lt;em&gt;Éthique&lt;/em&gt;, publiée après sa mort, est « démontrée selon l’ordre géométrique », comme un traité de mathématiques. Spinoza y défend une vision &lt;a href="https://fr.wikipedia.org/wiki/Monisme"    title="Le monisme est la position philosophique qui affirme l'unité indivisible de l'être"&gt;moniste&lt;/a&gt; : il n’existe qu’une seule substance, infinie, &lt;a href="https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur"  title="Dieu égale nature"&gt;« Dieu ou la Nature »&lt;/a&gt;. La pensée et l’étendue en sont deux attributs, et chaque corps, chaque esprit, en est une manière d’être. Dieu n’agit pas selon des fins : tout découle nécessairement de sa nature, d’où une philosophie &lt;a href="https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur"  title="Le déterminisme par le Précepteur"&gt;déterministe&lt;/a&gt;. &lt;a  href="https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur"   title="Le libre arbitre n'est il qu'une illusion? par le Précepteur"&gt;Le libre arbitre est une illusion&lt;/a&gt; : nous nous croyons libres parce que nous ignorons les causes qui nous déterminent. Chaque être s’efforce de persévérer dans son être : c’est le &lt;a href="https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur"   title="Le conatus par le Précepteur"&gt;&lt;em&gt;conatus&lt;/em&gt;&lt;/a&gt;, l’essence même de l’homme, son désir. Ce qui augmente notre puissance d’agir nous réjouit, ce qui la diminue nous attriste, et &lt;a href="https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos"  title="Les passions tristes par Kosmos"&gt;les passions&lt;/a&gt; tristes, la haine, la crainte, l’espoir, nous rendent esclaves. La liberté consiste à comprendre la nécessité des choses ; la plus haute joie est l’« amour intellectuel de Dieu ».&lt;/p&gt; &lt;p&gt;Dans le &lt;a href="https://www.youtube.com/watch?v=Zqt0QZVrTkI"   title="Le Traité TP par PrepaUp"&gt;&lt;em&gt;Traité théologico-politique&lt;/em&gt;&lt;/a&gt; (1670), il lit la Bible en historien et défend la liberté de penser, que l’État doit garantir. Accusé d’athéisme, il inspire les Lumières, Hegel, Nietzsche et Einstein.&lt;/p&gt;  &lt;audio controls title="Spinoza est il le philosophe du bonheur ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="47" t="inlineStr">
-        <is>
-          <t>7lTS73Xyct0</t>
-        </is>
-      </c>
-      <c r="G39" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Le parcourt de Spinoza" par Essence des Livres</t>
-        </is>
-      </c>
-      <c r="H39" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/spinoza-mini.webp</t>
-        </is>
-      </c>
-      <c r="I39" s="45" t="n"/>
-      <c r="J39" s="38" t="inlineStr">
-        <is>
-          <t>Néerlandaise</t>
-        </is>
-      </c>
-      <c r="K39" s="45" t="inlineStr">
-        <is>
-          <t>metaphysique ; ethique</t>
-        </is>
-      </c>
-      <c r="L39" s="46" t="inlineStr">
-        <is>
-          <t>Incompatibilisme ; Panthéisme ; Déterminisme ; Monisme</t>
-        </is>
-      </c>
-      <c r="M39" s="35" t="inlineStr">
-        <is>
-          <t>philosophe néerlandais qui prôna le Déterminisme par sa vision Rationaliste.</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juive</t>
-        </is>
-      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" ht="138" customHeight="1" s="39">
+    </row>
+    <row r="40" ht="168" customHeight="1" s="39">
       <c r="A40" s="47" t="n">
         <v>1632</v>
       </c>
       <c r="B40" s="47" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="C40" s="47" t="inlineStr">
         <is>
-          <t>1632 - 1704</t>
+          <t>1632 - 1677</t>
         </is>
       </c>
       <c r="D40" s="48" t="inlineStr">
         <is>
-          <t>John LOCKE</t>
-        </is>
-      </c>
-      <c r="E40" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Locke"  title=" Wikipedia"&gt;John LOCKE&lt;/a&gt; (1632-1704) est un philosophe anglais, fondateur de l’empirisme moderne et l’un des pères du libéralisme politique. Formé à Oxford, où il étudie aussi la médecine, il devient le médecin et le conseiller de Lord Shaftesbury, chef de l’opposition au roi. Exilé aux Pays-Bas en 1683, il ne revient en Angleterre qu’après la « Glorieuse Révolution » de 1688, qui établit une monarchie limitée, et publie alors ses grands livres.&lt;/p&gt; &lt;p&gt;Dans l’&lt;a href="https://fr.wikisource.org/wiki/Livre:Locke_-_Essai_sur_l%E2%80%99entendement_humain.djvu"  title="Essai sur l'entendement humain par Wikisource"&gt;&lt;em&gt;Essai sur l’entendement humain&lt;/em&gt;&lt;/a&gt; (1690), il combat la théorie des idées innées défendue par Descartes : à la naissance, l’esprit est comme une « table rase », une feuille blanche. Toutes nos idées viennent de l’expérience, soit de la sensation, qui nous fait connaître les choses extérieures, soit de la réflexion, qui nous fait connaître les opérations de notre esprit ; les idées simples se combinent ensuite en idées complexes. Locke définit aussi l’identité personnelle par la conscience et la mémoire. Dans le &lt;em&gt;Second Traité du gouvernement civil&lt;/em&gt; (1690), il imagine un état de nature où les hommes, libres et égaux, ont des droits naturels : la vie, la liberté et la propriété, qui naît du travail. Pour mieux les protéger, ils forment par un &lt;a href="https://www.youtube.com/watch?v=lU_sAreHchQ&amp;ab_channel=Lespodcastsphilosophiques"  title="la liberté politique par Les podcasts philo"&gt;contrat social&lt;/a&gt; un gouvernement qui ne tient son pouvoir que de leur consentement ; s’il viole ces droits, le peuple peut lui résister. Locke distingue enfin le pouvoir législatif et le pouvoir exécutif.&lt;/p&gt; &lt;p&gt;Dans sa &lt;em&gt;Lettre sur la tolérance&lt;/em&gt; (1689), il demande que l’État laisse chacun libre de sa religion. Ses idées inspirent Voltaire, Montesquieu et la Déclaration d’indépendance américaine.&lt;/p&gt;  &lt;audio controls title="L'invention de la conscience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21976-01.02.2021-ITEMA_22560721-2015C12410S0287.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+          <t>Baruch SPINOZA</t>
+        </is>
+      </c>
+      <c r="E40" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Baruch_Spinoza"  title=" Wikipedia"&gt;Baruch SPINOZA&lt;/a&gt; (1632-1677) est un philosophe néerlandais, l’un des grands rationalistes du XVIIe siècle. Né à Amsterdam dans une famille de marchands juifs d’origine portugaise, il est exclu de sa communauté en 1656 pour ses opinions jugées hérétiques. Il vit ensuite modestement, polissant des verres d’optique, refuse une chaire à l’université de Heidelberg pour garder sa liberté, et meurt à quarante-quatre ans.&lt;/p&gt; &lt;p&gt;Son œuvre majeure, l’&lt;em&gt;Éthique&lt;/em&gt;, publiée après sa mort, est « démontrée selon l’ordre géométrique », comme un traité de mathématiques. Spinoza y défend une vision &lt;a href="https://fr.wikipedia.org/wiki/Monisme"    title="Le monisme est la position philosophique qui affirme l'unité indivisible de l'être"&gt;moniste&lt;/a&gt; : il n’existe qu’une seule substance, infinie, &lt;a href="https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur"  title="Dieu égale nature"&gt;« Dieu ou la Nature »&lt;/a&gt;. La pensée et l’étendue en sont deux attributs, et chaque corps, chaque esprit, en est une manière d’être. Dieu n’agit pas selon des fins : tout découle nécessairement de sa nature, d’où une philosophie &lt;a href="https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur"  title="Le déterminisme par le Précepteur"&gt;déterministe&lt;/a&gt;. &lt;a  href="https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur"   title="Le libre arbitre n'est il qu'une illusion? par le Précepteur"&gt;Le libre arbitre est une illusion&lt;/a&gt; : nous nous croyons libres parce que nous ignorons les causes qui nous déterminent. Chaque être s’efforce de persévérer dans son être : c’est le &lt;a href="https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur"   title="Le conatus par le Précepteur"&gt;&lt;em&gt;conatus&lt;/em&gt;&lt;/a&gt;, l’essence même de l’homme, son désir. Ce qui augmente notre puissance d’agir nous réjouit, ce qui la diminue nous attriste, et &lt;a href="https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos"  title="Les passions tristes par Kosmos"&gt;les passions&lt;/a&gt; tristes, la haine, la crainte, l’espoir, nous rendent esclaves. La liberté consiste à comprendre la nécessité des choses ; la plus haute joie est l’« amour intellectuel de Dieu ».&lt;/p&gt; &lt;p&gt;Dans le &lt;a href="https://www.youtube.com/watch?v=Zqt0QZVrTkI"   title="Le Traité TP par PrepaUp"&gt;&lt;em&gt;Traité théologico-politique&lt;/em&gt;&lt;/a&gt; (1670), il lit la Bible en historien et défend la liberté de penser, que l’État doit garantir. Accusé d’athéisme, il inspire les Lumières, Hegel, Nietzsche et Einstein.&lt;/p&gt;  &lt;audio controls title="Spinoza est il le philosophe du bonheur ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F40" s="47" t="inlineStr">
         <is>
-          <t>Rx4BgGX0R0M</t>
+          <t>7lTS73Xyct0</t>
         </is>
       </c>
       <c r="G40" s="49" t="inlineStr">
         <is>
-          <t>"l'Empirisme de John LOCKE" par digiSchool</t>
+          <t xml:space="preserve">"Le parcourt de Spinoza" par Essence des Livres</t>
         </is>
       </c>
       <c r="H40" s="49" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/locke-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/spinoza-mini.webp</t>
         </is>
       </c>
       <c r="I40" s="45" t="n"/>
-      <c r="J40" s="55" t="inlineStr">
-        <is>
-          <t>Britannique</t>
+      <c r="J40" s="38" t="inlineStr">
+        <is>
+          <t>Néerlandaise</t>
         </is>
       </c>
       <c r="K40" s="45" t="inlineStr">
         <is>
-          <t>epistemologie ; politique</t>
+          <t>metaphysique ; ethique</t>
         </is>
       </c>
       <c r="L40" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empirisme ; Libéralisme ; Méthodisme ; Conceptualisme</t>
+          <t>Incompatibilisme ; Panthéisme ; Déterminisme ; Monisme</t>
         </is>
       </c>
       <c r="M40" s="35" t="inlineStr">
         <is>
-          <t>philosophe anglais qui a développé une théorie de la connaissance Empirique.</t>
+          <t>philosophe néerlandais qui prôna le Déterminisme par sa vision Rationaliste.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3322,93 +3319,162 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" ht="155.25" customHeight="1" s="39">
+    <row r="41" ht="138" customHeight="1" s="39">
       <c r="A41" s="47" t="n">
+        <v>1632</v>
+      </c>
+      <c r="B41" s="47" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="C41" s="47" t="inlineStr">
+        <is>
+          <t>1632 - 1704</t>
+        </is>
+      </c>
+      <c r="D41" s="48" t="inlineStr">
+        <is>
+          <t>John LOCKE</t>
+        </is>
+      </c>
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Locke"  title=" Wikipedia"&gt;John LOCKE&lt;/a&gt; (1632-1704) est un philosophe anglais, fondateur de l’empirisme moderne et l’un des pères du libéralisme politique. Formé à Oxford, où il étudie aussi la médecine, il devient le médecin et le conseiller de Lord Shaftesbury, chef de l’opposition au roi. Exilé aux Pays-Bas en 1683, il ne revient en Angleterre qu’après la « Glorieuse Révolution » de 1688, qui établit une monarchie limitée, et publie alors ses grands livres.&lt;/p&gt; &lt;p&gt;Dans l’&lt;a href="https://fr.wikisource.org/wiki/Livre:Locke_-_Essai_sur_l%E2%80%99entendement_humain.djvu"  title="Essai sur l'entendement humain par Wikisource"&gt;&lt;em&gt;Essai sur l’entendement humain&lt;/em&gt;&lt;/a&gt; (1690), il combat la théorie des idées innées défendue par Descartes : à la naissance, l’esprit est comme une « table rase », une feuille blanche. Toutes nos idées viennent de l’expérience, soit de la sensation, qui nous fait connaître les choses extérieures, soit de la réflexion, qui nous fait connaître les opérations de notre esprit ; les idées simples se combinent ensuite en idées complexes. Locke définit aussi l’identité personnelle par la conscience et la mémoire. Dans le &lt;em&gt;Second Traité du gouvernement civil&lt;/em&gt; (1690), il imagine un état de nature où les hommes, libres et égaux, ont des droits naturels : la vie, la liberté et la propriété, qui naît du travail. Pour mieux les protéger, ils forment par un &lt;a href="https://www.youtube.com/watch?v=lU_sAreHchQ&amp;ab_channel=Lespodcastsphilosophiques"  title="la liberté politique par Les podcasts philo"&gt;contrat social&lt;/a&gt; un gouvernement qui ne tient son pouvoir que de leur consentement ; s’il viole ces droits, le peuple peut lui résister. Locke distingue enfin le pouvoir législatif et le pouvoir exécutif.&lt;/p&gt; &lt;p&gt;Dans sa &lt;em&gt;Lettre sur la tolérance&lt;/em&gt; (1689), il demande que l’État laisse chacun libre de sa religion. Ses idées inspirent Voltaire, Montesquieu et la Déclaration d’indépendance américaine.&lt;/p&gt;  &lt;audio controls title="L'invention de la conscience par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21976-01.02.2021-ITEMA_22560721-2015C12410S0287.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F41" s="47" t="inlineStr">
+        <is>
+          <t>Rx4BgGX0R0M</t>
+        </is>
+      </c>
+      <c r="G41" s="49" t="inlineStr">
+        <is>
+          <t>"l'Empirisme de John LOCKE" par digiSchool</t>
+        </is>
+      </c>
+      <c r="H41" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/locke-mini.webp</t>
+        </is>
+      </c>
+      <c r="I41" s="45" t="n"/>
+      <c r="J41" s="55" t="inlineStr">
+        <is>
+          <t>Britannique</t>
+        </is>
+      </c>
+      <c r="K41" s="45" t="inlineStr">
+        <is>
+          <t>epistemologie ; politique</t>
+        </is>
+      </c>
+      <c r="L41" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empirisme ; Libéralisme ; Méthodisme ; Conceptualisme</t>
+        </is>
+      </c>
+      <c r="M41" s="35" t="inlineStr">
+        <is>
+          <t>philosophe anglais qui a développé une théorie de la connaissance Empirique.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" ht="155.25" customHeight="1" s="39">
+      <c r="A42" s="47" t="n">
         <v>1638</v>
       </c>
-      <c r="B41" s="47" t="inlineStr">
+      <c r="B42" s="47" t="inlineStr">
         <is>
           <t>1715</t>
         </is>
       </c>
-      <c r="C41" s="47" t="inlineStr">
+      <c r="C42" s="47" t="inlineStr">
         <is>
           <t>1638 – 1715</t>
         </is>
       </c>
-      <c r="D41" s="48" t="inlineStr">
+      <c r="D42" s="48" t="inlineStr">
         <is>
           <t>Nicolas MALEBRANCHE</t>
         </is>
       </c>
-      <c r="E41" s="58" t="inlineStr">
+      <c r="E42" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Malebranche" title=" Wikipedia"&gt;Nicolas MALEBRANCHE&lt;/a&gt; était un philosophe et théologien français, connu pour ses travaux en métaphysique, en épistémologie et en philosophie de la religion. En 1660, il rejoint l'Oratoire, une congrégation religieuse catholique, où il se consacre à l'étude de la philosophie et de la théologie et il découvre les travaux de Descartes, qui auront une influence majeure sur sa pensée. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de  &lt;a href="https://www.youtube.com/watch?v=3YvitSjZ2_4&amp;t=326s" title="Malebranche : Occasionalism par Leevark"&gt;l'occasionalisme&lt;/a&gt;, qu'il développe dans son ouvrage majeur " De la recherche de la vérité". Selon lui, les idées que nous avons des objets existent dans l'entendement divin, et c'est par la médiation de Dieu que nous accédons à ces idées. Cette théorie s'oppose à l'empirisme et à l'idée que nos perceptions sont directement causées par les objets eux-mêmes.  Il rejette l'interaction directe entre l'âme et le corps, une idée défendue par Descartes. Selon lui, l'âme et le corps ne peuvent pas agir l'un sur l'autre directement. Au lieu de cela, Dieu coordonne les états de l'âme et les états du corps de manière harmonieuse, sans qu'il y ait de causalité directe entre eux. Il a développé une théorie selon laquelle Dieu agit selon des "lois générales" plutôt que par des interventions particulières, ce qui laisse une place à la &lt;a href="https://fr.wikipedia.org/wiki/Libert%C3%A9_(philosophie)"  title="La liberté par Wikipedia"&gt;liberté humaine&lt;/a&gt; tout en maintenant la souveraineté divine. &lt;/p&gt; &lt;p&gt;Ses oeuvres principales : &lt;/p&gt; &lt;p&gt;De la recherche de la vérité : Théories sur la perception, la causalité et la métaphysique.  &lt;/p&gt; &lt;p&gt;Traité de la nature et de la grâce : Relation entre la grâce divine et les lois de la nature. &lt;/p&gt;
 &lt;p&gt;Entretiens sur la métaphysique et la religion : Un dialogue qui résume et défend ses idées. &lt;/p&gt; &lt;p&gt; Il reste une figure importante dans l'histoire de la philosophie, notamment pour sa tentative de concilier la pensée cartésienne avec une vision profondément théocentrique du monde. &lt;/p&gt;    &lt;audio controls title=" L’imagination selon Descartes et Malebranche par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-16.01.2024-ITEMA_23616134-2024C48904S0016-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
-      <c r="F41" s="47" t="inlineStr">
+      <c r="F42" s="47" t="inlineStr">
         <is>
           <t>rnc_oKmkwSY</t>
         </is>
       </c>
-      <c r="G41" s="49" t="inlineStr">
+      <c r="G42" s="49" t="inlineStr">
         <is>
           <t>"Nicolas MALEBRANCHE" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H41" s="49" t="inlineStr">
+      <c r="H42" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/malebranche-mini.webp</t>
         </is>
       </c>
-      <c r="I41" s="45" t="n"/>
-      <c r="J41" s="38" t="inlineStr">
+      <c r="I42" s="45" t="n"/>
+      <c r="J42" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K41" s="45" t="inlineStr">
+      <c r="K42" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>
         </is>
       </c>
-      <c r="L41" s="46" t="inlineStr">
+      <c r="L42" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Occasionalisme ; Ontologisme ; Dualisme</t>
         </is>
       </c>
-      <c r="M41" s="35" t="inlineStr">
+      <c r="M42" s="35" t="inlineStr">
         <is>
           <t>philosophe français principal représentant de l'occasionnalisme.</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="155.25" customHeight="1" s="39">
-      <c r="A42" s="47" t="n">
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="155.25" customHeight="1" s="39">
+      <c r="A43" s="47" t="n">
         <v>1646</v>
       </c>
-      <c r="B42" s="47" t="inlineStr">
+      <c r="B43" s="47" t="inlineStr">
         <is>
           <t>1716</t>
         </is>
       </c>
-      <c r="C42" s="47" t="inlineStr">
+      <c r="C43" s="47" t="inlineStr">
         <is>
           <t>1646 - 1716</t>
         </is>
       </c>
-      <c r="D42" s="48" t="inlineStr">
+      <c r="D43" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Gottfried Wilhelm LEIBNIZ</t>
         </is>
       </c>
-      <c r="E42" s="49" t="inlineStr">
+      <c r="E43" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Gottfried_Wilhelm_Leibniz"  title=" Wikipedia"&gt;Gottfried Wilhelm LEIBNIZ&lt;/a&gt; était un philosophe allemand très &lt;a href="https://fr.wikipedia.org/wiki/%C3%89clectisme"  title=""éclectisme par Wikipedia"&gt;éclectique&lt;/a&gt;, de la théologie en passant par les mathématiques, la logique et la philosophie politique ou encore la métaphysique où il est connu pour sa théorie des monades, selon laquelle l'univers est composé d'un nombre infini d'entités individuelles et autonomes appelées monades. Chaque monade est une substance simple, sans parties, qui possède une perception et une appétition, c'est-à-dire une tendance à rechercher le bien et à &lt;a href="https://www.youtube.com/watch?v=ZJKr-vJt3NE&amp;ab_channel=LePr%C3%A9cepteur"  title="Le mal n'existe pas par le Précepteur"&gt; éviter le mal&lt;/a&gt;. Les monades ne peuvent pas interagir directement les unes avec les autres, mais leur perception et leur appétition sont harmonisées par Dieu, qui a créé l'univers de manière à ce qu'il soit le meilleur des mondes possibles. &lt;/p&gt; &lt;p&gt;
 La théorie a des implications dans de nombreux domaines, y compris la métaphysique, la théologie, l'épistémologie et l'éthique. Elle implique que la connaissance de chaque monade est limitée à sa propre perspective, ce qui soulève des questions intéressantes sur la nature de la vérité et de la connaissance.&lt;/p&gt; &lt;p&gt; 
@@ -3416,106 +3482,40 @@
 En philosophie politique, Leibniz a soutenu que le pouvoir politique devrait être détenu par une élite instruite, qui gouvernerait de manière éclairée et rationnelle. &lt;/p&gt;  &lt;audio controls title="La Monadologie par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/11/s47/RF_F56A3AEF-9E04-487F-89BF-2C4FBCA2B21D_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F42" s="47" t="inlineStr">
+      <c r="F43" s="47" t="inlineStr">
         <is>
           <t>Nr-AYhVNUmI</t>
         </is>
       </c>
-      <c r="G42" s="49" t="inlineStr">
+      <c r="G43" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">"Leibniz et le sophisme paresseux" par Monsieur Phi</t>
         </is>
       </c>
-      <c r="H42" s="49" t="inlineStr">
+      <c r="H43" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/liebniz-mini.webp</t>
-        </is>
-      </c>
-      <c r="I42" s="45" t="n"/>
-      <c r="J42" s="38" t="inlineStr">
-        <is>
-          <t>Allemande</t>
-        </is>
-      </c>
-      <c r="K42" s="45" t="inlineStr">
-        <is>
-          <t>metaphysique ; logique</t>
-        </is>
-      </c>
-      <c r="L42" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rationalisme ; Fatalisme ; Oecuménisme ; Pansophisme</t>
-        </is>
-      </c>
-      <c r="M42" s="35" t="inlineStr">
-        <is>
-          <t>philosophe allemand et l'un des principaux représentants du Rationalisme.</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="131.25" customHeight="1" s="39">
-      <c r="A43" s="47" t="n">
-        <v>1647</v>
-      </c>
-      <c r="B43" s="47" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="C43" s="47" t="inlineStr">
-        <is>
-          <t>1647 – 1723</t>
-        </is>
-      </c>
-      <c r="D43" s="48" t="inlineStr">
-        <is>
-          <t>François POULLAIN de la Barre</t>
-        </is>
-      </c>
-      <c r="E43" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Poullain_de_La_Barre" title=" Wikipedia"&gt;François POULLAIN de la Barre&lt;/a&gt; était un  philosophe et écrivain français, connu comme un pionnier du  &lt;a href="https://www.youtube.com/watch?v=ddRMNFWa0lk"  title=" Un philosophe féministe à l'époque de Louis XIV par Citéphilo"&gt;féminisme moderne &lt;/a&gt; et un disciple de Descartes. Initialement étudiant en théologie et prêtre, il adopte la philosophie cartésienne et se convertit au protestantisme, s'exilant à Genève où il enseigne la philosophie. &lt;/p&gt; &lt;p&gt;  Il applique la méthode cartésienne pour démontrer que la prétendue infériorité des femmes n'a pas de fondement naturel, mais résulte de préjugés culturels. Dans son ouvrage anonyme de 1673,  &lt;a href="https://www.les-philosophes.fr/feminisme/de-l-egalite-des-deux-sexes.html"  title="De l'égalité des deux sexes, de l'éducation des dames, de l'excellence des hommes par Les Philosophes.fr"&gt; "De l’égalité des deux sexes"&lt;/a&gt;, il critique les idées patriarcales qui justifient les discriminations contre les femmes et revendique leur droit à une véritable éducation et à l'accès aux mêmes carrières que les hommes, y compris les sciences. Il publie également "De l’éducation des dames pour la conduite des esprits dans les sciences et dans les mœurs" en 1674 et plus tard, ironiquement, "De l’excellence des hommes contre l’égalité des sexes"  en 1675 dans le but de ridiculiser les arguments sexistes de son époque. Sa thèse centrale est que l'esprit, la raison, n'a pas de sexe, et que les différences sociales tiennent à l'éducation et aux préjugés. Sa formule « l’esprit n’a point de sexe » résume cette position : la raison étant la même chez tous, rien ne justifie d’exclure les femmes des savoirs, des métiers ou des fonctions publiques. Il invite aussi à se méfier de ce que les hommes ont écrit sur les femmes, puisqu’ils y sont à la fois juges et parties ; Simone de Beauvoir placera cette idée en exergue du &lt;em&gt;Deuxième Sexe&lt;/em&gt;. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F43" s="47" t="inlineStr">
-        <is>
-          <t>zF_9cr6xgDY</t>
-        </is>
-      </c>
-      <c r="G43" s="49" t="inlineStr">
-        <is>
-          <t>"François Poulain de la Barre, DE L’ÉGALITÉ DES DEUX SEXES" par Veilleur des Livres</t>
-        </is>
-      </c>
-      <c r="H43" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/barre-mini.webp</t>
         </is>
       </c>
       <c r="I43" s="45" t="n"/>
       <c r="J43" s="38" t="inlineStr">
         <is>
-          <t>Française</t>
+          <t>Allemande</t>
         </is>
       </c>
       <c r="K43" s="45" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>metaphysique ; logique</t>
         </is>
       </c>
       <c r="L43" s="46" t="inlineStr">
         <is>
-          <t>Féminisme</t>
+          <t xml:space="preserve">Rationalisme ; Fatalisme ; Oecuménisme ; Pansophisme</t>
         </is>
       </c>
       <c r="M43" s="35" t="inlineStr">
         <is>
-          <t>philosophe français et l'un des premiers féministes.</t>
+          <t>philosophe allemand et l'un des principaux représentants du Rationalisme.</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3524,26 +3524,92 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="158.25" customHeight="1" s="39">
+    <row r="44" ht="131.25" customHeight="1" s="39">
       <c r="A44" s="47" t="n">
         <v>1647</v>
       </c>
       <c r="B44" s="47" t="inlineStr">
         <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="C44" s="47" t="inlineStr">
+        <is>
+          <t>1647 – 1723</t>
+        </is>
+      </c>
+      <c r="D44" s="48" t="inlineStr">
+        <is>
+          <t>François POULLAIN de la Barre</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Poullain_de_La_Barre" title=" Wikipedia"&gt;François POULLAIN de la Barre&lt;/a&gt; était un  philosophe et écrivain français, connu comme un pionnier du  &lt;a href="https://www.youtube.com/watch?v=ddRMNFWa0lk"  title=" Un philosophe féministe à l'époque de Louis XIV par Citéphilo"&gt;féminisme moderne &lt;/a&gt; et un disciple de Descartes. Initialement étudiant en théologie et prêtre, il adopte la philosophie cartésienne et se convertit au protestantisme, s'exilant à Genève où il enseigne la philosophie. &lt;/p&gt; &lt;p&gt;  Il applique la méthode cartésienne pour démontrer que la prétendue infériorité des femmes n'a pas de fondement naturel, mais résulte de préjugés culturels. Dans son ouvrage anonyme de 1673,  &lt;a href="https://www.les-philosophes.fr/feminisme/de-l-egalite-des-deux-sexes.html"  title="De l'égalité des deux sexes, de l'éducation des dames, de l'excellence des hommes par Les Philosophes.fr"&gt; "De l’égalité des deux sexes"&lt;/a&gt;, il critique les idées patriarcales qui justifient les discriminations contre les femmes et revendique leur droit à une véritable éducation et à l'accès aux mêmes carrières que les hommes, y compris les sciences. Il publie également "De l’éducation des dames pour la conduite des esprits dans les sciences et dans les mœurs" en 1674 et plus tard, ironiquement, "De l’excellence des hommes contre l’égalité des sexes"  en 1675 dans le but de ridiculiser les arguments sexistes de son époque. Sa thèse centrale est que l'esprit, la raison, n'a pas de sexe, et que les différences sociales tiennent à l'éducation et aux préjugés. Sa formule « l’esprit n’a point de sexe » résume cette position : la raison étant la même chez tous, rien ne justifie d’exclure les femmes des savoirs, des métiers ou des fonctions publiques. Il invite aussi à se méfier de ce que les hommes ont écrit sur les femmes, puisqu’ils y sont à la fois juges et parties ; Simone de Beauvoir placera cette idée en exergue du &lt;em&gt;Deuxième Sexe&lt;/em&gt;. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F44" s="47" t="inlineStr">
+        <is>
+          <t>zF_9cr6xgDY</t>
+        </is>
+      </c>
+      <c r="G44" s="49" t="inlineStr">
+        <is>
+          <t>"François Poulain de la Barre, DE L’ÉGALITÉ DES DEUX SEXES" par Veilleur des Livres</t>
+        </is>
+      </c>
+      <c r="H44" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/barre-mini.webp</t>
+        </is>
+      </c>
+      <c r="I44" s="45" t="n"/>
+      <c r="J44" s="38" t="inlineStr">
+        <is>
+          <t>Française</t>
+        </is>
+      </c>
+      <c r="K44" s="45" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L44" s="46" t="inlineStr">
+        <is>
+          <t>Féminisme</t>
+        </is>
+      </c>
+      <c r="M44" s="35" t="inlineStr">
+        <is>
+          <t>philosophe français et l'un des premiers féministes.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="158.25" customHeight="1" s="39">
+      <c r="A45" s="47" t="n">
+        <v>1647</v>
+      </c>
+      <c r="B45" s="47" t="inlineStr">
+        <is>
           <t>1706</t>
         </is>
       </c>
-      <c r="C44" s="47" t="inlineStr">
+      <c r="C45" s="47" t="inlineStr">
         <is>
           <t>1647 – 1706</t>
         </is>
       </c>
-      <c r="D44" s="48" t="inlineStr">
+      <c r="D45" s="48" t="inlineStr">
         <is>
           <t>Pierre BAYLE</t>
         </is>
       </c>
-      <c r="E44" s="49" t="inlineStr">
+      <c r="E45" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Bayle"   title=" Wikipedia"&gt;Pierre BAYLE&lt;/a&gt; était un philosophe français connu pour son scepticisme, sa défense de  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1965_num_39_2_2413" title="Pierre Bayle précurseur des théologies modernes de la liberté religieuse  par Persée"&gt;la tolérance religieuse &lt;/a&gt; et son monumental Dictionnaire historique et critique, qui en fait un précurseur majeur des Lumières. Sa pensée mêle critique radicale des dogmes religieux, exigence de rigueur historique et réflexion sur les limites de la raison. &lt;/p&gt; &lt;p&gt; Il est souvent présenté comme un sceptique : il met en évidence les contradictions de la raison, notamment quand elle prétend démontrer les dogmes religieux (Trinité, providence, miracle, etc.). Il aime exposer des opinions paradoxales, voire scandaleuses, et les renforcer par des arguments rigoureux, sans dire clairement s’il les adopte lui‑même, ce qui déroutait ses contemporains. Concernant le problème du mal, il montre que la raison ne parvient pas à concilier l’existence du mal avec celle d’un Dieu tout‑puissant et parfaitement bon.
  &lt;/p&gt; &lt;p&gt; Il défend la tolérance civile : l’État ne doit pas persécuter pour des motifs religieux et doit protéger la liberté de conscience de toutes les confessions, y compris juifs, musulmans et athées. Il soutient qu’une société composée d’athées pourrait être ordonnée et morale, anticipant l’idée moderne d’une morale indépendante de la religion.  &lt;/p&gt; &lt;p&gt; 
@@ -3552,134 +3618,134 @@
  &lt;p&gt;  &lt;audio controls title="Le scandaleux Pierre Bayle par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/16409-04.04.2008-ITEMA_20118105-2008C6409S0095-NET_66658CCB-7933-4384-84A0-F0495954D09D_FC-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F44" s="47" t="inlineStr">
+      <c r="F45" s="47" t="inlineStr">
         <is>
           <t>OfBWQjxztPM</t>
         </is>
       </c>
-      <c r="G44" s="49" t="inlineStr">
+      <c r="G45" s="49" t="inlineStr">
         <is>
           <t>"Pierre Bayle, apôtre de la tolérance" par Regards protestants</t>
         </is>
       </c>
-      <c r="H44" s="49" t="inlineStr">
+      <c r="H45" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bayle-mini.webp</t>
         </is>
       </c>
-      <c r="I44" s="45" t="n"/>
-      <c r="J44" s="38" t="inlineStr">
+      <c r="I45" s="45" t="n"/>
+      <c r="J45" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K44" s="45" t="inlineStr">
+      <c r="K45" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; ethique</t>
         </is>
       </c>
-      <c r="L44" s="46" t="inlineStr">
+      <c r="L45" s="46" t="inlineStr">
         <is>
           <t>Scepticisme</t>
         </is>
       </c>
-      <c r="M44" s="35" t="inlineStr">
+      <c r="M45" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour sa défense de la tolérance religieuse.</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="130.5" customHeight="1" s="39">
-      <c r="A45" s="47">
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="130.5" customHeight="1" s="39">
+      <c r="A46" s="47">
         <v>1657</v>
       </c>
-      <c r="B45" s="47" t="inlineStr">
+      <c r="B46" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">1757</t>
         </is>
       </c>
-      <c r="C45" s="47" t="inlineStr">
+      <c r="C46" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">1657 – 1757</t>
         </is>
       </c>
-      <c r="D45" s="48" t="inlineStr">
+      <c r="D46" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Bernard Le Bouyer de FONTENELLE</t>
         </is>
       </c>
-      <c r="E45" s="68" t="inlineStr">
+      <c r="E46" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Le_Bouyer_de_Fontenelle" title=" Wikipedia"&gt;Bernard Le Bouyer de FONTENELLE&lt;/a&gt; est un écrivain et savant français, l’un des grands passeurs entre l’âge classique et les &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt;. Né à Rouen et neveu de Pierre et Thomas Corneille, il abandonne vite le barreau pour les lettres et le théâtre, sans grand succès, avant de trouver sa voie dans la diffusion des sciences. Dans les&lt;a href="https://www.youtube.com/watch?v=5JsNkt5BWC4&amp;amp;list=PLzEKOeY60frzFBdwN_ieACocW0grgZsqS" title="&amp;quot;Entretien sur la pluralité des mondes&amp;quot; Bernard Le Bouyer de Fontenelle -PREMIER SOIR- par French_With_Kathlyne"&gt; &lt;em&gt;Entretiens sur la pluralité des mondes&lt;/em&gt; &lt;/a&gt;(1686), un philosophe explique à une marquise, au cours de promenades nocturnes, le &lt;a href="https://www.youtube.com/watch?v=V1yLZNI0B8s" title="Entretiens sur la pluralité des mondes - Bernard Le Bouyer de Fontenelle | Résumé animé  📚🎬 par Livres en Scène"&gt;système de Copernic&lt;/a&gt; et les tourbillons de Descartes, et imagine des habitants sur les autres planètes.&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=MKV24MRfu4Y" title="Les Entretiens sur la Pluralité des Mondes de Fontenelle - Bac de Français par Coursitout"&gt;Ce livre élégant&lt;/a&gt;, l’un des premiers grands succès de la vulgarisation scientifique, enlève à la Terre et à l’homme leur place au centre du monde. L’année suivante, l’&lt;em&gt;Histoire des oracles&lt;/em&gt; (1687) montre que les oracles païens n’étaient pas l’œuvre des démons, mais des tromperies des prêtres : sous couvert d’Antiquité, c’est toute la crédulité religieuse qui est visée. Dans la querelle des Anciens et des Modernes, sa &lt;em&gt;Digression&lt;/em&gt; de 1688 prend le parti des Modernes : la nature n’a pas changé, et les connaissances s’accumulent au fil des siècles, ce qui annonce l’idée de progrès.&lt;/p&gt; &lt;p&gt;Élu à l’Académie française en 1691, il est de 1697 à 1740 le secrétaire perpétuel de l’Académie royale des sciences, dont il rédige chaque année l’histoire et les éloges des savants disparus, rendant accessibles les travaux de Leibniz ou de Newton. Fidèle jusqu’au bout à la physique de &lt;a href="https://fr.wikipedia.org/wiki/Ren%C3%A9_Descartes" title=" Wikipedia"&gt;Descartes&lt;/a&gt;, il défend encore les tourbillons contre l’attraction newtonienne. Il meurt à Paris à presque cent ans.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t xml:space="preserve">YAYJ4udP4WA</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">"Cours Bac Français | Fontenelle – Entretiens sur la pluralité des mondes" par MemoClasse</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/fontenelle-mini.webp</t>
         </is>
       </c>
-      <c r="J45" s="38" t="inlineStr">
+      <c r="J46" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Française</t>
         </is>
       </c>
-      <c r="K45" s="45" t="inlineStr">
+      <c r="K46" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">epistemologie ; metaphysique</t>
         </is>
       </c>
-      <c r="L45" s="46" t="inlineStr">
+      <c r="L46" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Cartésianisme ; Lumières</t>
         </is>
       </c>
-      <c r="M45" s="35" t="inlineStr">
+      <c r="M46" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">écrivain français, vulgarisateur de la science cartésienne et précurseur des Lumières.</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P45"/>
-    </row>
-    <row r="46" ht="207.75" customHeight="1" s="39">
-      <c r="A46" s="47" t="n">
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P46"/>
+    </row>
+    <row r="47" ht="207.75" customHeight="1" s="39">
+      <c r="A47" s="47" t="n">
         <v>1664</v>
       </c>
-      <c r="B46" s="47" t="inlineStr">
+      <c r="B47" s="47" t="inlineStr">
         <is>
           <t>1729</t>
         </is>
       </c>
-      <c r="C46" s="47" t="inlineStr">
+      <c r="C47" s="47" t="inlineStr">
         <is>
           <t>1664 - 1729</t>
         </is>
       </c>
-      <c r="D46" s="48" t="inlineStr">
+      <c r="D47" s="48" t="inlineStr">
         <is>
           <t>Jean MESLIER</t>
         </is>
       </c>
-      <c r="E46" s="49" t="inlineStr">
+      <c r="E47" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Meslier"  title=" Wikipedia"&gt;Jean MESLIER&lt;/a&gt; était un prêtre français connu pour son &lt;a href="https://www.youtube.com/watch?v=5s-nuRI6dKY&amp;ab_channel=AlainBajom%C3%A9e"   title="L'athéisme par Meslier par Alain Bajomée"&gt; athéisme radical&lt;/a&gt; et anticlérical. À sa mort, un manuscrit de plus de 200 pages, connu sous le nom de  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1971_num_69_2_5609_t1_0297_0000_1"  title="Oeuvre complète par le Persée"&gt; "Mémoire des Pensées et des Sentiments de Jean Meslier"&lt;/a&gt;, a été découvert et est considéré comme l'un des premiers manifestes de l'athéisme moderne en France car il remet en question la validité des dogmes religieux, dénonce l'injustice sociale, critique l'influence corruptrice de l'Église et prône une société égalitaire.  &lt;/p&gt; &lt;p&gt;   Quelques aspects de sa philosophie qui ont marqué l'histoire de la philosophie : &lt;/p&gt;&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=0lQrBmCTD74"   title="La bonne parole du curé Meslier par Théatre poème"&gt; Athéisme radical&lt;/a&gt; - Il a argumenté de  manière virulente contre l'existence de Dieu et la validité des croyances religieuses. Il a utilisé des arguments rationalistes pour contester les dogmes religieux et a soutenu que la religion était une invention humaine visant à maintenir le pouvoir et la domination des élites religieuses et politiques. &lt;/p&gt;
 &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=p8r9BYjZ7SQ"   title="Le matérialisme par Culture philo"&gt;  - Matérialisme : &lt;/a&gt; Il croyait que le monde était constitué de matière et que la conscience humaine découlait de processus matériels dans le cerveau. Ce point de vue était en accord avec les idées des philosophes matérialistes ultérieurs des Lumières. &lt;/p&gt;
@@ -3688,106 +3754,40 @@
 </t>
         </is>
       </c>
-      <c r="F46" s="47" t="inlineStr">
+      <c r="F47" s="47" t="inlineStr">
         <is>
           <t>5s-nuRI6dKY</t>
         </is>
       </c>
-      <c r="G46" s="49" t="inlineStr">
+      <c r="G47" s="49" t="inlineStr">
         <is>
           <t>"Jean Meslier et l'atéisme " par Alain Bajomée</t>
         </is>
       </c>
-      <c r="H46" s="49" t="inlineStr">
+      <c r="H47" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/meslier-mini.webp</t>
-        </is>
-      </c>
-      <c r="I46" s="45" t="n"/>
-      <c r="J46" s="38" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K46" s="45" t="inlineStr">
-        <is>
-          <t>politique ; ethique</t>
-        </is>
-      </c>
-      <c r="L46" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matérialisme ; Athéisme</t>
-        </is>
-      </c>
-      <c r="M46" s="35" t="inlineStr">
-        <is>
-          <t>philosophe et prêtre français connu pour son Athéisme radical.</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="147.75" customHeight="1" s="39">
-      <c r="A47" s="47" t="n">
-        <v>1668</v>
-      </c>
-      <c r="B47" s="47" t="inlineStr">
-        <is>
-          <t>1744</t>
-        </is>
-      </c>
-      <c r="C47" s="47" t="inlineStr">
-        <is>
-          <t>1668 – 1744</t>
-        </is>
-      </c>
-      <c r="D47" s="48" t="inlineStr">
-        <is>
-          <t>Giambattista VICO</t>
-        </is>
-      </c>
-      <c r="E47" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giambattista_Vico"  title=" Wikipedia"&gt;Giambattista VICO&lt;/a&gt; était un  philosophe, historien et pédagogue italien reconnu comme un pionnier de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_6790" style="color:#88A1E9" title=" La sagesse de l'histoire. Jean-Baptiste Vico et la philosophie pratique  par Persée"&gt; philosophie pratique&lt;/a&gt;, de l’histoire et des sciences humaines avec son ouvrage "La Science nouvelle" (paru en 1725), où il critique le rationalisme cartésien et propose une &lt;a href="https://www.youtube.com/watch?v=-OWc7ej_ixM" style="color:#88A1E9" title="Giambattista Vico: Consciousness and the Cycles of History par Spiritual Quest"&gt;approche alternative&lt;/a&gt;, centrée sur la complexité et l’historicité des sociétés humaines. Il y développe l’idée que la vérité n’est pas simplement découverte mais également construite. Selon lui, alors que Dieu connaît parfaitement la nature en tant que créateur, l’humain ne connaît parfaitement que ce qu’il crée lui-même, comme les mathématiques et les institutions humaines. &lt;/p&gt; &lt;p&gt; Il est aussi considéré comme le précurseur de la  &lt;a href="https://www.youtube.com/watch?v=vEYpuH4KdWM" style="color:#88A1E9" title=" Giambattista Vico, "The New Science" | A Philosophy of the History of Human Ideas and Institutions par Gavin Young Philosophy"&gt;philosophie de l’histoire&lt;/a&gt; et de l'épistémologie constructiviste, car il affirme que la connaissance humaine résulte essentiellement d’un processus collectif de création et d’invention. Sa critique du cartésianisme, son attention à la pluralité des formes de savoir (histoire, philologie, droit, rhétorique) et son intuition de la spécificité des sciences sociales l’inscrivent à contre-courant des philosophies réductionnistes de son époque. &lt;/p&gt; &lt;p&gt; Il élabore une théorie cyclique du développement des sociétés, fondée sur trois âges : l’âge des dieux, l’âge des héros et l’âge des hommes, chacun marquant une transformation des mœurs, du droit et de la politique. Il affirme que chaque peuple passe par ces étapes, de la mythologie religieuse à la raison civique, et que ce mouvement forme la trame de l’histoire humaine.  &lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F47" s="47" t="inlineStr">
-        <is>
-          <t>IohgI_XC3gI</t>
-        </is>
-      </c>
-      <c r="G47" s="49" t="inlineStr">
-        <is>
-          <t>"Vico : Une science de l'homme est-elle possible?" par Philo-Man</t>
-        </is>
-      </c>
-      <c r="H47" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/vico-mini.webp</t>
         </is>
       </c>
       <c r="I47" s="45" t="n"/>
       <c r="J47" s="38" t="inlineStr">
         <is>
-          <t>Italienne</t>
+          <t>Française</t>
         </is>
       </c>
       <c r="K47" s="45" t="inlineStr">
         <is>
-          <t>epistemologie ; politique</t>
+          <t>politique ; ethique</t>
         </is>
       </c>
       <c r="L47" s="46" t="inlineStr">
         <is>
-          <t>Herméneutique</t>
+          <t xml:space="preserve">Matérialisme ; Athéisme</t>
         </is>
       </c>
       <c r="M47" s="35" t="inlineStr">
         <is>
-          <t>philosophe italien qui élabora une métaphysique et une philosophie de l'histoire.</t>
+          <t>philosophe et prêtre français connu pour son Athéisme radical.</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3796,64 +3796,64 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="126.75" customHeight="1" s="39">
+    <row r="48" ht="147.75" customHeight="1" s="39">
       <c r="A48" s="47" t="n">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="B48" s="47" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="C48" s="47" t="inlineStr">
         <is>
-          <t>1670 – 1733</t>
+          <t>1668 – 1744</t>
         </is>
       </c>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>Bernard MANDEVILLE</t>
+          <t>Giambattista VICO</t>
         </is>
       </c>
       <c r="E48" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Mandeville_(philosophe)"   title=" Wikipedia"&gt;Bernard MANDEVILLE&lt;/a&gt; était un médecin et philosophe moral d’origine hollandaise, installé à Londres, devenu célèbre par son ouvrage satirique  &lt;a href="https://www.youtube.com/watch?v=hDQB2N3FzJA"  title=" La Fable des Abeilles – Et si le vice faisait tourner le monde ? | Mandeville par Capsio"&gt;"La Fable des abeilles" &lt;/a&gt; paru en 1714. Il y propose une vision provocatrice de la société commerciale moderne, qui fera de lui un précurseur à la fois du libéralisme économique et d’un certain utilitarisme. &lt;/p&gt; &lt;p&gt; Dans cet ouvrage, une ruche prospère vit grâce aux   &lt;a href="https://www.youtube.com/watch?v=Gdc0G67brI0"  title=" L' ÉLOGE DU VICE en 6 minutes ! (Bernard MANDEVILLE - Vices privés, vertu publique) par Culture Philo"&gt;passions égoïstes  &lt;/a&gt; de ses habitants (vanité, luxe, cupidité.). Lorsque ces abeilles deviennent soudain vertueuses et frugales, la prospérité disparaît : le commerce se contracte, les métiers liés au luxe s’effondrent, et la ruche finit pauvre mais “vertueuse”. &lt;/p&gt; &lt;p&gt; Il  a une conception très sombre de la nature humaine : pour lui, nos passions naturelles sont toutes intéressées, donc égoïstes. Une action n’est vraiment vertueuse que si elle implique un véritable renoncement à soi, ce qui la rend extrêmement rare ; pratiquement toutes les actions ordinaires restent traversées par l’amour de soi. Il en conclut que la &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1983_num_67_1_2319" title="Bernard Mandeville, moraliste et métaphysicien par Persée"&gt;morale “civile” &lt;/a&gt; est en grande partie une invention politique : les gouvernants transforment les passions (amour de la gloire, désir de reconnaissance, peur de la honte) en vertus utiles à l’ordre social. &lt;/p&gt; &lt;p&gt; Ses analyses de la consommation de luxe montrent que les dépenses ostentatoires des riches font vivre de nombreux artisans et ouvriers : ce qui apparaît comme “vice” du point de vue moral classique devient moteur d’activité du point de vue économique. Cette lecture en fait un des inspirateurs lointains d’Adam Smith, de Hayek et, via l’idée de demande effective, de Keynes.&lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giambattista_Vico"  title=" Wikipedia"&gt;Giambattista VICO&lt;/a&gt; était un  philosophe, historien et pédagogue italien reconnu comme un pionnier de la &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1993_num_91_90_6790" style="color:#88A1E9" title=" La sagesse de l'histoire. Jean-Baptiste Vico et la philosophie pratique  par Persée"&gt; philosophie pratique&lt;/a&gt;, de l’histoire et des sciences humaines avec son ouvrage "La Science nouvelle" (paru en 1725), où il critique le rationalisme cartésien et propose une &lt;a href="https://www.youtube.com/watch?v=-OWc7ej_ixM" style="color:#88A1E9" title="Giambattista Vico: Consciousness and the Cycles of History par Spiritual Quest"&gt;approche alternative&lt;/a&gt;, centrée sur la complexité et l’historicité des sociétés humaines. Il y développe l’idée que la vérité n’est pas simplement découverte mais également construite. Selon lui, alors que Dieu connaît parfaitement la nature en tant que créateur, l’humain ne connaît parfaitement que ce qu’il crée lui-même, comme les mathématiques et les institutions humaines. &lt;/p&gt; &lt;p&gt; Il est aussi considéré comme le précurseur de la  &lt;a href="https://www.youtube.com/watch?v=vEYpuH4KdWM" style="color:#88A1E9" title=" Giambattista Vico, "The New Science" | A Philosophy of the History of Human Ideas and Institutions par Gavin Young Philosophy"&gt;philosophie de l’histoire&lt;/a&gt; et de l'épistémologie constructiviste, car il affirme que la connaissance humaine résulte essentiellement d’un processus collectif de création et d’invention. Sa critique du cartésianisme, son attention à la pluralité des formes de savoir (histoire, philologie, droit, rhétorique) et son intuition de la spécificité des sciences sociales l’inscrivent à contre-courant des philosophies réductionnistes de son époque. &lt;/p&gt; &lt;p&gt; Il élabore une théorie cyclique du développement des sociétés, fondée sur trois âges : l’âge des dieux, l’âge des héros et l’âge des hommes, chacun marquant une transformation des mœurs, du droit et de la politique. Il affirme que chaque peuple passe par ces étapes, de la mythologie religieuse à la raison civique, et que ce mouvement forme la trame de l’histoire humaine.  &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F48" s="47" t="inlineStr">
         <is>
-          <t>PWsYvPlzhC8</t>
+          <t>IohgI_XC3gI</t>
         </is>
       </c>
       <c r="G48" s="49" t="inlineStr">
         <is>
-          <t>"BERNARD MANDEVILLE UN SACRÉ APICULTEUR : LA FABLE DES ABEILLES" par ECRITAU MAG</t>
+          <t>"Vico : Une science de l'homme est-elle possible?" par Philo-Man</t>
         </is>
       </c>
       <c r="H48" s="49" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/mandeville-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/vico-mini.webp</t>
         </is>
       </c>
       <c r="I48" s="45" t="n"/>
       <c r="J48" s="38" t="inlineStr">
         <is>
-          <t>Néerlandaise</t>
+          <t>Italienne</t>
         </is>
       </c>
       <c r="K48" s="45" t="inlineStr">
         <is>
-          <t>ethique ; politique</t>
+          <t>epistemologie ; politique</t>
         </is>
       </c>
       <c r="L48" s="46" t="inlineStr">
         <is>
-          <t>Libéralisme</t>
+          <t>Herméneutique</t>
         </is>
       </c>
       <c r="M48" s="35" t="inlineStr">
         <is>
-          <t>philosophe hollandais célèbre par son ouvrage satirique "La Fable des Abeilles".</t>
+          <t>philosophe italien qui élabora une métaphysique et une philosophie de l'histoire.</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3862,293 +3862,359 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="147.75" customHeight="1" s="39">
+    <row r="49" ht="126.75" customHeight="1" s="39">
       <c r="A49" s="47" t="n">
-        <v>1679</v>
+        <v>1670</v>
       </c>
       <c r="B49" s="47" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="C49" s="47" t="inlineStr">
         <is>
-          <t>1679 – 1754</t>
+          <t>1670 – 1733</t>
         </is>
       </c>
       <c r="D49" s="48" t="inlineStr">
         <is>
-          <t>Christian WOLFF</t>
+          <t>Bernard MANDEVILLE</t>
         </is>
       </c>
       <c r="E49" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Wolff_(philosophe)"   title=" Wikipedia"&gt;Christian WOLFF&lt;/a&gt; (1679-1754) est un philosophe, mathématicien et juriste allemand, le grand représentant des débuts des Lumières en Allemagne, l’&lt;em&gt;Aufklärung&lt;/em&gt;. Né à Breslau, il étudie la théologie et les mathématiques à Iéna, puis enseigne à l’université de Halle à partir de 1706, sur la recommandation de Leibniz, avec qui il correspond.&lt;/p&gt; &lt;p&gt;Wolff veut construire un système complet de la philosophie, démontré avec la rigueur des mathématiques à partir du principe de contradiction et du principe de raison suffisante. Il reprend de nombreuses idées de Leibniz, d’où le nom de « philosophie leibnizo-wolffienne », mais les organise en un ensemble ordonné, qui &lt;a href="https://www.youtube.com/watch?v=vfmME7Qcgh4"  title="Christian Wolff (philosopher) par WikiReader"&gt;structure la philosophie&lt;/a&gt; en disciplines : la logique, l’ontologie, ou science de l’être en général, la cosmologie, la psychologie rationnelle, la théologie naturelle, puis l’éthique, le droit et la politique. Il écrit d’abord en allemand, ce qui contribue à faire de cette langue une langue philosophique, avec de nombreux termes qu’il crée, puis en latin, dans de grands traités comme son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1964_num_62_74_7932_t1_0360_0000_2" title="Christian Wolff, Philosophia prima sive Ontologia edidit et curavit Joannes Ecole par Persée"&gt;&lt;em&gt;Ontologie&lt;/em&gt;&lt;/a&gt; (1730). En 1721, un discours où il loue la morale des Chinois, fondée sur la raison sans recours à la révélation, provoque la colère des théologiens piétistes, qui l’accusent de fatalisme. En 1723, le roi Frédéric-Guillaume Ier le chasse de Prusse en quarante-huit heures, sous peine de pendaison. Il trouve refuge à Marbourg, où sa renommée devient européenne.&lt;/p&gt; &lt;p&gt;Rappelé à Halle en 1740 par Frédéric II, il domine l’enseignement universitaire allemand. Kant, formé dans sa tradition, critiquera son « dogmatisme », tout en saluant sa rigueur.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_Mandeville_(philosophe)"   title=" Wikipedia"&gt;Bernard MANDEVILLE&lt;/a&gt; était un médecin et philosophe moral d’origine hollandaise, installé à Londres, devenu célèbre par son ouvrage satirique  &lt;a href="https://www.youtube.com/watch?v=hDQB2N3FzJA"  title=" La Fable des Abeilles – Et si le vice faisait tourner le monde ? | Mandeville par Capsio"&gt;"La Fable des abeilles" &lt;/a&gt; paru en 1714. Il y propose une vision provocatrice de la société commerciale moderne, qui fera de lui un précurseur à la fois du libéralisme économique et d’un certain utilitarisme. &lt;/p&gt; &lt;p&gt; Dans cet ouvrage, une ruche prospère vit grâce aux   &lt;a href="https://www.youtube.com/watch?v=Gdc0G67brI0"  title=" L' ÉLOGE DU VICE en 6 minutes ! (Bernard MANDEVILLE - Vices privés, vertu publique) par Culture Philo"&gt;passions égoïstes  &lt;/a&gt; de ses habitants (vanité, luxe, cupidité.). Lorsque ces abeilles deviennent soudain vertueuses et frugales, la prospérité disparaît : le commerce se contracte, les métiers liés au luxe s’effondrent, et la ruche finit pauvre mais “vertueuse”. &lt;/p&gt; &lt;p&gt; Il  a une conception très sombre de la nature humaine : pour lui, nos passions naturelles sont toutes intéressées, donc égoïstes. Une action n’est vraiment vertueuse que si elle implique un véritable renoncement à soi, ce qui la rend extrêmement rare ; pratiquement toutes les actions ordinaires restent traversées par l’amour de soi. Il en conclut que la &lt;a href="https://www.persee.fr/doc/raipr_0033-9075_1983_num_67_1_2319" title="Bernard Mandeville, moraliste et métaphysicien par Persée"&gt;morale “civile” &lt;/a&gt; est en grande partie une invention politique : les gouvernants transforment les passions (amour de la gloire, désir de reconnaissance, peur de la honte) en vertus utiles à l’ordre social. &lt;/p&gt; &lt;p&gt; Ses analyses de la consommation de luxe montrent que les dépenses ostentatoires des riches font vivre de nombreux artisans et ouvriers : ce qui apparaît comme “vice” du point de vue moral classique devient moteur d’activité du point de vue économique. Cette lecture en fait un des inspirateurs lointains d’Adam Smith, de Hayek et, via l’idée de demande effective, de Keynes.&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F49" s="47" t="inlineStr">
         <is>
-          <t>KWCHoM3ujTA</t>
+          <t>PWsYvPlzhC8</t>
         </is>
       </c>
       <c r="G49" s="49" t="inlineStr">
         <is>
-          <t>"CHRISTIAN WOLFF - The Genius Behind the Rationalism" par Few Minutes Knowledge</t>
+          <t>"BERNARD MANDEVILLE UN SACRÉ APICULTEUR : LA FABLE DES ABEILLES" par ECRITAU MAG</t>
         </is>
       </c>
       <c r="H49" s="49" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/wolff-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/mandeville-mini.webp</t>
         </is>
       </c>
       <c r="I49" s="45" t="n"/>
       <c r="J49" s="38" t="inlineStr">
         <is>
+          <t>Néerlandaise</t>
+        </is>
+      </c>
+      <c r="K49" s="45" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L49" s="46" t="inlineStr">
+        <is>
+          <t>Libéralisme</t>
+        </is>
+      </c>
+      <c r="M49" s="35" t="inlineStr">
+        <is>
+          <t>philosophe hollandais célèbre par son ouvrage satirique "La Fable des Abeilles".</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="147.75" customHeight="1" s="39">
+      <c r="A50" s="47" t="n">
+        <v>1679</v>
+      </c>
+      <c r="B50" s="47" t="inlineStr">
+        <is>
+          <t>1754</t>
+        </is>
+      </c>
+      <c r="C50" s="47" t="inlineStr">
+        <is>
+          <t>1679 – 1754</t>
+        </is>
+      </c>
+      <c r="D50" s="48" t="inlineStr">
+        <is>
+          <t>Christian WOLFF</t>
+        </is>
+      </c>
+      <c r="E50" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Wolff_(philosophe)"   title=" Wikipedia"&gt;Christian WOLFF&lt;/a&gt; (1679-1754) est un philosophe, mathématicien et juriste allemand, le grand représentant des débuts des Lumières en Allemagne, l’&lt;em&gt;Aufklärung&lt;/em&gt;. Né à Breslau, il étudie la théologie et les mathématiques à Iéna, puis enseigne à l’université de Halle à partir de 1706, sur la recommandation de Leibniz, avec qui il correspond.&lt;/p&gt; &lt;p&gt;Wolff veut construire un système complet de la philosophie, démontré avec la rigueur des mathématiques à partir du principe de contradiction et du principe de raison suffisante. Il reprend de nombreuses idées de Leibniz, d’où le nom de « philosophie leibnizo-wolffienne », mais les organise en un ensemble ordonné, qui &lt;a href="https://www.youtube.com/watch?v=vfmME7Qcgh4"  title="Christian Wolff (philosopher) par WikiReader"&gt;structure la philosophie&lt;/a&gt; en disciplines : la logique, l’ontologie, ou science de l’être en général, la cosmologie, la psychologie rationnelle, la théologie naturelle, puis l’éthique, le droit et la politique. Il écrit d’abord en allemand, ce qui contribue à faire de cette langue une langue philosophique, avec de nombreux termes qu’il crée, puis en latin, dans de grands traités comme son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1964_num_62_74_7932_t1_0360_0000_2" title="Christian Wolff, Philosophia prima sive Ontologia edidit et curavit Joannes Ecole par Persée"&gt;&lt;em&gt;Ontologie&lt;/em&gt;&lt;/a&gt; (1730). En 1721, un discours où il loue la morale des Chinois, fondée sur la raison sans recours à la révélation, provoque la colère des théologiens piétistes, qui l’accusent de fatalisme. En 1723, le roi Frédéric-Guillaume Ier le chasse de Prusse en quarante-huit heures, sous peine de pendaison. Il trouve refuge à Marbourg, où sa renommée devient européenne.&lt;/p&gt; &lt;p&gt;Rappelé à Halle en 1740 par Frédéric II, il domine l’enseignement universitaire allemand. Kant, formé dans sa tradition, critiquera son « dogmatisme », tout en saluant sa rigueur.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F50" s="47" t="inlineStr">
+        <is>
+          <t>KWCHoM3ujTA</t>
+        </is>
+      </c>
+      <c r="G50" s="49" t="inlineStr">
+        <is>
+          <t>"CHRISTIAN WOLFF - The Genius Behind the Rationalism" par Few Minutes Knowledge</t>
+        </is>
+      </c>
+      <c r="H50" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/wolff-mini.webp</t>
+        </is>
+      </c>
+      <c r="I50" s="45" t="n"/>
+      <c r="J50" s="38" t="inlineStr">
+        <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K49" s="45" t="inlineStr">
+      <c r="K50" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L49" s="46" t="inlineStr">
+      <c r="L50" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme ; Ontologie</t>
         </is>
       </c>
-      <c r="M49" s="35" t="inlineStr">
+      <c r="M50" s="35" t="inlineStr">
         <is>
           <t>philosophe allemand qui systématisa la philosophie rationnelle en allemand.</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="164.9" customHeight="1" s="39">
-      <c r="A50" s="47" t="n">
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="164.9" customHeight="1" s="39">
+      <c r="A51" s="47" t="n">
         <v>1685</v>
       </c>
-      <c r="B50" s="47" t="inlineStr">
+      <c r="B51" s="47" t="inlineStr">
         <is>
           <t>1753</t>
         </is>
       </c>
-      <c r="C50" s="47" t="inlineStr">
+      <c r="C51" s="47" t="inlineStr">
         <is>
           <t>1685 – 1753</t>
         </is>
       </c>
-      <c r="D50" s="48" t="inlineStr">
+      <c r="D51" s="48" t="inlineStr">
         <is>
           <t>Georges BERKELEY</t>
         </is>
       </c>
-      <c r="E50" s="49" t="inlineStr">
+      <c r="E51" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley"    title=" Wikipedia"&gt;Georges BERKELEY&lt;/a&gt; (1685-1753) est un philosophe irlandais et évêque anglican, célèbre pour sa formule &lt;a href="https://www.youtube.com/watch?v=gcyFtJ1ZtrA"  title=" Berkeley Être c'est être perçu ou percevoir par Coursitout"&gt;&lt;em&gt;esse est percipi&lt;/em&gt;&lt;/a&gt;, « être, c’est être perçu ». Né près de Kilkenny, il étudie et enseigne au Trinity College de Dublin. Il séjourne en Amérique pour fonder un collège aux Bermudes, projet qui échoue, puis devient en 1734 évêque de Cloyne, en Irlande.&lt;/p&gt; &lt;p&gt;Dans l’&lt;em&gt;Essai pour une nouvelle théorie de la vision&lt;/em&gt; (1709), il montre que nous ne voyons pas directement la distance : nous l’apprenons en associant la vue au toucher. Dans le &lt;a href="https://www.youtube.com/watch?v=wBivRdgKgd0"  title=" Berkeley pour les nuls  par Alexis Vildier"&gt;&lt;em&gt;Traité des principes de la connaissance humaine&lt;/em&gt;&lt;/a&gt; (1710), puis dans les &lt;em&gt;Trois Dialogues entre Hylas et Philonous&lt;/em&gt; (1713), il défend une position &lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Immatérialisme  par Wikipedia"&gt;immatérialiste&lt;/a&gt;. Locke distinguait les qualités secondes des choses, couleurs, sons ou saveurs, qui n’existent que dans notre esprit, et leurs qualités premières, étendue, figure, mouvement, qui existeraient dans une matière extérieure. Berkeley montre que ces dernières sont aussi des idées : on ne peut concevoir une étendue sans couleur. Une chose n’est donc qu’un ensemble d’idées, et l’idée d’une « substance matérielle » cachée derrière nos perceptions est vide. Seuls existent les esprits et leurs idées. Si l’arbre du jardin continue d’exister quand personne ne le regarde, c’est que Dieu le perçoit toujours. Berkeley pense ainsi combattre le scepticisme et l’athéisme, que favorisait selon lui la croyance en une matière indépendante.&lt;/p&gt; &lt;p&gt;Sa doctrine, jugée paradoxale par ses contemporains, a marqué Hume et Kant. Une ville de Californie, siège d’une célèbre université, porte son nom.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F50" s="47" t="inlineStr">
+      <c r="F51" s="47" t="inlineStr">
         <is>
           <t>x42AwlrUOII</t>
         </is>
       </c>
-      <c r="G50" s="49" t="inlineStr">
+      <c r="G51" s="49" t="inlineStr">
         <is>
           <t>"George Berkeley: Challenging Materialism" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H50" s="49" t="inlineStr">
+      <c r="H51" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/berkeley-mini.webp</t>
         </is>
       </c>
-      <c r="I50" s="45" t="n"/>
-      <c r="J50" s="55" t="inlineStr">
+      <c r="I51" s="45" t="n"/>
+      <c r="J51" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K50" s="45" t="inlineStr">
+      <c r="K51" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L50" s="46" t="inlineStr">
+      <c r="L51" s="46" t="inlineStr">
         <is>
           <t>Immatérialisme ; Phénoménisme</t>
         </is>
       </c>
-      <c r="M50" s="35" t="inlineStr">
+      <c r="M51" s="35" t="inlineStr">
         <is>
           <t>philosophe et évêque irlandais célèbre pour sa philosophie empiriste et idéaliste.</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P50">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P51">
         <v>2</v>
       </c>
     </row>
-    <row r="51" ht="150" customHeight="1" s="39">
-      <c r="A51" s="47" t="n">
+    <row r="52" ht="150" customHeight="1" s="39">
+      <c r="A52" s="47" t="n">
         <v>1688</v>
       </c>
-      <c r="B51" s="47" t="inlineStr">
+      <c r="B52" s="47" t="inlineStr">
         <is>
           <t>1772</t>
         </is>
       </c>
-      <c r="C51" s="47" t="inlineStr">
+      <c r="C52" s="47" t="inlineStr">
         <is>
           <t>1688 – 1772</t>
         </is>
       </c>
-      <c r="D51" s="48" t="inlineStr">
+      <c r="D52" s="48" t="inlineStr">
         <is>
           <t>Emanuel SWEDENBORG</t>
         </is>
       </c>
-      <c r="E51" s="49" t="inlineStr">
+      <c r="E52" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emanuel_Swedenborg"  title=" Wikipedia"&gt;Emanuel SWEDENBORG&lt;/a&gt;   était  un scientifique, philosophe et théologien suédois connu pour son passage du rationalisme scientifique au mysticisme chrétien. Issu d'une famille luthérienne, il excella en sciences avant de vivre des visions spirituelles dès 1744, affirmant recevoir des &lt;a href="https://www.youtube.com/watch?v=w4oPoKLes1w" title="Emanuel Swedenborg – Le Savant devenu Visionnaire | Biographie Mystique par SoulNym"&gt;révélations divines &lt;/a&gt; sur l'interprétation des Écritures. Fils d'un théologien et recteur d'université, il étudia la philosophie, les mathématiques et l'ingénierie à Uppsala, puis voyagea en Europe pour approfondir ses connaissances auprès de figures comme Christian Wolff. &lt;/p&gt; &lt;p&gt; Nommé assesseur au Collège du Mines en 1716, il inventa des machines et publia sur la métallurgie, tout en siégeant au parlement suédois. Vers 1745, une crise spirituelle le poussa à abandonner ses fonctions scientifiques pour se &lt;a href="https://www.persee.fr/doc/caief_0571-5865_1963_num_15_1_2263"  title="Balzac et Swedenborg par Persée"&gt;consacrer à la théologie,&lt;/a&gt;  voyageant entre Stockholm, Londres et Amsterdam jusqu'à sa mort le 29 mars 1772 à Londres. &lt;/p&gt; &lt;p&gt; Ses premiers travaux, comme "Opera Philosophica et Mineralia" en 1734, explorent la philosophie de la nature, la géométrie et la métallurgie, cherchant à unir matière et esprit via une méthode inductive proche des sciences modernes. "Oeconomia Regni Animalis" paru en 1740 analyse l'anatomie et la physiologie, anticipant des découvertes sur les glandes endocrines et les fonctions cérébrales. &lt;/p&gt; &lt;p&gt; À partir de Arcana Cœlestia (1749-1756), il développe une exégèse symbolique de la Bible, introduisant la théorie des "correspondances" entre monde physique et spirituel, et une vision unitaire de Dieu (Trinité comme amour, sagesse et action). Ses écrits, comme La Vraie Religion Chrétienne (1771), fondèrent l'Église de la Nouvelle Jérusalem, influençant Blake, Kant et le romantisme. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F51" s="47" t="inlineStr">
+      <c r="F52" s="47" t="inlineStr">
         <is>
           <t>aO2eXURYpSQ</t>
         </is>
       </c>
-      <c r="G51" s="49" t="inlineStr">
+      <c r="G52" s="49" t="inlineStr">
         <is>
           <t>"Emanuel Swedenborg: The Mystic Scientist" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H51" s="49" t="inlineStr">
+      <c r="H52" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/swedenborg-mini.webp</t>
-        </is>
-      </c>
-      <c r="I51" s="45" t="n"/>
-      <c r="J51" s="38" t="inlineStr">
-        <is>
-          <t>Suédoise</t>
-        </is>
-      </c>
-      <c r="K51" s="45" t="inlineStr">
-        <is>
-          <t>metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L51" s="46" t="inlineStr">
-        <is>
-          <t>Mysticisme ; Spiritualisme</t>
-        </is>
-      </c>
-      <c r="M51" s="35" t="inlineStr">
-        <is>
-          <t>philosophe suédois qui est passé du rationalisme scientifique au mysticisme chrétien.</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="168" customHeight="1" s="39">
-      <c r="A52" s="47" t="n">
-        <v>1689</v>
-      </c>
-      <c r="B52" s="47" t="inlineStr">
-        <is>
-          <t>1755</t>
-        </is>
-      </c>
-      <c r="C52" s="47" t="inlineStr">
-        <is>
-          <t>1689 – 1755</t>
-        </is>
-      </c>
-      <c r="D52" s="48" t="inlineStr">
-        <is>
-          <t>MONTESQUIEU</t>
-        </is>
-      </c>
-      <c r="E52" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Montesquieu"    title=" Wikipedia"&gt;MONTESTQUIEU&lt;/a&gt; était un grand philosophe et écrivain français  associé au mouvement des Lumières et connu pour sa théorie de la séparation des pouvoirs. Il s’appelle en réalité Charles‑Louis de Secondat, baron de La Brède et de Montesquieu, et naît  près de Bordeaux dans une famille de noblesse de robe. &lt;/p&gt; &lt;p&gt; Deux œuvres dominent sa postérité : &lt;a href="https://www.youtube.com/watch?v=e72jQdl52bM" title=" Les Lettres persanes, Montesquieu  par Les Bons Profs"&gt;"les Lettres persanes"&lt;/a&gt;, un roman épistolaire satirique où des voyageurs persans observent la société française et critiquent l’absolutisme, les mœurs et l’intolérance religieuse, en utilisant le regard extérieur comme miroir critique et &lt;a href="https://www.youtube.com/watch?v=IBc46RLZxe4" title=" L'ESPRIT DES LOIS en 8 minutes ! par Culture Philo"&gt;"De l’esprit des lois"&lt;/a&gt;, un vaste traité de science politique et sociale qui analyse les types de gouvernement, le rôle des lois, l’influence du climat et des mœurs, et propose une nouvelle manière “scientifique” d’étudier les sociétés.​ &lt;/p&gt; &lt;p&gt; Il est l’un des &lt;a href="https://expositions.bnf.fr/montesquieu/un-ecrivain-philosophe.htm" title=" un écrivain philosophe par BNF"&gt;grands théoriciens&lt;/a&gt; du libéralisme classique et de la limitation du pouvoir politique. Il distingue notamment trois grands types de gouvernement : républicain, monarchique et despotique, en fonction du principe qui les fait tenir. Il parle de séparation des pouvoirs : le pouvoir législatif, l’exécutif et le judiciaire doivent être confiés à des organes distincts afin d’empêcher la concentration du pouvoir et de garantir la liberté. &lt;/p&gt; &lt;p&gt; Il critique la monarchie absolue et met en garde contre le despotisme, qu’il considère comme le régime où la peur domine et où les lois se confondent avec le bon plaisir du souverain.​ Il défend la &lt;a href="https://www.youtube.com/watch?v=2Ye6LrpTq9g" title=" le père de la démocratie  par Portrait Historiques"&gt;liberté politique &lt;/a&gt; comme sécurité du citoyen, la tolérance religieuse et une certaine forme d’universalisme, positions qui en font un précurseur et un modèle pour d’autres philosophes des Lumières. &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="L'esprit de Montesquieu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24812-04.07.2011-ITEMA_23734145-2011C12410E0183-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F52" s="47" t="inlineStr">
-        <is>
-          <t>mK7zNAqI_GQ</t>
-        </is>
-      </c>
-      <c r="G52" s="49" t="inlineStr">
-        <is>
-          <t>"Montesquieu - Grand Ecrivain " par Culture Tube</t>
-        </is>
-      </c>
-      <c r="H52" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/montesquieu-mini.webp</t>
         </is>
       </c>
       <c r="I52" s="45" t="n"/>
       <c r="J52" s="38" t="inlineStr">
         <is>
+          <t>Suédoise</t>
+        </is>
+      </c>
+      <c r="K52" s="45" t="inlineStr">
+        <is>
+          <t>metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L52" s="46" t="inlineStr">
+        <is>
+          <t>Mysticisme ; Spiritualisme</t>
+        </is>
+      </c>
+      <c r="M52" s="35" t="inlineStr">
+        <is>
+          <t>philosophe suédois qui est passé du rationalisme scientifique au mysticisme chrétien.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="168" customHeight="1" s="39">
+      <c r="A53" s="47" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B53" s="47" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="C53" s="47" t="inlineStr">
+        <is>
+          <t>1689 – 1755</t>
+        </is>
+      </c>
+      <c r="D53" s="48" t="inlineStr">
+        <is>
+          <t>MONTESQUIEU</t>
+        </is>
+      </c>
+      <c r="E53" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Montesquieu"    title=" Wikipedia"&gt;MONTESTQUIEU&lt;/a&gt; était un grand philosophe et écrivain français  associé au mouvement des Lumières et connu pour sa théorie de la séparation des pouvoirs. Il s’appelle en réalité Charles‑Louis de Secondat, baron de La Brède et de Montesquieu, et naît  près de Bordeaux dans une famille de noblesse de robe. &lt;/p&gt; &lt;p&gt; Deux œuvres dominent sa postérité : &lt;a href="https://www.youtube.com/watch?v=e72jQdl52bM" title=" Les Lettres persanes, Montesquieu  par Les Bons Profs"&gt;"les Lettres persanes"&lt;/a&gt;, un roman épistolaire satirique où des voyageurs persans observent la société française et critiquent l’absolutisme, les mœurs et l’intolérance religieuse, en utilisant le regard extérieur comme miroir critique et &lt;a href="https://www.youtube.com/watch?v=IBc46RLZxe4" title=" L'ESPRIT DES LOIS en 8 minutes ! par Culture Philo"&gt;"De l’esprit des lois"&lt;/a&gt;, un vaste traité de science politique et sociale qui analyse les types de gouvernement, le rôle des lois, l’influence du climat et des mœurs, et propose une nouvelle manière “scientifique” d’étudier les sociétés.​ &lt;/p&gt; &lt;p&gt; Il est l’un des &lt;a href="https://expositions.bnf.fr/montesquieu/un-ecrivain-philosophe.htm" title=" un écrivain philosophe par BNF"&gt;grands théoriciens&lt;/a&gt; du libéralisme classique et de la limitation du pouvoir politique. Il distingue notamment trois grands types de gouvernement : républicain, monarchique et despotique, en fonction du principe qui les fait tenir. Il parle de séparation des pouvoirs : le pouvoir législatif, l’exécutif et le judiciaire doivent être confiés à des organes distincts afin d’empêcher la concentration du pouvoir et de garantir la liberté. &lt;/p&gt; &lt;p&gt; Il critique la monarchie absolue et met en garde contre le despotisme, qu’il considère comme le régime où la peur domine et où les lois se confondent avec le bon plaisir du souverain.​ Il défend la &lt;a href="https://www.youtube.com/watch?v=2Ye6LrpTq9g" title=" le père de la démocratie  par Portrait Historiques"&gt;liberté politique &lt;/a&gt; comme sécurité du citoyen, la tolérance religieuse et une certaine forme d’universalisme, positions qui en font un précurseur et un modèle pour d’autres philosophes des Lumières. &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="L'esprit de Montesquieu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/24812-04.07.2011-ITEMA_23734145-2011C12410E0183-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="47" t="inlineStr">
+        <is>
+          <t>mK7zNAqI_GQ</t>
+        </is>
+      </c>
+      <c r="G53" s="49" t="inlineStr">
+        <is>
+          <t>"Montesquieu - Grand Ecrivain " par Culture Tube</t>
+        </is>
+      </c>
+      <c r="H53" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/montesquieu-mini.webp</t>
+        </is>
+      </c>
+      <c r="I53" s="45" t="n"/>
+      <c r="J53" s="38" t="inlineStr">
+        <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K52" s="45" t="inlineStr">
+      <c r="K53" s="45" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="L52" s="46" t="inlineStr">
+      <c r="L53" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Libéralisme ; Lumières</t>
         </is>
       </c>
-      <c r="M52" s="35" t="inlineStr">
+      <c r="M53" s="35" t="inlineStr">
         <is>
           <t>philosophe penseur de l'organisation politique et sociale des sociétés modernes.</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="177" customHeight="1" s="39">
-      <c r="A53" s="47" t="n">
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="177" customHeight="1" s="39">
+      <c r="A54" s="47" t="n">
         <v>1694</v>
       </c>
-      <c r="B53" s="47" t="inlineStr">
+      <c r="B54" s="47" t="inlineStr">
         <is>
           <t>1778</t>
         </is>
       </c>
-      <c r="C53" s="47" t="inlineStr">
+      <c r="C54" s="47" t="inlineStr">
         <is>
           <t>1694 - 1778</t>
         </is>
       </c>
-      <c r="D53" s="48" t="inlineStr">
+      <c r="D54" s="48" t="inlineStr">
         <is>
           <t>VOLTAIRE</t>
         </is>
       </c>
-      <c r="E53" s="58" t="inlineStr">
+      <c r="E54" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Voltaire"   title=" Wikipedia"&gt; VOLTAIRE&lt;/a&gt;, de son vrai nom François-Marie Arouet, est un philosophe de l'époque des  &lt;a href="https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;t=380s&amp;ab_channel=LePr%C3%A9cepteur"  title=" La philosophie des lumières par le Précepteur "&gt;Lumières&lt;/a&gt; (ou Illuministe) en France. Il était aussi écrivain, poète, dramaturge et philosophe. &lt;/p&gt; &lt;p&gt;
 Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href="https://www.youtube.com/watch?v=XE1Z8jpVJUA" title=" la vie de Voltaire  par Portrait Historiques"&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation. Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;
@@ -4157,221 +4223,155 @@
 La contribution de Voltaire à la philosophie se caractérise par son engagement envers la raison, la liberté et la justice. Il a influencé de nombreux penseurs ultérieurs et a contribué à jeter les bases de la pensée libérale et humaniste qui a marqué les siècles suivants. Sa défense de la liberté d'expression reste une valeur fondamentale de nos sociétés démocratiques aujourd'hui. &lt;/p&gt; &lt;audio controls title="Voltaire et les Lumières par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-13.01.2021-ITEMA_22540842-2021C24632S0013.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F53" s="47" t="inlineStr">
+      <c r="F54" s="47" t="inlineStr">
         <is>
           <t>oUWrf3GUj0U</t>
         </is>
       </c>
-      <c r="G53" s="49" t="inlineStr">
+      <c r="G54" s="49" t="inlineStr">
         <is>
           <t>"Philosopher-Voltaire" par Guillaume Deloison</t>
         </is>
       </c>
-      <c r="H53" s="49" t="inlineStr">
+      <c r="H54" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/voltaire-mini.webp</t>
         </is>
       </c>
-      <c r="I53" s="45" t="n"/>
-      <c r="J53" s="38" t="inlineStr">
+      <c r="I54" s="45" t="n"/>
+      <c r="J54" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K53" s="45" t="inlineStr">
+      <c r="K54" s="45" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="L53" s="46" t="inlineStr">
+      <c r="L54" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Déisme ; Libéralisme ; Lumières</t>
         </is>
       </c>
-      <c r="M53" s="35" t="inlineStr">
+      <c r="M54" s="35" t="inlineStr">
         <is>
           <t>philosophe et écrivain français Déiste de l'époque des lumières.</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P53">
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P54">
         <v>3</v>
       </c>
     </row>
-    <row r="54" ht="147.75" customHeight="1" s="39">
-      <c r="A54" s="47" t="n">
+    <row r="55" ht="147.75" customHeight="1" s="39">
+      <c r="A55" s="47" t="n">
         <v>1694</v>
       </c>
-      <c r="B54" s="47" t="inlineStr">
+      <c r="B55" s="47" t="inlineStr">
         <is>
           <t>1746</t>
         </is>
       </c>
-      <c r="C54" s="47" t="inlineStr">
+      <c r="C55" s="47" t="inlineStr">
         <is>
           <t>1694 – 1746</t>
         </is>
       </c>
-      <c r="D54" s="48" t="inlineStr">
+      <c r="D55" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Francis HUTCHESON</t>
         </is>
       </c>
-      <c r="E54" s="62" t="inlineStr">
+      <c r="E55" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Francis_Hutcheson_(philosophe)"   title=" Wikipedia"&gt;Francis HUTCHESON&lt;/a&gt;  était un philosophe irlando-écossais  majeur des Lumières écossaises, surtout connu pour sa théorie du sens moral et pour son influence sur Hume, Smith et Reid. Il a enseigné la philosophie morale à l’université de Glasgow et a contribué aussi à l’esthétique, à la psychologie morale et à la pensée politique. Sa thèse la plus célèbre est que &lt;a href="https://www.persee.fr/doc/dhs_0070-6760_1994_num_26_1_2013_t1_0566_0000_3"   title=" Two Texts on Human Nature par Persée "&gt;l’être humain &lt;/a&gt; possède une faculté morale innée, un « moral sense », qui nous fait approuver spontanément les actions vertueuses et désapprouver les actions vicieuses, sans passer d’abord par un long raisonnement. &lt;/p&gt; &lt;p&gt; Il s’oppose aux théories qui réduisent la morale à l’égoïsme, comme celles de Hobbes ou de Mandeville, et il insiste au contraire sur le rôle de la bienveillance dans l’action morale. Il est aussi souvent vu comme un précurseur de &lt;a href="https://fr.wikipedia.org/wiki/Utilitarisme"   title=" Utilitarisme par Wikipedia "&gt;l’utilitarisme, &lt;/a&gt; parce qu’il relie le bien moral au bien-être général et à l’idée du « plus grand bonheur du plus grand nombre ». &lt;/p&gt; &lt;p&gt; Parmi ses textes les plus connus, on trouve An Inquiry into the Original of Our Ideas of Beauty and Virtue (1725) et An Essay on the Nature and Conduct of the Passions and Affections (1728). Ces ouvrages ont joué un rôle important dans la naissance de la philosophie morale moderne en langue anglaise. &lt;/p&gt; &lt;p&gt; Il  a fortement influencé la philosophie morale écossaise et des penseurs comme Adam Smith et David Hume. On lui doit aussi d’avoir contribué à faire de l’esthétique un domaine philosophique à part entière, en montrant que le beau peut aussi être perçu par une forme de sens intérieur. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F54" s="47" t="inlineStr">
+      <c r="F55" s="47" t="inlineStr">
         <is>
           <t>ARi0h-Izi5U</t>
         </is>
       </c>
-      <c r="G54" s="49" t="inlineStr">
+      <c r="G55" s="49" t="inlineStr">
         <is>
           <t>"When Self Meets Society |How Hutcheson’s Philosophy Inspires True Motivation?" par Success Saga Stories</t>
         </is>
       </c>
-      <c r="H54" s="49" t="inlineStr">
+      <c r="H55" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fhutcheson-mini.webp</t>
         </is>
       </c>
-      <c r="I54" s="45" t="n"/>
-      <c r="J54" s="38" t="inlineStr">
+      <c r="I55" s="45" t="n"/>
+      <c r="J55" s="38" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K54" s="45" t="inlineStr">
+      <c r="K55" s="45" t="inlineStr">
         <is>
           <t>ethique</t>
         </is>
       </c>
-      <c r="L54" s="46" t="inlineStr">
+      <c r="L55" s="46" t="inlineStr">
         <is>
           <t>Empirisme</t>
         </is>
       </c>
-      <c r="M54" s="35" t="inlineStr">
+      <c r="M55" s="35" t="inlineStr">
         <is>
           <t>philosophe irlando-écossais  majeur des Lumières écossaises.</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="133.5" customHeight="1" s="39">
-      <c r="A55" s="47" t="n">
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="133.5" customHeight="1" s="39">
+      <c r="A56" s="47" t="n">
         <v>1703</v>
       </c>
-      <c r="B55" s="47" t="inlineStr">
+      <c r="B56" s="47" t="inlineStr">
         <is>
           <t>1791</t>
         </is>
       </c>
-      <c r="C55" s="47" t="inlineStr">
+      <c r="C56" s="47" t="inlineStr">
         <is>
           <t>1703 – 1791</t>
         </is>
       </c>
-      <c r="D55" s="48" t="inlineStr">
+      <c r="D56" s="48" t="inlineStr">
         <is>
           <t>John WESLEY</t>
         </is>
       </c>
-      <c r="E55" s="49" t="inlineStr">
+      <c r="E56" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Wesley"  title=" Wikipedia"&gt;John WESLEY&lt;/a&gt; était un philosophe, religieux, théologien et évangélisateur anglais qui fut le déclencheur d'un mouvement de réveil au sein de l'Église d'Angleterre, connu sous le nom &lt;a href="https://www.youtube.com/watch?v=d1F_Ye3mSnE"  title="  John Wesley: les origines du méthodisme | Dans la lignée des héros de la foi par Ainsi parle l'éternel"&gt;de méthodisme&lt;/a&gt;.  Il combine une vaste culture (philosophie, langues, théologie) à une activité de prédication et de réforme. &lt;/p&gt; &lt;p&gt; Il étudie les lettres classiques à Oxford, apprend plusieurs langues et se destine à une vie religieuse dès 1725. Après un séjour d’évangélisation aux États-Unis, il revient marqué par la ferveur des moraves et, lors d’une  &lt;a href="https://www.youtube.com/watch?v=v-B6rEPbNQk"  title=" Qu’est ce qu’une expérience spirituelle par Numérologie &amp; Spiritualité"&gt;expérience spirituelle&lt;/a&gt; en 1738, affirme avoir trouvé l'assurance du salut – événement clé du méthodisme, qui repose sur le réveil personnel et l’expérience directe de la foi. Il se distingue par son opposition à la doctrine de la prédestination et par son attachement à l’arminianisme, qui valorise la responsabilité humaine et la conversion personnelle. Il insiste sur la « sanctification » : vivre selon l’amour du Christ et tendre vers une  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_2008_num_88_3_1347" title="Le Cheminement théologique de John Wesley (1703-1791) avec le catholicisme par Persée"&gt; perfection chrétienne&lt;/a&gt; dans la vie morale et sociale. Il combat aussi le déisme des Lumières, défendant un christianisme de révélation et d’engagement immédiat. &lt;/p&gt; &lt;p&gt; Il est aussi connu pour son engagement contre l’esclavage ; il considère la liberté comme un droit naturel et publie plusieurs écrits abolitionnistes. Il a influencé d’autres figures majeures du mouvement antiesclavagiste et prôné un christianisme impliqué dans la justice sociale. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F55" s="47" t="inlineStr">
+      <c r="F56" s="47" t="inlineStr">
         <is>
           <t>N8El4zSIY9A</t>
         </is>
       </c>
-      <c r="G55" s="49" t="inlineStr">
+      <c r="G56" s="49" t="inlineStr">
         <is>
           <t>"Prédication John Wesley en Français Marcher par la Foi ou par la vue" par Grâce &amp; Justice en Lui</t>
         </is>
       </c>
-      <c r="H55" s="49" t="inlineStr">
+      <c r="H56" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/wesley-mini.webp</t>
-        </is>
-      </c>
-      <c r="I55" s="45" t="n"/>
-      <c r="J55" s="55" t="inlineStr">
-        <is>
-          <t>Britannique</t>
-        </is>
-      </c>
-      <c r="K55" s="45" t="inlineStr">
-        <is>
-          <t>ethique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L55" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spiritualisme</t>
-        </is>
-      </c>
-      <c r="M55" s="35" t="inlineStr">
-        <is>
-          <t>philosophe anglais déclencheur d'un réveil de l'Église d'Angleterre, le méthodisme.</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="166.5" customHeight="1" s="39">
-      <c r="A56" s="47" t="n">
-        <v>1705</v>
-      </c>
-      <c r="B56" s="47" t="inlineStr">
-        <is>
-          <t>1757</t>
-        </is>
-      </c>
-      <c r="C56" s="47" t="inlineStr">
-        <is>
-          <t>1705 – 1757</t>
-        </is>
-      </c>
-      <c r="D56" s="48" t="inlineStr">
-        <is>
-          <t>David HARTLEY</t>
-        </is>
-      </c>
-      <c r="E56" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)"    title=" Wikipedia"&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href="https://www.youtube.com/watch?v=kbpEAw2gl40" title=" David Hartley par Crevoisier Philippe"&gt; développement de la psychologie&lt;/a&gt;, en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt;La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la "substance médullaire" (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt;La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des "vibratiuncules" (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs "vibratiuncules" respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href="https://www.youtube.com/shorts/BuqpLB9V41c"  title=" David Hartley par timelinephilosopher"&gt;  le fondement des idées et des pensées&lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des "vibratiuncules" de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, "Observations on Man, his Frame, his Duty, and his Expectations", publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt;L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt;Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F56" s="47" t="inlineStr">
-        <is>
-          <t>zYRbpPFmSWM</t>
-        </is>
-      </c>
-      <c r="G56" s="49" t="inlineStr">
-        <is>
-          <t>"Reprogramming Life with Hartley’s Wisdom |Reflections in the Mind’s Mirror" par Sucess saga Stories</t>
-        </is>
-      </c>
-      <c r="H56" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/hartley-mini.webp</t>
         </is>
       </c>
       <c r="I56" s="45" t="n"/>
@@ -4382,249 +4382,315 @@
       </c>
       <c r="K56" s="45" t="inlineStr">
         <is>
+          <t>ethique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L56" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spiritualisme</t>
+        </is>
+      </c>
+      <c r="M56" s="35" t="inlineStr">
+        <is>
+          <t>philosophe anglais déclencheur d'un réveil de l'Église d'Angleterre, le méthodisme.</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="166.5" customHeight="1" s="39">
+      <c r="A57" s="47" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B57" s="47" t="inlineStr">
+        <is>
+          <t>1757</t>
+        </is>
+      </c>
+      <c r="C57" s="47" t="inlineStr">
+        <is>
+          <t>1705 – 1757</t>
+        </is>
+      </c>
+      <c r="D57" s="48" t="inlineStr">
+        <is>
+          <t>David HARTLEY</t>
+        </is>
+      </c>
+      <c r="E57" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)"    title=" Wikipedia"&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href="https://www.youtube.com/watch?v=kbpEAw2gl40" title=" David Hartley par Crevoisier Philippe"&gt; développement de la psychologie&lt;/a&gt;, en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt;La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la "substance médullaire" (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt;La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des "vibratiuncules" (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs "vibratiuncules" respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href="https://www.youtube.com/shorts/BuqpLB9V41c"  title=" David Hartley par timelinephilosopher"&gt;  le fondement des idées et des pensées&lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des "vibratiuncules" de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, "Observations on Man, his Frame, his Duty, and his Expectations", publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt;L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt;Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F57" s="47" t="inlineStr">
+        <is>
+          <t>zYRbpPFmSWM</t>
+        </is>
+      </c>
+      <c r="G57" s="49" t="inlineStr">
+        <is>
+          <t>"Reprogramming Life with Hartley’s Wisdom |Reflections in the Mind’s Mirror" par Sucess saga Stories</t>
+        </is>
+      </c>
+      <c r="H57" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/hartley-mini.webp</t>
+        </is>
+      </c>
+      <c r="I57" s="45" t="n"/>
+      <c r="J57" s="55" t="inlineStr">
+        <is>
+          <t>Britannique</t>
+        </is>
+      </c>
+      <c r="K57" s="45" t="inlineStr">
+        <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L56" s="46" t="inlineStr">
+      <c r="L57" s="46" t="inlineStr">
         <is>
           <t>Empirisme</t>
         </is>
       </c>
-      <c r="M56" s="35" t="inlineStr">
+      <c r="M57" s="35" t="inlineStr">
         <is>
           <t>philosophe et psychologue anglais précurseur dans l'étude de l'esprit humain.</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="135" customHeight="1" s="39">
-      <c r="A57" s="47" t="n">
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="135" customHeight="1" s="39">
+      <c r="A58" s="47" t="n">
         <v>1709</v>
       </c>
-      <c r="B57" s="47" t="inlineStr">
+      <c r="B58" s="47" t="inlineStr">
         <is>
           <t>1751</t>
         </is>
       </c>
-      <c r="C57" s="47" t="inlineStr">
+      <c r="C58" s="47" t="inlineStr">
         <is>
           <t>1709 – 1751</t>
         </is>
       </c>
-      <c r="D57" s="48" t="inlineStr">
+      <c r="D58" s="48" t="inlineStr">
         <is>
           <t>Julien Offray de la METTRIE</t>
         </is>
       </c>
-      <c r="E57" s="63" t="inlineStr">
+      <c r="E58" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Julien_Offray_de_La_Mettrie"    title=" Wikipedia"&gt;Julien Onfray de la METTRIE&lt;/a&gt;  était un philosophe et médecin français des Lumières, connu pour son &lt;a href="https://www.youtube.com/watch?v=ATn23C-jw1M"  title=" Traité du bonheur de la Mettrie par Voyage interieur"&gt; matérialisme radical &lt;/a&gt; et son athéisme provocateur. Médecin militaire, il fut exilé de France après la publication de ses idées controversées, avant de trouver refuge auprès de Frédéric II de Prusse à Potsdam. &lt;/p&gt; &lt;p&gt; Dans L’Homme machine (1747), il affirme que l’être humain est une machine purement matérielle : l’âme n’existe pas comme substance distincte, mais émerge des processus physiques du cerveau et du corps, sans besoin de Dieu ou d’esprit immatériel. Il s’inspire de Descartes, mais pousse le mécanisme jusqu’au bout en rejetant le dualisme corps-âme.  &lt;/p&gt; &lt;p&gt; Ses écrits, comme Histoire naturelle de l’âme (1745), scandalisèrent l’Église et les autorités : ses livres furent brûlés publiquement et il perdit son poste aux Gardes-Françaises. Défenseur d’un hédonisme sensualiste, il prône le  &lt;a href="https://www.youtube.com/watch?v=FH2TDimoh7Q"  title=" La Mettrie ou l’art de jouir par Parole de philosophe"&gt; plaisir comme seul bien moral,&lt;/a&gt;  sans morale transcendante. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés : Histoire naturelle de l’âme (1745) : Critique du dualisme et fondement matérialiste. L’Homme machine (1747) : Thèse principale sur l’automatisme humain. L’Homme plante (1748) : Étend le mécanisme aux végétaux et animaux. &lt;/p&gt; &lt;p&gt; Précurseur du matérialisme moderne et de la philosophie de la vie, il influence Diderot et les Encyclopédistes, mais reste marginalisé pour son radicalisme. Il anticipe des idées sur l’évolution et la cybernétique en voyant l’humain comme un système organisé. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F57" s="47" t="inlineStr">
+      <c r="F58" s="47" t="inlineStr">
         <is>
           <t>kTzhhULUEtQ</t>
         </is>
       </c>
-      <c r="G57" s="49" t="inlineStr">
+      <c r="G58" s="49" t="inlineStr">
         <is>
           <t>"Julien Offray de La Mettrie : Défier l'âme" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H57" s="49" t="inlineStr">
+      <c r="H58" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jmettrie-mini.webp</t>
         </is>
       </c>
-      <c r="I57" s="45" t="n"/>
-      <c r="J57" s="38" t="inlineStr">
+      <c r="I58" s="45" t="n"/>
+      <c r="J58" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K57" s="45" t="inlineStr">
+      <c r="K58" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L57" s="46" t="inlineStr">
+      <c r="L58" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Matérialisme ; Épiphénoménisme ; Athéisme</t>
         </is>
       </c>
-      <c r="M57" s="35" t="inlineStr">
+      <c r="M58" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour son matérialisme radical et son athéisme.</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="120" customHeight="1" s="39">
-      <c r="A58" s="47" t="n">
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="120" customHeight="1" s="39">
+      <c r="A59" s="47" t="n">
         <v>1710</v>
       </c>
-      <c r="B58" s="47" t="inlineStr">
+      <c r="B59" s="47" t="inlineStr">
         <is>
           <t>1796</t>
         </is>
       </c>
-      <c r="C58" s="47" t="inlineStr">
+      <c r="C59" s="47" t="inlineStr">
         <is>
           <t>1710 – 1796</t>
         </is>
       </c>
-      <c r="D58" s="48" t="inlineStr">
+      <c r="D59" s="48" t="inlineStr">
         <is>
           <t>Thomas REID</t>
         </is>
       </c>
-      <c r="E58" s="62" t="inlineStr">
+      <c r="E59" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Reid"   title=" Wikipedia"&gt;Thomas REID&lt;/a&gt; était un philosophe écossais des Lumières écossaises, fondateur de l'école du sens commun. Contemporain et critique principal de David Hume, il enseigna à Aberdeen puis à Glasgow, où il succéda à Adam Smith. Il  défend le réalisme direct : nous percevons immédiatement les objets extérieurs eux-mêmes, sans passer par  &lt;a href="https://fr.wikisource.org/wiki/Grand_dictionnaire_universel_du_XIXe_si%C3%A8cle/Reid_(thomas)_(philosophe)"  title=" Reid philosophe par Wikisource"&gt; des "idées"  &lt;/a&gt; intermédiaires comme chez Locke ou Descartes. Le sens commun fournit des principes innés et indubitables (existence du monde, causalité, témoignage), que la philosophie doit respecter plutôt que miner. &lt;/p&gt; &lt;p&gt; Face au scepticisme humain, il argue que nier ces principes du sens commun mène à l'absurde : si nous doutons de tout, la philosophie devient inutilisable. Il réfute la "théorie des idées représentatives" qui, selon lui, engendre le doute hyperbolique. &lt;/p&gt; &lt;p&gt; Il expose sa pensée dans les &lt;em&gt;Recherches sur l'entendement humain d'après les principes du sens commun&lt;/em&gt; (1764), puis dans les &lt;em&gt;Essais sur les facultés intellectuelles&lt;/em&gt; (1785) et &lt;em&gt;sur les facultés actives&lt;/em&gt; de l'homme (1788), où il défend la liberté humaine contre le déterminisme. &lt;/p&gt; &lt;p&gt; Comme Hutcheson, il valorise une  &lt;a href="https://www.youtube.com/watch?v=Nq9g-OYRLLQ"  title=" Reid’s commun sense design philosophy par Discovery Science"&gt; faculté innée &lt;/a&gt;  (sens moral chez l'un, sens commun chez l'autre), mais appliquée à la connaissance plutôt qu'à la morale pure. Tous deux s'opposent au scepticisme et à l'égoïsme hobbesien. Sa philosophie du sens commun a dominé l’enseignement en Écosse et aux États-Unis, et en France, Royer-Collard et Victor Cousin s’en sont inspirés. Elle a été redécouverte au XXe siècle par G. E. Moore et par les épistémologues contemporains. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F58" s="47" t="inlineStr">
+      <c r="F59" s="47" t="inlineStr">
         <is>
           <t>D4l_YhfDN30</t>
         </is>
       </c>
-      <c r="G58" s="49" t="inlineStr">
+      <c r="G59" s="49" t="inlineStr">
         <is>
           <t>"Thomas Reid: Unraveling the Philosophical Mysteries" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H58" s="49" t="inlineStr">
+      <c r="H59" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/reid-mini.webp</t>
         </is>
       </c>
-      <c r="I58" s="45" t="n"/>
-      <c r="J58" s="55" t="inlineStr">
+      <c r="I59" s="45" t="n"/>
+      <c r="J59" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K58" s="45" t="inlineStr">
+      <c r="K59" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L58" s="46" t="inlineStr">
+      <c r="L59" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Empirisme ; Particularisme</t>
         </is>
       </c>
-      <c r="M58" s="35" t="inlineStr">
+      <c r="M59" s="35" t="inlineStr">
         <is>
           <t>philosophe des Lumières écossaises, fondateur de l'école du sens commun.</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="115.5" customHeight="1" s="39">
-      <c r="A59" s="47" t="n">
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="115.5" customHeight="1" s="39">
+      <c r="A60" s="47" t="n">
         <v>1711</v>
       </c>
-      <c r="B59" s="47" t="inlineStr">
+      <c r="B60" s="47" t="inlineStr">
         <is>
           <t>1776</t>
         </is>
       </c>
-      <c r="C59" s="47" t="inlineStr">
+      <c r="C60" s="47" t="inlineStr">
         <is>
           <t>1711 - 1776</t>
         </is>
       </c>
-      <c r="D59" s="48" t="inlineStr">
+      <c r="D60" s="48" t="inlineStr">
         <is>
           <t>David HUME</t>
         </is>
       </c>
-      <c r="E59" s="58" t="inlineStr">
+      <c r="E60" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/David_Hume"  title=" Wikipedia"&gt;David HUME&lt;/a&gt; était un philosophe, historien et économiste écossais de l'ère des Lumières. Il est surtout connu pour ses contributions à la philosophie empirique, la théorie de la connaissance, la métaphysique, l'éthique et l'esthétique. &lt;/p&gt; &lt;p&gt; Hume était un sceptique et a cherché à examiner de manière critique les idées préconçues et les &lt;a  href="https://www.youtube.com/watch?v=CLIoxw6TXuk&amp;ab_channel=LePr%C3%A9cepteur"  title="Tout n'est que croyance  par Le Précepteur"&gt;croyances reçues&lt;/a&gt;. Il a rejeté les arguments métaphysiques qui ne pouvaient pas être fondés sur l'expérience directe, et a affirmé que les connaissances humaines étaient basées sur les impressions et les idées que nous en avons. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de &lt;a  href="https://www.youtube.com/watch?v=ftd3vjw9lSU"  title=" la causalité par Skarblown Animations"&gt;la causalité&lt;/a&gt;, qui affirme que nous ne pouvons pas connaître la relation de cause à effet entre deux événements par simple observation, mais que nous sommes amenés à croire en une telle relation en raison de notre expérience passée.  &lt;/p&gt; &lt;p&gt; En éthique, il a affirmé que la morale était basée sur des sentiments plutôt que sur la raison et qu'elle ne peut pas être déduite de principes rationnels, mais doit être fondée sur l'empathie et la sympathie envers les autres.  &lt;/p&gt; &lt;p&gt; Il a également souligné l'importance du bonheur et du plaisir dans la vie, affirmant que ce sont des aspects essentiels de notre existence et de notre &lt;a  href="https://www.youtube.com/watch?v=52077nWSkPM&amp;t=11s&amp;ab_channel=LePr%C3%A9cepteur"   title="l'identité par le Précepteur"&gt;identité&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il a écrit sur la religion et a critiqué les arguments traditionnels pour l'existence de Dieu en affirmant que la religion était basée sur la superstition plutôt que sur la raison, et que la croyance en Dieu était fondée sur l'habitude plutôt que sur la preuve. &lt;/p&gt;  &lt;audio controls title="Pourquoi faut il lire David Hume par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22838-02.02.2022-ITEMA_22927004-2022C45539E0018-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F59" s="47" t="inlineStr">
+      <c r="F60" s="47" t="inlineStr">
         <is>
           <t>67YDDiB1Gms</t>
         </is>
       </c>
-      <c r="G59" s="49" t="inlineStr">
+      <c r="G60" s="49" t="inlineStr">
         <is>
           <t>David Hume par Bibiclo</t>
         </is>
       </c>
-      <c r="H59" s="49" t="inlineStr">
+      <c r="H60" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/hume-mini.webp</t>
         </is>
       </c>
-      <c r="I59" s="45" t="n"/>
-      <c r="J59" s="55" t="inlineStr">
+      <c r="I60" s="45" t="n"/>
+      <c r="J60" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K59" s="45" t="inlineStr">
+      <c r="K60" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; ethique</t>
         </is>
       </c>
-      <c r="L59" s="46" t="inlineStr">
+      <c r="L60" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Empirisme ; Scepticisme ; Agnosticisme ; Lumières ; Méthodisme ; Phénoménisme</t>
         </is>
       </c>
-      <c r="M59" s="35" t="inlineStr">
+      <c r="M60" s="35" t="inlineStr">
         <is>
           <t>philosophe écossais Sceptique et fondateur de l'Empirisme moderne.</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P59">
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P60">
         <v>3</v>
       </c>
     </row>
-    <row r="60" ht="126.75" customHeight="1" s="39">
-      <c r="A60" s="47" t="n">
+    <row r="61" ht="126.75" customHeight="1" s="39">
+      <c r="A61" s="47" t="n">
         <v>1712</v>
       </c>
-      <c r="B60" s="47" t="inlineStr">
+      <c r="B61" s="47" t="inlineStr">
         <is>
           <t>1778</t>
         </is>
       </c>
-      <c r="C60" s="47" t="inlineStr">
+      <c r="C61" s="47" t="inlineStr">
         <is>
           <t>1712 - 1778</t>
         </is>
       </c>
-      <c r="D60" s="48" t="inlineStr">
+      <c r="D61" s="48" t="inlineStr">
         <is>
           <t>Jean Jacques ROUSSEAU</t>
         </is>
       </c>
-      <c r="E60" s="58" t="inlineStr">
+      <c r="E61" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau" title=" Wikipedia"&gt; Jean-Jacques ROUSSEAU&lt;/a&gt; était un philosophe &lt;a href="https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;ab_channel=LePr%C3%A9cepteur"  title="Les Lumières par le Précepteur "&gt; des lumières&lt;/a&gt; et écrivain suisse-français, défenseur de la liberté et de l'égalité. Il et est surtout connu pour son livre &lt;a href="https://www.youtube.com/watch?v=tToAS8pUXzU"   title="Le texte fondateur par Alain Bajomée "&gt;"Du contrat social"&lt;/a&gt;, dans lequel il développe sa théorie politique ainsi que &lt;a href="https://www.youtube.com/watch?v=3-mPXD5CkJc"  title="L'Emile par Librairie Vrin"&gt;"Emile" &lt;/a&gt;considéré comme un "traité d'écucation" ou sa théorie de l'homme. &lt;/p&gt; &lt;p&gt;
 Rousseau a également écrit sur la philosophie morale, la théorie de l'éducation et la nature humaine et  &lt;a href="https://www.youtube.com/watch?v=cUtO8U9QbZs&amp;ab_channel=LePr%C3%A9cepteur"  style="color:#88A1E9"  title="Le désir par le Précepteur "&gt; le désir&lt;/a&gt;. Il croyait que &lt;a href="https://www.youtube.com/watch?v=FpXdTgerxiI&amp;ab_channel=LePr%C3%A9cepteur"   title="L''homme est naturellement bon par le Précepteur "&gt; l'homme est naturellement bon&lt;/a&gt;, mais corrompu par la société et la civilisation. Il a également affirmé que la liberté individuelle est essentielle à l'épanouissement humain et que les institutions politiques doivent être créées pour protéger les droits et les libertés des individus. &lt;/p&gt; &lt;p&gt;  Il est souvent considéré comme un précurseur du  &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1927_num_29_16_2482#"  title="La philosophie romantique par Persée "&gt; romantisme&lt;/a&gt; en raison de son accent mis sur les émotions, la nature, l'individualité et la subjectivité. Il a exprimé une méfiance envers la société civilisée et a prôné un retour à la nature et à la simplicité. Il a également souligné l'importance de l'émotion et de l'expérience personnelle dans la compréhension du monde, remettant en question l'approche rationnelle et scientifique des Lumières. Ses idées ont eu une influence significative sur les écrivains et les artistes romantiques ultérieurs, qui ont valorisé l'expression émotionnelle et l'expérience individuelle dans leurs œuvres.&lt;/p&gt; &lt;p&gt;
@@ -4632,71 +4698,71 @@
 </t>
         </is>
       </c>
-      <c r="F60" s="47" t="inlineStr">
+      <c r="F61" s="47" t="inlineStr">
         <is>
           <t>NA0upIwMLSk</t>
         </is>
       </c>
-      <c r="G60" s="49" t="inlineStr">
+      <c r="G61" s="49" t="inlineStr">
         <is>
           <t>"Jean Jacques ROUSSEAU" par Culture Tube</t>
         </is>
       </c>
-      <c r="H60" s="49" t="inlineStr">
+      <c r="H61" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/rousseau-mini.webp</t>
         </is>
       </c>
-      <c r="I60" s="45" t="n"/>
-      <c r="J60" s="38" t="inlineStr">
+      <c r="I61" s="45" t="n"/>
+      <c r="J61" s="38" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
       </c>
-      <c r="K60" s="45" t="inlineStr">
+      <c r="K61" s="45" t="inlineStr">
         <is>
           <t>politique ; ethique</t>
         </is>
       </c>
-      <c r="L60" s="46" t="inlineStr">
+      <c r="L61" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Contractualisme ; Lumières</t>
         </is>
       </c>
-      <c r="M60" s="35" t="inlineStr">
+      <c r="M61" s="35" t="inlineStr">
         <is>
           <t>philosophe et écrivain franco-suisse de l'époque des lumières.</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P60">
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P61">
         <v>3</v>
       </c>
     </row>
-    <row r="61" ht="148.5" customHeight="1" s="39">
-      <c r="A61" s="47" t="n">
+    <row r="62" ht="148.5" customHeight="1" s="39">
+      <c r="A62" s="47" t="n">
         <v>1713</v>
       </c>
-      <c r="B61" s="47" t="inlineStr">
+      <c r="B62" s="47" t="inlineStr">
         <is>
           <t>1784</t>
         </is>
       </c>
-      <c r="C61" s="47" t="inlineStr">
+      <c r="C62" s="47" t="inlineStr">
         <is>
           <t>1713 - 1784</t>
         </is>
       </c>
-      <c r="D61" s="48" t="inlineStr">
+      <c r="D62" s="48" t="inlineStr">
         <is>
           <t>Denis DIDEROT</t>
         </is>
       </c>
-      <c r="E61" s="58" t="inlineStr">
+      <c r="E62" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Denis_Diderot"  title=" Wikipedia"&gt; Denis DIDEROT&lt;/a&gt; était un philosophe des Lumières français ainsi qu' un écrivain, éditeur et encyclopédiste influent.  Il est surtout connu pour son rôle de coéditeur et contributeur majeur de &lt;a href="https://www.youtube.com/watch?v=LuRI5zg7tJY"   title="Diderot 1750 Encyclopedia par OER Project "&gt;l'Encyclopédie, &lt;/a&gt; ou Dictionnaire raisonné des sciences, des arts et des métiers.&lt;/p&gt; &lt;p&gt;
 Il était un fervent défenseur de la raison et de l'esprit critique et il rejetait les dogmes et les traditions aveugles, encourageant à la place l'examen rationnel et la remise en question des croyances établies. Il croyait en la capacité de l'homme à comprendre le monde à travers la science, la philosophie et l'observation directe. &lt;/p&gt; &lt;p&gt;
@@ -4705,107 +4771,40 @@
    &lt;audio controls title="Le Neveu de Rameau par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/10/s40/RF_38A1D24B-FA10-43F4-8B19-8C4921845BD4_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F61" s="47" t="inlineStr">
+      <c r="F62" s="47" t="inlineStr">
         <is>
           <t>MwdE6ig1mVw</t>
         </is>
       </c>
-      <c r="G61" s="49" t="inlineStr">
+      <c r="G62" s="49" t="inlineStr">
         <is>
           <t>"Philosopher-Diderot " par Guillaume Deloison</t>
         </is>
       </c>
-      <c r="H61" s="49" t="inlineStr">
+      <c r="H62" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/diderot-mini.webp</t>
-        </is>
-      </c>
-      <c r="I61" s="45" t="n"/>
-      <c r="J61" s="38" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K61" s="45" t="inlineStr">
-        <is>
-          <t>epistemologie ; politique</t>
-        </is>
-      </c>
-      <c r="L61" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matérialisme ; Lumières ; Athéisme</t>
-        </is>
-      </c>
-      <c r="M61" s="35" t="inlineStr">
-        <is>
-          <t>philosophe et écrivain français des lumières qui rejetait les dogmes.</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="166.5" customHeight="1" s="39">
-      <c r="A62" s="47" t="n">
-        <v>1714</v>
-      </c>
-      <c r="B62" s="47" t="inlineStr">
-        <is>
-          <t>1762</t>
-        </is>
-      </c>
-      <c r="C62" s="47" t="inlineStr">
-        <is>
-          <t>1714 – 1762</t>
-        </is>
-      </c>
-      <c r="D62" s="48" t="inlineStr">
-        <is>
-          <t>Alexander  Gottlieb BAUMGARTEN</t>
-        </is>
-      </c>
-      <c r="E62" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Gottlieb_Baumgarten"  title=" Wikipedia"&gt;Alexander Gottlieb BAUMGARTEN&lt;/a&gt;  était un philosophe allemand considéré comme le père de l'esthétique en tant que discipline philosophique autonome. Il  a étudié à Halle sous l'influence de Christian Wolff et de la tradition leibnizienne. Professeur à Halle puis à Francfort, il a développé une pensée rationaliste tout en valorisant la connaissance sensible.  &lt;/p&gt; &lt;p&gt; Dans son œuvre majeure Aesthetica (1750-1758), il introduit le terme &lt;a href="https://www.youtube.com/watch?v=izQeXqAcTVo"  title="Qu’est ce que l’esthétique aujourd’hui par Esthete Esthete"&gt;« esthétique » &lt;/a&gt; (du grec aisthēsis, sensation) pour désigner la « science de la connaissance sensible ». Contrairement à la logique qui traite de la connaissance rationnelle, l'esthétique étudie la perfection sensible, c'est-à-dire le beau perçu par les sens comme une forme complète de savoir. &lt;/p&gt; &lt;p&gt; Il  défend l'autonomie des « facultés inférieures » (sens, imagination, mémoire) face à la suprématie de la raison, voyant dans le beau une perfection analogue à la vérité (rationnelle) et au bien (moral). Son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1992_num_90_87_6745"  title="De Baumgarten à Kant par Persée"&gt;travail a influencé Kant &lt;/a&gt; et l'idéalisme allemand en légitimant l'étude philosophique de l'art et de l'expérience esthétique. Né à Berlin en 1714, il emploie le mot pour la première fois dès 1735, dans sa thèse sur la poésie. Pour lui, la connaissance sensible est un « analogue de la raison » : elle saisit les choses de manière confuse mais riche, comme le fait le poète, là où la raison les saisit de manière claire mais abstraite. Sa &lt;em&gt;Métaphysique&lt;/em&gt; (1739), manuel de la philosophie de Wolff, a servi de support aux cours de Kant pendant plusieurs décennies. Il insiste sur le rôle créatif de l'artiste, qui doit embellir la nature par l'ajout d'éléments sensibles. &lt;/p&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F62" s="47" t="inlineStr">
-        <is>
-          <t>7If2WywcyME</t>
-        </is>
-      </c>
-      <c r="G62" s="49" t="inlineStr">
-        <is>
-          <t>"Alexander Gottlieb Baumgarten : Redéfinir l'esthétique " par VIS PHILO</t>
-        </is>
-      </c>
-      <c r="H62" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/abaumgarten-mini.webp</t>
         </is>
       </c>
       <c r="I62" s="45" t="n"/>
       <c r="J62" s="38" t="inlineStr">
         <is>
-          <t>Allemande</t>
+          <t>Française</t>
         </is>
       </c>
       <c r="K62" s="45" t="inlineStr">
         <is>
-          <t>esthetique ; epistemologie</t>
+          <t>epistemologie ; politique</t>
         </is>
       </c>
       <c r="L62" s="46" t="inlineStr">
         <is>
-          <t>Rationalisme</t>
+          <t xml:space="preserve">Matérialisme ; Lumières ; Athéisme</t>
         </is>
       </c>
       <c r="M62" s="35" t="inlineStr">
         <is>
-          <t>philosophe allemand considéré comme le père de l'esthétique.</t>
+          <t>philosophe et écrivain français des lumières qui rejetait les dogmes.</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4818,841 +4817,842 @@
       <c r="A63" s="47" t="n">
         <v>1714</v>
       </c>
-      <c r="B63" s="47" t="n">
+      <c r="B63" s="47" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="C63" s="47" t="inlineStr">
+        <is>
+          <t>1714 – 1762</t>
+        </is>
+      </c>
+      <c r="D63" s="48" t="inlineStr">
+        <is>
+          <t>Alexander  Gottlieb BAUMGARTEN</t>
+        </is>
+      </c>
+      <c r="E63" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexander_Gottlieb_Baumgarten"  title=" Wikipedia"&gt;Alexander Gottlieb BAUMGARTEN&lt;/a&gt;  était un philosophe allemand considéré comme le père de l'esthétique en tant que discipline philosophique autonome. Il  a étudié à Halle sous l'influence de Christian Wolff et de la tradition leibnizienne. Professeur à Halle puis à Francfort, il a développé une pensée rationaliste tout en valorisant la connaissance sensible.  &lt;/p&gt; &lt;p&gt; Dans son œuvre majeure Aesthetica (1750-1758), il introduit le terme &lt;a href="https://www.youtube.com/watch?v=izQeXqAcTVo"  title="Qu’est ce que l’esthétique aujourd’hui par Esthete Esthete"&gt;« esthétique » &lt;/a&gt; (du grec aisthēsis, sensation) pour désigner la « science de la connaissance sensible ». Contrairement à la logique qui traite de la connaissance rationnelle, l'esthétique étudie la perfection sensible, c'est-à-dire le beau perçu par les sens comme une forme complète de savoir. &lt;/p&gt; &lt;p&gt; Il  défend l'autonomie des « facultés inférieures » (sens, imagination, mémoire) face à la suprématie de la raison, voyant dans le beau une perfection analogue à la vérité (rationnelle) et au bien (moral). Son &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1992_num_90_87_6745"  title="De Baumgarten à Kant par Persée"&gt;travail a influencé Kant &lt;/a&gt; et l'idéalisme allemand en légitimant l'étude philosophique de l'art et de l'expérience esthétique. Né à Berlin en 1714, il emploie le mot pour la première fois dès 1735, dans sa thèse sur la poésie. Pour lui, la connaissance sensible est un « analogue de la raison » : elle saisit les choses de manière confuse mais riche, comme le fait le poète, là où la raison les saisit de manière claire mais abstraite. Sa &lt;em&gt;Métaphysique&lt;/em&gt; (1739), manuel de la philosophie de Wolff, a servi de support aux cours de Kant pendant plusieurs décennies. Il insiste sur le rôle créatif de l'artiste, qui doit embellir la nature par l'ajout d'éléments sensibles. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F63" s="47" t="inlineStr">
+        <is>
+          <t>7If2WywcyME</t>
+        </is>
+      </c>
+      <c r="G63" s="49" t="inlineStr">
+        <is>
+          <t>"Alexander Gottlieb Baumgarten : Redéfinir l'esthétique " par VIS PHILO</t>
+        </is>
+      </c>
+      <c r="H63" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/abaumgarten-mini.webp</t>
+        </is>
+      </c>
+      <c r="I63" s="45" t="n"/>
+      <c r="J63" s="38" t="inlineStr">
+        <is>
+          <t>Allemande</t>
+        </is>
+      </c>
+      <c r="K63" s="45" t="inlineStr">
+        <is>
+          <t>esthetique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L63" s="46" t="inlineStr">
+        <is>
+          <t>Rationalisme</t>
+        </is>
+      </c>
+      <c r="M63" s="35" t="inlineStr">
+        <is>
+          <t>philosophe allemand considéré comme le père de l'esthétique.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="166.5" customHeight="1" s="39">
+      <c r="A64" s="47" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B64" s="47" t="n">
         <v>1804</v>
       </c>
-      <c r="C63" s="47" t="inlineStr">
+      <c r="C64" s="47" t="inlineStr">
         <is>
           <t>1714 – 1804</t>
         </is>
       </c>
-      <c r="D63" s="48" t="inlineStr">
+      <c r="D64" s="48" t="inlineStr">
         <is>
           <t>Johann Joachim SPALDING</t>
         </is>
       </c>
-      <c r="E63" s="63" t="inlineStr">
+      <c r="E64" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Joachim_Spalding" title=" Wikipedia"&gt;Johann Joachim SPALDING&lt;/a&gt; était un théologien protestant allemand, souvent considéré comme l’un des grands représentants des Lumières religieuses en Allemagne. Sa pensée cherche à concilier foi chrétienne, raison et morale, dans un esprit de réforme modérée plutôt que de rupture. Né en Poméranie suédoise, fils de pasteur, il traduit Shaftesbury, puis devient en 1764 prévôt de l’église Saint-Nicolas de Berlin. &lt;/p&gt; &lt;p&gt; Dans son œuvre la plus célèbre, &lt;em&gt;Die Bestimmung des Menschen&lt;/em&gt; (« La Destination de l’homme », 1748), il réfléchit au sens de la vie humaine. Pour lui, l’être humain n’est pas fait seulement pour satisfaire ses besoins matériels, mais pour se développer intérieurement, moralement et spirituellement. &lt;/p&gt; &lt;p&gt; Sa philosophie religieuse défend l’idée d’une religion naturelle compatible avec la Révélation. Il refuse le dogmatisme rigide et l’orthodoxie autoritaire, et insiste sur une foi plus vivante, fondée sur la conscience, le bon sens et l’expérience intérieure. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande importance &lt;a href="https://www.persee.fr/doc/ephe_0000-0002_1979_num_92_88_18346"  title="problèmes de la théologie allemande par persée"&gt;au sentiment religieux. &lt;/a&gt;  Dans ses &lt;em&gt;Pensées sur la valeur des sentiments dans le christianisme&lt;/em&gt; (1761), il montre que les émotions et la vie intérieure ont une vraie place dans le christianisme, sans que cela supprime l’exigence morale. Il représente une forme de christianisme éclairé : une religion raisonnable, morale et personnelle, qui veut rendre la foi plus humaine et plus intelligible. Son influence a compté dans la théologie protestante allemande, notamment dans le courant appelé néologie. En 1788, il renonce à prêcher après l’édit de Wöllner, qui impose aux pasteurs l’orthodoxie luthérienne. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F63" s="47" t="n"/>
-      <c r="G63" s="49" t="n"/>
-      <c r="H63" s="58" t="inlineStr">
+      <c r="F64" s="47" t="n"/>
+      <c r="G64" s="49" t="n"/>
+      <c r="H64" s="58" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jjspalding-mini.webp</t>
         </is>
       </c>
-      <c r="I63" s="45" t="inlineStr">
+      <c r="I64" s="45" t="inlineStr">
         <is>
           <t>https://laphilo.fr/photo/jjspalding.webp</t>
         </is>
       </c>
-      <c r="J63" s="38" t="inlineStr">
+      <c r="J64" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K63" s="45" t="inlineStr">
+      <c r="K64" s="45" t="inlineStr">
         <is>
           <t>spiritualite</t>
         </is>
       </c>
-      <c r="L63" s="46" t="inlineStr">
+      <c r="L64" s="46" t="inlineStr">
         <is>
           <t>Rationalisme</t>
         </is>
       </c>
-      <c r="M63" s="35" t="inlineStr">
+      <c r="M64" s="35" t="inlineStr">
         <is>
           <t>philosophe et théologien protestant allemand, représentant des Lumières religieuses.</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="153.75" customHeight="1" s="39">
-      <c r="A64" s="47" t="n">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="153.75" customHeight="1" s="39">
+      <c r="A65" s="47" t="n">
         <v>1715</v>
       </c>
-      <c r="B64" s="47" t="inlineStr">
+      <c r="B65" s="47" t="inlineStr">
         <is>
           <t>1771</t>
         </is>
       </c>
-      <c r="C64" s="47" t="inlineStr">
+      <c r="C65" s="47" t="inlineStr">
         <is>
           <t>1715 – 1771</t>
         </is>
       </c>
-      <c r="D64" s="48" t="inlineStr">
+      <c r="D65" s="48" t="inlineStr">
         <is>
           <t>Claude-Adrien HELVÉTIUS</t>
         </is>
       </c>
-      <c r="E64" s="62" t="inlineStr">
+      <c r="E65" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claude-Adrien_Helv%C3%A9tius" title=" Wikipedia"&gt;Claude-Adrien HELVÉTIUS&lt;/a&gt; était un philosophe français des Lumières, connu pour son matérialisme radical et son utilitarisme, qui a marqué le XVIIIe siècle par ses idées provocatrices sur l'esprit humain et la société. Il  fut fermier général, poète et mécène des philosophes, collaborant à l'Encyclopédie de Diderot. Son ouvrage  &lt;a href="https://fr.wikipedia.org/wiki/De_l%27esprit"  title="De l’esprit par Wikipedia"&gt;De l'esprit (1758)&lt;/a&gt;, publié anonymement, provoqua un scandale immense, fut condamné au feu par l'Église et le Parlement, mais diffusé en Hollande. &lt;/p&gt; &lt;p&gt; Influencé par Locke, il défend un sensualisme selon lequel toutes nos idées et connaissances proviennent des sensations physiques, sans innéisme ni libre arbitre clair. L'âme n'est que la faculté de sentir, et l'esprit en découle via la mémoire qui compare les impressions sensorielles.  &lt;/p&gt; &lt;p&gt; Pour lui, l'égoïsme personnel, motivé par le plaisir et la douleur, est la base de toute action vertueuse et sociale, transformé par l'éducation et les institutions en bonheur collectif. Il prône une société réformée par la raison, où lois et mœurs maximisent l'utilité commune sous une autorité éclairée. Il soutient aussi que les hommes naissent avec des capacités à peu près égales : les différences d’esprit viennent de l’éducation et des circonstances, d’où l’importance qu’il accorde à l’instruction publique. Il développe ces thèses dans &lt;em&gt;De l’homme&lt;/em&gt;, publié après sa mort. Sa pensée, qui fait de « l’utilité publique » le principe de la morale et des lois, inspire Bentham et l’utilitarisme anglais. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F64" s="47" t="inlineStr">
+      <c r="F65" s="47" t="inlineStr">
         <is>
           <t>DyvOZMOphM4</t>
         </is>
       </c>
-      <c r="G64" s="49" t="inlineStr">
+      <c r="G65" s="49" t="inlineStr">
         <is>
           <t>"Préface "De l'Homme" - C.A. Helvetius" par Paul Eymeric</t>
         </is>
       </c>
-      <c r="H64" s="49" t="inlineStr">
+      <c r="H65" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/helvetius-mini.webp</t>
         </is>
       </c>
-      <c r="I64" s="45" t="n"/>
-      <c r="J64" s="38" t="inlineStr">
+      <c r="I65" s="45" t="n"/>
+      <c r="J65" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K64" s="45" t="inlineStr">
+      <c r="K65" s="45" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="L64" s="46" t="inlineStr">
+      <c r="L65" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Matérialisme ; Utilitarisme ; Lumières</t>
         </is>
       </c>
-      <c r="M64" s="35" t="inlineStr">
+      <c r="M65" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour son matérialisme radical et son utilitarisme.</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="88.5" customHeight="1" s="39">
-      <c r="A65" s="47" t="n">
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="88.5" customHeight="1" s="39">
+      <c r="A66" s="47" t="n">
         <v>1720</v>
       </c>
-      <c r="B65" s="47" t="inlineStr">
+      <c r="B66" s="47" t="inlineStr">
         <is>
           <t>1793</t>
         </is>
       </c>
-      <c r="C65" s="47" t="inlineStr">
+      <c r="C66" s="47" t="inlineStr">
         <is>
           <t>1720 – 1793</t>
         </is>
       </c>
-      <c r="D65" s="48" t="inlineStr">
+      <c r="D66" s="48" t="inlineStr">
         <is>
           <t>Charles BONNET</t>
         </is>
       </c>
-      <c r="E65" s="63" t="inlineStr">
+      <c r="E66" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Charles_Bonnet_(naturaliste)"  title=" Wikipedia"&gt;Charles BONNET&lt;/a&gt;  était un philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie et sa découverte de la parthénogenèse. Il  étudie la botanique et l'entomologie dès sa jeunesse, influencé par Newton, Leibniz et Malebranche. Malgré des problèmes de vue et d'ouïe précoces, il devient membre du Conseil des Deux-Cents et correspondant de l'Académie des sciences de Paris. &lt;/p&gt; &lt;p&gt; Il démontre en 1745 la reproduction par parthénogenèse chez les pucerons, obtenant onze générations sans fécondation, et étudie la régénération des vers, des limaçons et des pattes d'écrevisse. Ses Recherches sur l'usage des feuilles (1754) préfigurent la photosynthèse, et il défend la théorie de la préformation, où les germes préexistent depuis la Création. &lt;/p&gt; &lt;p&gt; Dans Essai de psychologie (1754) et Essai analytique sur les facultés de l'âme (1760), il développe un sensualisme spiritualiste, voyant les idées naître des sensations via les fibres cérébrales. Sa &lt;a href="https://fr.wikipedia.org/wiki/Paling%C3%A9n%C3%A9sie"  title="palingénésie par Wikipedia"&gt;&lt;em&gt;Palingénésie philosophique&lt;/em&gt;&lt;/a&gt; (1769) postule l'immortalité des âmes humaines et animales dans une échelle continue des êtres. Pour lui, la nature forme une chaîne sans rupture, du minéral à l’homme, que décrit sa &lt;em&gt;Contemplation de la nature&lt;/em&gt; (1764), et chaque être y progressera après la mort. Devenu presque aveugle, il décrit les visions qu’éprouvait son grand-père, qui voyait des personnages et des objets imaginaires tout en sachant qu’ils n’existaient pas : ces hallucinations des personnes malvoyantes portent aujourd’hui le nom de « syndrome de Charles Bonnet ». &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F65" s="47" t="inlineStr">
+      <c r="F66" s="47" t="inlineStr">
         <is>
           <t>UWf2B79U0O0</t>
         </is>
       </c>
-      <c r="G65" s="49" t="inlineStr">
+      <c r="G66" s="49" t="inlineStr">
         <is>
           <t>"Charles Bonnet: Exploring Nature's Patterns" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H65" s="49" t="inlineStr">
+      <c r="H66" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cbonnet-mini.webp</t>
         </is>
       </c>
-      <c r="I65" s="45" t="n"/>
-      <c r="J65" s="38" t="inlineStr">
+      <c r="I66" s="45" t="n"/>
+      <c r="J66" s="38" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
       </c>
-      <c r="K65" s="45" t="inlineStr">
+      <c r="K66" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L65" s="46" t="inlineStr">
+      <c r="L66" s="46" t="inlineStr">
         <is>
           <t>Empirisme</t>
         </is>
       </c>
-      <c r="M65" s="35" t="inlineStr">
+      <c r="M66" s="35" t="inlineStr">
         <is>
           <t>philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie.</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="126" customHeight="1" s="39">
-      <c r="A66" s="47" t="n">
-        <v>1723</v>
-      </c>
-      <c r="B66" s="47" t="inlineStr">
-        <is>
-          <t>1790</t>
-        </is>
-      </c>
-      <c r="C66" s="47" t="inlineStr">
-        <is>
-          <t>1723 - 1790</t>
-        </is>
-      </c>
-      <c r="D66" s="48" t="inlineStr">
-        <is>
-          <t>Adam SMITH</t>
-        </is>
-      </c>
-      <c r="E66" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. Né à Kirkcaldy, professeur de philosophie morale à l’université de Glasgow et ami de David Hume, il publie ce livre en 1776. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie, il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. C’est l’objet de sa &lt;em&gt;Théorie des sentiments moraux&lt;/em&gt; (1759) : nous jugeons nos propres actes en imaginant le regard d’un « spectateur impartial ». &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F66" s="47" t="inlineStr">
-        <is>
-          <t>6onxSBxmBXs</t>
-        </is>
-      </c>
-      <c r="G66" s="49" t="inlineStr">
-        <is>
-          <t>"Adam Smith : le pere de l’éconnomie moderne" par Portrait Historiques</t>
-        </is>
-      </c>
-      <c r="H66" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/smith-mini.webp</t>
-        </is>
-      </c>
-      <c r="I66" s="45" t="n"/>
-      <c r="J66" s="55" t="inlineStr">
-        <is>
-          <t>Britannique</t>
-        </is>
-      </c>
-      <c r="K66" s="45" t="inlineStr">
-        <is>
-          <t>ethique ; politique</t>
-        </is>
-      </c>
-      <c r="L66" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Libéralisme ; Lumières</t>
-        </is>
-      </c>
-      <c r="M66" s="35" t="inlineStr">
-        <is>
-          <t>philosophe écossais Libéraliste qui développa sa théorie de la 'main invisible'.</t>
-        </is>
-      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="101.25" customHeight="1" s="39">
+    <row r="67" ht="126" customHeight="1" s="39">
       <c r="A67" s="47" t="n">
         <v>1723</v>
       </c>
       <c r="B67" s="47" t="inlineStr">
         <is>
+          <t>1790</t>
+        </is>
+      </c>
+      <c r="C67" s="47" t="inlineStr">
+        <is>
+          <t>1723 - 1790</t>
+        </is>
+      </c>
+      <c r="D67" s="48" t="inlineStr">
+        <is>
+          <t>Adam SMITH</t>
+        </is>
+      </c>
+      <c r="E67" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Smith" title=" Wikipedia"&gt;Adam SMITH&lt;/a&gt; était un philosophe et économiste écossais connu pour son livre &lt;a href="https://www.youtube.com/watch?v=a2HYf2VopU0"    title="La richesse des nations Adam Smith  par Gloria Lauzanne"&gt;"La Richesse des Nations"&lt;/a&gt;, où il a développé sa théorie de la &lt;a href="https://www.youtube.com/watch?v=OIvtWvDkkVk&amp;t=30s&amp;ab_channel=LePr%C3%A9cepteur"   title="la main invisible par le Précepteur"&gt;"main invisible"&lt;/a&gt;, selon laquelle les actions individuelles de chacun dans la poursuite de son propre intérêt contribuent à l'intérêt général de la société et a plaidé en faveur de la libre concurrence, qui permettrait de maintenir les prix bas et d'encourager l'innovation. Né à Kirkcaldy, professeur de philosophie morale à l’université de Glasgow et ami de David Hume, il publie ce livre en 1776. &lt;/p&gt; &lt;p&gt;  Il était un penseur de l'ère des Lumières et croyait en la capacité de la raison à résoudre les problèmes sociaux et économiques et que la division du travail par groupe ou compétences permettrait d'augmenter la productivité et de réduire les coûts. Cependant, il ne croyait pas que le marché pouvait fonctionner parfaitement sans intervention gouvernementale d'où la nécessité d'une réglementation pour empêcher les monopoles et d'autres formes de comportement anti-concurrentiel. &lt;/p&gt; &lt;p&gt;  En dehors de l'économie, il a également écrit sur la philosophie morale, en particulier sur la théorie de la sympathie, qui postule que les individus ont une capacité innée à se mettre à la place des autres et à ressentir de l'empathie pour eux. C’est l’objet de sa &lt;em&gt;Théorie des sentiments moraux&lt;/em&gt; (1759) : nous jugeons nos propres actes en imaginant le regard d’un « spectateur impartial ». &lt;/p&gt; &lt;p&gt; On considère néanmoins que c'est lui qui, en faisant de l'initiative privée et égoïste le moteur de l'économie et le ciment de la société, achève d'énoncer &lt;a href="https://www.youtube.com/watch?v=Olur9mRLNjM&amp;ab_channel=LeVortex-ARTE"   title="Le père du libéralisme par le Vortex"&gt; le dogme libéral&lt;/a&gt;.  &lt;/p&gt; &lt;audio controls title="Adam Smith par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/21977-26.01.2021-ITEMA_22560729-2018C29629E0366.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F67" s="47" t="inlineStr">
+        <is>
+          <t>6onxSBxmBXs</t>
+        </is>
+      </c>
+      <c r="G67" s="49" t="inlineStr">
+        <is>
+          <t>"Adam Smith : le pere de l’éconnomie moderne" par Portrait Historiques</t>
+        </is>
+      </c>
+      <c r="H67" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/smith-mini.webp</t>
+        </is>
+      </c>
+      <c r="I67" s="45" t="n"/>
+      <c r="J67" s="55" t="inlineStr">
+        <is>
+          <t>Britannique</t>
+        </is>
+      </c>
+      <c r="K67" s="45" t="inlineStr">
+        <is>
+          <t>ethique ; politique</t>
+        </is>
+      </c>
+      <c r="L67" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libéralisme ; Lumières</t>
+        </is>
+      </c>
+      <c r="M67" s="35" t="inlineStr">
+        <is>
+          <t>philosophe écossais Libéraliste qui développa sa théorie de la 'main invisible'.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="101.25" customHeight="1" s="39">
+      <c r="A68" s="47" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B68" s="47" t="inlineStr">
+        <is>
           <t>1789</t>
         </is>
       </c>
-      <c r="C67" s="47" t="inlineStr">
+      <c r="C68" s="47" t="inlineStr">
         <is>
           <t>1723 – 1789</t>
         </is>
       </c>
-      <c r="D67" s="48" t="inlineStr">
+      <c r="D68" s="48" t="inlineStr">
         <is>
           <t>Paul Thiry d'HOLBACH</t>
         </is>
       </c>
-      <c r="E67" s="58" t="inlineStr">
+      <c r="E68" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Paul_Thiry_d%27Holbach"  title=" Wikipedia"&gt;Paul Thiry d’HOLBACH&lt;/a&gt; (1723-1789) est un philosophe des Lumières, d’origine allemande et naturalisé français, l’un des penseurs les plus radicaux de son siècle. Né dans le Palatinat, élevé à Paris par un oncle dont il hérite la fortune et le titre de baron, il étudie à Leyde, puis s’installe à Paris. Il écrit pour l’&lt;em&gt;Encyclopédie&lt;/em&gt; de Diderot plusieurs centaines d’articles, surtout de chimie et de minéralogie.&lt;/p&gt; &lt;p&gt;Son salon de la rue Royale, que l’abbé Galiani appelait « le maître d’hôtel de la philosophie », réunit deux fois par semaine Diderot, Grimm, Helvétius, Raynal et les étrangers de passage, comme Hume, Adam Smith ou Beccaria. D’Holbach publie sous de faux noms une série d’ouvrages contre la religion, dont &lt;a href="https://www.youtube.com/watch?v=8Uohr5Y9xx0" title="Religions Are ROTTING ILLUSIONS | Baron d’Holbach par Unfiltered Philosophy"&gt;&lt;em&gt;Le Christianisme dévoilé&lt;/em&gt;&lt;/a&gt; (1766), et surtout le &lt;em&gt;Système de la nature&lt;/em&gt; (1770), attribué à un auteur mort, qui fait scandale et est condamné au feu. Il y défend un matérialisme intégral : l’univers n’est que matière en mouvement, régie par des lois nécessaires ; il n’y a ni Dieu, ni âme immortelle, ni liberté au sens d’un libre arbitre. La religion naît de l’ignorance et de la peur, et les prêtres et les rois s’appuient l’un sur l’autre pour asservir les peuples. La morale doit donc être fondée sur la nature humaine, qui recherche le bonheur, et sur l’utilité sociale : l’homme vertueux est celui qui contribue au bonheur des autres. Dans son pamphlet &lt;a href="https://www.youtube.com/watch?v=x99DRdMAd08"  title="Essai sur l'art de ramper à l'usage des courtisans - D'Holbach par Vox Plebeia"&gt;&lt;em&gt;Essai sur l’art de ramper, à l’usage des courtisans&lt;/em&gt;&lt;/a&gt;, il raille la servilité des grands.&lt;/p&gt; &lt;p&gt;Mort en 1789, quelques mois avant la Révolution, il a inspiré les matérialistes du XIXe siècle et la critique moderne de la religion.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F67" s="47" t="inlineStr">
+      <c r="F68" s="47" t="inlineStr">
         <is>
           <t>0t-kRccSANI</t>
         </is>
       </c>
-      <c r="G67" s="49" t="inlineStr">
+      <c r="G68" s="49" t="inlineStr">
         <is>
           <t>"Baron d'Holbach: Enlightening the World" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H67" s="49" t="inlineStr">
+      <c r="H68" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/holbach-mini.webp</t>
         </is>
       </c>
-      <c r="I67" s="45" t="n"/>
-      <c r="J67" s="38" t="inlineStr">
+      <c r="I68" s="45" t="n"/>
+      <c r="J68" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K67" s="45" t="inlineStr">
+      <c r="K68" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; politique</t>
         </is>
       </c>
-      <c r="L67" s="46" t="inlineStr">
+      <c r="L68" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Matérialisme ; Athéisme ; Lumières ; Incompatibilisme</t>
         </is>
       </c>
-      <c r="M67" s="35" t="inlineStr">
+      <c r="M68" s="35" t="inlineStr">
         <is>
           <t>philosophe matérialiste allemand athée des Lumières.</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="166.5" customHeight="1" s="39">
-      <c r="A68" s="47" t="n">
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="166.5" customHeight="1" s="39">
+      <c r="A69" s="47" t="n">
         <v>1724</v>
       </c>
-      <c r="B68" s="47" t="inlineStr">
+      <c r="B69" s="47" t="inlineStr">
         <is>
           <t>1804</t>
         </is>
       </c>
-      <c r="C68" s="47" t="inlineStr">
+      <c r="C69" s="47" t="inlineStr">
         <is>
           <t>1724 - 1804</t>
         </is>
       </c>
-      <c r="D68" s="48" t="inlineStr">
+      <c r="D69" s="48" t="inlineStr">
         <is>
           <t>Emmanuel KANT</t>
         </is>
       </c>
-      <c r="E68" s="58" t="inlineStr">
+      <c r="E69" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Kant"  title=" Wikipedia"&gt;Emmanuel KANT&lt;/a&gt; (1724-1804) est un philosophe allemand des &lt;a href="https://la-philosophie.com/philosophie-lumieres" style="color:#88A1E9"   title="La philosophie des Lumières par la-philosophie.com"&gt;Lumières&lt;/a&gt;, l’un des plus grands de l’histoire. Il passe toute sa vie à Königsberg, en Prusse orientale, où il enseigne à l’université. La lecture de Hume le « réveille de son sommeil dogmatique » et le conduit à examiner les pouvoirs et les limites de la raison.&lt;/p&gt; &lt;p&gt;Dans la &lt;a href="https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos"   title="C'est quoi la raison pure par Kosmos"&gt;&lt;em&gt;Critique de la raison pure&lt;/em&gt;&lt;/a&gt; (1781), il réconcilie le rationalisme et l’empirisme : toute connaissance commence avec l’expérience, mais n’en dérive pas tout entière. L’esprit impose ses propres formes, l’espace, le temps et des catégories comme la causalité, à ce qu’il perçoit : c’est sa « révolution copernicienne ». Nous ne connaissons donc que les phénomènes, non les choses en soi, et la raison ne peut démontrer ni l’existence de Dieu ni l’immortalité de l’âme. Dans les &lt;a href="https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur"  title="L'impératif catégorique par le Précepteur"&gt;&lt;em&gt;Fondements de la métaphysique des mœurs&lt;/em&gt;&lt;/a&gt; (1785), il fonde une &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant"  title="La philosophie pratique de Kant de l'encyclopédie Wikipédia"&gt;philosophie pratique&lt;/a&gt; sur le devoir. &lt;a href="https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos"  title="La loi morale par Kosmos"&gt;La loi morale&lt;/a&gt; ne dépend ni des circonstances ni des conséquences : c’est un impératif catégorique. « Agis uniquement d’après la maxime qui fait que tu peux vouloir en même temps qu’elle devienne une loi universelle », et traite toujours l’humanité, en toi et en autrui, comme une fin, jamais simplement comme un moyen. La &lt;em&gt;Critique de la faculté de juger&lt;/em&gt; (1790) analyse le &lt;a href="https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume"  title="Faculté de jugement par la-philosophie.com"&gt;jugement&lt;/a&gt; de goût : le beau plaît universellement, sans intérêt et sans concept.&lt;/p&gt; &lt;p&gt;Pour Kant, les Lumières sont « la sortie de l’homme hors de l’état de minorité » : « Ose savoir ! » Il réclame la liberté de l’usage public de la raison, qui fonde &lt;a href="https://la-philosophie.com/espace-public-et-democratie"  title="Espace public par la-philosophie.com"&gt;l’espace public&lt;/a&gt;, et rêve d’une paix perpétuelle entre les nations.&lt;/p&gt;  &lt;audio controls title="Le monde: entre déterminisme et liberté par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F68" s="47" t="inlineStr">
+      <c r="F69" s="47" t="inlineStr">
         <is>
           <t>WwrEOuVOkjk</t>
         </is>
       </c>
-      <c r="G68" s="49" t="inlineStr">
+      <c r="G69" s="49" t="inlineStr">
         <is>
           <t>"Emmanuel Kant: transformer le monde sans quitter sa ville" par Essences des Livres</t>
         </is>
       </c>
-      <c r="H68" s="49" t="inlineStr">
+      <c r="H69" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/kant-mini.webp</t>
         </is>
       </c>
-      <c r="I68" s="49" t="n"/>
-      <c r="J68" s="38" t="inlineStr">
+      <c r="I69" s="49" t="n"/>
+      <c r="J69" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K68" s="45" t="inlineStr">
+      <c r="K69" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="L68" s="46" t="inlineStr">
+      <c r="L69" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Criticisme ; Agnosticisme ; Anthropocentrisme ; Constructivisme ; Lumières ; Déontologisme</t>
         </is>
       </c>
-      <c r="M68" s="35" t="inlineStr">
+      <c r="M69" s="35" t="inlineStr">
         <is>
           <t>philosophe allemand qui a développé une théorie appelée « éthique kantienne ».</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-      <c r="P68">
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P69">
         <v>3</v>
       </c>
     </row>
-    <row r="69" ht="140.25" customHeight="1" s="39">
-      <c r="A69" s="47" t="n">
+    <row r="70" ht="140.25" customHeight="1" s="39">
+      <c r="A70" s="47" t="n">
         <v>1729</v>
       </c>
-      <c r="B69" s="47" t="inlineStr">
+      <c r="B70" s="47" t="inlineStr">
         <is>
           <t>1786</t>
         </is>
       </c>
-      <c r="C69" s="47" t="inlineStr">
+      <c r="C70" s="47" t="inlineStr">
         <is>
           <t>1729 – 1786</t>
         </is>
       </c>
-      <c r="D69" s="48" t="inlineStr">
+      <c r="D70" s="48" t="inlineStr">
         <is>
           <t>Moses MENDELSSOHN</t>
         </is>
       </c>
-      <c r="E69" s="49" t="inlineStr">
+      <c r="E70" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Moses_Mendelssohn"   title=" Wikipedia"&gt;Moses MENDELSSOHN&lt;/a&gt;  était un philosophe &lt;a href="https://www.youtube.com/watch?v=AvucqmG4Alk" title="Moses Mendelssohn et l’invention des Juifs allemands par Instituter of Jewish Studies"&gt;juif allemand des Lumières&lt;/a&gt;, né à Dessau et mort à Berlin, souvent considéré comme le "premier Juif allemand moderne" et l’une des grandes figures de  &lt;a href="https://www.youtube.com/watch?v=AaS7z6uRwWc" title="Le mythe de Moïse Mendelssohn par Efraim Palvanov"&gt;la Haskala, &lt;/a&gt; l’Aufklärung juive qui cherche à concilier fidélité au judaïsme et ouverture à la culture et à la philosophie modernes. &lt;/p&gt; &lt;p&gt; Il milite pour l’égalité civile des Juifs, la reconnaissance de leur spécificité au sein d’un État majoritairement chrétien, et la fin des discriminations légales et défend l’idée que les Juifs peuvent être pleinement intégrés comme citoyens allemands sans renoncer à leur religion. Il travaille sur la coexistence entre raison et foi, en soutenant que les vérités fondamentales de la religion sont accessibles à la raison humaine. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : "Phédon ou sur l’immortalité de l’âme" paru en 1767 qui  présente, sous forme de dialogues inspirés de Socrate, une défense de l’immortalité de l’âme et contribue à son surnom de "Socrate allemand". &lt; /p&gt; &lt;p&gt;"Jérusalem ou pouvoir religieux et judaïsme" en 1783 expose sa théorie de la séparation de l’Église et de l’État et sa vision d’un judaïsme compatible avec la liberté moderne. &lt;/p&gt; &lt;p&gt;&lt;a href="https://laviedesidees.fr/Mendelssohn-Heures-matinales" title="Le dernier métaphysicien par la vie des idées"&gt;"Morgenstunden"&lt;/a&gt;, recueil de leçons sur l’existence de Dieu, synthétise sa position philosophique dans ses dernières années
 . &lt;/p&gt; &lt;p&gt;  Il est l’un des pionniers du judaïsme libéral et un des fondateurs de la modernité juive européenne, en cherchant l’intégration sans assimilation forcée et a  eu une influence durablement la philosophie juive et la pensée allemande, préparant le terrain pour des figures comme Heinrich Heine, Hermann Cohen, Franz Rosenzweig, Walter Benjamin ou Hannah Arendt. &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F69" s="47" t="inlineStr">
+      <c r="F70" s="47" t="inlineStr">
         <is>
           <t>TJbV6JSLUeE</t>
         </is>
       </c>
-      <c r="G69" s="49" t="inlineStr">
+      <c r="G70" s="49" t="inlineStr">
         <is>
           <t>"Moses Mendelssohn: Enlightenment Pioneer" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H69" s="49" t="inlineStr">
+      <c r="H70" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mendelssohn-mini.webp</t>
         </is>
       </c>
-      <c r="I69" s="49" t="n"/>
-      <c r="J69" s="38" t="inlineStr">
+      <c r="I70" s="49" t="n"/>
+      <c r="J70" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K69" s="45" t="inlineStr">
+      <c r="K70" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; ethique</t>
         </is>
       </c>
-      <c r="L69" s="46" t="inlineStr">
+      <c r="L70" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme ; Lumières ; Haskala</t>
         </is>
       </c>
-      <c r="M69" s="35" t="inlineStr">
+      <c r="M70" s="35" t="inlineStr">
         <is>
           <t>philosophe juif allemand moderne &amp; figure de la Haskala.</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="127.5" customHeight="1" s="39">
-      <c r="A70" s="47" t="n">
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="127.5" customHeight="1" s="39">
+      <c r="A71" s="47" t="n">
         <v>1729</v>
       </c>
-      <c r="B70" s="47" t="inlineStr">
+      <c r="B71" s="47" t="inlineStr">
         <is>
           <t>1797</t>
         </is>
       </c>
-      <c r="C70" s="47" t="inlineStr">
+      <c r="C71" s="47" t="inlineStr">
         <is>
           <t>1729 – 1797</t>
         </is>
       </c>
-      <c r="D70" s="48" t="inlineStr">
+      <c r="D71" s="48" t="inlineStr">
         <is>
           <t>Edmund BURKE</t>
         </is>
       </c>
-      <c r="E70" s="63" t="inlineStr">
+      <c r="E71" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Edmund_Burke"   title=" Wikipedia"&gt;Edmund BURKE&lt;/a&gt; était un philosophe et homme politique anglo-irlandais, considéré comme l'un des fondateurs du conservatisme moderne. Il s'opposa farouchement à la Révolution française, défendant l'évolution graduelle des institutions plutôt que les ruptures radicales. Il étudia au Trinity College avant de s'installer à Londres pour exercer le droit et entrer en politique. Député whig à la Chambre des communes de 1766 à 1794, il soutint l'indépendance américaine tout en critiquant les excès fiscaux britanniques. Sa célèbre Réflexions sur la Révolution de France (1790) alerta sur les dangers de la "multitude perverse" et du rejet des traditions. &lt;/p&gt; &lt;p&gt; Il  voyait la société comme un "partenariat entre les vivants, les morts et ceux qui ne sont pas encore nés", valorisant les &lt;a href="https://www.youtube.com/watch?v=az1n7gSaKFE" title="La tradition permet elle le changement  par la chaine de Velours"&gt;préjugés hérités &lt;/a&gt; comme bank de sagesse collective supérieure à la raison individuelle. Dans Recherches philosophiques sur l'origine de nos idées du sublime et du beau (1757), il distingue le sublime (lié à la douleur, à la terreur et à Dieu) du beau (lié au plaisir et à la société), influençant l'esthétique romantique. Il prônait l'amélioration progressive de la nature humaine imparfaite, sans table rase. &lt;/p&gt; &lt;p&gt; Surnommé "conservateur des Lumières", il inspira des penseurs comme Roger Scruton et reste une référence contre les utopies rationalistes. En France, il fut parfois taxé de réactionnaire, mais son libéralisme tempéré et son sens de la responsabilité des élites résonnent encore. &lt;/p&gt;  &lt;audio controls title="Les britaniques ; Burke et ses héritiers par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-10.12.2024-ITEMA_23958056-2024C48904S0345-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F70" s="47" t="inlineStr">
+      <c r="F71" s="47" t="inlineStr">
         <is>
           <t>PazGgn9Bdsc</t>
         </is>
       </c>
-      <c r="G70" s="49" t="inlineStr">
+      <c r="G71" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">"Burke : la critique de la révolution" par Histoire sans complexe
 </t>
         </is>
       </c>
-      <c r="H70" s="49" t="inlineStr">
+      <c r="H71" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/burke-mini.webp</t>
         </is>
       </c>
-      <c r="I70" s="49" t="n"/>
-      <c r="J70" s="55" t="inlineStr">
+      <c r="I71" s="49" t="n"/>
+      <c r="J71" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K70" s="45" t="inlineStr">
+      <c r="K71" s="45" t="inlineStr">
         <is>
           <t>politique ; esthetique</t>
         </is>
       </c>
-      <c r="L70" s="46" t="inlineStr">
+      <c r="L71" s="46" t="inlineStr">
         <is>
           <t>Conservatisme</t>
         </is>
       </c>
-      <c r="M70" s="35" t="inlineStr">
+      <c r="M71" s="35" t="inlineStr">
         <is>
           <t>philosophe anglo-irlandais considéré comme l'un des fondateurs du conservatisme moderne.</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="143.25" customHeight="1" s="39">
-      <c r="A71" s="47" t="n">
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="143.25" customHeight="1" s="39">
+      <c r="A72" s="47" t="n">
         <v>1729</v>
       </c>
-      <c r="B71" s="47" t="n">
+      <c r="B72" s="47" t="n">
         <v>1781</v>
       </c>
-      <c r="C71" s="47" t="inlineStr">
+      <c r="C72" s="47" t="inlineStr">
         <is>
           <t>1729 – 1781</t>
         </is>
       </c>
-      <c r="D71" s="48" t="inlineStr">
+      <c r="D72" s="48" t="inlineStr">
         <is>
           <t>Gotthold Ephraim LESSING</t>
         </is>
       </c>
-      <c r="E71" s="62" t="inlineStr">
+      <c r="E72" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing"   title=" Wikipedia"&gt;Gotthold Ephraim LESSING&lt;/a&gt; était un écrivain, dramaturge et philosophe allemand, figure centrale des Lumières allemandes qui défendit la tolérance religieuse, la raison critique et un christianisme épuré de dogmes orthodoxes. Il rejeta l'interprétation littérale de la Bible au profit d'une révélation progressive de l'humanité via la raison, influencé par Spinoza et Leibniz, tout en prônant une harmonie entre foi et savoir. &lt;/p&gt; &lt;p&gt; Fils de pasteur luthérien à Kamenz (Saxe), Lessing étudia la théologie et la médecine avant de se consacrer à la littérature à Berlin et Leipzig. Critique théâtral virulent, il combattit l'imitation des modèles français dans la Hamburgische Dramaturgie (1767-1769), plaidant pour un théâtre national allemand réaliste. Directeur de bibliothèque à Wolfenbüttel, il noua des amitiés avec Mendelssohn et Jacobi, déclenchant la querelle du panthéisme par ses sympathies spinozistes. &lt;/p&gt; &lt;p&gt; Ses Œuvres théâtrales majeures : Miss Sara Sampson (1755) : Première tragédie bourgeoise allemande, explorant culpabilité et pardon. Minna von Barnhelm (1767) : Comédie sur la réconciliation post-Sept Ans. Emilia Galotti (1772) : Drame sur l'honneur et l'hypocrisie sociale. &lt;a href="https://www.radiofrance.fr/franceculture/nathan-le-sage-de-gotthold-ephraim-lessing-8205672" title="Nathan le sage de Lessing  par Radio France"&gt;Nathan le Sage (1779) &lt;/a&gt;  : Parabole tolérante où juif, chrétien et musulman incarnent la fraternité humaine via les trois anneaux (foi égale). &lt;/p&gt; &lt;p&gt; Dans L'Éducation du genre humain (1780), il voit l'histoire comme un processus divin d'éducation progressive : la révélation biblique n'est pas figée mais s'affine par la raison, menant à un "christianisme de raison". Laocoon (1766) distingue poésie (temps, action) et peinture (espace, corps). Son "fossé de Lessing" questionne : miracles historiques ne prouvent pas vérités éternelles. Il inspira Herder, Goethe et le romantisme par son relativisme esthétique et moral. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F71" s="47" t="inlineStr">
+      <c r="F72" s="47" t="inlineStr">
         <is>
           <t>4q_hrrQvNtA</t>
         </is>
       </c>
-      <c r="G71" s="49" t="inlineStr">
+      <c r="G72" s="49" t="inlineStr">
         <is>
           <t>« what did Gotthold Ephraim Lessing believe ? » Par Chronicles of Legends</t>
         </is>
       </c>
-      <c r="H71" s="58" t="inlineStr">
+      <c r="H72" s="58" t="inlineStr">
         <is>
           <t>https://laphilo.fr/pho/ghlessing-mini.webp</t>
         </is>
       </c>
-      <c r="I71" s="49" t="n"/>
-      <c r="J71" s="38" t="inlineStr">
+      <c r="I72" s="49" t="n"/>
+      <c r="J72" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K71" s="45" t="inlineStr">
+      <c r="K72" s="45" t="inlineStr">
         <is>
           <t>ethique ; esthetique</t>
         </is>
       </c>
-      <c r="L71" s="46" t="inlineStr">
+      <c r="L72" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Déisme ; Lumières</t>
         </is>
       </c>
-      <c r="M71" s="35" t="inlineStr">
+      <c r="M72" s="35" t="inlineStr">
         <is>
           <t>philosophe allemand &amp; figure centrale des Lumières allemandes.</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="131.25" customHeight="1" s="39">
-      <c r="A72" s="47" t="n">
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="131.25" customHeight="1" s="39">
+      <c r="A73" s="47" t="n">
         <v>1740</v>
       </c>
-      <c r="B72" s="47" t="inlineStr">
+      <c r="B73" s="47" t="inlineStr">
         <is>
           <t>1814</t>
         </is>
       </c>
-      <c r="C72" s="47" t="inlineStr">
+      <c r="C73" s="47" t="inlineStr">
         <is>
           <t>1740 - 1814</t>
         </is>
       </c>
-      <c r="D72" s="48" t="inlineStr">
+      <c r="D73" s="48" t="inlineStr">
         <is>
           <t>François de SADE</t>
         </is>
       </c>
-      <c r="E72" s="49" t="inlineStr">
+      <c r="E73" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donatien_Alphonse_Fran%C3%A7ois_de_Sade" title=" Wikipedia"&gt;Marquis François de SADE&lt;/a&gt; était un écrivain, philosophe Français surtout connu pour ses écrits provocateurs et controversés, qui abordent les thèmes de &lt;a href="https://www.youtube.com/watch?v=PJdCNc-0Ybk" title="Sade – justine ou les malheurs de la vertu par Kosmos"&gt;la sexualité, la violence et la morale&lt;/a&gt;. Il a passé une grande partie de sa vie en prison ou en exil en raison de ses opinions et de ses activités considérées comme immorales et illégales. &lt;/p&gt; &lt;p&gt;  Bien qu'il soit souvent associé à la pornographie et à la violence, il a exercé une influence importante sur la philosophie et la culture. Il a été considéré comme un précurseur du mouvement surréaliste, de &lt;a href="https://www.youtube.com/watch?v=KEh0vf7HCoI&amp;ab_channel=RayonPolar"   title="Donatien Alphonse François de Sade par RayonPolar"&gt; nombreux cinéastes&lt;/a&gt; tels que Brunel, Debordque, Bergma ont étaient inspirés et son travail qui a aussi été étudié par des philosophes tels que Michel Foucault et Gilles Deleuze. &lt;/p&gt; &lt;p&gt;  Sa pensée libertaire et sa critique de la société et de la religion ont également inspiré de nombreux mouvements politiques et sociaux.&lt;/p&gt; &lt;p&gt; 
 Son œuvre la plus célèbre, &lt;a href="https://fr.wikisource.org/wiki/Les_120_Journ%C3%A9es_de_Sodome"  title="Les 120 jours de Sodome par source Wikisource"&gt; "Les 120 Journées de Sodome" &lt;/a&gt; (également connue sous le nom de "La Philosophie dans le Boudoir"), est considérée comme l'un des premiers exemples de littérature érotique. Ce livre est aujourd'hui considéré comme extrêmement choquant en raison de sa description explicite de pratiques sexuelles déviantes et violentes. &lt;/p&gt; &lt;p&gt;  Son travail &lt;a href="https://www.youtube.com/watch?v=Qwfqw51JaGY" title=""L'apologie du mal" par le Précepteur"&gt;provocateur et choquant &lt;/a&gt;  a soulevé des questions importantes sur la sexualité, la morale et la liberté individuelle, qui continuent d'être pertinents aujourd'hui et on utilise le terme de 'sadique' aujourd'hui dans la langue Française.&lt;/p&gt; &lt;audio controls title="La vie en infamie du marquis de Sade par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/15537-14.01.2019-ITEMA_21950194-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F72" s="47" t="inlineStr">
+      <c r="F73" s="47" t="inlineStr">
         <is>
           <t>SSL6icGS7gg</t>
         </is>
       </c>
-      <c r="G72" s="49" t="inlineStr">
+      <c r="G73" s="49" t="inlineStr">
         <is>
           <t>"Marquis de sade : l’homme le plus dépravé de l’histoire" par Les Ombres de l’histoire</t>
         </is>
       </c>
-      <c r="H72" s="49" t="inlineStr">
+      <c r="H73" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/sade-mini.webp</t>
         </is>
       </c>
-      <c r="I72" s="49" t="n"/>
-      <c r="J72" s="38" t="inlineStr">
+      <c r="I73" s="49" t="n"/>
+      <c r="J73" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K72" s="45" t="inlineStr">
+      <c r="K73" s="45" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="L72" s="46" t="inlineStr">
+      <c r="L73" s="46" t="inlineStr">
         <is>
           <t>Matérialisme</t>
         </is>
       </c>
-      <c r="M72" s="35" t="inlineStr">
+      <c r="M73" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour ses écrits provocateurs et controversés.</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="116.25" customHeight="1" s="39">
-      <c r="A73" s="47" t="n">
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="116.25" customHeight="1" s="39">
+      <c r="A74" s="47" t="n">
         <v>1741</v>
       </c>
-      <c r="B73" s="47" t="inlineStr">
+      <c r="B74" s="47" t="inlineStr">
         <is>
           <t>1801</t>
         </is>
       </c>
-      <c r="C73" s="47" t="inlineStr">
+      <c r="C74" s="47" t="inlineStr">
         <is>
           <t>1741 – 1801</t>
         </is>
       </c>
-      <c r="D73" s="48" t="inlineStr">
+      <c r="D74" s="48" t="inlineStr">
         <is>
           <t>Johann Kaspar LAVATER</t>
         </is>
       </c>
-      <c r="E73" s="63" t="inlineStr">
+      <c r="E74" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Kaspar_Lavater"  title=" Wikipedia"&gt;Johann Kaspar LAVATER&lt;/a&gt;  était un théologien, poète et philosophe suisse, connu surtout comme pionnier de  &lt;a href="https://fr.wikipedia.org/wiki/Physiognomonie"  title="Physiognomonie par Wikipedia"&gt; "la physiognomonie, &lt;/a&gt;  une pseudoscience liant traits du visage et caractère moral. Pasteur réformé à Zurich, il mêla mysticisme chrétien, irrationalisme et influences des Lumières tardives dans ses écrits. Né à Zurich dans une famille bourgeoise, il étudia la théologie et la philosophie au Collegium Carolinum sous Johann Jakob Bodmer. Ordonné en 1762, il devint diacre puis pasteur à l'église St-Pierre, tout en s'engageant contre la corruption locale, ce qui l'exila brièvement à Berlin. Ami de Goethe (dont la relation se tendit) et de Moses Mendelssohn, il fut blessé lors de l'invasion française de 1799 et mourut de ses blessures. &lt;/p&gt; &lt;p&gt; Sa grande œuvre, Physiognomische Fragmente zur Beförderung der Menschenkenntnis und Menschenliebe (1775-1778), postule que le visage révèle l'âme divine en l'homme, reliant esthétique, vertu et théologie. Influencé par l'Empfindsamkeit et le Sturm und Drang, il valorisait le sentiment sur la raison pure, explorant prophétie, miracles et palingénésie (résurrection). Critiqué par Lichtenberg pour son subjectivisme, il inspira poésie mystique et débats sur  &lt;a href="https://www.youtube.com/watch?v=LUxSlXIY-Zk"  title="Johann Kaspar Lavater par Grow Wise"&gt; "l'intériorité humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il  incarna un pont entre piétisme, sentimentalisme et romantisme naissant, influençant esthétique et psychologie populaire en Europe. Ses idées déclinèrent avec les progrès scientifiques, mais sa quête d'une connaissance intuitive de l'homme reste débattue. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F73" s="47" t="inlineStr">
+      <c r="F74" s="47" t="inlineStr">
         <is>
           <t>bSAtDI9S6hU</t>
         </is>
       </c>
-      <c r="G73" s="49" t="inlineStr">
+      <c r="G74" s="49" t="inlineStr">
         <is>
           <t>Johann Kaspar Lavater par See Hear Say Learn</t>
         </is>
       </c>
-      <c r="H73" s="49" t="inlineStr">
+      <c r="H74" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/jklavater-mini.webp</t>
         </is>
       </c>
-      <c r="I73" s="49" t="n"/>
-      <c r="J73" s="38" t="inlineStr">
+      <c r="I74" s="49" t="n"/>
+      <c r="J74" s="38" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
       </c>
-      <c r="K73" s="45" t="inlineStr">
+      <c r="K74" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; spiritualite</t>
         </is>
       </c>
-      <c r="L73" s="46" t="inlineStr">
+      <c r="L74" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Spiritualisme</t>
         </is>
       </c>
-      <c r="M73" s="35" t="inlineStr">
+      <c r="M74" s="35" t="inlineStr">
         <is>
           <t>théologien, poète et philosophe suisse, connu comme pionnier de la physiognomonie.</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="158.25" customHeight="1" s="39">
-      <c r="A74" s="47" t="n">
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="158.25" customHeight="1" s="39">
+      <c r="A75" s="47" t="n">
         <v>1743</v>
       </c>
-      <c r="B74" s="47" t="inlineStr">
+      <c r="B75" s="47" t="inlineStr">
         <is>
           <t>1803</t>
         </is>
       </c>
-      <c r="C74" s="47" t="inlineStr">
+      <c r="C75" s="47" t="inlineStr">
         <is>
           <t>1743 – 1803</t>
         </is>
       </c>
-      <c r="D74" s="48" t="inlineStr">
+      <c r="D75" s="48" t="inlineStr">
         <is>
           <t>Louis-Claude de ST-MARTIN</t>
         </is>
       </c>
-      <c r="E74" s="62" t="inlineStr">
+      <c r="E75" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis-Claude_de_Saint-Martin"  title=" Wikipedia"&gt;Louis-Claude de ST-MARTIN&lt;/a&gt; dit &lt;a href="https://www.persee.fr/doc/dhs_0070-6760_1972_num_4_1_998"  title="Un philosophe toujours inconnu par Persée"&gt;« le Philosophe inconnu », &lt;/a&gt; était un philosophe et théosophe français, figure majeure du mysticisme chrétien au XVIIIe siècle. Issu d’une famille noble tourangelle, il chercha une voie spirituelle intérieure, rejetant les pratiques magiques pour privilégier la prière et la connaissance de soi comme moyens de réintégration divine.  &lt;/p&gt; &lt;p&gt; Militaire de formation, il rencontra en 1768 Martinez de Pasqually, fondateur de l’Ordre des Élus-Cohën, dont il devint un disciple fervent, assistant à ses rituels théurgiques. Après la mort de son maître en 1774, il s’éloigna des opérations extérieures, publiant anonymement des œuvres comme Des erreurs et de la vérité (1775) et Le Tableau naturel (1782).  Il a composé en 1790  &lt;a href="https://www.youtube.com/watch?v=4MFZG5b-lbI"  title="Le nouvel homme de St martin par Hermes Books Omega"&gt;« le nouvel homme » &lt;/a&gt; qui constitue une oeuvre majeure pour tous ceux qui s'intéressent à la pensée saint-martinienne et en premier chef pour les Martinistes, Vivant modestement comme secrétaire d’un magistrat à Paris, puis à Aulnay-la-Malherbe, il entretint une correspondance spirituelle avec des adeptes, influencé par Jakob Böhme et Swedenborg. &lt;/p&gt; &lt;p&gt; Pour lui, l’homme, issu d’une chute originelle, porte en lui une « pensée de Dieu » à développer par le libre arbitre et l’amour universel, menant à l’unité primordiale. Il opposait la raison matérialiste des Lumières à une révélation intérieure, voyant la société et l’individu comme des miroirs déformés de la Divinité à restaurer par la grâce et la vertu. Ses écrits insistent sur l’équilibre entre devoir moral, fraternité et intuition prophétique, préfigurant un ésotérisme non dogmatique. &lt;/p&gt; &lt;p&gt; Influençant Joseph de Maistre, Schelling ou René Guénon, il fonda une « école mystique » centrée sur la voie cardiaque, sans rituels extérieurs. Son rejet des utopies rationalistes et son appel à une régénération spirituelle résonnent encore dans la franc-maçonnerie  &lt;a href="https://fr.wikipedia.org/wiki/Martinisme"  title="Martinisme par Wikipedia"&gt; martiniste &lt;/a&gt; et la théosophie moderne. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F74" s="47" t="inlineStr">
+      <c r="F75" s="47" t="inlineStr">
         <is>
           <t>SJuwC2Mj59U</t>
         </is>
       </c>
-      <c r="G74" s="49" t="inlineStr">
+      <c r="G75" s="49" t="inlineStr">
         <is>
           <t>"Louis-Claude de SAINT-MARTIN et le martinisme" par promethee moi</t>
         </is>
       </c>
-      <c r="H74" s="49" t="inlineStr">
+      <c r="H75" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/martin-mini.webp</t>
-        </is>
-      </c>
-      <c r="I74" s="49" t="n"/>
-      <c r="J74" s="38" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K74" s="45" t="inlineStr">
-        <is>
-          <t>metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L74" s="46" t="inlineStr">
-        <is>
-          <t>Martinisme</t>
-        </is>
-      </c>
-      <c r="M74" s="35" t="inlineStr">
-        <is>
-          <t>philosophe français figure du mysticisme chrétien au XVIIIe siècle.</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="187.5" customHeight="1" s="39">
-      <c r="A75" s="47" t="n">
-        <v>1743</v>
-      </c>
-      <c r="B75" s="47" t="inlineStr">
-        <is>
-          <t>1794</t>
-        </is>
-      </c>
-      <c r="C75" s="47" t="inlineStr">
-        <is>
-          <t>1743 – 1794</t>
-        </is>
-      </c>
-      <c r="D75" s="48" t="inlineStr">
-        <is>
-          <t>Nicolas de CONDORCET</t>
-        </is>
-      </c>
-      <c r="E75" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet"  title=" Wikipedia"&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe, mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet féministe ? par Sud Radio"&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote.  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet et l’éloge de l’instruction par Culture philo"&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href="https://www.youtube.com/watch?v=avTI9GHZX1I"  title="Condorcet le paradoxe par Diable Positif"&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la "mathématique sociale", Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title="Nicolas de Condorcet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F75" s="47" t="inlineStr">
-        <is>
-          <t>2Acb4hqvw54</t>
-        </is>
-      </c>
-      <c r="G75" s="49" t="inlineStr">
-        <is>
-          <t>"Condorcet - Laissez-faire français " par Ecole de la Liberté</t>
-        </is>
-      </c>
-      <c r="H75" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/condorcet-mini.webp</t>
         </is>
       </c>
       <c r="I75" s="49" t="n"/>
@@ -5663,17 +5663,17 @@
       </c>
       <c r="K75" s="45" t="inlineStr">
         <is>
-          <t>politique ; epistemologie</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L75" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positivisme ; Lumières ; Progressisme</t>
+          <t>Martinisme</t>
         </is>
       </c>
       <c r="M75" s="35" t="inlineStr">
         <is>
-          <t>philosophe français figure des Lumières et défenseur du progrès humain indéfini.</t>
+          <t>philosophe français figure du mysticisme chrétien au XVIIIe siècle.</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5682,110 +5682,110 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="148.5" customHeight="1" s="39">
+    <row r="76" ht="187.5" customHeight="1" s="39">
       <c r="A76" s="47" t="n">
         <v>1743</v>
       </c>
       <c r="B76" s="47" t="inlineStr">
         <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="C76" s="47" t="inlineStr">
+        <is>
+          <t>1743 – 1794</t>
+        </is>
+      </c>
+      <c r="D76" s="48" t="inlineStr">
+        <is>
+          <t>Nicolas de CONDORCET</t>
+        </is>
+      </c>
+      <c r="E76" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet"  title=" Wikipedia"&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe, mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet féministe ? par Sud Radio"&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote.  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href="https://www.youtube.com/watch?v=3G3kVl0GbA8"  title="Condorcet et l’éloge de l’instruction par Culture philo"&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href="https://www.youtube.com/watch?v=avTI9GHZX1I"  title="Condorcet le paradoxe par Diable Positif"&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la "mathématique sociale", Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title="Nicolas de Condorcet par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F76" s="47" t="inlineStr">
+        <is>
+          <t>2Acb4hqvw54</t>
+        </is>
+      </c>
+      <c r="G76" s="49" t="inlineStr">
+        <is>
+          <t>"Condorcet - Laissez-faire français " par Ecole de la Liberté</t>
+        </is>
+      </c>
+      <c r="H76" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/condorcet-mini.webp</t>
+        </is>
+      </c>
+      <c r="I76" s="49" t="n"/>
+      <c r="J76" s="38" t="inlineStr">
+        <is>
+          <t>Française</t>
+        </is>
+      </c>
+      <c r="K76" s="45" t="inlineStr">
+        <is>
+          <t>politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L76" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positivisme ; Lumières ; Progressisme</t>
+        </is>
+      </c>
+      <c r="M76" s="35" t="inlineStr">
+        <is>
+          <t>philosophe français figure des Lumières et défenseur du progrès humain indéfini.</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="148.5" customHeight="1" s="39">
+      <c r="A77" s="47" t="n">
+        <v>1743</v>
+      </c>
+      <c r="B77" s="47" t="inlineStr">
+        <is>
           <t>1819</t>
         </is>
       </c>
-      <c r="C76" s="47" t="inlineStr">
+      <c r="C77" s="47" t="inlineStr">
         <is>
           <t>1743 – 1819</t>
         </is>
       </c>
-      <c r="D76" s="48" t="inlineStr">
+      <c r="D77" s="48" t="inlineStr">
         <is>
           <t>Friedrich Heinrich JACOBI</t>
         </is>
       </c>
-      <c r="E76" s="63" t="inlineStr">
+      <c r="E77" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi"  title=" Wikipedia"&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href="https://fr.wikipedia.org/wiki/Nihilisme"  title="Nihilisme par Wikipedia"&gt; nihilisme &lt;/a&gt; et au &lt;a href="https://fr.wikipedia.org/wiki/Panth%C3%A9isme"  title="Panthéisme par Wikipedia"&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse "querelle du panthéisme" en révélant que Lessing s'était  &lt;a href="https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321"  title="Jacobi et Spinoza par Persée"&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu. &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du "rien ne sort du néant") de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un "saut de la foi" hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F76" s="47" t="inlineStr">
+      <c r="F77" s="47" t="inlineStr">
         <is>
           <t>1omDmffUbaw</t>
         </is>
       </c>
-      <c r="G76" s="49" t="inlineStr">
+      <c r="G77" s="49" t="inlineStr">
         <is>
           <t>"Friedrich Heinrich Jacobi: Challenging Enlightenment Ideas" par VISPHILO</t>
         </is>
       </c>
-      <c r="H76" s="49" t="inlineStr">
+      <c r="H77" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/fhjacobi-mini.webp</t>
-        </is>
-      </c>
-      <c r="I76" s="49" t="n"/>
-      <c r="J76" s="38" t="inlineStr">
-        <is>
-          <t>Allemande</t>
-        </is>
-      </c>
-      <c r="K76" s="45" t="inlineStr">
-        <is>
-          <t>metaphysique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L76" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spiritualisme ; Irrationalisme</t>
-        </is>
-      </c>
-      <c r="M76" s="35" t="inlineStr">
-        <is>
-          <t>philosophe juif allemand critique majeur du rationalisme des Lumières.</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="155.25" customHeight="1" s="39">
-      <c r="A77" s="47" t="n">
-        <v>1744</v>
-      </c>
-      <c r="B77" s="47" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="C77" s="47" t="inlineStr">
-        <is>
-          <t>1744 – 1803</t>
-        </is>
-      </c>
-      <c r="D77" s="48" t="inlineStr">
-        <is>
-          <t>Johann Gottfried HERDER</t>
-        </is>
-      </c>
-      <c r="E77" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Gottfried_von_Herder"  title=" Wikipedia"&gt;Johann Gottfried HERDER&lt;/a&gt; était un philosophe  et écrivain allemand souvent considéré comme l’un des pères de la philosophie de la culture et de &lt;a href="https://www.jdarriulat.net/Introductionphiloesth/PhiloModerne/Herder.html"  title="INTRODUCTION A LA PHILOSOPHIE ESTHETIQUE par jdarriulat"&gt;l’idée moderne &lt;/a&gt; de "nation". Son œuvre se situe à la croisée des Lumières et du premier romantisme allemand. Il refuse l’idée d’un progrès linéaire et uniforme de l’humanité vers une &lt;a href="https://www.youtube.com/watch?v=Y8l9aJhT76U" title="Johann Gottfried Herder par Greatest Minds in History"&gt;seule forme de civilisation&lt;/a&gt;, telle qu’on la trouve chez certains auteurs des Lumières. Chaque époque et chaque peuple possède, selon lui, une valeur propre qui doit être comprise de l’intérieur et non jugée à l’aune d’un modèle abstrait. Il propose une philosophie de l’histoire "humanitaire" : l’histoire est le développement de l’humanité en tant que telle, dans sa pluralité de formes, sous le signe de la culture, de la liberté et de la perfectibilité.  &lt;/p&gt; &lt;p&gt; Il attribue au langage un rôle constitutif dans la formation de la pensée humaine, contre l’idée d’une raison pure préexistante à toute expérience linguistique. La raison ne précède pas le langage, elle se forme à travers lui, si bien que connaître, c’est toujours déjà interpréter à l’aide de mots et de symboles historiques. Il s’intéresse à l’origine des langues et parle d’un "roman des langues" pour décrire l’histoire par laquelle les hommes passent d’un stade prélinguistique à des formes complexes de communication et de socialisation. &lt;/p&gt; &lt;p&gt; Son œuvre est très abondante, mais quelques titres structurent sa pensée. On cite notamment : "Auch eine Philosophie der Geschichte zur Bildung der Menschheit" paru en 1774 et surtout &lt;a href="https://de.wikipedia.org/wiki/Ideen_zur_Philosophie_der_Geschichte_der_Menschheit" title="Ideen zur Philosophie der Geschichte der Menschheit par wikipedia"&gt;"Ideen zur Philosophie der Geschichte der Menschheit"&lt;/a&gt; qui proposent une vaste vision historico‑culturelle de l’humanité. &lt;/p&gt; &lt;p&gt;   À la fin de sa vie, il polémique avec Kant dans la "Métacritique de la critique de la raison pure" et développe une esthétique originale dans "Kalligone".  Son insistance sur la culture, la langue et le peuple marquera durablement les théories de la nation, de l’anthropologie culturelle et de la philosophie de l’histoire. &lt;/p&gt; </t>
-        </is>
-      </c>
-      <c r="F77" s="47" t="inlineStr">
-        <is>
-          <t>AWvhAGgW1v8</t>
-        </is>
-      </c>
-      <c r="G77" s="49" t="inlineStr">
-        <is>
-          <t>"Johann Gottfried Herder: Revolutionizing Political Thought" par VIS PHILO</t>
-        </is>
-      </c>
-      <c r="H77" s="49" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/herder-mini.webp</t>
         </is>
       </c>
       <c r="I77" s="49" t="n"/>
@@ -5796,17 +5796,17 @@
       </c>
       <c r="K77" s="45" t="inlineStr">
         <is>
-          <t>epistemologie ; esthetique</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L77" s="46" t="inlineStr">
         <is>
-          <t>Romantisme</t>
+          <t xml:space="preserve">Spiritualisme ; Irrationalisme</t>
         </is>
       </c>
       <c r="M77" s="35" t="inlineStr">
         <is>
-          <t>philosophe allemand père de la philosophie de la culture et de l’idée moderne de nation.</t>
+          <t>philosophe juif allemand critique majeur du rationalisme des Lumières.</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5815,9 +5815,9 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="112.5" customHeight="1" s="39">
+    <row r="78" ht="155.25" customHeight="1" s="39">
       <c r="A78" s="47" t="n">
-        <v>1747</v>
+        <v>1744</v>
       </c>
       <c r="B78" s="47" t="inlineStr">
         <is>
@@ -5826,32 +5826,32 @@
       </c>
       <c r="C78" s="47" t="inlineStr">
         <is>
-          <t>1747 – 1803</t>
+          <t>1744 – 1803</t>
         </is>
       </c>
       <c r="D78" s="48" t="inlineStr">
         <is>
-          <t>Marcus HERZ</t>
-        </is>
-      </c>
-      <c r="E78" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcus_Herz"  title=" Wikipedia"&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Emmanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2" title="Kant, Lettre à Marcus Herz du 21 février 1772 par Persée"&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la "révolution copernicienne"), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent "Betrachtungen aus der spekulativen Weltweisheit"  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et "Versuch über den Geschmack" en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; </t>
+          <t>Johann Gottfried HERDER</t>
+        </is>
+      </c>
+      <c r="E78" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Gottfried_von_Herder"  title=" Wikipedia"&gt;Johann Gottfried HERDER&lt;/a&gt; était un philosophe  et écrivain allemand souvent considéré comme l’un des pères de la philosophie de la culture et de &lt;a href="https://www.jdarriulat.net/Introductionphiloesth/PhiloModerne/Herder.html"  title="INTRODUCTION A LA PHILOSOPHIE ESTHETIQUE par jdarriulat"&gt;l’idée moderne &lt;/a&gt; de "nation". Son œuvre se situe à la croisée des Lumières et du premier romantisme allemand. Il refuse l’idée d’un progrès linéaire et uniforme de l’humanité vers une &lt;a href="https://www.youtube.com/watch?v=Y8l9aJhT76U" title="Johann Gottfried Herder par Greatest Minds in History"&gt;seule forme de civilisation&lt;/a&gt;, telle qu’on la trouve chez certains auteurs des Lumières. Chaque époque et chaque peuple possède, selon lui, une valeur propre qui doit être comprise de l’intérieur et non jugée à l’aune d’un modèle abstrait. Il propose une philosophie de l’histoire "humanitaire" : l’histoire est le développement de l’humanité en tant que telle, dans sa pluralité de formes, sous le signe de la culture, de la liberté et de la perfectibilité.  &lt;/p&gt; &lt;p&gt; Il attribue au langage un rôle constitutif dans la formation de la pensée humaine, contre l’idée d’une raison pure préexistante à toute expérience linguistique. La raison ne précède pas le langage, elle se forme à travers lui, si bien que connaître, c’est toujours déjà interpréter à l’aide de mots et de symboles historiques. Il s’intéresse à l’origine des langues et parle d’un "roman des langues" pour décrire l’histoire par laquelle les hommes passent d’un stade prélinguistique à des formes complexes de communication et de socialisation. &lt;/p&gt; &lt;p&gt; Son œuvre est très abondante, mais quelques titres structurent sa pensée. On cite notamment : "Auch eine Philosophie der Geschichte zur Bildung der Menschheit" paru en 1774 et surtout &lt;a href="https://de.wikipedia.org/wiki/Ideen_zur_Philosophie_der_Geschichte_der_Menschheit" title="Ideen zur Philosophie der Geschichte der Menschheit par wikipedia"&gt;"Ideen zur Philosophie der Geschichte der Menschheit"&lt;/a&gt; qui proposent une vaste vision historico‑culturelle de l’humanité. &lt;/p&gt; &lt;p&gt;   À la fin de sa vie, il polémique avec Kant dans la "Métacritique de la critique de la raison pure" et développe une esthétique originale dans "Kalligone".  Son insistance sur la culture, la langue et le peuple marquera durablement les théories de la nation, de l’anthropologie culturelle et de la philosophie de l’histoire. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F78" s="47" t="inlineStr">
         <is>
-          <t>vKkBVZaoOs4</t>
+          <t>AWvhAGgW1v8</t>
         </is>
       </c>
       <c r="G78" s="49" t="inlineStr">
         <is>
-          <t>"Marcus HERZ" par WikiTubia</t>
+          <t>"Johann Gottfried Herder: Revolutionizing Political Thought" par VIS PHILO</t>
         </is>
       </c>
       <c r="H78" s="49" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/herz-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/herder-mini.webp</t>
         </is>
       </c>
       <c r="I78" s="49" t="n"/>
@@ -5862,726 +5862,739 @@
       </c>
       <c r="K78" s="45" t="inlineStr">
         <is>
+          <t>epistemologie ; esthetique</t>
+        </is>
+      </c>
+      <c r="L78" s="46" t="inlineStr">
+        <is>
+          <t>Romantisme</t>
+        </is>
+      </c>
+      <c r="M78" s="35" t="inlineStr">
+        <is>
+          <t>philosophe allemand père de la philosophie de la culture et de l’idée moderne de nation.</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="112.5" customHeight="1" s="39">
+      <c r="A79" s="47" t="n">
+        <v>1747</v>
+      </c>
+      <c r="B79" s="47" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="C79" s="47" t="inlineStr">
+        <is>
+          <t>1747 – 1803</t>
+        </is>
+      </c>
+      <c r="D79" s="48" t="inlineStr">
+        <is>
+          <t>Marcus HERZ</t>
+        </is>
+      </c>
+      <c r="E79" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marcus_Herz"  title=" Wikipedia"&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Emmanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2" title="Kant, Lettre à Marcus Herz du 21 février 1772 par Persée"&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la "révolution copernicienne"), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent "Betrachtungen aus der spekulativen Weltweisheit"  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et "Versuch über den Geschmack" en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; </t>
+        </is>
+      </c>
+      <c r="F79" s="47" t="inlineStr">
+        <is>
+          <t>vKkBVZaoOs4</t>
+        </is>
+      </c>
+      <c r="G79" s="49" t="inlineStr">
+        <is>
+          <t>"Marcus HERZ" par WikiTubia</t>
+        </is>
+      </c>
+      <c r="H79" s="49" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/herz-mini.webp</t>
+        </is>
+      </c>
+      <c r="I79" s="49" t="n"/>
+      <c r="J79" s="38" t="inlineStr">
+        <is>
+          <t>Allemande</t>
+        </is>
+      </c>
+      <c r="K79" s="45" t="inlineStr">
+        <is>
           <t>epistemologie ; metaphysique</t>
         </is>
       </c>
-      <c r="L78" s="46" t="inlineStr">
+      <c r="L79" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Criticisme ; Haskala</t>
         </is>
       </c>
-      <c r="M78" s="35" t="inlineStr">
+      <c r="M79" s="35" t="inlineStr">
         <is>
           <t>philosophe juif allemand, disciple de Kant &amp; figure des Lumières berlinoises.</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="178.5" customHeight="1" s="39">
-      <c r="A79" s="47" t="n">
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="178.5" customHeight="1" s="39">
+      <c r="A80" s="47" t="n">
         <v>1748</v>
       </c>
-      <c r="B79" s="47" t="inlineStr">
+      <c r="B80" s="47" t="inlineStr">
         <is>
           <t>1832</t>
         </is>
       </c>
-      <c r="C79" s="47" t="inlineStr">
+      <c r="C80" s="47" t="inlineStr">
         <is>
           <t>1748 - 1832</t>
         </is>
       </c>
-      <c r="D79" s="48" t="inlineStr">
+      <c r="D80" s="48" t="inlineStr">
         <is>
           <t>Jérémy BENTHAM</t>
         </is>
       </c>
-      <c r="E79" s="60" t="inlineStr">
+      <c r="E80" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Jeremy_Bentham"  title=" Wikipedia"&gt;Jérémy BENTHAM&lt;/a&gt; était un philosophe Anglais, économiste et réformateur social. &lt;/p&gt; &lt;p&gt; Il est considéré comme l'un des fondateurs de &lt;a  href="https://www.youtube.com/watch?v=yCDOVcvNYpY&amp;t=2s&amp;ab_channel=AlainBajom%C3%A9e"  title="L'utilitarisme par Alain Bajomée"&gt;l'utilitarisme&lt;/a&gt;, une doctrine éthique qui affirme que la meilleure action est celle qui produit le plus grand bien-être pour le plus grand nombre de personnes possible. Selon lui, la nature humaine est motivée par la recherche du &lt;a  href="https://www.youtube.com/watch?v=2c6jMZr6-Jc&amp;ab_channel=LePr%C3%A9cepteur"  title="Sommes nous tous égoiste par Le Précepteur"&gt;plaisir personnel&lt;/a&gt; et l'évitement de la douleur, et donc la recherche du bonheur est la fin ultime de toute action. &lt;/p&gt; &lt;p&gt; Bentham rejette les fondements moraux traditionnels (coutume, religion, devoir abstrait) au profit de l'utilité : une loi ou action est bonne si elle augmente le bonheur net de la société, somme des bonheurs individuels. Il distingue plaisirs quantifiables (sans hiérarchie entre supérieurs ou inférieurs) et prône un État interventionniste pour protéger les libertés, redistribuer les richesses (taxe progressive sur héritages) et encourager la croissance économique et démographique. &lt;/p&gt; &lt;p&gt; Il a également proposé le principe de l'égalité morale, selon lequel chaque individu compte pour un dans le calcul du bonheur global, ce qui signifie que chaque vie a la même importance morale. Cela a conduit Bentham à être un défenseur de l'égalité des  &lt;a  href="https://www.youtube.com/watch?v=xJDQu0OLwME&amp;ab_channel=MonsieurPhi"  title="L'homosexualité par Mr Phi"&gt;droits pour tous&lt;/a&gt;, y compris les femmes et les minorités. &lt;/p&gt; &lt;p&gt;Il a été un critique de la philosophie morale traditionnelle, qui était souvent basée sur des notions abstraites telles que la vertu et le devoir. Il a plutôt cherché à fonder &lt;a  href="https://www.youtube.com/watch?v=mvamwoVi1KE"  title="Bentham, qu’est ce l’utilitarisme par Le Précepteur"&gt; l'éthique sur des principes empiriques, &lt;/a&gt; en se basant sur des observations et des expériences concrètes. Il  appliqua sa philosophie à la réforme pénale (contre la peine de mort arbitraire), juridique (code pénal rationnel), économique (rôle de l'État dans sécurité et subsistance) et sociale (éducation, santé publique). Critiqué pour son hédonisme mécanique, il influença Mill, le libéralisme social et les politiques publiques modernes.    &lt;/p&gt;  &lt;audio controls title="Dans la peau de Jeremy Bentham par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10081-29.01.2018-ITEMA_21570270-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F79" s="47" t="inlineStr">
+      <c r="F80" s="47" t="inlineStr">
         <is>
           <t>mvamwoVi1KE</t>
         </is>
       </c>
-      <c r="G79" s="49" t="inlineStr">
+      <c r="G80" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">"L'utilitarisme" par Le Précepteur</t>
         </is>
       </c>
-      <c r="H79" s="49" t="inlineStr">
+      <c r="H80" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bentham-mini.webp</t>
         </is>
       </c>
-      <c r="I79" s="49" t="n"/>
-      <c r="J79" s="55" t="inlineStr">
+      <c r="I80" s="49" t="n"/>
+      <c r="J80" s="55" t="inlineStr">
         <is>
           <t>Britannique</t>
         </is>
       </c>
-      <c r="K79" s="45" t="inlineStr">
+      <c r="K80" s="45" t="inlineStr">
         <is>
           <t>ethique ; politique</t>
         </is>
       </c>
-      <c r="L79" s="46" t="inlineStr">
+      <c r="L80" s="46" t="inlineStr">
         <is>
           <t>Utilitarisme ; Conséquentialisme</t>
         </is>
       </c>
-      <c r="M79" s="35" t="inlineStr">
+      <c r="M80" s="35" t="inlineStr">
         <is>
           <t>philosophe et économiste anglais considéré comme fondateur de l'Utilitarisme.</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="141.75" customHeight="1" s="39">
-      <c r="A80" s="47" t="n">
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="141.75" customHeight="1" s="39">
+      <c r="A81" s="47" t="n">
         <v>1750</v>
       </c>
-      <c r="B80" s="47" t="inlineStr">
+      <c r="B81" s="47" t="inlineStr">
         <is>
           <t>1834</t>
         </is>
       </c>
-      <c r="C80" s="47" t="inlineStr">
+      <c r="C81" s="47" t="inlineStr">
         <is>
           <t>1750 – 1834</t>
         </is>
       </c>
-      <c r="D80" s="48" t="inlineStr">
+      <c r="D81" s="48" t="inlineStr">
         <is>
           <t>David FRIEDLÄNDER</t>
         </is>
       </c>
-      <c r="E80" s="63" t="inlineStr">
+      <c r="E81" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/David_Friedl%C3%A4nder"  title=" Wikipedia"&gt;David FRIEDLÄNDER&lt;/a&gt;  était un intellectuel, marchand et réformateur juif allemand, disciple de Moses Mendelssohn, plus connu comme pionnier de l'Haskalah (Lumières juives) et de la  &lt;a  href="https://www.persee.fr/doc/reval_0035-0974_1973_num_5_3_1989"  title="D Friedlander et la réforme des communaités juives de prusse par Persée"&gt; réforme religieuse &lt;/a&gt; que comme philosophe académique strict. Il prôna l'émancipation des Juifs par l'assimilation culturelle et une dédogmatisation du judaïsme, fusionnant rationalisme des Lumières et monothéisme mosaïque originel contre les rituels "superstitieux". &lt;/p&gt; &lt;p&gt; Né à Königsberg, il s'installa à Berlin en 1770, fonda une usine de soie et intégra l'élite juive éclairée via son mariage avec la fille du banquier Daniel Itzig. Après la mort de Mendelssohn (1786), il mena la Haskalah berlinoise : création de la Chevrat Chinuch Ne’arim (école juive libre en 1778), traductions de prières en allemand, et plaidoyers pour l'égalité civile. Premier conseiller municipal juif à Berlin, il lutta contre les discriminations prussiennes. &lt;/p&gt; &lt;p&gt; Il rejetait le Talmud et les rites comme "œuvres de sainteté, verbiage et futilités", défendant un judaïsme "pur" : monothéisme rationnel commun aux religions abrahamiques, sans dogmes christologiques ni observances contraignantes. Dans son Sendschreiben anonyme (1799) à l'ecclésiastique Wilhelm Teller, il proposa une union judéo-protestante déiste – baptême symbolique sans trinité, en échange d'émancipation –, vu comme opportuniste mais innovant pour le judaïsme réformé naissant. Il resta juif par fidélité au "monothéisme mosaïque idéal", contrairement à sa famille convertie. &lt;/p&gt; &lt;p&gt; Précurseur du judaïsme réformé et de l'assimilation prussienne, Friedländer incarna le dilemme post-mendelssohnien : identité juive face à l'universalisme. Critiqué pour pragmatisme, il influença les réformes liturgiques et débats sur l'émancipation, bien que son projet fusionnel échouât face au romantisme montant. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F80" s="47" t="n"/>
-      <c r="G80" s="49" t="n"/>
-      <c r="H80" s="49" t="inlineStr">
+      <c r="F81" s="47" t="n"/>
+      <c r="G81" s="49" t="n"/>
+      <c r="H81" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/dfriedlander-mini.webp</t>
         </is>
       </c>
-      <c r="I80" s="58" t="inlineStr">
+      <c r="I81" s="58" t="inlineStr">
         <is>
           <t>https://laphilo.fr/photo/dfriedlander.webp</t>
         </is>
       </c>
-      <c r="J80" s="38" t="inlineStr">
+      <c r="J81" s="38" t="inlineStr">
         <is>
           <t>Allemande</t>
         </is>
       </c>
-      <c r="K80" s="45" t="inlineStr">
+      <c r="K81" s="45" t="inlineStr">
         <is>
           <t>ethique ; spiritualite</t>
         </is>
       </c>
-      <c r="L80" s="46" t="inlineStr">
+      <c r="L81" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Rationalisme ; Haskala</t>
         </is>
       </c>
-      <c r="M80" s="35" t="inlineStr">
+      <c r="M81" s="35" t="inlineStr">
         <is>
           <t>philosophe juif allemand plus connu comme pionnier de l'Haskalah.</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t xml:space="preserve">juive</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="157.5" customHeight="1" s="39">
-      <c r="A81" s="47" t="n">
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="157.5" customHeight="1" s="39">
+      <c r="A82" s="47" t="n">
         <v>1753</v>
       </c>
-      <c r="B81" s="47" t="inlineStr">
+      <c r="B82" s="47" t="inlineStr">
         <is>
           <t>1821</t>
         </is>
       </c>
-      <c r="C81" s="47" t="inlineStr">
+      <c r="C82" s="47" t="inlineStr">
         <is>
           <t>1753 – 1821</t>
         </is>
       </c>
-      <c r="D81" s="48" t="inlineStr">
+      <c r="D82" s="48" t="inlineStr">
         <is>
           <t>Joseph de MAISTRE</t>
         </is>
       </c>
-      <c r="E81" s="58" t="inlineStr">
+      <c r="E82" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Joseph_de_Maistre"  title=" Wikipedia"&gt;Joseph de MAISTRE&lt;/a&gt; était un philosophe, écrivain et diplomate savoyard, figure majeure de la contre-révolution et critique virulent des Lumières et de la Révolution française. Considéré comme un père de la pensée conservatrice moderne, il défend une vision organique de la société, hiérarchique et divinement ordonnée, où l'autorité monarchique et religieuse prime sur les idées contractualistes et individualistes. &lt;/p&gt; &lt;p&gt;  Pour lui, la Révolution française est un &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1989_num_1_2_1393" title="Sacré et sacrifice dans la pensée de Joseph de Maistre par Persée"&gt;châtiment providentiel &lt;/a&gt; des excès des philosophes des Lumières, punissant l'athéisme et le rationalisme par la Terreur. Les sociétés ne naissent pas d'un contrat rationnel (comme chez Rousseau), mais d'une autorité divine imposée d'en haut; l'individu abstrait n'existe pas, il est façonné par la tradition et l'État.  Il prône une monarchie absolue et l'autorité suprême du Pape pour unifier l'Europe spirituellement et temporellement. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures sont : "Considérations sur la France" paru en 1797 : Interprétation providentialiste de la Révolution comme mission divine de la France. "Essai sur le principe générateur des constitutions" paru en 1809 :  &lt;a href="https://www.youtube.com/watch?v=oPEzOiEdrNE"  title=" L'oecuménisme de Joseph de Maistre par BAGLIS TV"&gt;Les constitutions &lt;/a&gt; viennent de Dieu, non de la raison humaine et "Soirées de Saint-Pétersbourg"  en1821, posthume : Théodicée justifiant le mal (guerre, sacrifice) comme partie du plan divin. &lt;/p&gt; &lt;p&gt; Il a eu une influence durablement le conservatisme, le romantisme contre-révolutionnaire et des penseurs comme Donoso Cortés, tout en étant critiqué pour son apologie de la violence. Sa pensée hiérarchique et anti-individualiste reste débattue face aux idéaux démocratiques modernes. &lt;/p&gt; &lt;p&gt;  &lt;audio controls title="Troisième penseur, Joseph de Maistre. par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-26.10.2011-ITEMA_20317797-2011C12410S0299-NET_F022382B-0B64-4C5C-B335-284B201C884D_DF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F81" s="47" t="inlineStr">
+      <c r="F82" s="47" t="inlineStr">
         <is>
           <t>suyM7vu194w</t>
         </is>
       </c>
-      <c r="G81" s="49" t="inlineStr">
+      <c r="G82" s="49" t="inlineStr">
         <is>
           <t>"La défense des préjugés contre l’universalisme abstrait (Joseph de Maistre)" par Ego Non</t>
         </is>
       </c>
-      <c r="H81" s="49" t="inlineStr">
+      <c r="H82" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/maistre-mini.webp</t>
         </is>
       </c>
-      <c r="I81" s="49" t="n"/>
-      <c r="J81" s="38" t="inlineStr">
+      <c r="I82" s="49" t="n"/>
+      <c r="J82" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K81" s="45" t="inlineStr">
+      <c r="K82" s="45" t="inlineStr">
         <is>
           <t>politique ; spiritualite</t>
         </is>
       </c>
-      <c r="L81" s="46" t="inlineStr">
+      <c r="L82" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Conservatisme ; Martinisme</t>
         </is>
       </c>
-      <c r="M81" s="35" t="inlineStr">
+      <c r="M82" s="35" t="inlineStr">
         <is>
           <t>philosophe français figure de la contre-révolution &amp; critique des Lumières.</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="148.5" customHeight="1" s="39">
-      <c r="A82" s="47" t="n">
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="148.5" customHeight="1" s="39">
+      <c r="A83" s="47" t="n">
         <v>1754</v>
       </c>
-      <c r="B82" s="47" t="inlineStr">
+      <c r="B83" s="47" t="inlineStr">
         <is>
           <t>1840</t>
         </is>
       </c>
-      <c r="C82" s="47" t="inlineStr">
+      <c r="C83" s="47" t="inlineStr">
         <is>
           <t>1754 – 1840</t>
         </is>
       </c>
-      <c r="D82" s="48" t="inlineStr">
+      <c r="D83" s="48" t="inlineStr">
         <is>
           <t>Louis BONALD</t>
         </is>
       </c>
-      <c r="E82" s="63" t="inlineStr">
+      <c r="E83" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Louis_de_Bonald"  title=" Wikipedia"&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href="https://fr.wikipedia.org/wiki/Tradition_primordiale"  title=" Tradition Primordiale de Maistre par Wikipedia "&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href="https://www.youtube.com/watch?v=WMB9kethTWI"  title=" Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations "&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href="https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral"  title=" Maurrassisme par Wikipedia "&gt; maurrassisme, &lt;a&gt; voyant la France comme "nation-pilote" pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant. &lt;/p&gt;
 //</t>
         </is>
       </c>
-      <c r="F82" s="47" t="inlineStr">
+      <c r="F83" s="47" t="inlineStr">
         <is>
           <t>zJeETVwu1Zo</t>
         </is>
       </c>
-      <c r="G82" s="49" t="inlineStr">
+      <c r="G83" s="49" t="inlineStr">
         <is>
           <t>"L'Homme et la Société (Louis de Bonald)" par Ego Non</t>
         </is>
       </c>
-      <c r="H82" s="49" t="inlineStr">
+      <c r="H83" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/bonald-mini.webp</t>
         </is>
       </c>
-      <c r="I82" s="49" t="n"/>
-      <c r="J82" s="38" t="inlineStr">
+      <c r="I83" s="49" t="n"/>
+      <c r="J83" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K82" s="45" t="inlineStr">
+      <c r="K83" s="45" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="L82" s="46" t="inlineStr">
+      <c r="L83" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">Conservatisme</t>
         </is>
       </c>
-      <c r="M82" s="35" t="inlineStr">
+      <c r="M83" s="35" t="inlineStr">
         <is>
           <t>philosophe et théoricien contre-révolutionnaire français, chef de file du traditionalisme.</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="135" customHeight="1" s="39">
-      <c r="A83" s="34" t="n">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="135" customHeight="1" s="39">
+      <c r="A84" s="34" t="n">
         <v>1754</v>
       </c>
-      <c r="B83" s="34" t="n">
+      <c r="B84" s="34" t="n">
         <v>1836</v>
       </c>
-      <c r="C83" s="34" t="inlineStr">
+      <c r="C84" s="34" t="inlineStr">
         <is>
           <t>1754 – 1836</t>
         </is>
       </c>
-      <c r="D83" s="35" t="inlineStr">
+      <c r="D84" s="35" t="inlineStr">
         <is>
           <t>Destutt de TRACY</t>
         </is>
       </c>
-      <c r="E83" s="35" t="inlineStr">
+      <c r="E84" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine_Destutt_de_Tracy"  title=" Wikipedia"&gt;Destutt de TRACY&lt;/a&gt; était un philosophe et idéologue français, fondateur et théoricien principal du courant philosophique des Idéologues. Né Antoine Louis Claude Destutt, comte de Tracy, dans une famille noble auvergnate, il fit une carrière militaire avant de se consacrer à la philosophie après son emprisonnement pendant la Terreur. Membre de l'Institut national et de l'Académie française, il joua un rôle central dans la vie intellectuelle française sous le Directoire et le Consulat. &lt;/p&gt; &lt;p&gt; Sa contribution majeure est la création de l'« idéologie » comme science des idées. Dans ses &lt;em&gt;&lt;a href="https://www.youtube.com/watch?v=DAz6QsBdeyg"  title="Destrutt de DRACYi par Wikipedia Fan"&gt;Éléments d'idéologie &lt;/a&gt; &lt;/em&gt; (5 volumes, 1801-1815), il cherche à fonder une science générale des idées qui analyserait leur formation à partir des sensations et des signes. S'inscrivant dans la tradition sensualiste de Condillac, il développe une sémiologie et une grammaire générale visant à purifier le langage de ses ambiguïtés et à fonder les sciences humaines sur des bases empiriques solides. Son projet était d'édifier une « science des sciences » qui servirait de fondement à l'enseignement et à la réforme sociale. &lt;/p&gt; &lt;p&gt; Sa &lt;em&gt;Logique&lt;/em&gt; et son &lt;em&gt;Commentaire sur l'Esprit des Lois de Montesquieu&lt;/em&gt; (1811) témoignent de son intérêt pour la philosophie politique libérale. Jefferson, qui admirait sa pensée, fit traduire son &lt;em&gt;Traité de la volonté&lt;/em&gt; en anglais. Ironiquement, le terme même d'« idéologie » qu'il avait forgé fut retourné contre lui par Napoléon, qui qualifiait les Idéologues d'esprits abstraits et dangereux. Marx reprit ensuite ce terme dans un sens radicalement différent. Destutt de Tracy reste une figure essentielle pour comprendre l'émergence des sciences humaines en France. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F83" s="47" t="inlineStr">
+      <c r="F84" s="47" t="inlineStr">
         <is>
           <t>n69ITkX9DMU</t>
         </is>
       </c>
-      <c r="G83" s="49" t="inlineStr">
+      <c r="G84" s="49" t="inlineStr">
         <is>
           <t>« l’influence de Destutt de Tracy » par Ecole de la Liberté</t>
         </is>
       </c>
-      <c r="H83" s="35" t="inlineStr">
+      <c r="H84" s="35" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/destuttdetracy-mini.webp</t>
         </is>
       </c>
-      <c r="J83" s="38" t="inlineStr">
+      <c r="J84" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K83" s="45" t="inlineStr">
+      <c r="K84" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L83" s="46" t="inlineStr">
+      <c r="L84" s="46" t="inlineStr">
         <is>
           <t>Positivisme</t>
         </is>
       </c>
-      <c r="M83" s="35" t="inlineStr">
+      <c r="M84" s="35" t="inlineStr">
         <is>
           <t>philosophe français fondateur du courant philosophique des Idéologues.</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="104.25" customHeight="1" s="39">
-      <c r="A84" s="34" t="n">
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="104.25" customHeight="1" s="39">
+      <c r="A85" s="34" t="n">
         <v>1756</v>
       </c>
-      <c r="B84" s="34" t="n">
+      <c r="B85" s="34" t="n">
         <v>1837</v>
       </c>
-      <c r="C84" s="34" t="inlineStr">
+      <c r="C85" s="34" t="inlineStr">
         <is>
           <t>1756 – 1837</t>
         </is>
       </c>
-      <c r="D84" s="35" t="inlineStr">
+      <c r="D85" s="35" t="inlineStr">
         <is>
           <t>Pierre LAROMIGUIÈRE</t>
         </is>
       </c>
-      <c r="E84" s="35" t="inlineStr">
+      <c r="E85" s="35" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Laromigui%C3%A8re"  title=" Wikipedia"&gt;Pierre LAROMIGUIÈRE&lt;/a&gt; était un philosophe français, l'une des figures transitoires entre le sensualisme des Lumières et la philosophie spiritualiste du XIXe siècle. Né à Livinhac-le-Haut dans l'Aveyron, il fut d'abord prêtre avant la Révolution, puis professeur de philosophie à l'École centrale des arts et manufactures et enfin à la Sorbonne. Ses cours, qui attirèrent un public nombreux et enthousiaste dans les premières décennies du XIXe siècle, contribuèrent à renouveler l'enseignement de la philosophie en France. &lt;/p&gt; &lt;p&gt; Sa philosophie part du sensualisme de Condillac mais s'en écarte sur un point décisif : là où Condillac réduisait toutes les opérations de l'esprit à des sensations transformées, Laromiguière distingue soigneusement les sensations des opérations actives de l'attention, de la comparaison et du jugement. Cette distinction entre les facultés passives et les facultés actives de l'esprit ouvre la voie à une conception plus riche de la vie psychique, qui reconnaît la spécificité de l'activité intellectuelle irréductible à la simple réception sensorielle. &lt;/p&gt; &lt;p&gt; Dans ses &lt;em&gt;Leçons de philosophie&lt;/em&gt; (1815-1818), dont la clarté et l'agrément du style lui valurent un succès durable, il développe cette psychologie des facultés dans un cadre pédagogique accessible. Bien que sa pensée ait été éclipsée par le courant spiritualiste de Cousin et par le positivisme de Comte, Laromiguière représente une étape importante dans la constitution de la psychologie philosophique française. Sa manière de corriger Condillac par une attention accrue à l'activité de l'esprit préfigure les développements du spiritualisme ultérieur. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F84" s="47" t="inlineStr">
+      <c r="F85" s="47" t="inlineStr">
         <is>
           <t>STOo4oShj2g</t>
         </is>
       </c>
-      <c r="G84" s="49" t="inlineStr">
+      <c r="G85" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Pierre LAROMIGUIERE  par VIS PHILO </t>
         </is>
       </c>
-      <c r="H84" s="35" t="inlineStr">
+      <c r="H85" s="35" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/laromiguiere-mini.webp</t>
         </is>
       </c>
-      <c r="J84" s="38" t="inlineStr">
+      <c r="J85" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K84" s="45" t="inlineStr">
+      <c r="K85" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L84" s="46" t="inlineStr">
+      <c r="L85" s="46" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="M84" s="35" t="inlineStr">
+      <c r="M85" s="35" t="inlineStr">
         <is>
           <t>philosophe français connu pour avoir réformé la psychologie rationnelle.</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="109.5" customHeight="1" s="39">
-      <c r="A85" s="34" t="n">
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="109.5" customHeight="1" s="39">
+      <c r="A86" s="34" t="n">
         <v>1757</v>
       </c>
-      <c r="B85" s="34" t="n">
+      <c r="B86" s="34" t="n">
         <v>1808</v>
       </c>
-      <c r="C85" s="34" t="inlineStr">
+      <c r="C86" s="34" t="inlineStr">
         <is>
           <t>1757 – 1808</t>
         </is>
       </c>
-      <c r="D85" s="35" t="inlineStr">
+      <c r="D86" s="35" t="inlineStr">
         <is>
           <t>Pierre CABANIS</t>
         </is>
       </c>
-      <c r="E85" s="65" t="inlineStr">
+      <c r="E86" s="65" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Jean_Georges_Cabanis" title=" Wikipedia"&gt;Pierre CABANIS&lt;/a&gt; était un médecin et philosophe français, figure majeure du groupe des Idéologues et pionnier d'une approche naturaliste de la vie psychique. Né à Cosnac en Corrèze, il fut introduit dans les cercles intellectuels parisiens par Turgot et fréquenta le salon d'Helvétius. Ami intime de Mirabeau dont il soigna les derniers jours, il participa activement à la vie politique de la Révolution et du Directoire, siégeant au Conseil des Cinq-Cents. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;Rapports du physique et du moral de l'homme&lt;/em&gt; (1802), est un essai audacieux pour fonder une science de l'homme sur des bases physiologiques. Cabanis y soutient que les phénomènes psychiques sont intimement liés aux processus organiques du corps : le cerveau secrète la pensée comme le foie sécrète la bile. Cette formule provocatrice, souvent mal comprise, visait en réalité à établir une méthode empirique pour l'étude de l'âme, refusant tout recours à des entités métaphysiques abstraites. &lt;/p&gt; &lt;p&gt; Médecin réformateur, il œuvra à la réorganisation des hôpitaux parisiens et milita pour une médecine fondée sur l'observation clinique plutôt que sur les théories scolastiques. Ses travaux contribuèrent à l'essor de l'hygiénisme et de la médecine sociale. Sa pensée, qui anticipe certains aspects du matérialisme médical du XIXe siècle, représente une étape importante dans la constitution des sciences humaines. Bien que les Idéologues aient été rabroués par Napoléon qui les rendait responsables des « idéologues abstraits », l'influence de Cabanis sur la médecine et la psychologie françaises fut durable. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F85" s="34" t="inlineStr">
+      <c r="F86" s="34" t="inlineStr">
         <is>
           <t>7JWvo6-4cjA</t>
         </is>
       </c>
-      <c r="G85" s="64" t="inlineStr">
+      <c r="G86" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">« Pierre Jean Georges Cabanis » par  Everything Philosophers </t>
         </is>
       </c>
-      <c r="H85" s="35" t="inlineStr">
+      <c r="H86" s="35" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/cabanis-mini.webp</t>
         </is>
       </c>
-      <c r="J85" s="38" t="inlineStr">
+      <c r="J86" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K85" s="45" t="inlineStr">
+      <c r="K86" s="45" t="inlineStr">
         <is>
           <t>epistemologie</t>
         </is>
       </c>
-      <c r="L85" s="46" t="inlineStr">
+      <c r="L86" s="46" t="inlineStr">
         <is>
           <t>Matérialisme ; Épiphénoménisme</t>
         </is>
       </c>
-      <c r="M85" s="35" t="inlineStr">
+      <c r="M86" s="35" t="inlineStr">
         <is>
           <t>philosophe figure majeure du matérialisme et de l'idéologie de la Révolution française.</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="135.75" customHeight="1" s="39">
-      <c r="A86" s="47" t="n">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="135.75" customHeight="1" s="39">
+      <c r="A87" s="47" t="n">
         <v>1763</v>
       </c>
-      <c r="B86" s="47" t="inlineStr">
+      <c r="B87" s="47" t="inlineStr">
         <is>
           <t>1845</t>
         </is>
       </c>
-      <c r="C86" s="47" t="inlineStr">
+      <c r="C87" s="47" t="inlineStr">
         <is>
           <t>1763 – 1845</t>
         </is>
       </c>
-      <c r="D86" s="48" t="inlineStr">
+      <c r="D87" s="48" t="inlineStr">
         <is>
           <t>Pierre-Paul ROYER-COLLARD</t>
         </is>
       </c>
-      <c r="E86" s="50" t="inlineStr">
+      <c r="E87" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre-Paul_Royer-Collard"  title=" Wikipedia"&gt;Pierre-Paul ROYER-COLLARD&lt;/a&gt;  était un philosophe et homme politique français, figure majeure du libéralisme modéré sous la Restauration et chef des Doctrinaires. Né en Champagne, il commence comme avocat au Parlement de Paris avant de s'engager politiquement. Pendant la Révolution, il soutient les Girondins et fuit la Terreur, se retirant dans ses terres. Sous la Restauration, il devient député de la Marne et préside la Chambre des députés (1828–1830), tout en enseignant l'histoire de la philosophie moderne à la Sorbonne. &lt;/p&gt; &lt;p&gt; Sa philosophie se présente comme un rejet du sensualisme de Condillac qui dominait le XVIIIᵉ siècle français. Il s'inspire du philosophe écossais Thomas Reid et introduit en France la doctrine du sens commun. Contrairement aux sensualistes, il distingue clairement la sensation (subjective, plaisir ou peine) de la perception (appréhension d'un objet externe). Pour lui, la perception implique un jugement spontané de l'esprit actif, non déductible des seuls sens. &lt;/p&gt; &lt;p&gt; Il développe un spiritualisme rigoureux : l'esprit humain est actif et capable de jugements autonomes. Le sens commun – cette faculté naturelle de distinguer le bien du mal, le vrai du faux – fonde la vie communautaire et remplace l'autorité surnaturelle. Par les principes de causalité et d'induction, la raison conduit nécessairement à l'idée d'une Première Cause (Dieu). Il affirme la supériorité irréductible de la personne humaine sur l'État, les personnes étant &lt;a  href="https://www.youtube.com/watch?v=15bNqKMiW_w"  title="R Collard ou l’ambilalence des restaurations par Collège st Germain"&gt;« faites à l'image de Dieu et douées d'immortalité ».&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Politiquement, il est un royaliste libéral qui considère la Révolution de 1789 comme irréversible. Il cherche à fonder une monarchie constitutionnelle stable entre l'Ancien Régime (les Ultras) et le totalitarisme napoléonien, puis la démocratisation trop rapide sous Louis-Philippe. Il incarne la « philosophie de la Charte » et influence profondément François Guizot. N'a presque rien publié de son vivant : ses écrits philosophiques ont été rassemblés après coup par son admirateur Théodore Jouffroy.  &lt;/p&gt; </t>
         </is>
       </c>
-      <c r="F86" s="66" t="inlineStr">
+      <c r="F87" s="66" t="inlineStr">
         <is>
           <t>_6oY2zBA5lQ</t>
         </is>
       </c>
-      <c r="G86" s="67" t="inlineStr">
+      <c r="G87" s="67" t="inlineStr">
         <is>
           <t>"Pierre Paul Royer-Collard: Unleashing Mathematical Genius" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H86" s="58" t="inlineStr">
+      <c r="H87" s="58" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/pcollard-mini.webp</t>
         </is>
       </c>
-      <c r="I86" s="49" t="n"/>
-      <c r="J86" s="38" t="inlineStr">
+      <c r="I87" s="49" t="n"/>
+      <c r="J87" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K86" s="45" t="inlineStr">
+      <c r="K87" s="45" t="inlineStr">
         <is>
           <t>epistemologie ; politique</t>
         </is>
       </c>
-      <c r="L86" s="46" t="inlineStr">
+      <c r="L87" s="46" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="M86" s="35" t="inlineStr">
+      <c r="M87" s="35" t="inlineStr">
         <is>
           <t>philosophe français figure majeure du libéralisme modéré.</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="317.25" customFormat="1" customHeight="1" s="38">
-      <c r="A87" s="38" t="n">
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="317.25" customFormat="1" customHeight="1" s="38">
+      <c r="A88" s="38" t="n">
         <v>1760</v>
       </c>
-      <c r="B87" s="38" t="n">
+      <c r="B88" s="38" t="n">
         <v>1825</v>
       </c>
-      <c r="C87" s="38" t="inlineStr">
+      <c r="C88" s="38" t="inlineStr">
         <is>
           <t>1760 – 1825</t>
         </is>
       </c>
-      <c r="D87" s="38" t="inlineStr">
+      <c r="D88" s="38" t="inlineStr">
         <is>
           <t>Henri de SAINT-SIMON</t>
         </is>
       </c>
-      <c r="E87" s="45" t="inlineStr">
+      <c r="E88" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Claude-Henri_de_Rouvroy_de_Saint-Simon" title=" Wikipedia"&gt;Claude-Henri de ROUVROY, comte de SAINT-SIMON&lt;/a&gt; est un penseur et réformateur social français, issu d’une famille aristocratique qui revendiquait une lointaine parenté avec Charlemagne. Volontaire dans l’armée française envoyée soutenir l’indépendance américaine, il participe au siège de Yorktown avant de renoncer, sous la Révolution, à son titre de noblesse.  &lt;a href="https://maitron.fr/saint-simon-claude-henri-claude-henri-de-rouvroy-comte-de-saint-simon/" title="saint simon par le maitron"&gt;Spéculateur &lt;/a&gt; sur les biens nationaux, emprisonné pendant la Terreur, il connaît ensuite une vie mouvementée, tour à tour fortunée et misérable, entièrement vouée à la recherche d’une science nouvelle de la société. &lt;/p&gt; &lt;p&gt; Convaincu que la Révolution a détruit l’ancien ordre théologique et féodal sans encore bâtir l’ordre qui doit lui succéder, Saint-Simon appelle à fonder une organisation sociale confiée non plus aux militaires, aux juristes ou aux rentiers, mais aux savants, aux industriels et aux producteurs. Dans des ouvrages comme &lt;em&gt;L’Industrie&lt;/em&gt; ou &lt;em&gt;Du système industriel&lt;/em&gt;, il défend l’idée que le pouvoir politique doit être subordonné à la production utile : gouverner, pour lui, revient d’abord à administrer les choses et à organiser le travail, plutôt qu’à commander les hommes. &lt;/p&gt; &lt;p&gt; Il élabore ainsi une &lt;a href="https://fr.wikipedia.org/wiki/Saint-simonisme" title="Saint-simonisme par Wikipedia"&gt;philosophie de l’histoire&lt;/a&gt; fondée sur l’alternance de périodes « organiques » et « critiques », et annonce l’avènement d’un âge industriel où la science et la technique remplaceraient la théologie comme principe d’unité sociale. Son dernier livre, &lt;em&gt;Le Nouveau Christianisme&lt;/em&gt; (1825), publié l’année de sa mort, prône une religion de la fraternité entièrement tournée vers l’amélioration du sort des classes les plus pauvres, qu’il présente comme la fin ultime de toute organisation sociale et politique légitime. &lt;/p&gt; &lt;p&gt; Bien que ses écrits soient souvent fragmentaires et inachevés, Saint-Simon laisse une postérité considérable : ses disciples, réunis après sa mort en une école puis en une véritable Église saint-simonienne, diffusent et systématisent sa pensée sous le nom de saint-simonisme. Ce courant influencera profondément le socialisme utopique du XIXe siècle, la sociologie naissante d’Auguste Comte (un temps son secrétaire), ainsi que les grandes entreprises industrielles et financières du Second Empire, qui reprendront à leur compte son culte du progrès technique et de l’organisation rationnelle de la production. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F87" s="38" t="inlineStr">
+      <c r="F88" s="38" t="inlineStr">
         <is>
           <t>82O6eO6UQqY</t>
         </is>
       </c>
-      <c r="G87" s="45" t="inlineStr">
+      <c r="G88" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">saint simon – transformer la société par Thérence Carvalho</t>
         </is>
       </c>
-      <c r="H87" s="45" t="inlineStr">
+      <c r="H88" s="45" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/hssimon-mini.webp</t>
         </is>
       </c>
-      <c r="J87" s="45" t="inlineStr">
+      <c r="J88" s="45" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K87" s="45" t="inlineStr">
+      <c r="K88" s="45" t="inlineStr">
         <is>
           <t>politique</t>
         </is>
       </c>
-      <c r="L87" s="45" t="inlineStr">
+      <c r="L88" s="45" t="inlineStr">
         <is>
           <t>Saint-Simonisme</t>
         </is>
       </c>
-      <c r="M87" s="45" t="inlineStr">
+      <c r="M88" s="45" t="inlineStr">
         <is>
           <t>penseur et réformateur social français, fondateur du saint-simonisme.</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="130.5" customHeight="1" s="39">
-      <c r="A88" s="47" t="n">
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="130.5" customHeight="1" s="39">
+      <c r="A89" s="47" t="n">
         <v>1766</v>
       </c>
-      <c r="B88" s="47" t="inlineStr">
+      <c r="B89" s="47" t="inlineStr">
         <is>
           <t>1824</t>
         </is>
       </c>
-      <c r="C88" s="47" t="inlineStr">
+      <c r="C89" s="47" t="inlineStr">
         <is>
           <t>1766 – 1824</t>
         </is>
       </c>
-      <c r="D88" s="48" t="inlineStr">
+      <c r="D89" s="48" t="inlineStr">
         <is>
           <t>Maine de BIRAN</t>
         </is>
       </c>
-      <c r="E88" s="68" t="inlineStr">
+      <c r="E89" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maine_de_Biran"  title=" Wikipedia"&gt;Maine de BIRAN&lt;/a&gt; était un philosophe français, considéré comme l'un des fondateurs de la philosophie de l'intériorité et du spiritualisme français. Né François-Pierre Gonthier de Biran à Bergerac en Dordogne, il commença sa carrière comme officier de la garde du roi, avant de se consacrer à la philosophie et à la vie politique locale en Périgord. Administrateur apprécié sous plusieurs régimes successifs, il fut député et sous-préfet, mais c'est à travers ses journaux intimes et ses &lt;a  href="https://www.youtube.com/watch?v=ayhmQ5WQfJk"  title="Maine de Biran spiritualité &amp; phénoménologie par ICP"&gt;essais philosophiques &lt;/a&gt; que son originalité s'exprima pleinement. &lt;/p&gt; &lt;p&gt; Sa pensée prend pour point de départ l'expérience immédiate de l'effort : c'est dans l'acte volontaire par lequel le moi exerce une résistance contre le corps propre que la conscience se saisit elle-même comme force et comme liberté. Contre le sensualisme de Condillac qui réduisait l'âme à la sensation passive, il soutient que l'activité volontaire constitue le fait primitif de la conscience. Cette découverte du « moi voulant » comme donnée irréductible de l'intériorité marque une rupture décisive dans la philosophie française. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;t &lt;a  href="https://www.persee.fr/doc/bupsy_0007-4403_1963_num_17_224_9102"  title="Maine de Biran fondateur de la psychologie française par Persée"&gt;Essai sur les fondements de la psychologie &lt;/a&gt; &lt;/em&gt; (1812) et ses nombreux &lt;em&gt;Mémoires&lt;/em&gt; rédigés pour les concours de l'Institut, développent une psychologie de l'effort qui distingue trois ordres d'existence : la vie animale (sensations), la vie humaine (volonté et conscience) et la vie de l'esprit (grâce et amour mystique). Cette trilogie, d'inspiration néo-platonicienne et chrétienne dans sa dernière phase, influença profondément Ravaisson, Bergson et tout le courant spiritualiste français. Ses &lt;em&gt;Journal&lt;/em&gt; et &lt;em&gt;Mémoire sur les perceptions obscures&lt;/em&gt; témoignent d'une introspection d'une subtilité et d'une profondeur rares. &lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F88" s="66" t="inlineStr">
+      <c r="F89" s="66" t="inlineStr">
         <is>
           <t>e6lHF0weqtA</t>
         </is>
       </c>
-      <c r="G88" s="67" t="inlineStr">
+      <c r="G89" s="67" t="inlineStr">
         <is>
           <t>"Maine de Biran: Exploring the Human Mind" par VIS PHILO</t>
         </is>
       </c>
-      <c r="H88" s="49" t="inlineStr">
+      <c r="H89" s="49" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mbiran-mini.webp</t>
         </is>
       </c>
-      <c r="I88" s="49" t="n"/>
-      <c r="J88" s="38" t="inlineStr">
+      <c r="I89" s="49" t="n"/>
+      <c r="J89" s="38" t="inlineStr">
         <is>
           <t>Française</t>
         </is>
       </c>
-      <c r="K88" s="45" t="inlineStr">
+      <c r="K89" s="45" t="inlineStr">
         <is>
           <t>metaphysique ; epistemologie</t>
         </is>
       </c>
-      <c r="L88" s="46" t="inlineStr">
+      <c r="L89" s="46" t="inlineStr">
         <is>
           <t>Spiritualisme</t>
         </is>
       </c>
-      <c r="M88" s="35" t="inlineStr">
+      <c r="M89" s="35" t="inlineStr">
         <is>
           <t>philosophe français fondateur de la philosophie de l'intériorité et du spiritualisme.</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="130.5" customHeight="1" s="39">
-      <c r="A89" s="47">
-        <v>1565</v>
-      </c>
-      <c r="B89" s="47">
-        <v>1645</v>
-      </c>
-      <c r="C89" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1565 - 1645</t>
-        </is>
-      </c>
-      <c r="D89" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marie de GOURNAY</t>
-        </is>
-      </c>
-      <c r="E89" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marie_de_Gournay"  title=" Wikipedia"&gt;Marie de GOURNAY&lt;/a&gt; (1565-1645) est une femme de lettres et philosophe française. Autodidacte, elle apprit seule le latin et découvrit adolescente les &lt;em&gt;Essais&lt;/em&gt; de Montaigne, qui la bouleversèrent. Elle rencontra l'auteur en 1588 et devint sa « fille d'alliance », une amitié intellectuelle profonde.&lt;/p&gt; &lt;p&gt;Après la mort de Montaigne, sa veuve lui confia le manuscrit annoté des &lt;em&gt;Essais&lt;/em&gt;. Marie de Gournay consacra une grande partie de sa vie à en préparer les éditions, dont celle de 1595, qui a fait autorité pendant des siècles. Elle vécut de sa plume, chose très rare pour une femme de son époque, et fréquenta les milieux savants de Paris, où elle fut souvent moquée pour son indépendance.&lt;/p&gt; &lt;p&gt;Marie de Gournay s'intéressa aussi à la langue française, qu'elle défendit contre les réformes de Malherbe qui voulaient l'appauvrir selon elle, et publia un recueil de ses œuvres sous le titre &lt;em&gt;L'Ombre de la demoiselle de Gournay&lt;/em&gt; (1626), puis &lt;em&gt;Les Advis ou les Présens&lt;/em&gt; (1634). Elle y traite de l'éducation des princes, de la poésie, de la calomnie et de la condition des femmes savantes, qu'on ridiculisait pour mieux les écarter.&lt;/p&gt; &lt;p&gt;Elle est surtout connue pour deux textes pionniers : &lt;em&gt;Égalité des hommes et des femmes&lt;/em&gt; (1622) et &lt;em&gt;Grief des dames&lt;/em&gt; (1626). Elle y soutient que la différence entre hommes et femmes ne tient pas à la nature mais à l'éducation, et que « l'animal humain n'est ni homme ni femme » par l'âme. Elle s'appuie sur la Bible, les Pères de l'Église et les philosophes antiques pour montrer que rien ne justifie l'exclusion des femmes du savoir. Elle est considérée comme l'une des premières penseuses de l'égalité des sexes.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J89" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Française</t>
-        </is>
-      </c>
-      <c r="K89" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethique ; politique</t>
-        </is>
-      </c>
-      <c r="L89" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Humanisme ; Féminisme</t>
-        </is>
-      </c>
-      <c r="M89" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme de lettres française, « fille d'alliance » de Montaigne et pionnière de la défense de l'égalité des sexes.</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6592,44 +6605,44 @@
     </row>
     <row r="90" ht="130.5" customHeight="1" s="39">
       <c r="A90" s="47">
-        <v>1618</v>
+        <v>1565</v>
       </c>
       <c r="B90" s="47">
-        <v>1680</v>
+        <v>1645</v>
       </c>
       <c r="C90" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618 - 1680</t>
+          <t xml:space="preserve">1565 - 1645</t>
         </is>
       </c>
       <c r="D90" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ÉLISABETH de Bohême</t>
+          <t xml:space="preserve">Marie de GOURNAY</t>
         </is>
       </c>
       <c r="E90" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Élisabeth_de_Bohême_(1618-1680)"  title=" Wikipedia"&gt;ÉLISABETH de Bohême&lt;/a&gt; (1618-1680), princesse palatine, était la fille de Frédéric V, l'éphémère « roi d'hiver » de Bohême, chassé de son trône au début de la guerre de Trente Ans. Elle grandit en exil aux Pays-Bas, où elle reçut une éducation très poussée en langues, mathématiques et philosophie.&lt;/p&gt; &lt;p&gt;Elle est célèbre pour sa correspondance avec René Descartes, commencée en 1643. Dès sa première lettre, elle lui pose une question redoutable : si l'âme est une substance pensante, sans étendue, comment peut-elle mettre en mouvement le corps, qui est une chose étendue ? Descartes eut beaucoup de mal à lui répondre, et cette objection reste au cœur de ce que l'on appelle aujourd'hui le problème de l'esprit et du corps.&lt;/p&gt; &lt;p&gt;La correspondance entre Élisabeth et Descartes, qui dura jusqu'à la mort du philosophe en 1650, compte une soixantaine de lettres. On y voit la princesse contester, avec politesse mais fermeté, plusieurs points de la doctrine cartésienne, et proposer ses propres solutions, par exemple sur la manière dont l'âme peut être affectée par la maladie du corps. Descartes lui-même reconnaissait qu'elle était la personne qui comprenait le mieux sa philosophie.&lt;/p&gt; &lt;p&gt;Leurs échanges portèrent aussi sur les passions, la vertu, le bonheur et la politique : c'est pour elle que Descartes écrivit son &lt;em&gt;Traité des passions de l'âme&lt;/em&gt;, et il lui dédia ses &lt;em&gt;Principes de la philosophie&lt;/em&gt;. Élisabeth y défend une morale attentive aux réalités de la vie et du corps. Elle devint ensuite abbesse de l'abbaye protestante de Herford, en Allemagne, où elle accueillit des penseurs persécutés. Elle est aujourd'hui reconnue comme une philosophe à part entière, et non plus seulement comme une correspondante de Descartes.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marie_de_Gournay"  title=" Wikipedia"&gt;Marie de GOURNAY&lt;/a&gt; (1565-1645) est une femme de lettres et philosophe française. Autodidacte, elle apprit seule le latin et découvrit adolescente les &lt;em&gt;Essais&lt;/em&gt; de Montaigne, qui la bouleversèrent. Elle rencontra l'auteur en 1588 et devint sa « fille d'alliance », une amitié intellectuelle profonde.&lt;/p&gt; &lt;p&gt;Après la mort de Montaigne, sa veuve lui confia le manuscrit annoté des &lt;em&gt;Essais&lt;/em&gt;. Marie de Gournay consacra une grande partie de sa vie à en préparer les éditions, dont celle de 1595, qui a fait autorité pendant des siècles. Elle vécut de sa plume, chose très rare pour une femme de son époque, et fréquenta les milieux savants de Paris, où elle fut souvent moquée pour son indépendance.&lt;/p&gt; &lt;p&gt;Marie de Gournay s'intéressa aussi à la langue française, qu'elle défendit contre les réformes de Malherbe qui voulaient l'appauvrir selon elle, et publia un recueil de ses œuvres sous le titre &lt;em&gt;L'Ombre de la demoiselle de Gournay&lt;/em&gt; (1626), puis &lt;em&gt;Les Advis ou les Présens&lt;/em&gt; (1634). Elle y traite de l'éducation des princes, de la poésie, de la calomnie et de la condition des femmes savantes, qu'on ridiculisait pour mieux les écarter.&lt;/p&gt; &lt;p&gt;Elle est surtout connue pour deux textes pionniers : &lt;em&gt;Égalité des hommes et des femmes&lt;/em&gt; (1622) et &lt;em&gt;Grief des dames&lt;/em&gt; (1626). Elle y soutient que la différence entre hommes et femmes ne tient pas à la nature mais à l'éducation, et que « l'animal humain n'est ni homme ni femme » par l'âme. Elle s'appuie sur la Bible, les Pères de l'Église et les philosophes antiques pour montrer que rien ne justifie l'exclusion des femmes du savoir. Elle est considérée comme l'une des premières penseuses de l'égalité des sexes.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J90" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allemande</t>
+          <t xml:space="preserve">Française</t>
         </is>
       </c>
       <c r="K90" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; ethique</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L90" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartésianisme</t>
+          <t xml:space="preserve">Humanisme ; Féminisme</t>
         </is>
       </c>
       <c r="M90" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">princesse palatine dont la correspondance avec Descartes pose le problème de l'union de l'âme et du corps.</t>
+          <t xml:space="preserve">femme de lettres française, « fille d'alliance » de Montaigne et pionnière de la défense de l'égalité des sexes.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6641,51 +6654,48 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
-      </c>
-      <c r="P90">
-        <v>2</v>
       </c>
     </row>
     <row r="91" ht="130.5" customHeight="1" s="39">
       <c r="A91" s="47">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="B91" s="47">
-        <v>1673</v>
+        <v>1680</v>
       </c>
       <c r="C91" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623 - 1673</t>
+          <t xml:space="preserve">1618 - 1680</t>
         </is>
       </c>
       <c r="D91" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margaret CAVENDISH</t>
+          <t xml:space="preserve">ÉLISABETH de Bohême</t>
         </is>
       </c>
       <c r="E91" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Margaret_Cavendish"  title=" Wikipedia"&gt;Margaret CAVENDISH&lt;/a&gt; (1623-1673), duchesse de Newcastle, est une philosophe, poétesse et romancière anglaise. Pendant la guerre civile anglaise, elle suivit la reine en exil à Paris, où elle épousa William Cavendish et fréquenta, grâce à lui, des penseurs comme Hobbes, Descartes et Gassendi.&lt;/p&gt; &lt;p&gt;Elle publia sous son propre nom une douzaine d'ouvrages de philosophie naturelle, ce qui était presque impensable pour une femme de son temps. Elle y développe une philosophie matérialiste et vitaliste : la nature entière est faite d'une seule matière, mais cette matière est douée de mouvement, de perception et même de raison. Elle critique à la fois le mécanisme de Descartes et de Hobbes, et la science expérimentale de la Royal Society, qui prétendait connaître la nature grâce aux microscopes.&lt;/p&gt; &lt;p&gt;Cavendish réfléchit aussi à la condition des femmes, qu'elle juge tenues à l'écart du savoir et du pouvoir par la coutume plutôt que par la nature. Dans ses préfaces, elle revendique ouvertement le désir de gloire et de reconnaissance, ce qui choquait ses contemporains. Ses &lt;em&gt;Observations sur la philosophie expérimentale&lt;/em&gt; (1666) contiennent l'une des premières critiques philosophiques de la confiance aveugle dans les instruments scientifiques.&lt;/p&gt; &lt;p&gt;En 1667, elle fut la première femme invitée à assister à une séance de la Royal Society de Londres. Son récit &lt;em&gt;Le Monde glorieux&lt;/em&gt; (&lt;em&gt;The Blazing World&lt;/em&gt;, 1666), où une femme devient impératrice d'un monde imaginaire peuplé de savants animaux, est souvent considéré comme l'un des premiers romans de science-fiction. Surnommée « Mad Madge » par ses contemporains, elle est aujourd'hui redécouverte comme une philosophe originale et audacieuse.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Élisabeth_de_Bohême_(1618-1680)"  title=" Wikipedia"&gt;ÉLISABETH de Bohême&lt;/a&gt; (1618-1680), princesse palatine, était la fille de Frédéric V, l'éphémère « roi d'hiver » de Bohême, chassé de son trône au début de la guerre de Trente Ans. Elle grandit en exil aux Pays-Bas, où elle reçut une éducation très poussée en langues, mathématiques et philosophie.&lt;/p&gt; &lt;p&gt;Elle est célèbre pour sa correspondance avec René Descartes, commencée en 1643. Dès sa première lettre, elle lui pose une question redoutable : si l'âme est une substance pensante, sans étendue, comment peut-elle mettre en mouvement le corps, qui est une chose étendue ? Descartes eut beaucoup de mal à lui répondre, et cette objection reste au cœur de ce que l'on appelle aujourd'hui le problème de l'esprit et du corps.&lt;/p&gt; &lt;p&gt;La correspondance entre Élisabeth et Descartes, qui dura jusqu'à la mort du philosophe en 1650, compte une soixantaine de lettres. On y voit la princesse contester, avec politesse mais fermeté, plusieurs points de la doctrine cartésienne, et proposer ses propres solutions, par exemple sur la manière dont l'âme peut être affectée par la maladie du corps. Descartes lui-même reconnaissait qu'elle était la personne qui comprenait le mieux sa philosophie.&lt;/p&gt; &lt;p&gt;Leurs échanges portèrent aussi sur les passions, la vertu, le bonheur et la politique : c'est pour elle que Descartes écrivit son &lt;em&gt;Traité des passions de l'âme&lt;/em&gt;, et il lui dédia ses &lt;em&gt;Principes de la philosophie&lt;/em&gt;. Élisabeth y défend une morale attentive aux réalités de la vie et du corps. Elle devint ensuite abbesse de l'abbaye protestante de Herford, en Allemagne, où elle accueillit des penseurs persécutés. Elle est aujourd'hui reconnue comme une philosophe à part entière, et non plus seulement comme une correspondante de Descartes.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J91" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Britannique</t>
+          <t xml:space="preserve">Allemande</t>
         </is>
       </c>
       <c r="K91" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">metaphysique ; ethique</t>
         </is>
       </c>
       <c r="L91" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matérialisme</t>
+          <t xml:space="preserve">Cartésianisme</t>
         </is>
       </c>
       <c r="M91" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe anglaise, penseuse matérialiste de la nature et autrice de l'un des premiers romans de science-fiction.</t>
+          <t xml:space="preserve">princesse palatine dont la correspondance avec Descartes pose le problème de l'union de l'âme et du corps.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6697,28 +6707,31 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
+      </c>
+      <c r="P91">
+        <v>2</v>
       </c>
     </row>
     <row r="92" ht="130.5" customHeight="1" s="39">
       <c r="A92" s="47">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="B92" s="47">
-        <v>1679</v>
+        <v>1673</v>
       </c>
       <c r="C92" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631 - 1679</t>
+          <t xml:space="preserve">1623 - 1673</t>
         </is>
       </c>
       <c r="D92" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anne CONWAY</t>
+          <t xml:space="preserve">Margaret CAVENDISH</t>
         </is>
       </c>
       <c r="E92" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Conway"  title=" Wikipedia"&gt;Anne CONWAY&lt;/a&gt; (1631-1679) est une philosophe anglaise, proche du groupe des platoniciens de Cambridge. Souffrant toute sa vie de violentes migraines, elle reçut une éducation principalement par correspondance, notamment avec le philosophe Henry More, qui devint son ami et son maître.&lt;/p&gt; &lt;p&gt;Son unique ouvrage, les &lt;em&gt;Principes de la plus ancienne et de la plus moderne philosophie&lt;/em&gt;, fut publié après sa mort, en latin en 1690, puis en anglais. Elle y rejette le dualisme de Descartes, qui sépare l'esprit et la matière, et le matérialisme de Hobbes et de Spinoza. Pour elle, tout ce qui existe est à la fois esprit et corps à des degrés divers : la matière n'est qu'un esprit « épaissi », et toutes les créatures, même les pierres, sont vivantes et capables de se perfectionner.&lt;/p&gt; &lt;p&gt;Sa philosophie répond aussi à une question personnelle : comment donner un sens à la douleur ? Pour Anne Conway, la souffrance n'est pas un châtiment arbitraire mais un moyen de purification, qui permet à chaque créature de se rapprocher de Dieu. Aucune créature n'est condamnée pour toujours : toutes sont appelées à progresser vers le bien, ce qui fait de sa pensée l'une des plus optimistes de son temps.&lt;/p&gt; &lt;p&gt;Anne Conway propose une vision d'un monde en constante évolution vers le bien, où la souffrance a un sens puisqu'elle aide les êtres à progresser. Influencée par la kabbale et par les quakers, qu'elle rejoignit à la fin de sa vie, elle eut une influence directe sur Leibniz, qui la cite et lui emprunta sans doute l'idée de « monade ». Longtemps oubliée, elle est aujourd'hui considérée comme l'une des philosophes les plus originales du XVIIe siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Margaret_Cavendish"  title=" Wikipedia"&gt;Margaret CAVENDISH&lt;/a&gt; (1623-1673), duchesse de Newcastle, est une philosophe, poétesse et romancière anglaise. Pendant la guerre civile anglaise, elle suivit la reine en exil à Paris, où elle épousa William Cavendish et fréquenta, grâce à lui, des penseurs comme Hobbes, Descartes et Gassendi.&lt;/p&gt; &lt;p&gt;Elle publia sous son propre nom une douzaine d'ouvrages de philosophie naturelle, ce qui était presque impensable pour une femme de son temps. Elle y développe une philosophie matérialiste et vitaliste : la nature entière est faite d'une seule matière, mais cette matière est douée de mouvement, de perception et même de raison. Elle critique à la fois le mécanisme de Descartes et de Hobbes, et la science expérimentale de la Royal Society, qui prétendait connaître la nature grâce aux microscopes.&lt;/p&gt; &lt;p&gt;Cavendish réfléchit aussi à la condition des femmes, qu'elle juge tenues à l'écart du savoir et du pouvoir par la coutume plutôt que par la nature. Dans ses préfaces, elle revendique ouvertement le désir de gloire et de reconnaissance, ce qui choquait ses contemporains. Ses &lt;em&gt;Observations sur la philosophie expérimentale&lt;/em&gt; (1666) contiennent l'une des premières critiques philosophiques de la confiance aveugle dans les instruments scientifiques.&lt;/p&gt; &lt;p&gt;En 1667, elle fut la première femme invitée à assister à une séance de la Royal Society de Londres. Son récit &lt;em&gt;Le Monde glorieux&lt;/em&gt; (&lt;em&gt;The Blazing World&lt;/em&gt;, 1666), où une femme devient impératrice d'un monde imaginaire peuplé de savants animaux, est souvent considéré comme l'un des premiers romans de science-fiction. Surnommée « Mad Madge » par ses contemporains, elle est aujourd'hui redécouverte comme une philosophe originale et audacieuse.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J92" s="38" t="inlineStr">
@@ -6728,17 +6741,17 @@
       </c>
       <c r="K92" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="L92" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Néoplatonisme</t>
+          <t xml:space="preserve">Matérialisme</t>
         </is>
       </c>
       <c r="M92" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe anglaise, penseuse d'un monde fait d'un seul esprit vivant, qui influença Leibniz.</t>
+          <t xml:space="preserve">philosophe anglaise, penseuse matérialiste de la nature et autrice de l'un des premiers romans de science-fiction.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6754,24 +6767,24 @@
     </row>
     <row r="93" ht="130.5" customHeight="1" s="39">
       <c r="A93" s="47">
-        <v>1666</v>
+        <v>1631</v>
       </c>
       <c r="B93" s="47">
-        <v>1731</v>
+        <v>1679</v>
       </c>
       <c r="C93" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1666 - 1731</t>
+          <t xml:space="preserve">1631 - 1679</t>
         </is>
       </c>
       <c r="D93" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mary ASTELL</t>
+          <t xml:space="preserve">Anne CONWAY</t>
         </is>
       </c>
       <c r="E93" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Astell"  title=" Wikipedia"&gt;Mary ASTELL&lt;/a&gt; (1666-1731) est une philosophe et écrivaine anglaise, souvent présentée comme la première féministe anglaise. Fille d'un marchand de charbon de Newcastle, elle fut instruite par son oncle, puis s'installa seule à Londres, où elle vécut de sa plume grâce au soutien de protectrices aristocratiques.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Une proposition sérieuse aux dames&lt;/em&gt; (1694), elle propose de créer une sorte d'institution où les femmes pourraient se consacrer à l'étude et à la réflexion, loin des futilités auxquelles la société les condamne. Disciple de Descartes et du philosophe Malebranche, elle affirme que les femmes ont la même raison que les hommes et que leur prétendue infériorité vient uniquement de leur manque d'éducation.&lt;/p&gt; &lt;p&gt;Mary Astell fut aussi une polémiste redoutée, qui débattit avec les penseurs les plus en vue de son temps, dont John Locke et le philosophe John Norris, avec qui elle échangea des lettres sur l'amour de Dieu. Elle fonda à Chelsea une école de charité pour les filles pauvres, qu'elle soutint jusqu'à sa mort. Son idée d'une communauté de femmes consacrée à l'étude, jugée trop proche des couvents catholiques, ne vit jamais le jour, mais elle inspira de nombreuses féministes après elle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Réflexions sur le mariage&lt;/em&gt; (1700), elle critique avec ironie la condition des épouses, soumises à un pouvoir absolu de leur mari. Elle retourne contre ses adversaires les idées de John Locke : « si tous les hommes naissent libres, comment se fait-il que toutes les femmes naissent esclaves ? ». Anglicane conservatrice en politique, elle n'en fut pas moins l'une des premières à penser la domination des femmes comme une question philosophique et politique.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Conway"  title=" Wikipedia"&gt;Anne CONWAY&lt;/a&gt; (1631-1679) est une philosophe anglaise, proche du groupe des platoniciens de Cambridge. Souffrant toute sa vie de violentes migraines, elle reçut une éducation principalement par correspondance, notamment avec le philosophe Henry More, qui devint son ami et son maître.&lt;/p&gt; &lt;p&gt;Son unique ouvrage, les &lt;em&gt;Principes de la plus ancienne et de la plus moderne philosophie&lt;/em&gt;, fut publié après sa mort, en latin en 1690, puis en anglais. Elle y rejette le dualisme de Descartes, qui sépare l'esprit et la matière, et le matérialisme de Hobbes et de Spinoza. Pour elle, tout ce qui existe est à la fois esprit et corps à des degrés divers : la matière n'est qu'un esprit « épaissi », et toutes les créatures, même les pierres, sont vivantes et capables de se perfectionner.&lt;/p&gt; &lt;p&gt;Sa philosophie répond aussi à une question personnelle : comment donner un sens à la douleur ? Pour Anne Conway, la souffrance n'est pas un châtiment arbitraire mais un moyen de purification, qui permet à chaque créature de se rapprocher de Dieu. Aucune créature n'est condamnée pour toujours : toutes sont appelées à progresser vers le bien, ce qui fait de sa pensée l'une des plus optimistes de son temps.&lt;/p&gt; &lt;p&gt;Anne Conway propose une vision d'un monde en constante évolution vers le bien, où la souffrance a un sens puisqu'elle aide les êtres à progresser. Influencée par la kabbale et par les quakers, qu'elle rejoignit à la fin de sa vie, elle eut une influence directe sur Leibniz, qui la cite et lui emprunta sans doute l'idée de « monade ». Longtemps oubliée, elle est aujourd'hui considérée comme l'une des philosophes les plus originales du XVIIe siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J93" s="38" t="inlineStr">
@@ -6781,17 +6794,17 @@
       </c>
       <c r="K93" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="L93" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rationalisme ; Féminisme</t>
+          <t xml:space="preserve">Néoplatonisme</t>
         </is>
       </c>
       <c r="M93" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe anglaise, considérée comme l'une des premières féministes, qui défendit l'éducation des femmes.</t>
+          <t xml:space="preserve">philosophe anglaise, penseuse d'un monde fait d'un seul esprit vivant, qui influença Leibniz.</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6807,44 +6820,44 @@
     </row>
     <row r="94" ht="130.5" customHeight="1" s="39">
       <c r="A94" s="47">
-        <v>1706</v>
+        <v>1666</v>
       </c>
       <c r="B94" s="47">
-        <v>1749</v>
+        <v>1731</v>
       </c>
       <c r="C94" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1706 - 1749</t>
+          <t xml:space="preserve">1666 - 1731</t>
         </is>
       </c>
       <c r="D94" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Émilie du CHÂTELET</t>
+          <t xml:space="preserve">Mary ASTELL</t>
         </is>
       </c>
       <c r="E94" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Émilie_du_Châtelet"  title=" Wikipedia"&gt;Émilie du CHÂTELET&lt;/a&gt; (1706-1749) est une mathématicienne, physicienne et philosophe française des Lumières. Issue de l'aristocratie, elle reçut une éducation rare pour une fille, en latin, en mathématiques et en sciences. Compagne de Voltaire pendant quinze ans, elle fit de leur château de Cirey un véritable centre d'étude, où ils travaillaient côte à côte.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Institutions de physique&lt;/em&gt; (1740) tentent de concilier la physique de Newton et la métaphysique de Leibniz, en particulier le principe de raison suffisante. Elle participa à la grande controverse sur la notion de « force vive », en montrant que l'énergie d'un corps en mouvement dépend du carré de sa vitesse, une idée essentielle pour la physique moderne.&lt;/p&gt; &lt;p&gt;Elle entretint une correspondance avec les plus grands savants de son temps, comme les mathématiciens Maupertuis et Clairaut, et fut la première femme dont un mémoire scientifique, sur la nature du feu, fut publié par l'Académie des sciences de Paris en 1738. Elle ne pouvait pourtant pas en être membre, et il lui arriva de se déguiser en homme pour entrer dans les cafés où se retrouvaient les savants.&lt;/p&gt; &lt;p&gt;Son œuvre majeure est la traduction commentée en français des &lt;em&gt;Principes mathématiques de la philosophie naturelle&lt;/em&gt; de Newton, achevée juste avant sa mort en couches, à 42 ans. Elle reste aujourd'hui la seule traduction française complète de ce texte fondateur. Dans son &lt;em&gt;Discours sur le bonheur&lt;/em&gt;, elle fait de l'étude et de la passion du savoir une source de bonheur indépendante des autres, notamment pour les femmes, exclues de tant d'autres chemins de la gloire.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Astell"  title=" Wikipedia"&gt;Mary ASTELL&lt;/a&gt; (1666-1731) est une philosophe et écrivaine anglaise, souvent présentée comme la première féministe anglaise. Fille d'un marchand de charbon de Newcastle, elle fut instruite par son oncle, puis s'installa seule à Londres, où elle vécut de sa plume grâce au soutien de protectrices aristocratiques.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Une proposition sérieuse aux dames&lt;/em&gt; (1694), elle propose de créer une sorte d'institution où les femmes pourraient se consacrer à l'étude et à la réflexion, loin des futilités auxquelles la société les condamne. Disciple de Descartes et du philosophe Malebranche, elle affirme que les femmes ont la même raison que les hommes et que leur prétendue infériorité vient uniquement de leur manque d'éducation.&lt;/p&gt; &lt;p&gt;Mary Astell fut aussi une polémiste redoutée, qui débattit avec les penseurs les plus en vue de son temps, dont John Locke et le philosophe John Norris, avec qui elle échangea des lettres sur l'amour de Dieu. Elle fonda à Chelsea une école de charité pour les filles pauvres, qu'elle soutint jusqu'à sa mort. Son idée d'une communauté de femmes consacrée à l'étude, jugée trop proche des couvents catholiques, ne vit jamais le jour, mais elle inspira de nombreuses féministes après elle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Réflexions sur le mariage&lt;/em&gt; (1700), elle critique avec ironie la condition des épouses, soumises à un pouvoir absolu de leur mari. Elle retourne contre ses adversaires les idées de John Locke : « si tous les hommes naissent libres, comment se fait-il que toutes les femmes naissent esclaves ? ». Anglicane conservatrice en politique, elle n'en fut pas moins l'une des premières à penser la domination des femmes comme une question philosophique et politique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J94" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Française</t>
+          <t xml:space="preserve">Britannique</t>
         </is>
       </c>
       <c r="K94" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie ; metaphysique</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L94" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rationalisme ; Lumières</t>
+          <t xml:space="preserve">Rationalisme ; Féminisme</t>
         </is>
       </c>
       <c r="M94" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">mathématicienne et philosophe française des Lumières, traductrice de Newton et penseuse du bonheur.</t>
+          <t xml:space="preserve">philosophe anglaise, considérée comme l'une des premières féministes, qui défendit l'éducation des femmes.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -6856,31 +6869,28 @@
         <is>
           <t xml:space="preserve">occident</t>
         </is>
-      </c>
-      <c r="P94">
-        <v>2</v>
       </c>
     </row>
     <row r="95" ht="130.5" customHeight="1" s="39">
       <c r="A95" s="47">
-        <v>1748</v>
+        <v>1706</v>
       </c>
       <c r="B95" s="47">
-        <v>1793</v>
+        <v>1749</v>
       </c>
       <c r="C95" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1748 - 1793</t>
+          <t xml:space="preserve">1706 - 1749</t>
         </is>
       </c>
       <c r="D95" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Olympe de GOUGES</t>
+          <t xml:space="preserve">Émilie du CHÂTELET</t>
         </is>
       </c>
       <c r="E95" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympe_de_Gouges"  title=" Wikipedia"&gt;Olympe de GOUGES&lt;/a&gt; (1748-1793), de son vrai nom Marie Gouze, est une femme de lettres et une femme politique française. Née à Montauban dans un milieu modeste, veuve très jeune, elle s'installa à Paris où elle écrivit des pièces de théâtre, dont une dénonçant l'esclavage des Noirs, qui fit scandale.&lt;/p&gt; &lt;p&gt;Pendant la Révolution française, elle publia de nombreuses brochures sur les questions sociales et politiques : aide aux pauvres, divorce, protection des enfants nés hors mariage. En 1791, elle rédigea la &lt;em&gt;Déclaration des droits de la femme et de la citoyenne&lt;/em&gt;, qui reprend article par article la Déclaration de 1789 pour montrer qu'elle exclut la moitié de l'humanité. Elle y écrit : « La femme a le droit de monter sur l'échafaud ; elle doit avoir également celui de monter à la tribune ».&lt;/p&gt; &lt;p&gt;Olympe de Gouges réclamait aussi l'accès des femmes à toutes les fonctions publiques, le droit de vote, le partage des biens entre époux et le droit de rechercher la paternité. Dans le postambule de sa Déclaration, elle appelle les femmes à se réveiller et à reconnaître leurs droits. Sa pensée associe l'égalité des sexes, l'abolition de l'esclavage et la justice sociale, bien avant que ces combats soient reconnus.&lt;/p&gt; &lt;p&gt;Proche des Girondins, elle critiqua ouvertement Robespierre et la Terreur. Arrêtée pour ses écrits, elle fut condamnée à mort et guillotinée le 3 novembre 1793. Longtemps caricaturée, elle est aujourd'hui considérée comme une pionnière du féminisme et de la défense des droits humains.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Émilie_du_Châtelet"  title=" Wikipedia"&gt;Émilie du CHÂTELET&lt;/a&gt; (1706-1749) est une mathématicienne, physicienne et philosophe française des Lumières. Issue de l'aristocratie, elle reçut une éducation rare pour une fille, en latin, en mathématiques et en sciences. Compagne de Voltaire pendant quinze ans, elle fit de leur château de Cirey un véritable centre d'étude, où ils travaillaient côte à côte.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Institutions de physique&lt;/em&gt; (1740) tentent de concilier la physique de Newton et la métaphysique de Leibniz, en particulier le principe de raison suffisante. Elle participa à la grande controverse sur la notion de « force vive », en montrant que l'énergie d'un corps en mouvement dépend du carré de sa vitesse, une idée essentielle pour la physique moderne.&lt;/p&gt; &lt;p&gt;Elle entretint une correspondance avec les plus grands savants de son temps, comme les mathématiciens Maupertuis et Clairaut, et fut la première femme dont un mémoire scientifique, sur la nature du feu, fut publié par l'Académie des sciences de Paris en 1738. Elle ne pouvait pourtant pas en être membre, et il lui arriva de se déguiser en homme pour entrer dans les cafés où se retrouvaient les savants.&lt;/p&gt; &lt;p&gt;Son œuvre majeure est la traduction commentée en français des &lt;em&gt;Principes mathématiques de la philosophie naturelle&lt;/em&gt; de Newton, achevée juste avant sa mort en couches, à 42 ans. Elle reste aujourd'hui la seule traduction française complète de ce texte fondateur. Dans son &lt;em&gt;Discours sur le bonheur&lt;/em&gt;, elle fait de l'étude et de la passion du savoir une source de bonheur indépendante des autres, notamment pour les femmes, exclues de tant d'autres chemins de la gloire.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J95" s="38" t="inlineStr">
@@ -6890,17 +6900,17 @@
       </c>
       <c r="K95" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; ethique</t>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
         </is>
       </c>
       <c r="L95" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Féminisme ; Lumières</t>
+          <t xml:space="preserve">Rationalisme ; Lumières</t>
         </is>
       </c>
       <c r="M95" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">femme de lettres et révolutionnaire française, autrice de la Déclaration des droits de la femme et de la citoyenne.</t>
+          <t xml:space="preserve">mathématicienne et philosophe française des Lumières, traductrice de Newton et penseuse du bonheur.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -6919,56 +6929,49 @@
     </row>
     <row r="96" ht="130.5" customHeight="1" s="39">
       <c r="A96" s="47">
-        <v>1550</v>
-      </c>
-      <c r="B96" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1623</t>
-        </is>
+        <v>1748</v>
+      </c>
+      <c r="B96" s="47">
+        <v>1793</v>
       </c>
       <c r="C96" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550 – 1623</t>
+          <t xml:space="preserve">1748 - 1793</t>
         </is>
       </c>
       <c r="D96" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Francisco SANCHES</t>
+          <t xml:space="preserve">Olympe de GOUGES</t>
         </is>
       </c>
       <c r="E96" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Sanchez" title=" Wikipedia"&gt;Francisco SANCHES&lt;/a&gt; est un médecin et philosophe d’origine portugaise, l’un des grands sceptiques de la Renaissance. Né vers 1550, à Braga ou à Tui, dans une famille de juifs convertis, que la menace de l’Inquisition pousse à quitter la péninsule Ibérique, il grandit à Bordeaux. Il étudie la médecine à Montpellier, séjourne en Italie, puis s’installe à Toulouse, où il exerce la médecine à l’hôpital et enseigne la philosophie et la médecine à l’université jusqu’à sa mort en 1623. Il serait un parent de &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne" title=" Wikipedia"&gt;Montaigne&lt;/a&gt;, par la mère de celui-ci.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Que rien ne se sait&lt;/em&gt; (&lt;em&gt;Quod nihil scitur&lt;/em&gt;), publié à Lyon en 1581, attaque la science des écoles, fondée sur Aristote : ses définitions ne sont que des mots, ses syllogismes ne font que répéter ce qu’on savait déjà, et l’on croit savoir quand on ne fait que nommer. La connaissance parfaite d’une chose supposerait de la connaître dans toutes ses causes et ses relations avec tout le reste, ce qui est impossible à un esprit fini. Il commence chaque argument par une question et termine son livre par un « Quoi ? » ironique.&lt;/p&gt; &lt;p&gt;Mais son &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_%28philosophie%29" title=" Wikipedia"&gt;scepticisme&lt;/a&gt; n’est pas un renoncement. Faute de savoir parfait, il faut s’en remettre à l’observation attentive et à l’expérience, comme le fait le médecin au chevet des malades, et avancer prudemment de jugement en jugement. Il annonce ainsi, avant Bacon et Descartes, l’esprit de la méthode expérimentale. Son œuvre, contemporaine des &lt;em&gt;Essais&lt;/em&gt; de Montaigne, a été redécouverte au XXe siècle comme un moment important du doute moderne.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/sanches-mini.webp</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympe_de_Gouges"  title=" Wikipedia"&gt;Olympe de GOUGES&lt;/a&gt; (1748-1793), de son vrai nom Marie Gouze, est une femme de lettres et une femme politique française. Née à Montauban dans un milieu modeste, veuve très jeune, elle s'installa à Paris où elle écrivit des pièces de théâtre, dont une dénonçant l'esclavage des Noirs, qui fit scandale.&lt;/p&gt; &lt;p&gt;Pendant la Révolution française, elle publia de nombreuses brochures sur les questions sociales et politiques : aide aux pauvres, divorce, protection des enfants nés hors mariage. En 1791, elle rédigea la &lt;em&gt;Déclaration des droits de la femme et de la citoyenne&lt;/em&gt;, qui reprend article par article la Déclaration de 1789 pour montrer qu'elle exclut la moitié de l'humanité. Elle y écrit : « La femme a le droit de monter sur l'échafaud ; elle doit avoir également celui de monter à la tribune ».&lt;/p&gt; &lt;p&gt;Olympe de Gouges réclamait aussi l'accès des femmes à toutes les fonctions publiques, le droit de vote, le partage des biens entre époux et le droit de rechercher la paternité. Dans le postambule de sa Déclaration, elle appelle les femmes à se réveiller et à reconnaître leurs droits. Sa pensée associe l'égalité des sexes, l'abolition de l'esclavage et la justice sociale, bien avant que ces combats soient reconnus.&lt;/p&gt; &lt;p&gt;Proche des Girondins, elle critiqua ouvertement Robespierre et la Terreur. Arrêtée pour ses écrits, elle fut condamnée à mort et guillotinée le 3 novembre 1793. Longtemps caricaturée, elle est aujourd'hui considérée comme une pionnière du féminisme et de la défense des droits humains.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J96" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portugaise</t>
+          <t xml:space="preserve">Française</t>
         </is>
       </c>
       <c r="K96" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">epistemologie</t>
+          <t xml:space="preserve">politique ; ethique</t>
         </is>
       </c>
       <c r="L96" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scepticisme</t>
+          <t xml:space="preserve">Féminisme ; Lumières</t>
         </is>
       </c>
       <c r="M96" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">médecin et philosophe sceptique d’origine portugaise, auteur de Que rien ne se sait.</t>
+          <t xml:space="preserve">femme de lettres et révolutionnaire française, autrice de la Déclaration des droits de la femme et de la citoyenne.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -6982,31 +6985,31 @@
     </row>
     <row r="97" ht="130.5" customHeight="1" s="39">
       <c r="A97" s="47">
-        <v>1608</v>
+        <v>1550</v>
       </c>
       <c r="B97" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697</t>
+          <t xml:space="preserve">1623</t>
         </is>
       </c>
       <c r="C97" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1608 – 1697</t>
+          <t xml:space="preserve">1550 – 1623</t>
         </is>
       </c>
       <c r="D97" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">António VIEIRA</t>
+          <t xml:space="preserve">Francisco SANCHES</t>
         </is>
       </c>
       <c r="E97" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ant%C3%B3nio_Vieira" title=" Wikipedia"&gt;António VIEIRA&lt;/a&gt; est un prêtre jésuite portugais, prédicateur, diplomate et écrivain, l’un des plus grands prosateurs de la langue portugaise. Né à Lisbonne, il part enfant pour le Brésil, à Bahia, où il entre chez les jésuites et apprend les langues indiennes. Ses sermons, d’une éloquence baroque éblouissante, le rendent célèbre : il en a laissé plus de deux cents. Conseiller du roi Jean IV après la restauration de l’indépendance portugaise en 1640, il est chargé de missions diplomatiques en France, en Hollande et à Rome.&lt;/p&gt; &lt;p&gt;Il prend la défense des Indiens d’Amazonie, réduits en esclavage par les colons, et se fait de puissants ennemis : son &lt;em&gt;Sermon de saint Antoine aux poissons&lt;/em&gt; (1654), où il prêche aux poissons faute d’être écouté des hommes, est une satire célèbre des colons. Ses adversaires obtiennent son expulsion du Maranhão en 1661. Dans plusieurs sermons, il dénonce aussi la souffrance des esclaves africains, tout en restant prisonnier des idées de son temps. Il plaide enfin pour les « nouveaux chrétiens », juifs convertis persécutés au Portugal, et demande que l’&lt;a href="https://fr.wikipedia.org/wiki/Inquisition_portugaise" title=" Wikipedia"&gt;Inquisition&lt;/a&gt; cesse de les poursuivre et que leurs capitaux servent au royaume.&lt;/p&gt; &lt;p&gt;Ses rêves prophétiques d’un &lt;a href="https://fr.wikipedia.org/wiki/Quint-Empire" title=" Wikipedia"&gt;Cinquième Empire&lt;/a&gt;, un règne universel de paix et de justice dont le Portugal serait l’instrument, lui valent d’être poursuivi par l’Inquisition, qui l’emprisonne de 1665 à 1667. Libéré, il obtient du pape une protection contre elle. Il passe ses dernières années à Bahia, où il meurt en 1697. Le poète Fernando Pessoa l’appelait « l’empereur de la langue portugaise ».&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Sanchez" title=" Wikipedia"&gt;Francisco SANCHES&lt;/a&gt; est un médecin et philosophe d’origine portugaise, l’un des grands sceptiques de la Renaissance. Né vers 1550, à Braga ou à Tui, dans une famille de juifs convertis, que la menace de l’Inquisition pousse à quitter la péninsule Ibérique, il grandit à Bordeaux. Il étudie la médecine à Montpellier, séjourne en Italie, puis s’installe à Toulouse, où il exerce la médecine à l’hôpital et enseigne la philosophie et la médecine à l’université jusqu’à sa mort en 1623. Il serait un parent de &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne" title=" Wikipedia"&gt;Montaigne&lt;/a&gt;, par la mère de celui-ci.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Que rien ne se sait&lt;/em&gt; (&lt;em&gt;Quod nihil scitur&lt;/em&gt;), publié à Lyon en 1581, attaque la science des écoles, fondée sur Aristote : ses définitions ne sont que des mots, ses syllogismes ne font que répéter ce qu’on savait déjà, et l’on croit savoir quand on ne fait que nommer. La connaissance parfaite d’une chose supposerait de la connaître dans toutes ses causes et ses relations avec tout le reste, ce qui est impossible à un esprit fini. Il commence chaque argument par une question et termine son livre par un « Quoi ? » ironique.&lt;/p&gt; &lt;p&gt;Mais son &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_%28philosophie%29" title=" Wikipedia"&gt;scepticisme&lt;/a&gt; n’est pas un renoncement. Faute de savoir parfait, il faut s’en remettre à l’observation attentive et à l’expérience, comme le fait le médecin au chevet des malades, et avancer prudemment de jugement en jugement. Il annonce ainsi, avant Bacon et Descartes, l’esprit de la méthode expérimentale. Son œuvre, contemporaine des &lt;em&gt;Essais&lt;/em&gt; de Montaigne, a été redécouverte au XXe siècle comme un moment important du doute moderne.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/vieira-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/sanches-mini.webp</t>
         </is>
       </c>
       <c r="J97" s="38" t="inlineStr">
@@ -7016,17 +7019,22 @@
       </c>
       <c r="K97" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ethique ; politique</t>
+          <t xml:space="preserve">epistemologie</t>
         </is>
       </c>
       <c r="L97" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme</t>
+          <t xml:space="preserve">Scepticisme</t>
         </is>
       </c>
       <c r="M97" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">jésuite portugais, prédicateur baroque, défenseur des Indiens du Brésil et des nouveaux chrétiens.</t>
+          <t xml:space="preserve">médecin et philosophe sceptique d’origine portugaise, auteur de Que rien ne se sait.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7040,51 +7048,51 @@
     </row>
     <row r="98" ht="130.5" customHeight="1" s="39">
       <c r="A98" s="47">
-        <v>1530</v>
+        <v>1608</v>
       </c>
       <c r="B98" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1596</t>
+          <t xml:space="preserve">1697</t>
         </is>
       </c>
       <c r="C98" s="47" t="inlineStr">
         <is>
-          <t xml:space="preserve">vers 1530 – 1596</t>
+          <t xml:space="preserve">1608 – 1697</t>
         </is>
       </c>
       <c r="D98" s="48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jean BODIN</t>
+          <t xml:space="preserve">António VIEIRA</t>
         </is>
       </c>
       <c r="E98" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Bodin" title=" Wikipedia"&gt;Jean BODIN&lt;/a&gt; est un juriste, philosophe et économiste français de la Renaissance, le grand théoricien de la &lt;a href="https://fr.wikipedia.org/wiki/Souverainet%C3%A9" title=" Wikipedia"&gt;souveraineté&lt;/a&gt;. Né à Angers vers 1530, il est d’abord moine carme, puis étudie et enseigne le droit à Toulouse avant de devenir avocat au Parlement de Paris. Il vit les guerres de Religion qui déchirent la France. Député du tiers état aux états généraux de Blois en 1576, il s’oppose à la reprise de la guerre contre les protestants et à la vente du domaine royal. Il finit procureur du roi à Laon, où il meurt de la peste en 1596.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Les Six Livres de la République&lt;/em&gt; (1576), il définit l’État par la souveraineté, « puissance absolue et perpétuelle d’une République ». Elle est indivisible, et son premier attribut est de « donner et casser la loi » sans le consentement de personne. Le souverain reste pourtant soumis aux lois de Dieu et de la nature : il doit respecter la propriété de ses sujets et ne peut lever d’impôt sans leur accord. Écrite contre l’anarchie des guerres civiles, cette théorie prépare la monarchie absolue et toute la pensée moderne de l’État, de Hobbes à Rousseau. Bodin y expose aussi une théorie des climats que reprendra Montesquieu.&lt;/p&gt; &lt;p&gt;Il est aussi l’un des premiers économistes. Dans sa &lt;em&gt;Réponse aux paradoxes de M. de Malestroit&lt;/em&gt; (1568), il explique la hausse des prix qui frappe l’Europe par l’afflux de l’or et de l’argent d’Amérique : c’est une première forme de la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_quantitative_de_la_monnaie" title=" Wikipedia"&gt;théorie quantitative de la monnaie&lt;/a&gt;. Partisan d’un commerce actif et de la protection des manufactures, il annonce le &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt;. Son &lt;em&gt;Colloque des sept sages&lt;/em&gt; fait dialoguer un catholique, un luthérien, un calviniste, un juif, un musulman, un partisan de la religion naturelle et un sceptique, sans désigner de vainqueur : un plaidoyer pour la tolérance. Mais le même Bodin publie en 1580 une &lt;em&gt;Démonomanie des sorciers&lt;/em&gt; qui encourage leur persécution.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ant%C3%B3nio_Vieira" title=" Wikipedia"&gt;António VIEIRA&lt;/a&gt; est un prêtre jésuite portugais, prédicateur, diplomate et écrivain, l’un des plus grands prosateurs de la langue portugaise. Né à Lisbonne, il part enfant pour le Brésil, à Bahia, où il entre chez les jésuites et apprend les langues indiennes. Ses sermons, d’une éloquence baroque éblouissante, le rendent célèbre : il en a laissé plus de deux cents. Conseiller du roi Jean IV après la restauration de l’indépendance portugaise en 1640, il est chargé de missions diplomatiques en France, en Hollande et à Rome.&lt;/p&gt; &lt;p&gt;Il prend la défense des Indiens d’Amazonie, réduits en esclavage par les colons, et se fait de puissants ennemis : son &lt;em&gt;Sermon de saint Antoine aux poissons&lt;/em&gt; (1654), où il prêche aux poissons faute d’être écouté des hommes, est une satire célèbre des colons. Ses adversaires obtiennent son expulsion du Maranhão en 1661. Dans plusieurs sermons, il dénonce aussi la souffrance des esclaves africains, tout en restant prisonnier des idées de son temps. Il plaide enfin pour les « nouveaux chrétiens », juifs convertis persécutés au Portugal, et demande que l’&lt;a href="https://fr.wikipedia.org/wiki/Inquisition_portugaise" title=" Wikipedia"&gt;Inquisition&lt;/a&gt; cesse de les poursuivre et que leurs capitaux servent au royaume.&lt;/p&gt; &lt;p&gt;Ses rêves prophétiques d’un &lt;a href="https://fr.wikipedia.org/wiki/Quint-Empire" title=" Wikipedia"&gt;Cinquième Empire&lt;/a&gt;, un règne universel de paix et de justice dont le Portugal serait l’instrument, lui valent d’être poursuivi par l’Inquisition, qui l’emprisonne de 1665 à 1667. Libéré, il obtient du pape une protection contre elle. Il passe ses dernières années à Bahia, où il meurt en 1697. Le poète Fernando Pessoa l’appelait « l’empereur de la langue portugaise ».&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/bodin-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vieira-mini.webp</t>
         </is>
       </c>
       <c r="J98" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Française</t>
+          <t xml:space="preserve">Portugaise</t>
         </is>
       </c>
       <c r="K98" s="45" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; spiritualite</t>
+          <t xml:space="preserve">ethique ; politique</t>
         </is>
       </c>
       <c r="L98" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humanisme ; Mercantilisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="M98" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">juriste et philosophe français, théoricien de la souveraineté et pionnier de la pensée économique.</t>
+          <t xml:space="preserve">jésuite portugais, prédicateur baroque, défenseur des Indiens du Brésil et des nouveaux chrétiens.</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7092,7 +7100,9 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="P98"/>
+      <c r="P98">
+        <v>2</v>
+      </c>
     </row>
     <row r="99" ht="130.5" customHeight="1" s="39">
       <c r="A99" s="47">
@@ -7221,48 +7231,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_de_La_Ram%C3%A9e&quot;   title=&quot; Wikipedia&quot;&gt;Pierre de la RAMÉE&lt;/a&gt; , plus connu sous son nom latin de Petrus Ramus ou Ramus, était un philosophe, logicien, rhétoricien et pédagogue français de la Renaissance.  Il appartient au contexte intellectuel de l’humanisme et de la Réforme. Issu d’un milieu modeste, il parvient à étudier à Paris et devient professeur. Sa pensée s’inscrit dans une volonté générale de réformer l’enseignement et de rendre les savoirs plus clairs, plus pratiques et mieux organisés. &lt;/p&gt; &lt;p&gt; Sa philosophie se construit d’abord contre la scolastique et contre l’autorité excessive accordée à Aristote dans les universités. En 1543, ses Aristotelicae Animadversiones critiquent vivement la logique aristotélicienne et provoquent un scandale académique. Il ne rejette cependant pas toute la philosophie d’Aristote : il conteste surtout l’usage mécanique et scolaire de ses textes. Pour lui, on ne doit pas accepter une proposition parce qu’elle vient d’une autorité, mais l’examiner par la raison et par l’expérience du discours. &lt;/p&gt; &lt;p&gt; Son apport principal concerne la dialectique, qu’il identifie largement à la logique. Celle-ci est, selon lui, &lt;a href=&quot;https://www.youtube.com/watch?v=06iiHDjuuqU&quot;  title=&quot;Petrus ramus par vis philo &quot;&gt;l’« art de bien disserter » &lt;/a&gt; et se divise en deux opérations fondamentales : l’invention et le jugement. L’invention consiste à trouver les idées, les arguments et les preuves nécessaires à l’examen d’une question ; le jugement consiste ensuite à les évaluer et à les ordonner. Il simplifie ainsi la logique traditionnelle afin de la rapprocher de l’activité concrète de penser, d’argumenter et d’enseigner. &lt;/p&gt; &lt;p&gt; Il accorde également une importance décisive à la méthode en cherchant à organiser les connaissances selon une progression rationnelle, allant généralement du général au particulier, par définitions, divisions et exemples. Une méthode correcte doit ne retenir que ce qui est vrai et nécessaire, respecter le domaine propre de chaque discipline et traiter le général comme général et le particulier comme particulier. Cette conception contribue à faire de la méthode un problème central de la philosophie moderne et annonce, sur certains points, les préoccupations de penseurs comme Descartes, même si il ne peut pas être considéré comme un simple précurseur du cartésianisme. &lt;/p&gt; &lt;p&gt; Sa pensée est inséparable d’un projet de réforme de l’éducation. Il veut   &lt;a href=&quot;https://www.persee.fr/doc/rhren_0181-6799_2002_num_54_1_2510&quot;  title=&quot;pierre de la ramée grammaire par persée &quot;&gt;enseigner la grammaire, &lt;/a&gt;  la rhétorique, les mathématiques et les sciences selon des plans ordonnés, accessibles et utiles. Ses manuels de logique et de dialectique connaissent une large diffusion en Europe, notamment sa Dialectique de 1555, l’un des premiers grands ouvrages de logique publiés dans une langue moderne. Son influence fut importante, mais son système a aussi été critiqué parce qu’il réduisait parfois la richesse de la logique, de la rhétorique et de la philosophie à des schémas méthodiques. Ramus reste ainsi une figure majeure de la Renaissance : moins un philosophe spéculatif qu’un réformateur de la pensée, du langage et de l’enseignement. &lt;/p&gt; &#10;" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" display="https://www.laphilo.fr/pho/pdlramee-mini.webp" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Francesco_Patrizi&quot; title=&quot; Wikipedia&quot;&gt;Francesco PATRIZI&lt;/a&gt; était un philosophe et humaniste italien connu pour son rejet de l'aristotélisme et sa promotion d'une philosophie inspirée par Platon et les néoplatoniciens comme Plotin et Proclus. Il a cherché à revitaliser la philosophie naturelle en intégrant des éléments mystiques et hermétiques, ce qui l'a conduit à développer une vision du monde panthéiste et dynamique. Ses oeuvres principales sont : &lt;/p&gt; &lt;p&gt; - &quot;Nova de universis philosophia&quot; : C'est son œuvre majeure où il expose sa vision d'une nouvelle philosophie universelle. Il y critique sévèrement Aristote et propose une métaphysique fondée sur la lumière comme principe premier de l'univers. &lt;/p&gt; &#10;&lt;p&gt; - &quot;Discussiones peripateticae&quot; : Il attaque la philosophie aristotélicienne, qu'il juge dépassée et incompatible avec les découvertes scientifiques de son époque. Il plaide pour un retour à Platon et aux traditions pré-aristotéliciennes. &lt;p&gt; &#10;&lt;p&gt; - &quot;Della poetica&quot; : Il s'intéresse également à l'esthétique et à la littérature. Il explore la nature de la poésie et son rôle dans la connaissance et l'expression de la vérité. &lt;/p&gt; &lt;p&gt; Considéré comme un précurseur de certaines idées modernes, notamment en ce qui concerne la nature de la lumière et son rôle dans l'univers, sa tentative de dépasser l'aristotélisme et de proposer une nouvelle philosophie universelle fondée sur la lumière et l'harmonie cosmique en fait une figure importante dans l'histoire de la pensée occidentale. Bien que ses idées aient été parfois marginalisées, elles témoignent de la richesse et de la diversité de la philosophie de la Renaissance. &lt;/p&gt;" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Charron&quot;  title=&quot; Wikipedia&quot;&gt;Pierre CHARRON&lt;/a&gt; était un philosophe, orateur et moraliste français dont   &lt;a href=&quot;https://revuecorpus.com/pdf/CORPUS%20N%C2%B055.pdf&quot; style=&quot;color:#88A1E9&quot; title=&quot; n°55  Charron par Corpus&quot;&gt; l'œuvre&lt;/a&gt; est profondément marquée par le contexte religieux et intellectuel de son époque, notamment les guerres de religion et l'humanisme renaissant. &lt;/p&gt; &lt;p&gt;  Son ouvrage &quot;Les Trois Vérités&quot; est une apologie de la religion catholique, rédigée en réponse aux arguments protestants. Elle vise à défendre la foi contre les athées, idolâtres, juifs, mahométans, hérétiques et schismatiques. Il est présenté comme un fervent défenseur de l'orthodoxie catholique, &lt;/p&gt; &lt;p&gt; Son 2ème ouvrage &quot;De la Sagesse&quot; est sans doute le plus célèbre et le plus influent. Ce &lt;a href=&quot;https://www.youtube.com/watch?v=6n3OmEeVudo&quot; title=&quot; Charron et l'invention d'une sagesse laîque par Photon&quot;&gt; traité de morale &lt;/a&gt;  et de philosophie, divisé en trois livres, expose une conception de la sagesse humaine qui sera très commentée et parfois critiquée pour ses implications jugées irréligieuses par certains car il révèle une pensée plus nuancée, imprégnée de scepticisme et d'une forme de moralisme laïque. &lt;/p&gt; &lt;p&gt; Il est profondément influencé par le scepticisme des  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Essais_(Montaigne)&quot; title=&quot; Essais de Montaigne par Wikipedia&quot;&gt; Essais de Montaigne&lt;/a&gt; et partage l'idée de la faiblesse de la raison humaine et l'incertitude des connaissances. Pour lui, il faut &quot;commencer&quot; par le doute, reconnaître &quot;l'ignorance, faiblesse, incertitude&quot; de la condition humaine. Ce  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Scepticisme_(philosophie)&quot; title=&quot;  scepticisme par Wikipedia&quot;&gt; scepticisme&lt;/a&gt; initial n'est pas une fin en soi, mais un point de départ pour l'acquisition de la sagesse. &lt;/p&gt; &lt;p&gt;  Il est l'un des penseurs qui contribuent à la séparation de la sphère morale de la sphère théologique. Il cherche à établir une éthique autonome, fondée sur la raison et la nature humaine, sans la subordonner entièrement à la foi. Il  invite à fuir la &quot;contagion du monde&quot; et à rechercher la solitude comme moyen d'amender l'intellect par rapport aux erreurs populaires. Il insiste sur la capacité de l'homme à être maître de sa volonté et à s'affermir dans la raison, ce qui peut être vu comme un précurseur de l'individualisme moderne. &lt;/p&gt; &lt;p&gt; Il  a joué un rôle important dans la transition de l'humanisme vers le rationalisme, en ouvrant la voie à une réflexion morale et philosophique plus autonome par rapport à la théologie. Son œuvre est un témoignage précieux des tensions intellectuelles et religieuses de son époque. &lt;/p&gt; " r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Giordano_Bruno&quot;  title=&quot; Wikipedia&quot;&gt; Giordano BRUNO&lt;/a&gt; était un philosophe et penseur italien, connue pour ses  &lt;a href=&quot;https://www.youtube.com/watch?v=21dM3ZJtYY0&amp;t=11s&quot; style=&quot;color:#88A1E9&quot; title=&quot;Giordano BRUNO de Calvin par Le Pro Presente &quot;&gt;idées cosmologiques&lt;/a&gt; et philosophiques radicales dont voici quelques-uns de ses concepts clés : &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&#10;&lt;p&gt; - L'univers infini : et peuplé d'une infinité de mondes habités. Cette vision s'opposait à la conception géocentrique de l'univers, qui plaçait la Terre au centre de tout.  &lt;/p&gt;&#10;&lt;p&gt; -  L'unité de la matière et de l'esprit : vision panthéiste de l'univers, où il croyait que la matière et l'esprit étaient inséparables et que l'univers était animé par une force vitale universelle. &lt;/p&gt;&#10;&lt;p&gt;  - La relativité du mouvement : le mouvement est relatif et qu'il n'y a pas de point de référence absolu dans l'univers. &lt;/p&gt;&#10;&lt;p&gt; - La liberté de pensée : la liberté de pensée et d'expression, s'opposant à l'autorité dogmatique de l'Église. Il croyait que la vérité ne pouvait être découverte que par la raison et l'expérience, et non par la révélation divine. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; En raison de  &lt;a href=&quot;https://nospensees.fr/les-meilleures-phrases-de-giordano-bruno/&quot; title=&quot;Giordano BRUNO par nospensees &quot;&gt;ses idées controversées&lt;/a&gt;, il a été contraint de quitter l'Italie et de voyager à travers l'Europe, dans des villes comme Genève, Paris, Londres et Prague, où il a enseigné et publié  &lt;a href=&quot;https://www.willeime.com/bruno.htm&quot; title=&quot;Giordano BRUNO par willeime &quot;&gt;ses œuvres&lt;/a&gt;. Il a été arrêté par l'Inquisition vénitienne et extradé à Rome. Après 8 ans de procès, il a été accusé d'hérésie pour ses idées et condamné à mort. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus importantes, on peut citer : &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&#10;&lt;p&gt; -  &lt;a href=&quot;https://www.youtube.com/watch?v=vHfEKwAmhAQ&quot;  title=&quot;Giordano BRUNO par Filosofia&quot;&gt;&quot;De l'infinito, universo e mondi&quot;&lt;/a&gt;: Théorie de l'univers infini et des mondes multiples. &lt;/p&gt; &#10;&lt;p&gt; -&quot; La cena de le ceneri&quot; : Critique la philosophie aristotélicienne et défend les idées coperniciennes.&lt;/p&gt; &#10;&lt;p&gt; - &quot;De la causa, principio e uno&quot; : Nature de l'univers et l'unité de la matière et de l'esprit.&lt;/p&gt;  &lt;p&gt; &lt;/p&gt; &lt;p&gt;   &lt;p&gt; &lt;/p&gt;     &lt;audio controls title=&quot; Giordano BRUNO par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-16.11.2022-ITEMA_23198161-2015C3372E1085-NET_MFC_367A1BA4-BD9E-4C79-A1B2-C57FCE8CB809-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Hobbes&quot;  title=&quot; Wikipedia&quot;&gt;Thomas HOBBES&lt;/a&gt; était un philosophe anglais et fondateur de la philosophie politique moderne connu pour son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=8sYAaiDjf0U&amp;ab_channel=AlainBajom%C3%A9e&quot; title=&quot;Le Léviathan par Alain Bajomé&quot;&gt;&quot;Léviathan&quot;&lt;/a&gt;, publié en 1651, dans lequel il développe sa vision de la nature humaine et de la société. Il partait du constat que l'être humain est fondamentalement égoïste et cherchera toujours à obtenir ce qu'il désire, même si cela nuit aux autres, car &lt;a href=&quot;https://www.youtube.com/watch?v=isCVgDObx4c&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'homme est un loup pour l'homme par Le Précepteur&quot;&gt;&quot;L'homme est un loup pour l'homme&quot;&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Pour lui, cette tendance naturelle à l'égoïsme et à la violence rendait impossible la coexistence pacifique entre les hommes, à moins qu'ils ne se soumettent tous volontairement à une autorité souveraine forte. C'est pourquoi, la société doit être gouvernée par un pouvoir absolu, représenté par un souverain, qui impose l'ordre et la sécurité. &lt;/p&gt; &lt;p&gt;  Pour lui, le contrat social est un moyen pour les individus de renoncer à leur liberté naturelle en échange de la sécurité que leur offre l'Etat. Le souverain est donc le garant de cette sécurité, et il doit être obéi sans réserve, même si cela signifie restreindre certaines libertés individuelles. &lt;/p&gt; &lt;p&gt; &#10;Hobbes a également développé une théorie de l'Etat de nature, dans lequel les hommes vivraient dans un état de guerre perpétuelle, sans lois ni règles pour les protéger. Pour lui, l'Etat de nature était un état de violence, de peur et d'insécurité, et c'est pour échapper à cet état que les hommes ont créé la société. &lt;/p&gt;   &lt;audio controls title=&quot;Le pacte d'obéissance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22060-04.04.2021-ITEMA_22630431-2012C12410E0123.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;&lt;p&gt; &lt;/p&gt;" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Gassendi&quot;  title=&quot; Wikipedia&quot;&gt; Pierre GASSENDI&lt;/a&gt;  était un philosophe, scientifique, astronome et mathématicien français, connu pour &lt;a href=&quot;https://www.gassendi.fr/index.php&quot; style=&quot;color:#88A1E9&quot; title=&quot;Pierre GASSENDI par gassendi.fr &quot;&gt;ses contributions&lt;/a&gt; à la philosophie naturelle, à la renaissance de l'épicurisme et pour ses critiques des philosophies de Descartes et d'Aristote. Il  a été un observateur attentif des phénomènes célestes. Il est notamment connu pour avoir été le premier à observer le transit de Mercure devant le Soleil en 1631, confirmant ainsi les prédictions de Kepler. &lt;/p&gt; &lt;p&gt; Il  a joué un &lt;a href=&quot;https://www.persee.fr/doc/rhr_0035-1423_1958_num_154_2_8873&quot; title=&quot;Pierre GASSENDI par Persée &quot;&gt;rôle clé &lt;/a&gt; dans la réhabilitation de la philosophie d'Épicure, qu'il a adaptée à un contexte chrétien. Il a défendu une vision atomiste de la nature, mais a rejeté les aspects matérialistes et athées de l'épicurisme antique. Il a plaidé pour une approche empirique de la connaissance, insistant sur l'importance de l'observation et de l'expérience. &lt;/p&gt; &lt;p&gt; Il a influencé des penseurs ultérieurs tels que John Locke et Isaac Newton. Son empirisme et son atomisme ont contribué au développement de la philosophie naturelle moderne tout en cherchant à concilier la science naissante avec la foi chrétienne, montrant que les découvertes scientifiques pouvaient être compatibles avec une vision religieuse du monde. &lt;/p&gt; &#10;&#10;" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ren%C3%A9_Descartes&quot;  title=&quot; Wikipedia&quot;&gt;René DESCARTES&lt;/a&gt; était un philosophe et marthématicien Français considéré comme un pionnier de la philosophie &lt;a href=&quot;https://la-philosophie.com/philosophie-lumieres&quot;  title=&quot;La philosophie des Lumières par la-philosophie.com&quot;&gt;des lumières&lt;/a&gt;  et de la science moderne.&lt;/p&gt; &lt;p&gt; Il est surtout connu pour sa phrase célèbre &lt;a href=&quot;https://www.youtube.com/watch?v=OjKY5Okx9wQ&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Je pense donc je suis par le Précepteur&quot;&gt;&quot;Je pense, donc je suis&quot;&lt;/a&gt; (en latin &quot;Cogito, ergo sum&quot;), qui a été prononcée dans son œuvre phare  &lt;a href=&quot;https://www.youtube.com/watch?v=cGrhiO0CECs&quot;  title=&quot;Le Discours de la méthode par Essences des Livres&quot;&gt;&quot;Discours de la méthode&quot;&lt;/a&gt; écrite en 1637.  Issu d'une famille noble, il étudie au collège jésuite de La Flèche, puis à Poitiers où il obtient une licence en droit en 1616. Il voyage en Europe, sert dans l'armée, vit à Amsterdam en exil volontaire pour la liberté de pensée, et meurt à Stockholm invité par la reine Christine de Suède, probablement d'une pneumonie due au froid.  &lt;/p&gt;&lt;p&gt; &lt;a href=&quot;https://www.youtube.com/@paroledephilosophe/search?query=descartes&quot;  title=&quot;La philosophie de Descartes par Parole de philosophe&quot;&gt;Sa pensée &lt;/a&gt; est basée sur l'idée que la connaissance doit être fondée sur la raison et la logique, plutôt que sur la tradition ou l'autorité et que la science doit être basée sur des mathématiques rigoureuses, ce qui a conduit à l'adoption de la géométrie dans les sciences naturelles. &lt;/p&gt; &lt;p&gt;Il a également formulé une théorie de la dualité de la nature, selon laquelle l'univers est divisé en deux parties distinctes : la matière et l'esprit. Selon cette théorie, la matière est soumise aux lois de la physique, tandis que l'esprit est libre et capable de penser par lui-même. Il applique le doute hyperbolique (sur les sens, le rêve, un &quot;malin génie&quot;) pour atteindre l'évidence : &quot;Je pense, donc je suis&quot;, prouvant l'existence de l'ego cogitans (esprit pensant). Il distingue res cogitans (pensée immatérielle) et res extensa (matière étendue), fondant le dualisme cartésien, et conçoit Dieu comme garant de la vérité claire et distincte. Sa physique mécaniste voit l'univers comme une machine divine, préfigurant la science moderne. /p&gt; &lt;p&gt;En plus de ses contributions à la philosophie et à la science, il  a également écrit sur de nombreux autres sujets, notamment la métaphysique, &lt;a href=&quot;https://www.youtube.com/watch?v=BFFa7fHv_1I&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Sommes nous vraimant libre par le Précepteur&quot;&gt;la liberté&lt;/a&gt;,  &lt;a href=&quot;https://www.youtube.com/watch?v=dykLwHWB7qk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Peut on prouver l'existence de Dieu par le Précepteur&quot;&gt;l'existence de Dieu&lt;/a&gt;, la théologie et la politique. &lt;/p&gt; &lt;p&gt;Il était en opposition totale avec la pensée de Spinoza car ils conçoivent l'union de l'âme et du corps de manière très différente. Tandis que Descartes voit deux substances qui agissent l'une sur l'autre, pour Spinoza, c'est une seule et même chose, vue sous deux aspects différents.&lt;/p&gt;  &#10; &lt;audio controls title=&quot;meditations metaphysiques rené Descartes  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22789-31.10.2025-ITEMA_24296808-2025C53456E0008-NET_MFC_2769CAD8-FF20-4C7A-AB24-4D8965BD8B85-21-07dab51b3250d9a22eaab62a5c04edeb.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" display="https://www.laphilo.fr/pho/aarnauld-mini.webp" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Blaise_Pascal&quot; title=&quot;Blaise PASCAL par Wikipédia&quot;&gt; Blaise PASCAL&lt;/a&gt;  était un mathématicien, philosophe et écrivain français. Il a inventé à 19 ans, la première calculatrice mécanique, connue sous le nom de &quot;machine de Pascal&quot;. Il fut ensuite célèbre pour son &lt;a href=&quot;https://blaisepascal.bibliotheques-clermontmetropole.eu/son-oeuvre/pascal-savant/mathematiques/le-triangle-arithmetique&quot;  title=&quot;Le triangle arithmétique par Clermont metropole&quot;&gt; &quot;Triangle de Pascal&quot; &lt;/a&gt;, un arrangement de nombres qui est devenu un élément fondamental de la théorie des probabilités et de l'algèbre combinatoire. Il a aussi étudié la pression atmosphérique et a contribué à la compréhension de la manière dont la pression varie avec l'altitude. L'unité de pression &quot;pascal&quot; (Pa) porte son nom.  &lt;/p&gt; &lt;p&gt;&#10;Il était un chrétien dévot, et sa philosophie a été profondément influencée par sa foi. Il a écrit &lt;a href=&quot;https://www.youtube.com/watch?v=3uIjGv6jfSE&amp;ab_channel=Kosmos&quot;   title=&quot;Pensées par Kosmos&quot;&gt; &quot;Pensées&quot;&lt;/a&gt;, ce recueil de pensées, d'aphorismes et de réflexions où  Il a développé l'argument connu sous le nom de &lt;a href=&quot;https://www.youtube.com/watch?v=FoWFLpm8eX0&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;Le pari de Pascal par Alain Bajomée&quot;&gt; &quot;pari de Pascal,&quot;&lt;/a&gt; qui suggère que, même en l'absence de preuves rationnelles concluantes de l'existence de Dieu, il est plus raisonnable de &lt;a href=&quot;https://www.youtube.com/watch?v=6KLWy3dWFMw&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;le pari par Le Précepteur&quot;&gt;parier sur son existence&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;   Voici quelques-unes des contributions les plus importantes : &lt;p&gt;&#10;&lt;dd&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=OL4fFfld9Pw&amp;ab_channel=Kosmos&quot;  title=&quot;le pouvoir par Kosmos&quot;&gt;- La condition humaine :&lt;/a&gt;  Il l'aborde avec une perspective réaliste et parfois pessimiste. Il explore la vulnérabilité de l'homme, sa nature pécheresse et sa tendance à la vanité. Il souligne également l'incertitude de la vie humaine et la fragilité de l'existence. &lt;/dd&gt;&#10;&lt;dd&gt;  - Le désespoir et l'angoisse : Il a exploré le sentiment de vide et de malaise que les êtres humains peuvent ressentir lorsqu'ils sont confrontés à l'absurdité de la vie. Il a suggéré que la quête de sens et de bonheur peut être trouvée dans une relation personnelle avec Dieu.  &lt;/dd&gt;&#10;&lt;dd&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=CNr84ZlVfVY&amp;t=668s&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;le coeur à ses raisons par Le Précepteur&quot;&gt;La pensée et le cœur :&lt;/a&gt; Il a fait une distinction entre la &quot;raison du cœur&quot; et la &quot;raison de l'esprit.&quot; Il a soutenu que certaines vérités, en particulier celles liées à la foi et à la spiritualité, ne peuvent pas être pleinement saisies par la seule raison intellectuelle, mais nécessitent une approche du cœur et de l'émotion. &lt;/dd&gt;&#10;&lt;dd&gt; - La critique du rationalisme excessif :  qui réduisait toute connaissance à la raison et à la logique. Il croyait que la raison seule ne pouvait pas répondre à toutes les questions importantes de la vie et que l'expérience émotionnelle et spirituelle était tout aussi cruciale. &lt;/dd&gt;  &lt;audio controls title=&quot;Blaise Pascal, vers l'infini et au-delà par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-24.09.2018-ITEMA_21822263-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Nicole&quot; title=&quot; Wikipedia&quot;&gt;Pierre NICOLE&lt;/a&gt; était un philosophe, théologien, logicien et polémiste français, proche de Port-Royal et du mouvement janséniste. Né à Chartres, il enseigna la littérature et la philosophie à Port-Royal des Champs, où il collabora étroitement avec Antoine Arnauld. Il participa également à la défense des thèses jansénistes et fut lié au milieu intellectuel de Pascal. Son œuvre est toutefois plus diverse que celle d’un simple polémiste religieux : elle comprend des écrits de logique, de théologie, de morale et de politique. &lt;/p&gt; &lt;p&gt; Il est surtout connu comme le coauteur, avec Arnauld, de &lt;a href=&quot;https://www.youtube.com/watch?v=Gt4zoFWEKLM&quot; title=&quot;arnauld et Nicole, la logique ou l’art de penser par Sobrecrate&quot;&gt; la Logique ou l’art de penser,&lt;/a&gt;  publiée en 1662. Cet ouvrage, appelé communément « Logique de Port-Royal », présente la logique non seulement comme un ensemble de règles abstraites, mais comme un art pratique destiné à former le jugement. Il étudie successivement les idées, les jugements, les raisonnements et la méthode. Pour lui, bien penser suppose de lutter contre les préjugés, les passions et les habitudes intellectuelles qui déforment notre rapport à la vérité. &lt;/p&gt; &lt;p&gt;  Mais sa contribution la plus personnelle se trouve probablement dans  &lt;a href=&quot;https://www.fabula.org/revue/document1063.php&quot; title=&quot;la morale à l’essai par fabula&quot;&gt; les Essais de morale, &lt;/a&gt; dont la publication commence en 1671. Il y analyse les comportements humains, les relations sociales, l’éducation, la politique et les devoirs religieux. Sa morale est profondément augustinienne : l’homme naturel est dominé par l’amour-propre, c’est-à-dire par la tendance à rechercher son intérêt, son prestige et l’approbation des autres. Même les actions qui semblent généreuses peuvent donc être motivées par une recherche cachée de reconnaissance. &lt;/p&gt; &lt;p&gt;  Cette analyse le conduit à une vision assez pessimiste de la nature humaine. Il se méfie des prétendues vertus héroïques et montre que la société repose souvent sur des intérêts dissimulés, des conventions et des compromis. Cependant, il ne conclut pas qu’il est impossible de vivre moralement : ses Essais de morale ont précisément pour objectif d’enseigner une conduite plus lucide, plus modeste et plus charitable. La morale doit commencer par la connaissance de notre faiblesse, car celui qui ignore son amour-propre risque de prendre ses intérêts personnels pour de véritables exigences morales. &lt;/p&gt; " r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" display="https://www.laphilo.fr/pho/pnicole-mini.webp" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baruch_Spinoza&quot;  title=&quot; Wikipedia&quot;&gt; Baruch SPINOZA&lt;/a&gt; était un philosophe hollandais et un penseur influent en opposition à Descartes en son époque. &lt;/p&gt; &lt;p&gt; Sa philosophie &lt;a href=&quot;https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le déterminisme par le Précepteur&quot;&gt;Déterministe.&lt;/a&gt; se caractérise par sa vision &lt;a href=&quot;https://fr.wikipedia.org/wiki/Monisme&quot;    title=&quot;Le monisme est la position philosophique qui affirme l'unité indivisible de l'être&quot;&gt;moniste&lt;/a&gt; de l'univers, selon laquelle tout ce qui existe est une expression de la même substance divine, qu'il appelle &lt;a href=&quot;https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Dieu égale nature&quot;&gt;Dieu ou Nature&lt;/a&gt; et elle est souvent associée au rationalisme, à l'athéisme et au panthéisme. &lt;/p&gt; &lt;p&gt; Pour lui, la raison est la clé de la liberté et du bonheur. Il affirme que  &lt;a href=&quot;https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos&quot;  title=&quot;Les passions tristes par Kosmos&quot;&gt;les passions.&lt;/a&gt; peuvent nous éloigner de la vérité et nous rendre esclaves de nos désirs. &lt;/p&gt; &lt;p&gt;Pour être libre, l'homme doit comprendre la nature des choses et apprendre à contrôler ses passions. Cela implique une acceptation de la nécessité et de la causalité, car tout ce qui arrive est le résultat de la nature des choses et que, de ce fait, &lt;a  href=&quot;https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;Le libre arbitre n'est il qu'une illusion? par le Précepteur&quot;&gt;le libre arbitre n'existe pas.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Dans sa célèbre œuvre &quot;L'Éthique&quot;, il élabore une théorie éthique basée sur l'idée que la raison est la clé de la liberté et du bonheur avec sa notion de &lt;a href=&quot;https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;Le conatus par le Précepteur&quot;&gt;&quot;Conatus&quot;.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; En politique, il est souvent associé à la défense de la liberté d'expression et de la tolérance religieuse. Il a écrit un ouvrage intitulé  &lt;a href=&quot;https://www.youtube.com/watch?v=Zqt0QZVrTkI&quot;   title=&quot;Le Traité TP par PrepaUp&quot;&gt;&quot;Le Traité théologico-politique&quot;&lt;/a&gt; dans lequel il soutient que la religion doit être séparée de l'État et que chacun doit être libre de pratiquer sa religion sans être persécuté.&lt;/p&gt;    &lt;audio controls title=&quot;Spinoza est il le philosophe du bonheur ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&lt;p&gt; &lt;/p&gt;" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nicolas_Malebranche&quot; title=&quot; Wikipedia&quot;&gt;Nicolas MALEBRANCHE&lt;/a&gt; était un philosophe et théologien français, connu pour ses travaux en métaphysique, en épistémologie et en philosophie de la religion. En 1660, il rejoint l'Oratoire, une congrégation religieuse catholique, où il se consacre à l'étude de la philosophie et de la théologie et il découvre les travaux de Descartes, qui auront une influence majeure sur sa pensée. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de  &lt;a href=&quot;https://www.youtube.com/watch?v=3YvitSjZ2_4&amp;t=326s&quot; title=&quot;Malebranche : Occasionalism par Leevark&quot;&gt;l'occasionalisme&lt;/a&gt;, qu'il développe dans son ouvrage majeur &quot; De la recherche de la vérité&quot;. Selon lui, les idées que nous avons des objets existent dans l'entendement divin, et c'est par la médiation de Dieu que nous accédons à ces idées. Cette théorie s'oppose à l'empirisme et à l'idée que nos perceptions sont directement causées par les objets eux-mêmes.  Il rejette l'interaction directe entre l'âme et le corps, une idée défendue par Descartes. Selon lui, l'âme et le corps ne peuvent pas agir l'un sur l'autre directement. Au lieu de cela, Dieu coordonne les états de l'âme et les états du corps de manière harmonieuse, sans qu'il y ait de causalité directe entre eux. Il a développé une théorie selon laquelle Dieu agit selon des &quot;lois générales&quot; plutôt que par des interventions particulières, ce qui laisse une place à la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Libert%C3%A9_(philosophie)&quot;  title=&quot;La liberté par Wikipedia&quot;&gt;liberté humaine&lt;/a&gt; tout en maintenant la souveraineté divine. &lt;/p&gt; &lt;p&gt;Ses oeuvres principales : &lt;/p&gt; &#10;&lt;dd&gt; -De la recherche de la vérité : Théories sur la perception, la causalité et la métaphysique.  &lt;/dd&gt; &#10;&lt;dd&gt; - Traité de la nature et de la grâce : Relation entre la grâce divine et les lois de la nature. &lt;/dd&gt;&#10;&lt;dd&gt; - Entretiens sur la métaphysique et la religion : Un dialogue qui résume et défend ses idées. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il reste une figure importante dans l'histoire de la philosophie, notamment pour sa tentative de concilier la pensée cartésienne avec une vision profondément théocentrique du monde. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;   &lt;audio controls title=&quot; L’imagination selon Descartes et Malebranche par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-16.01.2024-ITEMA_23616134-2024C48904S0016-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Voltaire&quot;   title=&quot; Wikipedia&quot;&gt; VOLTAIRE&lt;/a&gt;, de son vrai nom François-Marie Arouet, est un philosophe de l'époque des  &lt;a href=&quot;https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;t=380s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot; La philosophie des lumières par le Précepteur &quot;&gt;Lumières&lt;/a&gt; (ou Illuministe) en France. Il était aussi écrivain, poète, dramaturge et philosophe. &lt;/p&gt; &lt;p&gt;&#10;Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href=&quot;https://www.youtube.com/watch?v=XE1Z8jpVJUA&quot; title=&quot; la vie de Voltaire  par Portrait Historiques&quot;&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation . Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;&#10;Voltaire, qui était &lt;a href=&quot;https://www.youtube.com/watch?v=RO_aeh1cBgA&amp;ab_channel=Kurious&quot;   title=&quot; Regard critique sur le déîsme par Kurious &quot;&gt;déiste&lt;/a&gt; s'est opposé aux abus de l'Église catholique et a plaidé en faveur de la tolérance envers les minorités religieuses. Dans son ouvrage &lt;a href=&quot;https://www.youtube.com/watch?v=1RlS8GKL7SU&quot;  title=&quot; Voltaire-Tolérence par Culture Philo &quot;&gt;&quot;Traité sur la tolérance&quot;&lt;/a&gt;, (1763) il a condamné les persécutions religieuses et a défendu le principe selon lequel chaque individu devait être libre de pratiquer sa religion sans être inquiété. &lt;/p&gt; &lt;p&gt;&#10;Son ouvrage le plus connu est  &lt;a href=&quot;https://www.youtube.com/watch?v=kom2zFvrj5I&amp;ab_channel=T%C3%A9l%C3%A9Crayon&quot;  title=&quot; Candide de Voltaire par TéléCrayon &quot;&gt;&quot;Candide&quot;&lt;/a&gt; (1759), un conte philosophique qui critique les idées optimistes de l'époque et souligne les absurdités et les injustices du monde. &lt;/p&gt; &lt;p&gt;&#10;La contribution de Voltaire à la philosophie se caractérise par son engagement envers la raison, la liberté et la justice. Il a influencé de nombreux penseurs ultérieurs et a contribué à jeter les bases de la pensée libérale et humaniste qui a marqué les siècles suivants. Sa défense de la liberté d'expression reste une valeur fondamentale de nos sociétés démocratiques aujourd'hui. &lt;/p&gt; &lt;audio controls title=&quot;Voltaire et les Lumières par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15537-13.01.2021-ITEMA_22540842-2021C24632S0013.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)&quot;    title=&quot; Wikipedia&quot;&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href=&quot;https://www.youtube.com/watch?v=kbpEAw2gl40&quot; title=&quot; David Hartley par Crevoisier Philippe&quot;&gt; développement de la psychologie &lt;/a&gt;  , en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt; - La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la &quot;substance médullaire&quot; (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt; - La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des &quot;vibratiuncules&quot; (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs &quot;vibratiuncules&quot; respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href=&quot;https://www.youtube.com/shorts/BuqpLB9V41c&quot;  title=&quot; David Hartley par timelinephilosopher&quot;&gt;  le fondement des idées et des pensées &lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des &quot;vibratiuncules&quot; de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &quot;Observations on Man, his Frame, his Duty, and his Expectations&quot;, publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt; &#10;- L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt; &#10;- Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; " r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Julien_Offray_de_La_Mettrie&quot;    title=&quot; Wikipedia&quot;&gt;Julien Onfray de la METTRIE&lt;/a&gt;  était un philosophe et médecin français des Lumières, connu pour son &lt;a href=&quot;https://www.youtube.com/watch?v=ATn23C-jw1M&quot;  title=&quot; Traité du bonheur de la Mettrie par Voyage interieur&quot;&gt; matérialisme radical &lt;/a&gt; et son athéisme provocateur. Médecin militaire, il fut exilé de France après la publication de ses idées controversées, avant de trouver refuge auprès de Frédéric II de Prusse à Potsdam. &lt;/p&gt; &lt;p&gt; Dans L’Homme machine (1747), il affirme que l’être humain est une machine purement matérielle : l’âme n’existe pas comme substance distincte, mais émerge des processus physiques du cerveau et du corps, sans besoin de Dieu ou d’esprit immatériel. Il s’inspire de Descartes, mais pousse le mécanisme jusqu’au bout en rejetant le dualisme corps-âme.  &lt;/p&gt; &lt;p&gt; Ses écrits, comme Histoire naturelle de l’âme (1745), scandalisèrent l’Église et les autorités : ses livres furent brûlés publiquement et il perdit son poste aux Gardes-Françaises. Défenseur d’un hédonisme sensualiste, il prône le  &lt;a href=&quot;https://www.youtube.com/watch?v=FH2TDimoh7Q&quot;  title=&quot; La Mettrie ou l’art de jouir par Parole de philosophe&quot;&gt; plaisir comme seul bien moral,&lt;/a&gt;  sans morale transcendante. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés : - Histoire naturelle de l’âme (1745) : Critique du dualisme et fondement matérialiste. - L’Homme machine (1747) : Thèse principale sur l’automatisme humain. - L’Homme plante (1748) : Étend le mécanisme aux végétaux et animaux. &lt;/p&gt; &lt;p&gt; Précurseur du matérialisme moderne et de la philosophie de la vie, il influence Diderot et les Encyclopédistes, mais reste marginalisé pour son radicalisme. Il anticipe des idées sur l’évolution et la cybernétique en voyant l’humain comme un système organisé. &lt;/p&gt; &#10;" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Hume&quot;  title=&quot; Wikipedia&quot;&gt;David HUME&lt;/a&gt; était un philosophe, historien et économiste écossais de l'ère des Lumières. Il est surtout connu pour ses contributions à la philosophie empirique, la théorie de la connaissance, la métaphysique, l'éthique et l'esthétique. &lt;/p&gt; &lt;p&gt; Hume était un sceptique et a cherché à examiner de manière critique les idées préconçues et les &lt;a  href=&quot;https://www.youtube.com/watch?v=CLIoxw6TXuk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Tout n'est que croyance  par Le Précepteur&quot;&gt;croyances reçues&lt;/a&gt;. Il a rejeté les arguments métaphysiques qui ne pouvaient pas être fondés sur l'expérience directe, et a affirmé que les connaissances humaines étaient basées sur les impressions et les idées que nous en avons. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de &lt;a  href=&quot;https://www.youtube.com/watch?v=ftd3vjw9lSU&quot;  title=&quot; la causalité par Skarblown Animations&quot;&gt;la causalité&lt;/a&gt;, qui affirme que nous ne pouvons pas connaître la relation de cause à effet entre deux événements par simple observation, mais que nous sommes amenés à croire en une telle relation en raison de notre expérience passée.  &lt;/p&gt; &lt;p&gt; En éthique, il a affirmé que la morale était basée sur des sentiments plutôt que sur la raison et qu'elle ne peut pas être déduite de principes rationnels, mais doit être fondée sur l'empathie et la sympathie envers les autres.  &lt;/p&gt; &lt;p&gt; Il a également souligné l'importance du bonheur et du plaisir dans la vie, affirmant que ce sont des aspects essentiels de notre existence et de notre &lt;a  href=&quot;https://www.youtube.com/watch?v=52077nWSkPM&amp;t=11s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;l'identité par le Précepteur&quot;&gt;identité&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il a écrit sur la religion et a critiqué les arguments traditionnels pour l'existence de Dieu en affirmant que la religion était basée sur la superstition plutôt que sur la raison, et que la croyance en Dieu était fondée sur l'habitude plutôt que sur la preuve. &lt;/p&gt;  &lt;audio controls title=&quot;Pourquoi faut il lire David Hume par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22838-02.02.2022-ITEMA_22927004-2022C45539E0018-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;&#10;" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau&quot; title=&quot; Wikipedia&quot;&gt; Jean-Jacques ROUSSEAU&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Les Lumières par le Précepteur &quot;&gt; des lumières&lt;/a&gt; et écrivain suisse-français, défenseur de la liberté et de l'égalité. Il et est surtout connu pour son livre &lt;a href=&quot;https://www.youtube.com/watch?v=tToAS8pUXzU&quot;   title=&quot;Le texte fondateur par Alain Bajomée &quot;&gt;&quot;Du contrat social&quot;&lt;/a&gt; , dans lequel il développe sa théorie politique ainsi que &lt;a href=&quot;https://www.youtube.com/watch?v=3-mPXD5CkJc&quot;  title=&quot;L'Emile par Librairie Vrin&quot;&gt;&quot;Emile&quot; &lt;/a&gt;considéré comme un &quot;traité d'écucation&quot; ou sa théorie de l'homme. &lt;/p&gt; &lt;p&gt;&#10;Rousseau a également écrit sur la philosophie morale, la théorie de l'éducation et la nature humaine et  &lt;a href=&quot;https://www.youtube.com/watch?v=cUtO8U9QbZs&amp;ab_channel=LePr%C3%A9cepteur&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Le désir par le Précepteur &quot;&gt; le désir&lt;/a&gt;. Il croyait que &lt;a href=&quot;https://www.youtube.com/watch?v=FpXdTgerxiI&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L''homme est naturellement bon par le Précepteur &quot;&gt; l'homme est naturellement bon&lt;/a&gt;, mais corrompu par la société et la civilisation. Il a également affirmé que la liberté individuelle est essentielle à l'épanouissement humain et que les institutions politiques doivent être créées pour protéger les droits et les libertés des individus. &lt;/p&gt; &lt;p&gt;  Il est souvent considéré comme un précurseur du  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0776-555x_1927_num_29_16_2482#&quot;  title=&quot;La philosophie romantique par Persée &quot;&gt; romantisme&lt;/a&gt; en raison de son accent mis sur les émotions, la nature, l'individualité et la subjectivité. Il a exprimé une méfiance envers la société civilisée et a prôné un retour à la nature et à la simplicité. Il a également souligné l'importance de l'émotion et de l'expérience personnelle dans la compréhension du monde, remettant en question l'approche rationnelle et scientifique des Lumières. Ses idées ont eu une influence significative sur les écrivains et les artistes romantiques ultérieurs, qui ont valorisé l'expression émotionnelle et l'expérience individuelle dans leurs œuvres.&lt;/p&gt; &lt;p&gt;&#10;En termes de théorie de l'éducation, Rousseau a proposé une approche de l'apprentissage basée sur l'observation et l'expérience plutôt que sur la mémorisation et l'étude académique et a souligné l'importance de la créativité et de l'expression personnelle dans l'éducation. &lt;/p&gt; &lt;p&gt; &lt;audio controls title=&quot;Rousseau, l'anti-économiste par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10081-28.12.2022-ITEMA_23239091-2022C29629E0022-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Denis_Diderot&quot;  title=&quot; Wikipedia&quot;&gt; Denis DIDEROT&lt;/a&gt; était un philosophe des Lumières français ainsi qu' un écrivain, éditeur et encyclopédiste influent.  Il est surtout connu pour son rôle de coéditeur et contributeur majeur de &lt;a href=&quot;https://www.youtube.com/watch?v=LuRI5zg7tJY&quot;   title=&quot;Diderot 1750 Encyclopedia par OER Project &quot;&gt;l'Encyclopédie, &lt;/a&gt; ou Dictionnaire raisonné des sciences, des arts et des métiers.&lt;/p&gt; &lt;p&gt;&#10;Il était un fervent défenseur de la raison et de l'esprit critique et il rejetait les dogmes et les traditions aveugles, encourageant à la place l'examen rationnel et la remise en question des croyances établies. Il croyait en la capacité de l'homme à comprendre le monde à travers la science, la philosophie et l'observation directe. &lt;/p&gt; &lt;p&gt;&#10;Il était un matérialiste convaincu et soutenait que l'univers était composé de matière en mouvement constant et rejetait l'idée d'une entité divine créatrice. Il écrit &lt;a href=&quot;https://www.youtube.com/watch?v=vkBC-MDLH_A&amp;ab_channel=BouillondeCulture&quot;  title=&quot;Le rêve d'Alembert  par Bouillon de culture&quot;&gt;Le Rêve de D’Alembert&lt;/a&gt;, un ensemble de trois dialogues philosophiques ou il expose sa théorie sur la vie et la nature. Sa vision matérialiste était étroitement liée à sa pensée scientifique et à son intérêt pour les sciences naturelles. &lt;/p&gt; &lt;p&gt; Il écrit aussi un roman (ou plutôt un anti-roman) &lt;a href=&quot;https://www.youtube.com/watch?v=NtxGWQ89g_k&quot; title=&quot;Jacques le Fataliste  par Kosmos&quot;&gt;&quot;Jacques le Fataliste et son maître&quot;&lt;/a&gt; où il refuse le cloisonnement et se positionne en rupture avec les conventions et invente une liberté à l'égard des pratiques existantes en France au XVIIIe siècle. &lt;/p&gt; &lt;p&gt;&#10;Il était un défenseur des libertés de pensée, d'expression et de la presse. Il critiquait les institutions religieuses et politiques oppressives de son époque et plaidait en faveur de l'égalité sociale et de la justice. Il croyait en l'éducation comme moyen d'émancipation et de progrès social, et il pensait que les individus devaient être libres de remettre en question les traditions et les dogmes établis. &lt;/p&gt; &#10;   &lt;audio controls title=&quot;Le Neveu de Rameau par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/10/s40/RF_38A1D24B-FA10-43F4-8B19-8C4921845BD4_GENE.MP3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Johann_Joachim_Spalding&quot; title=&quot; Wikipedia&quot;&gt;Johann Joachim SPALDING&lt;/a&gt; était un théologien protestant allemand, souvent considéré comme l’un des grands représentants des Lumières religieuses en Allemagne. Sa pensée cherche à concilier foi chrétienne, raison et morale, dans un esprit de réforme modérée plutôt que de rupture. &lt;/p&gt; &lt;p&gt; Dans son œuvre la plus célèbre, Die Bestimmung des Menschen (1748), il réfléchit au sens de la vie humaine. Pour lui, l’être humain n’est pas fait seulement pour satisfaire ses besoins matériels, mais pour se développer intérieurement, moralement et spirituellement. &lt;/p&gt; &lt;p&gt; Sa philosophie religieuse défend l’idée d’une religion naturelle compatible avec la Révélation. Il refuse le dogmatisme rigide et l’orthodoxie autoritaire, et insiste sur une foi plus vivante, fondée sur la conscience, le bon sens et l’expérience intérieure. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande importance &lt;a href=&quot;https://www.persee.fr/doc/ephe_0000-0002_1979_num_92_88_18346&quot;  title=&quot;problèmes de la théologie allemande par persée&quot;&gt;au sentiment religieux. &lt;/a&gt;  Dans son ouvrage de 1789, il montre que les émotions et la vie intérieure ont une vraie place dans le christianisme, sans que cela supprime l’exigence morale. Il représente une forme de christianisme éclairé : une religion raisonnable, morale et personnelle, qui veut rendre la foi plus humaine et plus intelligible. Son influence a compté dans la théologie protestante allemande, notamment dans le courant appelé néologie. &lt;/p&gt; &#10;" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" display="https://www.laphilo.fr/pho/jjspalding-mini.webp" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" display="https://laphilo.fr/photo/jjspalding.webp" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Bonnet_(naturaliste)&quot;  title=&quot; Wikipedia&quot;&gt;Charles BONNET&lt;/a&gt;  était un philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie et sa découverte de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Paling%C3%A9n%C3%A9sie&quot;  title=&quot;palingénésie par Wikipedia&quot;&gt;parthénogenèse. &lt;/a&gt; Il  étudie la botanique et l'entomologie dès sa jeunesse, influencé par Newton, Leibniz et Malebranche. Malgré des problèmes de vue et d'ouïe précoces, il devient membre du Conseil des Deux-Cents et correspondant de l'Académie des sciences de Paris. &lt;/p&gt; &lt;p&gt; Il démontre en 1745 la reproduction par parthénogenèse chez les pucerons, obtenant onze générations sans fécondation, et étudie la régénération des vers, des limaçons et des pattes d'écrevisse. Ses Recherches sur l'usage des feuilles (1754) préfigurent la photosynthèse, et il défend la théorie de la préformation, où les germes préexistent depuis la Création. &lt;/p&gt; &lt;p&gt; Dans Essai de psychologie (1754) et Essai analytique sur les facultés de l'âme (1760), il développe un sensualisme spiritualiste, voyant les idées naître des sensations via les fibres cérébrales. Sa Palingénésie philosophique (1769) postule l'immortalité des âmes humaines et animales dans une échelle continue des êtres. &lt;/p&gt; &#10;" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Thiry_d%27Holbach&quot;  title=&quot; Wikipedia&quot;&gt;Paul Thiry d'HOLBACH&lt;/a&gt;  était un philosophe allemand et devient encyclopédiste, traduit des œuvres scientifiques allemandes et anglaises pour l'Encyclopédie de Diderot. Hôte du célèbre &quot;cénacle d'Holbach&quot;, salon fréquenté par Diderot, Rousseau, Helvétius et Adam Smith, il anime un foyer intellectuel anticlérical jusqu'à sa mort en 1789. &lt;/p&gt; &lt;p&gt; Il défend un matérialisme radical: l'univers se compose uniquement de matière et de mouvement, régi par des  &lt;a href=&quot;https://www.youtube.com/watch?v=x99DRdMAd08&quot;  title=&quot;Essai sur l'art de ramper à l'usage des courtisans - D'Holbach&quot; par Vox Plebeia&quot;&gt;lois causales &lt;/a&gt; nécessaires, excluant Dieu ou toute intervention surnaturelle. Athée virulent, il combat les religions comme sources d'erreur, de peur et de superstition dans des pamphlets pseudonymes comme &lt;a href=&quot;https://www.youtube.com/watch?v=8Uohr5Y9xx0&quot; title=&quot;Religions Are ROTTING ILLUSIONS | Baron d’Holbach par Unfiltered Philosophy&quot;&gt;&quot;Le Christianisme dévoilé&quot; &lt;/a&gt; paru en 1761 ou &quot;Le Système de la nature&quot; (1770), bible de l'athéisme. &lt;/p&gt; &lt;p&gt; Sa morale est utilitariste et eudémoniste: la vertu réside dans l'utilité pour le bonheur individuel et collectif, fondée sur la raison et l'éducation, sans recours à la religion. Fataliste et déterministe, il prône la liberté sociale, l'égalité et une politique naturelle anti-despotique, influençant la Révolution française par sa critique des privilèges et du fanatisme. &lt;/p&gt; &#10;&#10;" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" display="&lt;a href=&quot;https://fr.wikipedia.org/wiki/Emmanuel_Kant&quot;  title=&quot; Wikipedia&quot;&gt; Immanuel KANT&lt;/a&gt; était un philosophe &lt;a href=&quot;https://la-philosophie.com/philosophie-lumieres&quot; style=&quot;color:#88A1E9&quot;   title=&quot;La philosophie des Lumières par la-philosophie.com&quot;&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant&quot;  title=&quot;La philosophie pratique de Kant de l'encyclopédie Wikipédia&quot;&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href=&quot;https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos&quot;   title=&quot;C'est quoi la raison pure par Kosmos&quot;&gt;&quot;Critique de la raison pure&quot;&lt;/a&gt; , publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href=&quot;https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos&quot;  title=&quot;La loi morale par Kosmos&quot;&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href=&quot;https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'impératif catégorique par le Précepteur&quot;&gt;&quot;Fondement de la métaphysique des moeurs&quot;&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href=&quot;https://la-philosophie.com/espace-public-et-democratie&quot;  title=&quot;Espace public par la-philosophie.com&quot;&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les &quot;Lumières&quot; comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href=&quot;https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume&quot;  title=&quot;Faculté de jugement par la-philosophie.com&quot;&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title=&quot;Le monde: entre déterminisme et liberté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edmund_Burke&quot;   title=&quot; Wikipedia&quot;&gt;Edmund BURKE&lt;/a&gt; était un philosophe et homme politique anglo-irlandais, considéré comme l'un des fondateurs du conservatisme moderne. Il s'opposa farouchement à la Révolution française, défendant l'évolution graduelle des institutions plutôt que les ruptures radicales. Il étudia au Trinity College avant de s'installer à Londres pour exercer le droit et entrer en politique. Député whig à la Chambre des communes de 1766 à 1794, il soutint l'indépendance américaine tout en critiquant les excès fiscaux britanniques. Sa célèbre Réflexions sur la Révolution de France (1790) alerta sur les dangers de la &quot;multitude perverse&quot; et du rejet des traditions. &lt;/p&gt; &lt;p&gt; Il  voyait la société comme un &quot;partenariat entre les vivants, les morts et ceux qui ne sont pas encore nés&quot;, valorisant les &lt;a href=&quot;https://www.youtube.com/watch?v=az1n7gSaKFE&quot; title=&quot;La tradition permet elle le changement  par la chaine de Velours&quot;&gt;préjugés hérités &lt;/a&gt; comme bank de sagesse collective supérieure à la raison individuelle. Dans Recherches philosophiques sur l'origine de nos idées du sublime et du beau (1757), il distingue le sublime (lié à la douleur, à la terreur et à Dieu) du beau (lié au plaisir et à la société), influençant l'esthétique romantique. Il prônait l'amélioration progressive de la nature humaine imparfaite, sans table rase. &lt;/p&gt; &lt;p&gt; Surnommé &quot;conservateur des Lumières&quot;, il inspira des penseurs comme Roger Scruton et reste une référence contre les utopies rationalistes. En France, il fut parfois taxé de réactionnaire, mais son libéralisme tempéré et son sens de la responsabilité des élites résonnent encore. &lt;/p&gt;  &lt;audio controls title=&quot;Les britaniques ; Burke et ses héritiers par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-10.12.2024-ITEMA_23958056-2024C48904S0345-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;&#10;&#10;" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" display="https://laphilo.fr/pho/ghlessing-mini.webp" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Johann_Kaspar_Lavater&quot;  title=&quot; Wikipedia&quot;&gt;Johann Kaspar LAVATER&lt;/a&gt;  était un théologien, poète et philosophe suisse, connu surtout comme pionnier de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Physiognomonie&quot;  title=&quot;Physiognomonie par Wikipedia&quot;&gt; &quot;la physiognomonie, &lt;/a&gt;  une pseudoscience liant traits du visage et caractère moral. Pasteur réformé à Zurich, il mêla mysticisme chrétien, irrationalisme et influences des Lumières tardives dans ses écrits. Né à Zurich dans une famille bourgeoise, il étudia la théologie et la philosophie au Collegium Carolinum sous Johann Jakob Bodmer. Ordonné en 1762, il devint diacre puis pasteur à l'église St-Pierre, tout en s'engageant contre la corruption locale, ce qui l'exila brièvement à Berlin. Ami de Goethe (dont la relation se tendit) et de Moses Mendelssohn, il fut blessé lors de l'invasion française de 1799 et mourut de ses blessures. &lt;/p&gt; &lt;p&gt; Sa grande œuvre, Physiognomische Fragmente zur Beförderung der Menschenkenntnis und Menschenliebe (1775-1778), postule que le visage révèle l'âme divine en l'homme, reliant esthétique, vertu et théologie. Influencé par l'Empfindsamkeit et le Sturm und Drang, il valorisait le sentiment sur la raison pure, explorant prophétie, miracles et palingénésie (résurrection). Critiqué par Lichtenberg pour son subjectivisme, il inspira poésie mystique et débats sur  &lt;a href=&quot;https://www.youtube.com/watch?v=LUxSlXIY-Zk&quot;  title=&quot;Johann Kaspar Lavater par Grow Wise&quot;&gt; &quot;l'intériorité humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il  incarna un pont entre piétisme, sentimentalisme et romantisme naissant, influençant esthétique et psychologie populaire en Europe. Ses idées déclinèrent avec les progrès scientifiques, mais sa quête d'une connaissance intuitive de l'homme reste débattue. &lt;/p&gt; &#10;" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet&quot;  title=&quot; Wikipedia&quot;&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe , mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href=&quot;https://www.youtube.com/watch?v=3G3kVl0GbA8&quot;  title=&quot;Condorcet féministe ? par Sud Radio&quot;&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote .  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href=&quot;https://www.youtube.com/watch?v=3G3kVl0GbA8&quot;  title=&quot;Condorcet et l’éloge de l’instruction par Culture philo&quot;&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href=&quot;https://www.youtube.com/watch?v=avTI9GHZX1I&quot;  title=&quot;Condorcet le paradoxe par Diable Positif&quot;&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la &quot;mathématique sociale&quot;, Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title=&quot;Nicolas de Condorcet par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nihilisme&quot;  title=&quot;Nihilisme par Wikipedia&quot;&gt; nihilisme &lt;/a&gt; et au &lt;a href=&quot;https://fr.wikipedia.org/wiki/Panth%C3%A9isme&quot;  title=&quot;Panthéisme par Wikipedia&quot;&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse &quot;querelle du panthéisme&quot; en révélant que Lessing s'était  &lt;a href=&quot;https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321&quot;  title=&quot;Jacobi et Spinoza par Persée&quot;&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu . &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du &quot;rien ne sort du néant&quot;) de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un &quot;saut de la foi&quot; hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. - David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. - Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; &#10;&#10;&#10;" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marcus_Herz&quot;  title=&quot; Wikipedia&quot;&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Immanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2&quot; title=&quot;Kant, Lettre à Marcus Herz du 21 février 1772 par Persée&quot;&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la &quot;révolution copernicienne&quot;), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent &quot;Betrachtungen aus der spekulativen Weltweisheit&quot;  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et &quot;Versuch über den Geschmack&quot; en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; " r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Friedl%C3%A4nder&quot;  title=&quot; Wikipedia&quot;&gt;David FRIEDLÄNDER&lt;/a&gt;  était un intellectuel, marchand et réformateur juif allemand, disciple de Moses Mendelssohn, plus connu comme pionnier de l'Haskalah (Lumières juives) et de la  &lt;a  href=&quot;https://www.persee.fr/doc/reval_0035-0974_1973_num_5_3_1989&quot;  title=&quot;D Friedlander et la réforme des communaités juives de prusse par Persée&quot;&gt; réforme religieuse &lt;/a&gt; que comme philosophe académique strict. Il prôna l'émancipation des Juifs par l'assimilation culturelle et une dédogmatisation du judaïsme, fusionnant rationalisme des Lumières et monothéisme mosaïque originel contre les rituels &quot;superstitieux&quot;. &lt;/p&gt; &lt;p&gt; Né à Königsberg, il s'installa à Berlin en 1770, fonda une usine de soie et intégra l'élite juive éclairée via son mariage avec la fille du banquier Daniel Itzig. Après la mort de Mendelssohn (1786), il mena la Haskalah berlinoise : création de la Chevrat Chinuch Ne’arim (école juive libre en 1778), traductions de prières en allemand, et plaidoyers pour l'égalité civile. Premier conseiller municipal juif à Berlin, il lutta contre les discriminations prussiennes. &lt;/p&gt; &lt;p&gt; Il rejetait le Talmud et les rites comme &quot;œuvres de sainteté, verbiage et futilités&quot;, défendant un judaïsme &quot;pur&quot; : monothéisme rationnel commun aux religions abrahamiques, sans dogmes christologiques ni observances contraignantes. Dans son Sendschreiben anonyme (1799) à l'ecclésiastique Wilhelm Teller, il proposa une union judéo-protestante déiste – baptême symbolique sans trinité, en échange d'émancipation –, vu comme opportuniste mais innovant pour le judaïsme réformé naissant. Il resta juif par fidélité au &quot;monothéisme mosaïque idéal&quot;, contrairement à sa famille convertie. &lt;/p&gt; &lt;p&gt; Précurseur du judaïsme réformé et de l'assimilation prussienne, Friedländer incarna le dilemme post-mendelssohnien : identité juive face à l'universalisme. Critiqué pour pragmatisme, il influença les réformes liturgiques et débats sur l'émancipation, bien que son projet fusionnel échouât face au romantisme montant. &lt;/p&gt; &#10;&#10;" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" display="https://laphilo.fr/photo/dfriedlander.webp" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joseph_de_Maistre&quot;  title=&quot; Wikipedia&quot;&gt;Joseph de MAISTRE&lt;/a&gt; était un philosophe, écrivain et diplomate savoyard, figure majeure de la contre-révolution et critique virulent des Lumières et de la Révolution française. Considéré comme un père de la pensée conservatrice moderne, il défend une vision organique de la société, hiérarchique et divinement ordonnée, où l'autorité monarchique et religieuse prime sur les idées contractualistes et individualistes. &lt;/p&gt; &lt;p&gt;  Pour lui, la Révolution française est un &lt;a href=&quot;https://www.persee.fr/doc/bude_0004-5527_1989_num_1_2_1393&quot; title=&quot;Sacré et sacrifice dans la pensée de Joseph de Maistre par Persée&quot;&gt;châtiment providentiel &lt;/a&gt; des excès des philosophes des Lumières, punissant l'athéisme et le rationalisme par la Terreur. Les sociétés ne naissent pas d'un contrat rationnel (comme chez Rousseau), mais d'une autorité divine imposée d'en haut; l'individu abstrait n'existe pas, il est façonné par la tradition et l'État.  Il prône une monarchie absolue et l'autorité suprême du Pape pour unifier l'Europe spirituellement et temporellement. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures sont : - &quot;Considérations sur la France&quot; paru en 1797 : Interprétation providentialiste de la Révolution comme mission divine de la France. - &quot;Essai sur le principe générateur des constitutions&quot; paru en 1809 :  &lt;a href=&quot;https://www.youtube.com/watch?v=oPEzOiEdrNE&quot;  title=&quot; L'oecuménisme de Joseph de Maistre par BAGLIS TV&quot;&gt;Les constitutions &lt;/a&gt; viennent de Dieu, non de la raison humaine et - &quot;Soirées de Saint-Pétersbourg&quot;  en1821, posthume : Théodicée justifiant le mal (guerre, sacrifice) comme partie du plan divin. &lt;/p&gt; &lt;p&gt; Il a eu une influence durablement le conservatisme, le romantisme contre-révolutionnaire et des penseurs comme Donoso Cortés, tout en étant critiqué pour son apologie de la violence. Sa pensée hiérarchique et anti-individualiste reste débattue face aux idéaux démocratiques modernes. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Troisième penseur, Joseph de Maistre. par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-26.10.2011-ITEMA_20317797-2011C12410S0299-NET_F022382B-0B64-4C5C-B335-284B201C884D_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Louis_de_Bonald&quot;  title=&quot; Wikipedia&quot;&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Tradition_primordiale&quot;  title=&quot; Tradition Primordiale de Maistre par Wikipedia &quot;&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. - Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. - Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href=&quot;https://www.youtube.com/watch?v=WMB9kethTWIe&quot;  title=&quot; Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations &quot;&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral&quot;  title=&quot; Maurrassisme par Wikipedia &quot;&gt; maurrassisme, &lt;a&gt; voyant la France comme &quot;nation-pilote&quot; pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant . &lt;/p&gt;&#10; &#10;&#10;//" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Antoine_Destutt_de_Tracy&quot;  title=&quot; Wikipedia&quot;&gt;Destutt de TRACY&lt;/a&gt; était un philosophe et idéologue français, fondateur et théoricien principal du courant philosophique des Idéologues. Né Antoine Louis Claude Destutt, comte de Tracy, dans une famille noble auvergnate, il fit une carrière militaire avant de se consacrer à la philosophie après son emprisonnement pendant la Terreur. Membre de l'Institut national et de l'Académie française, il joua un rôle central dans la vie intellectuelle française sous le Directoire et le Consulat. &lt;/p&gt; &lt;p&gt; Sa contribution majeure est la création de l'« idéologie » comme science des idées. Dans ses &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=DAz6QsBdeyg&quot;  title=&quot;Destrutt de DRACYi par Wikipedia Fan&quot;&gt;Éléments d'idéologie &lt;/a&gt; &lt;/em&gt; (5 volumes, 1801-1815), il cherche à fonder une science générale des idées qui analyserait leur formation à partir des sensations et des signes. S'inscrivant dans la tradition sensualiste de Condillac, il développe une sémiologie et une grammaire générale visant à purifier le langage de ses ambiguïtés et à fonder les sciences humaines sur des bases empiriques solides. Son projet était d'édifier une « science des sciences » qui servirait de fondement à l'enseignement et à la réforme sociale. &lt;/p&gt; &lt;p&gt; Sa &lt;em&gt;Logique&lt;/em&gt; et son &lt;em&gt;Commentaire sur l'Esprit des Lois de Montesquieu&lt;/em&gt; (1811) témoignent de son intérêt pour la philosophie politique libérale. Jefferson, qui admirait sa pensée, fit traduire son &lt;em&gt;Traité de la volonté&lt;/em&gt; en anglais. Ironiquement, le terme même d'« idéologie » qu'il avait forgé fut retourné contre lui par Napoléon, qui qualifiait les Idéologues d'esprits abstraits et dangereux. Marx reprit ensuite ce terme dans un sens radicalement différent. Destutt de Tracy reste une figure essentielle pour comprendre l'émergence des sciences humaines en France. &lt;/p&gt;" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Laromigui%C3%A8re&quot;  title=&quot; Wikipedia&quot;&gt;Pierre LAROMIGUIÈRE&lt;/a&gt; était un philosophe français, l'une des figures transitoires entre le sensualisme des Lumières et la philosophie spiritualiste du XIXe siècle. Né à Livinhac-le-Haut dans l'Aveyron, il fut d'abord prêtre avant la Révolution, puis professeur de philosophie à l'École centrale des arts et manufactures et enfin à la Sorbonne. Ses cours, qui attirèrent un public nombreux et enthousiaste dans les premières décennies du XIXe siècle, contribuèrent à renouveler l'enseignement de la philosophie en France. &lt;/p&gt; &lt;p&gt; Sa philosophie part du sensualisme de Condillac mais s'en écarte sur un point décisif : là où Condillac réduisait toutes les opérations de l'esprit à des sensations transformées, Laromiguière distingue soigneusement les sensations des opérations actives de l'attention, de la comparaison et du jugement. Cette distinction entre les facultés passives et les facultés actives de l'esprit ouvre la voie à une conception plus riche de la vie psychique, qui reconnaît la spécificité de l'activité intellectuelle irréductible à la simple réception sensorielle. &lt;/p&gt; &lt;p&gt; Dans ses &lt;em&gt;Leçons de philosophie&lt;/em&gt; (1815-1818), dont la clarté et l'agrément du style lui valurent un succès durable, il développe cette psychologie des facultés dans un cadre pédagogique accessible. Bien que sa pensée ait été éclipsée par le courant spiritualiste de Cousin et par le positivisme de Comte, Laromiguière représente une étape importante dans la constitution de la psychologie philosophique française. Sa manière de corriger Condillac par une attention accrue à l'activité de l'esprit préfigure les développements du spiritualisme ultérieur. &lt;/p&gt;" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Jean_Georges_Cabanis&quot; title=&quot; Wikipedia&quot;&gt;Pierre CABANIS&lt;/a&gt; était un médecin et philosophe français, figure majeure du groupe des Idéologues et pionnier d'une approche naturaliste de la vie psychique. Né à Cosnac en Corrèze, il fut introduit dans les cercles intellectuels parisiens par Turgot et fréquenta le salon d'Helvétius. Ami intime de Mirabeau dont il soigna les derniers jours, il participa activement à la vie politique de la Révolution et du Directoire, siégeant au Conseil des Cinq-Cents. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;Rapports du physique et du moral de l'homme&lt;/em&gt; (1802), est un essai audacieux pour fonder une science de l'homme sur des bases physiologiques. Cabanis y soutient que les phénomènes psychiques sont intimement liés aux processus organiques du corps : le cerveau secrète la pensée comme le foie sécrète la bile. Cette formule provocatrice, souvent mal comprise, visait en réalité à établir une méthode empirique pour l'étude de l'âme, refusant tout recours à des entités métaphysiques abstraites. &lt;/p&gt; &lt;p&gt; Médecin réformateur, il œuvra à la réorganisation des hôpitaux parisiens et milita pour une médecine fondée sur l'observation clinique plutôt que sur les théories scolastiques. Ses travaux contribuèrent à l'essor de l'hygiénisme et de la médecine sociale. Sa pensée, qui anticipe certains aspects du matérialisme médical du XIXe siècle, représente une étape importante dans la constitution des sciences humaines. Bien que les Idéologues aient été rabroués par Napoléon qui les rendait responsables des « idéologues abstraits », l'influence de Cabanis sur la médecine et la psychologie françaises fut durable. &lt;/p&gt;" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" display="https://www.laphilo.fr/pho/cabanis-mini.webp" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre-Paul_Royer-Collard&quot;  title=&quot; Wikipedia&quot;&gt;Pierre-Paul ROYER-COLLARD&lt;/a&gt;  était un philosophe et homme politique français, figure majeure du libéralisme modéré sous la Restauration et chef des Doctrinaires. Né en Champagne, il commence comme avocat au Parlement de Paris avant de s'engager politiquement. Pendant la Révolution, il soutient les Girondins et fuit la Terreur, se retirant dans ses terres. Sous la Restauration, il devient député de la Marne et préside la Chambre des députés (1828–1830), tout en enseignant l'histoire de la philosophie moderne à la Sorbonne. &lt;/p&gt; &lt;p&gt; Sa philosophie se présente comme un rejet du sensualisme de Condillac qui dominait le XVIIIᵉ siècle français. Il s'inspire du philosophe écossais Thomas Reid et introduit en France la doctrine du sens commun. Contrairement aux sensualistes, il distingue clairement la sensation (subjective, plaisir ou peine) de la perception (appréhension d'un objet externe). Pour lui, la perception implique un jugement spontané de l'esprit actif, non déductible des seuls sens. &lt;/p&gt; &lt;p&gt; Il développe un spiritualisme rigoureux : l'esprit humain est actif et capable de jugements autonomes. Le sens commun – cette faculté naturelle de distinguer le bien du mal, le vrai du faux – fonde la vie communautaire et remplace l'autorité surnaturelle. Par les principes de causalité et d'induction, la raison conduit nécessairement à l'idée d'une Première Cause (Dieu). Il affirme la supériorité irréductible de la personne humaine sur l'État, les personnes étant &lt;a  href=&quot;https://www.youtube.com/watch?v=15bNqKMiW_w&quot;  title=&quot;R Collard ou l’ambilalence des restaurations par Collège st Germain&quot;&gt;« faites à l'image de Dieu et douées d'immortalité ».&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Politiquement, il est un royaliste libéral qui considère la Révolution de 1789 comme irréversible. Il cherche à fonder une monarchie constitutionnelle stable entre l'Ancien Régime (les Ultras) et le totalitarisme napoléonien, puis la démocratisation trop rapide sous Louis-Philippe. Il incarne la « philosophie de la Charte » et influence profondément François Guizot. N'a presque rien publié de son vivant : ses écrits philosophiques ont été rassemblés après coup par son admirateur Théodore Jouffroy.  &lt;/p&gt; " r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" display="https://www.laphilo.fr/pho/pcollard-mini.webp" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Claude-Henri_de_Rouvroy_de_Saint-Simon&quot; title=&quot; Wikipedia&quot;&gt;Claude-Henri de ROUVROY, comte de SAINT-SIMON&lt;/a&gt; est un penseur et réformateur social français, issu d’une famille aristocratique qui revendiquait une lointaine parenté avec Charlemagne. Volontaire dans l’armée française envoyée soutenir l’indépendance américaine, il participe au siège de Yorktown avant de renoncer, sous la Révolution, à son titre de noblesse.  &lt;a href=&quot;https://maitron.fr/saint-simon-claude-henri-claude-henri-de-rouvroy-comte-de-saint-simon/&quot; title=&quot;saint simon par le maitron&quot;&gt;Spéculateur &lt;/a&gt; sur les biens nationaux, emprisonné pendant la Terreur, il connaît ensuite une vie mouvementée, tour à tour fortunée et misérable, entièrement vouée à la recherche d’une science nouvelle de la société. &lt;/p&gt; &lt;p&gt; Convaincu que la Révolution a détruit l’ancien ordre théologique et féodal sans encore bâtir l’ordre qui doit lui succéder, Saint-Simon appelle à fonder une organisation sociale confiée non plus aux militaires, aux juristes ou aux rentiers, mais aux savants, aux industriels et aux producteurs. Dans des ouvrages comme &lt;em&gt;L’Industrie&lt;/em&gt; ou &lt;em&gt;Du système industriel&lt;/em&gt;, il défend l’idée que le pouvoir politique doit être subordonné à la production utile : gouverner, pour lui, revient d’abord à administrer les choses et à organiser le travail, plutôt qu’à commander les hommes. &lt;/p&gt; &lt;p&gt; Il élabore ainsi une &lt;a href=&quot;https://fr.wikipedia.org/wiki/Saint-simonisme&quot; title=&quot;Saint-simonisme par Wikipedia&quot;&gt;philosophie de l’histoire&lt;/a&gt; fondée sur l’alternance de périodes « organiques » et « critiques », et annonce l’avènement d’un âge industriel où la science et la technique remplaceraient la théologie comme principe d’unité sociale. Son dernier livre, &lt;em&gt;Le Nouveau Christianisme&lt;/em&gt; (1825), publié l’année de sa mort, prône une religion de la fraternité entièrement tournée vers l’amélioration du sort des classes les plus pauvres, qu’il présente comme la fin ultime de toute organisation sociale et politique légitime. &lt;/p&gt; &lt;p&gt; Bien que ses écrits soient souvent fragmentaires et inachevés, Saint-Simon laisse une postérité considérable : ses disciples, réunis après sa mort en une école puis en une véritable Église saint-simonienne, diffusent et systématisent sa pensée sous le nom de saint-simonisme. Ce courant influencera profondément le socialisme utopique du XIXe siècle, la sociologie naissante d’Auguste Comte (un temps son secrétaire), ainsi que les grandes entreprises industrielles et financières du Second Empire, qui reprendront à leur compte son culte du progrès technique et de l’organisation rationnelle de la production. &lt;/p&gt;" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" display="https://www.laphilo.fr/pho/hssimon-mini.webp" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Maine_de_Biran&quot;  title=&quot; Wikipedia&quot;&gt;Maine de BIRAN&lt;/a&gt; était un philosophe français, considéré comme l'un des fondateurs de la philosophie de l'intériorité et du spiritualisme français. Né François-Pierre Gonthier de Biran à Bergerac en Dordogne, il commença sa carrière comme officier de la garde du roi, avant de se consacrer à la philosophie et à la vie politique locale en Périgord. Administrateur apprécié sous plusieurs régimes successifs, il fut député et sous-préfet, mais c'est à travers ses journaux intimes et ses &lt;a  href=&quot;https://www.youtube.com/watch?v=ayhmQ5WQfJk&quot;  title=&quot;Maine de Biran spiritualité &amp; phénoménologie par ICP&quot;&gt;essais philosophiques &lt;/a&gt; que son originalité s'exprima pleinement. &lt;/p&gt; &lt;p&gt; Sa pensée prend pour point de départ l'expérience immédiate de l'effort : c'est dans l'acte volontaire par lequel le moi exerce une résistance contre le corps propre que la conscience se saisit elle-même comme force et comme liberté. Contre le sensualisme de Condillac qui réduisait l'âme à la sensation passive, il soutient que l'activité volontaire constitue le fait primitif de la conscience. Cette découverte du « moi voulant » comme donnée irréductible de l'intériorité marque une rupture décisive dans la philosophie française. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;t &lt;a  href=&quot;https://www.persee.fr/doc/bupsy_0007-4403_1963_num_17_224_9102&quot;  title=&quot;Maine de Biran fondateur de la psychologie française par Persée&quot;&gt;Essai sur les fondements de la psychologie &lt;/a&gt; &lt;/em&gt; (1812) et ses nombreux &lt;em&gt;Mémoires&lt;/em&gt; rédigés pour les concours de l'Institut, développent une psychologie de l'effort qui distingue trois ordres d'existence : la vie animale (sensations), la vie humaine (volonté et conscience) et la vie de l'esprit (grâce et amour mystique). Cette trilogie, d'inspiration néo-platonicienne et chrétienne dans sa dernière phase, influença profondément Ravaisson, Bergson et tout le courant spiritualiste français. Ses &lt;em&gt;Journal&lt;/em&gt; et &lt;em&gt;Mémoire sur les perceptions obscures&lt;/em&gt; témoignent d'une introspection d'une subtilité et d'une profondeur rares. &lt;/p&gt;" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Charron&quot;  title=&quot; Wikipedia&quot;&gt;Pierre CHARRON&lt;/a&gt; était un philosophe, orateur et moraliste français dont   &lt;a href=&quot;https://revuecorpus.com/pdf/CORPUS%20N%C2%B055.pdf&quot; style=&quot;color:#88A1E9&quot; title=&quot; n°55  Charron par Corpus&quot;&gt; l'œuvre&lt;/a&gt; est profondément marquée par le contexte religieux et intellectuel de son époque, notamment les guerres de religion et l'humanisme renaissant. &lt;/p&gt; &lt;p&gt;  Son ouvrage &quot;Les Trois Vérités&quot; est une apologie de la religion catholique, rédigée en réponse aux arguments protestants. Elle vise à défendre la foi contre les athées, idolâtres, juifs, mahométans, hérétiques et schismatiques. Il est présenté comme un fervent défenseur de l'orthodoxie catholique, &lt;/p&gt; &lt;p&gt; Son 2ème ouvrage &quot;De la Sagesse&quot; est sans doute le plus célèbre et le plus influent. Ce &lt;a href=&quot;https://www.youtube.com/watch?v=6n3OmEeVudo&quot; title=&quot; Charron et l'invention d'une sagesse laîque par Photon&quot;&gt; traité de morale &lt;/a&gt;  et de philosophie, divisé en trois livres, expose une conception de la sagesse humaine qui sera très commentée et parfois critiquée pour ses implications jugées irréligieuses par certains car il révèle une pensée plus nuancée, imprégnée de scepticisme et d'une forme de moralisme laïque. &lt;/p&gt; &lt;p&gt; Il est profondément influencé par le scepticisme des  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Essais_(Montaigne)&quot; title=&quot; Essais de Montaigne par Wikipedia&quot;&gt; Essais de Montaigne&lt;/a&gt; et partage l'idée de la faiblesse de la raison humaine et l'incertitude des connaissances. Pour lui, il faut &quot;commencer&quot; par le doute, reconnaître &quot;l'ignorance, faiblesse, incertitude&quot; de la condition humaine. Ce  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Scepticisme_(philosophie)&quot; title=&quot;  scepticisme par Wikipedia&quot;&gt; scepticisme&lt;/a&gt; initial n'est pas une fin en soi, mais un point de départ pour l'acquisition de la sagesse. &lt;/p&gt; &lt;p&gt;  Il est l'un des penseurs qui contribuent à la séparation de la sphère morale de la sphère théologique. Il cherche à établir une éthique autonome, fondée sur la raison et la nature humaine, sans la subordonner entièrement à la foi. Il  invite à fuir la &quot;contagion du monde&quot; et à rechercher la solitude comme moyen d'amender l'intellect par rapport aux erreurs populaires. Il insiste sur la capacité de l'homme à être maître de sa volonté et à s'affermir dans la raison, ce qui peut être vu comme un précurseur de l'individualisme moderne. &lt;/p&gt; &lt;p&gt; Il  a joué un rôle important dans la transition de l'humanisme vers le rationalisme, en ouvrant la voie à une réflexion morale et philosophique plus autonome par rapport à la théologie. Son œuvre est un témoignage précieux des tensions intellectuelles et religieuses de son époque. &lt;/p&gt; " r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Giordano_Bruno&quot;  title=&quot; Wikipedia&quot;&gt; Giordano BRUNO&lt;/a&gt; était un philosophe et penseur italien, connue pour ses  &lt;a href=&quot;https://www.youtube.com/watch?v=21dM3ZJtYY0&amp;t=11s&quot; style=&quot;color:#88A1E9&quot; title=&quot;Giordano BRUNO de Calvin par Le Pro Presente &quot;&gt;idées cosmologiques&lt;/a&gt; et philosophiques radicales dont voici quelques-uns de ses concepts clés : &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&#10;&lt;p&gt; - L'univers infini : et peuplé d'une infinité de mondes habités. Cette vision s'opposait à la conception géocentrique de l'univers, qui plaçait la Terre au centre de tout.  &lt;/p&gt;&#10;&lt;p&gt; -  L'unité de la matière et de l'esprit : vision panthéiste de l'univers, où il croyait que la matière et l'esprit étaient inséparables et que l'univers était animé par une force vitale universelle. &lt;/p&gt;&#10;&lt;p&gt;  - La relativité du mouvement : le mouvement est relatif et qu'il n'y a pas de point de référence absolu dans l'univers. &lt;/p&gt;&#10;&lt;p&gt; - La liberté de pensée : la liberté de pensée et d'expression, s'opposant à l'autorité dogmatique de l'Église. Il croyait que la vérité ne pouvait être découverte que par la raison et l'expérience, et non par la révélation divine. &lt;/p&gt; &lt;p&gt;&lt;/p&gt; &lt;p&gt; En raison de  &lt;a href=&quot;https://nospensees.fr/les-meilleures-phrases-de-giordano-bruno/&quot; title=&quot;Giordano BRUNO par nospensees &quot;&gt;ses idées controversées&lt;/a&gt;, il a été contraint de quitter l'Italie et de voyager à travers l'Europe, dans des villes comme Genève, Paris, Londres et Prague, où il a enseigné et publié  &lt;a href=&quot;https://www.willeime.com/bruno.htm&quot; title=&quot;Giordano BRUNO par willeime &quot;&gt;ses œuvres&lt;/a&gt;. Il a été arrêté par l'Inquisition vénitienne et extradé à Rome. Après 8 ans de procès, il a été accusé d'hérésie pour ses idées et condamné à mort. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus importantes, on peut citer : &lt;/p&gt; &lt;p&gt; &lt;/p&gt;&#10;&lt;p&gt; -  &lt;a href=&quot;https://www.youtube.com/watch?v=vHfEKwAmhAQ&quot;  title=&quot;Giordano BRUNO par Filosofia&quot;&gt;&quot;De l'infinito, universo e mondi&quot;&lt;/a&gt;: Théorie de l'univers infini et des mondes multiples. &lt;/p&gt; &#10;&lt;p&gt; -&quot; La cena de le ceneri&quot; : Critique la philosophie aristotélicienne et défend les idées coperniciennes.&lt;/p&gt; &#10;&lt;p&gt; - &quot;De la causa, principio e uno&quot; : Nature de l'univers et l'unité de la matière et de l'esprit.&lt;/p&gt;  &lt;p&gt; &lt;/p&gt; &lt;p&gt;   &lt;p&gt; &lt;/p&gt;     &lt;audio controls title=&quot; Giordano BRUNO par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-16.11.2022-ITEMA_23198161-2015C3372E1085-NET_MFC_367A1BA4-BD9E-4C79-A1B2-C57FCE8CB809-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Thomas_Hobbes&quot;  title=&quot; Wikipedia&quot;&gt;Thomas HOBBES&lt;/a&gt; était un philosophe anglais et fondateur de la philosophie politique moderne connu pour son ouvrage majeur, &lt;a href=&quot;https://www.youtube.com/watch?v=8sYAaiDjf0U&amp;ab_channel=AlainBajom%C3%A9e&quot; title=&quot;Le Léviathan par Alain Bajomé&quot;&gt;&quot;Léviathan&quot;&lt;/a&gt;, publié en 1651, dans lequel il développe sa vision de la nature humaine et de la société. Il partait du constat que l'être humain est fondamentalement égoïste et cherchera toujours à obtenir ce qu'il désire, même si cela nuit aux autres, car &lt;a href=&quot;https://www.youtube.com/watch?v=isCVgDObx4c&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'homme est un loup pour l'homme par Le Précepteur&quot;&gt;&quot;L'homme est un loup pour l'homme&quot;&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Pour lui, cette tendance naturelle à l'égoïsme et à la violence rendait impossible la coexistence pacifique entre les hommes, à moins qu'ils ne se soumettent tous volontairement à une autorité souveraine forte. C'est pourquoi, la société doit être gouvernée par un pouvoir absolu, représenté par un souverain, qui impose l'ordre et la sécurité. &lt;/p&gt; &lt;p&gt;  Pour lui, le contrat social est un moyen pour les individus de renoncer à leur liberté naturelle en échange de la sécurité que leur offre l'Etat. Le souverain est donc le garant de cette sécurité, et il doit être obéi sans réserve, même si cela signifie restreindre certaines libertés individuelles. &lt;/p&gt; &lt;p&gt; &#10;Hobbes a également développé une théorie de l'Etat de nature, dans lequel les hommes vivraient dans un état de guerre perpétuelle, sans lois ni règles pour les protéger. Pour lui, l'Etat de nature était un état de violence, de peur et d'insécurité, et c'est pour échapper à cet état que les hommes ont créé la société. &lt;/p&gt;   &lt;audio controls title=&quot;Le pacte d'obéissance par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22060-04.04.2021-ITEMA_22630431-2012C12410E0123.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;&lt;p&gt; &lt;/p&gt;" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Gassendi&quot;  title=&quot; Wikipedia&quot;&gt; Pierre GASSENDI&lt;/a&gt;  était un philosophe, scientifique, astronome et mathématicien français, connu pour &lt;a href=&quot;https://www.gassendi.fr/index.php&quot; style=&quot;color:#88A1E9&quot; title=&quot;Pierre GASSENDI par gassendi.fr &quot;&gt;ses contributions&lt;/a&gt; à la philosophie naturelle, à la renaissance de l'épicurisme et pour ses critiques des philosophies de Descartes et d'Aristote. Il  a été un observateur attentif des phénomènes célestes. Il est notamment connu pour avoir été le premier à observer le transit de Mercure devant le Soleil en 1631, confirmant ainsi les prédictions de Kepler. &lt;/p&gt; &lt;p&gt; Il  a joué un &lt;a href=&quot;https://www.persee.fr/doc/rhr_0035-1423_1958_num_154_2_8873&quot; title=&quot;Pierre GASSENDI par Persée &quot;&gt;rôle clé &lt;/a&gt; dans la réhabilitation de la philosophie d'Épicure, qu'il a adaptée à un contexte chrétien. Il a défendu une vision atomiste de la nature, mais a rejeté les aspects matérialistes et athées de l'épicurisme antique. Il a plaidé pour une approche empirique de la connaissance, insistant sur l'importance de l'observation et de l'expérience. &lt;/p&gt; &lt;p&gt; Il a influencé des penseurs ultérieurs tels que John Locke et Isaac Newton. Son empirisme et son atomisme ont contribué au développement de la philosophie naturelle moderne tout en cherchant à concilier la science naissante avec la foi chrétienne, montrant que les découvertes scientifiques pouvaient être compatibles avec une vision religieuse du monde. &lt;/p&gt; &#10;&#10;" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ren%C3%A9_Descartes&quot;  title=&quot; Wikipedia&quot;&gt;René DESCARTES&lt;/a&gt; était un philosophe et marthématicien Français considéré comme un pionnier de la philosophie &lt;a href=&quot;https://la-philosophie.com/philosophie-lumieres&quot;  title=&quot;La philosophie des Lumières par la-philosophie.com&quot;&gt;des lumières&lt;/a&gt;  et de la science moderne.&lt;/p&gt; &lt;p&gt; Il est surtout connu pour sa phrase célèbre &lt;a href=&quot;https://www.youtube.com/watch?v=OjKY5Okx9wQ&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Je pense donc je suis par le Précepteur&quot;&gt;&quot;Je pense, donc je suis&quot;&lt;/a&gt; (en latin &quot;Cogito, ergo sum&quot;), qui a été prononcée dans son œuvre phare  &lt;a href=&quot;https://www.youtube.com/watch?v=cGrhiO0CECs&quot;  title=&quot;Le Discours de la méthode par Essences des Livres&quot;&gt;&quot;Discours de la méthode&quot;&lt;/a&gt; écrite en 1637.  Issu d'une famille noble, il étudie au collège jésuite de La Flèche, puis à Poitiers où il obtient une licence en droit en 1616. Il voyage en Europe, sert dans l'armée, vit à Amsterdam en exil volontaire pour la liberté de pensée, et meurt à Stockholm invité par la reine Christine de Suède, probablement d'une pneumonie due au froid.  &lt;/p&gt;&lt;p&gt; &lt;a href=&quot;https://www.youtube.com/@paroledephilosophe/search?query=descartes&quot;  title=&quot;La philosophie de Descartes par Parole de philosophe&quot;&gt;Sa pensée &lt;/a&gt; est basée sur l'idée que la connaissance doit être fondée sur la raison et la logique, plutôt que sur la tradition ou l'autorité et que la science doit être basée sur des mathématiques rigoureuses, ce qui a conduit à l'adoption de la géométrie dans les sciences naturelles. &lt;/p&gt; &lt;p&gt;Il a également formulé une théorie de la dualité de la nature, selon laquelle l'univers est divisé en deux parties distinctes : la matière et l'esprit. Selon cette théorie, la matière est soumise aux lois de la physique, tandis que l'esprit est libre et capable de penser par lui-même. Il applique le doute hyperbolique (sur les sens, le rêve, un &quot;malin génie&quot;) pour atteindre l'évidence : &quot;Je pense, donc je suis&quot;, prouvant l'existence de l'ego cogitans (esprit pensant). Il distingue res cogitans (pensée immatérielle) et res extensa (matière étendue), fondant le dualisme cartésien, et conçoit Dieu comme garant de la vérité claire et distincte. Sa physique mécaniste voit l'univers comme une machine divine, préfigurant la science moderne. /p&gt; &lt;p&gt;En plus de ses contributions à la philosophie et à la science, il  a également écrit sur de nombreux autres sujets, notamment la métaphysique, &lt;a href=&quot;https://www.youtube.com/watch?v=BFFa7fHv_1I&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Sommes nous vraimant libre par le Précepteur&quot;&gt;la liberté&lt;/a&gt;,  &lt;a href=&quot;https://www.youtube.com/watch?v=dykLwHWB7qk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Peut on prouver l'existence de Dieu par le Précepteur&quot;&gt;l'existence de Dieu&lt;/a&gt;, la théologie et la politique. &lt;/p&gt; &lt;p&gt;Il était en opposition totale avec la pensée de Spinoza car ils conçoivent l'union de l'âme et du corps de manière très différente. Tandis que Descartes voit deux substances qui agissent l'une sur l'autre, pour Spinoza, c'est une seule et même chose, vue sous deux aspects différents.&lt;/p&gt;  &#10; &lt;audio controls title=&quot;meditations metaphysiques rené Descartes  par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22789-31.10.2025-ITEMA_24296808-2025C53456E0008-NET_MFC_2769CAD8-FF20-4C7A-AB24-4D8965BD8B85-21-07dab51b3250d9a22eaab62a5c04edeb.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" display="https://www.laphilo.fr/pho/aarnauld-mini.webp" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Blaise_Pascal&quot; title=&quot;Blaise PASCAL par Wikipédia&quot;&gt; Blaise PASCAL&lt;/a&gt;  était un mathématicien, philosophe et écrivain français. Il a inventé à 19 ans, la première calculatrice mécanique, connue sous le nom de &quot;machine de Pascal&quot;. Il fut ensuite célèbre pour son &lt;a href=&quot;https://blaisepascal.bibliotheques-clermontmetropole.eu/son-oeuvre/pascal-savant/mathematiques/le-triangle-arithmetique&quot;  title=&quot;Le triangle arithmétique par Clermont metropole&quot;&gt; &quot;Triangle de Pascal&quot; &lt;/a&gt;, un arrangement de nombres qui est devenu un élément fondamental de la théorie des probabilités et de l'algèbre combinatoire. Il a aussi étudié la pression atmosphérique et a contribué à la compréhension de la manière dont la pression varie avec l'altitude. L'unité de pression &quot;pascal&quot; (Pa) porte son nom.  &lt;/p&gt; &lt;p&gt;&#10;Il était un chrétien dévot, et sa philosophie a été profondément influencée par sa foi. Il a écrit &lt;a href=&quot;https://www.youtube.com/watch?v=3uIjGv6jfSE&amp;ab_channel=Kosmos&quot;   title=&quot;Pensées par Kosmos&quot;&gt; &quot;Pensées&quot;&lt;/a&gt;, ce recueil de pensées, d'aphorismes et de réflexions où  Il a développé l'argument connu sous le nom de &lt;a href=&quot;https://www.youtube.com/watch?v=FoWFLpm8eX0&amp;ab_channel=AlainBajom%C3%A9e&quot;  title=&quot;Le pari de Pascal par Alain Bajomée&quot;&gt; &quot;pari de Pascal,&quot;&lt;/a&gt; qui suggère que, même en l'absence de preuves rationnelles concluantes de l'existence de Dieu, il est plus raisonnable de &lt;a href=&quot;https://www.youtube.com/watch?v=6KLWy3dWFMw&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;le pari par Le Précepteur&quot;&gt;parier sur son existence&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;   Voici quelques-unes des contributions les plus importantes : &lt;p&gt;&#10;&lt;dd&gt;  &lt;a href=&quot;https://www.youtube.com/watch?v=OL4fFfld9Pw&amp;ab_channel=Kosmos&quot;  title=&quot;le pouvoir par Kosmos&quot;&gt;- La condition humaine :&lt;/a&gt;  Il l'aborde avec une perspective réaliste et parfois pessimiste. Il explore la vulnérabilité de l'homme, sa nature pécheresse et sa tendance à la vanité. Il souligne également l'incertitude de la vie humaine et la fragilité de l'existence. &lt;/dd&gt;&#10;&lt;dd&gt;  - Le désespoir et l'angoisse : Il a exploré le sentiment de vide et de malaise que les êtres humains peuvent ressentir lorsqu'ils sont confrontés à l'absurdité de la vie. Il a suggéré que la quête de sens et de bonheur peut être trouvée dans une relation personnelle avec Dieu.  &lt;/dd&gt;&#10;&lt;dd&gt; &lt;a href=&quot;https://www.youtube.com/watch?v=CNr84ZlVfVY&amp;t=668s&amp;ab_channel=LePr%C3%A9cepteur&quot; title=&quot;le coeur à ses raisons par Le Précepteur&quot;&gt;La pensée et le cœur :&lt;/a&gt; Il a fait une distinction entre la &quot;raison du cœur&quot; et la &quot;raison de l'esprit.&quot; Il a soutenu que certaines vérités, en particulier celles liées à la foi et à la spiritualité, ne peuvent pas être pleinement saisies par la seule raison intellectuelle, mais nécessitent une approche du cœur et de l'émotion. &lt;/dd&gt;&#10;&lt;dd&gt; - La critique du rationalisme excessif :  qui réduisait toute connaissance à la raison et à la logique. Il croyait que la raison seule ne pouvait pas répondre à toutes les questions importantes de la vie et que l'expérience émotionnelle et spirituelle était tout aussi cruciale. &lt;/dd&gt;  &lt;audio controls title=&quot;Blaise Pascal, vers l'infini et au-delà par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-24.09.2018-ITEMA_21822263-2.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Nicole&quot; title=&quot; Wikipedia&quot;&gt;Pierre NICOLE&lt;/a&gt; était un philosophe, théologien, logicien et polémiste français, proche de Port-Royal et du mouvement janséniste. Né à Chartres, il enseigna la littérature et la philosophie à Port-Royal des Champs, où il collabora étroitement avec Antoine Arnauld. Il participa également à la défense des thèses jansénistes et fut lié au milieu intellectuel de Pascal. Son œuvre est toutefois plus diverse que celle d’un simple polémiste religieux : elle comprend des écrits de logique, de théologie, de morale et de politique. &lt;/p&gt; &lt;p&gt; Il est surtout connu comme le coauteur, avec Arnauld, de &lt;a href=&quot;https://www.youtube.com/watch?v=Gt4zoFWEKLM&quot; title=&quot;arnauld et Nicole, la logique ou l’art de penser par Sobrecrate&quot;&gt; la Logique ou l’art de penser,&lt;/a&gt;  publiée en 1662. Cet ouvrage, appelé communément « Logique de Port-Royal », présente la logique non seulement comme un ensemble de règles abstraites, mais comme un art pratique destiné à former le jugement. Il étudie successivement les idées, les jugements, les raisonnements et la méthode. Pour lui, bien penser suppose de lutter contre les préjugés, les passions et les habitudes intellectuelles qui déforment notre rapport à la vérité. &lt;/p&gt; &lt;p&gt;  Mais sa contribution la plus personnelle se trouve probablement dans  &lt;a href=&quot;https://www.fabula.org/revue/document1063.php&quot; title=&quot;la morale à l’essai par fabula&quot;&gt; les Essais de morale, &lt;/a&gt; dont la publication commence en 1671. Il y analyse les comportements humains, les relations sociales, l’éducation, la politique et les devoirs religieux. Sa morale est profondément augustinienne : l’homme naturel est dominé par l’amour-propre, c’est-à-dire par la tendance à rechercher son intérêt, son prestige et l’approbation des autres. Même les actions qui semblent généreuses peuvent donc être motivées par une recherche cachée de reconnaissance. &lt;/p&gt; &lt;p&gt;  Cette analyse le conduit à une vision assez pessimiste de la nature humaine. Il se méfie des prétendues vertus héroïques et montre que la société repose souvent sur des intérêts dissimulés, des conventions et des compromis. Cependant, il ne conclut pas qu’il est impossible de vivre moralement : ses Essais de morale ont précisément pour objectif d’enseigner une conduite plus lucide, plus modeste et plus charitable. La morale doit commencer par la connaissance de notre faiblesse, car celui qui ignore son amour-propre risque de prendre ses intérêts personnels pour de véritables exigences morales. &lt;/p&gt; " r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" display="https://www.laphilo.fr/pho/pnicole-mini.webp" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Baruch_Spinoza&quot;  title=&quot; Wikipedia&quot;&gt; Baruch SPINOZA&lt;/a&gt; était un philosophe hollandais et un penseur influent en opposition à Descartes en son époque. &lt;/p&gt; &lt;p&gt; Sa philosophie &lt;a href=&quot;https://www.youtube.com/watch?v=3pujnGvXZ-A&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Le déterminisme par le Précepteur&quot;&gt;Déterministe.&lt;/a&gt; se caractérise par sa vision &lt;a href=&quot;https://fr.wikipedia.org/wiki/Monisme&quot;    title=&quot;Le monisme est la position philosophique qui affirme l'unité indivisible de l'être&quot;&gt;moniste&lt;/a&gt; de l'univers, selon laquelle tout ce qui existe est une expression de la même substance divine, qu'il appelle &lt;a href=&quot;https://www.youtube.com/watch?v=crt1WS-SAC8&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Dieu égale nature&quot;&gt;Dieu ou Nature&lt;/a&gt; et elle est souvent associée au rationalisme, à l'athéisme et au panthéisme. &lt;/p&gt; &lt;p&gt; Pour lui, la raison est la clé de la liberté et du bonheur. Il affirme que  &lt;a href=&quot;https://www.youtube.com/watch?v=-0L3ltZwzac&amp;t=19s&amp;ab_channel=Kosmos&quot;  title=&quot;Les passions tristes par Kosmos&quot;&gt;les passions.&lt;/a&gt; peuvent nous éloigner de la vérité et nous rendre esclaves de nos désirs. &lt;/p&gt; &lt;p&gt;Pour être libre, l'homme doit comprendre la nature des choses et apprendre à contrôler ses passions. Cela implique une acceptation de la nécessité et de la causalité, car tout ce qui arrive est le résultat de la nature des choses et que, de ce fait, &lt;a  href=&quot;https://www.youtube.com/watch?v=kb_fhLt7kls&amp;t=216s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;Le libre arbitre n'est il qu'une illusion? par le Précepteur&quot;&gt;le libre arbitre n'existe pas.&lt;/a&gt; &lt;/p&gt; &lt;p&gt; Dans sa célèbre œuvre &quot;L'Éthique&quot;, il élabore une théorie éthique basée sur l'idée que la raison est la clé de la liberté et du bonheur avec sa notion de &lt;a href=&quot;https://www.youtube.com/watch?v=_Haf2S5Dbm8&amp;list=RDCMUCvRgiAmogg7a_BgQ_Ftm6fA&amp;start_radio=1&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;Le conatus par le Précepteur&quot;&gt;&quot;Conatus&quot;.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; En politique, il est souvent associé à la défense de la liberté d'expression et de la tolérance religieuse. Il a écrit un ouvrage intitulé  &lt;a href=&quot;https://www.youtube.com/watch?v=Zqt0QZVrTkI&quot;   title=&quot;Le Traité TP par PrepaUp&quot;&gt;&quot;Le Traité théologico-politique&quot;&lt;/a&gt; dans lequel il soutient que la religion doit être séparée de l'État et que chacun doit être libre de pratiquer sa religion sans être persécuté.&lt;/p&gt;    &lt;audio controls title=&quot;Spinoza est il le philosophe du bonheur ? par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-15.12.2022-ITEMA_23228294-2022C48904S0349-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&lt;p&gt; &lt;/p&gt;" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nicolas_Malebranche&quot; title=&quot; Wikipedia&quot;&gt;Nicolas MALEBRANCHE&lt;/a&gt; était un philosophe et théologien français, connu pour ses travaux en métaphysique, en épistémologie et en philosophie de la religion. En 1660, il rejoint l'Oratoire, une congrégation religieuse catholique, où il se consacre à l'étude de la philosophie et de la théologie et il découvre les travaux de Descartes, qui auront une influence majeure sur sa pensée. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de  &lt;a href=&quot;https://www.youtube.com/watch?v=3YvitSjZ2_4&amp;t=326s&quot; title=&quot;Malebranche : Occasionalism par Leevark&quot;&gt;l'occasionalisme&lt;/a&gt;, qu'il développe dans son ouvrage majeur &quot; De la recherche de la vérité&quot;. Selon lui, les idées que nous avons des objets existent dans l'entendement divin, et c'est par la médiation de Dieu que nous accédons à ces idées. Cette théorie s'oppose à l'empirisme et à l'idée que nos perceptions sont directement causées par les objets eux-mêmes.  Il rejette l'interaction directe entre l'âme et le corps, une idée défendue par Descartes. Selon lui, l'âme et le corps ne peuvent pas agir l'un sur l'autre directement. Au lieu de cela, Dieu coordonne les états de l'âme et les états du corps de manière harmonieuse, sans qu'il y ait de causalité directe entre eux. Il a développé une théorie selon laquelle Dieu agit selon des &quot;lois générales&quot; plutôt que par des interventions particulières, ce qui laisse une place à la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Libert%C3%A9_(philosophie)&quot;  title=&quot;La liberté par Wikipedia&quot;&gt;liberté humaine&lt;/a&gt; tout en maintenant la souveraineté divine. &lt;/p&gt; &lt;p&gt;Ses oeuvres principales : &lt;/p&gt; &#10;&lt;dd&gt; -De la recherche de la vérité : Théories sur la perception, la causalité et la métaphysique.  &lt;/dd&gt; &#10;&lt;dd&gt; - Traité de la nature et de la grâce : Relation entre la grâce divine et les lois de la nature. &lt;/dd&gt;&#10;&lt;dd&gt; - Entretiens sur la métaphysique et la religion : Un dialogue qui résume et défend ses idées. &lt;/dd&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il reste une figure importante dans l'histoire de la philosophie, notamment pour sa tentative de concilier la pensée cartésienne avec une vision profondément théocentrique du monde. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;   &lt;audio controls title=&quot; L’imagination selon Descartes et Malebranche par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-16.01.2024-ITEMA_23616134-2024C48904S0016-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Voltaire&quot;   title=&quot; Wikipedia&quot;&gt; VOLTAIRE&lt;/a&gt;, de son vrai nom François-Marie Arouet, est un philosophe de l'époque des  &lt;a href=&quot;https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;t=380s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot; La philosophie des lumières par le Précepteur &quot;&gt;Lumières&lt;/a&gt; (ou Illuministe) en France. Il était aussi écrivain, poète, dramaturge et philosophe. &lt;/p&gt; &lt;p&gt;&#10;Il était connu pour son esprit incisif, son ironie mordante et son engagement en faveur de la &lt;a href=&quot;https://www.youtube.com/watch?v=XE1Z8jpVJUA&quot; title=&quot; la vie de Voltaire  par Portrait Historiques&quot;&gt; liberté d'expression, &lt;/a&gt;  de la tolérance religieuse et de la justice sociale. Il s'est opposé aux abus de pouvoir et à l'intolérance de l'Église et de l'État et a défendu sa séparation . Il plaidait en faveur d'une monarchie modérée et libérale comme cela était le cas en Angleterre à cette époque qu'il avait connu suite a son exil.  Il croyait fermement que les individus devaient être libres de s'exprimer et de critiquer les autorités sans craindre la censure ou les représailles.  &lt;/p&gt; &lt;p&gt;&#10;Voltaire, qui était &lt;a href=&quot;https://www.youtube.com/watch?v=RO_aeh1cBgA&amp;ab_channel=Kurious&quot;   title=&quot; Regard critique sur le déîsme par Kurious &quot;&gt;déiste&lt;/a&gt; s'est opposé aux abus de l'Église catholique et a plaidé en faveur de la tolérance envers les minorités religieuses. Dans son ouvrage &lt;a href=&quot;https://www.youtube.com/watch?v=1RlS8GKL7SU&quot;  title=&quot; Voltaire-Tolérence par Culture Philo &quot;&gt;&quot;Traité sur la tolérance&quot;&lt;/a&gt;, (1763) il a condamné les persécutions religieuses et a défendu le principe selon lequel chaque individu devait être libre de pratiquer sa religion sans être inquiété. &lt;/p&gt; &lt;p&gt;&#10;Son ouvrage le plus connu est  &lt;a href=&quot;https://www.youtube.com/watch?v=kom2zFvrj5I&amp;ab_channel=T%C3%A9l%C3%A9Crayon&quot;  title=&quot; Candide de Voltaire par TéléCrayon &quot;&gt;&quot;Candide&quot;&lt;/a&gt; (1759), un conte philosophique qui critique les idées optimistes de l'époque et souligne les absurdités et les injustices du monde. &lt;/p&gt; &lt;p&gt;&#10;La contribution de Voltaire à la philosophie se caractérise par son engagement envers la raison, la liberté et la justice. Il a influencé de nombreux penseurs ultérieurs et a contribué à jeter les bases de la pensée libérale et humaniste qui a marqué les siècles suivants. Sa défense de la liberté d'expression reste une valeur fondamentale de nos sociétés démocratiques aujourd'hui. &lt;/p&gt; &lt;audio controls title=&quot;Voltaire et les Lumières par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/15537-13.01.2021-ITEMA_22540842-2021C24632S0013.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Hartley_(philosophe)&quot;    title=&quot; Wikipedia&quot;&gt;David HARTLEY&lt;/a&gt; était un  philosophe et psychologue anglais connu notamment pour son rôle de précurseur dans l'étude de l'esprit humain et sa philosophie a eu un impact majeur sur le &lt;a href=&quot;https://www.youtube.com/watch?v=kbpEAw2gl40&quot; title=&quot; David Hartley par Crevoisier Philippe&quot;&gt; développement de la psychologie &lt;/a&gt;  , en particulier le courant de l'associationnisme. Il a proposé une théorie selon laquelle toutes les idées complexes sont formées à partir d'idées simples par l'association. Sa théorie s'appuie sur deux piliers : &lt;/p&gt; &lt;p&gt; - La doctrine des vibrations : Inspiré par la physique de Newton, pour lui les sensations sont le résultat de vibrations physiques de la &quot;substance médullaire&quot; (le système nerveux). Les impressions sensorielles, comme la lumière ou le son, créent des vibrations dans les nerfs qui se propagent jusqu'au cerveau. &lt;/p&gt; &lt;p&gt; - La doctrine des associations : Ces vibrations nerveuses laisseraient des traces dans le cerveau, qu'il a appelées des &quot;vibratiuncules&quot; (de petites vibrations). Lorsque des sensations sont fréquemment associées dans le temps ou l'espace, leurs &quot;vibratiuncules&quot; respectives finissent par s'associer entre elles. Ces associations physiques sont &lt;a href=&quot;https://www.youtube.com/shorts/BuqpLB9V41c&quot;  title=&quot; David Hartley par timelinephilosopher&quot;&gt;  le fondement des idées et des pensées &lt;/a&gt;. Pour lui, une idée complexe, comme celle d'une orange, est simplement l'association des &quot;vibratiuncules&quot; de la couleur orange, de la forme ronde, de la texture, du goût, etc. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &quot;Observations on Man, his Frame, his Duty, and his Expectations&quot;, publiée en 1749, est divisée en deux parties :  &lt;/p&gt; &lt;p&gt; &#10;- L'Homme physique et mental : Cette section développe sa théorie des vibrations et des associations ou il y explique comment les sensations, la mémoire, l'imagination, la raison et les émotions peuvent être comprises à travers ces mécanismes. Il a même abordé la question du libre arbitre, se positionnant comme un déterministe. &lt;/p&gt; &lt;p&gt; &#10;- Les devoirs et les espérances : Ici, il applique ses principes psychologiques à des questions de morale et de religion. Il soutient que la moralité se développe également par l'association. Par exemple, un enfant apprend à associer les actions de bonté avec des sentiments de plaisir et d'approbation, et les mauvaises actions avec la douleur et le déplaisir. &lt;/p&gt; &lt;p&gt; Ses idées ont été reprises et développées par d'autres philosophes associationnistes, comme John Stuart Mill, qui a poursuivi l'idée que les lois de l'association expliquent l'intégralité de la vie mentale. Sa tentative de lier le mental au physique a posé les bases de la neuropsychologie moderne. &lt;/p&gt; " r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Julien_Offray_de_La_Mettrie&quot;    title=&quot; Wikipedia&quot;&gt;Julien Onfray de la METTRIE&lt;/a&gt;  était un philosophe et médecin français des Lumières, connu pour son &lt;a href=&quot;https://www.youtube.com/watch?v=ATn23C-jw1M&quot;  title=&quot; Traité du bonheur de la Mettrie par Voyage interieur&quot;&gt; matérialisme radical &lt;/a&gt; et son athéisme provocateur. Médecin militaire, il fut exilé de France après la publication de ses idées controversées, avant de trouver refuge auprès de Frédéric II de Prusse à Potsdam. &lt;/p&gt; &lt;p&gt; Dans L’Homme machine (1747), il affirme que l’être humain est une machine purement matérielle : l’âme n’existe pas comme substance distincte, mais émerge des processus physiques du cerveau et du corps, sans besoin de Dieu ou d’esprit immatériel. Il s’inspire de Descartes, mais pousse le mécanisme jusqu’au bout en rejetant le dualisme corps-âme.  &lt;/p&gt; &lt;p&gt; Ses écrits, comme Histoire naturelle de l’âme (1745), scandalisèrent l’Église et les autorités : ses livres furent brûlés publiquement et il perdit son poste aux Gardes-Françaises. Défenseur d’un hédonisme sensualiste, il prône le  &lt;a href=&quot;https://www.youtube.com/watch?v=FH2TDimoh7Q&quot;  title=&quot; La Mettrie ou l’art de jouir par Parole de philosophe&quot;&gt; plaisir comme seul bien moral,&lt;/a&gt;  sans morale transcendante. &lt;/p&gt; &lt;p&gt; Ses Œuvres clés : - Histoire naturelle de l’âme (1745) : Critique du dualisme et fondement matérialiste. - L’Homme machine (1747) : Thèse principale sur l’automatisme humain. - L’Homme plante (1748) : Étend le mécanisme aux végétaux et animaux. &lt;/p&gt; &lt;p&gt; Précurseur du matérialisme moderne et de la philosophie de la vie, il influence Diderot et les Encyclopédistes, mais reste marginalisé pour son radicalisme. Il anticipe des idées sur l’évolution et la cybernétique en voyant l’humain comme un système organisé. &lt;/p&gt; &#10;" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Hume&quot;  title=&quot; Wikipedia&quot;&gt;David HUME&lt;/a&gt; était un philosophe, historien et économiste écossais de l'ère des Lumières. Il est surtout connu pour ses contributions à la philosophie empirique, la théorie de la connaissance, la métaphysique, l'éthique et l'esthétique. &lt;/p&gt; &lt;p&gt; Hume était un sceptique et a cherché à examiner de manière critique les idées préconçues et les &lt;a  href=&quot;https://www.youtube.com/watch?v=CLIoxw6TXuk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Tout n'est que croyance  par Le Précepteur&quot;&gt;croyances reçues&lt;/a&gt;. Il a rejeté les arguments métaphysiques qui ne pouvaient pas être fondés sur l'expérience directe, et a affirmé que les connaissances humaines étaient basées sur les impressions et les idées que nous en avons. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de &lt;a  href=&quot;https://www.youtube.com/watch?v=ftd3vjw9lSU&quot;  title=&quot; la causalité par Skarblown Animations&quot;&gt;la causalité&lt;/a&gt;, qui affirme que nous ne pouvons pas connaître la relation de cause à effet entre deux événements par simple observation, mais que nous sommes amenés à croire en une telle relation en raison de notre expérience passée.  &lt;/p&gt; &lt;p&gt; En éthique, il a affirmé que la morale était basée sur des sentiments plutôt que sur la raison et qu'elle ne peut pas être déduite de principes rationnels, mais doit être fondée sur l'empathie et la sympathie envers les autres.  &lt;/p&gt; &lt;p&gt; Il a également souligné l'importance du bonheur et du plaisir dans la vie, affirmant que ce sont des aspects essentiels de notre existence et de notre &lt;a  href=&quot;https://www.youtube.com/watch?v=52077nWSkPM&amp;t=11s&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;l'identité par le Précepteur&quot;&gt;identité&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il a écrit sur la religion et a critiqué les arguments traditionnels pour l'existence de Dieu en affirmant que la religion était basée sur la superstition plutôt que sur la raison, et que la croyance en Dieu était fondée sur l'habitude plutôt que sur la preuve. &lt;/p&gt;  &lt;audio controls title=&quot;Pourquoi faut il lire David Hume par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22838-02.02.2022-ITEMA_22927004-2022C45539E0018-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;&#10;" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Jean-Jacques_Rousseau&quot; title=&quot; Wikipedia&quot;&gt; Jean-Jacques ROUSSEAU&lt;/a&gt; était un philosophe &lt;a href=&quot;https://www.youtube.com/watch?v=3IWYmQ81wyk&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;Les Lumières par le Précepteur &quot;&gt; des lumières&lt;/a&gt; et écrivain suisse-français, défenseur de la liberté et de l'égalité. Il et est surtout connu pour son livre &lt;a href=&quot;https://www.youtube.com/watch?v=tToAS8pUXzU&quot;   title=&quot;Le texte fondateur par Alain Bajomée &quot;&gt;&quot;Du contrat social&quot;&lt;/a&gt; , dans lequel il développe sa théorie politique ainsi que &lt;a href=&quot;https://www.youtube.com/watch?v=3-mPXD5CkJc&quot;  title=&quot;L'Emile par Librairie Vrin&quot;&gt;&quot;Emile&quot; &lt;/a&gt;considéré comme un &quot;traité d'écucation&quot; ou sa théorie de l'homme. &lt;/p&gt; &lt;p&gt;&#10;Rousseau a également écrit sur la philosophie morale, la théorie de l'éducation et la nature humaine et  &lt;a href=&quot;https://www.youtube.com/watch?v=cUtO8U9QbZs&amp;ab_channel=LePr%C3%A9cepteur&quot;  style=&quot;color:#88A1E9&quot;  title=&quot;Le désir par le Précepteur &quot;&gt; le désir&lt;/a&gt;. Il croyait que &lt;a href=&quot;https://www.youtube.com/watch?v=FpXdTgerxiI&amp;ab_channel=LePr%C3%A9cepteur&quot;   title=&quot;L''homme est naturellement bon par le Précepteur &quot;&gt; l'homme est naturellement bon&lt;/a&gt;, mais corrompu par la société et la civilisation. Il a également affirmé que la liberté individuelle est essentielle à l'épanouissement humain et que les institutions politiques doivent être créées pour protéger les droits et les libertés des individus. &lt;/p&gt; &lt;p&gt;  Il est souvent considéré comme un précurseur du  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0776-555x_1927_num_29_16_2482#&quot;  title=&quot;La philosophie romantique par Persée &quot;&gt; romantisme&lt;/a&gt; en raison de son accent mis sur les émotions, la nature, l'individualité et la subjectivité. Il a exprimé une méfiance envers la société civilisée et a prôné un retour à la nature et à la simplicité. Il a également souligné l'importance de l'émotion et de l'expérience personnelle dans la compréhension du monde, remettant en question l'approche rationnelle et scientifique des Lumières. Ses idées ont eu une influence significative sur les écrivains et les artistes romantiques ultérieurs, qui ont valorisé l'expression émotionnelle et l'expérience individuelle dans leurs œuvres.&lt;/p&gt; &lt;p&gt;&#10;En termes de théorie de l'éducation, Rousseau a proposé une approche de l'apprentissage basée sur l'observation et l'expérience plutôt que sur la mémorisation et l'étude académique et a souligné l'importance de la créativité et de l'expression personnelle dans l'éducation. &lt;/p&gt; &lt;p&gt; &lt;audio controls title=&quot;Rousseau, l'anti-économiste par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10081-28.12.2022-ITEMA_23239091-2022C29629E0022-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;&#10;&#10;" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" display="&lt;p&gt; &lt;a href=&quot;https://fr.wikipedia.org/wiki/Denis_Diderot&quot;  title=&quot; Wikipedia&quot;&gt; Denis DIDEROT&lt;/a&gt; était un philosophe des Lumières français ainsi qu' un écrivain, éditeur et encyclopédiste influent.  Il est surtout connu pour son rôle de coéditeur et contributeur majeur de &lt;a href=&quot;https://www.youtube.com/watch?v=LuRI5zg7tJY&quot;   title=&quot;Diderot 1750 Encyclopedia par OER Project &quot;&gt;l'Encyclopédie, &lt;/a&gt; ou Dictionnaire raisonné des sciences, des arts et des métiers.&lt;/p&gt; &lt;p&gt;&#10;Il était un fervent défenseur de la raison et de l'esprit critique et il rejetait les dogmes et les traditions aveugles, encourageant à la place l'examen rationnel et la remise en question des croyances établies. Il croyait en la capacité de l'homme à comprendre le monde à travers la science, la philosophie et l'observation directe. &lt;/p&gt; &lt;p&gt;&#10;Il était un matérialiste convaincu et soutenait que l'univers était composé de matière en mouvement constant et rejetait l'idée d'une entité divine créatrice. Il écrit &lt;a href=&quot;https://www.youtube.com/watch?v=vkBC-MDLH_A&amp;ab_channel=BouillondeCulture&quot;  title=&quot;Le rêve d'Alembert  par Bouillon de culture&quot;&gt;Le Rêve de D’Alembert&lt;/a&gt;, un ensemble de trois dialogues philosophiques ou il expose sa théorie sur la vie et la nature. Sa vision matérialiste était étroitement liée à sa pensée scientifique et à son intérêt pour les sciences naturelles. &lt;/p&gt; &lt;p&gt; Il écrit aussi un roman (ou plutôt un anti-roman) &lt;a href=&quot;https://www.youtube.com/watch?v=NtxGWQ89g_k&quot; title=&quot;Jacques le Fataliste  par Kosmos&quot;&gt;&quot;Jacques le Fataliste et son maître&quot;&lt;/a&gt; où il refuse le cloisonnement et se positionne en rupture avec les conventions et invente une liberté à l'égard des pratiques existantes en France au XVIIIe siècle. &lt;/p&gt; &lt;p&gt;&#10;Il était un défenseur des libertés de pensée, d'expression et de la presse. Il critiquait les institutions religieuses et politiques oppressives de son époque et plaidait en faveur de l'égalité sociale et de la justice. Il croyait en l'éducation comme moyen d'émancipation et de progrès social, et il pensait que les individus devaient être libres de remettre en question les traditions et les dogmes établis. &lt;/p&gt; &#10;   &lt;audio controls title=&quot;Le Neveu de Rameau par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/10/s40/RF_38A1D24B-FA10-43F4-8B19-8C4921845BD4_GENE.MP3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Johann_Joachim_Spalding&quot; title=&quot; Wikipedia&quot;&gt;Johann Joachim SPALDING&lt;/a&gt; était un théologien protestant allemand, souvent considéré comme l’un des grands représentants des Lumières religieuses en Allemagne. Sa pensée cherche à concilier foi chrétienne, raison et morale, dans un esprit de réforme modérée plutôt que de rupture. &lt;/p&gt; &lt;p&gt; Dans son œuvre la plus célèbre, Die Bestimmung des Menschen (1748), il réfléchit au sens de la vie humaine. Pour lui, l’être humain n’est pas fait seulement pour satisfaire ses besoins matériels, mais pour se développer intérieurement, moralement et spirituellement. &lt;/p&gt; &lt;p&gt; Sa philosophie religieuse défend l’idée d’une religion naturelle compatible avec la Révélation. Il refuse le dogmatisme rigide et l’orthodoxie autoritaire, et insiste sur une foi plus vivante, fondée sur la conscience, le bon sens et l’expérience intérieure. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande importance &lt;a href=&quot;https://www.persee.fr/doc/ephe_0000-0002_1979_num_92_88_18346&quot;  title=&quot;problèmes de la théologie allemande par persée&quot;&gt;au sentiment religieux. &lt;/a&gt;  Dans son ouvrage de 1789, il montre que les émotions et la vie intérieure ont une vraie place dans le christianisme, sans que cela supprime l’exigence morale. Il représente une forme de christianisme éclairé : une religion raisonnable, morale et personnelle, qui veut rendre la foi plus humaine et plus intelligible. Son influence a compté dans la théologie protestante allemande, notamment dans le courant appelé néologie. &lt;/p&gt; &#10;" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" display="https://www.laphilo.fr/pho/jjspalding-mini.webp" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" display="https://laphilo.fr/photo/jjspalding.webp" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Charles_Bonnet_(naturaliste)&quot;  title=&quot; Wikipedia&quot;&gt;Charles BONNET&lt;/a&gt;  était un philosophe &amp; naturaliste suisse célèbre pour ses travaux pionniers en biologie et sa découverte de la &lt;a href=&quot;https://fr.wikipedia.org/wiki/Paling%C3%A9n%C3%A9sie&quot;  title=&quot;palingénésie par Wikipedia&quot;&gt;parthénogenèse. &lt;/a&gt; Il  étudie la botanique et l'entomologie dès sa jeunesse, influencé par Newton, Leibniz et Malebranche. Malgré des problèmes de vue et d'ouïe précoces, il devient membre du Conseil des Deux-Cents et correspondant de l'Académie des sciences de Paris. &lt;/p&gt; &lt;p&gt; Il démontre en 1745 la reproduction par parthénogenèse chez les pucerons, obtenant onze générations sans fécondation, et étudie la régénération des vers, des limaçons et des pattes d'écrevisse. Ses Recherches sur l'usage des feuilles (1754) préfigurent la photosynthèse, et il défend la théorie de la préformation, où les germes préexistent depuis la Création. &lt;/p&gt; &lt;p&gt; Dans Essai de psychologie (1754) et Essai analytique sur les facultés de l'âme (1760), il développe un sensualisme spiritualiste, voyant les idées naître des sensations via les fibres cérébrales. Sa Palingénésie philosophique (1769) postule l'immortalité des âmes humaines et animales dans une échelle continue des êtres. &lt;/p&gt; &#10;" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Paul_Thiry_d%27Holbach&quot;  title=&quot; Wikipedia&quot;&gt;Paul Thiry d'HOLBACH&lt;/a&gt;  était un philosophe allemand et devient encyclopédiste, traduit des œuvres scientifiques allemandes et anglaises pour l'Encyclopédie de Diderot. Hôte du célèbre &quot;cénacle d'Holbach&quot;, salon fréquenté par Diderot, Rousseau, Helvétius et Adam Smith, il anime un foyer intellectuel anticlérical jusqu'à sa mort en 1789. &lt;/p&gt; &lt;p&gt; Il défend un matérialisme radical: l'univers se compose uniquement de matière et de mouvement, régi par des  &lt;a href=&quot;https://www.youtube.com/watch?v=x99DRdMAd08&quot;  title=&quot;Essai sur l'art de ramper à l'usage des courtisans - D'Holbach&quot; par Vox Plebeia&quot;&gt;lois causales &lt;/a&gt; nécessaires, excluant Dieu ou toute intervention surnaturelle. Athée virulent, il combat les religions comme sources d'erreur, de peur et de superstition dans des pamphlets pseudonymes comme &lt;a href=&quot;https://www.youtube.com/watch?v=8Uohr5Y9xx0&quot; title=&quot;Religions Are ROTTING ILLUSIONS | Baron d’Holbach par Unfiltered Philosophy&quot;&gt;&quot;Le Christianisme dévoilé&quot; &lt;/a&gt; paru en 1761 ou &quot;Le Système de la nature&quot; (1770), bible de l'athéisme. &lt;/p&gt; &lt;p&gt; Sa morale est utilitariste et eudémoniste: la vertu réside dans l'utilité pour le bonheur individuel et collectif, fondée sur la raison et l'éducation, sans recours à la religion. Fataliste et déterministe, il prône la liberté sociale, l'égalité et une politique naturelle anti-despotique, influençant la Révolution française par sa critique des privilèges et du fanatisme. &lt;/p&gt; &#10;&#10;" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" display="&lt;a href=&quot;https://fr.wikipedia.org/wiki/Emmanuel_Kant&quot;  title=&quot; Wikipedia&quot;&gt; Immanuel KANT&lt;/a&gt; était un philosophe &lt;a href=&quot;https://la-philosophie.com/philosophie-lumieres&quot; style=&quot;color:#88A1E9&quot;   title=&quot;La philosophie des Lumières par la-philosophie.com&quot;&gt;des lumières&lt;/a&gt; qui a développé une théorie morale fondée sur la raison et le devoir, appelée l'éthique  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Philosophie_pratique_d%27Emmanuel_Kant&quot;  title=&quot;La philosophie pratique de Kant de l'encyclopédie Wikipédia&quot;&gt;Kantienne&lt;/a&gt; qui considèrent qu'il est immoral de commettre certains actes, même si c'est pour maximiser le bien de tous.&lt;/p&gt; &lt;p&gt; Sa fameuse  &lt;a href=&quot;https://www.youtube.com/watch?v=nP2gQI9G4c0&amp;ab_channel=Kosmos&quot;   title=&quot;C'est quoi la raison pure par Kosmos&quot;&gt;&quot;Critique de la raison pure&quot;&lt;/a&gt; , publié en 1781 est une synthèse entre le Rationnalisme Cartésien de Descartes et  l'Empirisme de Hume car on ne peut pas résumer la connaissance simplement à la logique pure mais aussi à l'expérience et au contact sensoriel. &lt;/p&gt; &lt;p&gt; Pour lui, &lt;a href=&quot;https://www.youtube.com/watch?v=UsfaQ-VjRk4&amp;t=4s&amp;ab_channel=Kosmos&quot;  title=&quot;La loi morale par Kosmos&quot;&gt; les lois morales&lt;/a&gt; qu'il expose en autres dans un petit livre &lt;a href=&quot;https://www.youtube.com/watch?v=eftYgf0iC7s&amp;ab_channel=LePr%C3%A9cepteur&quot;  title=&quot;L'impératif catégorique par le Précepteur&quot;&gt;&quot;Fondement de la métaphysique des moeurs&quot;&lt;/a&gt; sont universelles et ne dépendent pas des circonstances individuelles, ni de la réussite ou de l'échec, mais plutôt de la volonté de faire ce qui est moralement juste. &lt;/p&gt; &lt;p&gt; Il a, le premier, donné à &lt;a href=&quot;https://la-philosophie.com/espace-public-et-democratie&quot;  title=&quot;Espace public par la-philosophie.com&quot;&gt;l’espace public&lt;/a&gt; « sa structure théorique achevée » car il définit les &quot;Lumières&quot; comme la « sortie hors de l’état de tutelle » c’est-à-dire la situation de l’homme hors d’état de faire usage par lui-même de sa raison.&lt;/p&gt; &lt;p&gt; C’est pourquoi l’éclaircissement progressif d’un peuple est suspendu à une condition : que l’usage public de la raison, la libre circulation des idées et des opinions, de manière orale ou écrite, soit érigé en « droit sacré de l’humanité » et que notre &lt;a href=&quot;https://la-philosophie.com/critique-de-la-faculte-juger-kant-resume&quot;  title=&quot;Faculté de jugement par la-philosophie.com&quot;&gt;faculté de jugement&lt;/a&gt; du Beau soit une réflexion personnelle.&lt;/p&gt;    &lt;audio controls title=&quot;Le monde: entre déterminisme et liberté par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22095-26.04.2021-ITEMA_22651648-2016C12410S0284.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Edmund_Burke&quot;   title=&quot; Wikipedia&quot;&gt;Edmund BURKE&lt;/a&gt; était un philosophe et homme politique anglo-irlandais, considéré comme l'un des fondateurs du conservatisme moderne. Il s'opposa farouchement à la Révolution française, défendant l'évolution graduelle des institutions plutôt que les ruptures radicales. Il étudia au Trinity College avant de s'installer à Londres pour exercer le droit et entrer en politique. Député whig à la Chambre des communes de 1766 à 1794, il soutint l'indépendance américaine tout en critiquant les excès fiscaux britanniques. Sa célèbre Réflexions sur la Révolution de France (1790) alerta sur les dangers de la &quot;multitude perverse&quot; et du rejet des traditions. &lt;/p&gt; &lt;p&gt; Il  voyait la société comme un &quot;partenariat entre les vivants, les morts et ceux qui ne sont pas encore nés&quot;, valorisant les &lt;a href=&quot;https://www.youtube.com/watch?v=az1n7gSaKFE&quot; title=&quot;La tradition permet elle le changement  par la chaine de Velours&quot;&gt;préjugés hérités &lt;/a&gt; comme bank de sagesse collective supérieure à la raison individuelle. Dans Recherches philosophiques sur l'origine de nos idées du sublime et du beau (1757), il distingue le sublime (lié à la douleur, à la terreur et à Dieu) du beau (lié au plaisir et à la société), influençant l'esthétique romantique. Il prônait l'amélioration progressive de la nature humaine imparfaite, sans table rase. &lt;/p&gt; &lt;p&gt; Surnommé &quot;conservateur des Lumières&quot;, il inspira des penseurs comme Roger Scruton et reste une référence contre les utopies rationalistes. En France, il fut parfois taxé de réactionnaire, mais son libéralisme tempéré et son sens de la responsabilité des élites résonnent encore. &lt;/p&gt;  &lt;audio controls title=&quot;Les britaniques ; Burke et ses héritiers par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-10.12.2024-ITEMA_23958056-2024C48904S0345-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;&#10;&#10;" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" display="https://laphilo.fr/pho/ghlessing-mini.webp" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Johann_Kaspar_Lavater&quot;  title=&quot; Wikipedia&quot;&gt;Johann Kaspar LAVATER&lt;/a&gt;  était un théologien, poète et philosophe suisse, connu surtout comme pionnier de  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Physiognomonie&quot;  title=&quot;Physiognomonie par Wikipedia&quot;&gt; &quot;la physiognomonie, &lt;/a&gt;  une pseudoscience liant traits du visage et caractère moral. Pasteur réformé à Zurich, il mêla mysticisme chrétien, irrationalisme et influences des Lumières tardives dans ses écrits. Né à Zurich dans une famille bourgeoise, il étudia la théologie et la philosophie au Collegium Carolinum sous Johann Jakob Bodmer. Ordonné en 1762, il devint diacre puis pasteur à l'église St-Pierre, tout en s'engageant contre la corruption locale, ce qui l'exila brièvement à Berlin. Ami de Goethe (dont la relation se tendit) et de Moses Mendelssohn, il fut blessé lors de l'invasion française de 1799 et mourut de ses blessures. &lt;/p&gt; &lt;p&gt; Sa grande œuvre, Physiognomische Fragmente zur Beförderung der Menschenkenntnis und Menschenliebe (1775-1778), postule que le visage révèle l'âme divine en l'homme, reliant esthétique, vertu et théologie. Influencé par l'Empfindsamkeit et le Sturm und Drang, il valorisait le sentiment sur la raison pure, explorant prophétie, miracles et palingénésie (résurrection). Critiqué par Lichtenberg pour son subjectivisme, il inspira poésie mystique et débats sur  &lt;a href=&quot;https://www.youtube.com/watch?v=LUxSlXIY-Zk&quot;  title=&quot;Johann Kaspar Lavater par Grow Wise&quot;&gt; &quot;l'intériorité humaine. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Il  incarna un pont entre piétisme, sentimentalisme et romantisme naissant, influençant esthétique et psychologie populaire en Europe. Ses idées déclinèrent avec les progrès scientifiques, mais sa quête d'une connaissance intuitive de l'homme reste débattue. &lt;/p&gt; &#10;" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nicolas_de_Condorcet&quot;  title=&quot; Wikipedia&quot;&gt;Nicolas de CONDORCET&lt;/a&gt;   était un philosophe , mathématicien et homme politique français, figure emblématique des Lumières et défenseur du progrès humain indéfini. Il milita pour &lt;a href=&quot;https://www.youtube.com/watch?v=3G3kVl0GbA8&quot;  title=&quot;Condorcet féministe ? par Sud Radio&quot;&gt;l’égalité des sexes, &lt;/a&gt; l’abolition de l’esclavage et de la peine de mort, tout en développant des idées pionnières en probabilités et en théorie du vote .  &lt;/p&gt; &lt;p&gt; Issu d’une famille noble picarde, il intégra l’Académie des sciences à 26 ans et succéda à d’Alembert comme secrétaire perpétuel. Proche de Turgot et Voltaire, il fut élu à l’Assemblée législative en 1791, rédigeant des projets d’éducation publique universelle et gratuite. Pourchassé par les Jacobins pour son opposition modérée à la Terreur, il fut emprisonné et mourut dans des circonstances mystérieuses en prison. &lt;/p&gt; &lt;p&gt; Dans son Esquisse d’un tableau historique des progrès de l’esprit humain (1795, posthume), il expose l’idée de perfectibilité humaine infinie grâce à la raison, la science et &lt;a href=&quot;https://www.youtube.com/watch?v=3G3kVl0GbA8&quot;  title=&quot;Condorcet et l’éloge de l’instruction par Culture philo&quot;&gt;l’éducation, &lt;/a&gt;  rejetant les fatalismes religieux ou historiques. Il inventa le t &lt;a href=&quot;https://www.youtube.com/watch?v=avTI9GHZX1I&quot;  title=&quot;Condorcet le paradoxe par Diable Positif&quot;&gt;« paradoxe de Condorcet » &lt;/a&gt; en analyse du vote et prôna une instruction publique laïque pour tous, y compris les femmes, comme vecteur d’émancipation sociale. Ses travaux mathématiques appliqués à la « mathématique sociale » visaient à optimiser les décisions collectives. &lt;/p&gt;  Sa philosophie  repose sur l'idée de perfectibilité humaine infinie, où la raison, la science et l'éducation universelle mènent à un progrès moral et social indéfini, rejetant les fatalismes religieux ou historiques. Il défend les droits naturels préexistants à l'État – comme la propriété et la liberté – et prône des lois justes émanant d'une autorité légitime sans enfreindre l'individu, même au nom de la majorité.  &lt;/p&gt; &lt;p&gt;Pionnier de la &quot;mathématique sociale&quot;, Condorcet publia Essai sur la théorie des probabilités appliquée aux décisions prises à la pluralité des voix (1785), introduisant le paradoxe portant son nom sur les incohérences des votes majoritaires. Parmi ses travaux : Du calcul intégral (1765), Du problème des trois corps (1767) et des mémoires sur les probabilités (1781-1784). Ces écrits appliquent les maths à la décision collective pour optimiser la justice sociale.&lt;/p&gt; &lt;p&gt;  Précurseur de la démocratie moderne et de l’école républicaine, il  inspira les réformateurs du XIXe siècle malgré son exécution tragique. Ses idées sur le progrès rationnel contrastent avec les mysticismes contemporains comme ceux de Saint-Martin. &lt;/p&gt; &lt;audio controls title=&quot;Nicolas de Condorcet par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-03.09.2012-ITEMA_20396586-2012C12410S0247-NET_8DCA5270-1BC9-4149-A100-ED7635D3968F_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Friedrich_Heinrich_Jacobi&quot;  title=&quot; Wikipedia&quot;&gt;Friedrich Heinrich JACOBI&lt;/a&gt;  était un philosophe juif allemand, critique majeur du rationalisme des Lumières et promoteur d'une philosophie du sentiment et de la foi, opposée à la raison spéculative. Il accusa les systèmes philosophiques de Spinoza, Kant et leurs successeurs de mener inévitablement au  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nihilisme&quot;  title=&quot;Nihilisme par Wikipedia&quot;&gt; nihilisme &lt;/a&gt; et au &lt;a href=&quot;https://fr.wikipedia.org/wiki/Panth%C3%A9isme&quot;  title=&quot;Panthéisme par Wikipedia&quot;&gt;panthéisme, &lt;/a&gt; en niant la réalité personnelle de Dieu et la liberté humaine. Issu d'une famille de marchands de sucre à Düsseldorf, il dirigea l'entreprise familiale avant d'entrer en politique comme conseiller ministériel dans les duchés de Berg et Juliers, puis président de l'Académie des sciences de Munich. Ami de Goethe et Lessing, il déclencha la fameuse &quot;querelle du panthéisme&quot; en révélant que Lessing s'était  &lt;a href=&quot;https://www.persee.fr/doc/cafon_0395-8418_1985_num_36_1_1321&quot;  title=&quot;Jacobi et Spinoza par Persée&quot;&gt;confessé spinoziste, &lt;/a&gt; critiquant ainsi l'idéalisme comme une réduction du réel à un mécanisme rationnel sans fondement absolu . &lt;/p&gt; &lt;p&gt; Il  distinguait la Verstand (raison discursive, limitée au conditionné et au déterminisme du &quot;rien ne sort du néant&quot;) de la Vernunft (raison supérieure, intuitive, accédant à la révélation immédiate via le sentiment et la foi). Pour lui, toute connaissance systématique repose sur un &quot;saut de la foi&quot; hors de la logique : Dieu, la liberté et l'immortalité ne se prouvent pas, mais se saisissent dans une certitude immédiate du cœur, évitant le nihilisme des philosophies conséquentes.&lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Sur la doctrine de Spinoza en lettres à Monsieur Moses Mendelssohn (1785) : Débat avec Mendelssohn, dénonçant Spinoza comme aboutissement fatal du rationalisme. - David Hume sur la foi (1787) : Défend la croyance immédiate contre le scepticisme empirique. - Du divin (1811) : Synthèse tardive sur la révélation personnelle et l'ordre divin des valeurs. &lt;/p&gt; &#10;&#10;&#10;" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marcus_Herz&quot;  title=&quot; Wikipedia&quot;&gt;Marcus HERZ&lt;/a&gt;    était  un médecin et philosophe juif allemand, disciple éminent d'Immanuel Kant et figure des Lumières berlinoises. Issu d'une famille modeste, il étudia la médecine et la philosophie à Königsberg, où il devint proche de Kant.  Après ses études, il s'installa à Berlin comme médecin à l'hôpital juif et professeur de philosophie à l'Académie des sciences en 1791, tout en tenant des conférences populaires sur la médecine et Kant. Ami de Moses Mendelssohn et correspondant de Kant  &lt;a href=&quot;https://www.persee.fr/doc/phlou_0035-3841_1973_num_71_10_5741_t1_0371_0000_2&quot; title=&quot;Kant, Lettre à Marcus Herz du 21 février 1772 par Persée&quot;&gt;(notamment la lettre de 1772  &lt;/a&gt; sur la &quot;révolution copernicienne&quot;), il fut un vecteur clé du kantisme à Berlin via son salon tenu par son épouse Henriette. Il mourut à Berlin le 19 janvier 1803, après une carrière mêlant pratique médicale et enseignement philosophique. &lt;/p&gt; &lt;p&gt; Parmi ses écrits figurent &quot;Betrachtungen aus der spekulativen Weltweisheit&quot;  paru en 1771, un commentaire de la dissertation inaugurale de Kant, et &quot;Versuch über den Geschmack&quot; en 1776, explorant le goût et la sensibilité dans une veine précritique. Il publia aussi sur la médecine et le vertige, reliant empirisme et métaphysique. &lt;/p&gt; &lt;p&gt; Il développa les idées kantiennes précritiques sur la sensibilité et la raison, insistant sur leurs implications métaphysiques via Maïmonide, et divergea de Kant sur la substantialité de l'âme. Son kantisme original influença les débats juifs des Lumières et la diffusion de la philosophie critique en Prusse. &lt;/p&gt; " r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/David_Friedl%C3%A4nder&quot;  title=&quot; Wikipedia&quot;&gt;David FRIEDLÄNDER&lt;/a&gt;  était un intellectuel, marchand et réformateur juif allemand, disciple de Moses Mendelssohn, plus connu comme pionnier de l'Haskalah (Lumières juives) et de la  &lt;a  href=&quot;https://www.persee.fr/doc/reval_0035-0974_1973_num_5_3_1989&quot;  title=&quot;D Friedlander et la réforme des communaités juives de prusse par Persée&quot;&gt; réforme religieuse &lt;/a&gt; que comme philosophe académique strict. Il prôna l'émancipation des Juifs par l'assimilation culturelle et une dédogmatisation du judaïsme, fusionnant rationalisme des Lumières et monothéisme mosaïque originel contre les rituels &quot;superstitieux&quot;. &lt;/p&gt; &lt;p&gt; Né à Königsberg, il s'installa à Berlin en 1770, fonda une usine de soie et intégra l'élite juive éclairée via son mariage avec la fille du banquier Daniel Itzig. Après la mort de Mendelssohn (1786), il mena la Haskalah berlinoise : création de la Chevrat Chinuch Ne’arim (école juive libre en 1778), traductions de prières en allemand, et plaidoyers pour l'égalité civile. Premier conseiller municipal juif à Berlin, il lutta contre les discriminations prussiennes. &lt;/p&gt; &lt;p&gt; Il rejetait le Talmud et les rites comme &quot;œuvres de sainteté, verbiage et futilités&quot;, défendant un judaïsme &quot;pur&quot; : monothéisme rationnel commun aux religions abrahamiques, sans dogmes christologiques ni observances contraignantes. Dans son Sendschreiben anonyme (1799) à l'ecclésiastique Wilhelm Teller, il proposa une union judéo-protestante déiste – baptême symbolique sans trinité, en échange d'émancipation –, vu comme opportuniste mais innovant pour le judaïsme réformé naissant. Il resta juif par fidélité au &quot;monothéisme mosaïque idéal&quot;, contrairement à sa famille convertie. &lt;/p&gt; &lt;p&gt; Précurseur du judaïsme réformé et de l'assimilation prussienne, Friedländer incarna le dilemme post-mendelssohnien : identité juive face à l'universalisme. Critiqué pour pragmatisme, il influença les réformes liturgiques et débats sur l'émancipation, bien que son projet fusionnel échouât face au romantisme montant. &lt;/p&gt; &#10;&#10;" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" display="https://laphilo.fr/photo/dfriedlander.webp" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Joseph_de_Maistre&quot;  title=&quot; Wikipedia&quot;&gt;Joseph de MAISTRE&lt;/a&gt; était un philosophe, écrivain et diplomate savoyard, figure majeure de la contre-révolution et critique virulent des Lumières et de la Révolution française. Considéré comme un père de la pensée conservatrice moderne, il défend une vision organique de la société, hiérarchique et divinement ordonnée, où l'autorité monarchique et religieuse prime sur les idées contractualistes et individualistes. &lt;/p&gt; &lt;p&gt;  Pour lui, la Révolution française est un &lt;a href=&quot;https://www.persee.fr/doc/bude_0004-5527_1989_num_1_2_1393&quot; title=&quot;Sacré et sacrifice dans la pensée de Joseph de Maistre par Persée&quot;&gt;châtiment providentiel &lt;/a&gt; des excès des philosophes des Lumières, punissant l'athéisme et le rationalisme par la Terreur. Les sociétés ne naissent pas d'un contrat rationnel (comme chez Rousseau), mais d'une autorité divine imposée d'en haut; l'individu abstrait n'existe pas, il est façonné par la tradition et l'État.  Il prône une monarchie absolue et l'autorité suprême du Pape pour unifier l'Europe spirituellement et temporellement. &lt;/p&gt; &lt;p&gt; Ses oeuvres majeures sont : - &quot;Considérations sur la France&quot; paru en 1797 : Interprétation providentialiste de la Révolution comme mission divine de la France. - &quot;Essai sur le principe générateur des constitutions&quot; paru en 1809 :  &lt;a href=&quot;https://www.youtube.com/watch?v=oPEzOiEdrNE&quot;  title=&quot; L'oecuménisme de Joseph de Maistre par BAGLIS TV&quot;&gt;Les constitutions &lt;/a&gt; viennent de Dieu, non de la raison humaine et - &quot;Soirées de Saint-Pétersbourg&quot;  en1821, posthume : Théodicée justifiant le mal (guerre, sacrifice) comme partie du plan divin. &lt;/p&gt; &lt;p&gt; Il a eu une influence durablement le conservatisme, le romantisme contre-révolutionnaire et des penseurs comme Donoso Cortés, tout en étant critiqué pour son apologie de la violence. Sa pensée hiérarchique et anti-individualiste reste débattue face aux idéaux démocratiques modernes. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt; &lt;p&gt;  &lt;audio controls title=&quot;Troisième penseur, Joseph de Maistre. par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-26.10.2011-ITEMA_20317797-2011C12410S0299-NET_F022382B-0B64-4C5C-B335-284B201C884D_DF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt;" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Louis_de_Bonald&quot;  title=&quot; Wikipedia&quot;&gt;Louis BONALD&lt;/a&gt;  était un philosophe et théoricien contre-révolutionnaire français, chef de file du  &lt;a href=&quot;https://fr.wikipedia.org/wiki/Tradition_primordiale&quot;  title=&quot; Tradition Primordiale de Maistre par Wikipedia &quot;&gt; traditionalisme, &lt;/a&gt; qui opposa la société organique et divine à l'individualisme des Lumières et de la Révolution. Pour lui, la société précède l'individu : « l'homme n'existe que pour la société et la société ne le forme que pour elle », avec un pouvoir partout présent (Dieu, roi, père) structurant famille, État et Église en triade cause-ministres-sujets. &lt;/p&gt; &lt;p&gt; Il  rejette la Déclaration des droits de l'homme comme génératrice d'anarchie, prônant la monarchie absolue adoucie par des contre-pouvoirs (noblesse, sacerdoce) pour réprimer les tendances mauvaises de l'homme déchu. Il critique divorce, héritage partitive et Révolution industrielle pour leur menace sur la famille traditionnelle, base de l'ordre social, et voit la Révolution non comme chute fatale mais comme avertissement pour une restauration morale. &lt;/p&gt; &lt;p&gt; Ses Œuvres principales : - Théorie du pouvoir politique et religieux (1796) : Matrice de sa philosophie, liant pouvoir divin et monarchique dans une métaphysique universaliste. - Essai analytique sur les lois naturelles de l'ordre social (1800) : Démonstration que la société repose sur des lois immuables antérieures à l'individu. - Réplique aux Considérations de Mme de Staël : Défense du trône et de l'autel contre le libéralisme. &lt;/p&gt; Précurseur de la &lt;a href=&quot;https://www.youtube.com/watch?v=WMB9kethTWIe&quot;  title=&quot; Louis de Bonald ,nostalgie ou modernité par Storiavoce histoire et civilisations &quot;&gt; sociologie conservatrice, &lt;/a&gt;  il influença Maurras, Veuillot et le &lt;a href=&quot;https://fr.wikipedia.org/wiki/Nationalisme_int%C3%A9gral&quot;  title=&quot; Maurrassisme par Wikipedia &quot;&gt; maurrassisme, &lt;a&gt; voyant la France comme &quot;nation-pilote&quot; pour régénérer l'Europe contre l'expansionnisme républicain. Distingué de Maistre par son optimisme régénérateur, il reste une référence contre l'égalitarisme atomisant . &lt;/p&gt;&#10; &#10;&#10;//" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Antoine_Destutt_de_Tracy&quot;  title=&quot; Wikipedia&quot;&gt;Destutt de TRACY&lt;/a&gt; était un philosophe et idéologue français, fondateur et théoricien principal du courant philosophique des Idéologues. Né Antoine Louis Claude Destutt, comte de Tracy, dans une famille noble auvergnate, il fit une carrière militaire avant de se consacrer à la philosophie après son emprisonnement pendant la Terreur. Membre de l'Institut national et de l'Académie française, il joua un rôle central dans la vie intellectuelle française sous le Directoire et le Consulat. &lt;/p&gt; &lt;p&gt; Sa contribution majeure est la création de l'« idéologie » comme science des idées. Dans ses &lt;em&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=DAz6QsBdeyg&quot;  title=&quot;Destrutt de DRACYi par Wikipedia Fan&quot;&gt;Éléments d'idéologie &lt;/a&gt; &lt;/em&gt; (5 volumes, 1801-1815), il cherche à fonder une science générale des idées qui analyserait leur formation à partir des sensations et des signes. S'inscrivant dans la tradition sensualiste de Condillac, il développe une sémiologie et une grammaire générale visant à purifier le langage de ses ambiguïtés et à fonder les sciences humaines sur des bases empiriques solides. Son projet était d'édifier une « science des sciences » qui servirait de fondement à l'enseignement et à la réforme sociale. &lt;/p&gt; &lt;p&gt; Sa &lt;em&gt;Logique&lt;/em&gt; et son &lt;em&gt;Commentaire sur l'Esprit des Lois de Montesquieu&lt;/em&gt; (1811) témoignent de son intérêt pour la philosophie politique libérale. Jefferson, qui admirait sa pensée, fit traduire son &lt;em&gt;Traité de la volonté&lt;/em&gt; en anglais. Ironiquement, le terme même d'« idéologie » qu'il avait forgé fut retourné contre lui par Napoléon, qui qualifiait les Idéologues d'esprits abstraits et dangereux. Marx reprit ensuite ce terme dans un sens radicalement différent. Destutt de Tracy reste une figure essentielle pour comprendre l'émergence des sciences humaines en France. &lt;/p&gt;" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Laromigui%C3%A8re&quot;  title=&quot; Wikipedia&quot;&gt;Pierre LAROMIGUIÈRE&lt;/a&gt; était un philosophe français, l'une des figures transitoires entre le sensualisme des Lumières et la philosophie spiritualiste du XIXe siècle. Né à Livinhac-le-Haut dans l'Aveyron, il fut d'abord prêtre avant la Révolution, puis professeur de philosophie à l'École centrale des arts et manufactures et enfin à la Sorbonne. Ses cours, qui attirèrent un public nombreux et enthousiaste dans les premières décennies du XIXe siècle, contribuèrent à renouveler l'enseignement de la philosophie en France. &lt;/p&gt; &lt;p&gt; Sa philosophie part du sensualisme de Condillac mais s'en écarte sur un point décisif : là où Condillac réduisait toutes les opérations de l'esprit à des sensations transformées, Laromiguière distingue soigneusement les sensations des opérations actives de l'attention, de la comparaison et du jugement. Cette distinction entre les facultés passives et les facultés actives de l'esprit ouvre la voie à une conception plus riche de la vie psychique, qui reconnaît la spécificité de l'activité intellectuelle irréductible à la simple réception sensorielle. &lt;/p&gt; &lt;p&gt; Dans ses &lt;em&gt;Leçons de philosophie&lt;/em&gt; (1815-1818), dont la clarté et l'agrément du style lui valurent un succès durable, il développe cette psychologie des facultés dans un cadre pédagogique accessible. Bien que sa pensée ait été éclipsée par le courant spiritualiste de Cousin et par le positivisme de Comte, Laromiguière représente une étape importante dans la constitution de la psychologie philosophique française. Sa manière de corriger Condillac par une attention accrue à l'activité de l'esprit préfigure les développements du spiritualisme ultérieur. &lt;/p&gt;" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_Jean_Georges_Cabanis&quot; title=&quot; Wikipedia&quot;&gt;Pierre CABANIS&lt;/a&gt; était un médecin et philosophe français, figure majeure du groupe des Idéologues et pionnier d'une approche naturaliste de la vie psychique. Né à Cosnac en Corrèze, il fut introduit dans les cercles intellectuels parisiens par Turgot et fréquenta le salon d'Helvétius. Ami intime de Mirabeau dont il soigna les derniers jours, il participa activement à la vie politique de la Révolution et du Directoire, siégeant au Conseil des Cinq-Cents. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;Rapports du physique et du moral de l'homme&lt;/em&gt; (1802), est un essai audacieux pour fonder une science de l'homme sur des bases physiologiques. Cabanis y soutient que les phénomènes psychiques sont intimement liés aux processus organiques du corps : le cerveau secrète la pensée comme le foie sécrète la bile. Cette formule provocatrice, souvent mal comprise, visait en réalité à établir une méthode empirique pour l'étude de l'âme, refusant tout recours à des entités métaphysiques abstraites. &lt;/p&gt; &lt;p&gt; Médecin réformateur, il œuvra à la réorganisation des hôpitaux parisiens et milita pour une médecine fondée sur l'observation clinique plutôt que sur les théories scolastiques. Ses travaux contribuèrent à l'essor de l'hygiénisme et de la médecine sociale. Sa pensée, qui anticipe certains aspects du matérialisme médical du XIXe siècle, représente une étape importante dans la constitution des sciences humaines. Bien que les Idéologues aient été rabroués par Napoléon qui les rendait responsables des « idéologues abstraits », l'influence de Cabanis sur la médecine et la psychologie françaises fut durable. &lt;/p&gt;" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" display="https://www.laphilo.fr/pho/cabanis-mini.webp" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre-Paul_Royer-Collard&quot;  title=&quot; Wikipedia&quot;&gt;Pierre-Paul ROYER-COLLARD&lt;/a&gt;  était un philosophe et homme politique français, figure majeure du libéralisme modéré sous la Restauration et chef des Doctrinaires. Né en Champagne, il commence comme avocat au Parlement de Paris avant de s'engager politiquement. Pendant la Révolution, il soutient les Girondins et fuit la Terreur, se retirant dans ses terres. Sous la Restauration, il devient député de la Marne et préside la Chambre des députés (1828–1830), tout en enseignant l'histoire de la philosophie moderne à la Sorbonne. &lt;/p&gt; &lt;p&gt; Sa philosophie se présente comme un rejet du sensualisme de Condillac qui dominait le XVIIIᵉ siècle français. Il s'inspire du philosophe écossais Thomas Reid et introduit en France la doctrine du sens commun. Contrairement aux sensualistes, il distingue clairement la sensation (subjective, plaisir ou peine) de la perception (appréhension d'un objet externe). Pour lui, la perception implique un jugement spontané de l'esprit actif, non déductible des seuls sens. &lt;/p&gt; &lt;p&gt; Il développe un spiritualisme rigoureux : l'esprit humain est actif et capable de jugements autonomes. Le sens commun – cette faculté naturelle de distinguer le bien du mal, le vrai du faux – fonde la vie communautaire et remplace l'autorité surnaturelle. Par les principes de causalité et d'induction, la raison conduit nécessairement à l'idée d'une Première Cause (Dieu). Il affirme la supériorité irréductible de la personne humaine sur l'État, les personnes étant &lt;a  href=&quot;https://www.youtube.com/watch?v=15bNqKMiW_w&quot;  title=&quot;R Collard ou l’ambilalence des restaurations par Collège st Germain&quot;&gt;« faites à l'image de Dieu et douées d'immortalité ».&lt;/a&gt;  &lt;/p&gt; &lt;p&gt; Politiquement, il est un royaliste libéral qui considère la Révolution de 1789 comme irréversible. Il cherche à fonder une monarchie constitutionnelle stable entre l'Ancien Régime (les Ultras) et le totalitarisme napoléonien, puis la démocratisation trop rapide sous Louis-Philippe. Il incarne la « philosophie de la Charte » et influence profondément François Guizot. N'a presque rien publié de son vivant : ses écrits philosophiques ont été rassemblés après coup par son admirateur Théodore Jouffroy.  &lt;/p&gt; " r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" display="https://www.laphilo.fr/pho/pcollard-mini.webp" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Claude-Henri_de_Rouvroy_de_Saint-Simon&quot; title=&quot; Wikipedia&quot;&gt;Claude-Henri de ROUVROY, comte de SAINT-SIMON&lt;/a&gt; est un penseur et réformateur social français, issu d’une famille aristocratique qui revendiquait une lointaine parenté avec Charlemagne. Volontaire dans l’armée française envoyée soutenir l’indépendance américaine, il participe au siège de Yorktown avant de renoncer, sous la Révolution, à son titre de noblesse.  &lt;a href=&quot;https://maitron.fr/saint-simon-claude-henri-claude-henri-de-rouvroy-comte-de-saint-simon/&quot; title=&quot;saint simon par le maitron&quot;&gt;Spéculateur &lt;/a&gt; sur les biens nationaux, emprisonné pendant la Terreur, il connaît ensuite une vie mouvementée, tour à tour fortunée et misérable, entièrement vouée à la recherche d’une science nouvelle de la société. &lt;/p&gt; &lt;p&gt; Convaincu que la Révolution a détruit l’ancien ordre théologique et féodal sans encore bâtir l’ordre qui doit lui succéder, Saint-Simon appelle à fonder une organisation sociale confiée non plus aux militaires, aux juristes ou aux rentiers, mais aux savants, aux industriels et aux producteurs. Dans des ouvrages comme &lt;em&gt;L’Industrie&lt;/em&gt; ou &lt;em&gt;Du système industriel&lt;/em&gt;, il défend l’idée que le pouvoir politique doit être subordonné à la production utile : gouverner, pour lui, revient d’abord à administrer les choses et à organiser le travail, plutôt qu’à commander les hommes. &lt;/p&gt; &lt;p&gt; Il élabore ainsi une &lt;a href=&quot;https://fr.wikipedia.org/wiki/Saint-simonisme&quot; title=&quot;Saint-simonisme par Wikipedia&quot;&gt;philosophie de l’histoire&lt;/a&gt; fondée sur l’alternance de périodes « organiques » et « critiques », et annonce l’avènement d’un âge industriel où la science et la technique remplaceraient la théologie comme principe d’unité sociale. Son dernier livre, &lt;em&gt;Le Nouveau Christianisme&lt;/em&gt; (1825), publié l’année de sa mort, prône une religion de la fraternité entièrement tournée vers l’amélioration du sort des classes les plus pauvres, qu’il présente comme la fin ultime de toute organisation sociale et politique légitime. &lt;/p&gt; &lt;p&gt; Bien que ses écrits soient souvent fragmentaires et inachevés, Saint-Simon laisse une postérité considérable : ses disciples, réunis après sa mort en une école puis en une véritable Église saint-simonienne, diffusent et systématisent sa pensée sous le nom de saint-simonisme. Ce courant influencera profondément le socialisme utopique du XIXe siècle, la sociologie naissante d’Auguste Comte (un temps son secrétaire), ainsi que les grandes entreprises industrielles et financières du Second Empire, qui reprendront à leur compte son culte du progrès technique et de l’organisation rationnelle de la production. &lt;/p&gt;" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" display="https://www.laphilo.fr/pho/hssimon-mini.webp" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Maine_de_Biran&quot;  title=&quot; Wikipedia&quot;&gt;Maine de BIRAN&lt;/a&gt; était un philosophe français, considéré comme l'un des fondateurs de la philosophie de l'intériorité et du spiritualisme français. Né François-Pierre Gonthier de Biran à Bergerac en Dordogne, il commença sa carrière comme officier de la garde du roi, avant de se consacrer à la philosophie et à la vie politique locale en Périgord. Administrateur apprécié sous plusieurs régimes successifs, il fut député et sous-préfet, mais c'est à travers ses journaux intimes et ses &lt;a  href=&quot;https://www.youtube.com/watch?v=ayhmQ5WQfJk&quot;  title=&quot;Maine de Biran spiritualité &amp; phénoménologie par ICP&quot;&gt;essais philosophiques &lt;/a&gt; que son originalité s'exprima pleinement. &lt;/p&gt; &lt;p&gt; Sa pensée prend pour point de départ l'expérience immédiate de l'effort : c'est dans l'acte volontaire par lequel le moi exerce une résistance contre le corps propre que la conscience se saisit elle-même comme force et comme liberté. Contre le sensualisme de Condillac qui réduisait l'âme à la sensation passive, il soutient que l'activité volontaire constitue le fait primitif de la conscience. Cette découverte du « moi voulant » comme donnée irréductible de l'intériorité marque une rupture décisive dans la philosophie française. &lt;/p&gt; &lt;p&gt; Son œuvre principale, &lt;em&gt;t &lt;a  href=&quot;https://www.persee.fr/doc/bupsy_0007-4403_1963_num_17_224_9102&quot;  title=&quot;Maine de Biran fondateur de la psychologie française par Persée&quot;&gt;Essai sur les fondements de la psychologie &lt;/a&gt; &lt;/em&gt; (1812) et ses nombreux &lt;em&gt;Mémoires&lt;/em&gt; rédigés pour les concours de l'Institut, développent une psychologie de l'effort qui distingue trois ordres d'existence : la vie animale (sensations), la vie humaine (volonté et conscience) et la vie de l'esprit (grâce et amour mystique). Cette trilogie, d'inspiration néo-platonicienne et chrétienne dans sa dernière phase, influença profondément Ravaisson, Bergson et tout le courant spiritualiste français. Ses &lt;em&gt;Journal&lt;/em&gt; et &lt;em&gt;Mémoire sur les perceptions obscures&lt;/em&gt; témoignent d'une introspection d'une subtilité et d'une profondeur rares. &lt;/p&gt;" r:id="rId51"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -1153,7 +1153,7 @@
       </c>
       <c r="L8" s="46" t="inlineStr">
         <is>
-          <t>Humanisme</t>
+          <t xml:space="preserve">Humanisme</t>
         </is>
       </c>
       <c r="M8" s="45" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -4622,8 +4622,7 @@
       </c>
       <c r="E60" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/David_Hume"  title=" Wikipedia"&gt;David HUME&lt;/a&gt; était un philosophe, historien et économiste écossais de l'ère des Lumières. Il est surtout connu pour ses contributions à la philosophie empirique, la théorie de la connaissance, la métaphysique, l'éthique et l'esthétique. &lt;/p&gt; &lt;p&gt; Hume était un sceptique et a cherché à examiner de manière critique les idées préconçues et les &lt;a  href="https://www.youtube.com/watch?v=CLIoxw6TXuk&amp;ab_channel=LePr%C3%A9cepteur"  title="Tout n'est que croyance  par Le Précepteur"&gt;croyances reçues&lt;/a&gt;. Il a rejeté les arguments métaphysiques qui ne pouvaient pas être fondés sur l'expérience directe, et a affirmé que les connaissances humaines étaient basées sur les impressions et les idées que nous en avons. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de &lt;a  href="https://www.youtube.com/watch?v=ftd3vjw9lSU"  title=" la causalité par Skarblown Animations"&gt;la causalité&lt;/a&gt;, qui affirme que nous ne pouvons pas connaître la relation de cause à effet entre deux événements par simple observation, mais que nous sommes amenés à croire en une telle relation en raison de notre expérience passée.  &lt;/p&gt; &lt;p&gt; En éthique, il a affirmé que la morale était basée sur des sentiments plutôt que sur la raison et qu'elle ne peut pas être déduite de principes rationnels, mais doit être fondée sur l'empathie et la sympathie envers les autres.  &lt;/p&gt; &lt;p&gt; Il a également souligné l'importance du bonheur et du plaisir dans la vie, affirmant que ce sont des aspects essentiels de notre existence et de notre &lt;a  href="https://www.youtube.com/watch?v=52077nWSkPM&amp;t=11s&amp;ab_channel=LePr%C3%A9cepteur"   title="l'identité par le Précepteur"&gt;identité&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il a écrit sur la religion et a critiqué les arguments traditionnels pour l'existence de Dieu en affirmant que la religion était basée sur la superstition plutôt que sur la raison, et que la croyance en Dieu était fondée sur l'habitude plutôt que sur la preuve. &lt;/p&gt;  &lt;audio controls title="Pourquoi faut il lire David Hume par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22838-02.02.2022-ITEMA_22927004-2022C45539E0018-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/David_Hume" title=" Wikipedia"&gt;David HUME&lt;/a&gt; était un philosophe, historien et économiste écossais de l'ère des Lumières. Il est surtout connu pour ses contributions à la philosophie empirique, la théorie de la connaissance, la métaphysique, l'éthique et l'esthétique. &lt;/p&gt; &lt;p&gt;Il était un sceptique et a cherché à examiner de manière critique les idées préconçues et les &lt;a href="https://www.youtube.com/watch?v=CLIoxw6TXuk&amp;amp;ab_channel=LePr%C3%A9cepteur" title="Tout n'est que croyance  par Le Précepteur"&gt;croyances reçues&lt;/a&gt;. Il a rejeté les arguments métaphysiques qui ne pouvaient pas être fondés sur l'expérience directe, et a affirmé que les connaissances humaines étaient basées sur les impressions et les idées que nous en avons. &lt;/p&gt; &lt;p&gt; Il est connu pour sa théorie de &lt;a href="https://www.youtube.com/watch?v=ftd3vjw9lSU" title=" la causalité par Skarblown Animations"&gt;la causalité&lt;/a&gt;, qui affirme que nous ne pouvons pas connaître la relation de cause à effet entre deux événements par simple observation, mais que nous sommes amenés à croire en une telle relation en raison de notre expérience passée.  &lt;/p&gt; &lt;p&gt; En éthique, il a affirmé que la morale était &lt;a href="https://www.youtube.com/watch?v=sAmpsfWIt4s" title="HUME - L'appel à la nature par Le Précepteur"&gt;basée sur des sentiments &lt;/a&gt;plutôt que sur la raison et qu'elle ne peut pas être déduite de principes rationnels, mais doit être fondée sur l'empathie et la sympathie envers les autres.  &lt;/p&gt; &lt;p&gt; Il a également souligné l'importance du bonheur et du plaisir dans la vie, affirmant que ce sont des aspects essentiels de notre existence et de notre &lt;a href="https://www.youtube.com/watch?v=52077nWSkPM&amp;amp;t=11s&amp;amp;ab_channel=LePr%C3%A9cepteur" title="l'identité par le Précepteur"&gt;identité&lt;/a&gt;.  &lt;/p&gt; &lt;p&gt; Il a écrit sur la religion et a critiqué les arguments traditionnels pour l'existence de Dieu en affirmant que la religion était basée sur la superstition plutôt que sur la raison, et que la croyance en Dieu était fondée sur l'habitude plutôt que sur la preuve. &lt;/p&gt;  &lt;audio controls title="Pourquoi faut il lire David Hume par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22838-02.02.2022-ITEMA_22927004-2022C45539E0018-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F60" s="47" t="inlineStr">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -7214,6 +7214,353 @@
         </is>
       </c>
       <c r="P100"/>
+    </row>
+    <row r="101" ht="130.5" customHeight="1" s="39">
+      <c r="A101" s="47">
+        <v>1714</v>
+      </c>
+      <c r="B101" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1780</t>
+        </is>
+      </c>
+      <c r="C101" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1714 – 1780</t>
+        </is>
+      </c>
+      <c r="D101" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Étienne Bonnot de CONDILLAC</t>
+        </is>
+      </c>
+      <c r="E101" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Bonnot_de_Condillac" title=" Wikipedia"&gt;Étienne Bonnot de CONDILLAC&lt;/a&gt; est un philosophe français. Né à Grenoble en 1714, frère cadet de l’abbé de Mably, il devient prêtre mais ne dit sa messe qu’une seule fois et se consacre entièrement à la philosophie. À Paris, il se lie avec Rousseau et Diderot. De 1758 à 1767, il est le précepteur du jeune prince de Parme, pour qui il rédige un vaste &lt;em&gt;Cours d’études&lt;/em&gt;. Élu à l’Académie française en 1768, il se retire ensuite dans son domaine de Flux, près de Beaugency, où il meurt en 1780.&lt;/p&gt; &lt;p&gt;Disciple de Locke, il veut aller plus loin que lui. Dans l’&lt;em&gt;Essai sur l’origine des connaissances humaines&lt;/em&gt; (1746), il montre le rôle décisif du langage : sans les signes, nous ne pourrions ni retenir ni combiner nos idées. Dans le &lt;em&gt;Traité des sensations&lt;/em&gt; (1754), il imagine une statue de marbre à laquelle on donnerait les sens un à un, en commençant par l’odorat : sentant une rose, elle « est » odeur de rose. Il montre ainsi que l’attention, la mémoire, le jugement et le désir ne sont que des « sensations transformées ». C’est le sensualisme, forme radicale de l’&lt;a href="https://fr.wikipedia.org/wiki/Empirisme" title=" Wikipedia"&gt;empirisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans le &lt;em&gt;Traité des systèmes&lt;/em&gt; (1749), il critique les grands systèmes de Descartes, Spinoza et Leibniz, bâtis sur des principes abstraits. Pour lui, une science n’est qu’« une langue bien faite » : penser juste, c’est analyser, c’est-à-dire décomposer et recomposer ses idées, comme en algèbre. Il est aussi l’un des premiers à fonder la valeur économique sur l’utilité. Ses idées inspirent les « Idéologues » de la Révolution et la réforme de l’enseignement.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/condillac-mini.webp</t>
+        </is>
+      </c>
+      <c r="J101" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K101" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; langage</t>
+        </is>
+      </c>
+      <c r="L101" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empirisme ; Lumières</t>
+        </is>
+      </c>
+      <c r="M101" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe français des Lumières, pour qui toutes nos idées sont des « sensations transformées ».</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P101"/>
+    </row>
+    <row r="102" ht="130.5" customHeight="1" s="39">
+      <c r="A102" s="47">
+        <v>1717</v>
+      </c>
+      <c r="B102" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1783</t>
+        </is>
+      </c>
+      <c r="C102" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717 – 1783</t>
+        </is>
+      </c>
+      <c r="D102" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jean Le Rond D'ALEMBERT</t>
+        </is>
+      </c>
+      <c r="E102" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Le_Rond_d%27Alembert" title=" Wikipedia"&gt;Jean Le Rond D'ALEMBERT&lt;/a&gt; est un mathématicien et philosophe français. Né à Paris en 1717, enfant illégitime de Mme de Tencin, il est abandonné sur les marches de l’église Saint-Jean-le-Rond, dont il tire son prénom, et élevé par la femme d’un vitrier. Son père lui assure une bonne éducation. Mathématicien précoce, il entre à l’Académie des sciences à 24 ans. Son &lt;em&gt;Traité de dynamique&lt;/em&gt; (1743) énonce le « principe de d’Alembert », et il découvre en 1747 l’équation qui décrit la vibration des cordes.&lt;/p&gt; &lt;p&gt;Avec Diderot, il dirige l’&lt;em&gt;Encyclopédie&lt;/em&gt; à partir de 1751 et en rédige le &lt;em&gt;Discours préliminaire&lt;/em&gt;. Inspiré de Bacon et de Locke, il y classe toutes les connaissances selon les trois facultés de l’esprit, la mémoire, la raison et l’imagination, qui donnent l’histoire, la philosophie et les beaux-arts. Il y retrace aussi l’histoire du progrès de l’esprit humain depuis la Renaissance. Son article « Genève » (1757) provoque la colère des pasteurs genevois et la réponse de Rousseau, la &lt;em&gt;Lettre à d’Alembert sur les spectacles&lt;/em&gt;. Lassé des attaques, il quitte la direction de l’&lt;em&gt;Encyclopédie&lt;/em&gt; en 1758.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Éléments de philosophie&lt;/em&gt; (1759), il défend une philosophie modeste, qui s’en tient aux faits et se méfie de la métaphysique. Secrétaire perpétuel de l’Académie française à partir de 1772, il est l’un des chefs du parti des philosophes et l’ami de Frédéric II de Prusse. Il meurt à Paris en 1783.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/dalembert-mini.webp</t>
+        </is>
+      </c>
+      <c r="J102" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K102" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L102" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumières ; Empirisme</t>
+        </is>
+      </c>
+      <c r="M102" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mathématicien et philosophe français, codirecteur de l’Encyclopédie avec Diderot.</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" ht="130.5" customHeight="1" s="39">
+      <c r="A103" s="47">
+        <v>1632</v>
+      </c>
+      <c r="B103" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1694</t>
+        </is>
+      </c>
+      <c r="C103" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1632 – 1694</t>
+        </is>
+      </c>
+      <c r="D103" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samuel von PUFENDORF</t>
+        </is>
+      </c>
+      <c r="E103" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_von_Pufendorf" title=" Wikipedia"&gt;Samuel von PUFENDORF&lt;/a&gt; est un juriste, philosophe et historien allemand. Né en 1632 en Saxe, fils d’un pasteur luthérien, il étudie à Leipzig et à Iéna. Précepteur dans la famille de l’ambassadeur de Suède à Copenhague, il est emprisonné pendant la guerre entre la Suède et le Danemark, et rédige en captivité ses premiers &lt;em&gt;Éléments de jurisprudence universelle&lt;/em&gt; (1660). En 1661, l’électeur palatin crée pour lui à Heidelberg la première chaire de droit naturel et de droit des gens. Il enseigne ensuite à Lund, en Suède, puis devient historiographe des rois de Suède et de l’électeur de Brandebourg. Il meurt à Berlin en 1694.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Du droit de la nature et des gens&lt;/em&gt; (1672) et son abrégé, &lt;em&gt;Les Devoirs de l’homme et du citoyen&lt;/em&gt; (1673), il fonde le droit naturel sur la sociabilité. L’homme, faible et incapable de survivre seul, a besoin des autres : la loi fondamentale de la nature lui commande donc de vivre en société et de la préserver. Les règles morales ne sont pas inscrites dans les choses, mais imposées par la volonté de Dieu, qui leur donne leur force obligatoire. L’État naît d’un double contrat, par lequel les hommes s’unissent puis se soumettent à un souverain.&lt;/p&gt; &lt;p&gt;Sous un pseudonyme, il décrit le Saint-Empire comme un « corps irrégulier, semblable à un monstre ». Traduit en français par Jean Barbeyrac, il est lu dans toute l’Europe, de Locke à Rousseau, et influence le &lt;a href="https://fr.wikipedia.org/wiki/Contractualisme" title=" Wikipedia"&gt;contractualisme&lt;/a&gt; et la pensée des droits de l’homme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/pufendorf-mini.webp</t>
+        </is>
+      </c>
+      <c r="J103" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allemande</t>
+        </is>
+      </c>
+      <c r="K103" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L103" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contractualisme</t>
+        </is>
+      </c>
+      <c r="M103" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juriste et philosophe allemand, grand théoricien du droit naturel fondé sur la sociabilité humaine.</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" ht="130.5" customHeight="1" s="39">
+      <c r="A104" s="47">
+        <v>1730</v>
+      </c>
+      <c r="B104" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1788</t>
+        </is>
+      </c>
+      <c r="C104" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1730 – 1788</t>
+        </is>
+      </c>
+      <c r="D104" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Johann Georg HAMANN</t>
+        </is>
+      </c>
+      <c r="E104" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Georg_Hamann" title=" Wikipedia"&gt;Johann Georg HAMANN&lt;/a&gt; est un philosophe et écrivain allemand. Né à Königsberg en 1730, fils d’un chirurgien-barbier, il étudie sans terminer ses études et devient précepteur. En 1757, envoyé à Londres pour une mission commerciale, il échoue, s’endette et traverse une grave crise. La lecture de la Bible le bouleverse et le convertit à un christianisme fervent. De retour à Königsberg, il refuse de revenir aux idées des Lumières que lui proposent ses amis, dont Kant. Il vit modestement comme employé des douanes et meurt à Münster en 1788. Ses contemporains l’appellent le « Mage du Nord ».&lt;/p&gt; &lt;p&gt;Dans les &lt;em&gt;Mémorables socratiques&lt;/em&gt; (1759), il fait de l’ignorance de Socrate le modèle de la foi : comme le montre Hume, nous ne pouvons rien prouver de l’existence des choses, nous ne pouvons que la croire. La raison n’est pas une faculté souveraine, détachée de la vie : elle est liée à la sensibilité, à l’histoire, à la tradition, et d’abord au langage. Dans &lt;em&gt;Aesthetica in nuce&lt;/em&gt; (1762), il proclame : « La poésie est la langue maternelle du genre humain. »&lt;/p&gt; &lt;p&gt;Dans sa &lt;em&gt;Métacritique du purisme de la raison&lt;/em&gt; (1784), il reproche à Kant d’avoir voulu purifier la raison de la tradition, de l’expérience et du langage : or le langage est « le premier et le dernier organe de la raison ». Son style obscur, fait d’allusions et de citations, a fasciné Herder, Goethe et le mouvement du Sturm und Drang, puis Kierkegaard. Il est l’un des grands critiques des Lumières et un précurseur du &lt;a href="https://fr.wikipedia.org/wiki/Romantisme" title=" Wikipedia"&gt;romantisme&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/hamann-mini.webp</t>
+        </is>
+      </c>
+      <c r="J104" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allemande</t>
+        </is>
+      </c>
+      <c r="K104" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L104" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irrationalisme ; Romantisme</t>
+        </is>
+      </c>
+      <c r="M104" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe allemand, le « Mage du Nord », critique des Lumières et penseur du langage.</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P104"/>
+    </row>
+    <row r="105" ht="130.5" customHeight="1" s="39">
+      <c r="A105" s="47">
+        <v>1671</v>
+      </c>
+      <c r="B105" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1713</t>
+        </is>
+      </c>
+      <c r="C105" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1671 – 1713</t>
+        </is>
+      </c>
+      <c r="D105" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHAFTESBURY</t>
+        </is>
+      </c>
+      <c r="E105" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anthony_Ashley-Cooper_%283e_comte_de_Shaftesbury%29" title=" Wikipedia"&gt;SHAFTESBURY&lt;/a&gt; est le nom sous lequel on connaît Anthony Ashley Cooper, troisième comte de Shaftesbury, philosophe et homme politique anglais. Né à Londres en 1671, petit-fils d’un grand homme d’État, il reçoit une éducation dirigée par John Locke, médecin et ami de la famille. Il siège au Parlement, puis à la Chambre des lords, mais une santé fragile l’éloigne de la politique. Il réunit ses essais dans les &lt;em&gt;Caractéristiques des hommes, des mœurs, des opinions et des temps&lt;/em&gt; (1711). Il part se soigner en Italie et meurt à Naples en 1713.&lt;/p&gt; &lt;p&gt;Contre Hobbes, pour qui l’homme n’agit que par intérêt, il soutient que nous avons des affections naturelles pour autrui et pour le bien commun. Nous possédons un « sens moral », une capacité spontanée de sentir ce qui est bon ou mauvais, comme nous sentons ce qui est beau ou laid. La vertu consiste à harmoniser nos affections entre elles et avec l’ordre de l’univers. Le beau, le bien et le vrai ne font qu’un. Il s’inspire des stoïciens et des platoniciens de Cambridge, et défend un &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9isme" title=" Wikipedia"&gt;déisme&lt;/a&gt; tolérant, où la morale n’a pas besoin des récompenses et des châtiments divins.&lt;/p&gt; &lt;p&gt;Il fait de l’humour et du ridicule une épreuve de la vérité : seules les idées fausses craignent la raillerie. Il influence Hutcheson et Hume, puis Diderot, qui traduit son &lt;em&gt;Essai sur le mérite et la vertu&lt;/em&gt; en 1745, et l’esthétique allemande. Son idée d’un plaisir désintéressé, pris au beau sans désir de le posséder, sera reprise par Kant.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/shaftesbury-mini.webp</t>
+        </is>
+      </c>
+      <c r="J105" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K105" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; esthetique</t>
+        </is>
+      </c>
+      <c r="L105" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Déisme ; Platonisme</t>
+        </is>
+      </c>
+      <c r="M105" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe anglais, inventeur du « sens moral » et penseur de l’harmonie entre le beau et le bien.</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P105"/>
+    </row>
+    <row r="106" ht="130.5" customHeight="1" s="39">
+      <c r="A106" s="47">
+        <v>1484</v>
+      </c>
+      <c r="B106" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1566</t>
+        </is>
+      </c>
+      <c r="C106" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1484 – 1566</t>
+        </is>
+      </c>
+      <c r="D106" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bartolomé de LAS CASAS</t>
+        </is>
+      </c>
+      <c r="E106" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bartolom%C3%A9_de_las_Casas" title=" Wikipedia"&gt;Bartolomé de LAS CASAS&lt;/a&gt; est un prêtre, historien et théologien espagnol. Né à Séville en 1484, il part en 1502 pour l’île d’Hispaniola, où il devient colon et reçoit des Indiens à son service. Ordonné prêtre, il participe encore à la conquête de Cuba. En 1514, en méditant un passage de la Bible, il prend conscience de l’injustice faite aux Indiens, renonce à ses biens et consacre le reste de sa longue vie à leur défense. Il entre dans l’ordre des Dominicains en 1522 et devient évêque du Chiapas, au Mexique, en 1544. Il meurt à Madrid en 1566.&lt;/p&gt; &lt;p&gt;Dans sa &lt;em&gt;Très brève relation de la destruction des Indes&lt;/em&gt; (1552), il décrit les massacres, l’esclavage et les mauvais traitements infligés par les conquérants. Ses démarches auprès de Charles Quint contribuent aux « Lois nouvelles » de 1542, qui interdisent de réduire les Indiens en esclavage. En 1550-1551, lors de la controverse de Valladolid, il s’oppose au juriste Juan Ginés de Sepúlveda, qui juge les Indiens inférieurs et faits pour obéir. Pour lui, « toutes les nations du monde sont des hommes », doués de raison et libres, et on ne peut les convertir que par la persuasion.&lt;/p&gt; &lt;p&gt;Il soutient que les civilisations amérindiennes valent celles des Grecs et des Romains. Il a d’abord proposé de faire venir des esclaves africains pour soulager les Indiens, mais il l’a regretté et a condamné aussi leur esclavage. Il est vu comme un précurseur des droits de l’homme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/lascasas-mini.webp</t>
+        </is>
+      </c>
+      <c r="J106" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espagnole</t>
+        </is>
+      </c>
+      <c r="K106" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L106" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Thomisme</t>
+        </is>
+      </c>
+      <c r="M106" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dominicain espagnol, défenseur des Indiens d’Amérique contre les colons, adversaire de Sepúlveda à Valladolid.</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P106">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P106"/>
+  <dimension ref="A1:P109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -7561,6 +7561,176 @@
       <c r="P106">
         <v>2</v>
       </c>
+    </row>
+    <row r="107" ht="130.5" customHeight="1" s="39">
+      <c r="A107" s="47">
+        <v>1497</v>
+      </c>
+      <c r="B107" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1560</t>
+        </is>
+      </c>
+      <c r="C107" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1497 – 1560</t>
+        </is>
+      </c>
+      <c r="D107" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippe MÉLANCHTHON</t>
+        </is>
+      </c>
+      <c r="E107" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippe_M%C3%A9lanchthon" title=" Wikipedia"&gt;Philippe MÉLANCHTHON&lt;/a&gt; est un humaniste, théologien et réformateur allemand. Né en 1497 à Bretten, dans le Bade, sous le nom de Philipp Schwartzerdt, « terre noire », il reçoit de son grand-oncle, l’humaniste Reuchlin, le nom grec de Melanchthon, qui a le même sens. Enfant prodige, il devient à 21 ans professeur de grec à l’université de Wittenberg, où il rencontre Luther. Il devient son plus proche collaborateur et le restera jusqu’à la mort de celui-ci. Il meurt à Wittenberg en 1560.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Lieux communs&lt;/em&gt; (1521), il donne le premier exposé systématique de la théologie de la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9forme_protestante" title=" Wikipedia"&gt;Réforme&lt;/a&gt; : le salut vient de la grâce de Dieu, reçue par la foi, et non des œuvres. En 1530, il rédige la &lt;em&gt;Confession d’Augsbourg&lt;/em&gt;, présentée à l’empereur Charles Quint, qui reste aujourd’hui le texte de référence des Églises luthériennes. D’un caractère plus conciliant que Luther, il cherche toute sa vie un accord avec les catholiques et les réformés, ce qui lui vaut de nombreux reproches.&lt;/p&gt; &lt;p&gt;Humaniste, il est convaincu que la foi a besoin des lettres et des sciences. Il réorganise les écoles et les universités allemandes, écrit des manuels de grammaire, de rhétorique, de dialectique, de physique et d’éthique, et réintroduit Aristote dans l’enseignement. Ses contemporains le surnomment le « précepteur de l’Allemagne ». Peu avant sa mort, il note qu’il sera bientôt délivré de la « rage des théologiens ».&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/melanchthon-mini.webp</t>
+        </is>
+      </c>
+      <c r="J107" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allemande</t>
+        </is>
+      </c>
+      <c r="K107" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; ethique</t>
+        </is>
+      </c>
+      <c r="L107" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme ; Réforme-protestante</t>
+        </is>
+      </c>
+      <c r="M107" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">humaniste et réformateur allemand, compagnon de Luther, surnommé le « précepteur de l’Allemagne ».</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" ht="130.5" customHeight="1" s="39">
+      <c r="A108" s="47">
+        <v>1655</v>
+      </c>
+      <c r="B108" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1728</t>
+        </is>
+      </c>
+      <c r="C108" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1655 – 1728</t>
+        </is>
+      </c>
+      <c r="D108" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christian THOMASIUS</t>
+        </is>
+      </c>
+      <c r="E108" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Thomasius" title=" Wikipedia"&gt;Christian THOMASIUS&lt;/a&gt; est un juriste et philosophe allemand, l’un des pionniers des Lumières allemandes. Né à Leipzig en 1655, fils du philosophe Jakob Thomasius, qui fut le maître de Leibniz, il étudie le droit et découvre l’œuvre de Pufendorf. Professeur à Leipzig, il fait scandale en 1687 en annonçant un cours en allemand, et non en latin comme l’exigeait la tradition. Il lance aussi l’une des premières revues savantes en langue allemande. Chassé de Leipzig en 1690 pour ses idées, il participe à la fondation de l’université de Halle, où il enseigne jusqu’à sa mort en 1728.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Fondements du droit de nature et des gens&lt;/em&gt; (1705), il distingue trois domaines : le juste, qui règle les rapports extérieurs entre les hommes et peut être imposé par la contrainte ; l’honnête, qui concerne la vie intérieure et la vertu ; et le convenable, qui relève de la politesse. Le droit ne doit pas se mêler des consciences : l’État doit garantir la paix extérieure, non imposer la vertu ou la vraie foi. Il défend ainsi la tolérance religieuse et la liberté de penser.&lt;/p&gt; &lt;p&gt;Il mène une campagne célèbre contre les procès de sorcellerie : dans un traité de 1701, il soutient que le pacte avec le diable est une invention et que les aveux obtenus sous la torture n’ont aucune valeur. Il combat aussi la torture elle-même. Son influence contribue à la fin des bûchers en Prusse. Il est l’un des initiateurs des &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt; en Allemagne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/thomasius-mini.webp</t>
+        </is>
+      </c>
+      <c r="J108" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allemande</t>
+        </is>
+      </c>
+      <c r="K108" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L108" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumières</t>
+        </is>
+      </c>
+      <c r="M108" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juriste et philosophe allemand, pionnier des Lumières allemandes et adversaire des procès de sorcellerie.</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P108"/>
+    </row>
+    <row r="109" ht="130.5" customHeight="1" s="39">
+      <c r="A109" s="47">
+        <v>1723</v>
+      </c>
+      <c r="B109" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1816</t>
+        </is>
+      </c>
+      <c r="C109" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1723 – 1816</t>
+        </is>
+      </c>
+      <c r="D109" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adam FERGUSON</t>
+        </is>
+      </c>
+      <c r="E109" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Ferguson" title=" Wikipedia"&gt;Adam FERGUSON&lt;/a&gt; est un philosophe et historien écossais, l’une des figures des Lumières écossaises, avec ses amis Hume et Adam Smith. Né en 1723 dans le Perthshire, dans une région de langue gaélique, il est d’abord aumônier d’un régiment écossais de l’armée britannique. Il enseigne ensuite à l’université d’Édimbourg la philosophie naturelle, puis la philosophie morale, de 1764 à 1785. En 1778, il accompagne une mission britannique chargée de négocier la paix avec les colonies américaines révoltées. Il meurt à St Andrews en 1816, à 92 ans.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Essai sur l’histoire de la société civile&lt;/em&gt; (1767), il refuse l’idée d’un état de nature où l’homme aurait vécu seul : l’homme a toujours vécu en société, et il faut l’étudier tel qu’il est, par l’observation et l’histoire. Les sociétés passent de l’état sauvage à la barbarie, puis à la civilisation. Les institutions sont souvent « le résultat de l’action des hommes, mais non de leurs desseins » : personne ne les a voulues telles qu’elles sont. Cette idée inspirera, bien plus tard, Hayek.&lt;/p&gt; &lt;p&gt;Il s’inquiète des effets de la société commerciale. La division du travail rend l’économie efficace, mais elle enferme chaque homme dans une tâche étroite et l’abrutit. Quand chacun ne pense plus qu’à ses affaires, la vertu civique s’éteint et le despotisme menace. Marx le citera. On voit souvent en lui l’un des fondateurs de la sociologie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ferguson-mini.webp</t>
+        </is>
+      </c>
+      <c r="J109" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K109" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L109" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumières ; Républicanisme</t>
+        </is>
+      </c>
+      <c r="M109" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et historien écossais des Lumières, l’un des pères de la sociologie, inquiet des effets du commerce sur la vertu civique.</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P109"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P109"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="34" min="1" max="1"/>
@@ -7731,6 +7731,404 @@
         </is>
       </c>
       <c r="P109"/>
+    </row>
+    <row r="110" ht="130.5" customHeight="1" s="39">
+      <c r="A110" s="47">
+        <v>1651</v>
+      </c>
+      <c r="B110" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1715</t>
+        </is>
+      </c>
+      <c r="C110" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1651 – 1715</t>
+        </is>
+      </c>
+      <c r="D110" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FÉNELON</t>
+        </is>
+      </c>
+      <c r="E110" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/F%C3%A9nelon" title=" Wikipedia"&gt;FÉNELON&lt;/a&gt; de son nom complet François de Salignac de La Mothe-Fénelon, est un prêtre, théologien et écrivain français. Né en 1651 dans le Périgord, dans une famille noble, il dirige d’abord une maison pour les jeunes protestantes converties et publie un &lt;em&gt;Traité de l’éducation des filles&lt;/em&gt; (1687), qui défend leur instruction. En 1689, Louis XIV lui confie l’éducation de son petit-fils, le duc de Bourgogne, héritier du trône. Il devient archevêque de Cambrai en 1695.&lt;/p&gt; &lt;p&gt;Pour son élève, il écrit &lt;em&gt;Les Aventures de Télémaque&lt;/em&gt; (1699), qui racontent les voyages du fils d’Ulysse guidé par la sagesse. Sous ce récit se cache une critique de la monarchie absolue : le bon roi doit servir son peuple, fuir la guerre, le luxe et la flatterie. Le livre fait scandale et Fénelon tombe en disgrâce. Dans une lettre anonyme à Louis XIV, il avait déjà dénoncé les guerres et la misère du royaume. Le &lt;em&gt;Télémaque&lt;/em&gt; devient l’un des livres les plus lus du XVIIIe siècle.&lt;/p&gt; &lt;p&gt;Proche de la mystique Madame Guyon, il défend le « pur amour » : l’âme parfaite aime Dieu pour lui-même, sans souci de sa propre récompense, ni même de son salut. Bossuet l’accuse de quiétisme, une doctrine qui ferait de la vie spirituelle un abandon passif. Après une violente querelle, le pape condamne en 1699 son &lt;em&gt;Explication des maximes des saints&lt;/em&gt;, et Fénelon se soumet. Il meurt à Cambrai en 1715. Il est une figure du &lt;a href="https://fr.wikipedia.org/wiki/Mysticisme" title=" Wikipedia"&gt;mysticisme&lt;/a&gt; chrétien.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fenelon-mini.webp</t>
+        </is>
+      </c>
+      <c r="J110" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K110" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L110" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme ; Spiritualisme</t>
+        </is>
+      </c>
+      <c r="M110" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">archevêque de Cambrai, auteur des Aventures de Télémaque, défenseur du « pur amour » de Dieu contre Bossuet.</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" ht="130.5" customHeight="1" s="39">
+      <c r="A111" s="47">
+        <v>1627</v>
+      </c>
+      <c r="B111" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1704</t>
+        </is>
+      </c>
+      <c r="C111" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1627 – 1704</t>
+        </is>
+      </c>
+      <c r="D111" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jacques-Bénigne BOSSUET</t>
+        </is>
+      </c>
+      <c r="E111" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques-B%C3%A9nigne_Bossuet" title=" Wikipedia"&gt;Jacques-Bénigne BOSSUET&lt;/a&gt; est un évêque, prédicateur et écrivain français. Né à Dijon en 1627, dans une famille de magistrats, il étudie la théologie à Paris et devient chanoine à Metz, où il se fait connaître par ses sermons. À Paris, il prêche devant la cour et devient le plus grand orateur sacré de son temps. Ses &lt;em&gt;Oraisons funèbres&lt;/em&gt;, prononcées pour les grands personnages du royaume, sont des chefs-d’œuvre de la prose française. Évêque de Meaux en 1681, on le surnomme « l’Aigle de Meaux ». Il meurt à Paris en 1704.&lt;/p&gt; &lt;p&gt;De 1670 à 1681, il est le précepteur du Dauphin, le fils de Louis XIV, pour qui il écrit ses grands ouvrages. Dans le &lt;em&gt;Discours sur l’histoire universelle&lt;/em&gt; (1681), il montre que la Providence divine conduit l’histoire des empires, qui tous passent, vers le triomphe de l’Église. Dans la &lt;em&gt;Politique tirée des propres paroles de l’Écriture sainte&lt;/em&gt;, il fonde la monarchie absolue sur la Bible : le roi tient son pouvoir de Dieu et n’a de comptes à rendre qu’à lui. Mais un pouvoir absolu n’est pas arbitraire : le roi doit gouverner selon la justice et la raison.&lt;/p&gt; &lt;p&gt;Défenseur de l’unité de l’Église, il combat les protestants dans son &lt;em&gt;Histoire des variations des Églises protestantes&lt;/em&gt; (1688), et approuve la révocation de l’édit de Nantes. Il s’oppose aussi au quiétisme de Fénelon et à la critique biblique de Richard Simon. Nourri de saint Augustin, il s’inscrit dans l’&lt;a href="https://fr.wikipedia.org/wiki/Augustinisme" title=" Wikipedia"&gt;augustinisme&lt;/a&gt; du XVIIe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/bossuet-mini.webp</t>
+        </is>
+      </c>
+      <c r="J111" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K111" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="L111" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Augustinisme</t>
+        </is>
+      </c>
+      <c r="M111" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">évêque de Meaux, orateur sacré, théoricien de la monarchie de droit divin et de l’histoire guidée par la Providence.</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" ht="130.5" customHeight="1" s="39">
+      <c r="A112" s="47">
+        <v>1738</v>
+      </c>
+      <c r="B112" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1794</t>
+        </is>
+      </c>
+      <c r="C112" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1738 – 1794</t>
+        </is>
+      </c>
+      <c r="D112" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cesare BECCARIA</t>
+        </is>
+      </c>
+      <c r="E112" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cesare_Beccaria" title=" Wikipedia"&gt;Cesare BECCARIA&lt;/a&gt; est un juriste, philosophe et économiste italien. Né à Milan en 1738 dans une famille noble, il étudie le droit à Pavie. Il fréquente à Milan un groupe de jeunes réformateurs réunis autour des frères Verri, qui publient la revue &lt;em&gt;Le Café&lt;/em&gt; et diffusent les idées des philosophes français. Encouragé par eux, il publie anonymement en 1764, à 26 ans, un petit livre qui va changer l’histoire du droit pénal : &lt;em&gt;Des délits et des peines&lt;/em&gt;. Il enseigne ensuite l’économie politique à Milan et meurt dans sa ville en 1794.&lt;/p&gt; &lt;p&gt;Il y applique au droit pénal les principes des &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt;. Le but des lois doit être « le plus grand bonheur partagé par le plus grand nombre ». Les délits et les peines doivent être fixés par des lois claires, connues de tous, et non laissés à l’arbitraire des juges. La peine doit être proportionnée au délit et ne servir qu’à empêcher le coupable de nuire de nouveau et à dissuader les autres. Ce qui dissuade, ce n’est pas la cruauté du châtiment, mais la certitude d’être puni.&lt;/p&gt; &lt;p&gt;Il condamne la torture, qui punit avant le jugement et fait avouer l’innocent faible plutôt que le coupable robuste. Il réclame aussi l’abolition de la peine de mort, inutile et nuisible, car elle donne l’exemple de la cruauté. Traduit en français dès 1766 et salué par Voltaire, son livre inspire les réformes de nombreux souverains : le grand-duc de Toscane abolit la peine de mort en 1786. Il est le grand-père de l’écrivain Alessandro Manzoni.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/beccaria-mini.webp</t>
+        </is>
+      </c>
+      <c r="J112" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italienne</t>
+        </is>
+      </c>
+      <c r="K112" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L112" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumières ; Utilitarisme</t>
+        </is>
+      </c>
+      <c r="M112" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juriste et philosophe italien des Lumières, auteur de Des délits et des peines, contre la torture et la peine de mort.</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" ht="130.5" customHeight="1" s="39">
+      <c r="A113" s="47">
+        <v>1486</v>
+      </c>
+      <c r="B113" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1535</t>
+        </is>
+      </c>
+      <c r="C113" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1486 – 1535</t>
+        </is>
+      </c>
+      <c r="D113" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henri-Corneille AGRIPPA</t>
+        </is>
+      </c>
+      <c r="E113" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri-Corneille_Agrippa_de_Nettesheim" title=" Wikipedia"&gt;Henri-Corneille AGRIPPA&lt;/a&gt; de Nettesheim est un humaniste, médecin, juriste et occultiste allemand de la Renaissance. Né à Cologne en 1486, il mène une vie d’aventures à travers l’Europe : soldat de l’empereur Maximilien, professeur à Dole, où il commente un traité de kabbale et se fait accuser de judaïser, orateur de la ville de Metz, où il défend une femme accusée de sorcellerie, médecin de la reine mère de France à Lyon, puis historiographe de Marguerite d’Autriche aux Pays-Bas. Souvent pauvre et persécuté, il meurt à Grenoble en 1535.&lt;/p&gt; &lt;p&gt;Son œuvre la plus célèbre, &lt;em&gt;La Philosophie occulte&lt;/em&gt;, écrite dès 1510 et publiée en 1533, est une grande synthèse de la magie de la Renaissance. Le monde y est divisé en trois : le monde élémentaire, le monde céleste des astres et le monde intellectuel des anges et de Dieu. Tout est lié par des correspondances secrètes, et le mage, qui les connaît, peut faire descendre les forces supérieures. Agrippa y mêle l’&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9tisme" title=" Wikipedia"&gt;hermétisme&lt;/a&gt;, le néoplatonisme et la kabbale juive.&lt;/p&gt; &lt;p&gt;Mais dans &lt;em&gt;De l’incertitude et de la vanité des sciences&lt;/em&gt; (1530), il soutient au contraire que toutes les sciences humaines, y compris la magie, sont vaines et incertaines, et que seule la parole de Dieu est sûre. Dans un autre traité, il défend la supériorité du sexe féminin. Ce double visage, celui du mage et celui du sceptique, a beaucoup intrigué ses lecteurs. Sa réputation de magicien, entretenue par ses ennemis, a inspiré la légende de Faust et apparaît encore chez Rabelais, qui le caricature sous les traits de Her Trippa.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/agrippa-mini.webp</t>
+        </is>
+      </c>
+      <c r="J113" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allemande</t>
+        </is>
+      </c>
+      <c r="K113" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L113" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hermétisme ; Kabbale ; Scepticisme</t>
+        </is>
+      </c>
+      <c r="M113" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">humaniste, médecin et occultiste allemand de la Renaissance, auteur de La Philosophie occulte.</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P113"/>
+    </row>
+    <row r="114" ht="130.5" customHeight="1" s="39">
+      <c r="A114" s="47">
+        <v>1493</v>
+      </c>
+      <c r="B114" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1540</t>
+        </is>
+      </c>
+      <c r="C114" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1493 – 1540</t>
+        </is>
+      </c>
+      <c r="D114" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juan Luis VIVES</t>
+        </is>
+      </c>
+      <c r="E114" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Louis_Viv%C3%A8s" title=" Wikipedia"&gt;Juan Luis VIVES&lt;/a&gt; est un humaniste, philosophe et pédagogue espagnol. Né à Valence en 1493 dans une famille juive convertie au christianisme, il quitte jeune l’Espagne, où l’Inquisition persécutera durement sa famille : son père sera brûlé en 1524. Il étudie à Paris, puis s’installe à Bruges, qui restera sa ville. Ami d’Érasme et de Thomas More, il enseigne à Louvain puis à Oxford, et devient le précepteur de la princesse Marie Tudor. Il meurt à Bruges en 1540.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Éducation de la femme chrétienne&lt;/em&gt; (1523), il défend l’instruction des filles. Dans son traité &lt;em&gt;Du secours aux pauvres&lt;/em&gt; (1526), écrit pour la ville de Bruges, il propose pour la première fois une organisation publique de l’aide aux pauvres : recenser les indigents, donner du travail à ceux qui le peuvent, soigner les malades et instruire les enfants, plutôt que de laisser la charité au hasard des aumônes. Dans &lt;em&gt;Des disciplines&lt;/em&gt; (1531), il critique l’enseignement scolastique de son temps, fait de disputes stériles, et propose une réforme de toutes les sciences fondée sur l’observation et l’utilité.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;De l’âme et de la vie&lt;/em&gt; (1538), il ne cherche pas à savoir ce qu’est l’âme, mais comment elle agit : il étudie la mémoire, l’association des idées et les émotions. On l’a parfois appelé le « père de la psychologie moderne ». Pacifiste, il plaide pour la concorde entre les princes chrétiens. Il est une grande figure de l’&lt;a href="https://fr.wikipedia.org/wiki/Humanisme" title=" Wikipedia"&gt;humanisme&lt;/a&gt; de la Renaissance.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/vives-mini.webp</t>
+        </is>
+      </c>
+      <c r="J114" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espagnole</t>
+        </is>
+      </c>
+      <c r="K114" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethique ; politique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="L114" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanisme</t>
+        </is>
+      </c>
+      <c r="M114" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">humaniste espagnol, ami d’Érasme, pionnier de l’aide aux pauvres, de l’éducation des femmes et de la psychologie.</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P114"/>
+    </row>
+    <row r="115" ht="130.5" customHeight="1" s="39">
+      <c r="A115" s="47">
+        <v>1757</v>
+      </c>
+      <c r="B115" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1820</t>
+        </is>
+      </c>
+      <c r="C115" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1757 – 1820</t>
+        </is>
+      </c>
+      <c r="D115" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOLNEY</t>
+        </is>
+      </c>
+      <c r="E115" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Volney" title=" Wikipedia"&gt;VOLNEY&lt;/a&gt; de son vrai nom Constantin-François Chassebœuf, est un philosophe, historien et voyageur français. Né en 1757 dans l’Anjou, il étudie la médecine et l’histoire à Paris, où il fréquente le salon de Madame Helvétius et les derniers philosophes des Lumières. De 1783 à 1785, il voyage en Égypte et en Syrie, et en tire un récit précis, le &lt;em&gt;Voyage en Syrie et en Égypte&lt;/em&gt; (1787), qui servira à Bonaparte lors de son expédition. Député en 1789, emprisonné sous la Terreur, il devient sénateur sous l’Empire et pair de France sous la Restauration. Il meurt à Paris en 1820.&lt;/p&gt; &lt;p&gt;Son livre le plus célèbre, &lt;em&gt;Les Ruines, ou méditation sur les révolutions des empires&lt;/em&gt; (1791), commence par une rêverie devant les ruines de Palmyre. Pourquoi les empires tombent-ils ? Non par la volonté des dieux, mais par l’ignorance, l’égoïsme et le despotisme des hommes. Un génie lui montre ensuite une assemblée de tous les peuples de la terre, dont les prêtres se disputent la vérité : chaque religion prétend être la seule vraie, et toutes sont nées de l’imagination humaine. La paix viendra quand les hommes suivront la seule loi naturelle, que la raison découvre.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Loi naturelle&lt;/em&gt; (1793), un catéchisme pour les citoyens, il fonde la morale sur la conservation de soi et l’intérêt bien compris. Proche des Idéologues, il s’intéresse aussi aux langues et propose un alphabet universel. Il prolonge l’esprit critique des &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/volney-mini.webp</t>
+        </is>
+      </c>
+      <c r="J115" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K115" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L115" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumières ; Déisme</t>
+        </is>
+      </c>
+      <c r="M115" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe et voyageur français, auteur des Ruines, méditation sur la chute des empires et la diversité des religions.</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P115"/>
+    </row>
+    <row r="116" ht="130.5" customHeight="1" s="39">
+      <c r="A116" s="47">
+        <v>1709</v>
+      </c>
+      <c r="B116" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1785</t>
+        </is>
+      </c>
+      <c r="C116" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1709 – 1785</t>
+        </is>
+      </c>
+      <c r="D116" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabriel Bonnot de MABLY</t>
+        </is>
+      </c>
+      <c r="E116" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gabriel_Bonnot_de_Mably" title=" Wikipedia"&gt;Gabriel Bonnot de MABLY&lt;/a&gt; est un philosophe, historien et penseur politique français. Né à Grenoble en 1709, frère aîné de Condillac, il entre au séminaire et reçoit le titre d’abbé, mais ne devient jamais prêtre. Il travaille plusieurs années comme conseiller du cardinal de Tencin, alors ministre, et publie un ouvrage sur le droit public de l’Europe. Il quitte ensuite la politique pour se consacrer à l’écriture, vivant modestement à Paris. Il meurt en 1785.&lt;/p&gt; &lt;p&gt;Admirateur de Sparte et de la République romaine, il pense que la politique doit former des citoyens vertueux, dévoués au bien commun, et non seulement enrichir les États. Dans ses &lt;em&gt;Doutes proposés aux philosophes économistes&lt;/em&gt; (1768), il critique les physiocrates, qui font de la propriété et du commerce les fondements de l’ordre social. Pour lui, la propriété privée est la source de l’avarice, de l’ambition et de l’inégalité. Dans &lt;em&gt;De la législation&lt;/em&gt; (1776), il rêve d’une communauté des biens, tout en la jugeant impossible à rétablir : il faut au moins limiter les richesses par les lois.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Des droits et des devoirs du citoyen&lt;/em&gt;, écrit en 1758 et publié en 1789, il appelle à la réunion des États généraux et à une « révolution ménagée » qui limiterait le pouvoir du roi. Consulté par les Polonais et les Américains sur leurs constitutions, il a influencé les révolutionnaires, jusqu’à Babeuf. Il est une figure du &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9publicanisme" title=" Wikipedia"&gt;républicanisme&lt;/a&gt; des Lumières.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mably-mini.webp</t>
+        </is>
+      </c>
+      <c r="J116" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Française</t>
+        </is>
+      </c>
+      <c r="K116" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; ethique</t>
+        </is>
+      </c>
+      <c r="L116" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Républicanisme ; Utopisme</t>
+        </is>
+      </c>
+      <c r="M116" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe politique français, frère de Condillac, critique de l’inégalité et penseur de la vertu républicaine.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P116"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-renaissance-lumieres.xlsx
+++ b/data/frise-philosophes-renaissance-lumieres.xlsx
@@ -6624,6 +6624,21 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marie_de_Gournay"  title=" Wikipedia"&gt;Marie de GOURNAY&lt;/a&gt; (1565-1645) est une femme de lettres et philosophe française. Autodidacte, elle apprit seule le latin et découvrit adolescente les &lt;em&gt;Essais&lt;/em&gt; de Montaigne, qui la bouleversèrent. Elle rencontra l'auteur en 1588 et devint sa « fille d'alliance », une amitié intellectuelle profonde.&lt;/p&gt; &lt;p&gt;Après la mort de Montaigne, sa veuve lui confia le manuscrit annoté des &lt;em&gt;Essais&lt;/em&gt;. Marie de Gournay consacra une grande partie de sa vie à en préparer les éditions, dont celle de 1595, qui a fait autorité pendant des siècles. Elle vécut de sa plume, chose très rare pour une femme de son époque, et fréquenta les milieux savants de Paris, où elle fut souvent moquée pour son indépendance.&lt;/p&gt; &lt;p&gt;Marie de Gournay s'intéressa aussi à la langue française, qu'elle défendit contre les réformes de Malherbe qui voulaient l'appauvrir selon elle, et publia un recueil de ses œuvres sous le titre &lt;em&gt;L'Ombre de la demoiselle de Gournay&lt;/em&gt; (1626), puis &lt;em&gt;Les Advis ou les Présens&lt;/em&gt; (1634). Elle y traite de l'éducation des princes, de la poésie, de la calomnie et de la condition des femmes savantes, qu'on ridiculisait pour mieux les écarter.&lt;/p&gt; &lt;p&gt;Elle est surtout connue pour deux textes pionniers : &lt;em&gt;Égalité des hommes et des femmes&lt;/em&gt; (1622) et &lt;em&gt;Grief des dames&lt;/em&gt; (1626). Elle y soutient que la différence entre hommes et femmes ne tient pas à la nature mais à l'éducation, et que « l'animal humain n'est ni homme ni femme » par l'âme. Elle s'appuie sur la Bible, les Pères de l'Église et les philosophes antiques pour montrer que rien ne justifie l'exclusion des femmes du savoir. Elle est considérée comme l'une des premières penseuses de l'égalité des sexes.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">273i07B4uyA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Marie de Gournay - Féministe et alchimiste" par Le microsophe</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mariedegournay-mini.webp</t>
+        </is>
+      </c>
       <c r="J90" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Française</t>
@@ -6677,6 +6692,21 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Élisabeth_de_Bohême_(1618-1680)"  title=" Wikipedia"&gt;ÉLISABETH de Bohême&lt;/a&gt; (1618-1680), princesse palatine, était la fille de Frédéric V, l'éphémère « roi d'hiver » de Bohême, chassé de son trône au début de la guerre de Trente Ans. Elle grandit en exil aux Pays-Bas, où elle reçut une éducation très poussée en langues, mathématiques et philosophie.&lt;/p&gt; &lt;p&gt;Elle est célèbre pour sa correspondance avec René Descartes, commencée en 1643. Dès sa première lettre, elle lui pose une question redoutable : si l'âme est une substance pensante, sans étendue, comment peut-elle mettre en mouvement le corps, qui est une chose étendue ? Descartes eut beaucoup de mal à lui répondre, et cette objection reste au cœur de ce que l'on appelle aujourd'hui le problème de l'esprit et du corps.&lt;/p&gt; &lt;p&gt;La correspondance entre Élisabeth et Descartes, qui dura jusqu'à la mort du philosophe en 1650, compte une soixantaine de lettres. On y voit la princesse contester, avec politesse mais fermeté, plusieurs points de la doctrine cartésienne, et proposer ses propres solutions, par exemple sur la manière dont l'âme peut être affectée par la maladie du corps. Descartes lui-même reconnaissait qu'elle était la personne qui comprenait le mieux sa philosophie.&lt;/p&gt; &lt;p&gt;Leurs échanges portèrent aussi sur les passions, la vertu, le bonheur et la politique : c'est pour elle que Descartes écrivit son &lt;em&gt;Traité des passions de l'âme&lt;/em&gt;, et il lui dédia ses &lt;em&gt;Principes de la philosophie&lt;/em&gt;. Élisabeth y défend une morale attentive aux réalités de la vie et du corps. Elle devint ensuite abbesse de l'abbaye protestante de Herford, en Allemagne, où elle accueillit des penseurs persécutés. Elle est aujourd'hui reconnue comme une philosophe à part entière, et non plus seulement comme une correspondante de Descartes.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tA5P6PytyW0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Élisabeth de Bohême : la princesse philosophe !" par Kant à moi</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/elisabethdeboheme-mini.webp</t>
+        </is>
+      </c>
       <c r="J91" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Allemande</t>
@@ -6733,6 +6763,21 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Margaret_Cavendish"  title=" Wikipedia"&gt;Margaret CAVENDISH&lt;/a&gt; (1623-1673), duchesse de Newcastle, est une philosophe, poétesse et romancière anglaise. Pendant la guerre civile anglaise, elle suivit la reine en exil à Paris, où elle épousa William Cavendish et fréquenta, grâce à lui, des penseurs comme Hobbes, Descartes et Gassendi.&lt;/p&gt; &lt;p&gt;Elle publia sous son propre nom une douzaine d'ouvrages de philosophie naturelle, ce qui était presque impensable pour une femme de son temps. Elle y développe une philosophie matérialiste et vitaliste : la nature entière est faite d'une seule matière, mais cette matière est douée de mouvement, de perception et même de raison. Elle critique à la fois le mécanisme de Descartes et de Hobbes, et la science expérimentale de la Royal Society, qui prétendait connaître la nature grâce aux microscopes.&lt;/p&gt; &lt;p&gt;Cavendish réfléchit aussi à la condition des femmes, qu'elle juge tenues à l'écart du savoir et du pouvoir par la coutume plutôt que par la nature. Dans ses préfaces, elle revendique ouvertement le désir de gloire et de reconnaissance, ce qui choquait ses contemporains. Ses &lt;em&gt;Observations sur la philosophie expérimentale&lt;/em&gt; (1666) contiennent l'une des premières critiques philosophiques de la confiance aveugle dans les instruments scientifiques.&lt;/p&gt; &lt;p&gt;En 1667, elle fut la première femme invitée à assister à une séance de la Royal Society de Londres. Son récit &lt;em&gt;Le Monde glorieux&lt;/em&gt; (&lt;em&gt;The Blazing World&lt;/em&gt;, 1666), où une femme devient impératrice d'un monde imaginaire peuplé de savants animaux, est souvent considéré comme l'un des premiers romans de science-fiction. Surnommée « Mad Madge » par ses contemporains, elle est aujourd'hui redécouverte comme une philosophe originale et audacieuse.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IBUMSr2zWMY</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La duchesse des sciences – Margaret Cavendish – #Mini-bio 43" par Sur les épaules de géantes</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/margaretcavendish-mini.webp</t>
+        </is>
+      </c>
       <c r="J92" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Britannique</t>
@@ -6786,6 +6831,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anne_Conway"  title=" Wikipedia"&gt;Anne CONWAY&lt;/a&gt; (1631-1679) est une philosophe anglaise, proche du groupe des platoniciens de Cambridge. Souffrant toute sa vie de violentes migraines, elle reçut une éducation principalement par correspondance, notamment avec le philosophe Henry More, qui devint son ami et son maître.&lt;/p&gt; &lt;p&gt;Son unique ouvrage, les &lt;em&gt;Principes de la plus ancienne et de la plus moderne philosophie&lt;/em&gt;, fut publié après sa mort, en latin en 1690, puis en anglais. Elle y rejette le dualisme de Descartes, qui sépare l'esprit et la matière, et le matérialisme de Hobbes et de Spinoza. Pour elle, tout ce qui existe est à la fois esprit et corps à des degrés divers : la matière n'est qu'un esprit « épaissi », et toutes les créatures, même les pierres, sont vivantes et capables de se perfectionner.&lt;/p&gt; &lt;p&gt;Sa philosophie répond aussi à une question personnelle : comment donner un sens à la douleur ? Pour Anne Conway, la souffrance n'est pas un châtiment arbitraire mais un moyen de purification, qui permet à chaque créature de se rapprocher de Dieu. Aucune créature n'est condamnée pour toujours : toutes sont appelées à progresser vers le bien, ce qui fait de sa pensée l'une des plus optimistes de son temps.&lt;/p&gt; &lt;p&gt;Anne Conway propose une vision d'un monde en constante évolution vers le bien, où la souffrance a un sens puisqu'elle aide les êtres à progresser. Influencée par la kabbale et par les quakers, qu'elle rejoignit à la fin de sa vie, elle eut une influence directe sur Leibniz, qui la cite et lui emprunta sans doute l'idée de « monade ». Longtemps oubliée, elle est aujourd'hui considérée comme l'une des philosophes les plus originales du XVIIe siècle.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L5JelC471Ec</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Laurence Vanin évoque Anne Finch Conway, philosophe et métaphysicienne !" par Laurence Vanin</t>
+        </is>
+      </c>
       <c r="J93" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Britannique</t>
@@ -6839,6 +6894,21 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mary_Astell"  title=" Wikipedia"&gt;Mary ASTELL&lt;/a&gt; (1666-1731) est une philosophe et écrivaine anglaise, souvent présentée comme la première féministe anglaise. Fille d'un marchand de charbon de Newcastle, elle fut instruite par son oncle, puis s'installa seule à Londres, où elle vécut de sa plume grâce au soutien de protectrices aristocratiques.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Une proposition sérieuse aux dames&lt;/em&gt; (1694), elle propose de créer une sorte d'institution où les femmes pourraient se consacrer à l'étude et à la réflexion, loin des futilités auxquelles la société les condamne. Disciple de Descartes et du philosophe Malebranche, elle affirme que les femmes ont la même raison que les hommes et que leur prétendue infériorité vient uniquement de leur manque d'éducation.&lt;/p&gt; &lt;p&gt;Mary Astell fut aussi une polémiste redoutée, qui débattit avec les penseurs les plus en vue de son temps, dont John Locke et le philosophe John Norris, avec qui elle échangea des lettres sur l'amour de Dieu. Elle fonda à Chelsea une école de charité pour les filles pauvres, qu'elle soutint jusqu'à sa mort. Son idée d'une communauté de femmes consacrée à l'étude, jugée trop proche des couvents catholiques, ne vit jamais le jour, mais elle inspira de nombreuses féministes après elle.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Réflexions sur le mariage&lt;/em&gt; (1700), elle critique avec ironie la condition des épouses, soumises à un pouvoir absolu de leur mari. Elle retourne contre ses adversaires les idées de John Locke : « si tous les hommes naissent libres, comment se fait-il que toutes les femmes naissent esclaves ? ». Anglicane conservatrice en politique, elle n'en fut pas moins l'une des premières à penser la domination des femmes comme une question philosophique et politique.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-QG7IhPOQ</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Mary Astell, une pionnière du féminisme dans l'Angleterre" par Fief89520</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/maryastell-mini.webp</t>
+        </is>
+      </c>
       <c r="J94" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Britannique</t>
@@ -6892,6 +6962,21 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Émilie_du_Châtelet"  title=" Wikipedia"&gt;Émilie du CHÂTELET&lt;/a&gt; (1706-1749) est une mathématicienne, physicienne et philosophe française des Lumières. Issue de l'aristocratie, elle reçut une éducation rare pour une fille, en latin, en mathématiques et en sciences. Compagne de Voltaire pendant quinze ans, elle fit de leur château de Cirey un véritable centre d'étude, où ils travaillaient côte à côte.&lt;/p&gt; &lt;p&gt;Ses &lt;em&gt;Institutions de physique&lt;/em&gt; (1740) tentent de concilier la physique de Newton et la métaphysique de Leibniz, en particulier le principe de raison suffisante. Elle participa à la grande controverse sur la notion de « force vive », en montrant que l'énergie d'un corps en mouvement dépend du carré de sa vitesse, une idée essentielle pour la physique moderne.&lt;/p&gt; &lt;p&gt;Elle entretint une correspondance avec les plus grands savants de son temps, comme les mathématiciens Maupertuis et Clairaut, et fut la première femme dont un mémoire scientifique, sur la nature du feu, fut publié par l'Académie des sciences de Paris en 1738. Elle ne pouvait pourtant pas en être membre, et il lui arriva de se déguiser en homme pour entrer dans les cafés où se retrouvaient les savants.&lt;/p&gt; &lt;p&gt;Son œuvre majeure est la traduction commentée en français des &lt;em&gt;Principes mathématiques de la philosophie naturelle&lt;/em&gt; de Newton, achevée juste avant sa mort en couches, à 42 ans. Elle reste aujourd'hui la seule traduction française complète de ce texte fondateur. Dans son &lt;em&gt;Discours sur le bonheur&lt;/em&gt;, elle fait de l'étude et de la passion du savoir une source de bonheur indépendante des autres, notamment pour les femmes, exclues de tant d'autres chemins de la gloire.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZqxS-muFxvE</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La passionnée – Emilie du Châtelet  – Sur les épaules de géantes #7" par Sur les épaules de géantes</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/emilieduchatelet-mini.webp</t>
+        </is>
+      </c>
       <c r="J95" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Française</t>
@@ -6948,6 +7033,21 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Olympe_de_Gouges"  title=" Wikipedia"&gt;Olympe de GOUGES&lt;/a&gt; (1748-1793), de son vrai nom Marie Gouze, est une femme de lettres et une femme politique française. Née à Montauban dans un milieu modeste, veuve très jeune, elle s'installa à Paris où elle écrivit des pièces de théâtre, dont une dénonçant l'esclavage des Noirs, qui fit scandale.&lt;/p&gt; &lt;p&gt;Pendant la Révolution française, elle publia de nombreuses brochures sur les questions sociales et politiques : aide aux pauvres, divorce, protection des enfants nés hors mariage. En 1791, elle rédigea la &lt;em&gt;Déclaration des droits de la femme et de la citoyenne&lt;/em&gt;, qui reprend article par article la Déclaration de 1789 pour montrer qu'elle exclut la moitié de l'humanité. Elle y écrit : « La femme a le droit de monter sur l'échafaud ; elle doit avoir également celui de monter à la tribune ».&lt;/p&gt; &lt;p&gt;Olympe de Gouges réclamait aussi l'accès des femmes à toutes les fonctions publiques, le droit de vote, le partage des biens entre époux et le droit de rechercher la paternité. Dans le postambule de sa Déclaration, elle appelle les femmes à se réveiller et à reconnaître leurs droits. Sa pensée associe l'égalité des sexes, l'abolition de l'esclavage et la justice sociale, bien avant que ces combats soient reconnus.&lt;/p&gt; &lt;p&gt;Proche des Girondins, elle critiqua ouvertement Robespierre et la Terreur. Arrêtée pour ses écrits, elle fut condamnée à mort et guillotinée le 3 novembre 1793. Longtemps caricaturée, elle est aujourd'hui considérée comme une pionnière du féminisme et de la défense des droits humains.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3EnaQCmZqxc</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Olympe De Gouges, pionnière des collages féministes" par France Culture</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/olympedegouges-mini.webp</t>
+        </is>
+      </c>
       <c r="J96" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Française</t>
@@ -7006,6 +7106,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fran%C3%A7ois_Sanchez" title=" Wikipedia"&gt;Francisco SANCHES&lt;/a&gt; est un médecin et philosophe d’origine portugaise, l’un des grands sceptiques de la Renaissance. Né vers 1550, à Braga ou à Tui, dans une famille de juifs convertis, que la menace de l’Inquisition pousse à quitter la péninsule Ibérique, il grandit à Bordeaux. Il étudie la médecine à Montpellier, séjourne en Italie, puis s’installe à Toulouse, où il exerce la médecine à l’hôpital et enseigne la philosophie et la médecine à l’université jusqu’à sa mort en 1623. Il serait un parent de &lt;a href="https://fr.wikipedia.org/wiki/Michel_de_Montaigne" title=" Wikipedia"&gt;Montaigne&lt;/a&gt;, par la mère de celui-ci.&lt;/p&gt; &lt;p&gt;Son livre &lt;em&gt;Que rien ne se sait&lt;/em&gt; (&lt;em&gt;Quod nihil scitur&lt;/em&gt;), publié à Lyon en 1581, attaque la science des écoles, fondée sur Aristote : ses définitions ne sont que des mots, ses syllogismes ne font que répéter ce qu’on savait déjà, et l’on croit savoir quand on ne fait que nommer. La connaissance parfaite d’une chose supposerait de la connaître dans toutes ses causes et ses relations avec tout le reste, ce qui est impossible à un esprit fini. Il commence chaque argument par une question et termine son livre par un « Quoi ? » ironique.&lt;/p&gt; &lt;p&gt;Mais son &lt;a href="https://fr.wikipedia.org/wiki/Scepticisme_%28philosophie%29" title=" Wikipedia"&gt;scepticisme&lt;/a&gt; n’est pas un renoncement. Faute de savoir parfait, il faut s’en remettre à l’observation attentive et à l’expérience, comme le fait le médecin au chevet des malades, et avancer prudemment de jugement en jugement. Il annonce ainsi, avant Bacon et Descartes, l’esprit de la méthode expérimentale. Son œuvre, contemporaine des &lt;em&gt;Essais&lt;/em&gt; de Montaigne, a été redécouverte au XXe siècle comme un moment important du doute moderne.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ah6TmUR8pNk</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Francisco Sanches: Renaissance Innovator｜Philosopher Biography" par VIS PHILO.</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/sanches-mini.webp</t>
@@ -7127,6 +7237,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Antoine_de_Montchrestien" title=" Wikipedia"&gt;Antoine de MONTCHRESTIEN&lt;/a&gt; est un dramaturge et économiste français, l’inventeur de l’expression « &lt;a href="https://fr.wikipedia.org/wiki/%C3%89conomie_politique" title=" Wikipedia"&gt;économie politique&lt;/a&gt; ». Né à Falaise, en Normandie, vers 1575, fils d’un apothicaire, il se fait d’abord connaître comme poète tragique : sa tragédie &lt;em&gt;L’Écossaise&lt;/em&gt;, sur la mort de Marie Stuart, est l’une des premières pièces françaises consacrées à l’histoire récente. Après avoir tué un adversaire en duel, il s’exile en Angleterre et aux Pays-Bas, où il observe l’essor du commerce et des manufactures.&lt;/p&gt; &lt;p&gt;Revenu en France, il fonde une fabrique de couteaux et d’outils, et publie en 1615 son &lt;em&gt;Traité de l’économie politique&lt;/em&gt;, dédié au jeune Louis XIII et à sa mère Marie de Médicis. Le titre est nouveau : l’« économie », qui désignait chez Aristote la gestion de la maison, devient la science de la richesse de tout le royaume. Pour Montchrestien, la vraie richesse n’est pas seulement l’or, mais le travail des hommes et l’abondance des choses nécessaires. Le roi doit développer les manufactures, mettre les oisifs au travail, réserver le marché national aux produits français, protéger la marine et fonder des colonies. Il dénonce les marchands étrangers qui s’enrichissent aux dépens de la France.&lt;/p&gt; &lt;p&gt;Ces idées font de lui l’un des grands auteurs du &lt;a href="https://fr.wikipedia.org/wiki/Mercantilisme" title=" Wikipedia"&gt;mercantilisme&lt;/a&gt; français, que la politique de Colbert mettra en œuvre un demi-siècle plus tard. Protestant, Montchrestien prend part au soulèvement huguenot de 1621 ; il est tué dans une embuscade près de Domfront, et son corps est jugé, puis brûlé. Son traité, longtemps oublié, a été redécouvert au XIXe siècle.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zAEAUCXqnuU</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L'économie politique selon Antoine de Montchrestien" par Rotin Rotin </t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/montchrestien-mini.webp</t>
@@ -7183,6 +7303,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Arthur_Collier" title=" Wikipedia (en)"&gt;Arthur COLLIER&lt;/a&gt; est un pasteur et philosophe anglais. Né en 1680 à Steeple Langford, dans le Wiltshire, dans une famille de pasteurs, il étudie à Oxford et succède à son père comme recteur de la paroisse de Langford Magna, où il passe toute sa vie. Lecteur de Descartes et surtout de Malebranche, il réfléchit dès 1703 à la question de l’existence du monde extérieur.&lt;/p&gt; &lt;p&gt;En 1713, il publie la &lt;em&gt;Clavis Universalis&lt;/em&gt;, « la clé universelle », sous-titrée « nouvelle recherche de la vérité, démonstration de la non-existence ou de l’impossibilité d’un monde extérieur ». Il y soutient, comme &lt;a href="https://fr.wikipedia.org/wiki/George_Berkeley" title=" Wikipedia"&gt;Berkeley&lt;/a&gt; dans ses &lt;em&gt;Principes&lt;/em&gt; de 1710, l’&lt;a href="https://fr.wikipedia.org/wiki/Immat%C3%A9rialisme" title=" Wikipedia"&gt;immatérialisme&lt;/a&gt; : le monde visible n’existe que dans l’esprit qui le perçoit, et une matière extérieure, indépendante de toute perception, est une idée contradictoire. Il en donne plusieurs preuves : l’idée d’un monde extérieur conduit à dire qu’il est à la fois fini et infini, divisible à l’infini et pourtant composé de parties.&lt;/p&gt; &lt;p&gt;Collier affirme être arrivé à ces conclusions seul, sans avoir lu Berkeley, et les historiens le croient généralement : les deux auteurs partent de Malebranche, mais avec des arguments différents. Son livre passe presque inaperçu de son vivant. Il publie encore deux essais de théologie, &lt;em&gt;A Specimen of True Philosophy&lt;/em&gt; (1730) et &lt;em&gt;Logology&lt;/em&gt; (1732), consacré au Verbe divin. Il meurt en 1732. Redécouvert au XVIIIe siècle par Thomas Reid, puis réédité au XIXe siècle, il est aujourd’hui considéré comme le second fondateur de l’immatérialisme.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9Bnxl5nEuxA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Arthur Collier: The Philosophical Priest｜Philosopher Biography" par VIS PHILO.</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/collier-mini.webp</t>
@@ -7239,6 +7369,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89tienne_Bonnot_de_Condillac" title=" Wikipedia"&gt;Étienne Bonnot de CONDILLAC&lt;/a&gt; est un philosophe français. Né à Grenoble en 1714, frère cadet de l’abbé de Mably, il devient prêtre mais ne dit sa messe qu’une seule fois et se consacre entièrement à la philosophie. À Paris, il se lie avec Rousseau et Diderot. De 1758 à 1767, il est le précepteur du jeune prince de Parme, pour qui il rédige un vaste &lt;em&gt;Cours d’études&lt;/em&gt;. Élu à l’Académie française en 1768, il se retire ensuite dans son domaine de Flux, près de Beaugency, où il meurt en 1780.&lt;/p&gt; &lt;p&gt;Disciple de Locke, il veut aller plus loin que lui. Dans l’&lt;em&gt;Essai sur l’origine des connaissances humaines&lt;/em&gt; (1746), il montre le rôle décisif du langage : sans les signes, nous ne pourrions ni retenir ni combiner nos idées. Dans le &lt;em&gt;Traité des sensations&lt;/em&gt; (1754), il imagine une statue de marbre à laquelle on donnerait les sens un à un, en commençant par l’odorat : sentant une rose, elle « est » odeur de rose. Il montre ainsi que l’attention, la mémoire, le jugement et le désir ne sont que des « sensations transformées ». C’est le sensualisme, forme radicale de l’&lt;a href="https://fr.wikipedia.org/wiki/Empirisme" title=" Wikipedia"&gt;empirisme&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Dans le &lt;em&gt;Traité des systèmes&lt;/em&gt; (1749), il critique les grands systèmes de Descartes, Spinoza et Leibniz, bâtis sur des principes abstraits. Pour lui, une science n’est qu’« une langue bien faite » : penser juste, c’est analyser, c’est-à-dire décomposer et recomposer ses idées, comme en algèbre. Il est aussi l’un des premiers à fonder la valeur économique sur l’utilité. Ses idées inspirent les « Idéologues » de la Révolution et la réforme de l’enseignement.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">k9BHRgJmRcM</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"As-tu déjà tenté l'expérience... de la statue de Condillac?" par PhiloCité ASBL</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/condillac-mini.webp</t>
@@ -7353,6 +7493,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Samuel_von_Pufendorf" title=" Wikipedia"&gt;Samuel von PUFENDORF&lt;/a&gt; est un juriste, philosophe et historien allemand. Né en 1632 en Saxe, fils d’un pasteur luthérien, il étudie à Leipzig et à Iéna. Précepteur dans la famille de l’ambassadeur de Suède à Copenhague, il est emprisonné pendant la guerre entre la Suède et le Danemark, et rédige en captivité ses premiers &lt;em&gt;Éléments de jurisprudence universelle&lt;/em&gt; (1660). En 1661, l’électeur palatin crée pour lui à Heidelberg la première chaire de droit naturel et de droit des gens. Il enseigne ensuite à Lund, en Suède, puis devient historiographe des rois de Suède et de l’électeur de Brandebourg. Il meurt à Berlin en 1694.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Du droit de la nature et des gens&lt;/em&gt; (1672) et son abrégé, &lt;em&gt;Les Devoirs de l’homme et du citoyen&lt;/em&gt; (1673), il fonde le droit naturel sur la sociabilité. L’homme, faible et incapable de survivre seul, a besoin des autres : la loi fondamentale de la nature lui commande donc de vivre en société et de la préserver. Les règles morales ne sont pas inscrites dans les choses, mais imposées par la volonté de Dieu, qui leur donne leur force obligatoire. L’État naît d’un double contrat, par lequel les hommes s’unissent puis se soumettent à un souverain.&lt;/p&gt; &lt;p&gt;Sous un pseudonyme, il décrit le Saint-Empire comme un « corps irrégulier, semblable à un monstre ». Traduit en français par Jean Barbeyrac, il est lu dans toute l’Europe, de Locke à Rousseau, et influence le &lt;a href="https://fr.wikipedia.org/wiki/Contractualisme" title=" Wikipedia"&gt;contractualisme&lt;/a&gt; et la pensée des droits de l’homme.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">l_DNf2jqfVU</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Pufendorf's Place in the History of Philosophy" par Gavin Victor</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/pufendorf-mini.webp</t>
@@ -7411,6 +7561,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Johann_Georg_Hamann" title=" Wikipedia"&gt;Johann Georg HAMANN&lt;/a&gt; est un philosophe et écrivain allemand. Né à Königsberg en 1730, fils d’un chirurgien-barbier, il étudie sans terminer ses études et devient précepteur. En 1757, envoyé à Londres pour une mission commerciale, il échoue, s’endette et traverse une grave crise. La lecture de la Bible le bouleverse et le convertit à un christianisme fervent. De retour à Königsberg, il refuse de revenir aux idées des Lumières que lui proposent ses amis, dont Kant. Il vit modestement comme employé des douanes et meurt à Münster en 1788. Ses contemporains l’appellent le « Mage du Nord ».&lt;/p&gt; &lt;p&gt;Dans les &lt;em&gt;Mémorables socratiques&lt;/em&gt; (1759), il fait de l’ignorance de Socrate le modèle de la foi : comme le montre Hume, nous ne pouvons rien prouver de l’existence des choses, nous ne pouvons que la croire. La raison n’est pas une faculté souveraine, détachée de la vie : elle est liée à la sensibilité, à l’histoire, à la tradition, et d’abord au langage. Dans &lt;em&gt;Aesthetica in nuce&lt;/em&gt; (1762), il proclame : « La poésie est la langue maternelle du genre humain. »&lt;/p&gt; &lt;p&gt;Dans sa &lt;em&gt;Métacritique du purisme de la raison&lt;/em&gt; (1784), il reproche à Kant d’avoir voulu purifier la raison de la tradition, de l’expérience et du langage : or le langage est « le premier et le dernier organe de la raison ». Son style obscur, fait d’allusions et de citations, a fasciné Herder, Goethe et le mouvement du Sturm und Drang, puis Kierkegaard. Il est l’un des grands critiques des Lumières et un précurseur du &lt;a href="https://fr.wikipedia.org/wiki/Romantisme" title=" Wikipedia"&gt;romantisme&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PnwN7VZylMc</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The Philosophy of Johann Hamann: Poetry and the Soul" par Paul Joseph Krause</t>
+        </is>
+      </c>
       <c r="H104" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/hamann-mini.webp</t>
@@ -7467,6 +7627,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Anthony_Ashley-Cooper_%283e_comte_de_Shaftesbury%29" title=" Wikipedia"&gt;SHAFTESBURY&lt;/a&gt; est le nom sous lequel on connaît Anthony Ashley Cooper, troisième comte de Shaftesbury, philosophe et homme politique anglais. Né à Londres en 1671, petit-fils d’un grand homme d’État, il reçoit une éducation dirigée par John Locke, médecin et ami de la famille. Il siège au Parlement, puis à la Chambre des lords, mais une santé fragile l’éloigne de la politique. Il réunit ses essais dans les &lt;em&gt;Caractéristiques des hommes, des mœurs, des opinions et des temps&lt;/em&gt; (1711). Il part se soigner en Italie et meurt à Naples en 1713.&lt;/p&gt; &lt;p&gt;Contre Hobbes, pour qui l’homme n’agit que par intérêt, il soutient que nous avons des affections naturelles pour autrui et pour le bien commun. Nous possédons un « sens moral », une capacité spontanée de sentir ce qui est bon ou mauvais, comme nous sentons ce qui est beau ou laid. La vertu consiste à harmoniser nos affections entre elles et avec l’ordre de l’univers. Le beau, le bien et le vrai ne font qu’un. Il s’inspire des stoïciens et des platoniciens de Cambridge, et défend un &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9isme" title=" Wikipedia"&gt;déisme&lt;/a&gt; tolérant, où la morale n’a pas besoin des récompenses et des châtiments divins.&lt;/p&gt; &lt;p&gt;Il fait de l’humour et du ridicule une épreuve de la vérité : seules les idées fausses craignent la raillerie. Il influence Hutcheson et Hume, puis Diderot, qui traduit son &lt;em&gt;Essai sur le mérite et la vertu&lt;/em&gt; en 1745, et l’esthétique allemande. Son idée d’un plaisir désintéressé, pris au beau sans désir de le posséder, sera reprise par Kant.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0wq6tJGUQr8</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Shaftesbury - La politesse, condition de toute culture et chemin vers la moralité ? Michel  Malherbe" par Editions M-Editer</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/shaftesbury-mini.webp</t>
@@ -7523,6 +7693,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bartolom%C3%A9_de_las_Casas" title=" Wikipedia"&gt;Bartolomé de LAS CASAS&lt;/a&gt; est un prêtre, historien et théologien espagnol. Né à Séville en 1484, il part en 1502 pour l’île d’Hispaniola, où il devient colon et reçoit des Indiens à son service. Ordonné prêtre, il participe encore à la conquête de Cuba. En 1514, en méditant un passage de la Bible, il prend conscience de l’injustice faite aux Indiens, renonce à ses biens et consacre le reste de sa longue vie à leur défense. Il entre dans l’ordre des Dominicains en 1522 et devient évêque du Chiapas, au Mexique, en 1544. Il meurt à Madrid en 1566.&lt;/p&gt; &lt;p&gt;Dans sa &lt;em&gt;Très brève relation de la destruction des Indes&lt;/em&gt; (1552), il décrit les massacres, l’esclavage et les mauvais traitements infligés par les conquérants. Ses démarches auprès de Charles Quint contribuent aux « Lois nouvelles » de 1542, qui interdisent de réduire les Indiens en esclavage. En 1550-1551, lors de la controverse de Valladolid, il s’oppose au juriste Juan Ginés de Sepúlveda, qui juge les Indiens inférieurs et faits pour obéir. Pour lui, « toutes les nations du monde sont des hommes », doués de raison et libres, et on ne peut les convertir que par la persuasion.&lt;/p&gt; &lt;p&gt;Il soutient que les civilisations amérindiennes valent celles des Grecs et des Romains. Il a d’abord proposé de faire venir des esclaves africains pour soulager les Indiens, mais il l’a regretté et a condamné aussi leur esclavage. Il est vu comme un précurseur des droits de l’homme.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A0L3LUltXjQ</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"VIDEO Bartolomé de Las Casas et La controverse de Valladolid (1992)" par Frédéric ANTOINE</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/lascasas-mini.webp</t>
@@ -7586,6 +7766,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philippe_M%C3%A9lanchthon" title=" Wikipedia"&gt;Philippe MÉLANCHTHON&lt;/a&gt; est un humaniste, théologien et réformateur allemand. Né en 1497 à Bretten, dans le Bade, sous le nom de Philipp Schwartzerdt, « terre noire », il reçoit de son grand-oncle, l’humaniste Reuchlin, le nom grec de Melanchthon, qui a le même sens. Enfant prodige, il devient à 21 ans professeur de grec à l’université de Wittenberg, où il rencontre Luther. Il devient son plus proche collaborateur et le restera jusqu’à la mort de celui-ci. Il meurt à Wittenberg en 1560.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Lieux communs&lt;/em&gt; (1521), il donne le premier exposé systématique de la théologie de la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9forme_protestante" title=" Wikipedia"&gt;Réforme&lt;/a&gt; : le salut vient de la grâce de Dieu, reçue par la foi, et non des œuvres. En 1530, il rédige la &lt;em&gt;Confession d’Augsbourg&lt;/em&gt;, présentée à l’empereur Charles Quint, qui reste aujourd’hui le texte de référence des Églises luthériennes. D’un caractère plus conciliant que Luther, il cherche toute sa vie un accord avec les catholiques et les réformés, ce qui lui vaut de nombreux reproches.&lt;/p&gt; &lt;p&gt;Humaniste, il est convaincu que la foi a besoin des lettres et des sciences. Il réorganise les écoles et les universités allemandes, écrit des manuels de grammaire, de rhétorique, de dialectique, de physique et d’éthique, et réintroduit Aristote dans l’enseignement. Ses contemporains le surnomment le « précepteur de l’Allemagne ». Peu avant sa mort, il note qu’il sera bientôt délivré de la « rage des théologiens ».&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bCLTlxMqMN4</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Philipp Melanchthon : le « Précepteur de l'Allemagne » à la croisée de l'humanisme et de la Réforme" par Richard Dujon</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/melanchthon-mini.webp</t>
@@ -7644,6 +7834,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christian_Thomasius" title=" Wikipedia"&gt;Christian THOMASIUS&lt;/a&gt; est un juriste et philosophe allemand, l’un des pionniers des Lumières allemandes. Né à Leipzig en 1655, fils du philosophe Jakob Thomasius, qui fut le maître de Leibniz, il étudie le droit et découvre l’œuvre de Pufendorf. Professeur à Leipzig, il fait scandale en 1687 en annonçant un cours en allemand, et non en latin comme l’exigeait la tradition. Il lance aussi l’une des premières revues savantes en langue allemande. Chassé de Leipzig en 1690 pour ses idées, il participe à la fondation de l’université de Halle, où il enseigne jusqu’à sa mort en 1728.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Fondements du droit de nature et des gens&lt;/em&gt; (1705), il distingue trois domaines : le juste, qui règle les rapports extérieurs entre les hommes et peut être imposé par la contrainte ; l’honnête, qui concerne la vie intérieure et la vertu ; et le convenable, qui relève de la politesse. Le droit ne doit pas se mêler des consciences : l’État doit garantir la paix extérieure, non imposer la vertu ou la vraie foi. Il défend ainsi la tolérance religieuse et la liberté de penser.&lt;/p&gt; &lt;p&gt;Il mène une campagne célèbre contre les procès de sorcellerie : dans un traité de 1701, il soutient que le pacte avec le diable est une invention et que les aveux obtenus sous la torture n’ont aucune valeur. Il combat aussi la torture elle-même. Son influence contribue à la fin des bûchers en Prusse. Il est l’un des initiateurs des &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt; en Allemagne.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h8bil9ujG1w</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"“Christian Thomasius” – Modern Philosophy, Video 34" par Holy Family Catholic Church</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/thomasius-mini.webp</t>
@@ -7700,6 +7900,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adam_Ferguson" title=" Wikipedia"&gt;Adam FERGUSON&lt;/a&gt; est un philosophe et historien écossais, l’une des figures des Lumières écossaises, avec ses amis Hume et Adam Smith. Né en 1723 dans le Perthshire, dans une région de langue gaélique, il est d’abord aumônier d’un régiment écossais de l’armée britannique. Il enseigne ensuite à l’université d’Édimbourg la philosophie naturelle, puis la philosophie morale, de 1764 à 1785. En 1778, il accompagne une mission britannique chargée de négocier la paix avec les colonies américaines révoltées. Il meurt à St Andrews en 1816, à 92 ans.&lt;/p&gt; &lt;p&gt;Dans son &lt;em&gt;Essai sur l’histoire de la société civile&lt;/em&gt; (1767), il refuse l’idée d’un état de nature où l’homme aurait vécu seul : l’homme a toujours vécu en société, et il faut l’étudier tel qu’il est, par l’observation et l’histoire. Les sociétés passent de l’état sauvage à la barbarie, puis à la civilisation. Les institutions sont souvent « le résultat de l’action des hommes, mais non de leurs desseins » : personne ne les a voulues telles qu’elles sont. Cette idée inspirera, bien plus tard, Hayek.&lt;/p&gt; &lt;p&gt;Il s’inquiète des effets de la société commerciale. La division du travail rend l’économie efficace, mais elle enferme chaque homme dans une tâche étroite et l’abrutit. Quand chacun ne pense plus qu’à ses affaires, la vertu civique s’éteint et le despotisme menace. Marx le citera. On voit souvent en lui l’un des fondateurs de la sociologie.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79A3pidbY7o</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Adam Ferguson: Champion of Traditional Societies｜Philosopher Biography" par VIS PHILO.</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/ferguson-mini.webp</t>
@@ -7756,6 +7966,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/F%C3%A9nelon" title=" Wikipedia"&gt;FÉNELON&lt;/a&gt; de son nom complet François de Salignac de La Mothe-Fénelon, est un prêtre, théologien et écrivain français. Né en 1651 dans le Périgord, dans une famille noble, il dirige d’abord une maison pour les jeunes protestantes converties et publie un &lt;em&gt;Traité de l’éducation des filles&lt;/em&gt; (1687), qui défend leur instruction. En 1689, Louis XIV lui confie l’éducation de son petit-fils, le duc de Bourgogne, héritier du trône. Il devient archevêque de Cambrai en 1695.&lt;/p&gt; &lt;p&gt;Pour son élève, il écrit &lt;em&gt;Les Aventures de Télémaque&lt;/em&gt; (1699), qui racontent les voyages du fils d’Ulysse guidé par la sagesse. Sous ce récit se cache une critique de la monarchie absolue : le bon roi doit servir son peuple, fuir la guerre, le luxe et la flatterie. Le livre fait scandale et Fénelon tombe en disgrâce. Dans une lettre anonyme à Louis XIV, il avait déjà dénoncé les guerres et la misère du royaume. Le &lt;em&gt;Télémaque&lt;/em&gt; devient l’un des livres les plus lus du XVIIIe siècle.&lt;/p&gt; &lt;p&gt;Proche de la mystique Madame Guyon, il défend le « pur amour » : l’âme parfaite aime Dieu pour lui-même, sans souci de sa propre récompense, ni même de son salut. Bossuet l’accuse de quiétisme, une doctrine qui ferait de la vie spirituelle un abandon passif. Après une violente querelle, le pape condamne en 1699 son &lt;em&gt;Explication des maximes des saints&lt;/em&gt;, et Fénelon se soumet. Il meurt à Cambrai en 1715. Il est une figure du &lt;a href="https://fr.wikipedia.org/wiki/Mysticisme" title=" Wikipedia"&gt;mysticisme&lt;/a&gt; chrétien.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m2eoLmJWFYM</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Les grands portraits d’Au cœur de l’Histoire: Le grand Fénelon" par Europe 1</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/fenelon-mini.webp</t>
@@ -7814,6 +8034,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques-B%C3%A9nigne_Bossuet" title=" Wikipedia"&gt;Jacques-Bénigne BOSSUET&lt;/a&gt; est un évêque, prédicateur et écrivain français. Né à Dijon en 1627, dans une famille de magistrats, il étudie la théologie à Paris et devient chanoine à Metz, où il se fait connaître par ses sermons. À Paris, il prêche devant la cour et devient le plus grand orateur sacré de son temps. Ses &lt;em&gt;Oraisons funèbres&lt;/em&gt;, prononcées pour les grands personnages du royaume, sont des chefs-d’œuvre de la prose française. Évêque de Meaux en 1681, on le surnomme « l’Aigle de Meaux ». Il meurt à Paris en 1704.&lt;/p&gt; &lt;p&gt;De 1670 à 1681, il est le précepteur du Dauphin, le fils de Louis XIV, pour qui il écrit ses grands ouvrages. Dans le &lt;em&gt;Discours sur l’histoire universelle&lt;/em&gt; (1681), il montre que la Providence divine conduit l’histoire des empires, qui tous passent, vers le triomphe de l’Église. Dans la &lt;em&gt;Politique tirée des propres paroles de l’Écriture sainte&lt;/em&gt;, il fonde la monarchie absolue sur la Bible : le roi tient son pouvoir de Dieu et n’a de comptes à rendre qu’à lui. Mais un pouvoir absolu n’est pas arbitraire : le roi doit gouverner selon la justice et la raison.&lt;/p&gt; &lt;p&gt;Défenseur de l’unité de l’Église, il combat les protestants dans son &lt;em&gt;Histoire des variations des Églises protestantes&lt;/em&gt; (1688), et approuve la révocation de l’édit de Nantes. Il s’oppose aussi au quiétisme de Fénelon et à la critique biblique de Richard Simon. Nourri de saint Augustin, il s’inscrit dans l’&lt;a href="https://fr.wikipedia.org/wiki/Augustinisme" title=" Wikipedia"&gt;augustinisme&lt;/a&gt; du XVIIe siècle.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fFTm4fzamzg</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Franck Ferrand raconte : Jacques-Bénigne Bossuet (récit intégral)" par Radio Classique</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/bossuet-mini.webp</t>
@@ -7872,6 +8102,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Cesare_Beccaria" title=" Wikipedia"&gt;Cesare BECCARIA&lt;/a&gt; est un juriste, philosophe et économiste italien. Né à Milan en 1738 dans une famille noble, il étudie le droit à Pavie. Il fréquente à Milan un groupe de jeunes réformateurs réunis autour des frères Verri, qui publient la revue &lt;em&gt;Le Café&lt;/em&gt; et diffusent les idées des philosophes français. Encouragé par eux, il publie anonymement en 1764, à 26 ans, un petit livre qui va changer l’histoire du droit pénal : &lt;em&gt;Des délits et des peines&lt;/em&gt;. Il enseigne ensuite l’économie politique à Milan et meurt dans sa ville en 1794.&lt;/p&gt; &lt;p&gt;Il y applique au droit pénal les principes des &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt;. Le but des lois doit être « le plus grand bonheur partagé par le plus grand nombre ». Les délits et les peines doivent être fixés par des lois claires, connues de tous, et non laissés à l’arbitraire des juges. La peine doit être proportionnée au délit et ne servir qu’à empêcher le coupable de nuire de nouveau et à dissuader les autres. Ce qui dissuade, ce n’est pas la cruauté du châtiment, mais la certitude d’être puni.&lt;/p&gt; &lt;p&gt;Il condamne la torture, qui punit avant le jugement et fait avouer l’innocent faible plutôt que le coupable robuste. Il réclame aussi l’abolition de la peine de mort, inutile et nuisible, car elle donne l’exemple de la cruauté. Traduit en français dès 1766 et salué par Voltaire, son livre inspire les réformes de nombreux souverains : le grand-duc de Toscane abolit la peine de mort en 1786. Il est le grand-père de l’écrivain Alessandro Manzoni.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BVpvI6clnQ8</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Cesare Beccaria (1738-1794) : le père du droit pénal moderne" par Richard Dujon</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/beccaria-mini.webp</t>
@@ -7930,6 +8170,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri-Corneille_Agrippa_de_Nettesheim" title=" Wikipedia"&gt;Henri-Corneille AGRIPPA&lt;/a&gt; de Nettesheim est un humaniste, médecin, juriste et occultiste allemand de la Renaissance. Né à Cologne en 1486, il mène une vie d’aventures à travers l’Europe : soldat de l’empereur Maximilien, professeur à Dole, où il commente un traité de kabbale et se fait accuser de judaïser, orateur de la ville de Metz, où il défend une femme accusée de sorcellerie, médecin de la reine mère de France à Lyon, puis historiographe de Marguerite d’Autriche aux Pays-Bas. Souvent pauvre et persécuté, il meurt à Grenoble en 1535.&lt;/p&gt; &lt;p&gt;Son œuvre la plus célèbre, &lt;em&gt;La Philosophie occulte&lt;/em&gt;, écrite dès 1510 et publiée en 1533, est une grande synthèse de la magie de la Renaissance. Le monde y est divisé en trois : le monde élémentaire, le monde céleste des astres et le monde intellectuel des anges et de Dieu. Tout est lié par des correspondances secrètes, et le mage, qui les connaît, peut faire descendre les forces supérieures. Agrippa y mêle l’&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9tisme" title=" Wikipedia"&gt;hermétisme&lt;/a&gt;, le néoplatonisme et la kabbale juive.&lt;/p&gt; &lt;p&gt;Mais dans &lt;em&gt;De l’incertitude et de la vanité des sciences&lt;/em&gt; (1530), il soutient au contraire que toutes les sciences humaines, y compris la magie, sont vaines et incertaines, et que seule la parole de Dieu est sûre. Dans un autre traité, il défend la supériorité du sexe féminin. Ce double visage, celui du mage et celui du sceptique, a beaucoup intrigué ses lecteurs. Sa réputation de magicien, entretenue par ses ennemis, a inspiré la légende de Faust et apparaît encore chez Rabelais, qui le caricature sous les traits de Her Trippa.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gx_uChXHEOY</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Henri-Corneille Agrippa : le mage de la renaissance - Les Sciences Occultes" par Arcana les Mystères du Monde</t>
+        </is>
+      </c>
       <c r="H113" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/agrippa-mini.webp</t>
@@ -7986,6 +8236,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Louis_Viv%C3%A8s" title=" Wikipedia"&gt;Juan Luis VIVES&lt;/a&gt; est un humaniste, philosophe et pédagogue espagnol. Né à Valence en 1493 dans une famille juive convertie au christianisme, il quitte jeune l’Espagne, où l’Inquisition persécutera durement sa famille : son père sera brûlé en 1524. Il étudie à Paris, puis s’installe à Bruges, qui restera sa ville. Ami d’Érasme et de Thomas More, il enseigne à Louvain puis à Oxford, et devient le précepteur de la princesse Marie Tudor. Il meurt à Bruges en 1540.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Éducation de la femme chrétienne&lt;/em&gt; (1523), il défend l’instruction des filles. Dans son traité &lt;em&gt;Du secours aux pauvres&lt;/em&gt; (1526), écrit pour la ville de Bruges, il propose pour la première fois une organisation publique de l’aide aux pauvres : recenser les indigents, donner du travail à ceux qui le peuvent, soigner les malades et instruire les enfants, plutôt que de laisser la charité au hasard des aumônes. Dans &lt;em&gt;Des disciplines&lt;/em&gt; (1531), il critique l’enseignement scolastique de son temps, fait de disputes stériles, et propose une réforme de toutes les sciences fondée sur l’observation et l’utilité.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;De l’âme et de la vie&lt;/em&gt; (1538), il ne cherche pas à savoir ce qu’est l’âme, mais comment elle agit : il étudie la mémoire, l’association des idées et les émotions. On l’a parfois appelé le « père de la psychologie moderne ». Pacifiste, il plaide pour la concorde entre les princes chrétiens. Il est une grande figure de l’&lt;a href="https://fr.wikipedia.org/wiki/Humanisme" title=" Wikipedia"&gt;humanisme&lt;/a&gt; de la Renaissance.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0-5AeGkzmP8</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The life of Juan Luis Vives with Tim Darcy Ellis" par History and Coffee</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/vives-mini.webp</t>
@@ -8042,6 +8302,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Volney" title=" Wikipedia"&gt;VOLNEY&lt;/a&gt; de son vrai nom Constantin-François Chassebœuf, est un philosophe, historien et voyageur français. Né en 1757 dans l’Anjou, il étudie la médecine et l’histoire à Paris, où il fréquente le salon de Madame Helvétius et les derniers philosophes des Lumières. De 1783 à 1785, il voyage en Égypte et en Syrie, et en tire un récit précis, le &lt;em&gt;Voyage en Syrie et en Égypte&lt;/em&gt; (1787), qui servira à Bonaparte lors de son expédition. Député en 1789, emprisonné sous la Terreur, il devient sénateur sous l’Empire et pair de France sous la Restauration. Il meurt à Paris en 1820.&lt;/p&gt; &lt;p&gt;Son livre le plus célèbre, &lt;em&gt;Les Ruines, ou méditation sur les révolutions des empires&lt;/em&gt; (1791), commence par une rêverie devant les ruines de Palmyre. Pourquoi les empires tombent-ils ? Non par la volonté des dieux, mais par l’ignorance, l’égoïsme et le despotisme des hommes. Un génie lui montre ensuite une assemblée de tous les peuples de la terre, dont les prêtres se disputent la vérité : chaque religion prétend être la seule vraie, et toutes sont nées de l’imagination humaine. La paix viendra quand les hommes suivront la seule loi naturelle, que la raison découvre.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;La Loi naturelle&lt;/em&gt; (1793), un catéchisme pour les citoyens, il fonde la morale sur la conservation de soi et l’intérêt bien compris. Proche des Idéologues, il s’intéresse aussi aux langues et propose un alphabet universel. Il prolonge l’esprit critique des &lt;a href="https://fr.wikipedia.org/wiki/Lumi%C3%A8res_%28philosophie%29" title=" Wikipedia"&gt;Lumières&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zod3XXt4yaM</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Volney, un 'idéologue' au service des faits" par Institut Coppet</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/volney-mini.webp</t>
@@ -8096,6 +8366,16 @@
       <c r="E116" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gabriel_Bonnot_de_Mably" title=" Wikipedia"&gt;Gabriel Bonnot de MABLY&lt;/a&gt; est un philosophe, historien et penseur politique français. Né à Grenoble en 1709, frère aîné de Condillac, il entre au séminaire et reçoit le titre d’abbé, mais ne devient jamais prêtre. Il travaille plusieurs années comme conseiller du cardinal de Tencin, alors ministre, et publie un ouvrage sur le droit public de l’Europe. Il quitte ensuite la politique pour se consacrer à l’écriture, vivant modestement à Paris. Il meurt en 1785.&lt;/p&gt; &lt;p&gt;Admirateur de Sparte et de la République romaine, il pense que la politique doit former des citoyens vertueux, dévoués au bien commun, et non seulement enrichir les États. Dans ses &lt;em&gt;Doutes proposés aux philosophes économistes&lt;/em&gt; (1768), il critique les physiocrates, qui font de la propriété et du commerce les fondements de l’ordre social. Pour lui, la propriété privée est la source de l’avarice, de l’ambition et de l’inégalité. Dans &lt;em&gt;De la législation&lt;/em&gt; (1776), il rêve d’une communauté des biens, tout en la jugeant impossible à rétablir : il faut au moins limiter les richesses par les lois.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Des droits et des devoirs du citoyen&lt;/em&gt;, écrit en 1758 et publié en 1789, il appelle à la réunion des États généraux et à une « révolution ménagée » qui limiterait le pouvoir du roi. Consulté par les Polonais et les Américains sur leurs constitutions, il a influencé les révolutionnaires, jusqu’à Babeuf. Il est une figure du &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9publicanisme" title=" Wikipedia"&gt;républicanisme&lt;/a&gt; des Lumières.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7_QITBUPyig</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"HANS-JÜRGEN LÜSEBRINK : '' Mably et la démocratie athénienne ''" par Faculté de philosophie - Université Laval</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
